--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>6536219</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>1.92700004577637</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>2.00600004196167</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>1.93400001525879</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>7399819</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>1.94200003147125</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>1.89400005340576</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>5755429</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>2.00399994850159</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>1.90799999237061</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>1.9099999666214</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>1.99800002574921</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>5057453</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.9559999704361</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.99800002574921</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.97099995613098</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>1817523</v>
+        <v>1530200</v>
       </c>
       <c r="C2715" t="n">
-        <v>2.19799995422363</v>
+        <v>2.18799996376038</v>
       </c>
       <c r="D2715" t="n">
         <v>2.16400003433228</v>
       </c>
       <c r="E2715" t="n">
-        <v>2.17400002479553</v>
+        <v>2.17000007629395</v>
       </c>
       <c r="F2715" t="n">
-        <v>2.18600010871887</v>
+        <v>2.17199993133545</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>26592149</v>
+        <v>1817523</v>
       </c>
       <c r="C2716" t="n">
-        <v>2.13199996948242</v>
+        <v>2.19799995422363</v>
       </c>
       <c r="D2716" t="n">
-        <v>1.98599994182587</v>
+        <v>2.16400003433228</v>
       </c>
       <c r="E2716" t="n">
-        <v>2.13199996948242</v>
+        <v>2.17400002479553</v>
       </c>
       <c r="F2716" t="n">
-        <v>2.01200008392334</v>
+        <v>2.18600010871887</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>8861909</v>
+        <v>26592149</v>
       </c>
       <c r="C2717" t="n">
-        <v>2.09800004959106</v>
+        <v>2.13199996948242</v>
       </c>
       <c r="D2717" t="n">
-        <v>2.00799989700317</v>
+        <v>1.98599994182587</v>
       </c>
       <c r="E2717" t="n">
+        <v>2.13199996948242</v>
+      </c>
+      <c r="F2717" t="n">
         <v>2.01200008392334</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>2.08400011062622</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>6804157</v>
+        <v>8861909</v>
       </c>
       <c r="C2718" t="n">
-        <v>2.10999989509583</v>
+        <v>2.09800004959106</v>
       </c>
       <c r="D2718" t="n">
-        <v>2.01399993896484</v>
+        <v>2.00799989700317</v>
       </c>
       <c r="E2718" t="n">
-        <v>2.09599995613098</v>
+        <v>2.01200008392334</v>
       </c>
       <c r="F2718" t="n">
-        <v>2.01399993896484</v>
+        <v>2.08400011062622</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>6536219</v>
+        <v>6804157</v>
       </c>
       <c r="C2719" t="n">
-        <v>2.01999998092651</v>
+        <v>2.10999989509583</v>
       </c>
       <c r="D2719" t="n">
-        <v>1.92700004577637</v>
+        <v>2.01399993896484</v>
       </c>
       <c r="E2719" t="n">
-        <v>2.00600004196167</v>
+        <v>2.09599995613098</v>
       </c>
       <c r="F2719" t="n">
-        <v>1.93400001525879</v>
+        <v>2.01399993896484</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>7399819</v>
+        <v>6536219</v>
       </c>
       <c r="C2720" t="n">
-        <v>1.94200003147125</v>
+        <v>2.01999998092651</v>
       </c>
       <c r="D2720" t="n">
-        <v>1.86000001430511</v>
+        <v>1.92700004577637</v>
       </c>
       <c r="E2720" t="n">
-        <v>1.94000005722046</v>
+        <v>2.00600004196167</v>
       </c>
       <c r="F2720" t="n">
-        <v>1.89400005340576</v>
+        <v>1.93400001525879</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>5755429</v>
+        <v>7399819</v>
       </c>
       <c r="C2721" t="n">
-        <v>2.00399994850159</v>
+        <v>1.94200003147125</v>
       </c>
       <c r="D2721" t="n">
-        <v>1.90799999237061</v>
+        <v>1.86000001430511</v>
       </c>
       <c r="E2721" t="n">
-        <v>1.9099999666214</v>
+        <v>1.94000005722046</v>
       </c>
       <c r="F2721" t="n">
-        <v>1.99800002574921</v>
+        <v>1.89400005340576</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>5057453</v>
+        <v>5755429</v>
       </c>
       <c r="C2722" t="n">
-        <v>2.01999998092651</v>
+        <v>2.00399994850159</v>
       </c>
       <c r="D2722" t="n">
-        <v>1.9559999704361</v>
+        <v>1.90799999237061</v>
       </c>
       <c r="E2722" t="n">
+        <v>1.9099999666214</v>
+      </c>
+      <c r="F2722" t="n">
         <v>1.99800002574921</v>
       </c>
-      <c r="F2722" t="n">
-        <v>1.97099995613098</v>
-      </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>5062470</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>1.99699997901917</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>1.91100001335144</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>1.9650000333786</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>1.93099999427795</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -473,7 +473,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G4" t="n">
-        <v>2.87366652488708</v>
+        <v>2.87366676330566</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78541326522827</v>
+        <v>2.78541302680969</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76218795776367</v>
+        <v>2.76218867301941</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G9" t="n">
-        <v>2.75289821624756</v>
+        <v>2.75289845466614</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75289821624756</v>
+        <v>2.75289845466614</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G11" t="n">
-        <v>2.69251394271851</v>
+        <v>2.69251418113708</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G12" t="n">
-        <v>2.61045360565186</v>
+        <v>2.61045408248901</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66464471817017</v>
+        <v>2.66464447975159</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G14" t="n">
-        <v>2.58877754211426</v>
+        <v>2.58877730369568</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G15" t="n">
-        <v>2.65690279006958</v>
+        <v>2.65690326690674</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G17" t="n">
-        <v>2.70180439949036</v>
+        <v>2.70180416107178</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7265772819519</v>
+        <v>2.72657775878906</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2.70954585075378</v>
+        <v>2.70954561233521</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G21" t="n">
-        <v>2.76993012428284</v>
+        <v>2.7699294090271</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G22" t="n">
-        <v>2.74205994606018</v>
+        <v>2.74206018447876</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63213038444519</v>
+        <v>2.63213062286377</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G24" t="n">
-        <v>2.55006980895996</v>
+        <v>2.5500693321228</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G26" t="n">
-        <v>2.55316662788391</v>
+        <v>2.55316615104675</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G27" t="n">
-        <v>2.43859171867371</v>
+        <v>2.43859124183655</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.39988303184509</v>
+        <v>2.39988350868225</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G29" t="n">
-        <v>2.47884726524353</v>
+        <v>2.47884750366211</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G30" t="n">
-        <v>2.27292156219482</v>
+        <v>2.2729218006134</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G31" t="n">
-        <v>2.31472611427307</v>
+        <v>2.31472635269165</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G32" t="n">
-        <v>2.413818359375</v>
+        <v>2.41381859779358</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G35" t="n">
-        <v>2.59342217445374</v>
+        <v>2.59342241287231</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G36" t="n">
-        <v>2.5376832485199</v>
+        <v>2.53768301010132</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G37" t="n">
-        <v>2.62438869476318</v>
+        <v>2.6243884563446</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G38" t="n">
-        <v>2.6398720741272</v>
+        <v>2.63987183570862</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G40" t="n">
-        <v>2.62129187583923</v>
+        <v>2.62129211425781</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G41" t="n">
-        <v>2.73122215270996</v>
+        <v>2.73122191429138</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>2.84115195274353</v>
+        <v>2.84115219116211</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G44" t="n">
-        <v>2.85199022293091</v>
+        <v>2.85199046134949</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G45" t="n">
-        <v>2.86747336387634</v>
+        <v>2.8674738407135</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87366652488708</v>
+        <v>2.87366676330566</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.80244421958923</v>
+        <v>2.80244398117065</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G51" t="n">
-        <v>2.83341073989868</v>
+        <v>2.83341097831726</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G52" t="n">
-        <v>2.88914966583252</v>
+        <v>2.8891499042511</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89069819450378</v>
+        <v>2.89069843292236</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>2.85199022293091</v>
+        <v>2.85199046134949</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G56" t="n">
-        <v>2.78076791763306</v>
+        <v>2.78076839447021</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G57" t="n">
-        <v>2.85199022293091</v>
+        <v>2.85199046134949</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G58" t="n">
-        <v>2.86592483520508</v>
+        <v>2.86592507362366</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G59" t="n">
-        <v>2.86127996444702</v>
+        <v>2.8612802028656</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G60" t="n">
-        <v>2.78696131706238</v>
+        <v>2.7869610786438</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.73277020454407</v>
+        <v>2.73277044296265</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G63" t="n">
-        <v>2.87521529197693</v>
+        <v>2.87521481513977</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.70954585075378</v>
+        <v>2.70954561233521</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G67" t="n">
-        <v>2.71109414100647</v>
+        <v>2.71109390258789</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G68" t="n">
-        <v>2.7265772819519</v>
+        <v>2.72657775878906</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G69" t="n">
-        <v>2.76993012428284</v>
+        <v>2.7699294090271</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G70" t="n">
-        <v>2.82412075996399</v>
+        <v>2.82412099838257</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80244421958923</v>
+        <v>2.80244398117065</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G73" t="n">
-        <v>2.89379501342773</v>
+        <v>2.89379453659058</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>2.84115195274353</v>
+        <v>2.84115219116211</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G75" t="n">
-        <v>2.84424877166748</v>
+        <v>2.84424901008606</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G77" t="n">
-        <v>2.88605284690857</v>
+        <v>2.88605308532715</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G79" t="n">
-        <v>2.87521529197693</v>
+        <v>2.87521481513977</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G80" t="n">
-        <v>2.85353875160217</v>
+        <v>2.85353899002075</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G81" t="n">
-        <v>2.85199022293091</v>
+        <v>2.85199046134949</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G84" t="n">
-        <v>2.95882439613342</v>
+        <v>2.95882368087769</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G85" t="n">
-        <v>2.98979020118713</v>
+        <v>2.98979043960571</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G86" t="n">
-        <v>2.93250226974487</v>
+        <v>2.93250274658203</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G87" t="n">
-        <v>2.9185676574707</v>
+        <v>2.91856813430786</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G88" t="n">
-        <v>2.87366652488708</v>
+        <v>2.87366676330566</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G89" t="n">
-        <v>2.839604139328</v>
+        <v>2.83960366249084</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>2.80244421958923</v>
+        <v>2.80244398117065</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88605284690857</v>
+        <v>2.88605308532715</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G98" t="n">
-        <v>2.84115195274353</v>
+        <v>2.84115219116211</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G99" t="n">
-        <v>2.84579706192017</v>
+        <v>2.84579753875732</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.48107194900513</v>
+        <v>2.48107147216797</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G104" t="n">
-        <v>2.4732449054718</v>
+        <v>2.47324538230896</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>2.41845798492432</v>
+        <v>2.41845774650574</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G108" t="n">
-        <v>2.38715076446533</v>
+        <v>2.38715100288391</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G110" t="n">
-        <v>2.40750026702881</v>
+        <v>2.40750074386597</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G111" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G112" t="n">
-        <v>2.44663429260254</v>
+        <v>2.44663405418396</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G116" t="n">
-        <v>2.18052554130554</v>
+        <v>2.18052577972412</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>2.14452290534973</v>
+        <v>2.14452242851257</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G120" t="n">
-        <v>2.22748589515686</v>
+        <v>2.22748565673828</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G122" t="n">
-        <v>2.21026659011841</v>
+        <v>2.21026706695557</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G129" t="n">
-        <v>2.15078377723694</v>
+        <v>2.15078401565552</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>2.0036416053772</v>
+        <v>2.00364136695862</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.11321544647217</v>
+        <v>2.11321592330933</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G136" t="n">
-        <v>2.21652841567993</v>
+        <v>2.21652817726135</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G137" t="n">
-        <v>2.16487240791321</v>
+        <v>2.16487216949463</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G138" t="n">
-        <v>2.21026659011841</v>
+        <v>2.21026706695557</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G139" t="n">
-        <v>2.18678689002991</v>
+        <v>2.18678665161133</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G140" t="n">
-        <v>2.18991756439209</v>
+        <v>2.18991780281067</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G141" t="n">
-        <v>2.17426419258118</v>
+        <v>2.1742639541626</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G142" t="n">
-        <v>2.14608812332153</v>
+        <v>2.14608788490295</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G146" t="n">
-        <v>2.14921879768372</v>
+        <v>2.14921855926514</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G149" t="n">
-        <v>2.11791157722473</v>
+        <v>2.11791181564331</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G150" t="n">
-        <v>2.06782054901123</v>
+        <v>2.06782078742981</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>1.94885468482971</v>
+        <v>1.94885432720184</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>1.94102764129639</v>
+        <v>1.94102787971497</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G154" t="n">
-        <v>1.96137702465057</v>
+        <v>1.96137726306915</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G155" t="n">
-        <v>2.01146841049194</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G156" t="n">
-        <v>2.00207614898682</v>
+        <v>2.0020763874054</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>1.99581456184387</v>
+        <v>1.99581491947174</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G160" t="n">
-        <v>2.08347392082214</v>
+        <v>2.08347415924072</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G161" t="n">
-        <v>2.05216717720032</v>
+        <v>2.0521674156189</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.11321544647217</v>
+        <v>2.11321592330933</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>2.07408261299133</v>
+        <v>2.07408213615417</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G169" t="n">
-        <v>2.11947703361511</v>
+        <v>2.11947655677795</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G171" t="n">
-        <v>2.1570451259613</v>
+        <v>2.15704536437988</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.13669562339783</v>
+        <v>2.13669586181641</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>2.16017603874207</v>
+        <v>2.16017580032349</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G174" t="n">
-        <v>2.14452290534973</v>
+        <v>2.14452242851257</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G175" t="n">
-        <v>2.14608812332153</v>
+        <v>2.14608788490295</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G178" t="n">
-        <v>2.15078377723694</v>
+        <v>2.15078401565552</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>2.01146841049194</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G181" t="n">
-        <v>2.00207614898682</v>
+        <v>2.0020763874054</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G182" t="n">
-        <v>1.98955368995667</v>
+        <v>1.98955357074738</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G184" t="n">
-        <v>1.99424946308136</v>
+        <v>1.99424970149994</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G185" t="n">
-        <v>1.92850482463837</v>
+        <v>1.92850506305695</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>1.98798811435699</v>
+        <v>1.98798775672913</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G189" t="n">
-        <v>1.91754746437073</v>
+        <v>1.91754734516144</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G191" t="n">
-        <v>2.05529761314392</v>
+        <v>2.0552978515625</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G192" t="n">
-        <v>1.99268424510956</v>
+        <v>1.99268412590027</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G193" t="n">
-        <v>2.00677180290222</v>
+        <v>2.00677227973938</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G194" t="n">
-        <v>1.9535505771637</v>
+        <v>1.95355045795441</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G195" t="n">
-        <v>1.94885468482971</v>
+        <v>1.94885432720184</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G201" t="n">
-        <v>1.9332013130188</v>
+        <v>1.93320083618164</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G202" t="n">
-        <v>1.9332013130188</v>
+        <v>1.93320083618164</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96450757980347</v>
+        <v>1.96450781822205</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G205" t="n">
-        <v>2.00207614898682</v>
+        <v>2.0020763874054</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>2.08973574638367</v>
+        <v>2.08973550796509</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G208" t="n">
-        <v>2.0819091796875</v>
+        <v>2.08190894126892</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G209" t="n">
-        <v>2.1038236618042</v>
+        <v>2.10382342338562</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G210" t="n">
-        <v>2.08660459518433</v>
+        <v>2.08660507202148</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>2.08973574638367</v>
+        <v>2.08973550796509</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G212" t="n">
-        <v>2.03338313102722</v>
+        <v>2.0333833694458</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>1.98798811435699</v>
+        <v>1.98798775672913</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G215" t="n">
-        <v>1.96137702465057</v>
+        <v>1.96137726306915</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G216" t="n">
-        <v>1.93163573741913</v>
+        <v>1.93163549900055</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G217" t="n">
-        <v>1.91128623485565</v>
+        <v>1.91128635406494</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89563250541687</v>
+        <v>1.89563286304474</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G219" t="n">
-        <v>1.93163573741913</v>
+        <v>1.93163549900055</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G220" t="n">
-        <v>1.91128623485565</v>
+        <v>1.91128635406494</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G222" t="n">
-        <v>2.08816981315613</v>
+        <v>2.08817005157471</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G226" t="n">
-        <v>2.08816981315613</v>
+        <v>2.08817005157471</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G227" t="n">
-        <v>2.08660459518433</v>
+        <v>2.08660507202148</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.57200002670288</v>
       </c>
       <c r="G228" t="n">
-        <v>2.01303339004517</v>
+        <v>2.01303362846375</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G229" t="n">
-        <v>1.99581456184387</v>
+        <v>1.99581491947174</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G230" t="n">
-        <v>2.01146841049194</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G231" t="n">
-        <v>2.01146841049194</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>1.99581456184387</v>
+        <v>1.99581491947174</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G233" t="n">
-        <v>1.98955368995667</v>
+        <v>1.98955357074738</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G242" t="n">
-        <v>2.26192331314087</v>
+        <v>2.26192355155945</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G244" t="n">
-        <v>2.26192331314087</v>
+        <v>2.26192355155945</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G250" t="n">
-        <v>2.38088965415955</v>
+        <v>2.38088989257812</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G252" t="n">
-        <v>2.4200234413147</v>
+        <v>2.42002320289612</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>2.36367082595825</v>
+        <v>2.36367106437683</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32923316955566</v>
+        <v>2.32923340797424</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G260" t="n">
-        <v>2.48576807975769</v>
+        <v>2.48576760292053</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G262" t="n">
-        <v>2.4935941696167</v>
+        <v>2.49359440803528</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G265" t="n">
-        <v>2.48576807975769</v>
+        <v>2.48576760292053</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.44976496696472</v>
+        <v>2.4497652053833</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.1159999370575</v>
       </c>
       <c r="G268" t="n">
-        <v>2.43880748748779</v>
+        <v>2.43880724906921</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G269" t="n">
-        <v>2.41376209259033</v>
+        <v>2.41376185417175</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G272" t="n">
-        <v>2.40280437469482</v>
+        <v>2.4028046131134</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G273" t="n">
-        <v>2.38402056694031</v>
+        <v>2.38402032852173</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G274" t="n">
-        <v>2.41376209259033</v>
+        <v>2.41376185417175</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G277" t="n">
-        <v>2.33862543106079</v>
+        <v>2.33862495422363</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.30888414382935</v>
+        <v>2.30888342857361</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>2.23061656951904</v>
+        <v>2.23061609268188</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G286" t="n">
-        <v>2.31827545166016</v>
+        <v>2.31827592849731</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G287" t="n">
-        <v>2.33862543106079</v>
+        <v>2.33862495422363</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G288" t="n">
-        <v>2.39341259002686</v>
+        <v>2.39341235160828</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G290" t="n">
-        <v>2.4200234413147</v>
+        <v>2.42002320289612</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G291" t="n">
-        <v>2.40436983108521</v>
+        <v>2.40436959266663</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G292" t="n">
-        <v>2.36993217468262</v>
+        <v>2.3699324131012</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G294" t="n">
-        <v>2.33862543106079</v>
+        <v>2.33862495422363</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>2.35584402084351</v>
+        <v>2.35584425926208</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G296" t="n">
-        <v>2.33705997467041</v>
+        <v>2.33705973625183</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G297" t="n">
-        <v>2.45289516448975</v>
+        <v>2.45289540290833</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G298" t="n">
-        <v>2.44819951057434</v>
+        <v>2.44819927215576</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G299" t="n">
-        <v>2.48107194900513</v>
+        <v>2.48107147216797</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G300" t="n">
-        <v>2.53429341316223</v>
+        <v>2.53429317474365</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G301" t="n">
-        <v>2.54525113105774</v>
+        <v>2.54525065422058</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="n">
-        <v>2.50455212593079</v>
+        <v>2.50455164909363</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>2.50455212593079</v>
+        <v>2.50455164909363</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G305" t="n">
-        <v>2.51707458496094</v>
+        <v>2.51707482337952</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G306" t="n">
-        <v>2.4935941696167</v>
+        <v>2.49359440803528</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G307" t="n">
-        <v>2.49202919006348</v>
+        <v>2.4920289516449</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G310" t="n">
-        <v>2.48889851570129</v>
+        <v>2.48889875411987</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G311" t="n">
-        <v>2.57342720031738</v>
+        <v>2.5734269618988</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G312" t="n">
-        <v>2.48733329772949</v>
+        <v>2.48733305931091</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G313" t="n">
-        <v>2.46541881561279</v>
+        <v>2.46541833877563</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G314" t="n">
-        <v>2.45132994651794</v>
+        <v>2.45133018493652</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G315" t="n">
-        <v>2.44663429260254</v>
+        <v>2.44663405418396</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G316" t="n">
-        <v>2.48263692855835</v>
+        <v>2.48263669013977</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.50455212593079</v>
+        <v>2.50455164909363</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G318" t="n">
-        <v>2.45446085929871</v>
+        <v>2.45446109771729</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G319" t="n">
-        <v>2.4935941696167</v>
+        <v>2.49359440803528</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G321" t="n">
-        <v>2.44193768501282</v>
+        <v>2.4419379234314</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G322" t="n">
-        <v>2.44193768501282</v>
+        <v>2.4419379234314</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G323" t="n">
-        <v>2.40280437469482</v>
+        <v>2.4028046131134</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G324" t="n">
-        <v>2.37619376182556</v>
+        <v>2.37619352340698</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G326" t="n">
-        <v>2.44506907463074</v>
+        <v>2.44506883621216</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.46541881561279</v>
+        <v>2.46541833877563</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.4732449054718</v>
+        <v>2.47324538230896</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>2.36836671829224</v>
+        <v>2.36836695671082</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G332" t="n">
-        <v>2.29792618751526</v>
+        <v>2.29792642593384</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G333" t="n">
-        <v>2.38715076446533</v>
+        <v>2.38715100288391</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G334" t="n">
-        <v>2.41532731056213</v>
+        <v>2.41532683372498</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G337" t="n">
-        <v>2.40750026702881</v>
+        <v>2.40750074386597</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>2.44976496696472</v>
+        <v>2.4497652053833</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G340" t="n">
-        <v>2.44506907463074</v>
+        <v>2.44506883621216</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G342" t="n">
-        <v>2.49046349525452</v>
+        <v>2.49046397209167</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G343" t="n">
-        <v>2.53272795677185</v>
+        <v>2.53272819519043</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G344" t="n">
-        <v>2.55151224136353</v>
+        <v>2.5515124797821</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G345" t="n">
-        <v>2.53742408752441</v>
+        <v>2.53742432594299</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>2.62195253372192</v>
+        <v>2.6219527721405</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>2.62195253372192</v>
+        <v>2.6219527721405</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G350" t="n">
-        <v>2.64543271064758</v>
+        <v>2.64543318748474</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.14599990844727</v>
       </c>
       <c r="G354" t="n">
-        <v>2.46228766441345</v>
+        <v>2.46228742599487</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G355" t="n">
-        <v>2.52040147781372</v>
+        <v>2.52040195465088</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G356" t="n">
-        <v>2.53791522979736</v>
+        <v>2.53791546821594</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>2.55542945861816</v>
+        <v>2.55542969703674</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G360" t="n">
-        <v>2.56020593643188</v>
+        <v>2.56020569801331</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>2.52358627319336</v>
+        <v>2.52358603477478</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G363" t="n">
-        <v>2.54269218444824</v>
+        <v>2.54269194602966</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.23399996757507</v>
       </c>
       <c r="G364" t="n">
-        <v>2.57453536987305</v>
+        <v>2.57453513145447</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G365" t="n">
-        <v>2.56816673278809</v>
+        <v>2.56816649436951</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G366" t="n">
-        <v>2.5522449016571</v>
+        <v>2.55224514007568</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G368" t="n">
-        <v>2.45830702781677</v>
+        <v>2.45830726623535</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>2.42009520530701</v>
+        <v>2.42009496688843</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G373" t="n">
-        <v>2.45193862915039</v>
+        <v>2.45193815231323</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G374" t="n">
-        <v>2.46785998344421</v>
+        <v>2.46786022186279</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G375" t="n">
-        <v>2.43124008178711</v>
+        <v>2.43124032020569</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G376" t="n">
-        <v>2.41531896591187</v>
+        <v>2.41531825065613</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G377" t="n">
-        <v>2.41531896591187</v>
+        <v>2.41531825065613</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>2.40417337417603</v>
+        <v>2.40417313575745</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G380" t="n">
-        <v>2.44397735595703</v>
+        <v>2.44397759437561</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G383" t="n">
-        <v>2.39780497550964</v>
+        <v>2.39780473709106</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.42805576324463</v>
+        <v>2.42805600166321</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G386" t="n">
-        <v>2.38984417915344</v>
+        <v>2.38984370231628</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>2.37232971191406</v>
+        <v>2.37233018875122</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G389" t="n">
-        <v>2.42646408081055</v>
+        <v>2.42646384239197</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G391" t="n">
-        <v>2.38188314437866</v>
+        <v>2.38188338279724</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G392" t="n">
-        <v>2.44716143608093</v>
+        <v>2.44716191291809</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G393" t="n">
-        <v>2.50129556655884</v>
+        <v>2.50129580497742</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G395" t="n">
-        <v>2.51084876060486</v>
+        <v>2.51084899902344</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G397" t="n">
-        <v>2.49492692947388</v>
+        <v>2.4949266910553</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G399" t="n">
-        <v>2.42805576324463</v>
+        <v>2.42805600166321</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G400" t="n">
-        <v>2.42805576324463</v>
+        <v>2.42805600166321</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>2.45193862915039</v>
+        <v>2.45193815231323</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G402" t="n">
-        <v>2.46626806259155</v>
+        <v>2.46626782417297</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>2.39621233940125</v>
+        <v>2.3962128162384</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G404" t="n">
-        <v>2.3675537109375</v>
+        <v>2.36755394935608</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G405" t="n">
-        <v>2.36596083641052</v>
+        <v>2.36596155166626</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G406" t="n">
-        <v>2.3675537109375</v>
+        <v>2.36755394935608</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G407" t="n">
-        <v>2.35481643676758</v>
+        <v>2.354816198349</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G408" t="n">
-        <v>2.36436915397644</v>
+        <v>2.36436891555786</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3</v>
       </c>
       <c r="G409" t="n">
-        <v>2.38825154304504</v>
+        <v>2.38825130462646</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G410" t="n">
-        <v>2.36436915397644</v>
+        <v>2.36436891555786</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G413" t="n">
-        <v>2.27679991722107</v>
+        <v>2.27680015563965</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G415" t="n">
-        <v>2.30068254470825</v>
+        <v>2.30068278312683</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G418" t="n">
-        <v>2.28157663345337</v>
+        <v>2.28157687187195</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G420" t="n">
-        <v>2.29431343078613</v>
+        <v>2.29431366920471</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G422" t="n">
-        <v>2.33411836624146</v>
+        <v>2.3341178894043</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G423" t="n">
-        <v>2.3484480381012</v>
+        <v>2.34844756126404</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="n">
-        <v>2.30864357948303</v>
+        <v>2.30864334106445</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G426" t="n">
-        <v>2.3484480381012</v>
+        <v>2.34844756126404</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G427" t="n">
-        <v>2.3484480381012</v>
+        <v>2.34844756126404</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G429" t="n">
-        <v>2.40258097648621</v>
+        <v>2.40258121490479</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43920087814331</v>
+        <v>2.43920111656189</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G432" t="n">
-        <v>2.46785998344421</v>
+        <v>2.46786022186279</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G437" t="n">
-        <v>2.59682583808899</v>
+        <v>2.59682536125183</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G439" t="n">
-        <v>2.55065274238586</v>
+        <v>2.55065298080444</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G440" t="n">
-        <v>2.58568072319031</v>
+        <v>2.58568048477173</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G441" t="n">
-        <v>2.58568072319031</v>
+        <v>2.58568048477173</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G443" t="n">
-        <v>2.56498217582703</v>
+        <v>2.56498241424561</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G444" t="n">
-        <v>2.60001015663147</v>
+        <v>2.60000991821289</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61433982849121</v>
+        <v>2.61433935165405</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G446" t="n">
-        <v>2.60001015663147</v>
+        <v>2.60000991821289</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>2.61911582946777</v>
+        <v>2.61911606788635</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G453" t="n">
-        <v>2.59204912185669</v>
+        <v>2.59204936027527</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G454" t="n">
-        <v>2.56020593643188</v>
+        <v>2.56020569801331</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G455" t="n">
-        <v>2.57612752914429</v>
+        <v>2.57612776756287</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G456" t="n">
-        <v>2.63822174072266</v>
+        <v>2.63822197914124</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G457" t="n">
-        <v>2.73056793212891</v>
+        <v>2.73056769371033</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G458" t="n">
-        <v>2.7050929069519</v>
+        <v>2.70509314537048</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G459" t="n">
-        <v>2.73852872848511</v>
+        <v>2.73852896690369</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G460" t="n">
-        <v>2.72419905662537</v>
+        <v>2.72419929504395</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G461" t="n">
-        <v>2.74012112617493</v>
+        <v>2.74012064933777</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G462" t="n">
-        <v>2.7050929069519</v>
+        <v>2.70509314537048</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G464" t="n">
-        <v>2.74330544471741</v>
+        <v>2.74330520629883</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G465" t="n">
-        <v>2.79903101921082</v>
+        <v>2.79903125762939</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G466" t="n">
-        <v>2.8022153377533</v>
+        <v>2.80221557617188</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G471" t="n">
-        <v>2.94073414802551</v>
+        <v>2.94073390960693</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G472" t="n">
-        <v>2.92640447616577</v>
+        <v>2.92640471458435</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>2.93754935264587</v>
+        <v>2.93754982948303</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G476" t="n">
-        <v>2.90252208709717</v>
+        <v>2.90252161026001</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G478" t="n">
-        <v>2.81017589569092</v>
+        <v>2.81017637252808</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G482" t="n">
-        <v>2.49492692947388</v>
+        <v>2.4949266910553</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49174284934998</v>
+        <v>2.4917426109314</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>2.46785998344421</v>
+        <v>2.46786022186279</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G485" t="n">
-        <v>2.46785998344421</v>
+        <v>2.46786022186279</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G486" t="n">
-        <v>2.48537397384644</v>
+        <v>2.48537421226501</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G488" t="n">
-        <v>2.44238543510437</v>
+        <v>2.44238567352295</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G489" t="n">
-        <v>2.46785998344421</v>
+        <v>2.46786022186279</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G491" t="n">
-        <v>2.44716143608093</v>
+        <v>2.44716191291809</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G492" t="n">
-        <v>2.44716143608093</v>
+        <v>2.44716191291809</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G494" t="n">
-        <v>2.51721739768982</v>
+        <v>2.51721715927124</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G495" t="n">
-        <v>2.53632307052612</v>
+        <v>2.5363233089447</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>2.48378133773804</v>
+        <v>2.4837818145752</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G498" t="n">
-        <v>2.52199363708496</v>
+        <v>2.52199387550354</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G499" t="n">
-        <v>2.52040147781372</v>
+        <v>2.52040195465088</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G500" t="n">
-        <v>2.53473091125488</v>
+        <v>2.53473114967346</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G502" t="n">
-        <v>2.55383729934692</v>
+        <v>2.55383706092834</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>2.50766468048096</v>
+        <v>2.50766444206238</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G505" t="n">
-        <v>2.51562523841858</v>
+        <v>2.51562571525574</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G507" t="n">
-        <v>2.56975889205933</v>
+        <v>2.56975865364075</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G508" t="n">
-        <v>2.51084876060486</v>
+        <v>2.51084899902344</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G513" t="n">
-        <v>2.59841799736023</v>
+        <v>2.59841775894165</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G514" t="n">
-        <v>2.62707686424255</v>
+        <v>2.62707662582397</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G515" t="n">
-        <v>2.65892028808594</v>
+        <v>2.65892004966736</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G519" t="n">
-        <v>2.74012112617493</v>
+        <v>2.74012064933777</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G521" t="n">
-        <v>2.67643427848816</v>
+        <v>2.67643404006958</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G522" t="n">
-        <v>2.63822174072266</v>
+        <v>2.63822197914124</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G523" t="n">
-        <v>2.63503789901733</v>
+        <v>2.63503766059875</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G524" t="n">
-        <v>2.63663005828857</v>
+        <v>2.63662981987</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G525" t="n">
-        <v>2.61911582946777</v>
+        <v>2.61911606788635</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G527" t="n">
-        <v>2.62070822715759</v>
+        <v>2.62070846557617</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G529" t="n">
-        <v>2.56816673278809</v>
+        <v>2.56816649436951</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G531" t="n">
-        <v>2.56816673278809</v>
+        <v>2.56816649436951</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>2.23699569702148</v>
+        <v>2.23699593544006</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G538" t="n">
-        <v>2.21311283111572</v>
+        <v>2.21311330795288</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G539" t="n">
-        <v>2.12872815132141</v>
+        <v>2.12872838973999</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G540" t="n">
-        <v>2.07618689537048</v>
+        <v>2.0761866569519</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G542" t="n">
-        <v>2.01409220695496</v>
+        <v>2.01409244537354</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G548" t="n">
-        <v>2.10643792152405</v>
+        <v>2.10643768310547</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.09370112419128</v>
+        <v>2.09370088577271</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G550" t="n">
-        <v>2.04593563079834</v>
+        <v>2.04593539237976</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G551" t="n">
-        <v>2.01727652549744</v>
+        <v>2.01727628707886</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G552" t="n">
-        <v>2.00294756889343</v>
+        <v>2.00294733047485</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G554" t="n">
-        <v>1.94881331920624</v>
+        <v>1.94881367683411</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90741682052612</v>
+        <v>1.90741693973541</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G556" t="n">
-        <v>1.89786410331726</v>
+        <v>1.89786398410797</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>2.00613164901733</v>
+        <v>2.00613141059875</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G559" t="n">
-        <v>2.0316059589386</v>
+        <v>2.03160619735718</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G562" t="n">
-        <v>1.91856217384338</v>
+        <v>1.91856229305267</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G563" t="n">
-        <v>1.80870306491852</v>
+        <v>1.80870294570923</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G565" t="n">
-        <v>2.05071210861206</v>
+        <v>2.05071187019348</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G566" t="n">
-        <v>2.01886892318726</v>
+        <v>2.01886868476868</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G567" t="n">
-        <v>1.99976289272308</v>
+        <v>1.99976313114166</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G568" t="n">
-        <v>1.93766856193542</v>
+        <v>1.93766820430756</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94562935829163</v>
+        <v>1.94562911987305</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G571" t="n">
-        <v>1.88990342617035</v>
+        <v>1.88990330696106</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91219353675842</v>
+        <v>1.91219341754913</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G574" t="n">
-        <v>1.91856217384338</v>
+        <v>1.91856229305267</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G576" t="n">
-        <v>1.90582513809204</v>
+        <v>1.90582501888275</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>1.90264070034027</v>
+        <v>1.90264058113098</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G583" t="n">
-        <v>1.89627182483673</v>
+        <v>1.89627194404602</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G584" t="n">
-        <v>1.88194227218628</v>
+        <v>1.88194251060486</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>1.8309930562973</v>
+        <v>1.83099317550659</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G589" t="n">
-        <v>1.81507110595703</v>
+        <v>1.81507122516632</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G590" t="n">
-        <v>1.81507110595703</v>
+        <v>1.81507122516632</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G591" t="n">
-        <v>1.80392634868622</v>
+        <v>1.80392611026764</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G593" t="n">
-        <v>1.78004360198975</v>
+        <v>1.78004395961761</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G594" t="n">
-        <v>1.88990342617035</v>
+        <v>1.88990330696106</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G598" t="n">
-        <v>1.87238943576813</v>
+        <v>1.87238907814026</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G599" t="n">
-        <v>1.85169112682343</v>
+        <v>1.851691365242</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G600" t="n">
-        <v>1.87238943576813</v>
+        <v>1.87238907814026</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G601" t="n">
-        <v>1.82621645927429</v>
+        <v>1.82621657848358</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G603" t="n">
-        <v>1.88353431224823</v>
+        <v>1.88353455066681</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G605" t="n">
-        <v>1.81825566291809</v>
+        <v>1.81825542449951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G606" t="n">
-        <v>1.80074179172516</v>
+        <v>1.80074214935303</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.77526700496674</v>
+        <v>1.77526712417603</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>1.81848669052124</v>
+        <v>1.81848680973053</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G611" t="n">
-        <v>1.82174837589264</v>
+        <v>1.82174825668335</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G612" t="n">
-        <v>1.78423738479614</v>
+        <v>1.78423714637756</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>1.72878539562225</v>
+        <v>1.72878551483154</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G615" t="n">
-        <v>1.72878539562225</v>
+        <v>1.72878551483154</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G616" t="n">
-        <v>1.71736896038055</v>
+        <v>1.71736907958984</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G617" t="n">
-        <v>1.7858681678772</v>
+        <v>1.78586804866791</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G618" t="n">
-        <v>1.75814211368561</v>
+        <v>1.75814235210419</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G620" t="n">
-        <v>1.7744517326355</v>
+        <v>1.77445185184479</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G626" t="n">
-        <v>1.8445817232132</v>
+        <v>1.84458196163177</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>1.86741471290588</v>
+        <v>1.86741459369659</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G628" t="n">
-        <v>1.8445817232132</v>
+        <v>1.84458196163177</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G630" t="n">
-        <v>1.82664132118225</v>
+        <v>1.82664144039154</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G631" t="n">
-        <v>1.76466619968414</v>
+        <v>1.76466608047485</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G636" t="n">
-        <v>1.74346399307251</v>
+        <v>1.7434641122818</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G639" t="n">
-        <v>1.89187848567963</v>
+        <v>1.89187836647034</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G641" t="n">
-        <v>1.86578369140625</v>
+        <v>1.86578381061554</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>1.87720024585724</v>
+        <v>1.87720000743866</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G643" t="n">
-        <v>1.9065568447113</v>
+        <v>1.90655672550201</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G644" t="n">
-        <v>1.88372409343719</v>
+        <v>1.88372397422791</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G645" t="n">
-        <v>1.84295058250427</v>
+        <v>1.84295070171356</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>1.86741471290588</v>
+        <v>1.86741459369659</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G648" t="n">
-        <v>1.81685590744019</v>
+        <v>1.81685566902161</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G649" t="n">
-        <v>1.81196296215057</v>
+        <v>1.81196320056915</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>1.81848669052124</v>
+        <v>1.81848680973053</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G652" t="n">
-        <v>1.7744517326355</v>
+        <v>1.77445185184479</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78749918937683</v>
+        <v>1.78749907016754</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G657" t="n">
-        <v>1.79728448390961</v>
+        <v>1.79728472232819</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G659" t="n">
-        <v>1.84295058250427</v>
+        <v>1.84295070171356</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G661" t="n">
-        <v>1.82337951660156</v>
+        <v>1.82337975502014</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G663" t="n">
-        <v>1.79076111316681</v>
+        <v>1.79076099395752</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G665" t="n">
-        <v>1.89187848567963</v>
+        <v>1.89187836647034</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G666" t="n">
-        <v>1.88046205043793</v>
+        <v>1.88046216964722</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G667" t="n">
-        <v>1.85925996303558</v>
+        <v>1.85925984382629</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G668" t="n">
-        <v>1.86415266990662</v>
+        <v>1.86415302753448</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G669" t="n">
-        <v>1.85762929916382</v>
+        <v>1.85762906074524</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G670" t="n">
-        <v>1.87556934356689</v>
+        <v>1.87556946277618</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G671" t="n">
-        <v>1.90818798542023</v>
+        <v>1.90818774700165</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G672" t="n">
-        <v>2.00441312789917</v>
+        <v>2.00441265106201</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G673" t="n">
-        <v>1.99136543273926</v>
+        <v>1.99136519432068</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G674" t="n">
-        <v>1.99136543273926</v>
+        <v>1.99136519432068</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G675" t="n">
-        <v>1.95548486709595</v>
+        <v>1.95548498630524</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G678" t="n">
-        <v>1.89024758338928</v>
+        <v>1.89024794101715</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G679" t="n">
-        <v>1.86415266990662</v>
+        <v>1.86415302753448</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G682" t="n">
-        <v>1.76466619968414</v>
+        <v>1.76466608047485</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82337951660156</v>
+        <v>1.82337975502014</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>1.82664132118225</v>
+        <v>1.82664144039154</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G687" t="n">
-        <v>1.91471171379089</v>
+        <v>1.9147115945816</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G689" t="n">
-        <v>1.91308033466339</v>
+        <v>1.91308045387268</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G690" t="n">
-        <v>1.89840257167816</v>
+        <v>1.89840233325958</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G691" t="n">
-        <v>1.86415266990662</v>
+        <v>1.86415302753448</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G692" t="n">
-        <v>1.88046205043793</v>
+        <v>1.88046216964722</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G693" t="n">
-        <v>1.84295058250427</v>
+        <v>1.84295070171356</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G694" t="n">
-        <v>1.81685590744019</v>
+        <v>1.81685566902161</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G695" t="n">
-        <v>1.80707049369812</v>
+        <v>1.80707025527954</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G697" t="n">
-        <v>1.79402279853821</v>
+        <v>1.7940229177475</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G698" t="n">
-        <v>1.78749918937683</v>
+        <v>1.78749907016754</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G702" t="n">
-        <v>1.70105993747711</v>
+        <v>1.70105981826782</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G703" t="n">
-        <v>1.62929892539978</v>
+        <v>1.62929904460907</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G704" t="n">
-        <v>1.65050101280212</v>
+        <v>1.65050089359283</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G705" t="n">
-        <v>1.6619176864624</v>
+        <v>1.66191756725311</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G709" t="n">
-        <v>1.5249195098877</v>
+        <v>1.52491939067841</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G710" t="n">
-        <v>1.4816997051239</v>
+        <v>1.48169958591461</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G716" t="n">
-        <v>1.50208628177643</v>
+        <v>1.50208640098572</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G717" t="n">
-        <v>1.4621285200119</v>
+        <v>1.46212863922119</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>1.45968210697174</v>
+        <v>1.45968222618103</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>1.53388953208923</v>
+        <v>1.53388965129852</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G721" t="n">
-        <v>1.53470504283905</v>
+        <v>1.53470492362976</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G725" t="n">
-        <v>1.62032866477966</v>
+        <v>1.62032878398895</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092970848083</v>
+        <v>1.63092994689941</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G729" t="n">
-        <v>1.62685263156891</v>
+        <v>1.62685251235962</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092970848083</v>
+        <v>1.63092994689941</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G731" t="n">
-        <v>1.61625158786774</v>
+        <v>1.61625134944916</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>1.59831118583679</v>
+        <v>1.59831130504608</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G733" t="n">
-        <v>1.51187205314636</v>
+        <v>1.51187193393707</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G735" t="n">
-        <v>1.53144299983978</v>
+        <v>1.53144311904907</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G739" t="n">
-        <v>1.44581937789917</v>
+        <v>1.44581925868988</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G745" t="n">
-        <v>1.49800908565521</v>
+        <v>1.49800896644592</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>1.45152747631073</v>
+        <v>1.45152759552002</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G750" t="n">
-        <v>1.41156983375549</v>
+        <v>1.4115697145462</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G751" t="n">
-        <v>1.41156983375549</v>
+        <v>1.4115697145462</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G752" t="n">
-        <v>1.36345732212067</v>
+        <v>1.36345744132996</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G753" t="n">
-        <v>1.36345732212067</v>
+        <v>1.36345744132996</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G755" t="n">
-        <v>1.10087752342224</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G756" t="n">
-        <v>1.09272313117981</v>
+        <v>1.09272301197052</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>1.03564047813416</v>
+        <v>1.03564023971558</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G759" t="n">
-        <v>1.01525390148163</v>
+        <v>1.01525378227234</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G760" t="n">
-        <v>1.03074777126312</v>
+        <v>1.03074753284454</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.32700002193451</v>
       </c>
       <c r="G761" t="n">
-        <v>1.08212220668793</v>
+        <v>1.08212208747864</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G762" t="n">
-        <v>1.10087752342224</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G765" t="n">
-        <v>1.1742696762085</v>
+        <v>1.17426955699921</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>1.1742696762085</v>
+        <v>1.17426955699921</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G767" t="n">
-        <v>1.26478600502014</v>
+        <v>1.26478612422943</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G769" t="n">
-        <v>1.30229759216309</v>
+        <v>1.3022974729538</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G770" t="n">
-        <v>1.35693371295929</v>
+        <v>1.35693359375</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G773" t="n">
-        <v>1.32920777797699</v>
+        <v>1.32920789718628</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G774" t="n">
-        <v>1.337362408638</v>
+        <v>1.33736228942871</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G775" t="n">
-        <v>1.36019563674927</v>
+        <v>1.36019551753998</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.38629055023193</v>
+        <v>1.38629043102264</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G777" t="n">
-        <v>1.39770674705505</v>
+        <v>1.39770686626434</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G778" t="n">
-        <v>1.31045210361481</v>
+        <v>1.3104522228241</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G779" t="n">
-        <v>1.33491623401642</v>
+        <v>1.33491599559784</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G781" t="n">
-        <v>1.435218334198</v>
+        <v>1.43521821498871</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G783" t="n">
-        <v>1.54693686962128</v>
+        <v>1.54693698883057</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G786" t="n">
-        <v>1.56650817394257</v>
+        <v>1.56650805473328</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.96300005912781</v>
       </c>
       <c r="G788" t="n">
-        <v>1.60075783729553</v>
+        <v>1.60075771808624</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G790" t="n">
-        <v>1.61625158786774</v>
+        <v>1.61625134944916</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G792" t="n">
-        <v>1.51839566230774</v>
+        <v>1.51839554309845</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G793" t="n">
-        <v>1.53470504283905</v>
+        <v>1.53470492362976</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G794" t="n">
-        <v>1.52084195613861</v>
+        <v>1.5208420753479</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G795" t="n">
-        <v>1.67985773086548</v>
+        <v>1.67985761165619</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G799" t="n">
-        <v>1.67985773086548</v>
+        <v>1.67985761165619</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G800" t="n">
-        <v>1.64071547985077</v>
+        <v>1.64071559906006</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G801" t="n">
-        <v>1.65702474117279</v>
+        <v>1.6570246219635</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G802" t="n">
-        <v>1.68148863315582</v>
+        <v>1.6814888715744</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G803" t="n">
-        <v>1.70595252513885</v>
+        <v>1.70595276355743</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G804" t="n">
-        <v>1.69453620910645</v>
+        <v>1.69453608989716</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G805" t="n">
-        <v>1.70921444892883</v>
+        <v>1.70921432971954</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G807" t="n">
-        <v>1.69616711139679</v>
+        <v>1.6961669921875</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G808" t="n">
-        <v>1.67985773086548</v>
+        <v>1.67985761165619</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G809" t="n">
-        <v>1.69942903518677</v>
+        <v>1.69942891597748</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G811" t="n">
-        <v>1.65865564346313</v>
+        <v>1.65865552425385</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G812" t="n">
-        <v>1.65865564346313</v>
+        <v>1.65865552425385</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G813" t="n">
-        <v>1.64560806751251</v>
+        <v>1.6456081867218</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G816" t="n">
-        <v>1.69290518760681</v>
+        <v>1.69290506839752</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G817" t="n">
-        <v>1.64071547985077</v>
+        <v>1.64071559906006</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G818" t="n">
-        <v>1.63582277297974</v>
+        <v>1.63582265377045</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.97099995613098</v>
       </c>
       <c r="G821" t="n">
-        <v>1.60728132724762</v>
+        <v>1.6072815656662</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G822" t="n">
-        <v>1.60157322883606</v>
+        <v>1.60157299041748</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G823" t="n">
-        <v>1.6733341217041</v>
+        <v>1.67333400249481</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G824" t="n">
-        <v>1.6619176864624</v>
+        <v>1.66191756725311</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G826" t="n">
-        <v>1.69127404689789</v>
+        <v>1.69127416610718</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G827" t="n">
-        <v>1.70921444892883</v>
+        <v>1.70921432971954</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>1.68475067615509</v>
+        <v>1.6847505569458</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G829" t="n">
-        <v>1.7043217420578</v>
+        <v>1.70432162284851</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G830" t="n">
-        <v>1.71736896038055</v>
+        <v>1.71736907958984</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G831" t="n">
-        <v>1.88372409343719</v>
+        <v>1.88372397422791</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G832" t="n">
-        <v>1.89187848567963</v>
+        <v>1.89187836647034</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G833" t="n">
-        <v>1.81196296215057</v>
+        <v>1.81196320056915</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G834" t="n">
-        <v>1.78260636329651</v>
+        <v>1.7826064825058</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G836" t="n">
-        <v>1.7744517326355</v>
+        <v>1.77445185184479</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>1.7858681678772</v>
+        <v>1.78586804866791</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G838" t="n">
-        <v>1.7858681678772</v>
+        <v>1.78586804866791</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G840" t="n">
-        <v>1.72063088417053</v>
+        <v>1.72063100337982</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>1.67985773086548</v>
+        <v>1.67985761165619</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G842" t="n">
-        <v>1.66028654575348</v>
+        <v>1.66028666496277</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>1.59831118583679</v>
+        <v>1.59831130504608</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G849" t="n">
-        <v>1.49148523807526</v>
+        <v>1.49148535728455</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G850" t="n">
-        <v>1.43929541110992</v>
+        <v>1.43929576873779</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G851" t="n">
-        <v>1.42543268203735</v>
+        <v>1.42543256282806</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G852" t="n">
-        <v>1.40830790996552</v>
+        <v>1.4083080291748</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G853" t="n">
-        <v>1.39852237701416</v>
+        <v>1.39852225780487</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G855" t="n">
-        <v>1.41890895366669</v>
+        <v>1.41890907287598</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G856" t="n">
-        <v>1.36345732212067</v>
+        <v>1.36345744132996</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G858" t="n">
-        <v>1.41890895366669</v>
+        <v>1.41890907287598</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G860" t="n">
-        <v>1.40830790996552</v>
+        <v>1.4083080291748</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G861" t="n">
-        <v>1.39281404018402</v>
+        <v>1.39281415939331</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G862" t="n">
-        <v>1.35204088687897</v>
+        <v>1.35204076766968</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G864" t="n">
-        <v>1.41483175754547</v>
+        <v>1.41483163833618</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G865" t="n">
-        <v>1.39770674705505</v>
+        <v>1.39770686626434</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G866" t="n">
-        <v>1.37487387657166</v>
+        <v>1.37487399578094</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.70899999141693</v>
       </c>
       <c r="G867" t="n">
-        <v>1.39362943172455</v>
+        <v>1.39362955093384</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G868" t="n">
-        <v>1.41890895366669</v>
+        <v>1.41890907287598</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G869" t="n">
-        <v>1.39770674705505</v>
+        <v>1.39770686626434</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G874" t="n">
-        <v>1.5249195098877</v>
+        <v>1.52491939067841</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.875</v>
       </c>
       <c r="G875" t="n">
-        <v>1.5289968252182</v>
+        <v>1.52899670600891</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.875</v>
       </c>
       <c r="G877" t="n">
-        <v>1.5289968252182</v>
+        <v>1.52899670600891</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G880" t="n">
-        <v>1.47436046600342</v>
+        <v>1.47436058521271</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G883" t="n">
-        <v>1.45152747631073</v>
+        <v>1.45152759552002</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G884" t="n">
-        <v>1.42869448661804</v>
+        <v>1.42869460582733</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G886" t="n">
-        <v>1.44908118247986</v>
+        <v>1.44908130168915</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G888" t="n">
-        <v>1.44581937789917</v>
+        <v>1.44581925868988</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G890" t="n">
-        <v>1.46865248680115</v>
+        <v>1.46865236759186</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G891" t="n">
-        <v>1.52573478221893</v>
+        <v>1.52573490142822</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G894" t="n">
-        <v>1.57058537006378</v>
+        <v>1.57058548927307</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G895" t="n">
-        <v>1.50290203094482</v>
+        <v>1.50290191173553</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.435218334198</v>
+        <v>1.43521821498871</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G900" t="n">
-        <v>1.3879212141037</v>
+        <v>1.38792133331299</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G901" t="n">
-        <v>1.33246958255768</v>
+        <v>1.33246970176697</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G902" t="n">
-        <v>1.2558159828186</v>
+        <v>1.25581586360931</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.51300001144409</v>
       </c>
       <c r="G903" t="n">
-        <v>1.23379838466644</v>
+        <v>1.23379850387573</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G907" t="n">
-        <v>1.37732017040253</v>
+        <v>1.37732005119324</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G911" t="n">
-        <v>1.41890895366669</v>
+        <v>1.41890907287598</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G912" t="n">
-        <v>1.50371742248535</v>
+        <v>1.50371718406677</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G914" t="n">
-        <v>1.54122865200043</v>
+        <v>1.54122877120972</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G916" t="n">
-        <v>1.54122865200043</v>
+        <v>1.54122877120972</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G919" t="n">
-        <v>1.41727805137634</v>
+        <v>1.41727817058563</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G923" t="n">
-        <v>1.45968210697174</v>
+        <v>1.45968222618103</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G925" t="n">
-        <v>1.45478940010071</v>
+        <v>1.45478951931</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G927" t="n">
-        <v>1.41890895366669</v>
+        <v>1.41890907287598</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G929" t="n">
-        <v>1.43277192115784</v>
+        <v>1.43277180194855</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G930" t="n">
-        <v>1.46539032459259</v>
+        <v>1.46539044380188</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G932" t="n">
-        <v>1.44255757331848</v>
+        <v>1.44255745410919</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G933" t="n">
-        <v>1.46865248680115</v>
+        <v>1.46865236759186</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G935" t="n">
-        <v>1.45152747631073</v>
+        <v>1.45152759552002</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.45152747631073</v>
+        <v>1.45152759552002</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G939" t="n">
-        <v>1.47680699825287</v>
+        <v>1.47680711746216</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G940" t="n">
-        <v>1.47680699825287</v>
+        <v>1.47680711746216</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G941" t="n">
-        <v>1.5795556306839</v>
+        <v>1.57955551147461</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G944" t="n">
-        <v>1.6765958070755</v>
+        <v>1.67659592628479</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G947" t="n">
-        <v>1.6651793718338</v>
+        <v>1.66517949104309</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G948" t="n">
-        <v>1.65050101280212</v>
+        <v>1.65050089359283</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G949" t="n">
-        <v>1.68148863315582</v>
+        <v>1.6814888715744</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G950" t="n">
-        <v>1.65702474117279</v>
+        <v>1.6570246219635</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G952" t="n">
-        <v>1.64071547985077</v>
+        <v>1.64071559906006</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G954" t="n">
-        <v>1.62685263156891</v>
+        <v>1.62685251235962</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G955" t="n">
-        <v>1.60401952266693</v>
+        <v>1.60401940345764</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G956" t="n">
-        <v>1.55916893482208</v>
+        <v>1.55916881561279</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G958" t="n">
-        <v>1.57058537006378</v>
+        <v>1.57058548927307</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G963" t="n">
-        <v>1.5281810760498</v>
+        <v>1.52818119525909</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G964" t="n">
-        <v>1.55019891262054</v>
+        <v>1.55019879341125</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>1.56161546707153</v>
+        <v>1.56161522865295</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G966" t="n">
-        <v>1.5795556306839</v>
+        <v>1.57955551147461</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G968" t="n">
-        <v>1.54938340187073</v>
+        <v>1.54938328266144</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G969" t="n">
-        <v>1.61135864257812</v>
+        <v>1.61135876178741</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G970" t="n">
-        <v>1.53307402133942</v>
+        <v>1.53307414054871</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.875</v>
       </c>
       <c r="G971" t="n">
-        <v>1.5289968252182</v>
+        <v>1.52899670600891</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G972" t="n">
-        <v>1.51921129226685</v>
+        <v>1.51921117305756</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G974" t="n">
-        <v>1.52002644538879</v>
+        <v>1.5200263261795</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G975" t="n">
-        <v>1.48740792274475</v>
+        <v>1.48740804195404</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G976" t="n">
-        <v>1.48903906345367</v>
+        <v>1.4890388250351</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G978" t="n">
-        <v>1.4621285200119</v>
+        <v>1.46212863922119</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G979" t="n">
-        <v>1.45968210697174</v>
+        <v>1.45968222618103</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>1.45968210697174</v>
+        <v>1.45968222618103</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G981" t="n">
-        <v>1.42053985595703</v>
+        <v>1.42053973674774</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G982" t="n">
-        <v>1.37324285507202</v>
+        <v>1.37324297428131</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.77199995517731</v>
       </c>
       <c r="G983" t="n">
-        <v>1.44500386714935</v>
+        <v>1.44500374794006</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G985" t="n">
-        <v>1.49556267261505</v>
+        <v>1.49556255340576</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G986" t="n">
-        <v>1.48414623737335</v>
+        <v>1.48414611816406</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G990" t="n">
-        <v>1.39036786556244</v>
+        <v>1.39036774635315</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.71099996566772</v>
       </c>
       <c r="G992" t="n">
-        <v>1.39526045322418</v>
+        <v>1.39526057243347</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G993" t="n">
-        <v>1.4311408996582</v>
+        <v>1.43114101886749</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G994" t="n">
-        <v>1.43277192115784</v>
+        <v>1.43277180194855</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G995" t="n">
-        <v>1.4621285200119</v>
+        <v>1.46212863922119</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G996" t="n">
-        <v>1.44174182415009</v>
+        <v>1.44174206256866</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G997" t="n">
-        <v>1.44337284564972</v>
+        <v>1.44337272644043</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.41483175754547</v>
+        <v>1.41483163833618</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.41727805137634</v>
+        <v>1.41727817058563</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.37487387657166</v>
+        <v>1.37487399578094</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.34633266925812</v>
+        <v>1.34633255004883</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.37487387657166</v>
+        <v>1.37487399578094</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.34470176696777</v>
+        <v>1.34470164775848</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.33573150634766</v>
+        <v>1.33573138713837</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.33002328872681</v>
+        <v>1.33002316951752</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.32268404960632</v>
+        <v>1.32268416881561</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.28843462467194</v>
+        <v>1.28843486309052</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.30474388599396</v>
+        <v>1.30474400520325</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.30229759216309</v>
+        <v>1.3022974729538</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.31779146194458</v>
+        <v>1.31779134273529</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.32268404960632</v>
+        <v>1.32268416881561</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.33328497409821</v>
+        <v>1.3332850933075</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.32431507110596</v>
+        <v>1.32431495189667</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.32105302810669</v>
+        <v>1.32105314731598</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.30474388599396</v>
+        <v>1.30474400520325</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.26397049427032</v>
+        <v>1.2639707326889</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.24521493911743</v>
+        <v>1.24521481990814</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.23706030845642</v>
+        <v>1.23706018924713</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.26397049427032</v>
+        <v>1.2639707326889</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.2558159828186</v>
+        <v>1.25581586360931</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.17834675312042</v>
+        <v>1.17834687232971</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.21993553638458</v>
+        <v>1.21993565559387</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.21504271030426</v>
+        <v>1.21504282951355</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.442999958992</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.17671597003937</v>
+        <v>1.17671585083008</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.2125962972641</v>
+        <v>1.21259653568268</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.2166736125946</v>
+        <v>1.21667349338531</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.47699999809265</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.20444166660309</v>
+        <v>1.20444178581238</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.20851910114288</v>
+        <v>1.20851898193359</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.47699999809265</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.20444166660309</v>
+        <v>1.20444178581238</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.2125962972641</v>
+        <v>1.21259653568268</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.23298275470734</v>
+        <v>1.23298287391663</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.19057881832123</v>
+        <v>1.19057893753052</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.0845685005188</v>
+        <v>1.08456838130951</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.12860357761383</v>
+        <v>1.12860345840454</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.1074013710022</v>
+        <v>1.10740149021149</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.05928897857666</v>
+        <v>1.05928909778595</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.03400957584381</v>
+        <v>1.03400945663452</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.03564047813416</v>
+        <v>1.03564023971558</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.804048359394073</v>
+        <v>0.804048418998718</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.760013222694397</v>
+        <v>0.760013163089752</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.564301788806915</v>
+        <v>0.564301729202271</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.588357985019684</v>
+        <v>0.588357925415039</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.593658447265625</v>
+        <v>0.59365838766098</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.738499999046326</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.602220833301544</v>
+        <v>0.602220892906189</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.858684480190277</v>
+        <v>0.858684539794922</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.898642241954803</v>
+        <v>0.898642361164093</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.02259302139282</v>
+        <v>1.02259314060211</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.937784671783447</v>
+        <v>0.937784731388092</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.913320660591125</v>
+        <v>0.91332072019577</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.950832009315491</v>
+        <v>0.95083212852478</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.949201285839081</v>
+        <v>0.949201166629791</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.12800002098083</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.919844448566437</v>
+        <v>0.919844388961792</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.956540167331696</v>
+        <v>0.95654022693634</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.02177751064301</v>
+        <v>1.02177762985229</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.9981290102005</v>
+        <v>0.99812912940979</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.06744360923767</v>
+        <v>1.06744349002838</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.10087752342224</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.33899998664856</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.0919075012207</v>
+        <v>1.09190738201141</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.08864557743073</v>
+        <v>1.08864569664001</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.0878301858902</v>
+        <v>1.08783006668091</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.10087752342224</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.10087752342224</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.09272313117981</v>
+        <v>1.09272301197052</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.0878301858902</v>
+        <v>1.08783006668091</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>1.34899997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.10006213188171</v>
+        <v>1.100062251091</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.06662809848785</v>
+        <v>1.06662821769714</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.31900000572205</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.07559812068939</v>
+        <v>1.07559835910797</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.05847346782684</v>
+        <v>1.05847334861755</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.04379510879517</v>
+        <v>1.04379522800446</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.979701161384583</v>
+        <v>0.979700982570648</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.991393983364105</v>
+        <v>0.991394102573395</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.25</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.04401218891144</v>
+        <v>1.04401230812073</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.05737566947937</v>
+        <v>1.05737578868866</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>1.22899997234344</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.02647292613983</v>
+        <v>1.02647280693054</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.04484736919403</v>
+        <v>1.04484748840332</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.26900005340576</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.05988144874573</v>
+        <v>1.05988132953644</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.08243203163147</v>
+        <v>1.08243191242218</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.19518530368805</v>
+        <v>1.19518518447876</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.18766832351685</v>
+        <v>1.18766844272614</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.20103168487549</v>
+        <v>1.20103180408478</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.17012894153595</v>
+        <v>1.17012882232666</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.23026406764984</v>
+        <v>1.23026418685913</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>1.44700002670288</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.20854866504669</v>
+        <v>1.2085485458374</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.24028670787811</v>
+        <v>1.24028646945953</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.23026406764984</v>
+        <v>1.23026418685913</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.17764592170715</v>
+        <v>1.17764580249786</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.18516266345978</v>
+        <v>1.18516278266907</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.140061378479</v>
+        <v>1.14006149768829</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.1642826795578</v>
+        <v>1.16428256034851</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.23276960849762</v>
+        <v>1.23276972770691</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.19852578639984</v>
+        <v>1.19852602481842</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.1734699010849</v>
+        <v>1.17346966266632</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.20938384532928</v>
+        <v>1.20938372612</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>1.45299994945526</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.21355986595154</v>
+        <v>1.21355974674225</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.20103168487549</v>
+        <v>1.20103180408478</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.18516266345978</v>
+        <v>1.18516278266907</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.20938384532928</v>
+        <v>1.20938372612</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>1.09899997711182</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.917895555496216</v>
+        <v>0.917895615100861</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.88615757226944</v>
+        <v>0.886157631874084</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.896179974079132</v>
+        <v>0.896180093288422</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.918730795383453</v>
+        <v>0.918730735778809</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.953809499740601</v>
+        <v>0.953809559345245</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.921236515045166</v>
+        <v>0.921236455440521</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.915389955043793</v>
+        <v>0.915389895439148</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.942951798439026</v>
+        <v>0.942951738834381</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.918730795383453</v>
+        <v>0.918730735778809</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.900356113910675</v>
+        <v>0.90035605430603</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.905367493629456</v>
+        <v>0.905367434024811</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.888663172721863</v>
+        <v>0.888663113117218</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.918730795383453</v>
+        <v>0.918730735778809</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.905367493629456</v>
+        <v>0.905367434024811</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.0809999704361</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.902861773967743</v>
+        <v>0.902861833572388</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.10800004005432</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.925412535667419</v>
+        <v>0.925412595272064</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.829363286495209</v>
+        <v>0.829363346099854</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.8343745470047</v>
+        <v>0.834374606609344</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.992500007152557</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.828945755958557</v>
+        <v>0.828945696353912</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.884487271308899</v>
+        <v>0.884487211704254</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.915389955043793</v>
+        <v>0.915389895439148</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.864442110061646</v>
+        <v>0.864442050457001</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.843561887741089</v>
+        <v>0.843561828136444</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>0.997500002384186</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.833121776580811</v>
+        <v>0.833121836185455</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>0.981500029563904</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.819758474826813</v>
+        <v>0.819758415222168</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>0.961000025272369</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.802636623382568</v>
+        <v>0.802636742591858</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.768393039703369</v>
+        <v>0.768392980098724</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.729973375797272</v>
+        <v>0.729973435401917</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.767975389957428</v>
+        <v>0.767975330352783</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.794284582138062</v>
+        <v>0.794284522533417</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.856090009212494</v>
+        <v>0.856090068817139</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.924577176570892</v>
+        <v>0.924577236175537</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.96466726064682</v>
+        <v>0.964667320251465</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.951303899288177</v>
+        <v>0.951304078102112</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.25</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.04401218891144</v>
+        <v>1.04401230812073</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.04985857009888</v>
+        <v>1.04985880851746</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.3289999961853</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.10999381542206</v>
+        <v>1.10999369621277</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.08577275276184</v>
+        <v>1.08577263355255</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.06906867027283</v>
+        <v>1.06906855106354</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.06906867027283</v>
+        <v>1.06906855106354</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.06489253044128</v>
+        <v>1.06489241123199</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.03733062744141</v>
+        <v>1.03733050823212</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.03148400783539</v>
+        <v>1.03148412704468</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.01227426528931</v>
+        <v>1.0122743844986</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.20299994945526</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.00475716590881</v>
+        <v>1.0047572851181</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.21899998188019</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.01812064647675</v>
+        <v>1.01812076568604</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.998075723648071</v>
+        <v>0.998075783252716</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.951303899288177</v>
+        <v>0.951304078102112</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.967172920703888</v>
+        <v>0.967173039913177</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.992229223251343</v>
+        <v>0.992229163646698</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.991393983364105</v>
+        <v>0.991394102573395</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.987218022346497</v>
+        <v>0.987217962741852</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.965502500534058</v>
+        <v>0.965502619743347</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.27699995040894</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.06656301021576</v>
+        <v>1.06656289100647</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.05737566947937</v>
+        <v>1.05737578868866</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.03148400783539</v>
+        <v>1.03148412704468</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.06322193145752</v>
+        <v>1.06322205066681</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.06906867027283</v>
+        <v>1.06906855106354</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.07575023174286</v>
+        <v>1.07575035095215</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.25899994373322</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.05152904987335</v>
+        <v>1.05152916908264</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.03482484817505</v>
+        <v>1.03482472896576</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.22899997234344</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.02647292613983</v>
+        <v>1.02647280693054</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.24100005626678</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.03649532794952</v>
+        <v>1.03649544715881</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.09579527378082</v>
+        <v>1.09579539299011</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.20270216464996</v>
+        <v>1.20270228385925</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.28371739387512</v>
+        <v>1.28371751308441</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.31378495693207</v>
+        <v>1.31378483772278</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.41484534740448</v>
+        <v>1.41484546661377</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.37392008304596</v>
+        <v>1.37392020225525</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.36222720146179</v>
+        <v>1.3622270822525</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.37392008304596</v>
+        <v>1.37392020225525</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.3705792427063</v>
+        <v>1.37057936191559</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.30793869495392</v>
+        <v>1.30793857574463</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.30376255512238</v>
+        <v>1.30376243591309</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.30125689506531</v>
+        <v>1.30125677585602</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.30877387523651</v>
+        <v>1.30877375602722</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.37392008304596</v>
+        <v>1.37392020225525</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.46829879283905</v>
+        <v>1.46829891204834</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.44491314888</v>
+        <v>1.44491291046143</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.43489050865173</v>
+        <v>1.43489062786102</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.47163987159729</v>
+        <v>1.47163963317871</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.44073688983917</v>
+        <v>1.44073700904846</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.50337767601013</v>
+        <v>1.50337755680084</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.49001443386078</v>
+        <v>1.49001431465149</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.50337767601013</v>
+        <v>1.50337755680084</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.56518304347992</v>
+        <v>1.56518316268921</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.51005935668945</v>
+        <v>1.51005947589874</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.52258741855621</v>
+        <v>1.5225875377655</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.53929173946381</v>
+        <v>1.5392918586731</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.53010439872742</v>
+        <v>1.53010427951813</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.55265498161316</v>
+        <v>1.55265510082245</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.52843403816223</v>
+        <v>1.52843415737152</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.51507043838501</v>
+        <v>1.5150705575943</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.51590597629547</v>
+        <v>1.51590585708618</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.50922417640686</v>
+        <v>1.50922429561615</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.52258741855621</v>
+        <v>1.5225875377655</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.51924657821655</v>
+        <v>1.51924669742584</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.51924657821655</v>
+        <v>1.51924669742584</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>1.98500001430511</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>2271100</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>2.00600004196167</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>1.96300005912781</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>2.00600004196167</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>1.96599996089935</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>1.96599996089935</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>1.9099999666214</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>1.95000004768372</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>2221497</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>1.96399998664856</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>1.93400001525879</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>1.9539999961853</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>1.9539999961853</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>1.96099996566772</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>3216438</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>1.95000004768372</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -63311,13 +63311,36 @@
         <v>1.97000002861023</v>
       </c>
       <c r="D2737" t="n">
-        <v>1.89999997615814</v>
+        <v>1.89199995994568</v>
       </c>
       <c r="E2737" t="n">
         <v>1.95000004768372</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>1.89199995994568</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>4604600</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>1.89300000667572</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1.85199999809265</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>1.88999998569489</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>1.88999998569489</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1.86699998378754</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>3498099</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>1.92599999904633</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>1.86199998855591</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>1.90600001811981</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>2689050</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1.87100005149841</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1.87199997901917</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>1.91199994087219</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G2" t="n">
-        <v>2.99598336219788</v>
+        <v>2.99598360061646</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91082644462585</v>
+        <v>2.91082620620728</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G4" t="n">
-        <v>2.87366676330566</v>
+        <v>2.87366700172424</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>2.75599503517151</v>
+        <v>2.75599479675293</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76218867301941</v>
+        <v>2.76218843460083</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G11" t="n">
-        <v>2.69251465797424</v>
+        <v>2.69251418113708</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G12" t="n">
-        <v>2.61045408248901</v>
+        <v>2.61045384407043</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66464495658875</v>
+        <v>2.66464424133301</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G15" t="n">
-        <v>2.65690302848816</v>
+        <v>2.65690326690674</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7482533454895</v>
+        <v>2.74825358390808</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G18" t="n">
-        <v>2.73896384239197</v>
+        <v>2.73896360397339</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G19" t="n">
-        <v>2.72657704353333</v>
+        <v>2.7265772819519</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2.70954585075378</v>
+        <v>2.70954608917236</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63213014602661</v>
+        <v>2.63213038444519</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6166467666626</v>
+        <v>2.61664700508118</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.39988350868225</v>
+        <v>2.39988327026367</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G30" t="n">
-        <v>2.2729218006134</v>
+        <v>2.27292203903198</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G31" t="n">
-        <v>2.31472635269165</v>
+        <v>2.31472611427307</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G33" t="n">
-        <v>2.39214181900024</v>
+        <v>2.39214158058167</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G35" t="n">
-        <v>2.59342217445374</v>
+        <v>2.59342241287231</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G36" t="n">
-        <v>2.5376832485199</v>
+        <v>2.53768348693848</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G38" t="n">
-        <v>2.63987183570862</v>
+        <v>2.63987135887146</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G39" t="n">
-        <v>2.54077982902527</v>
+        <v>2.54077959060669</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G40" t="n">
-        <v>2.62129187583923</v>
+        <v>2.62129211425781</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G41" t="n">
-        <v>2.73122239112854</v>
+        <v>2.73122191429138</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G42" t="n">
-        <v>2.77302694320679</v>
+        <v>2.77302622795105</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>2.84115242958069</v>
+        <v>2.84115219116211</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G46" t="n">
-        <v>2.9170196056366</v>
+        <v>2.91701936721802</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87366676330566</v>
+        <v>2.87366700172424</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G48" t="n">
-        <v>2.8225724697113</v>
+        <v>2.82257199287415</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.80244398117065</v>
+        <v>2.80244421958923</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G50" t="n">
-        <v>2.79005813598633</v>
+        <v>2.79005837440491</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G53" t="n">
-        <v>2.9170196056366</v>
+        <v>2.91701936721802</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89069795608521</v>
+        <v>2.89069819450378</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G56" t="n">
-        <v>2.78076815605164</v>
+        <v>2.78076839447021</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G58" t="n">
-        <v>2.86592507362366</v>
+        <v>2.86592531204224</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G59" t="n">
-        <v>2.86128044128418</v>
+        <v>2.8612802028656</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G60" t="n">
-        <v>2.78696131706238</v>
+        <v>2.7869610786438</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G65" t="n">
-        <v>2.77921962738037</v>
+        <v>2.77921986579895</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.70954585075378</v>
+        <v>2.70954608917236</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G67" t="n">
-        <v>2.71109390258789</v>
+        <v>2.71109366416931</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G68" t="n">
-        <v>2.72657704353333</v>
+        <v>2.7265772819519</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G70" t="n">
-        <v>2.82412075996399</v>
+        <v>2.82412099838257</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80244398117065</v>
+        <v>2.80244421958923</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G73" t="n">
-        <v>2.89379453659058</v>
+        <v>2.89379501342773</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>2.84115242958069</v>
+        <v>2.84115219116211</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.87985992431641</v>
+        <v>2.87986016273499</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G78" t="n">
-        <v>2.89844012260437</v>
+        <v>2.89843988418579</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G80" t="n">
-        <v>2.85353899002075</v>
+        <v>2.85353875160217</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G83" t="n">
-        <v>3.0099184513092</v>
+        <v>3.00991821289062</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G84" t="n">
-        <v>2.95882391929626</v>
+        <v>2.95882415771484</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G85" t="n">
-        <v>2.98979043960571</v>
+        <v>2.98979020118713</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G86" t="n">
-        <v>2.93250274658203</v>
+        <v>2.93250298500061</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G87" t="n">
-        <v>2.9185676574707</v>
+        <v>2.91856789588928</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G88" t="n">
-        <v>2.87366676330566</v>
+        <v>2.87366700172424</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>2.80244398117065</v>
+        <v>2.80244421958923</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G91" t="n">
-        <v>2.81328248977661</v>
+        <v>2.81328272819519</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>2.87985992431641</v>
+        <v>2.87986016273499</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G96" t="n">
-        <v>2.9170196056366</v>
+        <v>2.91701936721802</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G98" t="n">
-        <v>2.84115242958069</v>
+        <v>2.84115219116211</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G99" t="n">
-        <v>2.84579753875732</v>
+        <v>2.84579730033875</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.87240815162659</v>
+        <v>2.87240791320801</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G103" t="n">
-        <v>2.45759153366089</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G104" t="n">
-        <v>2.47324514389038</v>
+        <v>2.47324538230896</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932395935059</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G109" t="n">
-        <v>2.34958267211914</v>
+        <v>2.3495831489563</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G110" t="n">
-        <v>2.40750050544739</v>
+        <v>2.40750074386597</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G111" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932395935059</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G112" t="n">
-        <v>2.44663381576538</v>
+        <v>2.44663429260254</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G113" t="n">
-        <v>2.41219639778137</v>
+        <v>2.41219687461853</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G117" t="n">
-        <v>2.11634635925293</v>
+        <v>2.11634659767151</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G120" t="n">
-        <v>2.22748613357544</v>
+        <v>2.22748565673828</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G122" t="n">
-        <v>2.21026706695557</v>
+        <v>2.21026682853699</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G123" t="n">
-        <v>2.28696870803833</v>
+        <v>2.28696894645691</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G125" t="n">
-        <v>1.97233438491821</v>
+        <v>1.97233414649963</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G126" t="n">
-        <v>1.9394623041153</v>
+        <v>1.93946254253387</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G127" t="n">
-        <v>1.97389996051788</v>
+        <v>1.97390019893646</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G130" t="n">
-        <v>2.12260770797729</v>
+        <v>2.12260794639587</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>2.0036416053772</v>
+        <v>2.00364136695862</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.11321568489075</v>
+        <v>2.11321520805359</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G136" t="n">
-        <v>2.21652865409851</v>
+        <v>2.21652817726135</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G138" t="n">
-        <v>2.21026706695557</v>
+        <v>2.21026682853699</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G139" t="n">
-        <v>2.18678665161133</v>
+        <v>2.18678689002991</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G142" t="n">
-        <v>2.14608836174011</v>
+        <v>2.14608812332153</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G144" t="n">
-        <v>2.11478090286255</v>
+        <v>2.11478066444397</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G145" t="n">
-        <v>2.14765334129333</v>
+        <v>2.14765310287476</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G146" t="n">
-        <v>2.14921832084656</v>
+        <v>2.14921855926514</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G149" t="n">
-        <v>2.11791157722473</v>
+        <v>2.11791181564331</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G150" t="n">
-        <v>2.06782054901123</v>
+        <v>2.06782031059265</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G151" t="n">
-        <v>1.97859573364258</v>
+        <v>1.97859597206116</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>1.94885456562042</v>
+        <v>1.948854804039</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>1.94102740287781</v>
+        <v>1.94102776050568</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G154" t="n">
-        <v>1.96137714385986</v>
+        <v>1.96137738227844</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G156" t="n">
-        <v>2.0020763874054</v>
+        <v>2.00207614898682</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G158" t="n">
-        <v>2.105388879776</v>
+        <v>2.10538911819458</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.75</v>
       </c>
       <c r="G159" t="n">
-        <v>2.1523494720459</v>
+        <v>2.15234923362732</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G160" t="n">
-        <v>2.08347392082214</v>
+        <v>2.0834743976593</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G162" t="n">
-        <v>2.07721281051636</v>
+        <v>2.07721257209778</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.11321568489075</v>
+        <v>2.11321520805359</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>2.0740818977356</v>
+        <v>2.07408237457275</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.13669562339783</v>
+        <v>2.13669586181641</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>2.16017603874207</v>
+        <v>2.16017556190491</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G175" t="n">
-        <v>2.14608836174011</v>
+        <v>2.14608812332153</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>2.14765334129333</v>
+        <v>2.14765310287476</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G181" t="n">
-        <v>2.0020763874054</v>
+        <v>2.00207614898682</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G182" t="n">
-        <v>1.9895533323288</v>
+        <v>1.98955380916595</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.5</v>
       </c>
       <c r="G183" t="n">
-        <v>1.95668125152588</v>
+        <v>1.9566810131073</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G185" t="n">
-        <v>1.92850506305695</v>
+        <v>1.92850494384766</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>1.92537403106689</v>
+        <v>1.92537426948547</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G188" t="n">
-        <v>1.97859573364258</v>
+        <v>1.97859597206116</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>1.92537403106689</v>
+        <v>1.92537426948547</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G192" t="n">
-        <v>1.99268436431885</v>
+        <v>1.99268388748169</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G193" t="n">
-        <v>2.00677180290222</v>
+        <v>2.0067720413208</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G194" t="n">
-        <v>1.95355069637299</v>
+        <v>1.95355045795441</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G195" t="n">
-        <v>1.94885456562042</v>
+        <v>1.948854804039</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>1.97233438491821</v>
+        <v>1.97233414649963</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G201" t="n">
-        <v>1.93320107460022</v>
+        <v>1.93320083618164</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G202" t="n">
-        <v>1.93320107460022</v>
+        <v>1.93320083618164</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96450769901276</v>
+        <v>1.96450817584991</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G205" t="n">
-        <v>2.0020763874054</v>
+        <v>2.00207614898682</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G206" t="n">
-        <v>2.07721281051636</v>
+        <v>2.07721257209778</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G210" t="n">
-        <v>2.08660483360291</v>
+        <v>2.08660459518433</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G212" t="n">
-        <v>2.03338313102722</v>
+        <v>2.0333833694458</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G213" t="n">
-        <v>1.97859573364258</v>
+        <v>1.97859597206116</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G215" t="n">
-        <v>1.96137714385986</v>
+        <v>1.96137738227844</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G216" t="n">
-        <v>1.93163537979126</v>
+        <v>1.93163514137268</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G217" t="n">
-        <v>1.91128611564636</v>
+        <v>1.91128587722778</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89563274383545</v>
+        <v>1.89563262462616</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G219" t="n">
-        <v>1.93163537979126</v>
+        <v>1.93163514137268</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G220" t="n">
-        <v>1.91128611564636</v>
+        <v>1.91128587722778</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G223" t="n">
-        <v>2.0302529335022</v>
+        <v>2.03025269508362</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G224" t="n">
-        <v>2.16330647468567</v>
+        <v>2.16330695152283</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G225" t="n">
-        <v>2.14765334129333</v>
+        <v>2.14765310287476</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G227" t="n">
-        <v>2.08660483360291</v>
+        <v>2.08660459518433</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.57200002670288</v>
       </c>
       <c r="G228" t="n">
-        <v>2.01303339004517</v>
+        <v>2.01303362846375</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G233" t="n">
-        <v>1.9895533323288</v>
+        <v>1.98955380916595</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>1.92537403106689</v>
+        <v>1.92537426948547</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G238" t="n">
-        <v>2.04434061050415</v>
+        <v>2.04434037208557</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G240" t="n">
-        <v>2.17113327980042</v>
+        <v>2.17113351821899</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G241" t="n">
-        <v>2.23687839508057</v>
+        <v>2.23687791824341</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G243" t="n">
-        <v>2.24626994132996</v>
+        <v>2.24626970291138</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G245" t="n">
-        <v>2.30105710029602</v>
+        <v>2.3010573387146</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G246" t="n">
-        <v>2.34958267211914</v>
+        <v>2.3495831489563</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932395935059</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932395935059</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G250" t="n">
-        <v>2.38088965415955</v>
+        <v>2.38088941574097</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932395935059</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G253" t="n">
-        <v>2.39028191566467</v>
+        <v>2.39028167724609</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G254" t="n">
-        <v>2.39654326438904</v>
+        <v>2.39654350280762</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>2.36367082595825</v>
+        <v>2.36367130279541</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G257" t="n">
-        <v>2.34958267211914</v>
+        <v>2.3495831489563</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G258" t="n">
-        <v>2.43098044395447</v>
+        <v>2.43098068237305</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G259" t="n">
-        <v>2.47794103622437</v>
+        <v>2.47794127464294</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G261" t="n">
-        <v>2.45759153366089</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G263" t="n">
-        <v>2.4231538772583</v>
+        <v>2.42315411567688</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G264" t="n">
-        <v>2.45759153366089</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G266" t="n">
-        <v>2.47011423110962</v>
+        <v>2.47011399269104</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.44976449012756</v>
+        <v>2.44976472854614</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G271" t="n">
-        <v>2.4231538772583</v>
+        <v>2.42315411567688</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G272" t="n">
-        <v>2.40280413627625</v>
+        <v>2.40280437469482</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G273" t="n">
-        <v>2.38402009010315</v>
+        <v>2.38402032852173</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G275" t="n">
-        <v>2.42628479003906</v>
+        <v>2.42628455162048</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G277" t="n">
-        <v>2.33862495422363</v>
+        <v>2.33862519264221</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G281" t="n">
-        <v>2.30105710029602</v>
+        <v>2.3010573387146</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.27757692337036</v>
+        <v>2.27757716178894</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.24626994132996</v>
+        <v>2.24626970291138</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G285" t="n">
-        <v>2.23844313621521</v>
+        <v>2.23844337463379</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G287" t="n">
-        <v>2.33862495422363</v>
+        <v>2.33862519264221</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G288" t="n">
-        <v>2.39341235160828</v>
+        <v>2.3934121131897</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G292" t="n">
-        <v>2.36993217468262</v>
+        <v>2.3699324131012</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3</v>
       </c>
       <c r="G293" t="n">
-        <v>2.34801745414734</v>
+        <v>2.34801721572876</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G294" t="n">
-        <v>2.33862495422363</v>
+        <v>2.33862519264221</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>2.35584402084351</v>
+        <v>2.35584425926208</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G296" t="n">
-        <v>2.33705997467041</v>
+        <v>2.33706021308899</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G297" t="n">
-        <v>2.4528956413269</v>
+        <v>2.45289587974548</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G298" t="n">
-        <v>2.44819974899292</v>
+        <v>2.44819951057434</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G301" t="n">
-        <v>2.54525113105774</v>
+        <v>2.54525136947632</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G302" t="n">
-        <v>2.53585910797119</v>
+        <v>2.53585863113403</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="n">
-        <v>2.50455188751221</v>
+        <v>2.50455236434937</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>2.50455188751221</v>
+        <v>2.50455236434937</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G305" t="n">
-        <v>2.5170750617981</v>
+        <v>2.51707482337952</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>2.49672508239746</v>
+        <v>2.49672532081604</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>2.45759153366089</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G310" t="n">
-        <v>2.48889851570129</v>
+        <v>2.48889827728271</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G311" t="n">
-        <v>2.57342720031738</v>
+        <v>2.5734269618988</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G315" t="n">
-        <v>2.44663381576538</v>
+        <v>2.44663429260254</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G316" t="n">
-        <v>2.48263692855835</v>
+        <v>2.48263716697693</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.50455188751221</v>
+        <v>2.50455236434937</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G318" t="n">
-        <v>2.45446085929871</v>
+        <v>2.45446062088013</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G321" t="n">
-        <v>2.44193816184998</v>
+        <v>2.4419379234314</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G322" t="n">
-        <v>2.44193816184998</v>
+        <v>2.4419379234314</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G323" t="n">
-        <v>2.40280413627625</v>
+        <v>2.40280437469482</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G324" t="n">
-        <v>2.37619352340698</v>
+        <v>2.37619376182556</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G326" t="n">
-        <v>2.44506883621216</v>
+        <v>2.44506859779358</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.47324514389038</v>
+        <v>2.47324538230896</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G329" t="n">
-        <v>2.43254661560059</v>
+        <v>2.43254637718201</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G330" t="n">
-        <v>2.39028191566467</v>
+        <v>2.39028167724609</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G332" t="n">
-        <v>2.29792642593384</v>
+        <v>2.29792666435242</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G334" t="n">
-        <v>2.41532731056213</v>
+        <v>2.41532707214355</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.42628479003906</v>
+        <v>2.42628455162048</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G337" t="n">
-        <v>2.40750050544739</v>
+        <v>2.40750074386597</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>2.44976449012756</v>
+        <v>2.44976472854614</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G339" t="n">
-        <v>2.4231538772583</v>
+        <v>2.42315411567688</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G340" t="n">
-        <v>2.44506883621216</v>
+        <v>2.44506859779358</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>2.51237845420837</v>
+        <v>2.51237869262695</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G342" t="n">
-        <v>2.4904637336731</v>
+        <v>2.49046349525452</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G343" t="n">
-        <v>2.53272795677185</v>
+        <v>2.53272819519043</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G344" t="n">
-        <v>2.55151200294495</v>
+        <v>2.55151224136353</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G350" t="n">
-        <v>2.64543271064758</v>
+        <v>2.64543294906616</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G351" t="n">
-        <v>2.66578269004822</v>
+        <v>2.66578245162964</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.53585910797119</v>
+        <v>2.53585863113403</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G353" t="n">
-        <v>2.43098044395447</v>
+        <v>2.43098068237305</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G355" t="n">
-        <v>2.5204017162323</v>
+        <v>2.52040147781372</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G356" t="n">
-        <v>2.53791546821594</v>
+        <v>2.53791570663452</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>2.55542922019958</v>
+        <v>2.55542945861816</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>2.54746842384338</v>
+        <v>2.54746866226196</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G360" t="n">
-        <v>2.56020617485046</v>
+        <v>2.56020593643188</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>2.54746842384338</v>
+        <v>2.54746866226196</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G363" t="n">
-        <v>2.54269194602966</v>
+        <v>2.54269218444824</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G365" t="n">
-        <v>2.56816673278809</v>
+        <v>2.56816649436951</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G367" t="n">
-        <v>2.44875407218933</v>
+        <v>2.44875431060791</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G368" t="n">
-        <v>2.45830726623535</v>
+        <v>2.45830702781677</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G369" t="n">
-        <v>2.41372680664062</v>
+        <v>2.41372656822205</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>2.42009520530701</v>
+        <v>2.42009472846985</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G371" t="n">
-        <v>2.4965193271637</v>
+        <v>2.49651908874512</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G372" t="n">
-        <v>2.4965193271637</v>
+        <v>2.49651908874512</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G374" t="n">
-        <v>2.46786022186279</v>
+        <v>2.46785974502563</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G375" t="n">
-        <v>2.43124055862427</v>
+        <v>2.43124008178711</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G376" t="n">
-        <v>2.41531825065613</v>
+        <v>2.41531848907471</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G377" t="n">
-        <v>2.41531825065613</v>
+        <v>2.41531848907471</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G379" t="n">
-        <v>2.41213393211365</v>
+        <v>2.41213417053223</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G380" t="n">
-        <v>2.44397735595703</v>
+        <v>2.44397783279419</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.41213393211365</v>
+        <v>2.41213417053223</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.42805600166321</v>
+        <v>2.42805624008179</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G386" t="n">
-        <v>2.38984370231628</v>
+        <v>2.38984417915344</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G387" t="n">
-        <v>2.39461994171143</v>
+        <v>2.39462041854858</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G389" t="n">
-        <v>2.42646384239197</v>
+        <v>2.42646360397339</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.43601679801941</v>
+        <v>2.43601703643799</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G392" t="n">
-        <v>2.44716191291809</v>
+        <v>2.44716143608093</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G393" t="n">
-        <v>2.50129556655884</v>
+        <v>2.501296043396</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G394" t="n">
-        <v>2.45989918708801</v>
+        <v>2.45989942550659</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G395" t="n">
-        <v>2.51084876060486</v>
+        <v>2.51084899902344</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G399" t="n">
-        <v>2.42805600166321</v>
+        <v>2.42805624008179</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G400" t="n">
-        <v>2.42805600166321</v>
+        <v>2.42805624008179</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G402" t="n">
-        <v>2.46626782417297</v>
+        <v>2.46626806259155</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>2.39621257781982</v>
+        <v>2.3962128162384</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G404" t="n">
-        <v>2.36755323410034</v>
+        <v>2.36755347251892</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G406" t="n">
-        <v>2.36755323410034</v>
+        <v>2.36755347251892</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G407" t="n">
-        <v>2.354816198349</v>
+        <v>2.35481643676758</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G411" t="n">
-        <v>2.36118507385254</v>
+        <v>2.36118483543396</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G413" t="n">
-        <v>2.27679991722107</v>
+        <v>2.27680015563965</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G414" t="n">
-        <v>2.26724696159363</v>
+        <v>2.26724720001221</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G416" t="n">
-        <v>2.33571004867554</v>
+        <v>2.33571028709412</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G417" t="n">
-        <v>2.33571004867554</v>
+        <v>2.33571028709412</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G418" t="n">
-        <v>2.28157663345337</v>
+        <v>2.28157639503479</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G419" t="n">
-        <v>2.28316855430603</v>
+        <v>2.28316879272461</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G421" t="n">
-        <v>2.33730244636536</v>
+        <v>2.33730220794678</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G423" t="n">
-        <v>2.34844779968262</v>
+        <v>2.34844756126404</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="n">
-        <v>2.30864381790161</v>
+        <v>2.30864357948303</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G426" t="n">
-        <v>2.34844779968262</v>
+        <v>2.34844756126404</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G427" t="n">
-        <v>2.34844779968262</v>
+        <v>2.34844756126404</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G429" t="n">
-        <v>2.40258121490479</v>
+        <v>2.40258145332336</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G430" t="n">
-        <v>2.39461994171143</v>
+        <v>2.39462041854858</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43920087814331</v>
+        <v>2.43920135498047</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G432" t="n">
-        <v>2.46786022186279</v>
+        <v>2.46785974502563</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G433" t="n">
-        <v>2.52677035331726</v>
+        <v>2.52677059173584</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>2.54746842384338</v>
+        <v>2.54746866226196</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G436" t="n">
-        <v>2.54746842384338</v>
+        <v>2.54746866226196</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G437" t="n">
-        <v>2.59682607650757</v>
+        <v>2.59682631492615</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G438" t="n">
-        <v>2.54746842384338</v>
+        <v>2.54746866226196</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G439" t="n">
-        <v>2.55065274238586</v>
+        <v>2.55065298080444</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G440" t="n">
-        <v>2.58568048477173</v>
+        <v>2.58568024635315</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G441" t="n">
-        <v>2.58568048477173</v>
+        <v>2.58568024635315</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G442" t="n">
-        <v>2.59364151954651</v>
+        <v>2.59364128112793</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G443" t="n">
-        <v>2.56498217582703</v>
+        <v>2.56498241424561</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G444" t="n">
-        <v>2.60000991821289</v>
+        <v>2.60001015663147</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G446" t="n">
-        <v>2.60000991821289</v>
+        <v>2.60001015663147</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G450" t="n">
-        <v>2.60637903213501</v>
+        <v>2.60637879371643</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G454" t="n">
-        <v>2.56020617485046</v>
+        <v>2.56020593643188</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G456" t="n">
-        <v>2.63822197914124</v>
+        <v>2.63822221755981</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G457" t="n">
-        <v>2.73056793212891</v>
+        <v>2.73056769371033</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G460" t="n">
-        <v>2.72419929504395</v>
+        <v>2.72419905662537</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G461" t="n">
-        <v>2.74012088775635</v>
+        <v>2.74012064933777</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G463" t="n">
-        <v>2.72101473808289</v>
+        <v>2.72101497650146</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G465" t="n">
-        <v>2.79903078079224</v>
+        <v>2.79903125762939</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G466" t="n">
-        <v>2.8022153377533</v>
+        <v>2.80221509933472</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G467" t="n">
-        <v>2.81813716888428</v>
+        <v>2.8181369304657</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>2.84998059272766</v>
+        <v>2.8499801158905</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G469" t="n">
-        <v>2.88978457450867</v>
+        <v>2.88978433609009</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G470" t="n">
-        <v>2.88978457450867</v>
+        <v>2.88978433609009</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G472" t="n">
-        <v>2.92640471458435</v>
+        <v>2.92640447616577</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G473" t="n">
-        <v>2.89296865463257</v>
+        <v>2.89296889305115</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G474" t="n">
-        <v>2.92958879470825</v>
+        <v>2.92958903312683</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>2.93754982948303</v>
+        <v>2.93754959106445</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G478" t="n">
-        <v>2.81017589569092</v>
+        <v>2.8101761341095</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>3.4539999961853</v>
       </c>
       <c r="G479" t="n">
-        <v>2.74967360496521</v>
+        <v>2.74967408180237</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G481" t="n">
-        <v>2.54746842384338</v>
+        <v>2.54746866226196</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.4917426109314</v>
+        <v>2.49174284934998</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>2.46786022186279</v>
+        <v>2.46785974502563</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G485" t="n">
-        <v>2.46786022186279</v>
+        <v>2.46785974502563</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G486" t="n">
-        <v>2.48537373542786</v>
+        <v>2.48537397384644</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G487" t="n">
-        <v>2.45989918708801</v>
+        <v>2.45989942550659</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G488" t="n">
-        <v>2.44238543510437</v>
+        <v>2.44238519668579</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G489" t="n">
-        <v>2.46786022186279</v>
+        <v>2.46785974502563</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G490" t="n">
-        <v>2.43760895729065</v>
+        <v>2.43760919570923</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G491" t="n">
-        <v>2.44716191291809</v>
+        <v>2.44716143608093</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G492" t="n">
-        <v>2.44716191291809</v>
+        <v>2.44716143608093</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G494" t="n">
-        <v>2.51721739768982</v>
+        <v>2.51721692085266</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G495" t="n">
-        <v>2.53632354736328</v>
+        <v>2.5363233089447</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>2.4837818145752</v>
+        <v>2.48378157615662</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G499" t="n">
-        <v>2.5204017162323</v>
+        <v>2.52040147781372</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G502" t="n">
-        <v>2.55383729934692</v>
+        <v>2.55383706092834</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>2.5076642036438</v>
+        <v>2.50766444206238</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G505" t="n">
-        <v>2.51562523841858</v>
+        <v>2.51562547683716</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G508" t="n">
-        <v>2.51084876060486</v>
+        <v>2.51084899902344</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G509" t="n">
-        <v>2.52995467185974</v>
+        <v>2.529953956604</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G511" t="n">
-        <v>2.56179761886597</v>
+        <v>2.56179785728455</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G512" t="n">
-        <v>2.59364151954651</v>
+        <v>2.59364128112793</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G515" t="n">
-        <v>2.65892004966736</v>
+        <v>2.65892028808594</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G516" t="n">
-        <v>2.75604200363159</v>
+        <v>2.75604248046875</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G517" t="n">
-        <v>2.72579169273376</v>
+        <v>2.72579145431519</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G518" t="n">
-        <v>2.74808168411255</v>
+        <v>2.74808192253113</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G519" t="n">
-        <v>2.74012088775635</v>
+        <v>2.74012064933777</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G520" t="n">
-        <v>2.75604200363159</v>
+        <v>2.75604248046875</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G522" t="n">
-        <v>2.63822197914124</v>
+        <v>2.63822221755981</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G523" t="n">
-        <v>2.63503789901733</v>
+        <v>2.63503766059875</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G524" t="n">
-        <v>2.63663029670715</v>
+        <v>2.63663005828857</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G527" t="n">
-        <v>2.62070822715759</v>
+        <v>2.62070846557617</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G528" t="n">
-        <v>2.54746842384338</v>
+        <v>2.54746866226196</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G529" t="n">
-        <v>2.56816673278809</v>
+        <v>2.56816649436951</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G530" t="n">
-        <v>2.54109954833984</v>
+        <v>2.54109978675842</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G531" t="n">
-        <v>2.56816673278809</v>
+        <v>2.56816649436951</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G534" t="n">
-        <v>2.54746842384338</v>
+        <v>2.54746866226196</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G535" t="n">
-        <v>2.41213393211365</v>
+        <v>2.41213417053223</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G538" t="n">
-        <v>2.2131130695343</v>
+        <v>2.21311330795288</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G539" t="n">
-        <v>2.12872886657715</v>
+        <v>2.12872862815857</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G540" t="n">
-        <v>2.07618689537048</v>
+        <v>2.07618713378906</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>2.05389666557312</v>
+        <v>2.05389618873596</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G545" t="n">
-        <v>2.073002576828</v>
+        <v>2.07300281524658</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G548" t="n">
-        <v>2.10643839836121</v>
+        <v>2.10643815994263</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G553" t="n">
-        <v>1.98702561855316</v>
+        <v>1.98702538013458</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G554" t="n">
-        <v>1.94881355762482</v>
+        <v>1.94881331920624</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90741717815399</v>
+        <v>1.90741693973541</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G556" t="n">
-        <v>1.89786398410797</v>
+        <v>1.89786410331726</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>2.00613117218018</v>
+        <v>2.00613141059875</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G558" t="n">
-        <v>2.01090836524963</v>
+        <v>2.01090788841248</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G564" t="n">
-        <v>1.86442875862122</v>
+        <v>1.86442828178406</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G566" t="n">
-        <v>2.01886892318726</v>
+        <v>2.01886916160583</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G567" t="n">
-        <v>1.99976313114166</v>
+        <v>1.9997626543045</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G568" t="n">
-        <v>1.93766820430756</v>
+        <v>1.93766832351685</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>1.85487568378448</v>
+        <v>1.85487520694733</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94562911987305</v>
+        <v>1.94562935829163</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G572" t="n">
-        <v>1.912193775177</v>
+        <v>1.91219365596771</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G573" t="n">
-        <v>1.92015409469604</v>
+        <v>1.92015433311462</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G577" t="n">
-        <v>1.95199763774872</v>
+        <v>1.95199739933014</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G578" t="n">
-        <v>1.92015409469604</v>
+        <v>1.92015433311462</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.92652332782745</v>
+        <v>1.92652320861816</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G580" t="n">
-        <v>1.92970740795135</v>
+        <v>1.92970752716064</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>1.90264058113098</v>
+        <v>1.9026403427124</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G582" t="n">
-        <v>1.90423262119293</v>
+        <v>1.90423250198364</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G583" t="n">
-        <v>1.89627170562744</v>
+        <v>1.89627158641815</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G585" t="n">
-        <v>1.85487568378448</v>
+        <v>1.85487520694733</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G586" t="n">
-        <v>1.85009872913361</v>
+        <v>1.8500988483429</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G587" t="n">
-        <v>1.86283648014069</v>
+        <v>1.8628363609314</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>1.8309930562973</v>
+        <v>1.83099317550659</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G589" t="n">
-        <v>1.81507134437561</v>
+        <v>1.81507110595703</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G590" t="n">
-        <v>1.81507134437561</v>
+        <v>1.81507110595703</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G591" t="n">
-        <v>1.80392611026764</v>
+        <v>1.80392599105835</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G592" t="n">
-        <v>1.76412189006805</v>
+        <v>1.76412200927734</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G593" t="n">
-        <v>1.78004372119904</v>
+        <v>1.78004360198975</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G596" t="n">
-        <v>1.89149522781372</v>
+        <v>1.89149510860443</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>1.85487568378448</v>
+        <v>1.85487520694733</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G599" t="n">
-        <v>1.85169112682343</v>
+        <v>1.85169148445129</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G601" t="n">
-        <v>1.82621645927429</v>
+        <v>1.82621657848358</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>1.83576929569244</v>
+        <v>1.83576965332031</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.85487568378448</v>
+        <v>1.85487520694733</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G606" t="n">
-        <v>1.80074203014374</v>
+        <v>1.80074179172516</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.77526700496674</v>
+        <v>1.7752673625946</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G608" t="n">
-        <v>1.83642709255219</v>
+        <v>1.83642721176147</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G609" t="n">
-        <v>1.82501029968262</v>
+        <v>1.82501041889191</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>1.81848680973053</v>
+        <v>1.81848692893982</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G611" t="n">
-        <v>1.8217488527298</v>
+        <v>1.82174873352051</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G612" t="n">
-        <v>1.78423726558685</v>
+        <v>1.78423702716827</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>1.72878563404083</v>
+        <v>1.72878575325012</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G614" t="n">
-        <v>1.73367846012115</v>
+        <v>1.73367834091187</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G615" t="n">
-        <v>1.72878563404083</v>
+        <v>1.72878575325012</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G617" t="n">
-        <v>1.78586828708649</v>
+        <v>1.7858681678772</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G618" t="n">
-        <v>1.7581422328949</v>
+        <v>1.75814235210419</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G622" t="n">
-        <v>1.73857128620148</v>
+        <v>1.7385710477829</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G626" t="n">
-        <v>1.84458184242249</v>
+        <v>1.84458160400391</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>1.86741483211517</v>
+        <v>1.86741471290588</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G628" t="n">
-        <v>1.84458184242249</v>
+        <v>1.84458160400391</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G629" t="n">
-        <v>1.84947431087494</v>
+        <v>1.84947419166565</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G630" t="n">
-        <v>1.82664155960083</v>
+        <v>1.82664132118225</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G631" t="n">
-        <v>1.76466608047485</v>
+        <v>1.76466619968414</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G632" t="n">
-        <v>1.79239177703857</v>
+        <v>1.79239189624786</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G633" t="n">
-        <v>1.7548805475235</v>
+        <v>1.75488030910492</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G634" t="n">
-        <v>1.77282071113586</v>
+        <v>1.77282059192657</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G636" t="n">
-        <v>1.74346387386322</v>
+        <v>1.74346423149109</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G637" t="n">
-        <v>1.82011759281158</v>
+        <v>1.82011795043945</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G639" t="n">
-        <v>1.89187860488892</v>
+        <v>1.89187836647034</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G640" t="n">
-        <v>1.81359386444092</v>
+        <v>1.81359398365021</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G641" t="n">
-        <v>1.86578369140625</v>
+        <v>1.86578381061554</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>1.87720000743866</v>
+        <v>1.87720012664795</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G643" t="n">
-        <v>1.90655696392059</v>
+        <v>1.90655708312988</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G645" t="n">
-        <v>1.84295034408569</v>
+        <v>1.84295058250427</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>1.86741483211517</v>
+        <v>1.86741471290588</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G647" t="n">
-        <v>1.82827270030975</v>
+        <v>1.82827234268188</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G648" t="n">
-        <v>1.81685590744019</v>
+        <v>1.8168557882309</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G649" t="n">
-        <v>1.81196284294128</v>
+        <v>1.81196296215057</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>1.81848680973053</v>
+        <v>1.81848692893982</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G651" t="n">
-        <v>1.79239177703857</v>
+        <v>1.79239189624786</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G653" t="n">
-        <v>1.77282071113586</v>
+        <v>1.77282059192657</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78749895095825</v>
+        <v>1.78749907016754</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>1.75324940681458</v>
+        <v>1.75324952602386</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G656" t="n">
-        <v>1.73857128620148</v>
+        <v>1.7385710477829</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G659" t="n">
-        <v>1.84295034408569</v>
+        <v>1.84295058250427</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G660" t="n">
-        <v>1.84131968021393</v>
+        <v>1.84131956100464</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G661" t="n">
-        <v>1.82337975502014</v>
+        <v>1.82337963581085</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G662" t="n">
-        <v>1.79239177703857</v>
+        <v>1.79239189624786</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G663" t="n">
-        <v>1.79076111316681</v>
+        <v>1.79076135158539</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G664" t="n">
-        <v>1.82011759281158</v>
+        <v>1.82011795043945</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G665" t="n">
-        <v>1.89187860488892</v>
+        <v>1.89187836647034</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G668" t="n">
-        <v>1.86415278911591</v>
+        <v>1.8641529083252</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G669" t="n">
-        <v>1.85762917995453</v>
+        <v>1.85762906074524</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G670" t="n">
-        <v>1.87556946277618</v>
+        <v>1.87556934356689</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G678" t="n">
-        <v>1.89024782180786</v>
+        <v>1.89024758338928</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G679" t="n">
-        <v>1.86415278911591</v>
+        <v>1.8641529083252</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G680" t="n">
-        <v>1.81359386444092</v>
+        <v>1.81359398365021</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71084558963776</v>
+        <v>1.71084547042847</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G682" t="n">
-        <v>1.76466608047485</v>
+        <v>1.76466619968414</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G683" t="n">
-        <v>1.73367846012115</v>
+        <v>1.73367834091187</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82337975502014</v>
+        <v>1.82337963581085</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>1.82664155960083</v>
+        <v>1.82664132118225</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G686" t="n">
-        <v>1.85436701774597</v>
+        <v>1.85436737537384</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G689" t="n">
-        <v>1.91308081150055</v>
+        <v>1.91308057308197</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G691" t="n">
-        <v>1.86415278911591</v>
+        <v>1.8641529083252</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G693" t="n">
-        <v>1.84295034408569</v>
+        <v>1.84295058250427</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G694" t="n">
-        <v>1.81685590744019</v>
+        <v>1.8168557882309</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>1.81359386444092</v>
+        <v>1.81359398365021</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G697" t="n">
-        <v>1.7940229177475</v>
+        <v>1.79402303695679</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G698" t="n">
-        <v>1.78749895095825</v>
+        <v>1.78749907016754</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G699" t="n">
-        <v>1.75324940681458</v>
+        <v>1.75324952602386</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>1.75324940681458</v>
+        <v>1.75324952602386</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G701" t="n">
-        <v>1.73041641712189</v>
+        <v>1.73041653633118</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G708" t="n">
-        <v>1.57384717464447</v>
+        <v>1.57384729385376</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>1.48006892204285</v>
+        <v>1.48006880283356</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G712" t="n">
-        <v>1.48496174812317</v>
+        <v>1.48496162891388</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G713" t="n">
-        <v>1.53225862979889</v>
+        <v>1.5322585105896</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G715" t="n">
-        <v>1.4857771396637</v>
+        <v>1.48577702045441</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>1.45968222618103</v>
+        <v>1.45968210697174</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>1.53388965129852</v>
+        <v>1.53388953208923</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G722" t="n">
-        <v>1.60483503341675</v>
+        <v>1.60483491420746</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G723" t="n">
-        <v>1.57874000072479</v>
+        <v>1.5787398815155</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G724" t="n">
-        <v>1.58852577209473</v>
+        <v>1.58852565288544</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G725" t="n">
-        <v>1.62032890319824</v>
+        <v>1.62032878398895</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092982769012</v>
+        <v>1.63092994689941</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G728" t="n">
-        <v>1.61706686019897</v>
+        <v>1.61706697940826</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G729" t="n">
-        <v>1.62685251235962</v>
+        <v>1.62685263156891</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092982769012</v>
+        <v>1.63092994689941</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G735" t="n">
-        <v>1.53144299983978</v>
+        <v>1.53144311904907</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G736" t="n">
-        <v>1.54285955429077</v>
+        <v>1.54285967350006</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G737" t="n">
-        <v>1.51676487922668</v>
+        <v>1.5167647600174</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G738" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G739" t="n">
-        <v>1.44581925868988</v>
+        <v>1.44581937789917</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G740" t="n">
-        <v>1.45234310626984</v>
+        <v>1.45234322547913</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G741" t="n">
-        <v>1.47191417217255</v>
+        <v>1.47191405296326</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G743" t="n">
-        <v>1.51676487922668</v>
+        <v>1.5167647600174</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G745" t="n">
-        <v>1.49800896644592</v>
+        <v>1.49800908565521</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G748" t="n">
-        <v>1.46049773693085</v>
+        <v>1.46049761772156</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G749" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G752" t="n">
-        <v>1.36345744132996</v>
+        <v>1.36345756053925</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G753" t="n">
-        <v>1.36345744132996</v>
+        <v>1.36345756053925</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G756" t="n">
-        <v>1.09272289276123</v>
+        <v>1.09272313117981</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>1.03564047813416</v>
+        <v>1.03564059734344</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G759" t="n">
-        <v>1.01525390148163</v>
+        <v>1.01525378227234</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G763" t="n">
-        <v>1.15469837188721</v>
+        <v>1.15469825267792</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G764" t="n">
-        <v>1.15388286113739</v>
+        <v>1.15388298034668</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G768" t="n">
-        <v>1.27620267868042</v>
+        <v>1.27620279788971</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G771" t="n">
-        <v>1.31208312511444</v>
+        <v>1.31208288669586</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G772" t="n">
-        <v>1.3031131029129</v>
+        <v>1.30311298370361</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G775" t="n">
-        <v>1.3601952791214</v>
+        <v>1.36019539833069</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G780" t="n">
-        <v>1.37813580036163</v>
+        <v>1.37813568115234</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G781" t="n">
-        <v>1.43521821498871</v>
+        <v>1.43521809577942</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G782" t="n">
-        <v>1.50942552089691</v>
+        <v>1.50942540168762</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G783" t="n">
-        <v>1.54693698883057</v>
+        <v>1.54693710803986</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G786" t="n">
-        <v>1.56650805473328</v>
+        <v>1.56650793552399</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G787" t="n">
-        <v>1.57547831535339</v>
+        <v>1.5754781961441</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.96300005912781</v>
       </c>
       <c r="G788" t="n">
-        <v>1.60075783729553</v>
+        <v>1.60075771808624</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G791" t="n">
-        <v>1.53878211975098</v>
+        <v>1.53878235816956</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G794" t="n">
-        <v>1.5208420753479</v>
+        <v>1.52084219455719</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G796" t="n">
-        <v>1.65539395809174</v>
+        <v>1.65539371967316</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G797" t="n">
-        <v>1.66681027412415</v>
+        <v>1.66681039333344</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G802" t="n">
-        <v>1.6814888715744</v>
+        <v>1.68148863315582</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G803" t="n">
-        <v>1.70595276355743</v>
+        <v>1.70595264434814</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G806" t="n">
-        <v>1.70269060134888</v>
+        <v>1.70269072055817</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G807" t="n">
-        <v>1.69616711139679</v>
+        <v>1.6961669921875</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G809" t="n">
-        <v>1.69942891597748</v>
+        <v>1.69942903518677</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G810" t="n">
-        <v>1.68964338302612</v>
+        <v>1.68964326381683</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G811" t="n">
-        <v>1.65865552425385</v>
+        <v>1.65865564346313</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G812" t="n">
-        <v>1.65865552425385</v>
+        <v>1.65865564346313</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G815" t="n">
-        <v>1.66681027412415</v>
+        <v>1.66681039333344</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G818" t="n">
-        <v>1.63582277297974</v>
+        <v>1.63582265377045</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G820" t="n">
-        <v>1.61054337024689</v>
+        <v>1.6105432510376</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G822" t="n">
-        <v>1.60157299041748</v>
+        <v>1.60157322883606</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G825" t="n">
-        <v>1.67496490478516</v>
+        <v>1.67496478557587</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G826" t="n">
-        <v>1.69127404689789</v>
+        <v>1.69127428531647</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G829" t="n">
-        <v>1.7043217420578</v>
+        <v>1.70432162284851</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G832" t="n">
-        <v>1.89187860488892</v>
+        <v>1.89187836647034</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G833" t="n">
-        <v>1.81196284294128</v>
+        <v>1.81196296215057</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G834" t="n">
-        <v>1.78260624408722</v>
+        <v>1.7826064825058</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G835" t="n">
-        <v>1.77771365642548</v>
+        <v>1.77771353721619</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>1.78586828708649</v>
+        <v>1.7858681678772</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G838" t="n">
-        <v>1.78586828708649</v>
+        <v>1.7858681678772</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G840" t="n">
-        <v>1.72063064575195</v>
+        <v>1.72063088417053</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G842" t="n">
-        <v>1.66028654575348</v>
+        <v>1.66028666496277</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G843" t="n">
-        <v>1.63908457756042</v>
+        <v>1.63908445835114</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G844" t="n">
-        <v>1.55182993412018</v>
+        <v>1.55182981491089</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G846" t="n">
-        <v>1.51676487922668</v>
+        <v>1.5167647600174</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G848" t="n">
-        <v>1.52328836917877</v>
+        <v>1.52328860759735</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G852" t="n">
-        <v>1.40830790996552</v>
+        <v>1.40830814838409</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G853" t="n">
-        <v>1.39852237701416</v>
+        <v>1.39852225780487</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G856" t="n">
-        <v>1.36345744132996</v>
+        <v>1.36345756053925</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G859" t="n">
-        <v>1.38139760494232</v>
+        <v>1.38139772415161</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G860" t="n">
-        <v>1.40830790996552</v>
+        <v>1.40830814838409</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G861" t="n">
-        <v>1.39281404018402</v>
+        <v>1.39281392097473</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G862" t="n">
-        <v>1.35204100608826</v>
+        <v>1.35204076766968</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G863" t="n">
-        <v>1.38221311569214</v>
+        <v>1.38221299648285</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G866" t="n">
-        <v>1.37487399578094</v>
+        <v>1.37487387657166</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>1.70899999141693</v>
       </c>
       <c r="G867" t="n">
-        <v>1.39362955093384</v>
+        <v>1.39362967014313</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G872" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G873" t="n">
-        <v>1.47925341129303</v>
+        <v>1.47925329208374</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.875</v>
       </c>
       <c r="G875" t="n">
-        <v>1.52899670600891</v>
+        <v>1.5289968252182</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G876" t="n">
-        <v>1.51268744468689</v>
+        <v>1.51268756389618</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>1.875</v>
       </c>
       <c r="G877" t="n">
-        <v>1.52899670600891</v>
+        <v>1.5289968252182</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G879" t="n">
-        <v>1.45234310626984</v>
+        <v>1.45234322547913</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G880" t="n">
-        <v>1.47436058521271</v>
+        <v>1.474360704422</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G881" t="n">
-        <v>1.45886671543121</v>
+        <v>1.45886659622192</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G882" t="n">
-        <v>1.45886671543121</v>
+        <v>1.45886659622192</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G884" t="n">
-        <v>1.42869460582733</v>
+        <v>1.42869448661804</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G888" t="n">
-        <v>1.44581925868988</v>
+        <v>1.44581937789917</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G890" t="n">
-        <v>1.46865224838257</v>
+        <v>1.46865236759186</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G892" t="n">
-        <v>1.58689486980438</v>
+        <v>1.58689475059509</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G894" t="n">
-        <v>1.57058537006378</v>
+        <v>1.57058548927307</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G896" t="n">
-        <v>1.51676487922668</v>
+        <v>1.5167647600174</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G897" t="n">
-        <v>1.50697922706604</v>
+        <v>1.50697934627533</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G898" t="n">
-        <v>1.46049773693085</v>
+        <v>1.46049761772156</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.43521821498871</v>
+        <v>1.43521809577942</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G900" t="n">
-        <v>1.3879212141037</v>
+        <v>1.38792133331299</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G901" t="n">
-        <v>1.33246958255768</v>
+        <v>1.33246970176697</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G907" t="n">
-        <v>1.37732017040253</v>
+        <v>1.37732028961182</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G908" t="n">
-        <v>1.35367178916931</v>
+        <v>1.35367166996002</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G912" t="n">
-        <v>1.50371718406677</v>
+        <v>1.50371730327606</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G913" t="n">
-        <v>1.50045526027679</v>
+        <v>1.50045537948608</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G918" t="n">
-        <v>1.48251509666443</v>
+        <v>1.48251533508301</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G920" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G923" t="n">
-        <v>1.45968222618103</v>
+        <v>1.45968210697174</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G925" t="n">
-        <v>1.45478940010071</v>
+        <v>1.45478951931</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G926" t="n">
-        <v>1.45234310626984</v>
+        <v>1.45234322547913</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G931" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G933" t="n">
-        <v>1.46865224838257</v>
+        <v>1.46865236759186</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G937" t="n">
-        <v>1.46131312847137</v>
+        <v>1.46131324768066</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G938" t="n">
-        <v>1.49474704265594</v>
+        <v>1.49474716186523</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G941" t="n">
-        <v>1.5795556306839</v>
+        <v>1.57955551147461</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.67170286178589</v>
+        <v>1.67170310020447</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G944" t="n">
-        <v>1.6765958070755</v>
+        <v>1.67659592628479</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G945" t="n">
-        <v>1.73041641712189</v>
+        <v>1.73041653633118</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>1.66354846954346</v>
+        <v>1.66354835033417</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G947" t="n">
-        <v>1.66517949104309</v>
+        <v>1.6651793718338</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G949" t="n">
-        <v>1.6814888715744</v>
+        <v>1.68148863315582</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G951" t="n">
-        <v>1.67496490478516</v>
+        <v>1.67496478557587</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G954" t="n">
-        <v>1.62685251235962</v>
+        <v>1.62685263156891</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G955" t="n">
-        <v>1.60401940345764</v>
+        <v>1.60401928424835</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G956" t="n">
-        <v>1.55916881561279</v>
+        <v>1.55916893482208</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G957" t="n">
-        <v>1.57547831535339</v>
+        <v>1.5754781961441</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G958" t="n">
-        <v>1.57058537006378</v>
+        <v>1.57058548927307</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G959" t="n">
-        <v>1.52247297763824</v>
+        <v>1.52247285842896</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G961" t="n">
-        <v>1.54285955429077</v>
+        <v>1.54285967350006</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G966" t="n">
-        <v>1.5795556306839</v>
+        <v>1.57955551147461</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G967" t="n">
-        <v>1.53878211975098</v>
+        <v>1.53878235816956</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G969" t="n">
-        <v>1.61135864257812</v>
+        <v>1.61135840415955</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.875</v>
       </c>
       <c r="G971" t="n">
-        <v>1.52899670600891</v>
+        <v>1.5289968252182</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G974" t="n">
-        <v>1.52002668380737</v>
+        <v>1.52002656459808</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G975" t="n">
-        <v>1.48740816116333</v>
+        <v>1.48740792274475</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G977" t="n">
-        <v>1.48985433578491</v>
+        <v>1.4898544549942</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G979" t="n">
-        <v>1.45968222618103</v>
+        <v>1.45968210697174</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>1.45968222618103</v>
+        <v>1.45968210697174</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G984" t="n">
-        <v>1.50942552089691</v>
+        <v>1.50942540168762</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G985" t="n">
-        <v>1.49556267261505</v>
+        <v>1.49556279182434</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G987" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G989" t="n">
-        <v>1.41320085525513</v>
+        <v>1.41320073604584</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G990" t="n">
-        <v>1.39036774635315</v>
+        <v>1.39036762714386</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.38221311569214</v>
+        <v>1.38221299648285</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G993" t="n">
-        <v>1.4311408996582</v>
+        <v>1.43114078044891</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G997" t="n">
-        <v>1.44337296485901</v>
+        <v>1.44337284564972</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G999" t="n">
-        <v>1.3846595287323</v>
+        <v>1.38465929031372</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.3919985294342</v>
+        <v>1.39199876785278</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.3919985294342</v>
+        <v>1.39199876785278</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.37487399578094</v>
+        <v>1.37487387657166</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.37487399578094</v>
+        <v>1.37487387657166</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.61699998378754</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.31860673427582</v>
+        <v>1.31860685348511</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.28843462467194</v>
+        <v>1.28843486309052</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.30474400520325</v>
+        <v>1.30474412441254</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.33328497409821</v>
+        <v>1.3332850933075</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.32431495189667</v>
+        <v>1.32431483268738</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.30474400520325</v>
+        <v>1.30474412441254</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.24521505832672</v>
+        <v>1.24521493911743</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.22075092792511</v>
+        <v>1.22075080871582</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.17834663391113</v>
+        <v>1.17834675312042</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.442999958992</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.17671585083008</v>
+        <v>1.1767156124115</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.21667373180389</v>
+        <v>1.2166736125946</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.47699999809265</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.2044415473938</v>
+        <v>1.20444166660309</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.20851910114288</v>
+        <v>1.2085188627243</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.21830439567566</v>
+        <v>1.21830463409424</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.47699999809265</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.2044415473938</v>
+        <v>1.20444166660309</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.08456838130951</v>
+        <v>1.0845685005188</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.12860333919525</v>
+        <v>1.12860357761383</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.08538365364075</v>
+        <v>1.08538377285004</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.03400945663452</v>
+        <v>1.0340096950531</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.03564047813416</v>
+        <v>1.03564059734344</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.98834353685379</v>
+        <v>0.988343477249146</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.920659840106964</v>
+        <v>0.920659780502319</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.760013341903687</v>
+        <v>0.760013282299042</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.564301669597626</v>
+        <v>0.564301788806915</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.588357925415039</v>
+        <v>0.58835780620575</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.593658447265625</v>
+        <v>0.59365850687027</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.738499999046326</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.602220773696899</v>
+        <v>0.602220833301544</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.02259290218353</v>
+        <v>1.02259314060211</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.937784731388092</v>
+        <v>0.937784671783447</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.918213546276093</v>
+        <v>0.918213605880737</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.870916485786438</v>
+        <v>0.870916545391083</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.913320779800415</v>
+        <v>0.913320660591125</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.95083224773407</v>
+        <v>0.95083212852478</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.939415633678436</v>
+        <v>0.939415574073792</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.960617661476135</v>
+        <v>0.96061772108078</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.12800002098083</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.919844508171082</v>
+        <v>0.919844388961792</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.956540405750275</v>
+        <v>0.956540286540985</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.02177751064301</v>
+        <v>1.02177762985229</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.02014684677124</v>
+        <v>1.02014660835266</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.06744349002838</v>
+        <v>1.06744360923767</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.08538365364075</v>
+        <v>1.08538377285004</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.08864557743073</v>
+        <v>1.08864569664001</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.08783030509949</v>
+        <v>1.08783006668091</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.09924685955048</v>
+        <v>1.09924697875977</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.11310970783234</v>
+        <v>1.11310958862305</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.09272289276123</v>
+        <v>1.09272313117981</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.08783030509949</v>
+        <v>1.08783006668091</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>1.34899997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.100062251091</v>
+        <v>1.10006213188171</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.04379487037659</v>
+        <v>1.04379498958588</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.979701220989227</v>
+        <v>0.979701101779938</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.988888561725616</v>
+        <v>0.988888442516327</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.991393983364105</v>
+        <v>0.991394102573395</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.05737566947937</v>
+        <v>1.05737555027008</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>1.22899997234344</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.02647280693054</v>
+        <v>1.02647292613983</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.0448477268219</v>
+        <v>1.04484748840332</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.24300003051758</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.038165807724</v>
+        <v>1.03816568851471</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.08243191242218</v>
+        <v>1.08243179321289</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.19518518447876</v>
+        <v>1.19518530368805</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.22859370708466</v>
+        <v>1.22859358787537</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.17012894153595</v>
+        <v>1.17012906074524</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.0891135931015</v>
+        <v>1.08911347389221</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.11082899570465</v>
+        <v>1.11082911491394</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.23026406764984</v>
+        <v>1.23026394844055</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.24028658866882</v>
+        <v>1.24028646945953</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.23026406764984</v>
+        <v>1.23026394844055</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>1.43700003623962</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.20019662380219</v>
+        <v>1.20019638538361</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.21439516544342</v>
+        <v>1.21439504623413</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.17597532272339</v>
+        <v>1.17597544193268</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.17764580249786</v>
+        <v>1.17764568328857</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.1659529209137</v>
+        <v>1.16595280170441</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.14006149768829</v>
+        <v>1.140061378479</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.17597532272339</v>
+        <v>1.17597544193268</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.23276960849762</v>
+        <v>1.23276972770691</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.19852614402771</v>
+        <v>1.19852602481842</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.17346966266632</v>
+        <v>1.17346978187561</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>1.42900002002716</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.19351482391357</v>
+        <v>1.19351494312286</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.43700003623962</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.20019662380219</v>
+        <v>1.20019638538361</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.10247707366943</v>
+        <v>1.10247695446014</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.28100001811981</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.06990373134613</v>
+        <v>1.06990385055542</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.970513701438904</v>
+        <v>0.970513761043549</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.08899998664856</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.909543454647064</v>
+        <v>0.909543395042419</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.935435056686401</v>
+        <v>0.935434997081757</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.886157512664795</v>
+        <v>0.88615757226944</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.896180152893066</v>
+        <v>0.896180093288422</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.918730854988098</v>
+        <v>0.918730914592743</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.935435056686401</v>
+        <v>0.935434997081757</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.13300001621246</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.946292638778687</v>
+        <v>0.946292698383331</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.953809559345245</v>
+        <v>0.953809499740601</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.93794059753418</v>
+        <v>0.937940657138824</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.918730854988098</v>
+        <v>0.918730914592743</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.910378754138947</v>
+        <v>0.910378694534302</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.908708333969116</v>
+        <v>0.908708274364471</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.90035605430603</v>
+        <v>0.900356113910675</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.905367434024811</v>
+        <v>0.905367374420166</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>1.08899998664856</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.909543454647064</v>
+        <v>0.909543395042419</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.918730854988098</v>
+        <v>0.918730914592743</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.901191294193268</v>
+        <v>0.901191353797913</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.905367434024811</v>
+        <v>0.905367374420166</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.914554834365845</v>
+        <v>0.9145547747612</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.937105298042297</v>
+        <v>0.937105417251587</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.10800004005432</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.925412476062775</v>
+        <v>0.925412595272064</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.912049114704132</v>
+        <v>0.912049233913422</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.890333771705627</v>
+        <v>0.890333652496338</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.892004013061523</v>
+        <v>0.892004072666168</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>0.993499994277954</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.829780995845795</v>
+        <v>0.82978093624115</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.834374606609344</v>
+        <v>0.8343745470047</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.992500007152557</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.828945696353912</v>
+        <v>0.828945755958557</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.0110000371933</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.844397068023682</v>
+        <v>0.844397127628326</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>1.02799999713898</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.858595669269562</v>
+        <v>0.858595728874207</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.898685812950134</v>
+        <v>0.89868575334549</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.884487211704254</v>
+        <v>0.884487152099609</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.875299870967865</v>
+        <v>0.87529981136322</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.868618249893188</v>
+        <v>0.868618190288544</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.863607048988342</v>
+        <v>0.863606989383698</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>0.997500002384186</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.833121776580811</v>
+        <v>0.833121836185455</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>0.981500029563904</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.819758534431458</v>
+        <v>0.819758474826813</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.768392980098724</v>
+        <v>0.768393039703369</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.767975449562073</v>
+        <v>0.767975389957428</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>0.962499976158142</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.803889453411102</v>
+        <v>0.803889393806458</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.794284522533417</v>
+        <v>0.794284462928772</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>0.966499984264374</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.807230174541473</v>
+        <v>0.807230234146118</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>0.993499994277954</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.829780995845795</v>
+        <v>0.82978093624115</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.856089949607849</v>
+        <v>0.856090009212494</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.924577295780182</v>
+        <v>0.924577176570892</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.964667320251465</v>
+        <v>0.96466737985611</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.951303958892822</v>
+        <v>0.951303899288177</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.957150459289551</v>
+        <v>0.95715057849884</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.0298136472702</v>
+        <v>1.02981376647949</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.07491505146027</v>
+        <v>1.07491481304169</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.07491505146027</v>
+        <v>1.07491481304169</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.0891135931015</v>
+        <v>1.08911347389221</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.06906843185425</v>
+        <v>1.06906855106354</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.06906843185425</v>
+        <v>1.06906855106354</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.07909095287323</v>
+        <v>1.07909119129181</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.04317700862885</v>
+        <v>1.04317688941956</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>1.20299994945526</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.00475740432739</v>
+        <v>1.0047572851181</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.0298136472702</v>
+        <v>1.02981376647949</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.21899998188019</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.01812076568604</v>
+        <v>1.01812064647675</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.01060402393341</v>
+        <v>1.01060378551483</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.998075783252716</v>
+        <v>0.998075664043427</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.951303958892822</v>
+        <v>0.951303899288177</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.967172801494598</v>
+        <v>0.967173039913177</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.991393983364105</v>
+        <v>0.991394102573395</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.987217903137207</v>
+        <v>0.987218022346497</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.965502560138702</v>
+        <v>0.965502440929413</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.27699995040894</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.06656301021576</v>
+        <v>1.06656289100647</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.05737566947937</v>
+        <v>1.05737555027008</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.03398990631104</v>
+        <v>1.03398978710175</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.2610000371933</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.05319952964783</v>
+        <v>1.05319964885712</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.05069410800934</v>
+        <v>1.05069398880005</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.05570507049561</v>
+        <v>1.0557051897049</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.06322205066681</v>
+        <v>1.06322193145752</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.06906843185425</v>
+        <v>1.06906855106354</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.07575023174286</v>
+        <v>1.07575011253357</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.06071639060974</v>
+        <v>1.06071650981903</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>1.25899994373322</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.05152904987335</v>
+        <v>1.05152916908264</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>1.2610000371933</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.05319952964783</v>
+        <v>1.05319964885712</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.22899997234344</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.02647280693054</v>
+        <v>1.02647292613983</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>1.24100005626678</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.03649544715881</v>
+        <v>1.03649532794952</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.05069410800934</v>
+        <v>1.05069398880005</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.06071639060974</v>
+        <v>1.06071650981903</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.09579527378082</v>
+        <v>1.09579515457153</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.1141699552536</v>
+        <v>1.11416983604431</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.2678484916687</v>
+        <v>1.26784861087799</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.41484546661377</v>
+        <v>1.41484534740448</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.37392008304596</v>
+        <v>1.37391996383667</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.37392008304596</v>
+        <v>1.37391996383667</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.37141442298889</v>
+        <v>1.37141454219818</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.30793857574463</v>
+        <v>1.30793845653534</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.29875123500824</v>
+        <v>1.29875111579895</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.33550047874451</v>
+        <v>1.33550035953522</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.37392008304596</v>
+        <v>1.37391996383667</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.4215270280838</v>
+        <v>1.42152714729309</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.44825375080109</v>
+        <v>1.44825387001038</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.40565812587738</v>
+        <v>1.40565824508667</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.44825375080109</v>
+        <v>1.44825387001038</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.43489050865173</v>
+        <v>1.43489062786102</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.47163951396942</v>
+        <v>1.47163963317871</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.44073700904846</v>
+        <v>1.44073688983917</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.50170731544495</v>
+        <v>1.50170719623566</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.56768894195557</v>
+        <v>1.56768882274628</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.54012668132782</v>
+        <v>1.54012680053711</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.52258729934692</v>
+        <v>1.52258741855621</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.52342283725739</v>
+        <v>1.5234227180481</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.5317747592926</v>
+        <v>1.53177487850189</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.51507067680359</v>
+        <v>1.5150705575943</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.51590597629547</v>
+        <v>1.51590585708618</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.50922417640686</v>
+        <v>1.50922405719757</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.52258729934692</v>
+        <v>1.52258741855621</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.60709416866302</v>
+        <v>1.60709428787231</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.57436656951904</v>
+        <v>1.57436668872833</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.56489288806915</v>
+        <v>1.56489300727844</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.56489288806915</v>
+        <v>1.56489300727844</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.57264423370361</v>
+        <v>1.57264411449432</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.65187919139862</v>
+        <v>1.65187931060791</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.61053931713104</v>
+        <v>1.61053919792175</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.66565918922424</v>
+        <v>1.66565942764282</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.80173707008362</v>
+        <v>1.80173695087433</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.77589952945709</v>
+        <v>1.7758994102478</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.83963179588318</v>
+        <v>1.83963191509247</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.79656958580017</v>
+        <v>1.79656946659088</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.7982919216156</v>
+        <v>1.79829180240631</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.86891436576843</v>
+        <v>1.86891448497772</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>2.25</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.93781459331512</v>
+        <v>1.93781447410583</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.94470465183258</v>
+        <v>1.94470453262329</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.94125974178314</v>
+        <v>1.94125962257385</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.91542208194733</v>
+        <v>1.91542196273804</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.9326468706131</v>
+        <v>1.93264710903168</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.93436968326569</v>
+        <v>1.9343695640564</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.89475202560425</v>
+        <v>1.89475226402283</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.88441705703735</v>
+        <v>1.88441693782806</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.83790946006775</v>
+        <v>1.83790957927704</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.82068467140198</v>
+        <v>1.82068455219269</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.85168945789337</v>
+        <v>1.85168957710266</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.85168945789337</v>
+        <v>1.85168957710266</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.83790946006775</v>
+        <v>1.83790957927704</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.85685670375824</v>
+        <v>1.85685694217682</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.90336441993713</v>
+        <v>1.90336453914642</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.91886699199677</v>
+        <v>1.91886711120605</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.90508699417114</v>
+        <v>1.90508711338043</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.90508699417114</v>
+        <v>1.90508711338043</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.9929347038269</v>
+        <v>1.99293446540833</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.01704978942871</v>
+        <v>2.01704955101013</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.11006498336792</v>
+        <v>2.11006474494934</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.92231214046478</v>
+        <v>1.92231225967407</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.94125974178314</v>
+        <v>1.94125962257385</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.94814944267273</v>
+        <v>1.94814968109131</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.9929347038269</v>
+        <v>1.99293446540833</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G1447" t="n">
-        <v>2.02221703529358</v>
+        <v>2.02221727371216</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.00499224662781</v>
+        <v>2.00499200820923</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.98259973526001</v>
+        <v>1.98259949684143</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.89475202560425</v>
+        <v>1.89475226402283</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.90680921077728</v>
+        <v>1.90680932998657</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.89475202560425</v>
+        <v>1.89475226402283</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.87580454349518</v>
+        <v>1.87580442428589</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.8551344871521</v>
+        <v>1.85513460636139</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.85168945789337</v>
+        <v>1.85168957710266</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.85685670375824</v>
+        <v>1.85685694217682</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.84824419021606</v>
+        <v>1.84824430942535</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.85685670375824</v>
+        <v>1.85685694217682</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.81723928451538</v>
+        <v>1.81723916530609</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.83790946006775</v>
+        <v>1.83790957927704</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.82757425308228</v>
+        <v>1.82757437229156</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1505" t="n">
-        <v>1.71388924121857</v>
+        <v>1.71388912200928</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.72766935825348</v>
+        <v>1.72766923904419</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.79656958580017</v>
+        <v>1.79656946659088</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.80173707008362</v>
+        <v>1.80173695087433</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.80862677097321</v>
+        <v>1.80862665176392</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.76039683818817</v>
+        <v>1.76039695739746</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.81379437446594</v>
+        <v>1.81379425525665</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.80862677097321</v>
+        <v>1.80862665176392</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.79484701156616</v>
+        <v>1.79484689235687</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.79140198230743</v>
+        <v>1.79140186309814</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.80518198013306</v>
+        <v>1.80518186092377</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.80518198013306</v>
+        <v>1.80518186092377</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.72077929973602</v>
+        <v>1.72077918052673</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.72766935825348</v>
+        <v>1.72766923904419</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.72077929973602</v>
+        <v>1.72077918052673</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.69149661064148</v>
+        <v>1.69149672985077</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.61742925643921</v>
+        <v>1.61742913722992</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>1.875</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.61484551429749</v>
+        <v>1.6148453950882</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.56661534309387</v>
+        <v>1.56661546230316</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.59589803218842</v>
+        <v>1.59589791297913</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.60020422935486</v>
+        <v>1.60020434856415</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.52010762691498</v>
+        <v>1.52010786533356</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.57436656951904</v>
+        <v>1.57436668872833</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.53302645683289</v>
+        <v>1.53302657604218</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.59331429004669</v>
+        <v>1.5933141708374</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.58986914157867</v>
+        <v>1.58986902236938</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.49599266052246</v>
+        <v>1.49599277973175</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.44776284694672</v>
+        <v>1.44776272773743</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.39781033992767</v>
+        <v>1.39781022071838</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.26431620121002</v>
+        <v>1.26431632041931</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1574" t="n">
-        <v>1.36938905715942</v>
+        <v>1.36938893795013</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.36594390869141</v>
+        <v>1.36594378948212</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.43656659126282</v>
+        <v>1.43656647205353</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.39005899429321</v>
+        <v>1.39005887508392</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.39092028141022</v>
+        <v>1.39092016220093</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.39005899429321</v>
+        <v>1.39005887508392</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1588" t="n">
-        <v>1.4348441362381</v>
+        <v>1.43484401702881</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.40986776351929</v>
+        <v>1.40986764431</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.3874751329422</v>
+        <v>1.38747525215149</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>1.58800005912781</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.3676666021347</v>
+        <v>1.36766648292542</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.38661408424377</v>
+        <v>1.38661396503448</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>1.69700002670288</v>
       </c>
       <c r="G1603" t="n">
-        <v>1.46154284477234</v>
+        <v>1.46154272556305</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.42795419692993</v>
+        <v>1.42795407772064</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.39092028141022</v>
+        <v>1.39092016220093</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>1.625</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.39953279495239</v>
+        <v>1.3995326757431</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.36938905715942</v>
+        <v>1.36938893795013</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.33580029010773</v>
+        <v>1.33580017089844</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1620" t="n">
-        <v>1.43656659126282</v>
+        <v>1.43656647205353</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>1.62699997425079</v>
       </c>
       <c r="G1623" t="n">
-        <v>1.40125524997711</v>
+        <v>1.40125513076782</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1624" t="n">
-        <v>1.39092028141022</v>
+        <v>1.39092016220093</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G1627" t="n">
-        <v>1.45957458019257</v>
+        <v>1.45957446098328</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1629" t="n">
-        <v>1.51217985153198</v>
+        <v>1.51217997074127</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G1631" t="n">
-        <v>1.50058877468109</v>
+        <v>1.50058889389038</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.47919023036957</v>
+        <v>1.47919011116028</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.4836483001709</v>
+        <v>1.48364818096161</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>1.45099997520447</v>
       </c>
       <c r="G1642" t="n">
-        <v>1.29373407363892</v>
+        <v>1.29373395442963</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G1644" t="n">
-        <v>1.29997551441193</v>
+        <v>1.29997539520264</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>1.5110000371933</v>
       </c>
       <c r="G1646" t="n">
-        <v>1.34723103046417</v>
+        <v>1.34723091125488</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G1648" t="n">
-        <v>1.29105925559998</v>
+        <v>1.29105913639069</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>1.47699999809265</v>
       </c>
       <c r="G1651" t="n">
-        <v>1.31691598892212</v>
+        <v>1.31691610813141</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>1.47899997234344</v>
       </c>
       <c r="G1653" t="n">
-        <v>1.31869924068451</v>
+        <v>1.3186993598938</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1654" t="n">
-        <v>1.28927612304688</v>
+        <v>1.28927600383759</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>1.47899997234344</v>
       </c>
       <c r="G1662" t="n">
-        <v>1.31869924068451</v>
+        <v>1.3186993598938</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>1.46099996566772</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.30265021324158</v>
+        <v>1.30265033245087</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>1.49500000476837</v>
       </c>
       <c r="G1665" t="n">
-        <v>1.33296513557434</v>
+        <v>1.33296525478363</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>1.43700003623962</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.28125154972076</v>
+        <v>1.28125143051147</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1673" t="n">
-        <v>1.29284262657166</v>
+        <v>1.29284250736237</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.31513285636902</v>
+        <v>1.31513297557831</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G1679" t="n">
-        <v>1.29105925559998</v>
+        <v>1.29105913639069</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.30443346500397</v>
+        <v>1.30443358421326</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.27946829795837</v>
+        <v>1.27946817874908</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1683" t="n">
-        <v>1.31156623363495</v>
+        <v>1.31156635284424</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>1.46899998188019</v>
       </c>
       <c r="G1686" t="n">
-        <v>1.30978310108185</v>
+        <v>1.30978322029114</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1687" t="n">
-        <v>1.28927612304688</v>
+        <v>1.28927600383759</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>1.442999958992</v>
       </c>
       <c r="G1688" t="n">
-        <v>1.28660118579865</v>
+        <v>1.28660106658936</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>1.39699995517731</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.24558687210083</v>
+        <v>1.24558675289154</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>1.42900002002716</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.27411866188049</v>
+        <v>1.2741185426712</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>1.41299998760223</v>
       </c>
       <c r="G1693" t="n">
-        <v>1.25985276699066</v>
+        <v>1.25985264778137</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.2527197599411</v>
+        <v>1.25271964073181</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>1.41100001335144</v>
       </c>
       <c r="G1703" t="n">
-        <v>1.25806951522827</v>
+        <v>1.25806939601898</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>1.37100005149841</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.22240483760834</v>
+        <v>1.22240495681763</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.14661741256714</v>
+        <v>1.14661753177643</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.11897730827332</v>
+        <v>1.1189774274826</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1720" t="n">
-        <v>1.15375053882599</v>
+        <v>1.15375065803528</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>1.28100001811981</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.14215934276581</v>
+        <v>1.1421594619751</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>1.21899998188019</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.08687937259674</v>
+        <v>1.08687925338745</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.22329652309418</v>
+        <v>1.22329640388489</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>1.36600005626678</v>
       </c>
       <c r="G1743" t="n">
-        <v>1.2179468870163</v>
+        <v>1.21794676780701</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.29284262657166</v>
+        <v>1.29284250736237</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.31513285636902</v>
+        <v>1.31513297557831</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.32494056224823</v>
+        <v>1.32494068145752</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.38200402259827</v>
+        <v>1.38200390338898</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.3534722328186</v>
+        <v>1.35347235202789</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1751" t="n">
-        <v>1.36060523986816</v>
+        <v>1.36060535907745</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.37130451202393</v>
+        <v>1.37130463123322</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.38913691043854</v>
+        <v>1.38913679122925</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1757" t="n">
-        <v>1.37130451202393</v>
+        <v>1.37130463123322</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.36060523986816</v>
+        <v>1.36060535907745</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>1.48599994182587</v>
       </c>
       <c r="G1764" t="n">
-        <v>1.32494056224823</v>
+        <v>1.32494068145752</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>1.47699999809265</v>
       </c>
       <c r="G1765" t="n">
-        <v>1.31691598892212</v>
+        <v>1.31691610813141</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>1.45899999141693</v>
       </c>
       <c r="G1767" t="n">
-        <v>1.30086696147919</v>
+        <v>1.3008668422699</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G1769" t="n">
-        <v>1.28927612304688</v>
+        <v>1.28927600383759</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1770" t="n">
-        <v>1.31513285636902</v>
+        <v>1.31513297557831</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G1771" t="n">
-        <v>1.29997551441193</v>
+        <v>1.29997539520264</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>1.41100001335144</v>
       </c>
       <c r="G1773" t="n">
-        <v>1.25806951522827</v>
+        <v>1.25806939601898</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>1.41299998760223</v>
       </c>
       <c r="G1776" t="n">
-        <v>1.25985276699066</v>
+        <v>1.25985264778137</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.23756229877472</v>
+        <v>1.23756217956543</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>1.41100001335144</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.25806951522827</v>
+        <v>1.25806939601898</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1788" t="n">
-        <v>1.29284262657166</v>
+        <v>1.29284250736237</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>1.46099996566772</v>
       </c>
       <c r="G1789" t="n">
-        <v>1.30265021324158</v>
+        <v>1.30265033245087</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>1.46899998188019</v>
       </c>
       <c r="G1791" t="n">
-        <v>1.30978310108185</v>
+        <v>1.30978322029114</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1803" t="n">
-        <v>1.48721468448639</v>
+        <v>1.4872145652771</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.51663792133331</v>
+        <v>1.5166380405426</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.51217985153198</v>
+        <v>1.51217997074127</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.52466249465942</v>
+        <v>1.52466261386871</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.53179550170898</v>
+        <v>1.53179562091827</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1819" t="n">
-        <v>1.55141091346741</v>
+        <v>1.5514110326767</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.51217985153198</v>
+        <v>1.51217997074127</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>1.73199999332428</v>
       </c>
       <c r="G1823" t="n">
-        <v>1.54427802562714</v>
+        <v>1.54427814483643</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1827" t="n">
-        <v>1.55141091346741</v>
+        <v>1.5514110326767</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G1829" t="n">
-        <v>1.57459306716919</v>
+        <v>1.5745929479599</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1830" t="n">
-        <v>1.57637619972229</v>
+        <v>1.576376080513</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.54606115818024</v>
+        <v>1.54606127738953</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>1.70899999141693</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.52377080917358</v>
+        <v>1.52377092838287</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.4078608751297</v>
+        <v>1.40786099433899</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1847" t="n">
-        <v>1.87239253520966</v>
+        <v>1.87239241600037</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G1849" t="n">
-        <v>1.86525988578796</v>
+        <v>1.86525976657867</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1850" t="n">
-        <v>1.87774229049683</v>
+        <v>1.87774217128754</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.76004886627197</v>
+        <v>1.76004898548126</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G1858" t="n">
-        <v>1.76896524429321</v>
+        <v>1.76896512508392</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.73865020275116</v>
+        <v>1.73865032196045</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.71101009845734</v>
+        <v>1.71101021766663</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.73865020275116</v>
+        <v>1.73865032196045</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.71279323101044</v>
+        <v>1.71279335021973</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.77431488037109</v>
+        <v>1.7743147611618</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.76896524429321</v>
+        <v>1.76896512508392</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.72768151760101</v>
+        <v>1.72768139839172</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.73135352134705</v>
+        <v>1.73135340213776</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.74420559406281</v>
+        <v>1.74420547485352</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.71391141414642</v>
+        <v>1.71391129493713</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.70105946063995</v>
+        <v>1.70105934143066</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.68820738792419</v>
+        <v>1.6882072687149</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.71299338340759</v>
+        <v>1.71299350261688</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.69371545314789</v>
+        <v>1.6937153339386</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.56703090667725</v>
+        <v>1.56703102588654</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.55693280696869</v>
+        <v>1.55693292617798</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>1.68700003623962</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.54867076873779</v>
+        <v>1.54867088794708</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.61384904384613</v>
+        <v>1.61384916305542</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.70656740665436</v>
+        <v>1.70656728744507</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.6716833114624</v>
+        <v>1.67168319225311</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.67076528072357</v>
+        <v>1.67076516151428</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1923" t="n">
-        <v>1.67076528072357</v>
+        <v>1.67076516151428</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.61201310157776</v>
+        <v>1.61201322078705</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G1935" t="n">
-        <v>1.62302911281586</v>
+        <v>1.62302899360657</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1937" t="n">
-        <v>1.59181690216064</v>
+        <v>1.59181702136993</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1939" t="n">
-        <v>1.59181690216064</v>
+        <v>1.59181702136993</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1943" t="n">
-        <v>1.53673696517944</v>
+        <v>1.53673684597015</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.54958879947662</v>
+        <v>1.54958891868591</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1946" t="n">
-        <v>1.53306484222412</v>
+        <v>1.53306472301483</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.51562285423279</v>
+        <v>1.5156227350235</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.55601489543915</v>
+        <v>1.55601501464844</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>1.8860000371933</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.73135352134705</v>
+        <v>1.73135340213776</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G1953" t="n">
-        <v>1.72859954833984</v>
+        <v>1.72859942913055</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.67351925373077</v>
+        <v>1.67351913452148</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.65056920051575</v>
+        <v>1.65056908130646</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.65056920051575</v>
+        <v>1.65056908130646</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>1.78199994564056</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.63588118553162</v>
+        <v>1.63588106632233</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.56978487968445</v>
+        <v>1.56978499889374</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.53765487670898</v>
+        <v>1.53765475749969</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>1.67400002479553</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.53673696517944</v>
+        <v>1.53673684597015</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.54499876499176</v>
+        <v>1.54499888420105</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1973" t="n">
-        <v>1.54683470726013</v>
+        <v>1.54683482646942</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>1.64300000667572</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.50827884674072</v>
+        <v>1.50827872753143</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>1.69900000095367</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.55968677997589</v>
+        <v>1.55968689918518</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1981" t="n">
-        <v>1.55693280696869</v>
+        <v>1.55693292617798</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G1985" t="n">
-        <v>1.54499876499176</v>
+        <v>1.54499888420105</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52031,7 +52031,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G1987" t="n">
-        <v>1.51562285423279</v>
+        <v>1.5156227350235</v>
       </c>
       <c r="H1987" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.4825747013092</v>
+        <v>1.48257458209991</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.56244087219238</v>
+        <v>1.56244099140167</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>1.70899999141693</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.56886684894562</v>
+        <v>1.56886696815491</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G2005" t="n">
-        <v>1.66250312328339</v>
+        <v>1.66250324249268</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G2006" t="n">
-        <v>1.68820738792419</v>
+        <v>1.6882072687149</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>1.875</v>
       </c>
       <c r="G2012" t="n">
-        <v>1.72125542163849</v>
+        <v>1.7212553024292</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52707,7 +52707,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G2013" t="n">
-        <v>1.72217357158661</v>
+        <v>1.72217345237732</v>
       </c>
       <c r="H2013" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G2019" t="n">
-        <v>1.70564937591553</v>
+        <v>1.70564949512482</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>1.87600004673004</v>
       </c>
       <c r="G2020" t="n">
-        <v>1.72217357158661</v>
+        <v>1.72217345237732</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G2021" t="n">
-        <v>1.72768151760101</v>
+        <v>1.72768139839172</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2027" t="n">
-        <v>1.74420559406281</v>
+        <v>1.74420547485352</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G2028" t="n">
-        <v>1.74604153633118</v>
+        <v>1.74604141712189</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.72400951385498</v>
+        <v>1.72400939464569</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G2032" t="n">
-        <v>1.68637132644653</v>
+        <v>1.68637120723724</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G2046" t="n">
-        <v>1.72859954833984</v>
+        <v>1.72859942913055</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>1.95799994468689</v>
       </c>
       <c r="G2057" t="n">
-        <v>1.79744958877563</v>
+        <v>1.79744970798492</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>1.95099997520447</v>
       </c>
       <c r="G2058" t="n">
-        <v>1.7910236120224</v>
+        <v>1.79102373123169</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G2059" t="n">
-        <v>1.76256549358368</v>
+        <v>1.76256561279297</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.73594355583191</v>
+        <v>1.73594343662262</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2062" t="n">
-        <v>1.74420559406281</v>
+        <v>1.74420547485352</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G2067" t="n">
-        <v>1.72859954833984</v>
+        <v>1.72859942913055</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G2073" t="n">
-        <v>1.74420559406281</v>
+        <v>1.74420547485352</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>1.89100003242493</v>
       </c>
       <c r="G2074" t="n">
-        <v>1.73594355583191</v>
+        <v>1.73594343662262</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54319,7 +54319,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2075" t="n">
-        <v>1.72584557533264</v>
+        <v>1.72584545612335</v>
       </c>
       <c r="H2075" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.74236953258514</v>
+        <v>1.74236941337585</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.83416986465454</v>
+        <v>1.83416974544525</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>1.98099994659424</v>
       </c>
       <c r="G2081" t="n">
-        <v>1.81856369972229</v>
+        <v>1.81856381893158</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2082" t="n">
-        <v>2.01960635185242</v>
+        <v>2.019606590271</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G2083" t="n">
-        <v>2.03613042831421</v>
+        <v>2.03613018989563</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2084" t="n">
-        <v>2.09304666519165</v>
+        <v>2.09304642677307</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54631,7 +54631,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G2087" t="n">
-        <v>2.19402718544006</v>
+        <v>2.19402694702148</v>
       </c>
       <c r="H2087" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G2089" t="n">
-        <v>2.25277924537659</v>
+        <v>2.25277900695801</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G2091" t="n">
-        <v>2.19769906997681</v>
+        <v>2.19769883155823</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G2093" t="n">
-        <v>2.28582715988159</v>
+        <v>2.28582739830017</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -55073,7 +55073,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.09304666519165</v>
+        <v>2.09304642677307</v>
       </c>
       <c r="H2104" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.10773468017578</v>
+        <v>2.1077344417572</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55255,7 +55255,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G2111" t="n">
-        <v>2.07101464271545</v>
+        <v>2.07101440429688</v>
       </c>
       <c r="H2111" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G2117" t="n">
-        <v>1.9883941411972</v>
+        <v>1.98839426040649</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G2120" t="n">
-        <v>2.16832304000854</v>
+        <v>2.16832280158997</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G2122" t="n">
-        <v>2.13527464866638</v>
+        <v>2.13527488708496</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G2123" t="n">
-        <v>2.16465091705322</v>
+        <v>2.16465067863464</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55593,7 +55593,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G2124" t="n">
-        <v>2.17933917045593</v>
+        <v>2.17933893203735</v>
       </c>
       <c r="H2124" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G2127" t="n">
-        <v>2.19219088554382</v>
+        <v>2.19219064712524</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G2129" t="n">
-        <v>2.21238708496094</v>
+        <v>2.21238684654236</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G2130" t="n">
-        <v>2.19219088554382</v>
+        <v>2.19219064712524</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.19769906997681</v>
+        <v>2.19769883155823</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>1.87000000476837</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>2121333</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>1.90900003910065</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>1.87600004673004</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>1.89400005340576</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>1.90799999237061</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>1.90799999237061</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9959831237793</v>
+        <v>2.99598336219788</v>
       </c>
       <c r="H2" t="n">
         <v>726355</v>
@@ -456,7 +456,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91082620620728</v>
+        <v>2.91082644462585</v>
       </c>
       <c r="H3" t="n">
         <v>1077659</v>
@@ -543,7 +543,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78541302680969</v>
+        <v>2.78541278839111</v>
       </c>
       <c r="H6" t="n">
         <v>761745</v>
@@ -572,7 +572,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>2.75599503517151</v>
+        <v>2.75599527359009</v>
       </c>
       <c r="H7" t="n">
         <v>914159</v>
@@ -601,7 +601,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76218867301941</v>
+        <v>2.76218819618225</v>
       </c>
       <c r="H8" t="n">
         <v>789466</v>
@@ -630,7 +630,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G9" t="n">
-        <v>2.75289821624756</v>
+        <v>2.75289797782898</v>
       </c>
       <c r="H9" t="n">
         <v>581213</v>
@@ -659,7 +659,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75289821624756</v>
+        <v>2.75289797782898</v>
       </c>
       <c r="H10" t="n">
         <v>1613399</v>
@@ -746,7 +746,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66464495658875</v>
+        <v>2.66464471817017</v>
       </c>
       <c r="H13" t="n">
         <v>964050</v>
@@ -804,7 +804,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G15" t="n">
-        <v>2.65690302848816</v>
+        <v>2.65690279006958</v>
       </c>
       <c r="H15" t="n">
         <v>1385445</v>
@@ -833,7 +833,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7482533454895</v>
+        <v>2.74825382232666</v>
       </c>
       <c r="H16" t="n">
         <v>1094217</v>
@@ -862,7 +862,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7018039226532</v>
+        <v>2.70180416107178</v>
       </c>
       <c r="H17" t="n">
         <v>491722</v>
@@ -891,7 +891,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G18" t="n">
-        <v>2.73896384239197</v>
+        <v>2.73896336555481</v>
       </c>
       <c r="H18" t="n">
         <v>900919</v>
@@ -1065,7 +1065,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G24" t="n">
-        <v>2.55006980895996</v>
+        <v>2.55006957054138</v>
       </c>
       <c r="H24" t="n">
         <v>965335</v>
@@ -1123,7 +1123,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G26" t="n">
-        <v>2.55316638946533</v>
+        <v>2.55316662788391</v>
       </c>
       <c r="H26" t="n">
         <v>2005520</v>
@@ -1152,7 +1152,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G27" t="n">
-        <v>2.43859076499939</v>
+        <v>2.43859171867371</v>
       </c>
       <c r="H27" t="n">
         <v>2592460</v>
@@ -1326,7 +1326,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G33" t="n">
-        <v>2.39214158058167</v>
+        <v>2.39214181900024</v>
       </c>
       <c r="H33" t="n">
         <v>1757704</v>
@@ -1355,7 +1355,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G34" t="n">
-        <v>2.60116362571716</v>
+        <v>2.60116386413574</v>
       </c>
       <c r="H34" t="n">
         <v>2832395</v>
@@ -1384,7 +1384,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G35" t="n">
-        <v>2.59342217445374</v>
+        <v>2.59342265129089</v>
       </c>
       <c r="H35" t="n">
         <v>1621895</v>
@@ -1413,7 +1413,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G36" t="n">
-        <v>2.5376832485199</v>
+        <v>2.53768301010132</v>
       </c>
       <c r="H36" t="n">
         <v>1099387</v>
@@ -1442,7 +1442,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G37" t="n">
-        <v>2.6243884563446</v>
+        <v>2.62438821792603</v>
       </c>
       <c r="H37" t="n">
         <v>1413624</v>
@@ -1500,7 +1500,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G39" t="n">
-        <v>2.54077959060669</v>
+        <v>2.54078006744385</v>
       </c>
       <c r="H39" t="n">
         <v>1700027</v>
@@ -1529,7 +1529,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G40" t="n">
-        <v>2.62129211425781</v>
+        <v>2.62129187583923</v>
       </c>
       <c r="H40" t="n">
         <v>924194</v>
@@ -1558,7 +1558,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G41" t="n">
-        <v>2.73122191429138</v>
+        <v>2.73122215270996</v>
       </c>
       <c r="H41" t="n">
         <v>1616252</v>
@@ -1645,7 +1645,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G44" t="n">
-        <v>2.85199069976807</v>
+        <v>2.85199046134949</v>
       </c>
       <c r="H44" t="n">
         <v>1524438</v>
@@ -1761,7 +1761,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G48" t="n">
-        <v>2.82257223129272</v>
+        <v>2.82257270812988</v>
       </c>
       <c r="H48" t="n">
         <v>1053721</v>
@@ -1790,7 +1790,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.80244421958923</v>
+        <v>2.80244445800781</v>
       </c>
       <c r="H49" t="n">
         <v>851655</v>
@@ -1819,7 +1819,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G50" t="n">
-        <v>2.79005789756775</v>
+        <v>2.79005813598633</v>
       </c>
       <c r="H50" t="n">
         <v>1078720</v>
@@ -1877,7 +1877,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G52" t="n">
-        <v>2.88915014266968</v>
+        <v>2.8891499042511</v>
       </c>
       <c r="H52" t="n">
         <v>1341195</v>
@@ -1964,7 +1964,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>2.85199069976807</v>
+        <v>2.85199046134949</v>
       </c>
       <c r="H55" t="n">
         <v>3876711</v>
@@ -2022,7 +2022,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G57" t="n">
-        <v>2.85199069976807</v>
+        <v>2.85199046134949</v>
       </c>
       <c r="H57" t="n">
         <v>1362718</v>
@@ -2051,7 +2051,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G58" t="n">
-        <v>2.86592507362366</v>
+        <v>2.86592531204224</v>
       </c>
       <c r="H58" t="n">
         <v>663781</v>
@@ -2080,7 +2080,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G59" t="n">
-        <v>2.8612802028656</v>
+        <v>2.86128044128418</v>
       </c>
       <c r="H59" t="n">
         <v>582437</v>
@@ -2109,7 +2109,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G60" t="n">
-        <v>2.78696084022522</v>
+        <v>2.78696131706238</v>
       </c>
       <c r="H60" t="n">
         <v>440085</v>
@@ -2138,7 +2138,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.73277020454407</v>
+        <v>2.73276996612549</v>
       </c>
       <c r="H61" t="n">
         <v>652481</v>
@@ -2196,7 +2196,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G63" t="n">
-        <v>2.87521529197693</v>
+        <v>2.87521505355835</v>
       </c>
       <c r="H63" t="n">
         <v>1458208</v>
@@ -2312,7 +2312,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G67" t="n">
-        <v>2.71109414100647</v>
+        <v>2.71109390258789</v>
       </c>
       <c r="H67" t="n">
         <v>574845</v>
@@ -2428,7 +2428,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80244421958923</v>
+        <v>2.80244445800781</v>
       </c>
       <c r="H71" t="n">
         <v>1384237</v>
@@ -2457,7 +2457,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>2.86437726020813</v>
+        <v>2.86437678337097</v>
       </c>
       <c r="H72" t="n">
         <v>2605699</v>
@@ -2486,7 +2486,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G73" t="n">
-        <v>2.89379477500916</v>
+        <v>2.89379453659058</v>
       </c>
       <c r="H73" t="n">
         <v>1090424</v>
@@ -2573,7 +2573,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.87985992431641</v>
+        <v>2.87986040115356</v>
       </c>
       <c r="H76" t="n">
         <v>593773</v>
@@ -2602,7 +2602,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G77" t="n">
-        <v>2.88605332374573</v>
+        <v>2.88605356216431</v>
       </c>
       <c r="H77" t="n">
         <v>824413</v>
@@ -2660,7 +2660,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G79" t="n">
-        <v>2.87521529197693</v>
+        <v>2.87521505355835</v>
       </c>
       <c r="H79" t="n">
         <v>1011988</v>
@@ -2718,7 +2718,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G81" t="n">
-        <v>2.85199069976807</v>
+        <v>2.85199046134949</v>
       </c>
       <c r="H81" t="n">
         <v>1284292</v>
@@ -2776,7 +2776,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G83" t="n">
-        <v>3.00991797447205</v>
+        <v>3.0099184513092</v>
       </c>
       <c r="H83" t="n">
         <v>2440016</v>
@@ -2805,7 +2805,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G84" t="n">
-        <v>2.95882391929626</v>
+        <v>2.95882439613342</v>
       </c>
       <c r="H84" t="n">
         <v>1543779</v>
@@ -2834,7 +2834,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G85" t="n">
-        <v>2.98979020118713</v>
+        <v>2.98978996276855</v>
       </c>
       <c r="H85" t="n">
         <v>771249</v>
@@ -2950,7 +2950,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G89" t="n">
-        <v>2.839604139328</v>
+        <v>2.83960390090942</v>
       </c>
       <c r="H89" t="n">
         <v>589749</v>
@@ -2979,7 +2979,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>2.80244421958923</v>
+        <v>2.80244445800781</v>
       </c>
       <c r="H90" t="n">
         <v>352951</v>
@@ -3008,7 +3008,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G91" t="n">
-        <v>2.81328248977661</v>
+        <v>2.81328296661377</v>
       </c>
       <c r="H91" t="n">
         <v>397299</v>
@@ -3037,7 +3037,7 @@
         <v>3.69199991226196</v>
       </c>
       <c r="G92" t="n">
-        <v>2.85818386077881</v>
+        <v>2.85818314552307</v>
       </c>
       <c r="H92" t="n">
         <v>520677</v>
@@ -3124,7 +3124,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>2.87985992431641</v>
+        <v>2.87986040115356</v>
       </c>
       <c r="H95" t="n">
         <v>502468</v>
@@ -3182,7 +3182,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88605332374573</v>
+        <v>2.88605356216431</v>
       </c>
       <c r="H97" t="n">
         <v>857610</v>
@@ -3240,7 +3240,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G99" t="n">
-        <v>2.84579753875732</v>
+        <v>2.84579706192017</v>
       </c>
       <c r="H99" t="n">
         <v>552258</v>
@@ -3269,7 +3269,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.87240791320801</v>
+        <v>2.87240815162659</v>
       </c>
       <c r="H100" t="n">
         <v>2157318</v>
@@ -3298,7 +3298,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.48107194900513</v>
+        <v>2.48107171058655</v>
       </c>
       <c r="H101" t="n">
         <v>14577083</v>
@@ -3327,7 +3327,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G102" t="n">
-        <v>2.49515986442566</v>
+        <v>2.49515962600708</v>
       </c>
       <c r="H102" t="n">
         <v>6755386</v>
@@ -3356,7 +3356,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G103" t="n">
-        <v>2.45759153366089</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H103" t="n">
         <v>4846198</v>
@@ -3414,7 +3414,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G105" t="n">
-        <v>2.4685492515564</v>
+        <v>2.46854877471924</v>
       </c>
       <c r="H105" t="n">
         <v>2374462</v>
@@ -3443,7 +3443,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>2.41845774650574</v>
+        <v>2.41845798492432</v>
       </c>
       <c r="H106" t="n">
         <v>2536181</v>
@@ -3472,7 +3472,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>2.37932419776917</v>
+        <v>2.37932395935059</v>
       </c>
       <c r="H107" t="n">
         <v>2771779</v>
@@ -3501,7 +3501,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G108" t="n">
-        <v>2.38715076446533</v>
+        <v>2.38715124130249</v>
       </c>
       <c r="H108" t="n">
         <v>1816564</v>
@@ -3588,7 +3588,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G111" t="n">
-        <v>2.37932419776917</v>
+        <v>2.37932395935059</v>
       </c>
       <c r="H111" t="n">
         <v>1834416</v>
@@ -3646,7 +3646,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G113" t="n">
-        <v>2.41219663619995</v>
+        <v>2.41219687461853</v>
       </c>
       <c r="H113" t="n">
         <v>3288781</v>
@@ -3675,7 +3675,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>2.3527135848999</v>
+        <v>2.35271310806274</v>
       </c>
       <c r="H114" t="n">
         <v>1983083</v>
@@ -3704,7 +3704,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G115" t="n">
-        <v>2.24940085411072</v>
+        <v>2.2494010925293</v>
       </c>
       <c r="H115" t="n">
         <v>2114026</v>
@@ -3733,7 +3733,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G116" t="n">
-        <v>2.18052554130554</v>
+        <v>2.18052530288696</v>
       </c>
       <c r="H116" t="n">
         <v>1635751</v>
@@ -3762,7 +3762,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G117" t="n">
-        <v>2.11634612083435</v>
+        <v>2.11634635925293</v>
       </c>
       <c r="H117" t="n">
         <v>2151270</v>
@@ -3820,7 +3820,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>2.14452242851257</v>
+        <v>2.14452290534973</v>
       </c>
       <c r="H119" t="n">
         <v>3285866</v>
@@ -3849,7 +3849,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G120" t="n">
-        <v>2.22748589515686</v>
+        <v>2.22748565673828</v>
       </c>
       <c r="H120" t="n">
         <v>2220357</v>
@@ -3907,7 +3907,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G122" t="n">
-        <v>2.21026682853699</v>
+        <v>2.21026706695557</v>
       </c>
       <c r="H122" t="n">
         <v>1579649</v>
@@ -3936,7 +3936,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G123" t="n">
-        <v>2.28696894645691</v>
+        <v>2.28696870803833</v>
       </c>
       <c r="H123" t="n">
         <v>1894721</v>
@@ -4023,7 +4023,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G126" t="n">
-        <v>1.93946242332458</v>
+        <v>1.9394623041153</v>
       </c>
       <c r="H126" t="n">
         <v>1598076</v>
@@ -4052,7 +4052,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G127" t="n">
-        <v>1.97390007972717</v>
+        <v>1.9738997220993</v>
       </c>
       <c r="H127" t="n">
         <v>2900139</v>
@@ -4168,7 +4168,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G131" t="n">
-        <v>2.09130072593689</v>
+        <v>2.09130096435547</v>
       </c>
       <c r="H131" t="n">
         <v>2319336</v>
@@ -4197,7 +4197,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>2.00364112854004</v>
+        <v>2.00364136695862</v>
       </c>
       <c r="H132" t="n">
         <v>3889902</v>
@@ -4255,7 +4255,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.11321568489075</v>
+        <v>2.11321544647217</v>
       </c>
       <c r="H134" t="n">
         <v>2706963</v>
@@ -4371,7 +4371,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G138" t="n">
-        <v>2.21026682853699</v>
+        <v>2.21026706695557</v>
       </c>
       <c r="H138" t="n">
         <v>738553</v>
@@ -4429,7 +4429,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G140" t="n">
-        <v>2.18991780281067</v>
+        <v>2.18991756439209</v>
       </c>
       <c r="H140" t="n">
         <v>492382</v>
@@ -4487,7 +4487,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G142" t="n">
-        <v>2.14608812332153</v>
+        <v>2.14608788490295</v>
       </c>
       <c r="H142" t="n">
         <v>760877</v>
@@ -4516,7 +4516,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16800284385681</v>
+        <v>2.16800260543823</v>
       </c>
       <c r="H143" t="n">
         <v>1335820</v>
@@ -4603,7 +4603,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G146" t="n">
-        <v>2.14921855926514</v>
+        <v>2.14921879768372</v>
       </c>
       <c r="H146" t="n">
         <v>1633106</v>
@@ -4632,7 +4632,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G147" t="n">
-        <v>2.20400547981262</v>
+        <v>2.2040057182312</v>
       </c>
       <c r="H147" t="n">
         <v>1296535</v>
@@ -4661,7 +4661,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G148" t="n">
-        <v>2.07564735412598</v>
+        <v>2.07564783096313</v>
       </c>
       <c r="H148" t="n">
         <v>6229742</v>
@@ -4719,7 +4719,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G150" t="n">
-        <v>2.06782054901123</v>
+        <v>2.06782031059265</v>
       </c>
       <c r="H150" t="n">
         <v>2120646</v>
@@ -4748,7 +4748,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G151" t="n">
-        <v>1.97859621047974</v>
+        <v>1.97859632968903</v>
       </c>
       <c r="H151" t="n">
         <v>1640032</v>
@@ -4777,7 +4777,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>1.94885468482971</v>
+        <v>1.94885456562042</v>
       </c>
       <c r="H152" t="n">
         <v>1298678</v>
@@ -4806,7 +4806,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>1.94102787971497</v>
+        <v>1.94102776050568</v>
       </c>
       <c r="H153" t="n">
         <v>1093413</v>
@@ -4835,7 +4835,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G154" t="n">
-        <v>1.96137726306915</v>
+        <v>1.96137690544128</v>
       </c>
       <c r="H154" t="n">
         <v>876363</v>
@@ -4864,7 +4864,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G155" t="n">
-        <v>2.01146817207336</v>
+        <v>2.01146793365479</v>
       </c>
       <c r="H155" t="n">
         <v>1272598</v>
@@ -4893,7 +4893,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G156" t="n">
-        <v>2.00207614898682</v>
+        <v>2.0020763874054</v>
       </c>
       <c r="H156" t="n">
         <v>1568347</v>
@@ -4922,7 +4922,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>1.99581468105316</v>
+        <v>1.99581491947174</v>
       </c>
       <c r="H157" t="n">
         <v>930572</v>
@@ -5038,7 +5038,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G161" t="n">
-        <v>2.05216693878174</v>
+        <v>2.05216717720032</v>
       </c>
       <c r="H161" t="n">
         <v>1296754</v>
@@ -5125,7 +5125,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>2.05842876434326</v>
+        <v>2.05842852592468</v>
       </c>
       <c r="H164" t="n">
         <v>1061581</v>
@@ -5154,7 +5154,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G165" t="n">
-        <v>2.09756231307983</v>
+        <v>2.09756207466125</v>
       </c>
       <c r="H165" t="n">
         <v>837027</v>
@@ -5183,7 +5183,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.11321568489075</v>
+        <v>2.11321544647217</v>
       </c>
       <c r="H166" t="n">
         <v>813589</v>
@@ -5212,7 +5212,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>2.07408237457275</v>
+        <v>2.0740818977356</v>
       </c>
       <c r="H167" t="n">
         <v>749117</v>
@@ -5241,7 +5241,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G168" t="n">
-        <v>2.09756231307983</v>
+        <v>2.09756207466125</v>
       </c>
       <c r="H168" t="n">
         <v>697763</v>
@@ -5270,7 +5270,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G169" t="n">
-        <v>2.11947703361511</v>
+        <v>2.11947679519653</v>
       </c>
       <c r="H169" t="n">
         <v>499989</v>
@@ -5357,7 +5357,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.13669586181641</v>
+        <v>2.13669562339783</v>
       </c>
       <c r="H172" t="n">
         <v>1131229</v>
@@ -5386,7 +5386,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>2.16017627716064</v>
+        <v>2.16017603874207</v>
       </c>
       <c r="H173" t="n">
         <v>498741</v>
@@ -5415,7 +5415,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G174" t="n">
-        <v>2.14452242851257</v>
+        <v>2.14452290534973</v>
       </c>
       <c r="H174" t="n">
         <v>280821</v>
@@ -5444,7 +5444,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G175" t="n">
-        <v>2.14608812332153</v>
+        <v>2.14608788490295</v>
       </c>
       <c r="H175" t="n">
         <v>554785</v>
@@ -5589,7 +5589,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>2.01146817207336</v>
+        <v>2.01146793365479</v>
       </c>
       <c r="H180" t="n">
         <v>939604</v>
@@ -5618,7 +5618,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G181" t="n">
-        <v>2.00207614898682</v>
+        <v>2.0020763874054</v>
       </c>
       <c r="H181" t="n">
         <v>923059</v>
@@ -5647,7 +5647,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G182" t="n">
-        <v>1.98955321311951</v>
+        <v>1.98955357074738</v>
       </c>
       <c r="H182" t="n">
         <v>1468702</v>
@@ -5676,7 +5676,7 @@
         <v>2.5</v>
       </c>
       <c r="G183" t="n">
-        <v>1.95668113231659</v>
+        <v>1.95668125152588</v>
       </c>
       <c r="H183" t="n">
         <v>2497228</v>
@@ -5705,7 +5705,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G184" t="n">
-        <v>1.99424970149994</v>
+        <v>1.99424922466278</v>
       </c>
       <c r="H184" t="n">
         <v>1176506</v>
@@ -5734,7 +5734,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G185" t="n">
-        <v>1.92850542068481</v>
+        <v>1.92850494384766</v>
       </c>
       <c r="H185" t="n">
         <v>1274216</v>
@@ -5763,7 +5763,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>1.92537426948547</v>
+        <v>1.92537415027618</v>
       </c>
       <c r="H186" t="n">
         <v>703328</v>
@@ -5821,7 +5821,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G188" t="n">
-        <v>1.97859621047974</v>
+        <v>1.97859632968903</v>
       </c>
       <c r="H188" t="n">
         <v>375877</v>
@@ -5850,7 +5850,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G189" t="n">
-        <v>1.91754758358002</v>
+        <v>1.91754770278931</v>
       </c>
       <c r="H189" t="n">
         <v>786779</v>
@@ -5879,7 +5879,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>1.92537426948547</v>
+        <v>1.92537415027618</v>
       </c>
       <c r="H190" t="n">
         <v>1867839</v>
@@ -5908,7 +5908,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G191" t="n">
-        <v>2.05529761314392</v>
+        <v>2.05529808998108</v>
       </c>
       <c r="H191" t="n">
         <v>3388408</v>
@@ -5995,7 +5995,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G194" t="n">
-        <v>1.95355045795441</v>
+        <v>1.95355021953583</v>
       </c>
       <c r="H194" t="n">
         <v>944804</v>
@@ -6024,7 +6024,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G195" t="n">
-        <v>1.94885468482971</v>
+        <v>1.94885456562042</v>
       </c>
       <c r="H195" t="n">
         <v>460629</v>
@@ -6053,7 +6053,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G196" t="n">
-        <v>2.02868700027466</v>
+        <v>2.02868747711182</v>
       </c>
       <c r="H196" t="n">
         <v>1217923</v>
@@ -6111,7 +6111,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G198" t="n">
-        <v>1.96763849258423</v>
+        <v>1.96763825416565</v>
       </c>
       <c r="H198" t="n">
         <v>843471</v>
@@ -6169,7 +6169,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G200" t="n">
-        <v>1.96763849258423</v>
+        <v>1.96763825416565</v>
       </c>
       <c r="H200" t="n">
         <v>746930</v>
@@ -6198,7 +6198,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G201" t="n">
-        <v>1.93320083618164</v>
+        <v>1.93320119380951</v>
       </c>
       <c r="H201" t="n">
         <v>830606</v>
@@ -6227,7 +6227,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G202" t="n">
-        <v>1.93320083618164</v>
+        <v>1.93320119380951</v>
       </c>
       <c r="H202" t="n">
         <v>1085623</v>
@@ -6256,7 +6256,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G203" t="n">
-        <v>1.96763849258423</v>
+        <v>1.96763825416565</v>
       </c>
       <c r="H203" t="n">
         <v>470437</v>
@@ -6285,7 +6285,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96450817584991</v>
+        <v>1.96450793743134</v>
       </c>
       <c r="H204" t="n">
         <v>817690</v>
@@ -6314,7 +6314,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G205" t="n">
-        <v>2.00207614898682</v>
+        <v>2.0020763874054</v>
       </c>
       <c r="H205" t="n">
         <v>1166619</v>
@@ -6430,7 +6430,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G209" t="n">
-        <v>2.10382342338562</v>
+        <v>2.1038236618042</v>
       </c>
       <c r="H209" t="n">
         <v>987784</v>
@@ -6517,7 +6517,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G212" t="n">
-        <v>2.03338265419006</v>
+        <v>2.03338289260864</v>
       </c>
       <c r="H212" t="n">
         <v>1605178</v>
@@ -6546,7 +6546,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G213" t="n">
-        <v>1.97859621047974</v>
+        <v>1.97859632968903</v>
       </c>
       <c r="H213" t="n">
         <v>1439805</v>
@@ -6604,7 +6604,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G215" t="n">
-        <v>1.96137726306915</v>
+        <v>1.96137690544128</v>
       </c>
       <c r="H215" t="n">
         <v>535801</v>
@@ -6633,7 +6633,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G216" t="n">
-        <v>1.93163549900055</v>
+        <v>1.93163561820984</v>
       </c>
       <c r="H216" t="n">
         <v>1190452</v>
@@ -6662,7 +6662,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G217" t="n">
-        <v>1.91128611564636</v>
+        <v>1.91128635406494</v>
       </c>
       <c r="H217" t="n">
         <v>763654</v>
@@ -6691,7 +6691,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89563262462616</v>
+        <v>1.89563238620758</v>
       </c>
       <c r="H218" t="n">
         <v>762448</v>
@@ -6720,7 +6720,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G219" t="n">
-        <v>1.93163549900055</v>
+        <v>1.93163561820984</v>
       </c>
       <c r="H219" t="n">
         <v>511910</v>
@@ -6749,7 +6749,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G220" t="n">
-        <v>1.91128611564636</v>
+        <v>1.91128635406494</v>
       </c>
       <c r="H220" t="n">
         <v>476146</v>
@@ -6778,7 +6778,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>2.05842876434326</v>
+        <v>2.05842852592468</v>
       </c>
       <c r="H221" t="n">
         <v>7385474</v>
@@ -6807,7 +6807,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G222" t="n">
-        <v>2.08817005157471</v>
+        <v>2.08816981315613</v>
       </c>
       <c r="H222" t="n">
         <v>4219197</v>
@@ -6836,7 +6836,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G223" t="n">
-        <v>2.03025245666504</v>
+        <v>2.03025269508362</v>
       </c>
       <c r="H223" t="n">
         <v>2200910</v>
@@ -6865,7 +6865,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G224" t="n">
-        <v>2.16330647468567</v>
+        <v>2.16330695152283</v>
       </c>
       <c r="H224" t="n">
         <v>3314695</v>
@@ -6923,7 +6923,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G226" t="n">
-        <v>2.08817005157471</v>
+        <v>2.08816981315613</v>
       </c>
       <c r="H226" t="n">
         <v>1286080</v>
@@ -6981,7 +6981,7 @@
         <v>2.57200002670288</v>
       </c>
       <c r="G228" t="n">
-        <v>2.01303362846375</v>
+        <v>2.01303339004517</v>
       </c>
       <c r="H228" t="n">
         <v>1577781</v>
@@ -7010,7 +7010,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G229" t="n">
-        <v>1.99581468105316</v>
+        <v>1.99581491947174</v>
       </c>
       <c r="H229" t="n">
         <v>1137034</v>
@@ -7039,7 +7039,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G230" t="n">
-        <v>2.01146817207336</v>
+        <v>2.01146793365479</v>
       </c>
       <c r="H230" t="n">
         <v>871707</v>
@@ -7068,7 +7068,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G231" t="n">
-        <v>2.01146817207336</v>
+        <v>2.01146793365479</v>
       </c>
       <c r="H231" t="n">
         <v>940946</v>
@@ -7097,7 +7097,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>1.99581468105316</v>
+        <v>1.99581491947174</v>
       </c>
       <c r="H232" t="n">
         <v>459440</v>
@@ -7126,7 +7126,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G233" t="n">
-        <v>1.98955321311951</v>
+        <v>1.98955357074738</v>
       </c>
       <c r="H233" t="n">
         <v>602925</v>
@@ -7155,7 +7155,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>1.92537426948547</v>
+        <v>1.92537415027618</v>
       </c>
       <c r="H234" t="n">
         <v>1382971</v>
@@ -7184,7 +7184,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G235" t="n">
-        <v>1.96763849258423</v>
+        <v>1.96763825416565</v>
       </c>
       <c r="H235" t="n">
         <v>925158</v>
@@ -7271,7 +7271,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G238" t="n">
-        <v>2.04434037208557</v>
+        <v>2.04434084892273</v>
       </c>
       <c r="H238" t="n">
         <v>1826358</v>
@@ -7300,7 +7300,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G239" t="n">
-        <v>2.09756231307983</v>
+        <v>2.09756207466125</v>
       </c>
       <c r="H239" t="n">
         <v>1527580</v>
@@ -7329,7 +7329,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G240" t="n">
-        <v>2.17113304138184</v>
+        <v>2.17113351821899</v>
       </c>
       <c r="H240" t="n">
         <v>2515736</v>
@@ -7358,7 +7358,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G241" t="n">
-        <v>2.23687815666199</v>
+        <v>2.23687767982483</v>
       </c>
       <c r="H241" t="n">
         <v>3252090</v>
@@ -7532,7 +7532,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G247" t="n">
-        <v>2.37775897979736</v>
+        <v>2.37775921821594</v>
       </c>
       <c r="H247" t="n">
         <v>1476950</v>
@@ -7561,7 +7561,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>2.37932419776917</v>
+        <v>2.37932395935059</v>
       </c>
       <c r="H248" t="n">
         <v>2467677</v>
@@ -7590,7 +7590,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>2.37932419776917</v>
+        <v>2.37932395935059</v>
       </c>
       <c r="H249" t="n">
         <v>2372938</v>
@@ -7619,7 +7619,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G250" t="n">
-        <v>2.38088965415955</v>
+        <v>2.38088989257812</v>
       </c>
       <c r="H250" t="n">
         <v>1340592</v>
@@ -7648,7 +7648,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>2.37932419776917</v>
+        <v>2.37932395935059</v>
       </c>
       <c r="H251" t="n">
         <v>1637113</v>
@@ -7677,7 +7677,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G252" t="n">
-        <v>2.4200234413147</v>
+        <v>2.42002296447754</v>
       </c>
       <c r="H252" t="n">
         <v>2194065</v>
@@ -7793,7 +7793,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32923316955566</v>
+        <v>2.32923340797424</v>
       </c>
       <c r="H256" t="n">
         <v>542985</v>
@@ -7851,7 +7851,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G258" t="n">
-        <v>2.43098092079163</v>
+        <v>2.43098044395447</v>
       </c>
       <c r="H258" t="n">
         <v>1363312</v>
@@ -7880,7 +7880,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G259" t="n">
-        <v>2.47794127464294</v>
+        <v>2.47794103622437</v>
       </c>
       <c r="H259" t="n">
         <v>1728143</v>
@@ -7909,7 +7909,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G260" t="n">
-        <v>2.48576807975769</v>
+        <v>2.48576784133911</v>
       </c>
       <c r="H260" t="n">
         <v>1766326</v>
@@ -7938,7 +7938,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G261" t="n">
-        <v>2.45759153366089</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H261" t="n">
         <v>853673</v>
@@ -7996,7 +7996,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G263" t="n">
-        <v>2.4231538772583</v>
+        <v>2.42315411567688</v>
       </c>
       <c r="H263" t="n">
         <v>982274</v>
@@ -8025,7 +8025,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G264" t="n">
-        <v>2.45759153366089</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H264" t="n">
         <v>879469</v>
@@ -8054,7 +8054,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G265" t="n">
-        <v>2.48576807975769</v>
+        <v>2.48576784133911</v>
       </c>
       <c r="H265" t="n">
         <v>829436</v>
@@ -8112,7 +8112,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.4497652053833</v>
+        <v>2.44976472854614</v>
       </c>
       <c r="H267" t="n">
         <v>771245</v>
@@ -8141,7 +8141,7 @@
         <v>3.1159999370575</v>
       </c>
       <c r="G268" t="n">
-        <v>2.43880724906921</v>
+        <v>2.43880748748779</v>
       </c>
       <c r="H268" t="n">
         <v>962333</v>
@@ -8199,7 +8199,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.39497756958008</v>
+        <v>2.3949773311615</v>
       </c>
       <c r="H270" t="n">
         <v>486139</v>
@@ -8228,7 +8228,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G271" t="n">
-        <v>2.4231538772583</v>
+        <v>2.42315411567688</v>
       </c>
       <c r="H271" t="n">
         <v>1200352</v>
@@ -8257,7 +8257,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G272" t="n">
-        <v>2.40280437469482</v>
+        <v>2.4028046131134</v>
       </c>
       <c r="H272" t="n">
         <v>626345</v>
@@ -8286,7 +8286,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G273" t="n">
-        <v>2.38402032852173</v>
+        <v>2.38402009010315</v>
       </c>
       <c r="H273" t="n">
         <v>1065395</v>
@@ -8373,7 +8373,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G276" t="n">
-        <v>2.35897469520569</v>
+        <v>2.35897493362427</v>
       </c>
       <c r="H276" t="n">
         <v>1343547</v>
@@ -8402,7 +8402,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G277" t="n">
-        <v>2.33862519264221</v>
+        <v>2.33862543106079</v>
       </c>
       <c r="H277" t="n">
         <v>900267</v>
@@ -8460,7 +8460,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G279" t="n">
-        <v>2.2556619644165</v>
+        <v>2.25566220283508</v>
       </c>
       <c r="H279" t="n">
         <v>863160</v>
@@ -8576,7 +8576,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>2.23061656951904</v>
+        <v>2.23061609268188</v>
       </c>
       <c r="H283" t="n">
         <v>840338</v>
@@ -8663,7 +8663,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G286" t="n">
-        <v>2.31827569007874</v>
+        <v>2.31827592849731</v>
       </c>
       <c r="H286" t="n">
         <v>1191078</v>
@@ -8692,7 +8692,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G287" t="n">
-        <v>2.33862519264221</v>
+        <v>2.33862543106079</v>
       </c>
       <c r="H287" t="n">
         <v>1633765</v>
@@ -8750,7 +8750,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>2.41063070297241</v>
+        <v>2.41063094139099</v>
       </c>
       <c r="H289" t="n">
         <v>1135351</v>
@@ -8779,7 +8779,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G290" t="n">
-        <v>2.4200234413147</v>
+        <v>2.42002296447754</v>
       </c>
       <c r="H290" t="n">
         <v>2382345</v>
@@ -8808,7 +8808,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G291" t="n">
-        <v>2.40437006950378</v>
+        <v>2.40436983108521</v>
       </c>
       <c r="H291" t="n">
         <v>2490093</v>
@@ -8837,7 +8837,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G292" t="n">
-        <v>2.36993265151978</v>
+        <v>2.3699324131012</v>
       </c>
       <c r="H292" t="n">
         <v>1275136</v>
@@ -8866,7 +8866,7 @@
         <v>3</v>
       </c>
       <c r="G293" t="n">
-        <v>2.34801769256592</v>
+        <v>2.34801721572876</v>
       </c>
       <c r="H293" t="n">
         <v>865361</v>
@@ -8895,7 +8895,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G294" t="n">
-        <v>2.33862519264221</v>
+        <v>2.33862543106079</v>
       </c>
       <c r="H294" t="n">
         <v>975000</v>
@@ -8924,7 +8924,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>2.35584425926208</v>
+        <v>2.35584449768066</v>
       </c>
       <c r="H295" t="n">
         <v>931240</v>
@@ -8953,7 +8953,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G296" t="n">
-        <v>2.33706021308899</v>
+        <v>2.33705973625183</v>
       </c>
       <c r="H296" t="n">
         <v>869769</v>
@@ -8982,7 +8982,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G297" t="n">
-        <v>2.45289540290833</v>
+        <v>2.4528956413269</v>
       </c>
       <c r="H297" t="n">
         <v>4692514</v>
@@ -9011,7 +9011,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G298" t="n">
-        <v>2.44819974899292</v>
+        <v>2.44819927215576</v>
       </c>
       <c r="H298" t="n">
         <v>1305027</v>
@@ -9040,7 +9040,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G299" t="n">
-        <v>2.48107194900513</v>
+        <v>2.48107171058655</v>
       </c>
       <c r="H299" t="n">
         <v>1238634</v>
@@ -9069,7 +9069,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G300" t="n">
-        <v>2.53429365158081</v>
+        <v>2.53429341316223</v>
       </c>
       <c r="H300" t="n">
         <v>2015772</v>
@@ -9098,7 +9098,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G301" t="n">
-        <v>2.54525089263916</v>
+        <v>2.54525136947632</v>
       </c>
       <c r="H301" t="n">
         <v>1841917</v>
@@ -9127,7 +9127,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G302" t="n">
-        <v>2.53585886955261</v>
+        <v>2.53585839271545</v>
       </c>
       <c r="H302" t="n">
         <v>879229</v>
@@ -9214,7 +9214,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G305" t="n">
-        <v>2.51707458496094</v>
+        <v>2.51707482337952</v>
       </c>
       <c r="H305" t="n">
         <v>842737</v>
@@ -9272,7 +9272,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G307" t="n">
-        <v>2.49202942848206</v>
+        <v>2.49202919006348</v>
       </c>
       <c r="H307" t="n">
         <v>1006054</v>
@@ -9301,7 +9301,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>2.49672508239746</v>
+        <v>2.49672532081604</v>
       </c>
       <c r="H308" t="n">
         <v>948293</v>
@@ -9330,7 +9330,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>2.45759153366089</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H309" t="n">
         <v>969086</v>
@@ -9359,7 +9359,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G310" t="n">
-        <v>2.48889827728271</v>
+        <v>2.48889851570129</v>
       </c>
       <c r="H310" t="n">
         <v>615008</v>
@@ -9417,7 +9417,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G312" t="n">
-        <v>2.48733282089233</v>
+        <v>2.48733305931091</v>
       </c>
       <c r="H312" t="n">
         <v>2780058</v>
@@ -9446,7 +9446,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G313" t="n">
-        <v>2.46541810035706</v>
+        <v>2.46541881561279</v>
       </c>
       <c r="H313" t="n">
         <v>1680814</v>
@@ -9475,7 +9475,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G314" t="n">
-        <v>2.45133018493652</v>
+        <v>2.4513304233551</v>
       </c>
       <c r="H314" t="n">
         <v>1373872</v>
@@ -9649,7 +9649,7 @@
         <v>3.10400009155273</v>
       </c>
       <c r="G320" t="n">
-        <v>2.42941498756409</v>
+        <v>2.42941546440125</v>
       </c>
       <c r="H320" t="n">
         <v>1672455</v>
@@ -9736,7 +9736,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G323" t="n">
-        <v>2.40280437469482</v>
+        <v>2.4028046131134</v>
       </c>
       <c r="H323" t="n">
         <v>1842216</v>
@@ -9765,7 +9765,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G324" t="n">
-        <v>2.37619400024414</v>
+        <v>2.37619352340698</v>
       </c>
       <c r="H324" t="n">
         <v>1263595</v>
@@ -9794,7 +9794,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G325" t="n">
-        <v>2.41063070297241</v>
+        <v>2.41063094139099</v>
       </c>
       <c r="H325" t="n">
         <v>1145350</v>
@@ -9823,7 +9823,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G326" t="n">
-        <v>2.44506859779358</v>
+        <v>2.44506907463074</v>
       </c>
       <c r="H326" t="n">
         <v>1236854</v>
@@ -9852,7 +9852,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.46541810035706</v>
+        <v>2.46541881561279</v>
       </c>
       <c r="H327" t="n">
         <v>1448459</v>
@@ -9910,7 +9910,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G329" t="n">
-        <v>2.43254566192627</v>
+        <v>2.43254613876343</v>
       </c>
       <c r="H329" t="n">
         <v>922372</v>
@@ -9997,7 +9997,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G332" t="n">
-        <v>2.29792666435242</v>
+        <v>2.29792642593384</v>
       </c>
       <c r="H332" t="n">
         <v>1838891</v>
@@ -10026,7 +10026,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G333" t="n">
-        <v>2.38715076446533</v>
+        <v>2.38715124130249</v>
       </c>
       <c r="H333" t="n">
         <v>1119719</v>
@@ -10055,7 +10055,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G334" t="n">
-        <v>2.41532707214355</v>
+        <v>2.41532731056213</v>
       </c>
       <c r="H334" t="n">
         <v>1143561</v>
@@ -10084,7 +10084,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>2.39497756958008</v>
+        <v>2.3949773311615</v>
       </c>
       <c r="H335" t="n">
         <v>2078075</v>
@@ -10171,7 +10171,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>2.4497652053833</v>
+        <v>2.44976472854614</v>
       </c>
       <c r="H338" t="n">
         <v>2519037</v>
@@ -10200,7 +10200,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G339" t="n">
-        <v>2.4231538772583</v>
+        <v>2.42315411567688</v>
       </c>
       <c r="H339" t="n">
         <v>1415458</v>
@@ -10229,7 +10229,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G340" t="n">
-        <v>2.44506859779358</v>
+        <v>2.44506907463074</v>
       </c>
       <c r="H340" t="n">
         <v>1747619</v>
@@ -10258,7 +10258,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G341" t="n">
-        <v>2.51237845420837</v>
+        <v>2.51237893104553</v>
       </c>
       <c r="H341" t="n">
         <v>2866186</v>
@@ -10345,7 +10345,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G344" t="n">
-        <v>2.55151200294495</v>
+        <v>2.55151224136353</v>
       </c>
       <c r="H344" t="n">
         <v>1479263</v>
@@ -10403,7 +10403,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>2.6219527721405</v>
+        <v>2.62195301055908</v>
       </c>
       <c r="H346" t="n">
         <v>3151258</v>
@@ -10432,7 +10432,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G347" t="n">
-        <v>2.65169429779053</v>
+        <v>2.65169453620911</v>
       </c>
       <c r="H347" t="n">
         <v>1207699</v>
@@ -10461,7 +10461,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>2.6219527721405</v>
+        <v>2.62195301055908</v>
       </c>
       <c r="H348" t="n">
         <v>2137829</v>
@@ -10519,7 +10519,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G350" t="n">
-        <v>2.64543294906616</v>
+        <v>2.64543318748474</v>
       </c>
       <c r="H350" t="n">
         <v>1368979</v>
@@ -10548,7 +10548,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G351" t="n">
-        <v>2.66578245162964</v>
+        <v>2.66578221321106</v>
       </c>
       <c r="H351" t="n">
         <v>1367008</v>
@@ -10577,7 +10577,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.53585886955261</v>
+        <v>2.53585839271545</v>
       </c>
       <c r="H352" t="n">
         <v>2123505</v>
@@ -10606,7 +10606,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G353" t="n">
-        <v>2.43098092079163</v>
+        <v>2.43098044395447</v>
       </c>
       <c r="H353" t="n">
         <v>3812104</v>
@@ -10635,7 +10635,7 @@
         <v>3.14599990844727</v>
       </c>
       <c r="G354" t="n">
-        <v>2.46228766441345</v>
+        <v>2.46228742599487</v>
       </c>
       <c r="H354" t="n">
         <v>1374536</v>
@@ -10664,7 +10664,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G355" t="n">
-        <v>2.52040195465088</v>
+        <v>2.5204017162323</v>
       </c>
       <c r="H355" t="n">
         <v>818695</v>
@@ -10693,7 +10693,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G356" t="n">
-        <v>2.53791546821594</v>
+        <v>2.53791570663452</v>
       </c>
       <c r="H356" t="n">
         <v>987101</v>
@@ -10780,7 +10780,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>2.54746866226196</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H359" t="n">
         <v>1292142</v>
@@ -10809,7 +10809,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G360" t="n">
-        <v>2.56020593643188</v>
+        <v>2.56020617485046</v>
       </c>
       <c r="H360" t="n">
         <v>747549</v>
@@ -10838,7 +10838,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>2.52358603477478</v>
+        <v>2.52358627319336</v>
       </c>
       <c r="H361" t="n">
         <v>1301649</v>
@@ -10867,7 +10867,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>2.54746866226196</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H362" t="n">
         <v>1966210</v>
@@ -10925,7 +10925,7 @@
         <v>3.23399996757507</v>
       </c>
       <c r="G364" t="n">
-        <v>2.57453513145447</v>
+        <v>2.57453536987305</v>
       </c>
       <c r="H364" t="n">
         <v>1210712</v>
@@ -10983,7 +10983,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G366" t="n">
-        <v>2.5522449016571</v>
+        <v>2.55224514007568</v>
       </c>
       <c r="H366" t="n">
         <v>1387432</v>
@@ -11041,7 +11041,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G368" t="n">
-        <v>2.45830726623535</v>
+        <v>2.45830702781677</v>
       </c>
       <c r="H368" t="n">
         <v>2334871</v>
@@ -11070,7 +11070,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G369" t="n">
-        <v>2.41372632980347</v>
+        <v>2.41372656822205</v>
       </c>
       <c r="H369" t="n">
         <v>1844465</v>
@@ -11099,7 +11099,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>2.42009496688843</v>
+        <v>2.42009472846985</v>
       </c>
       <c r="H370" t="n">
         <v>1292806</v>
@@ -11331,7 +11331,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>2.4041736125946</v>
+        <v>2.40417313575745</v>
       </c>
       <c r="H378" t="n">
         <v>554483</v>
@@ -11360,7 +11360,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G379" t="n">
-        <v>2.41213440895081</v>
+        <v>2.41213417053223</v>
       </c>
       <c r="H379" t="n">
         <v>550090</v>
@@ -11447,7 +11447,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G382" t="n">
-        <v>2.4869658946991</v>
+        <v>2.48696637153625</v>
       </c>
       <c r="H382" t="n">
         <v>1591740</v>
@@ -11505,7 +11505,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.41213440895081</v>
+        <v>2.41213417053223</v>
       </c>
       <c r="H384" t="n">
         <v>1637111</v>
@@ -11534,7 +11534,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.42805600166321</v>
+        <v>2.42805576324463</v>
       </c>
       <c r="H385" t="n">
         <v>929588</v>
@@ -11563,7 +11563,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G386" t="n">
-        <v>2.38984417915344</v>
+        <v>2.38984394073486</v>
       </c>
       <c r="H386" t="n">
         <v>1146093</v>
@@ -11621,7 +11621,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>2.37233018875122</v>
+        <v>2.37232995033264</v>
       </c>
       <c r="H388" t="n">
         <v>814149</v>
@@ -11650,7 +11650,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G389" t="n">
-        <v>2.42646384239197</v>
+        <v>2.42646408081055</v>
       </c>
       <c r="H389" t="n">
         <v>1267851</v>
@@ -11679,7 +11679,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.43601655960083</v>
+        <v>2.43601703643799</v>
       </c>
       <c r="H390" t="n">
         <v>1532503</v>
@@ -11708,7 +11708,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G391" t="n">
-        <v>2.38188314437866</v>
+        <v>2.38188338279724</v>
       </c>
       <c r="H391" t="n">
         <v>1358951</v>
@@ -11737,7 +11737,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G392" t="n">
-        <v>2.44716191291809</v>
+        <v>2.44716167449951</v>
       </c>
       <c r="H392" t="n">
         <v>1622777</v>
@@ -11795,7 +11795,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G394" t="n">
-        <v>2.45989894866943</v>
+        <v>2.45989918708801</v>
       </c>
       <c r="H394" t="n">
         <v>617432</v>
@@ -11824,7 +11824,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G395" t="n">
-        <v>2.51084876060486</v>
+        <v>2.51084899902344</v>
       </c>
       <c r="H395" t="n">
         <v>4508418</v>
@@ -11911,7 +11911,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G398" t="n">
-        <v>2.46149158477783</v>
+        <v>2.46149134635925</v>
       </c>
       <c r="H398" t="n">
         <v>1226827</v>
@@ -11940,7 +11940,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G399" t="n">
-        <v>2.42805600166321</v>
+        <v>2.42805576324463</v>
       </c>
       <c r="H399" t="n">
         <v>1376064</v>
@@ -11969,7 +11969,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G400" t="n">
-        <v>2.42805600166321</v>
+        <v>2.42805576324463</v>
       </c>
       <c r="H400" t="n">
         <v>669595</v>
@@ -12027,7 +12027,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G402" t="n">
-        <v>2.46626806259155</v>
+        <v>2.46626830101013</v>
       </c>
       <c r="H402" t="n">
         <v>623443</v>
@@ -12114,7 +12114,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G405" t="n">
-        <v>2.3659610748291</v>
+        <v>2.36596131324768</v>
       </c>
       <c r="H405" t="n">
         <v>997374</v>
@@ -12172,7 +12172,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G407" t="n">
-        <v>2.35481572151184</v>
+        <v>2.354816198349</v>
       </c>
       <c r="H407" t="n">
         <v>777560</v>
@@ -12288,7 +12288,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G411" t="n">
-        <v>2.36118507385254</v>
+        <v>2.36118531227112</v>
       </c>
       <c r="H411" t="n">
         <v>872287</v>
@@ -12346,7 +12346,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G413" t="n">
-        <v>2.27679991722107</v>
+        <v>2.27679967880249</v>
       </c>
       <c r="H413" t="n">
         <v>1403718</v>
@@ -12404,7 +12404,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G415" t="n">
-        <v>2.30068254470825</v>
+        <v>2.30068278312683</v>
       </c>
       <c r="H415" t="n">
         <v>613532</v>
@@ -12491,7 +12491,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G418" t="n">
-        <v>2.28157615661621</v>
+        <v>2.28157639503479</v>
       </c>
       <c r="H418" t="n">
         <v>1740213</v>
@@ -12578,7 +12578,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G421" t="n">
-        <v>2.33730244636536</v>
+        <v>2.33730268478394</v>
       </c>
       <c r="H421" t="n">
         <v>1265104</v>
@@ -12636,7 +12636,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G423" t="n">
-        <v>2.34844779968262</v>
+        <v>2.34844756126404</v>
       </c>
       <c r="H423" t="n">
         <v>685400</v>
@@ -12723,7 +12723,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G426" t="n">
-        <v>2.34844779968262</v>
+        <v>2.34844756126404</v>
       </c>
       <c r="H426" t="n">
         <v>723093</v>
@@ -12752,7 +12752,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G427" t="n">
-        <v>2.34844779968262</v>
+        <v>2.34844756126404</v>
       </c>
       <c r="H427" t="n">
         <v>1614230</v>
@@ -12781,7 +12781,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G428" t="n">
-        <v>2.3755145072937</v>
+        <v>2.37551426887512</v>
       </c>
       <c r="H428" t="n">
         <v>1245196</v>
@@ -12868,7 +12868,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43920063972473</v>
+        <v>2.43920111656189</v>
       </c>
       <c r="H431" t="n">
         <v>1993777</v>
@@ -12984,7 +12984,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>2.54746866226196</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H435" t="n">
         <v>1669492</v>
@@ -13013,7 +13013,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G436" t="n">
-        <v>2.54746866226196</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H436" t="n">
         <v>607602</v>
@@ -13042,7 +13042,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G437" t="n">
-        <v>2.59682583808899</v>
+        <v>2.59682607650757</v>
       </c>
       <c r="H437" t="n">
         <v>1443378</v>
@@ -13071,7 +13071,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G438" t="n">
-        <v>2.54746866226196</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H438" t="n">
         <v>650215</v>
@@ -13100,7 +13100,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G439" t="n">
-        <v>2.55065298080444</v>
+        <v>2.55065274238586</v>
       </c>
       <c r="H439" t="n">
         <v>489510</v>
@@ -13129,7 +13129,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G440" t="n">
-        <v>2.58568024635315</v>
+        <v>2.58568048477173</v>
       </c>
       <c r="H440" t="n">
         <v>421765</v>
@@ -13158,7 +13158,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G441" t="n">
-        <v>2.58568024635315</v>
+        <v>2.58568048477173</v>
       </c>
       <c r="H441" t="n">
         <v>629599</v>
@@ -13216,7 +13216,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G443" t="n">
-        <v>2.56498217582703</v>
+        <v>2.56498193740845</v>
       </c>
       <c r="H443" t="n">
         <v>512784</v>
@@ -13274,7 +13274,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61433935165405</v>
+        <v>2.61433982849121</v>
       </c>
       <c r="H445" t="n">
         <v>607795</v>
@@ -13332,7 +13332,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>2.61911630630493</v>
+        <v>2.61911606788635</v>
       </c>
       <c r="H447" t="n">
         <v>569921</v>
@@ -13361,7 +13361,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G448" t="n">
-        <v>2.65573620796204</v>
+        <v>2.65573596954346</v>
       </c>
       <c r="H448" t="n">
         <v>958763</v>
@@ -13390,7 +13390,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G449" t="n">
-        <v>2.61274766921997</v>
+        <v>2.61274743080139</v>
       </c>
       <c r="H449" t="n">
         <v>1008192</v>
@@ -13419,7 +13419,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G450" t="n">
-        <v>2.60637831687927</v>
+        <v>2.60637879371643</v>
       </c>
       <c r="H450" t="n">
         <v>654933</v>
@@ -13477,7 +13477,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G452" t="n">
-        <v>2.64459109306335</v>
+        <v>2.6445906162262</v>
       </c>
       <c r="H452" t="n">
         <v>818061</v>
@@ -13506,7 +13506,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G453" t="n">
-        <v>2.59204959869385</v>
+        <v>2.59204936027527</v>
       </c>
       <c r="H453" t="n">
         <v>921065</v>
@@ -13535,7 +13535,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G454" t="n">
-        <v>2.56020593643188</v>
+        <v>2.56020617485046</v>
       </c>
       <c r="H454" t="n">
         <v>934398</v>
@@ -13564,7 +13564,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G455" t="n">
-        <v>2.57612776756287</v>
+        <v>2.57612752914429</v>
       </c>
       <c r="H455" t="n">
         <v>580340</v>
@@ -13593,7 +13593,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G456" t="n">
-        <v>2.63822197914124</v>
+        <v>2.63822221755981</v>
       </c>
       <c r="H456" t="n">
         <v>1023456</v>
@@ -13709,7 +13709,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G460" t="n">
-        <v>2.72419929504395</v>
+        <v>2.72419905662537</v>
       </c>
       <c r="H460" t="n">
         <v>716646</v>
@@ -13825,7 +13825,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G464" t="n">
-        <v>2.74330544471741</v>
+        <v>2.74330520629883</v>
       </c>
       <c r="H464" t="n">
         <v>810084</v>
@@ -13854,7 +13854,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G465" t="n">
-        <v>2.79903125762939</v>
+        <v>2.79903101921082</v>
       </c>
       <c r="H465" t="n">
         <v>1541603</v>
@@ -13970,7 +13970,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G469" t="n">
-        <v>2.88978481292725</v>
+        <v>2.88978433609009</v>
       </c>
       <c r="H469" t="n">
         <v>2260751</v>
@@ -13999,7 +13999,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G470" t="n">
-        <v>2.88978481292725</v>
+        <v>2.88978433609009</v>
       </c>
       <c r="H470" t="n">
         <v>1595268</v>
@@ -14028,7 +14028,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G471" t="n">
-        <v>2.94073414802551</v>
+        <v>2.94073390960693</v>
       </c>
       <c r="H471" t="n">
         <v>2019957</v>
@@ -14057,7 +14057,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G472" t="n">
-        <v>2.92640471458435</v>
+        <v>2.92640447616577</v>
       </c>
       <c r="H472" t="n">
         <v>1536307</v>
@@ -14144,7 +14144,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>2.93754959106445</v>
+        <v>2.93754982948303</v>
       </c>
       <c r="H475" t="n">
         <v>968072</v>
@@ -14173,7 +14173,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G476" t="n">
-        <v>2.90252184867859</v>
+        <v>2.90252161026001</v>
       </c>
       <c r="H476" t="n">
         <v>1820893</v>
@@ -14202,7 +14202,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G477" t="n">
-        <v>2.84201955795288</v>
+        <v>2.84201979637146</v>
       </c>
       <c r="H477" t="n">
         <v>4515902</v>
@@ -14231,7 +14231,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G478" t="n">
-        <v>2.81017637252808</v>
+        <v>2.8101761341095</v>
       </c>
       <c r="H478" t="n">
         <v>3456844</v>
@@ -14260,7 +14260,7 @@
         <v>3.4539999961853</v>
       </c>
       <c r="G479" t="n">
-        <v>2.74967360496521</v>
+        <v>2.74967384338379</v>
       </c>
       <c r="H479" t="n">
         <v>5446955</v>
@@ -14318,7 +14318,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G481" t="n">
-        <v>2.54746866226196</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H481" t="n">
         <v>6308592</v>
@@ -14463,7 +14463,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G486" t="n">
-        <v>2.48537397384644</v>
+        <v>2.48537373542786</v>
       </c>
       <c r="H486" t="n">
         <v>1237843</v>
@@ -14492,7 +14492,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G487" t="n">
-        <v>2.45989894866943</v>
+        <v>2.45989918708801</v>
       </c>
       <c r="H487" t="n">
         <v>932298</v>
@@ -14521,7 +14521,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G488" t="n">
-        <v>2.44238543510437</v>
+        <v>2.44238567352295</v>
       </c>
       <c r="H488" t="n">
         <v>1422705</v>
@@ -14579,7 +14579,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G490" t="n">
-        <v>2.43760919570923</v>
+        <v>2.43760871887207</v>
       </c>
       <c r="H490" t="n">
         <v>1832928</v>
@@ -14608,7 +14608,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G491" t="n">
-        <v>2.44716191291809</v>
+        <v>2.44716167449951</v>
       </c>
       <c r="H491" t="n">
         <v>2154714</v>
@@ -14637,7 +14637,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G492" t="n">
-        <v>2.44716191291809</v>
+        <v>2.44716167449951</v>
       </c>
       <c r="H492" t="n">
         <v>1691378</v>
@@ -14666,7 +14666,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G493" t="n">
-        <v>2.46149158477783</v>
+        <v>2.46149134635925</v>
       </c>
       <c r="H493" t="n">
         <v>2679317</v>
@@ -14724,7 +14724,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G495" t="n">
-        <v>2.53632378578186</v>
+        <v>2.5363233089447</v>
       </c>
       <c r="H495" t="n">
         <v>1344034</v>
@@ -14753,7 +14753,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G496" t="n">
-        <v>2.53154683113098</v>
+        <v>2.53154730796814</v>
       </c>
       <c r="H496" t="n">
         <v>2034742</v>
@@ -14782,7 +14782,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>2.4837818145752</v>
+        <v>2.48378157615662</v>
       </c>
       <c r="H497" t="n">
         <v>1452840</v>
@@ -14811,7 +14811,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G498" t="n">
-        <v>2.52199363708496</v>
+        <v>2.52199387550354</v>
       </c>
       <c r="H498" t="n">
         <v>1764419</v>
@@ -14840,7 +14840,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G499" t="n">
-        <v>2.52040195465088</v>
+        <v>2.5204017162323</v>
       </c>
       <c r="H499" t="n">
         <v>1758820</v>
@@ -14869,7 +14869,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G500" t="n">
-        <v>2.53473114967346</v>
+        <v>2.53473091125488</v>
       </c>
       <c r="H500" t="n">
         <v>1330089</v>
@@ -14898,7 +14898,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G501" t="n">
-        <v>2.60160231590271</v>
+        <v>2.60160207748413</v>
       </c>
       <c r="H501" t="n">
         <v>1303907</v>
@@ -14927,7 +14927,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G502" t="n">
-        <v>2.55383729934692</v>
+        <v>2.55383706092834</v>
       </c>
       <c r="H502" t="n">
         <v>1941059</v>
@@ -14956,7 +14956,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G503" t="n">
-        <v>2.53154683113098</v>
+        <v>2.53154730796814</v>
       </c>
       <c r="H503" t="n">
         <v>1750900</v>
@@ -14985,7 +14985,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>2.5076642036438</v>
+        <v>2.50766444206238</v>
       </c>
       <c r="H504" t="n">
         <v>1490065</v>
@@ -15014,7 +15014,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G505" t="n">
-        <v>2.515625</v>
+        <v>2.51562523841858</v>
       </c>
       <c r="H505" t="n">
         <v>2056515</v>
@@ -15043,7 +15043,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G506" t="n">
-        <v>2.58886504173279</v>
+        <v>2.58886528015137</v>
       </c>
       <c r="H506" t="n">
         <v>4068179</v>
@@ -15101,7 +15101,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G508" t="n">
-        <v>2.51084876060486</v>
+        <v>2.51084899902344</v>
       </c>
       <c r="H508" t="n">
         <v>2514530</v>
@@ -15130,7 +15130,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G509" t="n">
-        <v>2.52995467185974</v>
+        <v>2.52995443344116</v>
       </c>
       <c r="H509" t="n">
         <v>917841</v>
@@ -15188,7 +15188,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G511" t="n">
-        <v>2.5617983341217</v>
+        <v>2.56179809570312</v>
       </c>
       <c r="H511" t="n">
         <v>494732</v>
@@ -15304,7 +15304,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G515" t="n">
-        <v>2.65891981124878</v>
+        <v>2.65892028808594</v>
       </c>
       <c r="H515" t="n">
         <v>1978965</v>
@@ -15333,7 +15333,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G516" t="n">
-        <v>2.75604248046875</v>
+        <v>2.75604271888733</v>
       </c>
       <c r="H516" t="n">
         <v>1906217</v>
@@ -15362,7 +15362,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G517" t="n">
-        <v>2.72579121589661</v>
+        <v>2.72579145431519</v>
       </c>
       <c r="H517" t="n">
         <v>1064648</v>
@@ -15391,7 +15391,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G518" t="n">
-        <v>2.74808168411255</v>
+        <v>2.74808144569397</v>
       </c>
       <c r="H518" t="n">
         <v>1415599</v>
@@ -15449,7 +15449,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G520" t="n">
-        <v>2.75604248046875</v>
+        <v>2.75604271888733</v>
       </c>
       <c r="H520" t="n">
         <v>605258</v>
@@ -15478,7 +15478,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G521" t="n">
-        <v>2.676433801651</v>
+        <v>2.67643404006958</v>
       </c>
       <c r="H521" t="n">
         <v>2011203</v>
@@ -15507,7 +15507,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G522" t="n">
-        <v>2.63822197914124</v>
+        <v>2.63822221755981</v>
       </c>
       <c r="H522" t="n">
         <v>1918826</v>
@@ -15594,7 +15594,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G525" t="n">
-        <v>2.61911630630493</v>
+        <v>2.61911606788635</v>
       </c>
       <c r="H525" t="n">
         <v>990093</v>
@@ -15623,7 +15623,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G526" t="n">
-        <v>2.63185358047485</v>
+        <v>2.63185334205627</v>
       </c>
       <c r="H526" t="n">
         <v>1221618</v>
@@ -15652,7 +15652,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G527" t="n">
-        <v>2.62070846557617</v>
+        <v>2.62070822715759</v>
       </c>
       <c r="H527" t="n">
         <v>2511181</v>
@@ -15681,7 +15681,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G528" t="n">
-        <v>2.54746866226196</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H528" t="n">
         <v>2145554</v>
@@ -15797,7 +15797,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G532" t="n">
-        <v>2.58249616622925</v>
+        <v>2.58249592781067</v>
       </c>
       <c r="H532" t="n">
         <v>1967995</v>
@@ -15826,7 +15826,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G533" t="n">
-        <v>2.58090400695801</v>
+        <v>2.58090424537659</v>
       </c>
       <c r="H533" t="n">
         <v>735592</v>
@@ -15855,7 +15855,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G534" t="n">
-        <v>2.54746866226196</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H534" t="n">
         <v>2025801</v>
@@ -15884,7 +15884,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G535" t="n">
-        <v>2.41213440895081</v>
+        <v>2.41213417053223</v>
       </c>
       <c r="H535" t="n">
         <v>3237676</v>
@@ -15913,7 +15913,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G536" t="n">
-        <v>2.34526348114014</v>
+        <v>2.34526324272156</v>
       </c>
       <c r="H536" t="n">
         <v>2994862</v>
@@ -15942,7 +15942,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>2.23699593544006</v>
+        <v>2.23699569702148</v>
       </c>
       <c r="H537" t="n">
         <v>6215290</v>
@@ -16000,7 +16000,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G539" t="n">
-        <v>2.12872838973999</v>
+        <v>2.12872862815857</v>
       </c>
       <c r="H539" t="n">
         <v>4819283</v>
@@ -16058,7 +16058,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>2.0538969039917</v>
+        <v>2.05389666557312</v>
       </c>
       <c r="H541" t="n">
         <v>1892118</v>
@@ -16087,7 +16087,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G542" t="n">
-        <v>2.01409220695496</v>
+        <v>2.01409244537354</v>
       </c>
       <c r="H542" t="n">
         <v>2601422</v>
@@ -16348,7 +16348,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G551" t="n">
-        <v>2.01727700233459</v>
+        <v>2.01727652549744</v>
       </c>
       <c r="H551" t="n">
         <v>1462101</v>
@@ -16377,7 +16377,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G552" t="n">
-        <v>2.00294709205627</v>
+        <v>2.0029468536377</v>
       </c>
       <c r="H552" t="n">
         <v>2572034</v>
@@ -16406,7 +16406,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G553" t="n">
-        <v>1.98702573776245</v>
+        <v>1.98702538013458</v>
       </c>
       <c r="H553" t="n">
         <v>1328048</v>
@@ -16435,7 +16435,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G554" t="n">
-        <v>1.94881331920624</v>
+        <v>1.94881319999695</v>
       </c>
       <c r="H554" t="n">
         <v>1690849</v>
@@ -16464,7 +16464,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90741682052612</v>
+        <v>1.90741717815399</v>
       </c>
       <c r="H555" t="n">
         <v>2204356</v>
@@ -16551,7 +16551,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G558" t="n">
-        <v>2.01090788841248</v>
+        <v>2.01090812683105</v>
       </c>
       <c r="H558" t="n">
         <v>1799452</v>
@@ -16580,7 +16580,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G559" t="n">
-        <v>2.0316059589386</v>
+        <v>2.03160619735718</v>
       </c>
       <c r="H559" t="n">
         <v>1090698</v>
@@ -16609,7 +16609,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G560" t="n">
-        <v>2.10325360298157</v>
+        <v>2.10325384140015</v>
       </c>
       <c r="H560" t="n">
         <v>2761128</v>
@@ -16638,7 +16638,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G561" t="n">
-        <v>2.03001403808594</v>
+        <v>2.03001379966736</v>
       </c>
       <c r="H561" t="n">
         <v>1984054</v>
@@ -16667,7 +16667,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G562" t="n">
-        <v>1.91856253147125</v>
+        <v>1.91856229305267</v>
       </c>
       <c r="H562" t="n">
         <v>4495971</v>
@@ -16696,7 +16696,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G563" t="n">
-        <v>1.80870282649994</v>
+        <v>1.80870270729065</v>
       </c>
       <c r="H563" t="n">
         <v>11295853</v>
@@ -16754,7 +16754,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G565" t="n">
-        <v>2.05071210861206</v>
+        <v>2.05071258544922</v>
       </c>
       <c r="H565" t="n">
         <v>10241397</v>
@@ -16783,7 +16783,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G566" t="n">
-        <v>2.01886868476868</v>
+        <v>2.01886916160583</v>
       </c>
       <c r="H566" t="n">
         <v>2915816</v>
@@ -16812,7 +16812,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G567" t="n">
-        <v>1.99976336956024</v>
+        <v>1.9997626543045</v>
       </c>
       <c r="H567" t="n">
         <v>1325179</v>
@@ -16870,7 +16870,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>1.85487532615662</v>
+        <v>1.8548755645752</v>
       </c>
       <c r="H569" t="n">
         <v>4051183</v>
@@ -16899,7 +16899,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94562923908234</v>
+        <v>1.94562888145447</v>
       </c>
       <c r="H570" t="n">
         <v>2696695</v>
@@ -16957,7 +16957,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91219353675842</v>
+        <v>1.91219365596771</v>
       </c>
       <c r="H572" t="n">
         <v>1317721</v>
@@ -16986,7 +16986,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G573" t="n">
-        <v>1.92015421390533</v>
+        <v>1.92015433311462</v>
       </c>
       <c r="H573" t="n">
         <v>1478662</v>
@@ -17015,7 +17015,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G574" t="n">
-        <v>1.91856253147125</v>
+        <v>1.91856229305267</v>
       </c>
       <c r="H574" t="n">
         <v>1225403</v>
@@ -17044,7 +17044,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G575" t="n">
-        <v>1.89945614337921</v>
+        <v>1.89945638179779</v>
       </c>
       <c r="H575" t="n">
         <v>1034331</v>
@@ -17073,7 +17073,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G576" t="n">
-        <v>1.90582489967346</v>
+        <v>1.90582478046417</v>
       </c>
       <c r="H576" t="n">
         <v>1701979</v>
@@ -17102,7 +17102,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G577" t="n">
-        <v>1.9519978761673</v>
+        <v>1.95199739933014</v>
       </c>
       <c r="H577" t="n">
         <v>2027295</v>
@@ -17131,7 +17131,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G578" t="n">
-        <v>1.92015421390533</v>
+        <v>1.92015433311462</v>
       </c>
       <c r="H578" t="n">
         <v>2780712</v>
@@ -17160,7 +17160,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.92652368545532</v>
+        <v>1.92652320861816</v>
       </c>
       <c r="H579" t="n">
         <v>722313</v>
@@ -17218,7 +17218,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>1.90264058113098</v>
+        <v>1.90264081954956</v>
       </c>
       <c r="H581" t="n">
         <v>921579</v>
@@ -17247,7 +17247,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G582" t="n">
-        <v>1.90423274040222</v>
+        <v>1.90423250198364</v>
       </c>
       <c r="H582" t="n">
         <v>1500268</v>
@@ -17276,7 +17276,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G583" t="n">
-        <v>1.89627206325531</v>
+        <v>1.89627194404602</v>
       </c>
       <c r="H583" t="n">
         <v>944622</v>
@@ -17305,7 +17305,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G584" t="n">
-        <v>1.88194262981415</v>
+        <v>1.88194251060486</v>
       </c>
       <c r="H584" t="n">
         <v>1407864</v>
@@ -17334,7 +17334,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G585" t="n">
-        <v>1.85487532615662</v>
+        <v>1.8548755645752</v>
       </c>
       <c r="H585" t="n">
         <v>1777023</v>
@@ -17363,7 +17363,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G586" t="n">
-        <v>1.85009908676147</v>
+        <v>1.85009872913361</v>
       </c>
       <c r="H586" t="n">
         <v>1482418</v>
@@ -17392,7 +17392,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G587" t="n">
-        <v>1.86283624172211</v>
+        <v>1.86283648014069</v>
       </c>
       <c r="H587" t="n">
         <v>2223013</v>
@@ -17450,7 +17450,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G589" t="n">
-        <v>1.8150714635849</v>
+        <v>1.81507134437561</v>
       </c>
       <c r="H589" t="n">
         <v>1297798</v>
@@ -17479,7 +17479,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G590" t="n">
-        <v>1.8150714635849</v>
+        <v>1.81507134437561</v>
       </c>
       <c r="H590" t="n">
         <v>1110350</v>
@@ -17508,7 +17508,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G591" t="n">
-        <v>1.80392599105835</v>
+        <v>1.80392611026764</v>
       </c>
       <c r="H591" t="n">
         <v>1332399</v>
@@ -17537,7 +17537,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G592" t="n">
-        <v>1.76412200927734</v>
+        <v>1.76412189006805</v>
       </c>
       <c r="H592" t="n">
         <v>2941699</v>
@@ -17566,7 +17566,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G593" t="n">
-        <v>1.78004384040833</v>
+        <v>1.78004360198975</v>
       </c>
       <c r="H593" t="n">
         <v>1670608</v>
@@ -17653,7 +17653,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G596" t="n">
-        <v>1.89149522781372</v>
+        <v>1.89149510860443</v>
       </c>
       <c r="H596" t="n">
         <v>13135214</v>
@@ -17682,7 +17682,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>1.85487532615662</v>
+        <v>1.8548755645752</v>
       </c>
       <c r="H597" t="n">
         <v>5522687</v>
@@ -17711,7 +17711,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G598" t="n">
-        <v>1.87238919734955</v>
+        <v>1.87238955497742</v>
       </c>
       <c r="H598" t="n">
         <v>2693236</v>
@@ -17769,7 +17769,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G600" t="n">
-        <v>1.87238919734955</v>
+        <v>1.87238955497742</v>
       </c>
       <c r="H600" t="n">
         <v>1249089</v>
@@ -17798,7 +17798,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G601" t="n">
-        <v>1.82621657848358</v>
+        <v>1.82621645927429</v>
       </c>
       <c r="H601" t="n">
         <v>2208316</v>
@@ -17827,7 +17827,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>1.83576941490173</v>
+        <v>1.83576965332031</v>
       </c>
       <c r="H602" t="n">
         <v>981017</v>
@@ -17856,7 +17856,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G603" t="n">
-        <v>1.8835346698761</v>
+        <v>1.88353455066681</v>
       </c>
       <c r="H603" t="n">
         <v>2143576</v>
@@ -17885,7 +17885,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.85487532615662</v>
+        <v>1.8548755645752</v>
       </c>
       <c r="H604" t="n">
         <v>1300520</v>
@@ -17914,7 +17914,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G605" t="n">
-        <v>1.81825566291809</v>
+        <v>1.81825578212738</v>
       </c>
       <c r="H605" t="n">
         <v>3157751</v>
@@ -17943,7 +17943,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G606" t="n">
-        <v>1.80074179172516</v>
+        <v>1.80074191093445</v>
       </c>
       <c r="H606" t="n">
         <v>1597477</v>
@@ -17972,7 +17972,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.77526724338531</v>
+        <v>1.77526712417603</v>
       </c>
       <c r="H607" t="n">
         <v>1953879</v>
@@ -18001,7 +18001,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G608" t="n">
-        <v>1.83642685413361</v>
+        <v>1.8364269733429</v>
       </c>
       <c r="H608" t="n">
         <v>1235443</v>
@@ -18030,7 +18030,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G609" t="n">
-        <v>1.82501029968262</v>
+        <v>1.82501041889191</v>
       </c>
       <c r="H609" t="n">
         <v>1866217</v>
@@ -18059,7 +18059,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>1.81848692893982</v>
+        <v>1.81848669052124</v>
       </c>
       <c r="H610" t="n">
         <v>1189890</v>
@@ -18088,7 +18088,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G611" t="n">
-        <v>1.82174861431122</v>
+        <v>1.82174873352051</v>
       </c>
       <c r="H611" t="n">
         <v>639504</v>
@@ -18117,7 +18117,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G612" t="n">
-        <v>1.78423726558685</v>
+        <v>1.78423714637756</v>
       </c>
       <c r="H612" t="n">
         <v>1133216</v>
@@ -18146,7 +18146,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>1.72878551483154</v>
+        <v>1.72878575325012</v>
       </c>
       <c r="H613" t="n">
         <v>2708744</v>
@@ -18175,7 +18175,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G614" t="n">
-        <v>1.73367822170258</v>
+        <v>1.73367846012115</v>
       </c>
       <c r="H614" t="n">
         <v>2260783</v>
@@ -18204,7 +18204,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G615" t="n">
-        <v>1.72878551483154</v>
+        <v>1.72878575325012</v>
       </c>
       <c r="H615" t="n">
         <v>1733659</v>
@@ -18262,7 +18262,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G617" t="n">
-        <v>1.78586828708649</v>
+        <v>1.7858681678772</v>
       </c>
       <c r="H617" t="n">
         <v>2304857</v>
@@ -18349,7 +18349,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G620" t="n">
-        <v>1.77445161342621</v>
+        <v>1.77445185184479</v>
       </c>
       <c r="H620" t="n">
         <v>1303635</v>
@@ -18465,7 +18465,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G624" t="n">
-        <v>1.76629710197449</v>
+        <v>1.76629686355591</v>
       </c>
       <c r="H624" t="n">
         <v>2399225</v>
@@ -18494,7 +18494,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G625" t="n">
-        <v>1.76629710197449</v>
+        <v>1.76629686355591</v>
       </c>
       <c r="H625" t="n">
         <v>566494</v>
@@ -18523,7 +18523,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G626" t="n">
-        <v>1.8445817232132</v>
+        <v>1.84458184242249</v>
       </c>
       <c r="H626" t="n">
         <v>1938784</v>
@@ -18552,7 +18552,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>1.8674144744873</v>
+        <v>1.86741471290588</v>
       </c>
       <c r="H627" t="n">
         <v>2849945</v>
@@ -18581,7 +18581,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G628" t="n">
-        <v>1.8445817232132</v>
+        <v>1.84458184242249</v>
       </c>
       <c r="H628" t="n">
         <v>450028</v>
@@ -18610,7 +18610,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G629" t="n">
-        <v>1.84947419166565</v>
+        <v>1.84947431087494</v>
       </c>
       <c r="H629" t="n">
         <v>517248</v>
@@ -18639,7 +18639,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G630" t="n">
-        <v>1.82664132118225</v>
+        <v>1.82664155960083</v>
       </c>
       <c r="H630" t="n">
         <v>683361</v>
@@ -18668,7 +18668,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G631" t="n">
-        <v>1.76466608047485</v>
+        <v>1.76466619968414</v>
       </c>
       <c r="H631" t="n">
         <v>968829</v>
@@ -18697,7 +18697,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G632" t="n">
-        <v>1.79239201545715</v>
+        <v>1.79239177703857</v>
       </c>
       <c r="H632" t="n">
         <v>2137127</v>
@@ -18726,7 +18726,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G633" t="n">
-        <v>1.7548805475235</v>
+        <v>1.75488030910492</v>
       </c>
       <c r="H633" t="n">
         <v>634287</v>
@@ -18755,7 +18755,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G634" t="n">
-        <v>1.77282071113586</v>
+        <v>1.77282083034515</v>
       </c>
       <c r="H634" t="n">
         <v>471187</v>
@@ -18813,7 +18813,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G636" t="n">
-        <v>1.7434641122818</v>
+        <v>1.74346399307251</v>
       </c>
       <c r="H636" t="n">
         <v>489960</v>
@@ -18871,7 +18871,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G638" t="n">
-        <v>1.8869856595993</v>
+        <v>1.88698589801788</v>
       </c>
       <c r="H638" t="n">
         <v>2351541</v>
@@ -18900,7 +18900,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G639" t="n">
-        <v>1.89187848567963</v>
+        <v>1.89187836647034</v>
       </c>
       <c r="H639" t="n">
         <v>1290827</v>
@@ -18929,7 +18929,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G640" t="n">
-        <v>1.81359386444092</v>
+        <v>1.81359398365021</v>
       </c>
       <c r="H640" t="n">
         <v>2559667</v>
@@ -18958,7 +18958,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G641" t="n">
-        <v>1.86578404903412</v>
+        <v>1.86578369140625</v>
       </c>
       <c r="H641" t="n">
         <v>1601256</v>
@@ -19016,7 +19016,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G643" t="n">
-        <v>1.90655696392059</v>
+        <v>1.9065568447113</v>
       </c>
       <c r="H643" t="n">
         <v>1155916</v>
@@ -19045,7 +19045,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G644" t="n">
-        <v>1.88372385501862</v>
+        <v>1.88372397422791</v>
       </c>
       <c r="H644" t="n">
         <v>1335295</v>
@@ -19103,7 +19103,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>1.8674144744873</v>
+        <v>1.86741471290588</v>
       </c>
       <c r="H646" t="n">
         <v>465309</v>
@@ -19132,7 +19132,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G647" t="n">
-        <v>1.82827258110046</v>
+        <v>1.82827246189117</v>
       </c>
       <c r="H647" t="n">
         <v>550682</v>
@@ -19161,7 +19161,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G648" t="n">
-        <v>1.81685590744019</v>
+        <v>1.81685566902161</v>
       </c>
       <c r="H648" t="n">
         <v>605104</v>
@@ -19219,7 +19219,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>1.81848692893982</v>
+        <v>1.81848669052124</v>
       </c>
       <c r="H650" t="n">
         <v>710538</v>
@@ -19248,7 +19248,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G651" t="n">
-        <v>1.79239201545715</v>
+        <v>1.79239177703857</v>
       </c>
       <c r="H651" t="n">
         <v>2071396</v>
@@ -19277,7 +19277,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G652" t="n">
-        <v>1.77445161342621</v>
+        <v>1.77445185184479</v>
       </c>
       <c r="H652" t="n">
         <v>882911</v>
@@ -19306,7 +19306,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G653" t="n">
-        <v>1.77282071113586</v>
+        <v>1.77282083034515</v>
       </c>
       <c r="H653" t="n">
         <v>747019</v>
@@ -19335,7 +19335,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78749918937683</v>
+        <v>1.78749907016754</v>
       </c>
       <c r="H654" t="n">
         <v>659037</v>
@@ -19364,7 +19364,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>1.75324976444244</v>
+        <v>1.75324964523315</v>
       </c>
       <c r="H655" t="n">
         <v>913367</v>
@@ -19451,7 +19451,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G658" t="n">
-        <v>1.8331652879715</v>
+        <v>1.83316504955292</v>
       </c>
       <c r="H658" t="n">
         <v>1422538</v>
@@ -19509,7 +19509,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G660" t="n">
-        <v>1.84131956100464</v>
+        <v>1.84131979942322</v>
       </c>
       <c r="H660" t="n">
         <v>617222</v>
@@ -19538,7 +19538,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G661" t="n">
-        <v>1.82337975502014</v>
+        <v>1.82337963581085</v>
       </c>
       <c r="H661" t="n">
         <v>839503</v>
@@ -19567,7 +19567,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G662" t="n">
-        <v>1.79239201545715</v>
+        <v>1.79239177703857</v>
       </c>
       <c r="H662" t="n">
         <v>897689</v>
@@ -19596,7 +19596,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G663" t="n">
-        <v>1.79076099395752</v>
+        <v>1.7907612323761</v>
       </c>
       <c r="H663" t="n">
         <v>561281</v>
@@ -19654,7 +19654,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G665" t="n">
-        <v>1.89187848567963</v>
+        <v>1.89187836647034</v>
       </c>
       <c r="H665" t="n">
         <v>4688332</v>
@@ -19712,7 +19712,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G667" t="n">
-        <v>1.85926032066345</v>
+        <v>1.85925996303558</v>
       </c>
       <c r="H667" t="n">
         <v>963738</v>
@@ -19741,7 +19741,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G668" t="n">
-        <v>1.86415302753448</v>
+        <v>1.86415266990662</v>
       </c>
       <c r="H668" t="n">
         <v>885313</v>
@@ -19770,7 +19770,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G669" t="n">
-        <v>1.85762917995453</v>
+        <v>1.85762906074524</v>
       </c>
       <c r="H669" t="n">
         <v>854370</v>
@@ -19828,7 +19828,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G671" t="n">
-        <v>1.90818762779236</v>
+        <v>1.90818798542023</v>
       </c>
       <c r="H671" t="n">
         <v>1160035</v>
@@ -19886,7 +19886,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G673" t="n">
-        <v>1.99136543273926</v>
+        <v>1.99136555194855</v>
       </c>
       <c r="H673" t="n">
         <v>853924</v>
@@ -19915,7 +19915,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G674" t="n">
-        <v>1.99136543273926</v>
+        <v>1.99136555194855</v>
       </c>
       <c r="H674" t="n">
         <v>854975</v>
@@ -19944,7 +19944,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G675" t="n">
-        <v>1.95548486709595</v>
+        <v>1.95548498630524</v>
       </c>
       <c r="H675" t="n">
         <v>2650527</v>
@@ -20002,7 +20002,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G677" t="n">
-        <v>1.90329527854919</v>
+        <v>1.90329551696777</v>
       </c>
       <c r="H677" t="n">
         <v>1584415</v>
@@ -20060,7 +20060,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G679" t="n">
-        <v>1.86415302753448</v>
+        <v>1.86415266990662</v>
       </c>
       <c r="H679" t="n">
         <v>868801</v>
@@ -20089,7 +20089,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G680" t="n">
-        <v>1.81359386444092</v>
+        <v>1.81359398365021</v>
       </c>
       <c r="H680" t="n">
         <v>1115411</v>
@@ -20118,7 +20118,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71084547042847</v>
+        <v>1.71084570884705</v>
       </c>
       <c r="H681" t="n">
         <v>2819967</v>
@@ -20147,7 +20147,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G682" t="n">
-        <v>1.76466608047485</v>
+        <v>1.76466619968414</v>
       </c>
       <c r="H682" t="n">
         <v>4168427</v>
@@ -20176,7 +20176,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G683" t="n">
-        <v>1.73367822170258</v>
+        <v>1.73367846012115</v>
       </c>
       <c r="H683" t="n">
         <v>2641844</v>
@@ -20205,7 +20205,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82337975502014</v>
+        <v>1.82337963581085</v>
       </c>
       <c r="H684" t="n">
         <v>2326497</v>
@@ -20234,7 +20234,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>1.82664132118225</v>
+        <v>1.82664155960083</v>
       </c>
       <c r="H685" t="n">
         <v>2020822</v>
@@ -20292,7 +20292,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G687" t="n">
-        <v>1.91471183300018</v>
+        <v>1.91471195220947</v>
       </c>
       <c r="H687" t="n">
         <v>1051261</v>
@@ -20321,7 +20321,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G688" t="n">
-        <v>1.90329527854919</v>
+        <v>1.90329551696777</v>
       </c>
       <c r="H688" t="n">
         <v>523293</v>
@@ -20350,7 +20350,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G689" t="n">
-        <v>1.91308081150055</v>
+        <v>1.91308057308197</v>
       </c>
       <c r="H689" t="n">
         <v>689161</v>
@@ -20379,7 +20379,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G690" t="n">
-        <v>1.89840221405029</v>
+        <v>1.89840233325958</v>
       </c>
       <c r="H690" t="n">
         <v>429766</v>
@@ -20408,7 +20408,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G691" t="n">
-        <v>1.86415302753448</v>
+        <v>1.86415266990662</v>
       </c>
       <c r="H691" t="n">
         <v>339281</v>
@@ -20495,7 +20495,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G694" t="n">
-        <v>1.81685590744019</v>
+        <v>1.81685566902161</v>
       </c>
       <c r="H694" t="n">
         <v>1394273</v>
@@ -20524,7 +20524,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G695" t="n">
-        <v>1.80707037448883</v>
+        <v>1.80707013607025</v>
       </c>
       <c r="H695" t="n">
         <v>756669</v>
@@ -20553,7 +20553,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>1.81359386444092</v>
+        <v>1.81359398365021</v>
       </c>
       <c r="H696" t="n">
         <v>998393</v>
@@ -20611,7 +20611,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G698" t="n">
-        <v>1.78749918937683</v>
+        <v>1.78749907016754</v>
       </c>
       <c r="H698" t="n">
         <v>796654</v>
@@ -20640,7 +20640,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G699" t="n">
-        <v>1.75324976444244</v>
+        <v>1.75324964523315</v>
       </c>
       <c r="H699" t="n">
         <v>1589594</v>
@@ -20669,7 +20669,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>1.75324976444244</v>
+        <v>1.75324964523315</v>
       </c>
       <c r="H700" t="n">
         <v>570256</v>
@@ -20698,7 +20698,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G701" t="n">
-        <v>1.73041665554047</v>
+        <v>1.73041653633118</v>
       </c>
       <c r="H701" t="n">
         <v>811499</v>
@@ -20785,7 +20785,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G704" t="n">
-        <v>1.65050101280212</v>
+        <v>1.65050089359283</v>
       </c>
       <c r="H704" t="n">
         <v>2017014</v>
@@ -20814,7 +20814,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G705" t="n">
-        <v>1.6619176864624</v>
+        <v>1.66191756725311</v>
       </c>
       <c r="H705" t="n">
         <v>6571728</v>
@@ -20872,7 +20872,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G707" t="n">
-        <v>1.58607935905457</v>
+        <v>1.58607923984528</v>
       </c>
       <c r="H707" t="n">
         <v>1261183</v>
@@ -20959,7 +20959,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G710" t="n">
-        <v>1.4816997051239</v>
+        <v>1.48169982433319</v>
       </c>
       <c r="H710" t="n">
         <v>2572970</v>
@@ -20988,7 +20988,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>1.48006904125214</v>
+        <v>1.48006880283356</v>
       </c>
       <c r="H711" t="n">
         <v>2169717</v>
@@ -21017,7 +21017,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G712" t="n">
-        <v>1.48496162891388</v>
+        <v>1.48496174812317</v>
       </c>
       <c r="H712" t="n">
         <v>915632</v>
@@ -21046,7 +21046,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G713" t="n">
-        <v>1.53225839138031</v>
+        <v>1.5322585105896</v>
       </c>
       <c r="H713" t="n">
         <v>1420345</v>
@@ -21075,7 +21075,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.48822331428528</v>
+        <v>1.48822355270386</v>
       </c>
       <c r="H714" t="n">
         <v>3092187</v>
@@ -21133,7 +21133,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G716" t="n">
-        <v>1.50208640098572</v>
+        <v>1.50208628177643</v>
       </c>
       <c r="H716" t="n">
         <v>2096415</v>
@@ -21162,7 +21162,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G717" t="n">
-        <v>1.46212875843048</v>
+        <v>1.4621285200119</v>
       </c>
       <c r="H717" t="n">
         <v>814779</v>
@@ -21336,7 +21336,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G723" t="n">
-        <v>1.57874023914337</v>
+        <v>1.5787398815155</v>
       </c>
       <c r="H723" t="n">
         <v>621410</v>
@@ -21365,7 +21365,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G724" t="n">
-        <v>1.58852553367615</v>
+        <v>1.58852565288544</v>
       </c>
       <c r="H724" t="n">
         <v>629415</v>
@@ -21394,7 +21394,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G725" t="n">
-        <v>1.62032878398895</v>
+        <v>1.62032866477966</v>
       </c>
       <c r="H725" t="n">
         <v>678094</v>
@@ -21423,7 +21423,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G726" t="n">
-        <v>1.63419163227081</v>
+        <v>1.6341917514801</v>
       </c>
       <c r="H726" t="n">
         <v>1024698</v>
@@ -21452,7 +21452,7 @@
         <v>2</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092982769012</v>
+        <v>1.63092994689941</v>
       </c>
       <c r="H727" t="n">
         <v>594452</v>
@@ -21481,7 +21481,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G728" t="n">
-        <v>1.61706709861755</v>
+        <v>1.61706686019897</v>
       </c>
       <c r="H728" t="n">
         <v>586071</v>
@@ -21539,7 +21539,7 @@
         <v>2</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092982769012</v>
+        <v>1.63092994689941</v>
       </c>
       <c r="H730" t="n">
         <v>355011</v>
@@ -21568,7 +21568,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G731" t="n">
-        <v>1.61625134944916</v>
+        <v>1.61625158786774</v>
       </c>
       <c r="H731" t="n">
         <v>498536</v>
@@ -21597,7 +21597,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>1.59831130504608</v>
+        <v>1.59831118583679</v>
       </c>
       <c r="H732" t="n">
         <v>398648</v>
@@ -21626,7 +21626,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G733" t="n">
-        <v>1.51187181472778</v>
+        <v>1.51187205314636</v>
       </c>
       <c r="H733" t="n">
         <v>1759383</v>
@@ -21655,7 +21655,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G734" t="n">
-        <v>1.50453281402588</v>
+        <v>1.50453293323517</v>
       </c>
       <c r="H734" t="n">
         <v>1397140</v>
@@ -21713,7 +21713,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G736" t="n">
-        <v>1.54285955429077</v>
+        <v>1.54285979270935</v>
       </c>
       <c r="H736" t="n">
         <v>867680</v>
@@ -21771,7 +21771,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G738" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H738" t="n">
         <v>609667</v>
@@ -21887,7 +21887,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G742" t="n">
-        <v>1.51024091243744</v>
+        <v>1.51024103164673</v>
       </c>
       <c r="H742" t="n">
         <v>802068</v>
@@ -21945,7 +21945,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G744" t="n">
-        <v>1.50453281402588</v>
+        <v>1.50453293323517</v>
       </c>
       <c r="H744" t="n">
         <v>1047194</v>
@@ -21974,7 +21974,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G745" t="n">
-        <v>1.4980092048645</v>
+        <v>1.49800908565521</v>
       </c>
       <c r="H745" t="n">
         <v>859693</v>
@@ -22003,7 +22003,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>1.45152771472931</v>
+        <v>1.45152747631073</v>
       </c>
       <c r="H746" t="n">
         <v>1189559</v>
@@ -22032,7 +22032,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G747" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H747" t="n">
         <v>878377</v>
@@ -22061,7 +22061,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G748" t="n">
-        <v>1.46049761772156</v>
+        <v>1.46049773693085</v>
       </c>
       <c r="H748" t="n">
         <v>456440</v>
@@ -22090,7 +22090,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G749" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H749" t="n">
         <v>408407</v>
@@ -22177,7 +22177,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G752" t="n">
-        <v>1.36345732212067</v>
+        <v>1.36345744132996</v>
       </c>
       <c r="H752" t="n">
         <v>722243</v>
@@ -22206,7 +22206,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G753" t="n">
-        <v>1.36345732212067</v>
+        <v>1.36345744132996</v>
       </c>
       <c r="H753" t="n">
         <v>680677</v>
@@ -22235,7 +22235,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G754" t="n">
-        <v>1.37242746353149</v>
+        <v>1.3724273443222</v>
       </c>
       <c r="H754" t="n">
         <v>1083070</v>
@@ -22293,7 +22293,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G756" t="n">
-        <v>1.09272301197052</v>
+        <v>1.09272289276123</v>
       </c>
       <c r="H756" t="n">
         <v>13977981</v>
@@ -22322,7 +22322,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>1.03564035892487</v>
+        <v>1.03564047813416</v>
       </c>
       <c r="H757" t="n">
         <v>3305025</v>
@@ -22351,7 +22351,7 @@
         <v>1.25</v>
       </c>
       <c r="G758" t="n">
-        <v>1.01933109760284</v>
+        <v>1.01933121681213</v>
       </c>
       <c r="H758" t="n">
         <v>3318339</v>
@@ -22438,7 +22438,7 @@
         <v>1.32700002193451</v>
       </c>
       <c r="G761" t="n">
-        <v>1.08212196826935</v>
+        <v>1.08212184906006</v>
       </c>
       <c r="H761" t="n">
         <v>3813414</v>
@@ -22496,7 +22496,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G763" t="n">
-        <v>1.15469837188721</v>
+        <v>1.15469813346863</v>
       </c>
       <c r="H763" t="n">
         <v>2560889</v>
@@ -22554,7 +22554,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G765" t="n">
-        <v>1.17426955699921</v>
+        <v>1.1742696762085</v>
       </c>
       <c r="H765" t="n">
         <v>2107430</v>
@@ -22583,7 +22583,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>1.17426955699921</v>
+        <v>1.1742696762085</v>
       </c>
       <c r="H766" t="n">
         <v>1555652</v>
@@ -22757,7 +22757,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G772" t="n">
-        <v>1.30311286449432</v>
+        <v>1.3031131029129</v>
       </c>
       <c r="H772" t="n">
         <v>1651898</v>
@@ -22786,7 +22786,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G773" t="n">
-        <v>1.32920789718628</v>
+        <v>1.32920777797699</v>
       </c>
       <c r="H773" t="n">
         <v>2959691</v>
@@ -22844,7 +22844,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G775" t="n">
-        <v>1.36019551753998</v>
+        <v>1.36019539833069</v>
       </c>
       <c r="H775" t="n">
         <v>1881833</v>
@@ -22873,7 +22873,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.38629019260406</v>
+        <v>1.38629031181335</v>
       </c>
       <c r="H776" t="n">
         <v>2583893</v>
@@ -22902,7 +22902,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G777" t="n">
-        <v>1.39770674705505</v>
+        <v>1.39770698547363</v>
       </c>
       <c r="H777" t="n">
         <v>2242382</v>
@@ -22931,7 +22931,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G778" t="n">
-        <v>1.31045210361481</v>
+        <v>1.3104522228241</v>
       </c>
       <c r="H778" t="n">
         <v>3033007</v>
@@ -22989,7 +22989,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G780" t="n">
-        <v>1.37813580036163</v>
+        <v>1.37813568115234</v>
       </c>
       <c r="H780" t="n">
         <v>3667223</v>
@@ -23047,7 +23047,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G782" t="n">
-        <v>1.50942552089691</v>
+        <v>1.50942540168762</v>
       </c>
       <c r="H782" t="n">
         <v>2051305</v>
@@ -23076,7 +23076,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G783" t="n">
-        <v>1.54693686962128</v>
+        <v>1.54693710803986</v>
       </c>
       <c r="H783" t="n">
         <v>2009197</v>
@@ -23163,7 +23163,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G786" t="n">
-        <v>1.56650817394257</v>
+        <v>1.56650805473328</v>
       </c>
       <c r="H786" t="n">
         <v>2160067</v>
@@ -23221,7 +23221,7 @@
         <v>1.96300005912781</v>
       </c>
       <c r="G788" t="n">
-        <v>1.60075771808624</v>
+        <v>1.60075759887695</v>
       </c>
       <c r="H788" t="n">
         <v>1529047</v>
@@ -23250,7 +23250,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G789" t="n">
-        <v>1.62440621852875</v>
+        <v>1.62440598011017</v>
       </c>
       <c r="H789" t="n">
         <v>3370317</v>
@@ -23279,7 +23279,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G790" t="n">
-        <v>1.61625134944916</v>
+        <v>1.61625158786774</v>
       </c>
       <c r="H790" t="n">
         <v>1851199</v>
@@ -23308,7 +23308,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G791" t="n">
-        <v>1.53878235816956</v>
+        <v>1.53878223896027</v>
       </c>
       <c r="H791" t="n">
         <v>937385</v>
@@ -23337,7 +23337,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G792" t="n">
-        <v>1.51839566230774</v>
+        <v>1.51839542388916</v>
       </c>
       <c r="H792" t="n">
         <v>1104048</v>
@@ -23395,7 +23395,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G794" t="n">
-        <v>1.5208420753479</v>
+        <v>1.52084219455719</v>
       </c>
       <c r="H794" t="n">
         <v>765785</v>
@@ -23511,7 +23511,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G798" t="n">
-        <v>1.67007207870483</v>
+        <v>1.67007219791412</v>
       </c>
       <c r="H798" t="n">
         <v>497000</v>
@@ -23569,7 +23569,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G800" t="n">
-        <v>1.64071559906006</v>
+        <v>1.64071547985077</v>
       </c>
       <c r="H800" t="n">
         <v>489775</v>
@@ -23627,7 +23627,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G802" t="n">
-        <v>1.68148875236511</v>
+        <v>1.6814888715744</v>
       </c>
       <c r="H802" t="n">
         <v>808567</v>
@@ -23656,7 +23656,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G803" t="n">
-        <v>1.70595276355743</v>
+        <v>1.70595252513885</v>
       </c>
       <c r="H803" t="n">
         <v>1273027</v>
@@ -23685,7 +23685,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G804" t="n">
-        <v>1.69453597068787</v>
+        <v>1.69453608989716</v>
       </c>
       <c r="H804" t="n">
         <v>415996</v>
@@ -23743,7 +23743,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G806" t="n">
-        <v>1.70269083976746</v>
+        <v>1.70269072055817</v>
       </c>
       <c r="H806" t="n">
         <v>871066</v>
@@ -23830,7 +23830,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G809" t="n">
-        <v>1.69942879676819</v>
+        <v>1.69942891597748</v>
       </c>
       <c r="H809" t="n">
         <v>580157</v>
@@ -23859,7 +23859,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G810" t="n">
-        <v>1.68964350223541</v>
+        <v>1.68964326381683</v>
       </c>
       <c r="H810" t="n">
         <v>653322</v>
@@ -23888,7 +23888,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G811" t="n">
-        <v>1.65865564346313</v>
+        <v>1.65865552425385</v>
       </c>
       <c r="H811" t="n">
         <v>550811</v>
@@ -23917,7 +23917,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G812" t="n">
-        <v>1.65865564346313</v>
+        <v>1.65865552425385</v>
       </c>
       <c r="H812" t="n">
         <v>382456</v>
@@ -23946,7 +23946,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G813" t="n">
-        <v>1.64560806751251</v>
+        <v>1.6456081867218</v>
       </c>
       <c r="H813" t="n">
         <v>341000</v>
@@ -23975,7 +23975,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G814" t="n">
-        <v>1.67007207870483</v>
+        <v>1.67007219791412</v>
       </c>
       <c r="H814" t="n">
         <v>399189</v>
@@ -24062,7 +24062,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G817" t="n">
-        <v>1.64071559906006</v>
+        <v>1.64071547985077</v>
       </c>
       <c r="H817" t="n">
         <v>8186934</v>
@@ -24120,7 +24120,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G819" t="n">
-        <v>1.60238862037659</v>
+        <v>1.6023885011673</v>
       </c>
       <c r="H819" t="n">
         <v>996560</v>
@@ -24149,7 +24149,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G820" t="n">
-        <v>1.6105432510376</v>
+        <v>1.61054337024689</v>
       </c>
       <c r="H820" t="n">
         <v>620149</v>
@@ -24178,7 +24178,7 @@
         <v>1.97099995613098</v>
       </c>
       <c r="G821" t="n">
-        <v>1.60728132724762</v>
+        <v>1.60728144645691</v>
       </c>
       <c r="H821" t="n">
         <v>607512</v>
@@ -24207,7 +24207,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G822" t="n">
-        <v>1.60157310962677</v>
+        <v>1.60157322883606</v>
       </c>
       <c r="H822" t="n">
         <v>833731</v>
@@ -24236,7 +24236,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G823" t="n">
-        <v>1.6733341217041</v>
+        <v>1.67333388328552</v>
       </c>
       <c r="H823" t="n">
         <v>1131670</v>
@@ -24265,7 +24265,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G824" t="n">
-        <v>1.6619176864624</v>
+        <v>1.66191756725311</v>
       </c>
       <c r="H824" t="n">
         <v>1727495</v>
@@ -24294,7 +24294,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G825" t="n">
-        <v>1.67496490478516</v>
+        <v>1.67496478557587</v>
       </c>
       <c r="H825" t="n">
         <v>666086</v>
@@ -24323,7 +24323,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G826" t="n">
-        <v>1.69127428531647</v>
+        <v>1.69127404689789</v>
       </c>
       <c r="H826" t="n">
         <v>1668598</v>
@@ -24381,7 +24381,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>1.68475043773651</v>
+        <v>1.6847505569458</v>
       </c>
       <c r="H828" t="n">
         <v>596412</v>
@@ -24468,7 +24468,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G831" t="n">
-        <v>1.88372385501862</v>
+        <v>1.88372397422791</v>
       </c>
       <c r="H831" t="n">
         <v>8604870</v>
@@ -24497,7 +24497,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G832" t="n">
-        <v>1.89187848567963</v>
+        <v>1.89187836647034</v>
       </c>
       <c r="H832" t="n">
         <v>3573577</v>
@@ -24613,7 +24613,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G836" t="n">
-        <v>1.77445161342621</v>
+        <v>1.77445185184479</v>
       </c>
       <c r="H836" t="n">
         <v>445873</v>
@@ -24642,7 +24642,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>1.78586828708649</v>
+        <v>1.7858681678772</v>
       </c>
       <c r="H837" t="n">
         <v>450642</v>
@@ -24671,7 +24671,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G838" t="n">
-        <v>1.78586828708649</v>
+        <v>1.7858681678772</v>
       </c>
       <c r="H838" t="n">
         <v>377864</v>
@@ -24729,7 +24729,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G840" t="n">
-        <v>1.72063100337982</v>
+        <v>1.72063076496124</v>
       </c>
       <c r="H840" t="n">
         <v>770563</v>
@@ -24816,7 +24816,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G843" t="n">
-        <v>1.63908445835114</v>
+        <v>1.63908433914185</v>
       </c>
       <c r="H843" t="n">
         <v>1322486</v>
@@ -24845,7 +24845,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G844" t="n">
-        <v>1.55182957649231</v>
+        <v>1.55182981491089</v>
       </c>
       <c r="H844" t="n">
         <v>4032631</v>
@@ -24874,7 +24874,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>1.59831130504608</v>
+        <v>1.59831118583679</v>
       </c>
       <c r="H845" t="n">
         <v>2241138</v>
@@ -24932,7 +24932,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G847" t="n">
-        <v>1.54775238037109</v>
+        <v>1.5477522611618</v>
       </c>
       <c r="H847" t="n">
         <v>1669046</v>
@@ -24961,7 +24961,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G848" t="n">
-        <v>1.52328836917877</v>
+        <v>1.52328860759735</v>
       </c>
       <c r="H848" t="n">
         <v>1102200</v>
@@ -24990,7 +24990,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G849" t="n">
-        <v>1.49148547649384</v>
+        <v>1.49148523807526</v>
       </c>
       <c r="H849" t="n">
         <v>955483</v>
@@ -25048,7 +25048,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G851" t="n">
-        <v>1.42543256282806</v>
+        <v>1.42543268203735</v>
       </c>
       <c r="H851" t="n">
         <v>880260</v>
@@ -25077,7 +25077,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G852" t="n">
-        <v>1.40830779075623</v>
+        <v>1.4083080291748</v>
       </c>
       <c r="H852" t="n">
         <v>1055190</v>
@@ -25106,7 +25106,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G853" t="n">
-        <v>1.39852237701416</v>
+        <v>1.39852225780487</v>
       </c>
       <c r="H853" t="n">
         <v>977323</v>
@@ -25164,7 +25164,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G855" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H855" t="n">
         <v>367882</v>
@@ -25193,7 +25193,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G856" t="n">
-        <v>1.36345732212067</v>
+        <v>1.36345744132996</v>
       </c>
       <c r="H856" t="n">
         <v>726614</v>
@@ -25222,7 +25222,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G857" t="n">
-        <v>1.4034149646759</v>
+        <v>1.40341520309448</v>
       </c>
       <c r="H857" t="n">
         <v>480477</v>
@@ -25251,7 +25251,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G858" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H858" t="n">
         <v>480695</v>
@@ -25280,7 +25280,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G859" t="n">
-        <v>1.38139748573303</v>
+        <v>1.38139760494232</v>
       </c>
       <c r="H859" t="n">
         <v>457572</v>
@@ -25309,7 +25309,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G860" t="n">
-        <v>1.40830779075623</v>
+        <v>1.4083080291748</v>
       </c>
       <c r="H860" t="n">
         <v>331863</v>
@@ -25338,7 +25338,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G861" t="n">
-        <v>1.39281404018402</v>
+        <v>1.39281392097473</v>
       </c>
       <c r="H861" t="n">
         <v>257728</v>
@@ -25367,7 +25367,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G862" t="n">
-        <v>1.35204088687897</v>
+        <v>1.35204076766968</v>
       </c>
       <c r="H862" t="n">
         <v>465276</v>
@@ -25396,7 +25396,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G863" t="n">
-        <v>1.38221299648285</v>
+        <v>1.38221311569214</v>
       </c>
       <c r="H863" t="n">
         <v>444989</v>
@@ -25425,7 +25425,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G864" t="n">
-        <v>1.41483163833618</v>
+        <v>1.41483151912689</v>
       </c>
       <c r="H864" t="n">
         <v>442927</v>
@@ -25454,7 +25454,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G865" t="n">
-        <v>1.39770674705505</v>
+        <v>1.39770698547363</v>
       </c>
       <c r="H865" t="n">
         <v>690821</v>
@@ -25483,7 +25483,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G866" t="n">
-        <v>1.37487387657166</v>
+        <v>1.37487363815308</v>
       </c>
       <c r="H866" t="n">
         <v>389202</v>
@@ -25541,7 +25541,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G868" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H868" t="n">
         <v>929548</v>
@@ -25570,7 +25570,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G869" t="n">
-        <v>1.39770674705505</v>
+        <v>1.39770698547363</v>
       </c>
       <c r="H869" t="n">
         <v>452853</v>
@@ -25599,7 +25599,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G870" t="n">
-        <v>1.44989657402039</v>
+        <v>1.44989669322968</v>
       </c>
       <c r="H870" t="n">
         <v>1022788</v>
@@ -25628,7 +25628,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G871" t="n">
-        <v>1.47599148750305</v>
+        <v>1.47599136829376</v>
       </c>
       <c r="H871" t="n">
         <v>608455</v>
@@ -25657,7 +25657,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G872" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H872" t="n">
         <v>430010</v>
@@ -25686,7 +25686,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G873" t="n">
-        <v>1.47925317287445</v>
+        <v>1.47925341129303</v>
       </c>
       <c r="H873" t="n">
         <v>295354</v>
@@ -25744,7 +25744,7 @@
         <v>1.875</v>
       </c>
       <c r="G875" t="n">
-        <v>1.52899670600891</v>
+        <v>1.5289968252182</v>
       </c>
       <c r="H875" t="n">
         <v>341943</v>
@@ -25802,7 +25802,7 @@
         <v>1.875</v>
       </c>
       <c r="G877" t="n">
-        <v>1.52899670600891</v>
+        <v>1.5289968252182</v>
       </c>
       <c r="H877" t="n">
         <v>428422</v>
@@ -25976,7 +25976,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G883" t="n">
-        <v>1.45152771472931</v>
+        <v>1.45152747631073</v>
       </c>
       <c r="H883" t="n">
         <v>362785</v>
@@ -26005,7 +26005,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G884" t="n">
-        <v>1.42869460582733</v>
+        <v>1.42869448661804</v>
       </c>
       <c r="H884" t="n">
         <v>364330</v>
@@ -26034,7 +26034,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G885" t="n">
-        <v>1.44989657402039</v>
+        <v>1.44989669322968</v>
       </c>
       <c r="H885" t="n">
         <v>2306619</v>
@@ -26150,7 +26150,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G889" t="n">
-        <v>1.44989657402039</v>
+        <v>1.44989669322968</v>
       </c>
       <c r="H889" t="n">
         <v>308646</v>
@@ -26295,7 +26295,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G894" t="n">
-        <v>1.57058537006378</v>
+        <v>1.57058548927307</v>
       </c>
       <c r="H894" t="n">
         <v>1453003</v>
@@ -26411,7 +26411,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G898" t="n">
-        <v>1.46049761772156</v>
+        <v>1.46049773693085</v>
       </c>
       <c r="H898" t="n">
         <v>1349408</v>
@@ -26556,7 +26556,7 @@
         <v>1.51300001144409</v>
       </c>
       <c r="G903" t="n">
-        <v>1.23379838466644</v>
+        <v>1.23379850387573</v>
       </c>
       <c r="H903" t="n">
         <v>1637956</v>
@@ -26585,7 +26585,7 @@
         <v>1.51900005340576</v>
       </c>
       <c r="G904" t="n">
-        <v>1.23869121074677</v>
+        <v>1.23869132995605</v>
       </c>
       <c r="H904" t="n">
         <v>714326</v>
@@ -26614,7 +26614,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G905" t="n">
-        <v>1.27049434185028</v>
+        <v>1.27049446105957</v>
       </c>
       <c r="H905" t="n">
         <v>1458633</v>
@@ -26643,7 +26643,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G906" t="n">
-        <v>1.33083868026733</v>
+        <v>1.33083879947662</v>
       </c>
       <c r="H906" t="n">
         <v>1628033</v>
@@ -26672,7 +26672,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G907" t="n">
-        <v>1.37732005119324</v>
+        <v>1.37732040882111</v>
       </c>
       <c r="H907" t="n">
         <v>2492653</v>
@@ -26788,7 +26788,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G911" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H911" t="n">
         <v>3720832</v>
@@ -26817,7 +26817,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G912" t="n">
-        <v>1.50371730327606</v>
+        <v>1.50371718406677</v>
       </c>
       <c r="H912" t="n">
         <v>2212773</v>
@@ -26875,7 +26875,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G914" t="n">
-        <v>1.54122853279114</v>
+        <v>1.54122877120972</v>
       </c>
       <c r="H914" t="n">
         <v>1837118</v>
@@ -26904,7 +26904,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G915" t="n">
-        <v>1.51024091243744</v>
+        <v>1.51024103164673</v>
       </c>
       <c r="H915" t="n">
         <v>2409241</v>
@@ -26933,7 +26933,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G916" t="n">
-        <v>1.54122853279114</v>
+        <v>1.54122877120972</v>
       </c>
       <c r="H916" t="n">
         <v>871736</v>
@@ -26962,7 +26962,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G917" t="n">
-        <v>1.55753791332245</v>
+        <v>1.55753815174103</v>
       </c>
       <c r="H917" t="n">
         <v>1214649</v>
@@ -27020,7 +27020,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G919" t="n">
-        <v>1.41727793216705</v>
+        <v>1.41727817058563</v>
       </c>
       <c r="H919" t="n">
         <v>3017439</v>
@@ -27049,7 +27049,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G920" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H920" t="n">
         <v>948111</v>
@@ -27078,7 +27078,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G921" t="n">
-        <v>1.4034149646759</v>
+        <v>1.40341520309448</v>
       </c>
       <c r="H921" t="n">
         <v>457312</v>
@@ -27107,7 +27107,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G922" t="n">
-        <v>1.3993376493454</v>
+        <v>1.39933788776398</v>
       </c>
       <c r="H922" t="n">
         <v>482861</v>
@@ -27165,7 +27165,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G924" t="n">
-        <v>1.44092643260956</v>
+        <v>1.44092655181885</v>
       </c>
       <c r="H924" t="n">
         <v>445435</v>
@@ -27252,7 +27252,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G927" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H927" t="n">
         <v>310073</v>
@@ -27281,7 +27281,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G928" t="n">
-        <v>1.3993376493454</v>
+        <v>1.39933788776398</v>
       </c>
       <c r="H928" t="n">
         <v>1082932</v>
@@ -27368,7 +27368,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G931" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H931" t="n">
         <v>513932</v>
@@ -27455,7 +27455,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H934" t="n">
         <v>267950</v>
@@ -27484,7 +27484,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G935" t="n">
-        <v>1.45152771472931</v>
+        <v>1.45152747631073</v>
       </c>
       <c r="H935" t="n">
         <v>676456</v>
@@ -27513,7 +27513,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.45152771472931</v>
+        <v>1.45152747631073</v>
       </c>
       <c r="H936" t="n">
         <v>484220</v>
@@ -27542,7 +27542,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G937" t="n">
-        <v>1.46131300926208</v>
+        <v>1.46131324768066</v>
       </c>
       <c r="H937" t="n">
         <v>276015</v>
@@ -27600,7 +27600,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G939" t="n">
-        <v>1.47680699825287</v>
+        <v>1.47680687904358</v>
       </c>
       <c r="H939" t="n">
         <v>314613</v>
@@ -27629,7 +27629,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G940" t="n">
-        <v>1.47680699825287</v>
+        <v>1.47680687904358</v>
       </c>
       <c r="H940" t="n">
         <v>612587</v>
@@ -27745,7 +27745,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G944" t="n">
-        <v>1.6765958070755</v>
+        <v>1.67659592628479</v>
       </c>
       <c r="H944" t="n">
         <v>894351</v>
@@ -27774,7 +27774,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G945" t="n">
-        <v>1.73041665554047</v>
+        <v>1.73041653633118</v>
       </c>
       <c r="H945" t="n">
         <v>2501849</v>
@@ -27861,7 +27861,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G948" t="n">
-        <v>1.65050101280212</v>
+        <v>1.65050089359283</v>
       </c>
       <c r="H948" t="n">
         <v>447219</v>
@@ -27890,7 +27890,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G949" t="n">
-        <v>1.68148875236511</v>
+        <v>1.6814888715744</v>
       </c>
       <c r="H949" t="n">
         <v>561915</v>
@@ -27948,7 +27948,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G951" t="n">
-        <v>1.67496490478516</v>
+        <v>1.67496478557587</v>
       </c>
       <c r="H951" t="n">
         <v>449178</v>
@@ -27977,7 +27977,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G952" t="n">
-        <v>1.64071559906006</v>
+        <v>1.64071547985077</v>
       </c>
       <c r="H952" t="n">
         <v>314585</v>
@@ -28006,7 +28006,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G953" t="n">
-        <v>1.63256072998047</v>
+        <v>1.63256084918976</v>
       </c>
       <c r="H953" t="n">
         <v>297419</v>
@@ -28151,7 +28151,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G958" t="n">
-        <v>1.57058537006378</v>
+        <v>1.57058548927307</v>
       </c>
       <c r="H958" t="n">
         <v>358093</v>
@@ -28238,7 +28238,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G961" t="n">
-        <v>1.54285955429077</v>
+        <v>1.54285979270935</v>
       </c>
       <c r="H961" t="n">
         <v>444176</v>
@@ -28267,7 +28267,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G962" t="n">
-        <v>1.55753791332245</v>
+        <v>1.55753815174103</v>
       </c>
       <c r="H962" t="n">
         <v>432157</v>
@@ -28296,7 +28296,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G963" t="n">
-        <v>1.5281810760498</v>
+        <v>1.52818119525909</v>
       </c>
       <c r="H963" t="n">
         <v>376603</v>
@@ -28325,7 +28325,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G964" t="n">
-        <v>1.55019867420197</v>
+        <v>1.55019891262054</v>
       </c>
       <c r="H964" t="n">
         <v>472301</v>
@@ -28412,7 +28412,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G967" t="n">
-        <v>1.53878235816956</v>
+        <v>1.53878223896027</v>
       </c>
       <c r="H967" t="n">
         <v>338780</v>
@@ -28470,7 +28470,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G969" t="n">
-        <v>1.61135864257812</v>
+        <v>1.61135852336884</v>
       </c>
       <c r="H969" t="n">
         <v>2221457</v>
@@ -28499,7 +28499,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G970" t="n">
-        <v>1.533074259758</v>
+        <v>1.53307402133942</v>
       </c>
       <c r="H970" t="n">
         <v>1687835</v>
@@ -28528,7 +28528,7 @@
         <v>1.875</v>
       </c>
       <c r="G971" t="n">
-        <v>1.52899670600891</v>
+        <v>1.5289968252182</v>
       </c>
       <c r="H971" t="n">
         <v>1073312</v>
@@ -28557,7 +28557,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G972" t="n">
-        <v>1.51921105384827</v>
+        <v>1.51921129226685</v>
       </c>
       <c r="H972" t="n">
         <v>814738</v>
@@ -28586,7 +28586,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G973" t="n">
-        <v>1.49311649799347</v>
+        <v>1.49311625957489</v>
       </c>
       <c r="H973" t="n">
         <v>788984</v>
@@ -28615,7 +28615,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G974" t="n">
-        <v>1.52002668380737</v>
+        <v>1.52002656459808</v>
       </c>
       <c r="H974" t="n">
         <v>392240</v>
@@ -28644,7 +28644,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G975" t="n">
-        <v>1.48740804195404</v>
+        <v>1.48740792274475</v>
       </c>
       <c r="H975" t="n">
         <v>965861</v>
@@ -28673,7 +28673,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G976" t="n">
-        <v>1.4890388250351</v>
+        <v>1.48903894424438</v>
       </c>
       <c r="H976" t="n">
         <v>660748</v>
@@ -28731,7 +28731,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G978" t="n">
-        <v>1.46212875843048</v>
+        <v>1.4621285200119</v>
       </c>
       <c r="H978" t="n">
         <v>2195345</v>
@@ -28818,7 +28818,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G981" t="n">
-        <v>1.42053985595703</v>
+        <v>1.42053997516632</v>
       </c>
       <c r="H981" t="n">
         <v>7154588</v>
@@ -28905,7 +28905,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G984" t="n">
-        <v>1.50942552089691</v>
+        <v>1.50942540168762</v>
       </c>
       <c r="H984" t="n">
         <v>15216437</v>
@@ -28934,7 +28934,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G985" t="n">
-        <v>1.49556267261505</v>
+        <v>1.49556255340576</v>
       </c>
       <c r="H985" t="n">
         <v>8238334</v>
@@ -28992,7 +28992,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G987" t="n">
-        <v>1.46783685684204</v>
+        <v>1.46783673763275</v>
       </c>
       <c r="H987" t="n">
         <v>2409711</v>
@@ -29021,7 +29021,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G988" t="n">
-        <v>1.44092643260956</v>
+        <v>1.44092655181885</v>
       </c>
       <c r="H988" t="n">
         <v>1635432</v>
@@ -29050,7 +29050,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G989" t="n">
-        <v>1.41320085525513</v>
+        <v>1.41320073604584</v>
       </c>
       <c r="H989" t="n">
         <v>2882134</v>
@@ -29108,7 +29108,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.38221299648285</v>
+        <v>1.38221311569214</v>
       </c>
       <c r="H991" t="n">
         <v>1472350</v>
@@ -29166,7 +29166,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G993" t="n">
-        <v>1.43114101886749</v>
+        <v>1.4311408996582</v>
       </c>
       <c r="H993" t="n">
         <v>4664408</v>
@@ -29224,7 +29224,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G995" t="n">
-        <v>1.46212875843048</v>
+        <v>1.4621285200119</v>
       </c>
       <c r="H995" t="n">
         <v>4135413</v>
@@ -29282,7 +29282,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G997" t="n">
-        <v>1.44337272644043</v>
+        <v>1.44337296485901</v>
       </c>
       <c r="H997" t="n">
         <v>1986347</v>
@@ -29311,7 +29311,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>1.39444506168365</v>
+        <v>1.39444518089294</v>
       </c>
       <c r="H998" t="n">
         <v>2423018</v>
@@ -29340,7 +29340,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G999" t="n">
-        <v>1.38465929031372</v>
+        <v>1.38465940952301</v>
       </c>
       <c r="H999" t="n">
         <v>1961726</v>
@@ -29369,7 +29369,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.41483163833618</v>
+        <v>1.41483151912689</v>
       </c>
       <c r="H1000" t="n">
         <v>2449613</v>
@@ -29427,7 +29427,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.41727793216705</v>
+        <v>1.41727817058563</v>
       </c>
       <c r="H1002" t="n">
         <v>1850120</v>
@@ -29456,7 +29456,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.39199864864349</v>
+        <v>1.3919985294342</v>
       </c>
       <c r="H1003" t="n">
         <v>1669083</v>
@@ -29485,7 +29485,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.39199864864349</v>
+        <v>1.3919985294342</v>
       </c>
       <c r="H1004" t="n">
         <v>964142</v>
@@ -29514,7 +29514,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.37487387657166</v>
+        <v>1.37487363815308</v>
       </c>
       <c r="H1005" t="n">
         <v>1982853</v>
@@ -29572,7 +29572,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.34633243083954</v>
+        <v>1.34633255004883</v>
       </c>
       <c r="H1007" t="n">
         <v>2611930</v>
@@ -29601,7 +29601,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.37487387657166</v>
+        <v>1.37487363815308</v>
       </c>
       <c r="H1008" t="n">
         <v>2577287</v>
@@ -29659,7 +29659,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.34470176696777</v>
+        <v>1.34470164775848</v>
       </c>
       <c r="H1010" t="n">
         <v>1693548</v>
@@ -29833,7 +29833,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.34796369075775</v>
+        <v>1.34796345233917</v>
       </c>
       <c r="H1016" t="n">
         <v>1488754</v>
@@ -29862,7 +29862,7 @@
         <v>1.61699998378754</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.31860673427582</v>
+        <v>1.31860685348511</v>
       </c>
       <c r="H1017" t="n">
         <v>3637322</v>
@@ -29920,7 +29920,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.30474400520325</v>
+        <v>1.30474388599396</v>
       </c>
       <c r="H1019" t="n">
         <v>1457803</v>
@@ -29978,7 +29978,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.317791223526</v>
+        <v>1.31779134273529</v>
       </c>
       <c r="H1021" t="n">
         <v>1664512</v>
@@ -30065,7 +30065,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.3332850933075</v>
+        <v>1.33328521251678</v>
       </c>
       <c r="H1024" t="n">
         <v>1949168</v>
@@ -30152,7 +30152,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.33083868026733</v>
+        <v>1.33083879947662</v>
       </c>
       <c r="H1027" t="n">
         <v>2738968</v>
@@ -30181,7 +30181,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.30474400520325</v>
+        <v>1.30474388599396</v>
       </c>
       <c r="H1028" t="n">
         <v>2569962</v>
@@ -30239,7 +30239,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.2639707326889</v>
+        <v>1.26397049427032</v>
       </c>
       <c r="H1030" t="n">
         <v>1941692</v>
@@ -30268,7 +30268,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.24521493911743</v>
+        <v>1.24521481990814</v>
       </c>
       <c r="H1031" t="n">
         <v>4013072</v>
@@ -30297,7 +30297,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.27212512493134</v>
+        <v>1.27212524414062</v>
       </c>
       <c r="H1032" t="n">
         <v>2267819</v>
@@ -30326,7 +30326,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.23706030845642</v>
+        <v>1.23706018924713</v>
       </c>
       <c r="H1033" t="n">
         <v>2193205</v>
@@ -30355,7 +30355,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.2639707326889</v>
+        <v>1.26397049427032</v>
       </c>
       <c r="H1034" t="n">
         <v>1698992</v>
@@ -30413,7 +30413,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.2207510471344</v>
+        <v>1.22075092792511</v>
       </c>
       <c r="H1036" t="n">
         <v>2935812</v>
@@ -30442,7 +30442,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.19302523136139</v>
+        <v>1.1930251121521</v>
       </c>
       <c r="H1037" t="n">
         <v>2136222</v>
@@ -30500,7 +30500,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.19302523136139</v>
+        <v>1.1930251121521</v>
       </c>
       <c r="H1039" t="n">
         <v>1987577</v>
@@ -30558,7 +30558,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.21504271030426</v>
+        <v>1.21504259109497</v>
       </c>
       <c r="H1041" t="n">
         <v>1855988</v>
@@ -30616,7 +30616,7 @@
         <v>1.442999958992</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.17671585083008</v>
+        <v>1.17671573162079</v>
       </c>
       <c r="H1043" t="n">
         <v>1518662</v>
@@ -30761,7 +30761,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.21830451488495</v>
+        <v>1.21830463409424</v>
       </c>
       <c r="H1048" t="n">
         <v>1782186</v>
@@ -30848,7 +30848,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.23298299312592</v>
+        <v>1.23298287391663</v>
       </c>
       <c r="H1051" t="n">
         <v>4186263</v>
@@ -30906,7 +30906,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.08456826210022</v>
+        <v>1.08456838130951</v>
       </c>
       <c r="H1053" t="n">
         <v>6068429</v>
@@ -30935,7 +30935,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.12860345840454</v>
+        <v>1.12860357761383</v>
       </c>
       <c r="H1054" t="n">
         <v>4617523</v>
@@ -30993,7 +30993,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.10740149021149</v>
+        <v>1.1074013710022</v>
       </c>
       <c r="H1056" t="n">
         <v>2426604</v>
@@ -31080,7 +31080,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.03400945663452</v>
+        <v>1.0340096950531</v>
       </c>
       <c r="H1059" t="n">
         <v>2652066</v>
@@ -31109,7 +31109,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.03564035892487</v>
+        <v>1.03564047813416</v>
       </c>
       <c r="H1060" t="n">
         <v>3564489</v>
@@ -31138,7 +31138,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.988343358039856</v>
+        <v>0.98834353685379</v>
       </c>
       <c r="H1061" t="n">
         <v>4115706</v>
@@ -31167,7 +31167,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.920659780502319</v>
+        <v>0.920659899711609</v>
       </c>
       <c r="H1062" t="n">
         <v>4436272</v>
@@ -31196,7 +31196,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.804048359394073</v>
+        <v>0.804048418998718</v>
       </c>
       <c r="H1063" t="n">
         <v>4912177</v>
@@ -31225,7 +31225,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.760013341903687</v>
+        <v>0.760013282299042</v>
       </c>
       <c r="H1064" t="n">
         <v>6550694</v>
@@ -31254,7 +31254,7 @@
         <v>0.922500014305115</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.752266407012939</v>
+        <v>0.752266466617584</v>
       </c>
       <c r="H1065" t="n">
         <v>5103415</v>
@@ -31283,7 +31283,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.564301729202271</v>
+        <v>0.564301788806915</v>
       </c>
       <c r="H1066" t="n">
         <v>9939899</v>
@@ -31312,7 +31312,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.588357925415039</v>
+        <v>0.588357865810394</v>
       </c>
       <c r="H1067" t="n">
         <v>5899770</v>
@@ -31515,7 +31515,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.02259290218353</v>
+        <v>1.02259302139282</v>
       </c>
       <c r="H1074" t="n">
         <v>3835933</v>
@@ -31573,7 +31573,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.918213427066803</v>
+        <v>0.918213486671448</v>
       </c>
       <c r="H1076" t="n">
         <v>2250973</v>
@@ -31602,7 +31602,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.870916545391083</v>
+        <v>0.870916604995728</v>
       </c>
       <c r="H1077" t="n">
         <v>1971172</v>
@@ -31631,7 +31631,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.913320660591125</v>
+        <v>0.913320779800415</v>
       </c>
       <c r="H1078" t="n">
         <v>1366165</v>
@@ -31660,7 +31660,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.95083224773407</v>
+        <v>0.95083212852478</v>
       </c>
       <c r="H1079" t="n">
         <v>2082037</v>
@@ -31689,7 +31689,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.939415633678436</v>
+        <v>0.939415514469147</v>
       </c>
       <c r="H1080" t="n">
         <v>655666</v>
@@ -31718,7 +31718,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.949201107025146</v>
+        <v>0.949201166629791</v>
       </c>
       <c r="H1081" t="n">
         <v>929547</v>
@@ -31747,7 +31747,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.951647639274597</v>
+        <v>0.951647758483887</v>
       </c>
       <c r="H1082" t="n">
         <v>443405</v>
@@ -31776,7 +31776,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.960617661476135</v>
+        <v>0.96061772108078</v>
       </c>
       <c r="H1083" t="n">
         <v>863388</v>
@@ -31834,7 +31834,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.956540405750275</v>
+        <v>0.956540286540985</v>
       </c>
       <c r="H1085" t="n">
         <v>1486613</v>
@@ -31892,7 +31892,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.05276525020599</v>
+        <v>1.0527651309967</v>
       </c>
       <c r="H1087" t="n">
         <v>4106371</v>
@@ -31921,7 +31921,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.998129189014435</v>
+        <v>0.998128950595856</v>
       </c>
       <c r="H1088" t="n">
         <v>2104508</v>
@@ -31979,7 +31979,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.06744360923767</v>
+        <v>1.06744349002838</v>
       </c>
       <c r="H1090" t="n">
         <v>2209568</v>
@@ -32037,7 +32037,7 @@
         <v>1.33899998664856</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.0919075012207</v>
+        <v>1.09190762042999</v>
       </c>
       <c r="H1092" t="n">
         <v>1156803</v>
@@ -32095,7 +32095,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.08864569664001</v>
+        <v>1.08864593505859</v>
       </c>
       <c r="H1094" t="n">
         <v>648171</v>
@@ -32124,7 +32124,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.08783030509949</v>
+        <v>1.08783006668091</v>
       </c>
       <c r="H1095" t="n">
         <v>841392</v>
@@ -32182,7 +32182,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.09924674034119</v>
+        <v>1.09924685955048</v>
       </c>
       <c r="H1097" t="n">
         <v>2452809</v>
@@ -32211,7 +32211,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.11310946941376</v>
+        <v>1.11310958862305</v>
       </c>
       <c r="H1098" t="n">
         <v>2249016</v>
@@ -32269,7 +32269,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.09272301197052</v>
+        <v>1.09272289276123</v>
       </c>
       <c r="H1100" t="n">
         <v>1093846</v>
@@ -32298,7 +32298,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.08783030509949</v>
+        <v>1.08783006668091</v>
       </c>
       <c r="H1101" t="n">
         <v>1883969</v>
@@ -32327,7 +32327,7 @@
         <v>1.34899997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.100062251091</v>
+        <v>1.10006201267242</v>
       </c>
       <c r="H1102" t="n">
         <v>427120</v>
@@ -32443,7 +32443,7 @@
         <v>1.29799997806549</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.05847346782684</v>
+        <v>1.05847334861755</v>
       </c>
       <c r="H1106" t="n">
         <v>634271</v>
@@ -32472,7 +32472,7 @@
         <v>1.307000041008</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.06581282615662</v>
+        <v>1.06581270694733</v>
       </c>
       <c r="H1107" t="n">
         <v>548797</v>
@@ -32501,7 +32501,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.04379522800446</v>
+        <v>1.04379498958588</v>
       </c>
       <c r="H1108" t="n">
         <v>692318</v>
@@ -32530,7 +32530,7 @@
         <v>1.26900005340576</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.03482508659363</v>
+        <v>1.03482496738434</v>
       </c>
       <c r="H1109" t="n">
         <v>390613</v>
@@ -32559,7 +32559,7 @@
         <v>1.26300001144409</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.0548700094223</v>
+        <v>1.05487012863159</v>
       </c>
       <c r="H1110" t="n">
         <v>531961</v>
@@ -32588,7 +32588,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.979701161384583</v>
+        <v>0.979701101779938</v>
       </c>
       <c r="H1111" t="n">
         <v>3876340</v>
@@ -32617,7 +32617,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.988888382911682</v>
+        <v>0.988888442516327</v>
       </c>
       <c r="H1112" t="n">
         <v>1956180</v>
@@ -32646,7 +32646,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.991393983364105</v>
+        <v>0.991394102573395</v>
       </c>
       <c r="H1113" t="n">
         <v>885134</v>
@@ -32704,7 +32704,7 @@
         <v>1.25</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.04401218891144</v>
+        <v>1.04401230812073</v>
       </c>
       <c r="H1115" t="n">
         <v>711035</v>
@@ -32733,7 +32733,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.05737566947937</v>
+        <v>1.05737555027008</v>
       </c>
       <c r="H1116" t="n">
         <v>1440577</v>
@@ -32820,7 +32820,7 @@
         <v>1.24300003051758</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.03816592693329</v>
+        <v>1.038165807724</v>
       </c>
       <c r="H1119" t="n">
         <v>1124431</v>
@@ -32878,7 +32878,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.08243203163147</v>
+        <v>1.08243191242218</v>
       </c>
       <c r="H1121" t="n">
         <v>1294125</v>
@@ -32907,7 +32907,7 @@
         <v>1.36099994182587</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.13672065734863</v>
+        <v>1.13672053813934</v>
       </c>
       <c r="H1122" t="n">
         <v>2770265</v>
@@ -32994,7 +32994,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.22859358787537</v>
+        <v>1.22859346866608</v>
       </c>
       <c r="H1125" t="n">
         <v>3885164</v>
@@ -33197,7 +33197,7 @@
         <v>1.44700002670288</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.20854878425598</v>
+        <v>1.20854866504669</v>
       </c>
       <c r="H1132" t="n">
         <v>2622105</v>
@@ -33226,7 +33226,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.24028658866882</v>
+        <v>1.24028646945953</v>
       </c>
       <c r="H1133" t="n">
         <v>2907813</v>
@@ -33342,7 +33342,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.17597532272339</v>
+        <v>1.17597544193268</v>
       </c>
       <c r="H1137" t="n">
         <v>1151867</v>
@@ -33371,7 +33371,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.17764580249786</v>
+        <v>1.17764568328857</v>
       </c>
       <c r="H1138" t="n">
         <v>954584</v>
@@ -33400,7 +33400,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.16595304012299</v>
+        <v>1.1659529209137</v>
       </c>
       <c r="H1139" t="n">
         <v>669422</v>
@@ -33458,7 +33458,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.16511762142181</v>
+        <v>1.1651177406311</v>
       </c>
       <c r="H1141" t="n">
         <v>1238514</v>
@@ -33516,7 +33516,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.17597532272339</v>
+        <v>1.17597544193268</v>
       </c>
       <c r="H1143" t="n">
         <v>748993</v>
@@ -33603,7 +33603,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.19435000419617</v>
+        <v>1.19434988498688</v>
       </c>
       <c r="H1146" t="n">
         <v>662446</v>
@@ -33661,7 +33661,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.19852590560913</v>
+        <v>1.19852602481842</v>
       </c>
       <c r="H1148" t="n">
         <v>8763913</v>
@@ -33690,7 +33690,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.1734699010849</v>
+        <v>1.17346978187561</v>
       </c>
       <c r="H1149" t="n">
         <v>1614825</v>
@@ -33719,7 +33719,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G1150" t="n">
-        <v>1.20938384532928</v>
+        <v>1.20938372612</v>
       </c>
       <c r="H1150" t="n">
         <v>1266052</v>
@@ -33748,7 +33748,7 @@
         <v>1.42900002002716</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.19351482391357</v>
+        <v>1.19351494312286</v>
       </c>
       <c r="H1151" t="n">
         <v>2176067</v>
@@ -33777,7 +33777,7 @@
         <v>1.45299994945526</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.21355986595154</v>
+        <v>1.21355974674225</v>
       </c>
       <c r="H1152" t="n">
         <v>3560690</v>
@@ -33806,7 +33806,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.19435000419617</v>
+        <v>1.19434988498688</v>
       </c>
       <c r="H1153" t="n">
         <v>2312871</v>
@@ -33922,7 +33922,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.20938384532928</v>
+        <v>1.20938372612</v>
       </c>
       <c r="H1157" t="n">
         <v>1738584</v>
@@ -33980,7 +33980,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.16177678108215</v>
+        <v>1.16177690029144</v>
       </c>
       <c r="H1159" t="n">
         <v>1134501</v>
@@ -34009,7 +34009,7 @@
         <v>1.32299995422363</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.10498261451721</v>
+        <v>1.10498237609863</v>
       </c>
       <c r="H1160" t="n">
         <v>2253150</v>
@@ -34038,7 +34038,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.10247707366943</v>
+        <v>1.10247695446014</v>
       </c>
       <c r="H1161" t="n">
         <v>1753450</v>
@@ -34067,7 +34067,7 @@
         <v>1.28100001811981</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.06990373134613</v>
+        <v>1.06990385055542</v>
       </c>
       <c r="H1162" t="n">
         <v>1647900</v>
@@ -34096,7 +34096,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.970513701438904</v>
+        <v>0.970513641834259</v>
       </c>
       <c r="H1163" t="n">
         <v>4861508</v>
@@ -34183,7 +34183,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.935434937477112</v>
+        <v>0.935435116291046</v>
       </c>
       <c r="H1166" t="n">
         <v>3217787</v>
@@ -34212,7 +34212,7 @@
         <v>1.09899997711182</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.917895615100861</v>
+        <v>0.917895495891571</v>
       </c>
       <c r="H1167" t="n">
         <v>2532403</v>
@@ -34241,7 +34241,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.886157631874084</v>
+        <v>0.88615757226944</v>
       </c>
       <c r="H1168" t="n">
         <v>1993581</v>
@@ -34270,7 +34270,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.896180033683777</v>
+        <v>0.896180152893066</v>
       </c>
       <c r="H1169" t="n">
         <v>1798654</v>
@@ -34328,7 +34328,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.935434937477112</v>
+        <v>0.935435116291046</v>
       </c>
       <c r="H1171" t="n">
         <v>2331133</v>
@@ -34386,7 +34386,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.950468778610229</v>
+        <v>0.950468897819519</v>
       </c>
       <c r="H1173" t="n">
         <v>1092249</v>
@@ -34415,7 +34415,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.953809499740601</v>
+        <v>0.953809559345245</v>
       </c>
       <c r="H1174" t="n">
         <v>982082</v>
@@ -34444,7 +34444,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.945457458496094</v>
+        <v>0.945457398891449</v>
       </c>
       <c r="H1175" t="n">
         <v>642129</v>
@@ -34560,7 +34560,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.915390014648438</v>
+        <v>0.915389955043793</v>
       </c>
       <c r="H1179" t="n">
         <v>613195</v>
@@ -34589,7 +34589,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.942951738834381</v>
+        <v>0.942951798439026</v>
       </c>
       <c r="H1180" t="n">
         <v>992299</v>
@@ -34676,7 +34676,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.917060375213623</v>
+        <v>0.917060494422913</v>
       </c>
       <c r="H1183" t="n">
         <v>768682</v>
@@ -34705,7 +34705,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.917060375213623</v>
+        <v>0.917060494422913</v>
       </c>
       <c r="H1184" t="n">
         <v>876059</v>
@@ -34734,7 +34734,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.908708274364471</v>
+        <v>0.908708333969116</v>
       </c>
       <c r="H1185" t="n">
         <v>1886603</v>
@@ -34763,7 +34763,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.900356113910675</v>
+        <v>0.90035605430603</v>
       </c>
       <c r="H1186" t="n">
         <v>905278</v>
@@ -34792,7 +34792,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.905367434024811</v>
+        <v>0.905367374420166</v>
       </c>
       <c r="H1187" t="n">
         <v>1392144</v>
@@ -34821,7 +34821,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.90369701385498</v>
+        <v>0.903697073459625</v>
       </c>
       <c r="H1188" t="n">
         <v>1543314</v>
@@ -34850,7 +34850,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.888663232326508</v>
+        <v>0.888663291931152</v>
       </c>
       <c r="H1189" t="n">
         <v>842442</v>
@@ -34966,7 +34966,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.901191353797913</v>
+        <v>0.901191413402557</v>
       </c>
       <c r="H1193" t="n">
         <v>993458</v>
@@ -34995,7 +34995,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.905367434024811</v>
+        <v>0.905367374420166</v>
       </c>
       <c r="H1194" t="n">
         <v>698588</v>
@@ -35024,7 +35024,7 @@
         <v>1.0809999704361</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.902861773967743</v>
+        <v>0.902861714363098</v>
       </c>
       <c r="H1195" t="n">
         <v>652835</v>
@@ -35082,7 +35082,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.9145547747612</v>
+        <v>0.914554715156555</v>
       </c>
       <c r="H1197" t="n">
         <v>1059605</v>
@@ -35111,7 +35111,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.937105357646942</v>
+        <v>0.937105298042297</v>
       </c>
       <c r="H1198" t="n">
         <v>1687673</v>
@@ -35140,7 +35140,7 @@
         <v>1.10800004005432</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.925412535667419</v>
+        <v>0.92541241645813</v>
       </c>
       <c r="H1199" t="n">
         <v>870459</v>
@@ -35169,7 +35169,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.912049055099487</v>
+        <v>0.912049114704132</v>
       </c>
       <c r="H1200" t="n">
         <v>1226727</v>
@@ -35227,7 +35227,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.892004072666168</v>
+        <v>0.892004132270813</v>
       </c>
       <c r="H1202" t="n">
         <v>631454</v>
@@ -35256,7 +35256,7 @@
         <v>1.08299994468689</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.904532253742218</v>
+        <v>0.904532194137573</v>
       </c>
       <c r="H1203" t="n">
         <v>1011010</v>
@@ -35285,7 +35285,7 @@
         <v>1.05099999904633</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.877805471420288</v>
+        <v>0.877805531024933</v>
       </c>
       <c r="H1204" t="n">
         <v>2019330</v>
@@ -35314,7 +35314,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.829363286495209</v>
+        <v>0.829363346099854</v>
       </c>
       <c r="H1205" t="n">
         <v>5785783</v>
@@ -35343,7 +35343,7 @@
         <v>0.993499994277954</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.82978093624115</v>
+        <v>0.829780876636505</v>
       </c>
       <c r="H1206" t="n">
         <v>1701993</v>
@@ -35430,7 +35430,7 @@
         <v>1.0110000371933</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.844397127628326</v>
+        <v>0.844397187232971</v>
       </c>
       <c r="H1209" t="n">
         <v>918635</v>
@@ -35488,7 +35488,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.89868575334549</v>
+        <v>0.898685693740845</v>
       </c>
       <c r="H1211" t="n">
         <v>2105739</v>
@@ -35546,7 +35546,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.917060375213623</v>
+        <v>0.917060494422913</v>
       </c>
       <c r="H1213" t="n">
         <v>1682730</v>
@@ -35575,7 +35575,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.88949853181839</v>
+        <v>0.889498472213745</v>
       </c>
       <c r="H1214" t="n">
         <v>2208181</v>
@@ -35662,7 +35662,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.915390014648438</v>
+        <v>0.915389955043793</v>
       </c>
       <c r="H1217" t="n">
         <v>2997238</v>
@@ -35691,7 +35691,7 @@
         <v>1.04799997806549</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.875299870967865</v>
+        <v>0.87529981136322</v>
       </c>
       <c r="H1218" t="n">
         <v>866000</v>
@@ -35720,7 +35720,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.868618190288544</v>
+        <v>0.868618249893188</v>
       </c>
       <c r="H1219" t="n">
         <v>1717438</v>
@@ -35807,7 +35807,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.843561887741089</v>
+        <v>0.843561947345734</v>
       </c>
       <c r="H1222" t="n">
         <v>990227</v>
@@ -35836,7 +35836,7 @@
         <v>0.997500002384186</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.833121776580811</v>
+        <v>0.833121836185455</v>
       </c>
       <c r="H1223" t="n">
         <v>909875</v>
@@ -35981,7 +35981,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.729973316192627</v>
+        <v>0.729973375797272</v>
       </c>
       <c r="H1228" t="n">
         <v>1596505</v>
@@ -36010,7 +36010,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.767975330352783</v>
+        <v>0.767975389957428</v>
       </c>
       <c r="H1229" t="n">
         <v>1412591</v>
@@ -36039,7 +36039,7 @@
         <v>0.962499976158142</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.803889453411102</v>
+        <v>0.803889393806458</v>
       </c>
       <c r="H1230" t="n">
         <v>1720467</v>
@@ -36068,7 +36068,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.794284522533417</v>
+        <v>0.794284462928772</v>
       </c>
       <c r="H1231" t="n">
         <v>1081621</v>
@@ -36126,7 +36126,7 @@
         <v>0.993499994277954</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.82978093624115</v>
+        <v>0.829780876636505</v>
       </c>
       <c r="H1233" t="n">
         <v>1561801</v>
@@ -36184,7 +36184,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.924577176570892</v>
+        <v>0.924577295780182</v>
       </c>
       <c r="H1235" t="n">
         <v>4003298</v>
@@ -36271,7 +36271,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.95715057849884</v>
+        <v>0.957150459289551</v>
       </c>
       <c r="H1238" t="n">
         <v>2938823</v>
@@ -36358,7 +36358,7 @@
         <v>1.25</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.04401218891144</v>
+        <v>1.04401230812073</v>
       </c>
       <c r="H1241" t="n">
         <v>2955163</v>
@@ -36387,7 +36387,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.04985857009888</v>
+        <v>1.04985880851746</v>
       </c>
       <c r="H1242" t="n">
         <v>2344652</v>
@@ -36416,7 +36416,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.02981376647949</v>
+        <v>1.0298136472702</v>
       </c>
       <c r="H1243" t="n">
         <v>2819086</v>
@@ -36445,7 +36445,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.07491505146027</v>
+        <v>1.07491493225098</v>
       </c>
       <c r="H1244" t="n">
         <v>2961990</v>
@@ -36474,7 +36474,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.07491505146027</v>
+        <v>1.07491493225098</v>
       </c>
       <c r="H1245" t="n">
         <v>2543126</v>
@@ -36590,7 +36590,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.06906867027283</v>
+        <v>1.06906855106354</v>
       </c>
       <c r="H1249" t="n">
         <v>3269294</v>
@@ -36619,7 +36619,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.06906867027283</v>
+        <v>1.06906855106354</v>
       </c>
       <c r="H1250" t="n">
         <v>1487972</v>
@@ -36648,7 +36648,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.07909107208252</v>
+        <v>1.0790913105011</v>
       </c>
       <c r="H1251" t="n">
         <v>1682016</v>
@@ -36706,7 +36706,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.06489253044128</v>
+        <v>1.06489241123199</v>
       </c>
       <c r="H1253" t="n">
         <v>1869943</v>
@@ -36764,7 +36764,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.03733062744141</v>
+        <v>1.03733050823212</v>
       </c>
       <c r="H1255" t="n">
         <v>940733</v>
@@ -36793,7 +36793,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.03148400783539</v>
+        <v>1.03148424625397</v>
       </c>
       <c r="H1256" t="n">
         <v>1184716</v>
@@ -36822,7 +36822,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.02229690551758</v>
+        <v>1.02229678630829</v>
       </c>
       <c r="H1257" t="n">
         <v>1511324</v>
@@ -36851,7 +36851,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.01227414608002</v>
+        <v>1.0122743844986</v>
       </c>
       <c r="H1258" t="n">
         <v>1499780</v>
@@ -36880,7 +36880,7 @@
         <v>1.20299994945526</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.0047572851181</v>
+        <v>1.00475752353668</v>
       </c>
       <c r="H1259" t="n">
         <v>892409</v>
@@ -36909,7 +36909,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.01478004455566</v>
+        <v>1.01477992534637</v>
       </c>
       <c r="H1260" t="n">
         <v>1115623</v>
@@ -36938,7 +36938,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.02981376647949</v>
+        <v>1.0298136472702</v>
       </c>
       <c r="H1261" t="n">
         <v>1624816</v>
@@ -36967,7 +36967,7 @@
         <v>1.21899998188019</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.01812064647675</v>
+        <v>1.01812052726746</v>
       </c>
       <c r="H1262" t="n">
         <v>752242</v>
@@ -37025,7 +37025,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.998075842857361</v>
+        <v>0.998075783252716</v>
       </c>
       <c r="H1264" t="n">
         <v>1064295</v>
@@ -37141,7 +37141,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.01478004455566</v>
+        <v>1.01477992534637</v>
       </c>
       <c r="H1268" t="n">
         <v>1173116</v>
@@ -37170,7 +37170,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.991393983364105</v>
+        <v>0.991394102573395</v>
       </c>
       <c r="H1269" t="n">
         <v>1600769</v>
@@ -37199,7 +37199,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.987218141555786</v>
+        <v>0.987218022346497</v>
       </c>
       <c r="H1270" t="n">
         <v>866193</v>
@@ -37228,7 +37228,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.965502500534058</v>
+        <v>0.965502619743347</v>
       </c>
       <c r="H1271" t="n">
         <v>1757719</v>
@@ -37344,7 +37344,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.05737566947937</v>
+        <v>1.05737555027008</v>
       </c>
       <c r="H1275" t="n">
         <v>1591028</v>
@@ -37373,7 +37373,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.03398978710175</v>
+        <v>1.03398990631104</v>
       </c>
       <c r="H1276" t="n">
         <v>1603132</v>
@@ -37402,7 +37402,7 @@
         <v>1.2610000371933</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.05319952964783</v>
+        <v>1.05319964885712</v>
       </c>
       <c r="H1277" t="n">
         <v>1062423</v>
@@ -37431,7 +37431,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.05069410800934</v>
+        <v>1.05069398880005</v>
       </c>
       <c r="H1278" t="n">
         <v>718663</v>
@@ -37489,7 +37489,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.03148400783539</v>
+        <v>1.03148424625397</v>
       </c>
       <c r="H1280" t="n">
         <v>1054107</v>
@@ -37547,7 +37547,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.06906867027283</v>
+        <v>1.06906855106354</v>
       </c>
       <c r="H1282" t="n">
         <v>1751527</v>
@@ -37576,7 +37576,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.07575011253357</v>
+        <v>1.07575023174286</v>
       </c>
       <c r="H1283" t="n">
         <v>1878041</v>
@@ -37663,7 +37663,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.03482472896576</v>
+        <v>1.03482484817505</v>
       </c>
       <c r="H1286" t="n">
         <v>1259004</v>
@@ -37692,7 +37692,7 @@
         <v>1.2610000371933</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.05319952964783</v>
+        <v>1.05319964885712</v>
       </c>
       <c r="H1287" t="n">
         <v>1291561</v>
@@ -37750,7 +37750,7 @@
         <v>1.24100005626678</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.03649532794952</v>
+        <v>1.03649544715881</v>
       </c>
       <c r="H1289" t="n">
         <v>1078393</v>
@@ -37779,7 +37779,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.02229690551758</v>
+        <v>1.02229678630829</v>
       </c>
       <c r="H1290" t="n">
         <v>860970</v>
@@ -37808,7 +37808,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.05069410800934</v>
+        <v>1.05069398880005</v>
       </c>
       <c r="H1291" t="n">
         <v>1203524</v>
@@ -37895,7 +37895,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.1141699552536</v>
+        <v>1.11416983604431</v>
       </c>
       <c r="H1294" t="n">
         <v>1778230</v>
@@ -37924,7 +37924,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.20270216464996</v>
+        <v>1.20270228385925</v>
       </c>
       <c r="H1295" t="n">
         <v>8584230</v>
@@ -37953,7 +37953,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.28371751308441</v>
+        <v>1.28371739387512</v>
       </c>
       <c r="H1296" t="n">
         <v>8648318</v>
@@ -38011,7 +38011,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.31378507614136</v>
+        <v>1.31378495693207</v>
       </c>
       <c r="H1298" t="n">
         <v>6077912</v>
@@ -38040,7 +38040,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.29290473461151</v>
+        <v>1.2929048538208</v>
       </c>
       <c r="H1299" t="n">
         <v>4101534</v>
@@ -38127,7 +38127,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.37391996383667</v>
+        <v>1.37392008304596</v>
       </c>
       <c r="H1302" t="n">
         <v>7579786</v>
@@ -38185,7 +38185,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.37391996383667</v>
+        <v>1.37392008304596</v>
       </c>
       <c r="H1304" t="n">
         <v>5369157</v>
@@ -38214,7 +38214,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.3705792427063</v>
+        <v>1.37057936191559</v>
       </c>
       <c r="H1305" t="n">
         <v>2174460</v>
@@ -38272,7 +38272,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.35638070106506</v>
+        <v>1.35638058185577</v>
       </c>
       <c r="H1307" t="n">
         <v>1681134</v>
@@ -38301,7 +38301,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.35638070106506</v>
+        <v>1.35638058185577</v>
       </c>
       <c r="H1308" t="n">
         <v>1410687</v>
@@ -38330,7 +38330,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.30793869495392</v>
+        <v>1.30793857574463</v>
       </c>
       <c r="H1309" t="n">
         <v>2216085</v>
@@ -38359,7 +38359,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.29875135421753</v>
+        <v>1.29875111579895</v>
       </c>
       <c r="H1310" t="n">
         <v>2003780</v>
@@ -38417,7 +38417,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.30376255512238</v>
+        <v>1.30376243591309</v>
       </c>
       <c r="H1312" t="n">
         <v>1457296</v>
@@ -38446,7 +38446,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.30125689506531</v>
+        <v>1.3012570142746</v>
       </c>
       <c r="H1313" t="n">
         <v>2530993</v>
@@ -38504,7 +38504,7 @@
         <v>1.56700003147125</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.30877363681793</v>
+        <v>1.30877375602722</v>
       </c>
       <c r="H1315" t="n">
         <v>1316719</v>
@@ -38533,7 +38533,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.3355005979538</v>
+        <v>1.33550047874451</v>
       </c>
       <c r="H1316" t="n">
         <v>1494787</v>
@@ -38562,7 +38562,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.35638070106506</v>
+        <v>1.35638058185577</v>
       </c>
       <c r="H1317" t="n">
         <v>3043688</v>
@@ -38591,7 +38591,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.37391996383667</v>
+        <v>1.37392008304596</v>
       </c>
       <c r="H1318" t="n">
         <v>2115244</v>
@@ -38620,7 +38620,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.36807358264923</v>
+        <v>1.36807370185852</v>
       </c>
       <c r="H1319" t="n">
         <v>2810879</v>
@@ -38678,7 +38678,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.42152726650238</v>
+        <v>1.42152714729309</v>
       </c>
       <c r="H1321" t="n">
         <v>9920232</v>
@@ -38881,7 +38881,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.47163963317871</v>
+        <v>1.47163951396942</v>
       </c>
       <c r="H1328" t="n">
         <v>2715511</v>
@@ -38997,7 +38997,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.50170707702637</v>
+        <v>1.50170719623566</v>
       </c>
       <c r="H1332" t="n">
         <v>2345616</v>
@@ -39026,7 +39026,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.49001443386078</v>
+        <v>1.49001431465149</v>
       </c>
       <c r="H1333" t="n">
         <v>1783246</v>
@@ -39084,7 +39084,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.56518304347992</v>
+        <v>1.56518316268921</v>
       </c>
       <c r="H1335" t="n">
         <v>6436688</v>
@@ -39142,7 +39142,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.5401269197464</v>
+        <v>1.54012668132782</v>
       </c>
       <c r="H1337" t="n">
         <v>3492731</v>
@@ -39171,7 +39171,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.51005935668945</v>
+        <v>1.51005923748016</v>
       </c>
       <c r="H1338" t="n">
         <v>3127651</v>
@@ -39200,7 +39200,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.52258729934692</v>
+        <v>1.5225875377655</v>
       </c>
       <c r="H1339" t="n">
         <v>2478018</v>
@@ -39229,7 +39229,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.5242577791214</v>
+        <v>1.52425789833069</v>
       </c>
       <c r="H1340" t="n">
         <v>1890433</v>
@@ -39316,7 +39316,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.53261005878448</v>
+        <v>1.53261017799377</v>
       </c>
       <c r="H1343" t="n">
         <v>1607652</v>
@@ -39374,7 +39374,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.49084937572479</v>
+        <v>1.49084949493408</v>
       </c>
       <c r="H1345" t="n">
         <v>1848196</v>
@@ -39403,7 +39403,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.49084937572479</v>
+        <v>1.49084949493408</v>
       </c>
       <c r="H1346" t="n">
         <v>1588629</v>
@@ -39519,7 +39519,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.52843403816223</v>
+        <v>1.52843391895294</v>
       </c>
       <c r="H1350" t="n">
         <v>1164177</v>
@@ -39577,7 +39577,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.51507043838501</v>
+        <v>1.51507067680359</v>
       </c>
       <c r="H1352" t="n">
         <v>1198582</v>
@@ -39606,7 +39606,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.49753129482269</v>
+        <v>1.49753105640411</v>
       </c>
       <c r="H1353" t="n">
         <v>985226</v>
@@ -39635,7 +39635,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.51590597629547</v>
+        <v>1.51590585708618</v>
       </c>
       <c r="H1354" t="n">
         <v>1355627</v>
@@ -39693,7 +39693,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.52258729934692</v>
+        <v>1.5225875377655</v>
       </c>
       <c r="H1356" t="n">
         <v>1042227</v>
@@ -39722,7 +39722,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.51924657821655</v>
+        <v>1.51924645900726</v>
       </c>
       <c r="H1357" t="n">
         <v>1221440</v>
@@ -39751,7 +39751,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.51924657821655</v>
+        <v>1.51924645900726</v>
       </c>
       <c r="H1358" t="n">
         <v>1480530</v>
@@ -39780,7 +39780,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.60709428787231</v>
+        <v>1.60709416866302</v>
       </c>
       <c r="H1359" t="n">
         <v>4790217</v>
@@ -39809,7 +39809,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.5924528837204</v>
+        <v>1.59245300292969</v>
       </c>
       <c r="H1360" t="n">
         <v>1658439</v>
@@ -39867,7 +39867,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.57350540161133</v>
+        <v>1.57350552082062</v>
       </c>
       <c r="H1362" t="n">
         <v>2619062</v>
@@ -39925,7 +39925,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.56489288806915</v>
+        <v>1.56489300727844</v>
       </c>
       <c r="H1364" t="n">
         <v>1599198</v>
@@ -39983,7 +39983,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.56489288806915</v>
+        <v>1.56489300727844</v>
       </c>
       <c r="H1366" t="n">
         <v>2449408</v>
@@ -40070,7 +40070,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.57264399528503</v>
+        <v>1.57264411449432</v>
       </c>
       <c r="H1369" t="n">
         <v>1456339</v>
@@ -40099,7 +40099,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.65187931060791</v>
+        <v>1.65187919139862</v>
       </c>
       <c r="H1370" t="n">
         <v>6774314</v>
@@ -40186,7 +40186,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.66565942764282</v>
+        <v>1.66565930843353</v>
       </c>
       <c r="H1373" t="n">
         <v>2970585</v>
@@ -40215,7 +40215,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.69235801696777</v>
+        <v>1.69235789775848</v>
       </c>
       <c r="H1374" t="n">
         <v>3511135</v>
@@ -40302,7 +40302,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.831019282341</v>
+        <v>1.83101940155029</v>
       </c>
       <c r="H1377" t="n">
         <v>5655370</v>
@@ -40331,7 +40331,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.83274185657501</v>
+        <v>1.8327419757843</v>
       </c>
       <c r="H1378" t="n">
         <v>2364501</v>
@@ -40360,7 +40360,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.80173695087433</v>
+        <v>1.80173683166504</v>
       </c>
       <c r="H1379" t="n">
         <v>2810289</v>
@@ -40418,7 +40418,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.76728689670563</v>
+        <v>1.76728677749634</v>
       </c>
       <c r="H1381" t="n">
         <v>4332546</v>
@@ -40476,7 +40476,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.78106701374054</v>
+        <v>1.78106689453125</v>
       </c>
       <c r="H1383" t="n">
         <v>2001920</v>
@@ -40563,7 +40563,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.83963191509247</v>
+        <v>1.83963203430176</v>
       </c>
       <c r="H1386" t="n">
         <v>6728917</v>
@@ -40592,7 +40592,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.82585179805756</v>
+        <v>1.82585191726685</v>
       </c>
       <c r="H1387" t="n">
         <v>2856954</v>
@@ -40650,7 +40650,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.79656946659088</v>
+        <v>1.79656934738159</v>
       </c>
       <c r="H1389" t="n">
         <v>2547377</v>
@@ -40708,7 +40708,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.79829204082489</v>
+        <v>1.79829180240631</v>
       </c>
       <c r="H1391" t="n">
         <v>2148110</v>
@@ -40766,7 +40766,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.87063717842102</v>
+        <v>1.87063694000244</v>
       </c>
       <c r="H1393" t="n">
         <v>3124693</v>
@@ -40795,7 +40795,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.86891448497772</v>
+        <v>1.86891436576843</v>
       </c>
       <c r="H1394" t="n">
         <v>3432153</v>
@@ -40940,7 +40940,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.95503926277161</v>
+        <v>1.95503950119019</v>
       </c>
       <c r="H1399" t="n">
         <v>2249090</v>
@@ -40969,7 +40969,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.94470429420471</v>
+        <v>1.94470453262329</v>
       </c>
       <c r="H1400" t="n">
         <v>6000564</v>
@@ -41085,7 +41085,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.91197693347931</v>
+        <v>1.9119770526886</v>
       </c>
       <c r="H1404" t="n">
         <v>1741874</v>
@@ -41143,7 +41143,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.92058968544006</v>
+        <v>1.92058944702148</v>
       </c>
       <c r="H1406" t="n">
         <v>1626077</v>
@@ -41230,7 +41230,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.78106701374054</v>
+        <v>1.78106689453125</v>
       </c>
       <c r="H1409" t="n">
         <v>4726963</v>
@@ -41259,7 +41259,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.81207203865051</v>
+        <v>1.81207191944122</v>
       </c>
       <c r="H1410" t="n">
         <v>3028379</v>
@@ -41288,7 +41288,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.84652197360992</v>
+        <v>1.84652185440063</v>
       </c>
       <c r="H1411" t="n">
         <v>2012524</v>
@@ -41317,7 +41317,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.83790946006775</v>
+        <v>1.83790934085846</v>
       </c>
       <c r="H1412" t="n">
         <v>1424377</v>
@@ -41433,7 +41433,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.83790946006775</v>
+        <v>1.83790934085846</v>
       </c>
       <c r="H1416" t="n">
         <v>1709498</v>
@@ -41520,7 +41520,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.92920196056366</v>
+        <v>1.92920219898224</v>
       </c>
       <c r="H1419" t="n">
         <v>22194642</v>
@@ -41665,7 +41665,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.90508675575256</v>
+        <v>1.90508699417114</v>
       </c>
       <c r="H1424" t="n">
         <v>1834534</v>
@@ -41694,7 +41694,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.90508675575256</v>
+        <v>1.90508699417114</v>
       </c>
       <c r="H1425" t="n">
         <v>3197473</v>
@@ -41810,7 +41810,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.06183457374573</v>
+        <v>2.06183433532715</v>
       </c>
       <c r="H1429" t="n">
         <v>4144115</v>
@@ -41839,7 +41839,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.98087704181671</v>
+        <v>1.98087680339813</v>
       </c>
       <c r="H1430" t="n">
         <v>5086497</v>
@@ -41955,7 +41955,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.92058968544006</v>
+        <v>1.92058944702148</v>
       </c>
       <c r="H1434" t="n">
         <v>2727200</v>
@@ -41984,7 +41984,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.91197693347931</v>
+        <v>1.9119770526886</v>
       </c>
       <c r="H1435" t="n">
         <v>1399216</v>
@@ -42100,7 +42100,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.96020710468292</v>
+        <v>1.9602073431015</v>
       </c>
       <c r="H1439" t="n">
         <v>1459843</v>
@@ -42187,7 +42187,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.01532673835754</v>
+        <v>2.01532697677612</v>
       </c>
       <c r="H1442" t="n">
         <v>4357519</v>
@@ -42216,7 +42216,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.01360464096069</v>
+        <v>2.01360440254211</v>
       </c>
       <c r="H1443" t="n">
         <v>6083558</v>
@@ -42245,7 +42245,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.00671458244324</v>
+        <v>2.00671434402466</v>
       </c>
       <c r="H1444" t="n">
         <v>1600191</v>
@@ -42303,7 +42303,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.01360464096069</v>
+        <v>2.01360440254211</v>
       </c>
       <c r="H1446" t="n">
         <v>2019884</v>
@@ -42361,7 +42361,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G1448" t="n">
-        <v>2.01188230514526</v>
+        <v>2.01188206672668</v>
       </c>
       <c r="H1448" t="n">
         <v>2593978</v>
@@ -42593,7 +42593,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.92058968544006</v>
+        <v>1.92058944702148</v>
       </c>
       <c r="H1456" t="n">
         <v>920719</v>
@@ -42622,7 +42622,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.92058968544006</v>
+        <v>1.92058944702148</v>
       </c>
       <c r="H1457" t="n">
         <v>1237770</v>
@@ -42651,7 +42651,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.90680932998657</v>
+        <v>1.90680956840515</v>
       </c>
       <c r="H1458" t="n">
         <v>1242219</v>
@@ -42738,7 +42738,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.86030209064484</v>
+        <v>1.86030197143555</v>
       </c>
       <c r="H1461" t="n">
         <v>1395726</v>
@@ -42825,7 +42825,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.87580442428589</v>
+        <v>1.87580454349518</v>
       </c>
       <c r="H1464" t="n">
         <v>1232432</v>
@@ -42941,7 +42941,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.85513436794281</v>
+        <v>1.85513460636139</v>
       </c>
       <c r="H1468" t="n">
         <v>1757422</v>
@@ -43057,7 +43057,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.84824430942535</v>
+        <v>1.84824442863464</v>
       </c>
       <c r="H1472" t="n">
         <v>2858480</v>
@@ -43086,7 +43086,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.86202442646027</v>
+        <v>1.86202430725098</v>
       </c>
       <c r="H1473" t="n">
         <v>2883877</v>
@@ -43173,7 +43173,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.86030209064484</v>
+        <v>1.86030197143555</v>
       </c>
       <c r="H1476" t="n">
         <v>1643206</v>
@@ -43231,7 +43231,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.89302957057953</v>
+        <v>1.89302933216095</v>
       </c>
       <c r="H1478" t="n">
         <v>1181498</v>
@@ -43260,7 +43260,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.89130699634552</v>
+        <v>1.8913072347641</v>
       </c>
       <c r="H1479" t="n">
         <v>1405366</v>
@@ -43405,7 +43405,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.87408196926117</v>
+        <v>1.87408208847046</v>
       </c>
       <c r="H1484" t="n">
         <v>2025662</v>
@@ -43463,7 +43463,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.81723940372467</v>
+        <v>1.81723928451538</v>
       </c>
       <c r="H1486" t="n">
         <v>1966762</v>
@@ -43492,7 +43492,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.83790946006775</v>
+        <v>1.83790934085846</v>
       </c>
       <c r="H1487" t="n">
         <v>3745529</v>
@@ -43608,7 +43608,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.86030209064484</v>
+        <v>1.86030197143555</v>
       </c>
       <c r="H1491" t="n">
         <v>3727686</v>
@@ -43637,7 +43637,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.86202442646027</v>
+        <v>1.86202430725098</v>
       </c>
       <c r="H1492" t="n">
         <v>1317744</v>
@@ -43695,7 +43695,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G1494" t="n">
-        <v>1.82757449150085</v>
+        <v>1.82757437229156</v>
       </c>
       <c r="H1494" t="n">
         <v>1300642</v>
@@ -43753,7 +43753,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.81207203865051</v>
+        <v>1.81207191944122</v>
       </c>
       <c r="H1496" t="n">
         <v>1731235</v>
@@ -43840,7 +43840,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G1499" t="n">
-        <v>1.78451204299927</v>
+        <v>1.78451192378998</v>
       </c>
       <c r="H1499" t="n">
         <v>2123675</v>
@@ -43869,7 +43869,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.76211941242218</v>
+        <v>1.76211929321289</v>
       </c>
       <c r="H1500" t="n">
         <v>1463157</v>
@@ -43927,7 +43927,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G1502" t="n">
-        <v>1.76728689670563</v>
+        <v>1.76728677749634</v>
       </c>
       <c r="H1502" t="n">
         <v>782320</v>
@@ -43985,7 +43985,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.74833929538727</v>
+        <v>1.74833917617798</v>
       </c>
       <c r="H1504" t="n">
         <v>1584665</v>
@@ -44043,7 +44043,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.74489438533783</v>
+        <v>1.74489450454712</v>
       </c>
       <c r="H1506" t="n">
         <v>3370365</v>
@@ -44072,7 +44072,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.75006186962128</v>
+        <v>1.75006198883057</v>
       </c>
       <c r="H1507" t="n">
         <v>1520737</v>
@@ -44188,7 +44188,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.79656946659088</v>
+        <v>1.79656934738159</v>
       </c>
       <c r="H1511" t="n">
         <v>752410</v>
@@ -44217,7 +44217,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.80173695087433</v>
+        <v>1.80173683166504</v>
       </c>
       <c r="H1512" t="n">
         <v>897905</v>
@@ -44246,7 +44246,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.80862677097321</v>
+        <v>1.8086268901825</v>
       </c>
       <c r="H1513" t="n">
         <v>811698</v>
@@ -44304,7 +44304,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.74833929538727</v>
+        <v>1.74833917617798</v>
       </c>
       <c r="H1515" t="n">
         <v>1761149</v>
@@ -44391,7 +44391,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.76211941242218</v>
+        <v>1.76211929321289</v>
       </c>
       <c r="H1518" t="n">
         <v>1147183</v>
@@ -44449,7 +44449,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.74489438533783</v>
+        <v>1.74489450454712</v>
       </c>
       <c r="H1520" t="n">
         <v>1054836</v>
@@ -44478,7 +44478,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.78106701374054</v>
+        <v>1.78106689453125</v>
       </c>
       <c r="H1521" t="n">
         <v>682870</v>
@@ -44536,7 +44536,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.81379425525665</v>
+        <v>1.81379413604736</v>
       </c>
       <c r="H1523" t="n">
         <v>858585</v>
@@ -44565,7 +44565,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.80862677097321</v>
+        <v>1.8086268901825</v>
       </c>
       <c r="H1524" t="n">
         <v>974166</v>
@@ -44594,7 +44594,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.79484677314758</v>
+        <v>1.79484689235687</v>
       </c>
       <c r="H1525" t="n">
         <v>785060</v>
@@ -44623,7 +44623,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.79140186309814</v>
+        <v>1.79140198230743</v>
       </c>
       <c r="H1526" t="n">
         <v>717448</v>
@@ -44739,7 +44739,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.75006186962128</v>
+        <v>1.75006198883057</v>
       </c>
       <c r="H1530" t="n">
         <v>1262011</v>
@@ -44826,7 +44826,7 @@
         <v>1.96300005912781</v>
       </c>
       <c r="G1533" t="n">
-        <v>1.69063568115234</v>
+        <v>1.69063556194305</v>
       </c>
       <c r="H1533" t="n">
         <v>1179114</v>
@@ -44942,7 +44942,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.78278923034668</v>
+        <v>1.78278934955597</v>
       </c>
       <c r="H1537" t="n">
         <v>2586008</v>
@@ -45000,7 +45000,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G1539" t="n">
-        <v>1.74489438533783</v>
+        <v>1.74489450454712</v>
       </c>
       <c r="H1539" t="n">
         <v>1187215</v>
@@ -45058,7 +45058,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G1541" t="n">
-        <v>1.69149672985077</v>
+        <v>1.69149684906006</v>
       </c>
       <c r="H1541" t="n">
         <v>2074185</v>
@@ -45087,7 +45087,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.61742913722992</v>
+        <v>1.61742925643921</v>
       </c>
       <c r="H1542" t="n">
         <v>3300233</v>
@@ -45145,7 +45145,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.56661534309387</v>
+        <v>1.56661522388458</v>
       </c>
       <c r="H1544" t="n">
         <v>6401161</v>
@@ -45174,7 +45174,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.5924528837204</v>
+        <v>1.59245300292969</v>
       </c>
       <c r="H1545" t="n">
         <v>6343872</v>
@@ -45261,7 +45261,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.6036491394043</v>
+        <v>1.60364902019501</v>
       </c>
       <c r="H1548" t="n">
         <v>2683469</v>
@@ -45290,7 +45290,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.60020434856415</v>
+        <v>1.60020422935486</v>
       </c>
       <c r="H1549" t="n">
         <v>2078255</v>
@@ -45319,7 +45319,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.56403172016144</v>
+        <v>1.56403160095215</v>
       </c>
       <c r="H1550" t="n">
         <v>2641754</v>
@@ -45348,7 +45348,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.52010786533356</v>
+        <v>1.52010774612427</v>
       </c>
       <c r="H1551" t="n">
         <v>3034166</v>
@@ -45377,7 +45377,7 @@
         <v>1.74699997901917</v>
       </c>
       <c r="G1552" t="n">
-        <v>1.50460529327393</v>
+        <v>1.50460541248322</v>
       </c>
       <c r="H1552" t="n">
         <v>2404808</v>
@@ -45406,7 +45406,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.52958142757416</v>
+        <v>1.52958154678345</v>
       </c>
       <c r="H1553" t="n">
         <v>1791724</v>
@@ -45435,7 +45435,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.55972540378571</v>
+        <v>1.55972528457642</v>
       </c>
       <c r="H1554" t="n">
         <v>1475966</v>
@@ -45522,7 +45522,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.53302669525146</v>
+        <v>1.53302657604218</v>
       </c>
       <c r="H1557" t="n">
         <v>1921397</v>
@@ -45551,7 +45551,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.57608926296234</v>
+        <v>1.57608914375305</v>
       </c>
       <c r="H1558" t="n">
         <v>1301192</v>
@@ -45580,7 +45580,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.5933141708374</v>
+        <v>1.59331429004669</v>
       </c>
       <c r="H1559" t="n">
         <v>1734770</v>
@@ -45696,7 +45696,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.47101652622223</v>
+        <v>1.47101640701294</v>
       </c>
       <c r="H1563" t="n">
         <v>2448765</v>
@@ -45725,7 +45725,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.44776284694672</v>
+        <v>1.44776272773743</v>
       </c>
       <c r="H1564" t="n">
         <v>1508958</v>
@@ -45754,7 +45754,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.39781010150909</v>
+        <v>1.39781022071838</v>
       </c>
       <c r="H1565" t="n">
         <v>4082257</v>
@@ -45812,7 +45812,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.45206904411316</v>
+        <v>1.45206892490387</v>
       </c>
       <c r="H1567" t="n">
         <v>2169113</v>
@@ -45841,7 +45841,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.40383899211884</v>
+        <v>1.40383887290955</v>
       </c>
       <c r="H1568" t="n">
         <v>2918108</v>
@@ -45870,7 +45870,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.41245150566101</v>
+        <v>1.41245138645172</v>
       </c>
       <c r="H1569" t="n">
         <v>3160029</v>
@@ -45957,7 +45957,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.26431632041931</v>
+        <v>1.2643164396286</v>
       </c>
       <c r="H1572" t="n">
         <v>3671085</v>
@@ -45986,7 +45986,7 @@
         <v>1.49899995326996</v>
       </c>
       <c r="G1573" t="n">
-        <v>1.29101514816284</v>
+        <v>1.29101490974426</v>
       </c>
       <c r="H1573" t="n">
         <v>1926092</v>
@@ -46015,7 +46015,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1574" t="n">
-        <v>1.36938893795013</v>
+        <v>1.36938905715942</v>
       </c>
       <c r="H1574" t="n">
         <v>1620281</v>
@@ -46044,7 +46044,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.3306325674057</v>
+        <v>1.33063268661499</v>
       </c>
       <c r="H1575" t="n">
         <v>891189</v>
@@ -46189,7 +46189,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1580" t="n">
-        <v>1.44862401485443</v>
+        <v>1.44862413406372</v>
       </c>
       <c r="H1580" t="n">
         <v>1140545</v>
@@ -46305,7 +46305,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.39092028141022</v>
+        <v>1.39092040061951</v>
       </c>
       <c r="H1584" t="n">
         <v>1647838</v>
@@ -46334,7 +46334,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.4003940820694</v>
+        <v>1.40039420127869</v>
       </c>
       <c r="H1585" t="n">
         <v>939327</v>
@@ -46392,7 +46392,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G1587" t="n">
-        <v>1.4003940820694</v>
+        <v>1.40039420127869</v>
       </c>
       <c r="H1587" t="n">
         <v>1414021</v>
@@ -46421,7 +46421,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1588" t="n">
-        <v>1.43484389781952</v>
+        <v>1.43484401702881</v>
       </c>
       <c r="H1588" t="n">
         <v>2104855</v>
@@ -46479,7 +46479,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.38747525215149</v>
+        <v>1.38747501373291</v>
       </c>
       <c r="H1590" t="n">
         <v>1732002</v>
@@ -46537,7 +46537,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.41589641571045</v>
+        <v>1.41589653491974</v>
       </c>
       <c r="H1592" t="n">
         <v>1112144</v>
@@ -46769,7 +46769,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.41589641571045</v>
+        <v>1.41589653491974</v>
       </c>
       <c r="H1600" t="n">
         <v>941807</v>
@@ -46827,7 +46827,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.45551407337189</v>
+        <v>1.4555139541626</v>
       </c>
       <c r="H1602" t="n">
         <v>1352805</v>
@@ -46885,7 +46885,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.42795407772064</v>
+        <v>1.42795395851135</v>
       </c>
       <c r="H1604" t="n">
         <v>1349109</v>
@@ -46943,7 +46943,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.39608776569366</v>
+        <v>1.39608788490295</v>
       </c>
       <c r="H1606" t="n">
         <v>1293537</v>
@@ -47001,7 +47001,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.39092028141022</v>
+        <v>1.39092040061951</v>
       </c>
       <c r="H1608" t="n">
         <v>444474</v>
@@ -47030,7 +47030,7 @@
         <v>1.625</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.3995326757431</v>
+        <v>1.39953255653381</v>
       </c>
       <c r="H1609" t="n">
         <v>792740</v>
@@ -47059,7 +47059,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G1610" t="n">
-        <v>1.3754175901413</v>
+        <v>1.37541770935059</v>
       </c>
       <c r="H1610" t="n">
         <v>804436</v>
@@ -47146,7 +47146,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.36938893795013</v>
+        <v>1.36938905715942</v>
       </c>
       <c r="H1613" t="n">
         <v>1295309</v>
@@ -47175,7 +47175,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.37197279930115</v>
+        <v>1.37197268009186</v>
       </c>
       <c r="H1614" t="n">
         <v>1717276</v>
@@ -47233,7 +47233,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.33924520015717</v>
+        <v>1.33924508094788</v>
       </c>
       <c r="H1616" t="n">
         <v>1434960</v>
@@ -47262,7 +47262,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G1617" t="n">
-        <v>1.39608776569366</v>
+        <v>1.39608788490295</v>
       </c>
       <c r="H1617" t="n">
         <v>904146</v>
@@ -47291,7 +47291,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.3780015707016</v>
+        <v>1.37800145149231</v>
       </c>
       <c r="H1618" t="n">
         <v>976808</v>
@@ -47407,7 +47407,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.42278647422791</v>
+        <v>1.42278635501862</v>
       </c>
       <c r="H1622" t="n">
         <v>505791</v>
@@ -47436,7 +47436,7 @@
         <v>1.62699997425079</v>
       </c>
       <c r="G1623" t="n">
-        <v>1.4012553691864</v>
+        <v>1.40125524997711</v>
       </c>
       <c r="H1623" t="n">
         <v>461646</v>
@@ -47465,7 +47465,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1624" t="n">
-        <v>1.39092028141022</v>
+        <v>1.39092040061951</v>
       </c>
       <c r="H1624" t="n">
         <v>793598</v>
@@ -79951,6 +79951,64 @@
         <v>2121333</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>1.90900003910065</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>1.87600004673004</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>1.90699994564056</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>1.90699994564056</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>2074763</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>1.89800000190735</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>1.85000002384186</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>1.89300000667572</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>1.89300000667572</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>2893559</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G2" t="n">
-        <v>2.99598336219788</v>
+        <v>2.99598288536072</v>
       </c>
       <c r="H2" t="n">
         <v>726355</v>
@@ -456,7 +456,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91082644462585</v>
+        <v>2.91082620620728</v>
       </c>
       <c r="H3" t="n">
         <v>1077659</v>
@@ -485,7 +485,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G4" t="n">
-        <v>2.87366652488708</v>
+        <v>2.87366676330566</v>
       </c>
       <c r="H4" t="n">
         <v>1045563</v>
@@ -514,7 +514,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G5" t="n">
-        <v>2.80089616775513</v>
+        <v>2.80089592933655</v>
       </c>
       <c r="H5" t="n">
         <v>1006703</v>
@@ -543,7 +543,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78541278839111</v>
+        <v>2.78541350364685</v>
       </c>
       <c r="H6" t="n">
         <v>761745</v>
@@ -572,7 +572,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>2.75599527359009</v>
+        <v>2.75599503517151</v>
       </c>
       <c r="H7" t="n">
         <v>914159</v>
@@ -601,7 +601,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76218819618225</v>
+        <v>2.76218843460083</v>
       </c>
       <c r="H8" t="n">
         <v>789466</v>
@@ -630,7 +630,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G9" t="n">
-        <v>2.75289797782898</v>
+        <v>2.75289821624756</v>
       </c>
       <c r="H9" t="n">
         <v>581213</v>
@@ -659,7 +659,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75289797782898</v>
+        <v>2.75289821624756</v>
       </c>
       <c r="H10" t="n">
         <v>1613399</v>
@@ -775,7 +775,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G14" t="n">
-        <v>2.58877754211426</v>
+        <v>2.58877778053284</v>
       </c>
       <c r="H14" t="n">
         <v>2075260</v>
@@ -804,7 +804,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G15" t="n">
-        <v>2.65690279006958</v>
+        <v>2.65690302848816</v>
       </c>
       <c r="H15" t="n">
         <v>1385445</v>
@@ -833,7 +833,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G16" t="n">
-        <v>2.74825382232666</v>
+        <v>2.74825358390808</v>
       </c>
       <c r="H16" t="n">
         <v>1094217</v>
@@ -862,7 +862,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G17" t="n">
-        <v>2.70180416107178</v>
+        <v>2.7018039226532</v>
       </c>
       <c r="H17" t="n">
         <v>491722</v>
@@ -920,7 +920,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G19" t="n">
-        <v>2.72657704353333</v>
+        <v>2.7265772819519</v>
       </c>
       <c r="H19" t="n">
         <v>765235</v>
@@ -949,7 +949,7 @@
         <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2.70954561233521</v>
+        <v>2.70954585075378</v>
       </c>
       <c r="H20" t="n">
         <v>1434225</v>
@@ -1007,7 +1007,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G22" t="n">
-        <v>2.74206018447876</v>
+        <v>2.74206042289734</v>
       </c>
       <c r="H22" t="n">
         <v>585827</v>
@@ -1036,7 +1036,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63213014602661</v>
+        <v>2.63212990760803</v>
       </c>
       <c r="H23" t="n">
         <v>529297</v>
@@ -1065,7 +1065,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G24" t="n">
-        <v>2.55006957054138</v>
+        <v>2.5500693321228</v>
       </c>
       <c r="H24" t="n">
         <v>965335</v>
@@ -1094,7 +1094,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G25" t="n">
-        <v>2.61664724349976</v>
+        <v>2.61664700508118</v>
       </c>
       <c r="H25" t="n">
         <v>1715094</v>
@@ -1123,7 +1123,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G26" t="n">
-        <v>2.55316662788391</v>
+        <v>2.55316638946533</v>
       </c>
       <c r="H26" t="n">
         <v>2005520</v>
@@ -1152,7 +1152,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G27" t="n">
-        <v>2.43859171867371</v>
+        <v>2.43859124183655</v>
       </c>
       <c r="H27" t="n">
         <v>2592460</v>
@@ -1181,7 +1181,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.39988327026367</v>
+        <v>2.39988350868225</v>
       </c>
       <c r="H28" t="n">
         <v>2628393</v>
@@ -1210,7 +1210,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G29" t="n">
-        <v>2.47884726524353</v>
+        <v>2.47884702682495</v>
       </c>
       <c r="H29" t="n">
         <v>1883723</v>
@@ -1268,7 +1268,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G31" t="n">
-        <v>2.31472635269165</v>
+        <v>2.31472611427307</v>
       </c>
       <c r="H31" t="n">
         <v>1452187</v>
@@ -1355,7 +1355,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G34" t="n">
-        <v>2.60116386413574</v>
+        <v>2.60116410255432</v>
       </c>
       <c r="H34" t="n">
         <v>2832395</v>
@@ -1384,7 +1384,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G35" t="n">
-        <v>2.59342265129089</v>
+        <v>2.59342217445374</v>
       </c>
       <c r="H35" t="n">
         <v>1621895</v>
@@ -1413,7 +1413,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G36" t="n">
-        <v>2.53768301010132</v>
+        <v>2.5376832485199</v>
       </c>
       <c r="H36" t="n">
         <v>1099387</v>
@@ -1442,7 +1442,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G37" t="n">
-        <v>2.62438821792603</v>
+        <v>2.6243884563446</v>
       </c>
       <c r="H37" t="n">
         <v>1413624</v>
@@ -1471,7 +1471,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G38" t="n">
-        <v>2.63987183570862</v>
+        <v>2.63987159729004</v>
       </c>
       <c r="H38" t="n">
         <v>1416246</v>
@@ -1558,7 +1558,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G41" t="n">
-        <v>2.73122215270996</v>
+        <v>2.73122239112854</v>
       </c>
       <c r="H41" t="n">
         <v>1616252</v>
@@ -1616,7 +1616,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>2.84115242958069</v>
+        <v>2.84115219116211</v>
       </c>
       <c r="H43" t="n">
         <v>992208</v>
@@ -1703,7 +1703,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G46" t="n">
-        <v>2.9170196056366</v>
+        <v>2.91701912879944</v>
       </c>
       <c r="H46" t="n">
         <v>1310637</v>
@@ -1732,7 +1732,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87366652488708</v>
+        <v>2.87366676330566</v>
       </c>
       <c r="H47" t="n">
         <v>1022713</v>
@@ -1761,7 +1761,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G48" t="n">
-        <v>2.82257270812988</v>
+        <v>2.82257223129272</v>
       </c>
       <c r="H48" t="n">
         <v>1053721</v>
@@ -1790,7 +1790,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.80244445800781</v>
+        <v>2.80244398117065</v>
       </c>
       <c r="H49" t="n">
         <v>851655</v>
@@ -1848,7 +1848,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G51" t="n">
-        <v>2.83341097831726</v>
+        <v>2.8334105014801</v>
       </c>
       <c r="H51" t="n">
         <v>1171012</v>
@@ -1877,7 +1877,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G52" t="n">
-        <v>2.8891499042511</v>
+        <v>2.88915014266968</v>
       </c>
       <c r="H52" t="n">
         <v>1341195</v>
@@ -1906,7 +1906,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G53" t="n">
-        <v>2.9170196056366</v>
+        <v>2.91701912879944</v>
       </c>
       <c r="H53" t="n">
         <v>764014</v>
@@ -1993,7 +1993,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G56" t="n">
-        <v>2.78076839447021</v>
+        <v>2.78076791763306</v>
       </c>
       <c r="H56" t="n">
         <v>2141845</v>
@@ -2051,7 +2051,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G58" t="n">
-        <v>2.86592531204224</v>
+        <v>2.86592507362366</v>
       </c>
       <c r="H58" t="n">
         <v>663781</v>
@@ -2109,7 +2109,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G60" t="n">
-        <v>2.78696131706238</v>
+        <v>2.7869610786438</v>
       </c>
       <c r="H60" t="n">
         <v>440085</v>
@@ -2138,7 +2138,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.73276996612549</v>
+        <v>2.73277020454407</v>
       </c>
       <c r="H61" t="n">
         <v>652481</v>
@@ -2196,7 +2196,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G63" t="n">
-        <v>2.87521505355835</v>
+        <v>2.87521529197693</v>
       </c>
       <c r="H63" t="n">
         <v>1458208</v>
@@ -2254,7 +2254,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G65" t="n">
-        <v>2.77921938896179</v>
+        <v>2.77921962738037</v>
       </c>
       <c r="H65" t="n">
         <v>1268914</v>
@@ -2283,7 +2283,7 @@
         <v>3.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.70954561233521</v>
+        <v>2.70954585075378</v>
       </c>
       <c r="H66" t="n">
         <v>781074</v>
@@ -2312,7 +2312,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G67" t="n">
-        <v>2.71109390258789</v>
+        <v>2.71109437942505</v>
       </c>
       <c r="H67" t="n">
         <v>574845</v>
@@ -2341,7 +2341,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G68" t="n">
-        <v>2.72657704353333</v>
+        <v>2.7265772819519</v>
       </c>
       <c r="H68" t="n">
         <v>1070111</v>
@@ -2399,7 +2399,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G70" t="n">
-        <v>2.82412052154541</v>
+        <v>2.82412075996399</v>
       </c>
       <c r="H70" t="n">
         <v>925444</v>
@@ -2428,7 +2428,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80244445800781</v>
+        <v>2.80244398117065</v>
       </c>
       <c r="H71" t="n">
         <v>1384237</v>
@@ -2457,7 +2457,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>2.86437678337097</v>
+        <v>2.86437654495239</v>
       </c>
       <c r="H72" t="n">
         <v>2605699</v>
@@ -2486,7 +2486,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G73" t="n">
-        <v>2.89379453659058</v>
+        <v>2.89379477500916</v>
       </c>
       <c r="H73" t="n">
         <v>1090424</v>
@@ -2515,7 +2515,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>2.84115242958069</v>
+        <v>2.84115219116211</v>
       </c>
       <c r="H74" t="n">
         <v>539769</v>
@@ -2544,7 +2544,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G75" t="n">
-        <v>2.84424877166748</v>
+        <v>2.84424901008606</v>
       </c>
       <c r="H75" t="n">
         <v>709531</v>
@@ -2573,7 +2573,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.87986040115356</v>
+        <v>2.87986016273499</v>
       </c>
       <c r="H76" t="n">
         <v>593773</v>
@@ -2602,7 +2602,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G77" t="n">
-        <v>2.88605356216431</v>
+        <v>2.88605332374573</v>
       </c>
       <c r="H77" t="n">
         <v>824413</v>
@@ -2660,7 +2660,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G79" t="n">
-        <v>2.87521505355835</v>
+        <v>2.87521529197693</v>
       </c>
       <c r="H79" t="n">
         <v>1011988</v>
@@ -2689,7 +2689,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G80" t="n">
-        <v>2.85353899002075</v>
+        <v>2.85353851318359</v>
       </c>
       <c r="H80" t="n">
         <v>489744</v>
@@ -2776,7 +2776,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G83" t="n">
-        <v>3.0099184513092</v>
+        <v>3.00991821289062</v>
       </c>
       <c r="H83" t="n">
         <v>2440016</v>
@@ -2805,7 +2805,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G84" t="n">
-        <v>2.95882439613342</v>
+        <v>2.95882391929626</v>
       </c>
       <c r="H84" t="n">
         <v>1543779</v>
@@ -2834,7 +2834,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G85" t="n">
-        <v>2.98978996276855</v>
+        <v>2.98979020118713</v>
       </c>
       <c r="H85" t="n">
         <v>771249</v>
@@ -2863,7 +2863,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G86" t="n">
-        <v>2.93250274658203</v>
+        <v>2.93250250816345</v>
       </c>
       <c r="H86" t="n">
         <v>839175</v>
@@ -2921,7 +2921,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G88" t="n">
-        <v>2.87366652488708</v>
+        <v>2.87366676330566</v>
       </c>
       <c r="H88" t="n">
         <v>401319</v>
@@ -2979,7 +2979,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>2.80244445800781</v>
+        <v>2.80244398117065</v>
       </c>
       <c r="H90" t="n">
         <v>352951</v>
@@ -3008,7 +3008,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G91" t="n">
-        <v>2.81328296661377</v>
+        <v>2.81328272819519</v>
       </c>
       <c r="H91" t="n">
         <v>397299</v>
@@ -3037,7 +3037,7 @@
         <v>3.69199991226196</v>
       </c>
       <c r="G92" t="n">
-        <v>2.85818314552307</v>
+        <v>2.85818362236023</v>
       </c>
       <c r="H92" t="n">
         <v>520677</v>
@@ -3095,7 +3095,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87057018280029</v>
+        <v>2.87057042121887</v>
       </c>
       <c r="H94" t="n">
         <v>882620</v>
@@ -3124,7 +3124,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>2.87986040115356</v>
+        <v>2.87986016273499</v>
       </c>
       <c r="H95" t="n">
         <v>502468</v>
@@ -3153,7 +3153,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G96" t="n">
-        <v>2.9170196056366</v>
+        <v>2.91701912879944</v>
       </c>
       <c r="H96" t="n">
         <v>1488002</v>
@@ -3182,7 +3182,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88605356216431</v>
+        <v>2.88605332374573</v>
       </c>
       <c r="H97" t="n">
         <v>857610</v>
@@ -3211,7 +3211,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G98" t="n">
-        <v>2.84115242958069</v>
+        <v>2.84115219116211</v>
       </c>
       <c r="H98" t="n">
         <v>1366830</v>
@@ -3240,7 +3240,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G99" t="n">
-        <v>2.84579706192017</v>
+        <v>2.84579753875732</v>
       </c>
       <c r="H99" t="n">
         <v>552258</v>
@@ -3298,7 +3298,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.48107171058655</v>
+        <v>2.48107194900513</v>
       </c>
       <c r="H101" t="n">
         <v>14577083</v>
@@ -3327,7 +3327,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G102" t="n">
-        <v>2.49515962600708</v>
+        <v>2.49515986442566</v>
       </c>
       <c r="H102" t="n">
         <v>6755386</v>
@@ -3356,7 +3356,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G103" t="n">
-        <v>2.45759177207947</v>
+        <v>2.45759153366089</v>
       </c>
       <c r="H103" t="n">
         <v>4846198</v>
@@ -3385,7 +3385,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G104" t="n">
-        <v>2.4732449054718</v>
+        <v>2.47324514389038</v>
       </c>
       <c r="H104" t="n">
         <v>4700172</v>
@@ -3414,7 +3414,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G105" t="n">
-        <v>2.46854877471924</v>
+        <v>2.46854901313782</v>
       </c>
       <c r="H105" t="n">
         <v>2374462</v>
@@ -3472,7 +3472,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>2.37932395935059</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H107" t="n">
         <v>2771779</v>
@@ -3501,7 +3501,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G108" t="n">
-        <v>2.38715124130249</v>
+        <v>2.38715100288391</v>
       </c>
       <c r="H108" t="n">
         <v>1816564</v>
@@ -3530,7 +3530,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G109" t="n">
-        <v>2.34958291053772</v>
+        <v>2.3495831489563</v>
       </c>
       <c r="H109" t="n">
         <v>3325389</v>
@@ -3588,7 +3588,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G111" t="n">
-        <v>2.37932395935059</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H111" t="n">
         <v>1834416</v>
@@ -3646,7 +3646,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G113" t="n">
-        <v>2.41219687461853</v>
+        <v>2.41219639778137</v>
       </c>
       <c r="H113" t="n">
         <v>3288781</v>
@@ -3675,7 +3675,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>2.35271310806274</v>
+        <v>2.3527135848999</v>
       </c>
       <c r="H114" t="n">
         <v>1983083</v>
@@ -3704,7 +3704,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G115" t="n">
-        <v>2.2494010925293</v>
+        <v>2.24940061569214</v>
       </c>
       <c r="H115" t="n">
         <v>2114026</v>
@@ -3762,7 +3762,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G117" t="n">
-        <v>2.11634635925293</v>
+        <v>2.11634683609009</v>
       </c>
       <c r="H117" t="n">
         <v>2151270</v>
@@ -3820,7 +3820,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>2.14452290534973</v>
+        <v>2.14452219009399</v>
       </c>
       <c r="H119" t="n">
         <v>3285866</v>
@@ -3849,7 +3849,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G120" t="n">
-        <v>2.22748565673828</v>
+        <v>2.22748613357544</v>
       </c>
       <c r="H120" t="n">
         <v>2220357</v>
@@ -3907,7 +3907,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G122" t="n">
-        <v>2.21026706695557</v>
+        <v>2.21026682853699</v>
       </c>
       <c r="H122" t="n">
         <v>1579649</v>
@@ -3965,7 +3965,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G124" t="n">
-        <v>2.00990271568298</v>
+        <v>2.00990295410156</v>
       </c>
       <c r="H124" t="n">
         <v>2255357</v>
@@ -4023,7 +4023,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G126" t="n">
-        <v>1.9394623041153</v>
+        <v>1.93946206569672</v>
       </c>
       <c r="H126" t="n">
         <v>1598076</v>
@@ -4052,7 +4052,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G127" t="n">
-        <v>1.9738997220993</v>
+        <v>1.97389960289001</v>
       </c>
       <c r="H127" t="n">
         <v>2900139</v>
@@ -4081,7 +4081,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G128" t="n">
-        <v>1.9864227771759</v>
+        <v>1.98642313480377</v>
       </c>
       <c r="H128" t="n">
         <v>1698763</v>
@@ -4139,7 +4139,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G130" t="n">
-        <v>2.12260794639587</v>
+        <v>2.12260770797729</v>
       </c>
       <c r="H130" t="n">
         <v>1365226</v>
@@ -4168,7 +4168,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G131" t="n">
-        <v>2.09130096435547</v>
+        <v>2.09130072593689</v>
       </c>
       <c r="H131" t="n">
         <v>2319336</v>
@@ -4226,7 +4226,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G133" t="n">
-        <v>2.00990271568298</v>
+        <v>2.00990295410156</v>
       </c>
       <c r="H133" t="n">
         <v>2375724</v>
@@ -4255,7 +4255,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.11321544647217</v>
+        <v>2.11321568489075</v>
       </c>
       <c r="H134" t="n">
         <v>2706963</v>
@@ -4284,7 +4284,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G135" t="n">
-        <v>2.17582964897156</v>
+        <v>2.1758291721344</v>
       </c>
       <c r="H135" t="n">
         <v>2019536</v>
@@ -4371,7 +4371,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G138" t="n">
-        <v>2.21026706695557</v>
+        <v>2.21026682853699</v>
       </c>
       <c r="H138" t="n">
         <v>738553</v>
@@ -4400,7 +4400,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G139" t="n">
-        <v>2.18678665161133</v>
+        <v>2.18678689002991</v>
       </c>
       <c r="H139" t="n">
         <v>440899</v>
@@ -4429,7 +4429,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G140" t="n">
-        <v>2.18991756439209</v>
+        <v>2.18991804122925</v>
       </c>
       <c r="H140" t="n">
         <v>492382</v>
@@ -4487,7 +4487,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G142" t="n">
-        <v>2.14608788490295</v>
+        <v>2.14608764648438</v>
       </c>
       <c r="H142" t="n">
         <v>760877</v>
@@ -4574,7 +4574,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G145" t="n">
-        <v>2.14765310287476</v>
+        <v>2.14765334129333</v>
       </c>
       <c r="H145" t="n">
         <v>979578</v>
@@ -4632,7 +4632,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G147" t="n">
-        <v>2.2040057182312</v>
+        <v>2.20400547981262</v>
       </c>
       <c r="H147" t="n">
         <v>1296535</v>
@@ -4661,7 +4661,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G148" t="n">
-        <v>2.07564783096313</v>
+        <v>2.0756471157074</v>
       </c>
       <c r="H148" t="n">
         <v>6229742</v>
@@ -4690,7 +4690,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G149" t="n">
-        <v>2.11791181564331</v>
+        <v>2.11791205406189</v>
       </c>
       <c r="H149" t="n">
         <v>3166446</v>
@@ -4719,7 +4719,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G150" t="n">
-        <v>2.06782031059265</v>
+        <v>2.06782054901123</v>
       </c>
       <c r="H150" t="n">
         <v>2120646</v>
@@ -4748,7 +4748,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G151" t="n">
-        <v>1.97859632968903</v>
+        <v>1.97859597206116</v>
       </c>
       <c r="H151" t="n">
         <v>1640032</v>
@@ -4777,7 +4777,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>1.94885456562042</v>
+        <v>1.94885432720184</v>
       </c>
       <c r="H152" t="n">
         <v>1298678</v>
@@ -4806,7 +4806,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>1.94102776050568</v>
+        <v>1.94102799892426</v>
       </c>
       <c r="H153" t="n">
         <v>1093413</v>
@@ -4835,7 +4835,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G154" t="n">
-        <v>1.96137690544128</v>
+        <v>1.96137714385986</v>
       </c>
       <c r="H154" t="n">
         <v>876363</v>
@@ -4864,7 +4864,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G155" t="n">
-        <v>2.01146793365479</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H155" t="n">
         <v>1272598</v>
@@ -4922,7 +4922,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>1.99581491947174</v>
+        <v>1.99581444263458</v>
       </c>
       <c r="H157" t="n">
         <v>930572</v>
@@ -4951,7 +4951,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G158" t="n">
-        <v>2.10538911819458</v>
+        <v>2.10538864135742</v>
       </c>
       <c r="H158" t="n">
         <v>3572397</v>
@@ -4980,7 +4980,7 @@
         <v>2.75</v>
       </c>
       <c r="G159" t="n">
-        <v>2.1523494720459</v>
+        <v>2.15234971046448</v>
       </c>
       <c r="H159" t="n">
         <v>2034937</v>
@@ -5009,7 +5009,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G160" t="n">
-        <v>2.08347392082214</v>
+        <v>2.08347415924072</v>
       </c>
       <c r="H160" t="n">
         <v>1937826</v>
@@ -5125,7 +5125,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>2.05842852592468</v>
+        <v>2.05842876434326</v>
       </c>
       <c r="H164" t="n">
         <v>1061581</v>
@@ -5154,7 +5154,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G165" t="n">
-        <v>2.09756207466125</v>
+        <v>2.09756231307983</v>
       </c>
       <c r="H165" t="n">
         <v>837027</v>
@@ -5183,7 +5183,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.11321544647217</v>
+        <v>2.11321568489075</v>
       </c>
       <c r="H166" t="n">
         <v>813589</v>
@@ -5212,7 +5212,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>2.0740818977356</v>
+        <v>2.07408213615417</v>
       </c>
       <c r="H167" t="n">
         <v>749117</v>
@@ -5241,7 +5241,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G168" t="n">
-        <v>2.09756207466125</v>
+        <v>2.09756231307983</v>
       </c>
       <c r="H168" t="n">
         <v>697763</v>
@@ -5270,7 +5270,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G169" t="n">
-        <v>2.11947679519653</v>
+        <v>2.11947703361511</v>
       </c>
       <c r="H169" t="n">
         <v>499989</v>
@@ -5299,7 +5299,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G170" t="n">
-        <v>2.15861034393311</v>
+        <v>2.15861058235168</v>
       </c>
       <c r="H170" t="n">
         <v>1280318</v>
@@ -5328,7 +5328,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G171" t="n">
-        <v>2.15704536437988</v>
+        <v>2.15704560279846</v>
       </c>
       <c r="H171" t="n">
         <v>898895</v>
@@ -5415,7 +5415,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G174" t="n">
-        <v>2.14452290534973</v>
+        <v>2.14452219009399</v>
       </c>
       <c r="H174" t="n">
         <v>280821</v>
@@ -5444,7 +5444,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G175" t="n">
-        <v>2.14608788490295</v>
+        <v>2.14608764648438</v>
       </c>
       <c r="H175" t="n">
         <v>554785</v>
@@ -5473,7 +5473,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G176" t="n">
-        <v>2.17582964897156</v>
+        <v>2.1758291721344</v>
       </c>
       <c r="H176" t="n">
         <v>876827</v>
@@ -5502,7 +5502,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>2.14765310287476</v>
+        <v>2.14765334129333</v>
       </c>
       <c r="H177" t="n">
         <v>959389</v>
@@ -5589,7 +5589,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>2.01146793365479</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H180" t="n">
         <v>939604</v>
@@ -5647,7 +5647,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G182" t="n">
-        <v>1.98955357074738</v>
+        <v>1.9895533323288</v>
       </c>
       <c r="H182" t="n">
         <v>1468702</v>
@@ -5676,7 +5676,7 @@
         <v>2.5</v>
       </c>
       <c r="G183" t="n">
-        <v>1.95668125152588</v>
+        <v>1.95668137073517</v>
       </c>
       <c r="H183" t="n">
         <v>2497228</v>
@@ -5705,7 +5705,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G184" t="n">
-        <v>1.99424922466278</v>
+        <v>1.99424946308136</v>
       </c>
       <c r="H184" t="n">
         <v>1176506</v>
@@ -5792,7 +5792,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>1.98798799514771</v>
+        <v>1.98798811435699</v>
       </c>
       <c r="H187" t="n">
         <v>900283</v>
@@ -5821,7 +5821,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G188" t="n">
-        <v>1.97859632968903</v>
+        <v>1.97859597206116</v>
       </c>
       <c r="H188" t="n">
         <v>375877</v>
@@ -5850,7 +5850,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G189" t="n">
-        <v>1.91754770278931</v>
+        <v>1.91754758358002</v>
       </c>
       <c r="H189" t="n">
         <v>786779</v>
@@ -5908,7 +5908,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G191" t="n">
-        <v>2.05529808998108</v>
+        <v>2.0552978515625</v>
       </c>
       <c r="H191" t="n">
         <v>3388408</v>
@@ -5937,7 +5937,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G192" t="n">
-        <v>1.99268436431885</v>
+        <v>1.99268424510956</v>
       </c>
       <c r="H192" t="n">
         <v>1798626</v>
@@ -5995,7 +5995,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G194" t="n">
-        <v>1.95355021953583</v>
+        <v>1.95355069637299</v>
       </c>
       <c r="H194" t="n">
         <v>944804</v>
@@ -6024,7 +6024,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G195" t="n">
-        <v>1.94885456562042</v>
+        <v>1.94885432720184</v>
       </c>
       <c r="H195" t="n">
         <v>460629</v>
@@ -6053,7 +6053,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G196" t="n">
-        <v>2.02868747711182</v>
+        <v>2.02868700027466</v>
       </c>
       <c r="H196" t="n">
         <v>1217923</v>
@@ -6082,7 +6082,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G197" t="n">
-        <v>2.02242588996887</v>
+        <v>2.02242612838745</v>
       </c>
       <c r="H197" t="n">
         <v>682441</v>
@@ -6111,7 +6111,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G198" t="n">
-        <v>1.96763825416565</v>
+        <v>1.96763873100281</v>
       </c>
       <c r="H198" t="n">
         <v>843471</v>
@@ -6169,7 +6169,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G200" t="n">
-        <v>1.96763825416565</v>
+        <v>1.96763873100281</v>
       </c>
       <c r="H200" t="n">
         <v>746930</v>
@@ -6198,7 +6198,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G201" t="n">
-        <v>1.93320119380951</v>
+        <v>1.93320107460022</v>
       </c>
       <c r="H201" t="n">
         <v>830606</v>
@@ -6227,7 +6227,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G202" t="n">
-        <v>1.93320119380951</v>
+        <v>1.93320107460022</v>
       </c>
       <c r="H202" t="n">
         <v>1085623</v>
@@ -6256,7 +6256,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G203" t="n">
-        <v>1.96763825416565</v>
+        <v>1.96763873100281</v>
       </c>
       <c r="H203" t="n">
         <v>470437</v>
@@ -6285,7 +6285,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96450793743134</v>
+        <v>1.96450781822205</v>
       </c>
       <c r="H204" t="n">
         <v>817690</v>
@@ -6372,7 +6372,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>2.08973550796509</v>
+        <v>2.08973574638367</v>
       </c>
       <c r="H207" t="n">
         <v>859886</v>
@@ -6430,7 +6430,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G209" t="n">
-        <v>2.1038236618042</v>
+        <v>2.10382342338562</v>
       </c>
       <c r="H209" t="n">
         <v>987784</v>
@@ -6459,7 +6459,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G210" t="n">
-        <v>2.08660483360291</v>
+        <v>2.08660507202148</v>
       </c>
       <c r="H210" t="n">
         <v>726475</v>
@@ -6488,7 +6488,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>2.08973550796509</v>
+        <v>2.08973574638367</v>
       </c>
       <c r="H211" t="n">
         <v>544659</v>
@@ -6517,7 +6517,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G212" t="n">
-        <v>2.03338289260864</v>
+        <v>2.03338313102722</v>
       </c>
       <c r="H212" t="n">
         <v>1605178</v>
@@ -6546,7 +6546,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G213" t="n">
-        <v>1.97859632968903</v>
+        <v>1.97859597206116</v>
       </c>
       <c r="H213" t="n">
         <v>1439805</v>
@@ -6575,7 +6575,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>1.98798799514771</v>
+        <v>1.98798811435699</v>
       </c>
       <c r="H214" t="n">
         <v>951415</v>
@@ -6604,7 +6604,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G215" t="n">
-        <v>1.96137690544128</v>
+        <v>1.96137714385986</v>
       </c>
       <c r="H215" t="n">
         <v>535801</v>
@@ -6662,7 +6662,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G217" t="n">
-        <v>1.91128635406494</v>
+        <v>1.91128611564636</v>
       </c>
       <c r="H217" t="n">
         <v>763654</v>
@@ -6691,7 +6691,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89563238620758</v>
+        <v>1.89563274383545</v>
       </c>
       <c r="H218" t="n">
         <v>762448</v>
@@ -6749,7 +6749,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G220" t="n">
-        <v>1.91128635406494</v>
+        <v>1.91128611564636</v>
       </c>
       <c r="H220" t="n">
         <v>476146</v>
@@ -6778,7 +6778,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>2.05842852592468</v>
+        <v>2.05842876434326</v>
       </c>
       <c r="H221" t="n">
         <v>7385474</v>
@@ -6807,7 +6807,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G222" t="n">
-        <v>2.08816981315613</v>
+        <v>2.08817028999329</v>
       </c>
       <c r="H222" t="n">
         <v>4219197</v>
@@ -6836,7 +6836,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G223" t="n">
-        <v>2.03025269508362</v>
+        <v>2.03025245666504</v>
       </c>
       <c r="H223" t="n">
         <v>2200910</v>
@@ -6894,7 +6894,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G225" t="n">
-        <v>2.14765310287476</v>
+        <v>2.14765334129333</v>
       </c>
       <c r="H225" t="n">
         <v>2264389</v>
@@ -6923,7 +6923,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G226" t="n">
-        <v>2.08816981315613</v>
+        <v>2.08817028999329</v>
       </c>
       <c r="H226" t="n">
         <v>1286080</v>
@@ -6952,7 +6952,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G227" t="n">
-        <v>2.08660483360291</v>
+        <v>2.08660507202148</v>
       </c>
       <c r="H227" t="n">
         <v>977540</v>
@@ -7010,7 +7010,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G229" t="n">
-        <v>1.99581491947174</v>
+        <v>1.99581444263458</v>
       </c>
       <c r="H229" t="n">
         <v>1137034</v>
@@ -7039,7 +7039,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G230" t="n">
-        <v>2.01146793365479</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H230" t="n">
         <v>871707</v>
@@ -7068,7 +7068,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G231" t="n">
-        <v>2.01146793365479</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H231" t="n">
         <v>940946</v>
@@ -7097,7 +7097,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>1.99581491947174</v>
+        <v>1.99581444263458</v>
       </c>
       <c r="H232" t="n">
         <v>459440</v>
@@ -7126,7 +7126,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G233" t="n">
-        <v>1.98955357074738</v>
+        <v>1.9895533323288</v>
       </c>
       <c r="H233" t="n">
         <v>602925</v>
@@ -7184,7 +7184,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G235" t="n">
-        <v>1.96763825416565</v>
+        <v>1.96763873100281</v>
       </c>
       <c r="H235" t="n">
         <v>925158</v>
@@ -7213,7 +7213,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G236" t="n">
-        <v>2.03807926177979</v>
+        <v>2.03807950019836</v>
       </c>
       <c r="H236" t="n">
         <v>1447942</v>
@@ -7242,7 +7242,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G237" t="n">
-        <v>2.03807926177979</v>
+        <v>2.03807950019836</v>
       </c>
       <c r="H237" t="n">
         <v>614516</v>
@@ -7271,7 +7271,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G238" t="n">
-        <v>2.04434084892273</v>
+        <v>2.04434037208557</v>
       </c>
       <c r="H238" t="n">
         <v>1826358</v>
@@ -7300,7 +7300,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G239" t="n">
-        <v>2.09756207466125</v>
+        <v>2.09756231307983</v>
       </c>
       <c r="H239" t="n">
         <v>1527580</v>
@@ -7329,7 +7329,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G240" t="n">
-        <v>2.17113351821899</v>
+        <v>2.17113304138184</v>
       </c>
       <c r="H240" t="n">
         <v>2515736</v>
@@ -7358,7 +7358,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G241" t="n">
-        <v>2.23687767982483</v>
+        <v>2.23687791824341</v>
       </c>
       <c r="H241" t="n">
         <v>3252090</v>
@@ -7416,7 +7416,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G243" t="n">
-        <v>2.24626970291138</v>
+        <v>2.24626994132996</v>
       </c>
       <c r="H243" t="n">
         <v>2334527</v>
@@ -7503,7 +7503,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G246" t="n">
-        <v>2.34958291053772</v>
+        <v>2.3495831489563</v>
       </c>
       <c r="H246" t="n">
         <v>3285193</v>
@@ -7532,7 +7532,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G247" t="n">
-        <v>2.37775921821594</v>
+        <v>2.37775874137878</v>
       </c>
       <c r="H247" t="n">
         <v>1476950</v>
@@ -7561,7 +7561,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>2.37932395935059</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H248" t="n">
         <v>2467677</v>
@@ -7590,7 +7590,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>2.37932395935059</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H249" t="n">
         <v>2372938</v>
@@ -7619,7 +7619,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G250" t="n">
-        <v>2.38088989257812</v>
+        <v>2.38088965415955</v>
       </c>
       <c r="H250" t="n">
         <v>1340592</v>
@@ -7648,7 +7648,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>2.37932395935059</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H251" t="n">
         <v>1637113</v>
@@ -7677,7 +7677,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G252" t="n">
-        <v>2.42002296447754</v>
+        <v>2.42002320289612</v>
       </c>
       <c r="H252" t="n">
         <v>2194065</v>
@@ -7706,7 +7706,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G253" t="n">
-        <v>2.39028143882751</v>
+        <v>2.39028167724609</v>
       </c>
       <c r="H253" t="n">
         <v>1171723</v>
@@ -7735,7 +7735,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G254" t="n">
-        <v>2.39654326438904</v>
+        <v>2.39654302597046</v>
       </c>
       <c r="H254" t="n">
         <v>358245</v>
@@ -7764,7 +7764,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G255" t="n">
-        <v>2.36367082595825</v>
+        <v>2.36367106437683</v>
       </c>
       <c r="H255" t="n">
         <v>645515</v>
@@ -7822,7 +7822,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G257" t="n">
-        <v>2.34958291053772</v>
+        <v>2.3495831489563</v>
       </c>
       <c r="H257" t="n">
         <v>574581</v>
@@ -7851,7 +7851,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G258" t="n">
-        <v>2.43098044395447</v>
+        <v>2.43098092079163</v>
       </c>
       <c r="H258" t="n">
         <v>1363312</v>
@@ -7938,7 +7938,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G261" t="n">
-        <v>2.45759177207947</v>
+        <v>2.45759153366089</v>
       </c>
       <c r="H261" t="n">
         <v>853673</v>
@@ -8025,7 +8025,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G264" t="n">
-        <v>2.45759177207947</v>
+        <v>2.45759153366089</v>
       </c>
       <c r="H264" t="n">
         <v>879469</v>
@@ -8170,7 +8170,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G269" t="n">
-        <v>2.41376209259033</v>
+        <v>2.41376185417175</v>
       </c>
       <c r="H269" t="n">
         <v>690659</v>
@@ -8199,7 +8199,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.3949773311615</v>
+        <v>2.39497756958008</v>
       </c>
       <c r="H270" t="n">
         <v>486139</v>
@@ -8257,7 +8257,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G272" t="n">
-        <v>2.4028046131134</v>
+        <v>2.40280413627625</v>
       </c>
       <c r="H272" t="n">
         <v>626345</v>
@@ -8286,7 +8286,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G273" t="n">
-        <v>2.38402009010315</v>
+        <v>2.38402056694031</v>
       </c>
       <c r="H273" t="n">
         <v>1065395</v>
@@ -8315,7 +8315,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G274" t="n">
-        <v>2.41376209259033</v>
+        <v>2.41376185417175</v>
       </c>
       <c r="H274" t="n">
         <v>621910</v>
@@ -8431,7 +8431,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.30888414382935</v>
+        <v>2.30888366699219</v>
       </c>
       <c r="H278" t="n">
         <v>1234287</v>
@@ -8460,7 +8460,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G279" t="n">
-        <v>2.25566220283508</v>
+        <v>2.2556619644165</v>
       </c>
       <c r="H279" t="n">
         <v>863160</v>
@@ -8576,7 +8576,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>2.23061609268188</v>
+        <v>2.23061633110046</v>
       </c>
       <c r="H283" t="n">
         <v>840338</v>
@@ -8605,7 +8605,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.24626970291138</v>
+        <v>2.24626994132996</v>
       </c>
       <c r="H284" t="n">
         <v>930384</v>
@@ -8634,7 +8634,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G285" t="n">
-        <v>2.23844313621521</v>
+        <v>2.23844289779663</v>
       </c>
       <c r="H285" t="n">
         <v>543762</v>
@@ -8663,7 +8663,7 @@
         <v>2.96199989318848</v>
       </c>
       <c r="G286" t="n">
-        <v>2.31827592849731</v>
+        <v>2.31827545166016</v>
       </c>
       <c r="H286" t="n">
         <v>1191078</v>
@@ -8721,7 +8721,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G288" t="n">
-        <v>2.39341259002686</v>
+        <v>2.39341282844543</v>
       </c>
       <c r="H288" t="n">
         <v>860854</v>
@@ -8750,7 +8750,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>2.41063094139099</v>
+        <v>2.41063117980957</v>
       </c>
       <c r="H289" t="n">
         <v>1135351</v>
@@ -8779,7 +8779,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G290" t="n">
-        <v>2.42002296447754</v>
+        <v>2.42002320289612</v>
       </c>
       <c r="H290" t="n">
         <v>2382345</v>
@@ -8837,7 +8837,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G292" t="n">
-        <v>2.3699324131012</v>
+        <v>2.36993217468262</v>
       </c>
       <c r="H292" t="n">
         <v>1275136</v>
@@ -8866,7 +8866,7 @@
         <v>3</v>
       </c>
       <c r="G293" t="n">
-        <v>2.34801721572876</v>
+        <v>2.34801745414734</v>
       </c>
       <c r="H293" t="n">
         <v>865361</v>
@@ -8924,7 +8924,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>2.35584449768066</v>
+        <v>2.35584402084351</v>
       </c>
       <c r="H295" t="n">
         <v>931240</v>
@@ -8953,7 +8953,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G296" t="n">
-        <v>2.33705973625183</v>
+        <v>2.33705997467041</v>
       </c>
       <c r="H296" t="n">
         <v>869769</v>
@@ -8982,7 +8982,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G297" t="n">
-        <v>2.4528956413269</v>
+        <v>2.45289540290833</v>
       </c>
       <c r="H297" t="n">
         <v>4692514</v>
@@ -9040,7 +9040,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G299" t="n">
-        <v>2.48107171058655</v>
+        <v>2.48107194900513</v>
       </c>
       <c r="H299" t="n">
         <v>1238634</v>
@@ -9127,7 +9127,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G302" t="n">
-        <v>2.53585839271545</v>
+        <v>2.53585863113403</v>
       </c>
       <c r="H302" t="n">
         <v>879229</v>
@@ -9156,7 +9156,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="n">
-        <v>2.50455212593079</v>
+        <v>2.50455188751221</v>
       </c>
       <c r="H303" t="n">
         <v>952772</v>
@@ -9185,7 +9185,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>2.50455212593079</v>
+        <v>2.50455188751221</v>
       </c>
       <c r="H304" t="n">
         <v>820425</v>
@@ -9272,7 +9272,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G307" t="n">
-        <v>2.49202919006348</v>
+        <v>2.49202871322632</v>
       </c>
       <c r="H307" t="n">
         <v>1006054</v>
@@ -9301,7 +9301,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>2.49672532081604</v>
+        <v>2.49672508239746</v>
       </c>
       <c r="H308" t="n">
         <v>948293</v>
@@ -9330,7 +9330,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>2.45759177207947</v>
+        <v>2.45759153366089</v>
       </c>
       <c r="H309" t="n">
         <v>969086</v>
@@ -9388,7 +9388,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G311" t="n">
-        <v>2.5734269618988</v>
+        <v>2.57342672348022</v>
       </c>
       <c r="H311" t="n">
         <v>2285027</v>
@@ -9446,7 +9446,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G313" t="n">
-        <v>2.46541881561279</v>
+        <v>2.46541857719421</v>
       </c>
       <c r="H313" t="n">
         <v>1680814</v>
@@ -9475,7 +9475,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G314" t="n">
-        <v>2.4513304233551</v>
+        <v>2.45132994651794</v>
       </c>
       <c r="H314" t="n">
         <v>1373872</v>
@@ -9562,7 +9562,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.50455212593079</v>
+        <v>2.50455188751221</v>
       </c>
       <c r="H317" t="n">
         <v>1108703</v>
@@ -9649,7 +9649,7 @@
         <v>3.10400009155273</v>
       </c>
       <c r="G320" t="n">
-        <v>2.42941546440125</v>
+        <v>2.42941570281982</v>
       </c>
       <c r="H320" t="n">
         <v>1672455</v>
@@ -9736,7 +9736,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G323" t="n">
-        <v>2.4028046131134</v>
+        <v>2.40280413627625</v>
       </c>
       <c r="H323" t="n">
         <v>1842216</v>
@@ -9794,7 +9794,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G325" t="n">
-        <v>2.41063094139099</v>
+        <v>2.41063117980957</v>
       </c>
       <c r="H325" t="n">
         <v>1145350</v>
@@ -9823,7 +9823,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G326" t="n">
-        <v>2.44506907463074</v>
+        <v>2.44506883621216</v>
       </c>
       <c r="H326" t="n">
         <v>1236854</v>
@@ -9852,7 +9852,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.46541881561279</v>
+        <v>2.46541857719421</v>
       </c>
       <c r="H327" t="n">
         <v>1448459</v>
@@ -9881,7 +9881,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.4732449054718</v>
+        <v>2.47324514389038</v>
       </c>
       <c r="H328" t="n">
         <v>633759</v>
@@ -9939,7 +9939,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G330" t="n">
-        <v>2.39028143882751</v>
+        <v>2.39028167724609</v>
       </c>
       <c r="H330" t="n">
         <v>977417</v>
@@ -9997,7 +9997,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G332" t="n">
-        <v>2.29792642593384</v>
+        <v>2.29792666435242</v>
       </c>
       <c r="H332" t="n">
         <v>1838891</v>
@@ -10026,7 +10026,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G333" t="n">
-        <v>2.38715124130249</v>
+        <v>2.38715100288391</v>
       </c>
       <c r="H333" t="n">
         <v>1119719</v>
@@ -10084,7 +10084,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>2.3949773311615</v>
+        <v>2.39497756958008</v>
       </c>
       <c r="H335" t="n">
         <v>2078075</v>
@@ -10229,7 +10229,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G340" t="n">
-        <v>2.44506907463074</v>
+        <v>2.44506883621216</v>
       </c>
       <c r="H340" t="n">
         <v>1747619</v>
@@ -10287,7 +10287,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G342" t="n">
-        <v>2.49046397209167</v>
+        <v>2.49046349525452</v>
       </c>
       <c r="H342" t="n">
         <v>772862</v>
@@ -10316,7 +10316,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G343" t="n">
-        <v>2.53272819519043</v>
+        <v>2.53272795677185</v>
       </c>
       <c r="H343" t="n">
         <v>1468440</v>
@@ -10374,7 +10374,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G345" t="n">
-        <v>2.53742432594299</v>
+        <v>2.53742408752441</v>
       </c>
       <c r="H345" t="n">
         <v>1106003</v>
@@ -10403,7 +10403,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>2.62195301055908</v>
+        <v>2.6219527721405</v>
       </c>
       <c r="H346" t="n">
         <v>3151258</v>
@@ -10461,7 +10461,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>2.62195301055908</v>
+        <v>2.6219527721405</v>
       </c>
       <c r="H348" t="n">
         <v>2137829</v>
@@ -10490,7 +10490,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G349" t="n">
-        <v>2.62508344650269</v>
+        <v>2.62508368492126</v>
       </c>
       <c r="H349" t="n">
         <v>1648864</v>
@@ -10519,7 +10519,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G350" t="n">
-        <v>2.64543318748474</v>
+        <v>2.64543294906616</v>
       </c>
       <c r="H350" t="n">
         <v>1368979</v>
@@ -10577,7 +10577,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.53585839271545</v>
+        <v>2.53585863113403</v>
       </c>
       <c r="H352" t="n">
         <v>2123505</v>
@@ -10606,7 +10606,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G353" t="n">
-        <v>2.43098044395447</v>
+        <v>2.43098092079163</v>
       </c>
       <c r="H353" t="n">
         <v>3812104</v>
@@ -10664,7 +10664,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G355" t="n">
-        <v>2.5204017162323</v>
+        <v>2.52040147781372</v>
       </c>
       <c r="H355" t="n">
         <v>818695</v>
@@ -10751,7 +10751,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>2.55542922019958</v>
+        <v>2.55542945861816</v>
       </c>
       <c r="H358" t="n">
         <v>654062</v>
@@ -10925,7 +10925,7 @@
         <v>3.23399996757507</v>
       </c>
       <c r="G364" t="n">
-        <v>2.57453536987305</v>
+        <v>2.57453513145447</v>
       </c>
       <c r="H364" t="n">
         <v>1210712</v>
@@ -10954,7 +10954,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G365" t="n">
-        <v>2.56816673278809</v>
+        <v>2.56816697120667</v>
       </c>
       <c r="H365" t="n">
         <v>1146192</v>
@@ -10983,7 +10983,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G366" t="n">
-        <v>2.55224514007568</v>
+        <v>2.55224537849426</v>
       </c>
       <c r="H366" t="n">
         <v>1387432</v>
@@ -11099,7 +11099,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>2.42009472846985</v>
+        <v>2.42009520530701</v>
       </c>
       <c r="H370" t="n">
         <v>1292806</v>
@@ -11186,7 +11186,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G373" t="n">
-        <v>2.45193839073181</v>
+        <v>2.45193862915039</v>
       </c>
       <c r="H373" t="n">
         <v>732913</v>
@@ -11215,7 +11215,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G374" t="n">
-        <v>2.46785974502563</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H374" t="n">
         <v>2480349</v>
@@ -11244,7 +11244,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G375" t="n">
-        <v>2.43124008178711</v>
+        <v>2.43124032020569</v>
       </c>
       <c r="H375" t="n">
         <v>894485</v>
@@ -11331,7 +11331,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>2.40417313575745</v>
+        <v>2.4041736125946</v>
       </c>
       <c r="H378" t="n">
         <v>554483</v>
@@ -11563,7 +11563,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G386" t="n">
-        <v>2.38984394073486</v>
+        <v>2.38984417915344</v>
       </c>
       <c r="H386" t="n">
         <v>1146093</v>
@@ -11650,7 +11650,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G389" t="n">
-        <v>2.42646408081055</v>
+        <v>2.42646384239197</v>
       </c>
       <c r="H389" t="n">
         <v>1267851</v>
@@ -11679,7 +11679,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.43601703643799</v>
+        <v>2.43601655960083</v>
       </c>
       <c r="H390" t="n">
         <v>1532503</v>
@@ -11708,7 +11708,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G391" t="n">
-        <v>2.38188338279724</v>
+        <v>2.38188290596008</v>
       </c>
       <c r="H391" t="n">
         <v>1358951</v>
@@ -11737,7 +11737,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G392" t="n">
-        <v>2.44716167449951</v>
+        <v>2.44716191291809</v>
       </c>
       <c r="H392" t="n">
         <v>1622777</v>
@@ -11766,7 +11766,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G393" t="n">
-        <v>2.50129556655884</v>
+        <v>2.50129580497742</v>
       </c>
       <c r="H393" t="n">
         <v>2306454</v>
@@ -11795,7 +11795,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G394" t="n">
-        <v>2.45989918708801</v>
+        <v>2.45989942550659</v>
       </c>
       <c r="H394" t="n">
         <v>617432</v>
@@ -11824,7 +11824,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G395" t="n">
-        <v>2.51084899902344</v>
+        <v>2.51084876060486</v>
       </c>
       <c r="H395" t="n">
         <v>4508418</v>
@@ -11998,7 +11998,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>2.45193839073181</v>
+        <v>2.45193862915039</v>
       </c>
       <c r="H401" t="n">
         <v>871950</v>
@@ -12027,7 +12027,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G402" t="n">
-        <v>2.46626830101013</v>
+        <v>2.46626806259155</v>
       </c>
       <c r="H402" t="n">
         <v>623443</v>
@@ -12085,7 +12085,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G404" t="n">
-        <v>2.36755347251892</v>
+        <v>2.36755394935608</v>
       </c>
       <c r="H404" t="n">
         <v>1503729</v>
@@ -12143,7 +12143,7 @@
         <v>2.97399997711182</v>
       </c>
       <c r="G406" t="n">
-        <v>2.36755347251892</v>
+        <v>2.36755394935608</v>
       </c>
       <c r="H406" t="n">
         <v>1069692</v>
@@ -12172,7 +12172,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G407" t="n">
-        <v>2.354816198349</v>
+        <v>2.35481643676758</v>
       </c>
       <c r="H407" t="n">
         <v>777560</v>
@@ -12201,7 +12201,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G408" t="n">
-        <v>2.3643696308136</v>
+        <v>2.36436915397644</v>
       </c>
       <c r="H408" t="n">
         <v>484836</v>
@@ -12230,7 +12230,7 @@
         <v>3</v>
       </c>
       <c r="G409" t="n">
-        <v>2.3882520198822</v>
+        <v>2.38825178146362</v>
       </c>
       <c r="H409" t="n">
         <v>757900</v>
@@ -12259,7 +12259,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G410" t="n">
-        <v>2.3643696308136</v>
+        <v>2.36436915397644</v>
       </c>
       <c r="H410" t="n">
         <v>977540</v>
@@ -12288,7 +12288,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G411" t="n">
-        <v>2.36118531227112</v>
+        <v>2.36118507385254</v>
       </c>
       <c r="H411" t="n">
         <v>872287</v>
@@ -12317,7 +12317,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G412" t="n">
-        <v>2.31660437583923</v>
+        <v>2.31660413742065</v>
       </c>
       <c r="H412" t="n">
         <v>1233935</v>
@@ -12375,7 +12375,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G414" t="n">
-        <v>2.26724696159363</v>
+        <v>2.26724720001221</v>
       </c>
       <c r="H414" t="n">
         <v>1196625</v>
@@ -12433,7 +12433,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G416" t="n">
-        <v>2.33571004867554</v>
+        <v>2.33571028709412</v>
       </c>
       <c r="H416" t="n">
         <v>923284</v>
@@ -12462,7 +12462,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G417" t="n">
-        <v>2.33571004867554</v>
+        <v>2.33571028709412</v>
       </c>
       <c r="H417" t="n">
         <v>656989</v>
@@ -12520,7 +12520,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G419" t="n">
-        <v>2.28316879272461</v>
+        <v>2.28316855430603</v>
       </c>
       <c r="H419" t="n">
         <v>481583</v>
@@ -12607,7 +12607,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G422" t="n">
-        <v>2.33411812782288</v>
+        <v>2.3341178894043</v>
       </c>
       <c r="H422" t="n">
         <v>683681</v>
@@ -12636,7 +12636,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G423" t="n">
-        <v>2.34844756126404</v>
+        <v>2.34844732284546</v>
       </c>
       <c r="H423" t="n">
         <v>685400</v>
@@ -12723,7 +12723,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G426" t="n">
-        <v>2.34844756126404</v>
+        <v>2.34844732284546</v>
       </c>
       <c r="H426" t="n">
         <v>723093</v>
@@ -12752,7 +12752,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G427" t="n">
-        <v>2.34844756126404</v>
+        <v>2.34844732284546</v>
       </c>
       <c r="H427" t="n">
         <v>1614230</v>
@@ -12781,7 +12781,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G428" t="n">
-        <v>2.37551426887512</v>
+        <v>2.3755145072937</v>
       </c>
       <c r="H428" t="n">
         <v>1245196</v>
@@ -12810,7 +12810,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G429" t="n">
-        <v>2.40258121490479</v>
+        <v>2.40258097648621</v>
       </c>
       <c r="H429" t="n">
         <v>1162563</v>
@@ -12897,7 +12897,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G432" t="n">
-        <v>2.46785974502563</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H432" t="n">
         <v>1295449</v>
@@ -13042,7 +13042,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G437" t="n">
-        <v>2.59682607650757</v>
+        <v>2.59682583808899</v>
       </c>
       <c r="H437" t="n">
         <v>1443378</v>
@@ -13187,7 +13187,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G442" t="n">
-        <v>2.59364128112793</v>
+        <v>2.59364151954651</v>
       </c>
       <c r="H442" t="n">
         <v>856254</v>
@@ -13216,7 +13216,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G443" t="n">
-        <v>2.56498193740845</v>
+        <v>2.56498217582703</v>
       </c>
       <c r="H443" t="n">
         <v>512784</v>
@@ -13274,7 +13274,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61433982849121</v>
+        <v>2.61433935165405</v>
       </c>
       <c r="H445" t="n">
         <v>607795</v>
@@ -13332,7 +13332,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>2.61911606788635</v>
+        <v>2.61911630630493</v>
       </c>
       <c r="H447" t="n">
         <v>569921</v>
@@ -13361,7 +13361,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G448" t="n">
-        <v>2.65573596954346</v>
+        <v>2.65573620796204</v>
       </c>
       <c r="H448" t="n">
         <v>958763</v>
@@ -13419,7 +13419,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G450" t="n">
-        <v>2.60637879371643</v>
+        <v>2.60637831687927</v>
       </c>
       <c r="H450" t="n">
         <v>654933</v>
@@ -13506,7 +13506,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G453" t="n">
-        <v>2.59204936027527</v>
+        <v>2.59204959869385</v>
       </c>
       <c r="H453" t="n">
         <v>921065</v>
@@ -13593,7 +13593,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G456" t="n">
-        <v>2.63822221755981</v>
+        <v>2.63822174072266</v>
       </c>
       <c r="H456" t="n">
         <v>1023456</v>
@@ -13622,7 +13622,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G457" t="n">
-        <v>2.73056769371033</v>
+        <v>2.73056817054749</v>
       </c>
       <c r="H457" t="n">
         <v>5446721</v>
@@ -13709,7 +13709,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G460" t="n">
-        <v>2.72419905662537</v>
+        <v>2.72419929504395</v>
       </c>
       <c r="H460" t="n">
         <v>716646</v>
@@ -13796,7 +13796,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G463" t="n">
-        <v>2.72101473808289</v>
+        <v>2.72101497650146</v>
       </c>
       <c r="H463" t="n">
         <v>1178918</v>
@@ -13825,7 +13825,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G464" t="n">
-        <v>2.74330520629883</v>
+        <v>2.74330496788025</v>
       </c>
       <c r="H464" t="n">
         <v>810084</v>
@@ -13854,7 +13854,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G465" t="n">
-        <v>2.79903101921082</v>
+        <v>2.79903125762939</v>
       </c>
       <c r="H465" t="n">
         <v>1541603</v>
@@ -13883,7 +13883,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G466" t="n">
-        <v>2.8022153377533</v>
+        <v>2.80221557617188</v>
       </c>
       <c r="H466" t="n">
         <v>1027608</v>
@@ -13970,7 +13970,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G469" t="n">
-        <v>2.88978433609009</v>
+        <v>2.88978481292725</v>
       </c>
       <c r="H469" t="n">
         <v>2260751</v>
@@ -13999,7 +13999,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G470" t="n">
-        <v>2.88978433609009</v>
+        <v>2.88978481292725</v>
       </c>
       <c r="H470" t="n">
         <v>1595268</v>
@@ -14057,7 +14057,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G472" t="n">
-        <v>2.92640447616577</v>
+        <v>2.92640471458435</v>
       </c>
       <c r="H472" t="n">
         <v>1536307</v>
@@ -14144,7 +14144,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>2.93754982948303</v>
+        <v>2.93754959106445</v>
       </c>
       <c r="H475" t="n">
         <v>968072</v>
@@ -14173,7 +14173,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G476" t="n">
-        <v>2.90252161026001</v>
+        <v>2.90252184867859</v>
       </c>
       <c r="H476" t="n">
         <v>1820893</v>
@@ -14202,7 +14202,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G477" t="n">
-        <v>2.84201979637146</v>
+        <v>2.84201955795288</v>
       </c>
       <c r="H477" t="n">
         <v>4515902</v>
@@ -14231,7 +14231,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G478" t="n">
-        <v>2.8101761341095</v>
+        <v>2.81017637252808</v>
       </c>
       <c r="H478" t="n">
         <v>3456844</v>
@@ -14260,7 +14260,7 @@
         <v>3.4539999961853</v>
       </c>
       <c r="G479" t="n">
-        <v>2.74967384338379</v>
+        <v>2.74967336654663</v>
       </c>
       <c r="H479" t="n">
         <v>5446955</v>
@@ -14405,7 +14405,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>2.46785974502563</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H484" t="n">
         <v>2655168</v>
@@ -14434,7 +14434,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G485" t="n">
-        <v>2.46785974502563</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H485" t="n">
         <v>1101568</v>
@@ -14463,7 +14463,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G486" t="n">
-        <v>2.48537373542786</v>
+        <v>2.48537421226501</v>
       </c>
       <c r="H486" t="n">
         <v>1237843</v>
@@ -14492,7 +14492,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G487" t="n">
-        <v>2.45989918708801</v>
+        <v>2.45989942550659</v>
       </c>
       <c r="H487" t="n">
         <v>932298</v>
@@ -14521,7 +14521,7 @@
         <v>3.06800007820129</v>
       </c>
       <c r="G488" t="n">
-        <v>2.44238567352295</v>
+        <v>2.44238543510437</v>
       </c>
       <c r="H488" t="n">
         <v>1422705</v>
@@ -14550,7 +14550,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G489" t="n">
-        <v>2.46785974502563</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H489" t="n">
         <v>2139896</v>
@@ -14608,7 +14608,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G491" t="n">
-        <v>2.44716167449951</v>
+        <v>2.44716191291809</v>
       </c>
       <c r="H491" t="n">
         <v>2154714</v>
@@ -14637,7 +14637,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G492" t="n">
-        <v>2.44716167449951</v>
+        <v>2.44716191291809</v>
       </c>
       <c r="H492" t="n">
         <v>1691378</v>
@@ -14753,7 +14753,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G496" t="n">
-        <v>2.53154730796814</v>
+        <v>2.53154683113098</v>
       </c>
       <c r="H496" t="n">
         <v>2034742</v>
@@ -14811,7 +14811,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G498" t="n">
-        <v>2.52199387550354</v>
+        <v>2.5219943523407</v>
       </c>
       <c r="H498" t="n">
         <v>1764419</v>
@@ -14840,7 +14840,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G499" t="n">
-        <v>2.5204017162323</v>
+        <v>2.52040147781372</v>
       </c>
       <c r="H499" t="n">
         <v>1758820</v>
@@ -14898,7 +14898,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G501" t="n">
-        <v>2.60160207748413</v>
+        <v>2.60160183906555</v>
       </c>
       <c r="H501" t="n">
         <v>1303907</v>
@@ -14927,7 +14927,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G502" t="n">
-        <v>2.55383706092834</v>
+        <v>2.5538375377655</v>
       </c>
       <c r="H502" t="n">
         <v>1941059</v>
@@ -14956,7 +14956,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G503" t="n">
-        <v>2.53154730796814</v>
+        <v>2.53154683113098</v>
       </c>
       <c r="H503" t="n">
         <v>1750900</v>
@@ -15072,7 +15072,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G507" t="n">
-        <v>2.56975865364075</v>
+        <v>2.56975889205933</v>
       </c>
       <c r="H507" t="n">
         <v>1259757</v>
@@ -15101,7 +15101,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G508" t="n">
-        <v>2.51084899902344</v>
+        <v>2.51084876060486</v>
       </c>
       <c r="H508" t="n">
         <v>2514530</v>
@@ -15130,7 +15130,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G509" t="n">
-        <v>2.52995443344116</v>
+        <v>2.52995467185974</v>
       </c>
       <c r="H509" t="n">
         <v>917841</v>
@@ -15217,7 +15217,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G512" t="n">
-        <v>2.59364128112793</v>
+        <v>2.59364151954651</v>
       </c>
       <c r="H512" t="n">
         <v>863626</v>
@@ -15246,7 +15246,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G513" t="n">
-        <v>2.59841775894165</v>
+        <v>2.59841752052307</v>
       </c>
       <c r="H513" t="n">
         <v>975318</v>
@@ -15275,7 +15275,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G514" t="n">
-        <v>2.62707686424255</v>
+        <v>2.62707710266113</v>
       </c>
       <c r="H514" t="n">
         <v>1221081</v>
@@ -15304,7 +15304,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G515" t="n">
-        <v>2.65892028808594</v>
+        <v>2.65892052650452</v>
       </c>
       <c r="H515" t="n">
         <v>1978965</v>
@@ -15478,7 +15478,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G521" t="n">
-        <v>2.67643404006958</v>
+        <v>2.676433801651</v>
       </c>
       <c r="H521" t="n">
         <v>2011203</v>
@@ -15507,7 +15507,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G522" t="n">
-        <v>2.63822221755981</v>
+        <v>2.63822174072266</v>
       </c>
       <c r="H522" t="n">
         <v>1918826</v>
@@ -15594,7 +15594,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G525" t="n">
-        <v>2.61911606788635</v>
+        <v>2.61911630630493</v>
       </c>
       <c r="H525" t="n">
         <v>990093</v>
@@ -15623,7 +15623,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G526" t="n">
-        <v>2.63185334205627</v>
+        <v>2.63185358047485</v>
       </c>
       <c r="H526" t="n">
         <v>1221618</v>
@@ -15652,7 +15652,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G527" t="n">
-        <v>2.62070822715759</v>
+        <v>2.62070846557617</v>
       </c>
       <c r="H527" t="n">
         <v>2511181</v>
@@ -15710,7 +15710,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G529" t="n">
-        <v>2.56816673278809</v>
+        <v>2.56816697120667</v>
       </c>
       <c r="H529" t="n">
         <v>1409532</v>
@@ -15768,7 +15768,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G531" t="n">
-        <v>2.56816673278809</v>
+        <v>2.56816697120667</v>
       </c>
       <c r="H531" t="n">
         <v>2024887</v>
@@ -15797,7 +15797,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G532" t="n">
-        <v>2.58249592781067</v>
+        <v>2.58249616622925</v>
       </c>
       <c r="H532" t="n">
         <v>1967995</v>
@@ -15913,7 +15913,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G536" t="n">
-        <v>2.34526324272156</v>
+        <v>2.34526348114014</v>
       </c>
       <c r="H536" t="n">
         <v>2994862</v>
@@ -15971,7 +15971,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G538" t="n">
-        <v>2.21311330795288</v>
+        <v>2.2131130695343</v>
       </c>
       <c r="H538" t="n">
         <v>4141672</v>
@@ -16000,7 +16000,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G539" t="n">
-        <v>2.12872862815857</v>
+        <v>2.12872838973999</v>
       </c>
       <c r="H539" t="n">
         <v>4819283</v>
@@ -16029,7 +16029,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G540" t="n">
-        <v>2.07618689537048</v>
+        <v>2.0761866569519</v>
       </c>
       <c r="H540" t="n">
         <v>2779913</v>
@@ -16058,7 +16058,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>2.05389666557312</v>
+        <v>2.05389642715454</v>
       </c>
       <c r="H541" t="n">
         <v>1892118</v>
@@ -16087,7 +16087,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G542" t="n">
-        <v>2.01409244537354</v>
+        <v>2.01409220695496</v>
       </c>
       <c r="H542" t="n">
         <v>2601422</v>
@@ -16116,7 +16116,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G543" t="n">
-        <v>2.05708074569702</v>
+        <v>2.05708146095276</v>
       </c>
       <c r="H543" t="n">
         <v>1323647</v>
@@ -16145,7 +16145,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G544" t="n">
-        <v>2.07459473609924</v>
+        <v>2.07459449768066</v>
       </c>
       <c r="H544" t="n">
         <v>1590563</v>
@@ -16174,7 +16174,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G545" t="n">
-        <v>2.07300233840942</v>
+        <v>2.07300281524658</v>
       </c>
       <c r="H545" t="n">
         <v>2877331</v>
@@ -16203,7 +16203,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G546" t="n">
-        <v>2.05708074569702</v>
+        <v>2.05708146095276</v>
       </c>
       <c r="H546" t="n">
         <v>755000</v>
@@ -16232,7 +16232,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G547" t="n">
-        <v>2.05708074569702</v>
+        <v>2.05708146095276</v>
       </c>
       <c r="H547" t="n">
         <v>813711</v>
@@ -16261,7 +16261,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G548" t="n">
-        <v>2.10643792152405</v>
+        <v>2.10643768310547</v>
       </c>
       <c r="H548" t="n">
         <v>1554469</v>
@@ -16348,7 +16348,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G551" t="n">
-        <v>2.01727652549744</v>
+        <v>2.01727676391602</v>
       </c>
       <c r="H551" t="n">
         <v>1462101</v>
@@ -16377,7 +16377,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G552" t="n">
-        <v>2.0029468536377</v>
+        <v>2.00294709205627</v>
       </c>
       <c r="H552" t="n">
         <v>2572034</v>
@@ -16406,7 +16406,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G553" t="n">
-        <v>1.98702538013458</v>
+        <v>1.98702573776245</v>
       </c>
       <c r="H553" t="n">
         <v>1328048</v>
@@ -16435,7 +16435,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G554" t="n">
-        <v>1.94881319999695</v>
+        <v>1.94881343841553</v>
       </c>
       <c r="H554" t="n">
         <v>1690849</v>
@@ -16464,7 +16464,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90741717815399</v>
+        <v>1.90741693973541</v>
       </c>
       <c r="H555" t="n">
         <v>2204356</v>
@@ -16493,7 +16493,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G556" t="n">
-        <v>1.89786410331726</v>
+        <v>1.89786434173584</v>
       </c>
       <c r="H556" t="n">
         <v>1534891</v>
@@ -16580,7 +16580,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G559" t="n">
-        <v>2.03160619735718</v>
+        <v>2.0316059589386</v>
       </c>
       <c r="H559" t="n">
         <v>1090698</v>
@@ -16609,7 +16609,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G560" t="n">
-        <v>2.10325384140015</v>
+        <v>2.10325360298157</v>
       </c>
       <c r="H560" t="n">
         <v>2761128</v>
@@ -16667,7 +16667,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G562" t="n">
-        <v>1.91856229305267</v>
+        <v>1.91856241226196</v>
       </c>
       <c r="H562" t="n">
         <v>4495971</v>
@@ -16696,7 +16696,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G563" t="n">
-        <v>1.80870270729065</v>
+        <v>1.80870246887207</v>
       </c>
       <c r="H563" t="n">
         <v>11295853</v>
@@ -16754,7 +16754,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G565" t="n">
-        <v>2.05071258544922</v>
+        <v>2.05071210861206</v>
       </c>
       <c r="H565" t="n">
         <v>10241397</v>
@@ -16812,7 +16812,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G567" t="n">
-        <v>1.9997626543045</v>
+        <v>1.99976277351379</v>
       </c>
       <c r="H567" t="n">
         <v>1325179</v>
@@ -16870,7 +16870,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>1.8548755645752</v>
+        <v>1.85487544536591</v>
       </c>
       <c r="H569" t="n">
         <v>4051183</v>
@@ -16899,7 +16899,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94562888145447</v>
+        <v>1.94562911987305</v>
       </c>
       <c r="H570" t="n">
         <v>2696695</v>
@@ -16928,7 +16928,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G571" t="n">
-        <v>1.88990342617035</v>
+        <v>1.88990330696106</v>
       </c>
       <c r="H571" t="n">
         <v>1404482</v>
@@ -16957,7 +16957,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91219365596771</v>
+        <v>1.91219353675842</v>
       </c>
       <c r="H572" t="n">
         <v>1317721</v>
@@ -16986,7 +16986,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G573" t="n">
-        <v>1.92015433311462</v>
+        <v>1.9201545715332</v>
       </c>
       <c r="H573" t="n">
         <v>1478662</v>
@@ -17015,7 +17015,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G574" t="n">
-        <v>1.91856229305267</v>
+        <v>1.91856241226196</v>
       </c>
       <c r="H574" t="n">
         <v>1225403</v>
@@ -17044,7 +17044,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G575" t="n">
-        <v>1.89945638179779</v>
+        <v>1.89945614337921</v>
       </c>
       <c r="H575" t="n">
         <v>1034331</v>
@@ -17073,7 +17073,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G576" t="n">
-        <v>1.90582478046417</v>
+        <v>1.90582489967346</v>
       </c>
       <c r="H576" t="n">
         <v>1701979</v>
@@ -17102,7 +17102,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G577" t="n">
-        <v>1.95199739933014</v>
+        <v>1.95199775695801</v>
       </c>
       <c r="H577" t="n">
         <v>2027295</v>
@@ -17131,7 +17131,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G578" t="n">
-        <v>1.92015433311462</v>
+        <v>1.9201545715332</v>
       </c>
       <c r="H578" t="n">
         <v>2780712</v>
@@ -17160,7 +17160,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.92652320861816</v>
+        <v>1.9265228509903</v>
       </c>
       <c r="H579" t="n">
         <v>722313</v>
@@ -17218,7 +17218,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>1.90264081954956</v>
+        <v>1.9026403427124</v>
       </c>
       <c r="H581" t="n">
         <v>921579</v>
@@ -17247,7 +17247,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G582" t="n">
-        <v>1.90423250198364</v>
+        <v>1.90423285961151</v>
       </c>
       <c r="H582" t="n">
         <v>1500268</v>
@@ -17276,7 +17276,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G583" t="n">
-        <v>1.89627194404602</v>
+        <v>1.89627206325531</v>
       </c>
       <c r="H583" t="n">
         <v>944622</v>
@@ -17305,7 +17305,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G584" t="n">
-        <v>1.88194251060486</v>
+        <v>1.88194239139557</v>
       </c>
       <c r="H584" t="n">
         <v>1407864</v>
@@ -17334,7 +17334,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G585" t="n">
-        <v>1.8548755645752</v>
+        <v>1.85487544536591</v>
       </c>
       <c r="H585" t="n">
         <v>1777023</v>
@@ -17363,7 +17363,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G586" t="n">
-        <v>1.85009872913361</v>
+        <v>1.85009896755219</v>
       </c>
       <c r="H586" t="n">
         <v>1482418</v>
@@ -17421,7 +17421,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>1.83099293708801</v>
+        <v>1.8309930562973</v>
       </c>
       <c r="H588" t="n">
         <v>2040960</v>
@@ -17450,7 +17450,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G589" t="n">
-        <v>1.81507134437561</v>
+        <v>1.8150714635849</v>
       </c>
       <c r="H589" t="n">
         <v>1297798</v>
@@ -17479,7 +17479,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G590" t="n">
-        <v>1.81507134437561</v>
+        <v>1.8150714635849</v>
       </c>
       <c r="H590" t="n">
         <v>1110350</v>
@@ -17508,7 +17508,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G591" t="n">
-        <v>1.80392611026764</v>
+        <v>1.80392634868622</v>
       </c>
       <c r="H591" t="n">
         <v>1332399</v>
@@ -17566,7 +17566,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G593" t="n">
-        <v>1.78004360198975</v>
+        <v>1.78004372119904</v>
       </c>
       <c r="H593" t="n">
         <v>1670608</v>
@@ -17595,7 +17595,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G594" t="n">
-        <v>1.88990342617035</v>
+        <v>1.88990330696106</v>
       </c>
       <c r="H594" t="n">
         <v>5320330</v>
@@ -17682,7 +17682,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>1.8548755645752</v>
+        <v>1.85487544536591</v>
       </c>
       <c r="H597" t="n">
         <v>5522687</v>
@@ -17711,7 +17711,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G598" t="n">
-        <v>1.87238955497742</v>
+        <v>1.87238931655884</v>
       </c>
       <c r="H598" t="n">
         <v>2693236</v>
@@ -17740,7 +17740,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G599" t="n">
-        <v>1.85169112682343</v>
+        <v>1.851691365242</v>
       </c>
       <c r="H599" t="n">
         <v>1869245</v>
@@ -17769,7 +17769,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G600" t="n">
-        <v>1.87238955497742</v>
+        <v>1.87238931655884</v>
       </c>
       <c r="H600" t="n">
         <v>1249089</v>
@@ -17798,7 +17798,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G601" t="n">
-        <v>1.82621645927429</v>
+        <v>1.82621657848358</v>
       </c>
       <c r="H601" t="n">
         <v>2208316</v>
@@ -17827,7 +17827,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>1.83576965332031</v>
+        <v>1.83576941490173</v>
       </c>
       <c r="H602" t="n">
         <v>981017</v>
@@ -17856,7 +17856,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G603" t="n">
-        <v>1.88353455066681</v>
+        <v>1.88353443145752</v>
       </c>
       <c r="H603" t="n">
         <v>2143576</v>
@@ -17885,7 +17885,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.8548755645752</v>
+        <v>1.85487544536591</v>
       </c>
       <c r="H604" t="n">
         <v>1300520</v>
@@ -17972,7 +17972,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.77526712417603</v>
+        <v>1.7752673625946</v>
       </c>
       <c r="H607" t="n">
         <v>1953879</v>
@@ -18059,7 +18059,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>1.81848669052124</v>
+        <v>1.81848704814911</v>
       </c>
       <c r="H610" t="n">
         <v>1189890</v>
@@ -18088,7 +18088,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G611" t="n">
-        <v>1.82174873352051</v>
+        <v>1.82174837589264</v>
       </c>
       <c r="H611" t="n">
         <v>639504</v>
@@ -18146,7 +18146,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>1.72878575325012</v>
+        <v>1.72878551483154</v>
       </c>
       <c r="H613" t="n">
         <v>2708744</v>
@@ -18204,7 +18204,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G615" t="n">
-        <v>1.72878575325012</v>
+        <v>1.72878551483154</v>
       </c>
       <c r="H615" t="n">
         <v>1733659</v>
@@ -18262,7 +18262,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G617" t="n">
-        <v>1.7858681678772</v>
+        <v>1.78586804866791</v>
       </c>
       <c r="H617" t="n">
         <v>2304857</v>
@@ -18291,7 +18291,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G618" t="n">
-        <v>1.7581422328949</v>
+        <v>1.75814235210419</v>
       </c>
       <c r="H618" t="n">
         <v>921766</v>
@@ -18320,7 +18320,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G619" t="n">
-        <v>1.76140439510345</v>
+        <v>1.76140415668488</v>
       </c>
       <c r="H619" t="n">
         <v>995750</v>
@@ -18378,7 +18378,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G621" t="n">
-        <v>1.76140439510345</v>
+        <v>1.76140415668488</v>
       </c>
       <c r="H621" t="n">
         <v>808647</v>
@@ -18407,7 +18407,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G622" t="n">
-        <v>1.7385710477829</v>
+        <v>1.73857128620148</v>
       </c>
       <c r="H622" t="n">
         <v>583631</v>
@@ -18436,7 +18436,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G623" t="n">
-        <v>1.76140439510345</v>
+        <v>1.76140415668488</v>
       </c>
       <c r="H623" t="n">
         <v>810246</v>
@@ -18465,7 +18465,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G624" t="n">
-        <v>1.76629686355591</v>
+        <v>1.7662969827652</v>
       </c>
       <c r="H624" t="n">
         <v>2399225</v>
@@ -18494,7 +18494,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G625" t="n">
-        <v>1.76629686355591</v>
+        <v>1.7662969827652</v>
       </c>
       <c r="H625" t="n">
         <v>566494</v>
@@ -18552,7 +18552,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>1.86741471290588</v>
+        <v>1.86741459369659</v>
       </c>
       <c r="H627" t="n">
         <v>2849945</v>
@@ -18639,7 +18639,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G630" t="n">
-        <v>1.82664155960083</v>
+        <v>1.82664132118225</v>
       </c>
       <c r="H630" t="n">
         <v>683361</v>
@@ -18668,7 +18668,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G631" t="n">
-        <v>1.76466619968414</v>
+        <v>1.76466631889343</v>
       </c>
       <c r="H631" t="n">
         <v>968829</v>
@@ -18697,7 +18697,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G632" t="n">
-        <v>1.79239177703857</v>
+        <v>1.79239201545715</v>
       </c>
       <c r="H632" t="n">
         <v>2137127</v>
@@ -18755,7 +18755,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G634" t="n">
-        <v>1.77282083034515</v>
+        <v>1.77282094955444</v>
       </c>
       <c r="H634" t="n">
         <v>471187</v>
@@ -18784,7 +18784,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G635" t="n">
-        <v>1.75161862373352</v>
+        <v>1.7516188621521</v>
       </c>
       <c r="H635" t="n">
         <v>794317</v>
@@ -18813,7 +18813,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G636" t="n">
-        <v>1.74346399307251</v>
+        <v>1.74346387386322</v>
       </c>
       <c r="H636" t="n">
         <v>489960</v>
@@ -18842,7 +18842,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G637" t="n">
-        <v>1.82011783123016</v>
+        <v>1.82011795043945</v>
       </c>
       <c r="H637" t="n">
         <v>2298555</v>
@@ -18929,7 +18929,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G640" t="n">
-        <v>1.81359398365021</v>
+        <v>1.8135941028595</v>
       </c>
       <c r="H640" t="n">
         <v>2559667</v>
@@ -18958,7 +18958,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G641" t="n">
-        <v>1.86578369140625</v>
+        <v>1.86578381061554</v>
       </c>
       <c r="H641" t="n">
         <v>1601256</v>
@@ -18987,7 +18987,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>1.87720012664795</v>
+        <v>1.87720000743866</v>
       </c>
       <c r="H642" t="n">
         <v>1729727</v>
@@ -19045,7 +19045,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G644" t="n">
-        <v>1.88372397422791</v>
+        <v>1.88372373580933</v>
       </c>
       <c r="H644" t="n">
         <v>1335295</v>
@@ -19103,7 +19103,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>1.86741471290588</v>
+        <v>1.86741459369659</v>
       </c>
       <c r="H646" t="n">
         <v>465309</v>
@@ -19132,7 +19132,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G647" t="n">
-        <v>1.82827246189117</v>
+        <v>1.82827234268188</v>
       </c>
       <c r="H647" t="n">
         <v>550682</v>
@@ -19161,7 +19161,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G648" t="n">
-        <v>1.81685566902161</v>
+        <v>1.8168557882309</v>
       </c>
       <c r="H648" t="n">
         <v>605104</v>
@@ -19190,7 +19190,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G649" t="n">
-        <v>1.81196296215057</v>
+        <v>1.81196284294128</v>
       </c>
       <c r="H649" t="n">
         <v>492569</v>
@@ -19219,7 +19219,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>1.81848669052124</v>
+        <v>1.81848704814911</v>
       </c>
       <c r="H650" t="n">
         <v>710538</v>
@@ -19248,7 +19248,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G651" t="n">
-        <v>1.79239177703857</v>
+        <v>1.79239201545715</v>
       </c>
       <c r="H651" t="n">
         <v>2071396</v>
@@ -19306,7 +19306,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G653" t="n">
-        <v>1.77282083034515</v>
+        <v>1.77282094955444</v>
       </c>
       <c r="H653" t="n">
         <v>747019</v>
@@ -19335,7 +19335,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78749907016754</v>
+        <v>1.78749918937683</v>
       </c>
       <c r="H654" t="n">
         <v>659037</v>
@@ -19364,7 +19364,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>1.75324964523315</v>
+        <v>1.75324952602386</v>
       </c>
       <c r="H655" t="n">
         <v>913367</v>
@@ -19393,7 +19393,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G656" t="n">
-        <v>1.7385710477829</v>
+        <v>1.73857128620148</v>
       </c>
       <c r="H656" t="n">
         <v>3598224</v>
@@ -19509,7 +19509,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G660" t="n">
-        <v>1.84131979942322</v>
+        <v>1.84131968021393</v>
       </c>
       <c r="H660" t="n">
         <v>617222</v>
@@ -19538,7 +19538,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G661" t="n">
-        <v>1.82337963581085</v>
+        <v>1.82337951660156</v>
       </c>
       <c r="H661" t="n">
         <v>839503</v>
@@ -19567,7 +19567,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G662" t="n">
-        <v>1.79239177703857</v>
+        <v>1.79239201545715</v>
       </c>
       <c r="H662" t="n">
         <v>897689</v>
@@ -19596,7 +19596,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G663" t="n">
-        <v>1.7907612323761</v>
+        <v>1.79076111316681</v>
       </c>
       <c r="H663" t="n">
         <v>561281</v>
@@ -19625,7 +19625,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G664" t="n">
-        <v>1.82011783123016</v>
+        <v>1.82011795043945</v>
       </c>
       <c r="H664" t="n">
         <v>676673</v>
@@ -19683,7 +19683,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G666" t="n">
-        <v>1.88046216964722</v>
+        <v>1.88046193122864</v>
       </c>
       <c r="H666" t="n">
         <v>845679</v>
@@ -19712,7 +19712,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G667" t="n">
-        <v>1.85925996303558</v>
+        <v>1.85926008224487</v>
       </c>
       <c r="H667" t="n">
         <v>963738</v>
@@ -19741,7 +19741,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G668" t="n">
-        <v>1.86415266990662</v>
+        <v>1.86415278911591</v>
       </c>
       <c r="H668" t="n">
         <v>885313</v>
@@ -19770,7 +19770,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G669" t="n">
-        <v>1.85762906074524</v>
+        <v>1.85762917995453</v>
       </c>
       <c r="H669" t="n">
         <v>854370</v>
@@ -19828,7 +19828,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G671" t="n">
-        <v>1.90818798542023</v>
+        <v>1.90818786621094</v>
       </c>
       <c r="H671" t="n">
         <v>1160035</v>
@@ -19857,7 +19857,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G672" t="n">
-        <v>2.00441265106201</v>
+        <v>2.00441241264343</v>
       </c>
       <c r="H672" t="n">
         <v>5364988</v>
@@ -19886,7 +19886,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G673" t="n">
-        <v>1.99136555194855</v>
+        <v>1.99136543273926</v>
       </c>
       <c r="H673" t="n">
         <v>853924</v>
@@ -19915,7 +19915,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G674" t="n">
-        <v>1.99136555194855</v>
+        <v>1.99136543273926</v>
       </c>
       <c r="H674" t="n">
         <v>854975</v>
@@ -20002,7 +20002,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G677" t="n">
-        <v>1.90329551696777</v>
+        <v>1.90329539775848</v>
       </c>
       <c r="H677" t="n">
         <v>1584415</v>
@@ -20031,7 +20031,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G678" t="n">
-        <v>1.89024782180786</v>
+        <v>1.89024758338928</v>
       </c>
       <c r="H678" t="n">
         <v>886735</v>
@@ -20060,7 +20060,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G679" t="n">
-        <v>1.86415266990662</v>
+        <v>1.86415278911591</v>
       </c>
       <c r="H679" t="n">
         <v>868801</v>
@@ -20089,7 +20089,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G680" t="n">
-        <v>1.81359398365021</v>
+        <v>1.8135941028595</v>
       </c>
       <c r="H680" t="n">
         <v>1115411</v>
@@ -20118,7 +20118,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71084570884705</v>
+        <v>1.71084558963776</v>
       </c>
       <c r="H681" t="n">
         <v>2819967</v>
@@ -20147,7 +20147,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G682" t="n">
-        <v>1.76466619968414</v>
+        <v>1.76466631889343</v>
       </c>
       <c r="H682" t="n">
         <v>4168427</v>
@@ -20205,7 +20205,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82337963581085</v>
+        <v>1.82337951660156</v>
       </c>
       <c r="H684" t="n">
         <v>2326497</v>
@@ -20234,7 +20234,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>1.82664155960083</v>
+        <v>1.82664132118225</v>
       </c>
       <c r="H685" t="n">
         <v>2020822</v>
@@ -20292,7 +20292,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G687" t="n">
-        <v>1.91471195220947</v>
+        <v>1.9147115945816</v>
       </c>
       <c r="H687" t="n">
         <v>1051261</v>
@@ -20321,7 +20321,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G688" t="n">
-        <v>1.90329551696777</v>
+        <v>1.90329539775848</v>
       </c>
       <c r="H688" t="n">
         <v>523293</v>
@@ -20379,7 +20379,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G690" t="n">
-        <v>1.89840233325958</v>
+        <v>1.89840245246887</v>
       </c>
       <c r="H690" t="n">
         <v>429766</v>
@@ -20408,7 +20408,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G691" t="n">
-        <v>1.86415266990662</v>
+        <v>1.86415278911591</v>
       </c>
       <c r="H691" t="n">
         <v>339281</v>
@@ -20437,7 +20437,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G692" t="n">
-        <v>1.88046216964722</v>
+        <v>1.88046193122864</v>
       </c>
       <c r="H692" t="n">
         <v>471227</v>
@@ -20495,7 +20495,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G694" t="n">
-        <v>1.81685566902161</v>
+        <v>1.8168557882309</v>
       </c>
       <c r="H694" t="n">
         <v>1394273</v>
@@ -20553,7 +20553,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>1.81359398365021</v>
+        <v>1.8135941028595</v>
       </c>
       <c r="H696" t="n">
         <v>998393</v>
@@ -20611,7 +20611,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G698" t="n">
-        <v>1.78749907016754</v>
+        <v>1.78749918937683</v>
       </c>
       <c r="H698" t="n">
         <v>796654</v>
@@ -20640,7 +20640,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G699" t="n">
-        <v>1.75324964523315</v>
+        <v>1.75324952602386</v>
       </c>
       <c r="H699" t="n">
         <v>1589594</v>
@@ -20669,7 +20669,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>1.75324964523315</v>
+        <v>1.75324952602386</v>
       </c>
       <c r="H700" t="n">
         <v>570256</v>
@@ -20698,7 +20698,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G701" t="n">
-        <v>1.73041653633118</v>
+        <v>1.73041641712189</v>
       </c>
       <c r="H701" t="n">
         <v>811499</v>
@@ -20727,7 +20727,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G702" t="n">
-        <v>1.70105981826782</v>
+        <v>1.70105969905853</v>
       </c>
       <c r="H702" t="n">
         <v>929920</v>
@@ -20756,7 +20756,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G703" t="n">
-        <v>1.62929892539978</v>
+        <v>1.62929904460907</v>
       </c>
       <c r="H703" t="n">
         <v>2772603</v>
@@ -20785,7 +20785,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G704" t="n">
-        <v>1.65050089359283</v>
+        <v>1.65050101280212</v>
       </c>
       <c r="H704" t="n">
         <v>2017014</v>
@@ -20872,7 +20872,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G707" t="n">
-        <v>1.58607923984528</v>
+        <v>1.58607912063599</v>
       </c>
       <c r="H707" t="n">
         <v>1261183</v>
@@ -20901,7 +20901,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G708" t="n">
-        <v>1.57384717464447</v>
+        <v>1.57384729385376</v>
       </c>
       <c r="H708" t="n">
         <v>980940</v>
@@ -20959,7 +20959,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G710" t="n">
-        <v>1.48169982433319</v>
+        <v>1.4816997051239</v>
       </c>
       <c r="H710" t="n">
         <v>2572970</v>
@@ -20988,7 +20988,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>1.48006880283356</v>
+        <v>1.48006892204285</v>
       </c>
       <c r="H711" t="n">
         <v>2169717</v>
@@ -21075,7 +21075,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.48822355270386</v>
+        <v>1.48822331428528</v>
       </c>
       <c r="H714" t="n">
         <v>3092187</v>
@@ -21191,7 +21191,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>1.45968210697174</v>
+        <v>1.45968234539032</v>
       </c>
       <c r="H718" t="n">
         <v>1383440</v>
@@ -21249,7 +21249,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>1.53388953208923</v>
+        <v>1.53388941287994</v>
       </c>
       <c r="H720" t="n">
         <v>1295036</v>
@@ -21278,7 +21278,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G721" t="n">
-        <v>1.53470492362976</v>
+        <v>1.53470504283905</v>
       </c>
       <c r="H721" t="n">
         <v>621201</v>
@@ -21307,7 +21307,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G722" t="n">
-        <v>1.60483503341675</v>
+        <v>1.60483491420746</v>
       </c>
       <c r="H722" t="n">
         <v>1425242</v>
@@ -21336,7 +21336,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G723" t="n">
-        <v>1.5787398815155</v>
+        <v>1.57874011993408</v>
       </c>
       <c r="H723" t="n">
         <v>621410</v>
@@ -21394,7 +21394,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G725" t="n">
-        <v>1.62032866477966</v>
+        <v>1.62032878398895</v>
       </c>
       <c r="H725" t="n">
         <v>678094</v>
@@ -21423,7 +21423,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G726" t="n">
-        <v>1.6341917514801</v>
+        <v>1.63419163227081</v>
       </c>
       <c r="H726" t="n">
         <v>1024698</v>
@@ -21452,7 +21452,7 @@
         <v>2</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092994689941</v>
+        <v>1.63092982769012</v>
       </c>
       <c r="H727" t="n">
         <v>594452</v>
@@ -21539,7 +21539,7 @@
         <v>2</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092994689941</v>
+        <v>1.63092982769012</v>
       </c>
       <c r="H730" t="n">
         <v>355011</v>
@@ -21568,7 +21568,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G731" t="n">
-        <v>1.61625158786774</v>
+        <v>1.61625134944916</v>
       </c>
       <c r="H731" t="n">
         <v>498536</v>
@@ -21626,7 +21626,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G733" t="n">
-        <v>1.51187205314636</v>
+        <v>1.51187193393707</v>
       </c>
       <c r="H733" t="n">
         <v>1759383</v>
@@ -21655,7 +21655,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G734" t="n">
-        <v>1.50453293323517</v>
+        <v>1.50453269481659</v>
       </c>
       <c r="H734" t="n">
         <v>1397140</v>
@@ -21742,7 +21742,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G737" t="n">
-        <v>1.5167647600174</v>
+        <v>1.51676487922668</v>
       </c>
       <c r="H737" t="n">
         <v>745389</v>
@@ -21800,7 +21800,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G739" t="n">
-        <v>1.44581925868988</v>
+        <v>1.44581937789917</v>
       </c>
       <c r="H739" t="n">
         <v>982774</v>
@@ -21858,7 +21858,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G741" t="n">
-        <v>1.47191417217255</v>
+        <v>1.47191429138184</v>
       </c>
       <c r="H741" t="n">
         <v>414540</v>
@@ -21887,7 +21887,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G742" t="n">
-        <v>1.51024103164673</v>
+        <v>1.51024091243744</v>
       </c>
       <c r="H742" t="n">
         <v>802068</v>
@@ -21916,7 +21916,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G743" t="n">
-        <v>1.5167647600174</v>
+        <v>1.51676487922668</v>
       </c>
       <c r="H743" t="n">
         <v>805198</v>
@@ -21945,7 +21945,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G744" t="n">
-        <v>1.50453293323517</v>
+        <v>1.50453269481659</v>
       </c>
       <c r="H744" t="n">
         <v>1047194</v>
@@ -22003,7 +22003,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>1.45152747631073</v>
+        <v>1.45152771472931</v>
       </c>
       <c r="H746" t="n">
         <v>1189559</v>
@@ -22177,7 +22177,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G752" t="n">
-        <v>1.36345744132996</v>
+        <v>1.36345732212067</v>
       </c>
       <c r="H752" t="n">
         <v>722243</v>
@@ -22206,7 +22206,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G753" t="n">
-        <v>1.36345744132996</v>
+        <v>1.36345732212067</v>
       </c>
       <c r="H753" t="n">
         <v>680677</v>
@@ -22235,7 +22235,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G754" t="n">
-        <v>1.3724273443222</v>
+        <v>1.37242746353149</v>
       </c>
       <c r="H754" t="n">
         <v>1083070</v>
@@ -22293,7 +22293,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G756" t="n">
-        <v>1.09272289276123</v>
+        <v>1.09272313117981</v>
       </c>
       <c r="H756" t="n">
         <v>13977981</v>
@@ -22351,7 +22351,7 @@
         <v>1.25</v>
       </c>
       <c r="G758" t="n">
-        <v>1.01933121681213</v>
+        <v>1.01933133602142</v>
       </c>
       <c r="H758" t="n">
         <v>3318339</v>
@@ -22409,7 +22409,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G760" t="n">
-        <v>1.03074765205383</v>
+        <v>1.03074777126312</v>
       </c>
       <c r="H760" t="n">
         <v>6151251</v>
@@ -22438,7 +22438,7 @@
         <v>1.32700002193451</v>
       </c>
       <c r="G761" t="n">
-        <v>1.08212184906006</v>
+        <v>1.08212196826935</v>
       </c>
       <c r="H761" t="n">
         <v>3813414</v>
@@ -22496,7 +22496,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G763" t="n">
-        <v>1.15469813346863</v>
+        <v>1.15469825267792</v>
       </c>
       <c r="H763" t="n">
         <v>2560889</v>
@@ -22525,7 +22525,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G764" t="n">
-        <v>1.15388286113739</v>
+        <v>1.1538827419281</v>
       </c>
       <c r="H764" t="n">
         <v>1226156</v>
@@ -22554,7 +22554,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G765" t="n">
-        <v>1.1742696762085</v>
+        <v>1.17426955699921</v>
       </c>
       <c r="H765" t="n">
         <v>2107430</v>
@@ -22583,7 +22583,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>1.1742696762085</v>
+        <v>1.17426955699921</v>
       </c>
       <c r="H766" t="n">
         <v>1555652</v>
@@ -22612,7 +22612,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G767" t="n">
-        <v>1.26478612422943</v>
+        <v>1.26478600502014</v>
       </c>
       <c r="H767" t="n">
         <v>2353519</v>
@@ -22641,7 +22641,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G768" t="n">
-        <v>1.27620267868042</v>
+        <v>1.27620255947113</v>
       </c>
       <c r="H768" t="n">
         <v>2602064</v>
@@ -22670,7 +22670,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G769" t="n">
-        <v>1.3022974729538</v>
+        <v>1.30229759216309</v>
       </c>
       <c r="H769" t="n">
         <v>1170678</v>
@@ -22699,7 +22699,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G770" t="n">
-        <v>1.35693371295929</v>
+        <v>1.35693383216858</v>
       </c>
       <c r="H770" t="n">
         <v>1347520</v>
@@ -22728,7 +22728,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G771" t="n">
-        <v>1.31208300590515</v>
+        <v>1.31208312511444</v>
       </c>
       <c r="H771" t="n">
         <v>1290857</v>
@@ -22757,7 +22757,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G772" t="n">
-        <v>1.3031131029129</v>
+        <v>1.30311298370361</v>
       </c>
       <c r="H772" t="n">
         <v>1651898</v>
@@ -22844,7 +22844,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G775" t="n">
-        <v>1.36019539833069</v>
+        <v>1.36019551753998</v>
       </c>
       <c r="H775" t="n">
         <v>1881833</v>
@@ -22960,7 +22960,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G779" t="n">
-        <v>1.33491611480713</v>
+        <v>1.33491599559784</v>
       </c>
       <c r="H779" t="n">
         <v>3214064</v>
@@ -23018,7 +23018,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G781" t="n">
-        <v>1.43521821498871</v>
+        <v>1.435218334198</v>
       </c>
       <c r="H781" t="n">
         <v>2217306</v>
@@ -23076,7 +23076,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G783" t="n">
-        <v>1.54693710803986</v>
+        <v>1.54693698883057</v>
       </c>
       <c r="H783" t="n">
         <v>2009197</v>
@@ -23105,7 +23105,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G784" t="n">
-        <v>1.58037090301514</v>
+        <v>1.58037102222443</v>
       </c>
       <c r="H784" t="n">
         <v>2580032</v>
@@ -23134,7 +23134,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G785" t="n">
-        <v>1.56569254398346</v>
+        <v>1.56569266319275</v>
       </c>
       <c r="H785" t="n">
         <v>2561988</v>
@@ -23221,7 +23221,7 @@
         <v>1.96300005912781</v>
       </c>
       <c r="G788" t="n">
-        <v>1.60075759887695</v>
+        <v>1.60075771808624</v>
       </c>
       <c r="H788" t="n">
         <v>1529047</v>
@@ -23250,7 +23250,7 @@
         <v>1.99199998378754</v>
       </c>
       <c r="G789" t="n">
-        <v>1.62440598011017</v>
+        <v>1.62440621852875</v>
       </c>
       <c r="H789" t="n">
         <v>3370317</v>
@@ -23279,7 +23279,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G790" t="n">
-        <v>1.61625158786774</v>
+        <v>1.61625134944916</v>
       </c>
       <c r="H790" t="n">
         <v>1851199</v>
@@ -23308,7 +23308,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G791" t="n">
-        <v>1.53878223896027</v>
+        <v>1.53878235816956</v>
       </c>
       <c r="H791" t="n">
         <v>937385</v>
@@ -23337,7 +23337,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G792" t="n">
-        <v>1.51839542388916</v>
+        <v>1.51839554309845</v>
       </c>
       <c r="H792" t="n">
         <v>1104048</v>
@@ -23366,7 +23366,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G793" t="n">
-        <v>1.53470492362976</v>
+        <v>1.53470504283905</v>
       </c>
       <c r="H793" t="n">
         <v>557746</v>
@@ -23482,7 +23482,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G797" t="n">
-        <v>1.66681015491486</v>
+        <v>1.66681027412415</v>
       </c>
       <c r="H797" t="n">
         <v>631363</v>
@@ -23598,7 +23598,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G801" t="n">
-        <v>1.65702486038208</v>
+        <v>1.65702474117279</v>
       </c>
       <c r="H801" t="n">
         <v>829278</v>
@@ -23627,7 +23627,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G802" t="n">
-        <v>1.6814888715744</v>
+        <v>1.68148875236511</v>
       </c>
       <c r="H802" t="n">
         <v>808567</v>
@@ -23656,7 +23656,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G803" t="n">
-        <v>1.70595252513885</v>
+        <v>1.70595264434814</v>
       </c>
       <c r="H803" t="n">
         <v>1273027</v>
@@ -23685,7 +23685,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G804" t="n">
-        <v>1.69453608989716</v>
+        <v>1.69453597068787</v>
       </c>
       <c r="H804" t="n">
         <v>415996</v>
@@ -23714,7 +23714,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G805" t="n">
-        <v>1.70921444892883</v>
+        <v>1.70921421051025</v>
       </c>
       <c r="H805" t="n">
         <v>511806</v>
@@ -23743,7 +23743,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G806" t="n">
-        <v>1.70269072055817</v>
+        <v>1.70269060134888</v>
       </c>
       <c r="H806" t="n">
         <v>871066</v>
@@ -23859,7 +23859,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G810" t="n">
-        <v>1.68964326381683</v>
+        <v>1.68964338302612</v>
       </c>
       <c r="H810" t="n">
         <v>653322</v>
@@ -24004,7 +24004,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G815" t="n">
-        <v>1.66681015491486</v>
+        <v>1.66681027412415</v>
       </c>
       <c r="H815" t="n">
         <v>693096</v>
@@ -24033,7 +24033,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G816" t="n">
-        <v>1.69290518760681</v>
+        <v>1.69290506839752</v>
       </c>
       <c r="H816" t="n">
         <v>1060991</v>
@@ -24091,7 +24091,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G818" t="n">
-        <v>1.63582265377045</v>
+        <v>1.63582253456116</v>
       </c>
       <c r="H818" t="n">
         <v>1354848</v>
@@ -24120,7 +24120,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G819" t="n">
-        <v>1.6023885011673</v>
+        <v>1.60238862037659</v>
       </c>
       <c r="H819" t="n">
         <v>996560</v>
@@ -24178,7 +24178,7 @@
         <v>1.97099995613098</v>
       </c>
       <c r="G821" t="n">
-        <v>1.60728144645691</v>
+        <v>1.60728120803833</v>
       </c>
       <c r="H821" t="n">
         <v>607512</v>
@@ -24207,7 +24207,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G822" t="n">
-        <v>1.60157322883606</v>
+        <v>1.60157299041748</v>
       </c>
       <c r="H822" t="n">
         <v>833731</v>
@@ -24236,7 +24236,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G823" t="n">
-        <v>1.67333388328552</v>
+        <v>1.6733341217041</v>
       </c>
       <c r="H823" t="n">
         <v>1131670</v>
@@ -24294,7 +24294,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G825" t="n">
-        <v>1.67496478557587</v>
+        <v>1.67496490478516</v>
       </c>
       <c r="H825" t="n">
         <v>666086</v>
@@ -24323,7 +24323,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G826" t="n">
-        <v>1.69127404689789</v>
+        <v>1.69127428531647</v>
       </c>
       <c r="H826" t="n">
         <v>1668598</v>
@@ -24352,7 +24352,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G827" t="n">
-        <v>1.70921444892883</v>
+        <v>1.70921421051025</v>
       </c>
       <c r="H827" t="n">
         <v>422823</v>
@@ -24381,7 +24381,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>1.6847505569458</v>
+        <v>1.68475067615509</v>
       </c>
       <c r="H828" t="n">
         <v>596412</v>
@@ -24468,7 +24468,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G831" t="n">
-        <v>1.88372397422791</v>
+        <v>1.88372373580933</v>
       </c>
       <c r="H831" t="n">
         <v>8604870</v>
@@ -24526,7 +24526,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G833" t="n">
-        <v>1.81196296215057</v>
+        <v>1.81196284294128</v>
       </c>
       <c r="H833" t="n">
         <v>2500836</v>
@@ -24555,7 +24555,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G834" t="n">
-        <v>1.78260636329651</v>
+        <v>1.7826064825058</v>
       </c>
       <c r="H834" t="n">
         <v>1213282</v>
@@ -24584,7 +24584,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G835" t="n">
-        <v>1.77771353721619</v>
+        <v>1.77771377563477</v>
       </c>
       <c r="H835" t="n">
         <v>401140</v>
@@ -24642,7 +24642,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>1.7858681678772</v>
+        <v>1.78586804866791</v>
       </c>
       <c r="H837" t="n">
         <v>450642</v>
@@ -24671,7 +24671,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G838" t="n">
-        <v>1.7858681678772</v>
+        <v>1.78586804866791</v>
       </c>
       <c r="H838" t="n">
         <v>377864</v>
@@ -24700,7 +24700,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G839" t="n">
-        <v>1.76140439510345</v>
+        <v>1.76140415668488</v>
       </c>
       <c r="H839" t="n">
         <v>472267</v>
@@ -24729,7 +24729,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G840" t="n">
-        <v>1.72063076496124</v>
+        <v>1.72063100337982</v>
       </c>
       <c r="H840" t="n">
         <v>770563</v>
@@ -24816,7 +24816,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G843" t="n">
-        <v>1.63908433914185</v>
+        <v>1.63908457756042</v>
       </c>
       <c r="H843" t="n">
         <v>1322486</v>
@@ -24845,7 +24845,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G844" t="n">
-        <v>1.55182981491089</v>
+        <v>1.5518296957016</v>
       </c>
       <c r="H844" t="n">
         <v>4032631</v>
@@ -24903,7 +24903,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G846" t="n">
-        <v>1.5167647600174</v>
+        <v>1.51676487922668</v>
       </c>
       <c r="H846" t="n">
         <v>2988966</v>
@@ -24932,7 +24932,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G847" t="n">
-        <v>1.5477522611618</v>
+        <v>1.54775249958038</v>
       </c>
       <c r="H847" t="n">
         <v>1669046</v>
@@ -24961,7 +24961,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G848" t="n">
-        <v>1.52328860759735</v>
+        <v>1.52328848838806</v>
       </c>
       <c r="H848" t="n">
         <v>1102200</v>
@@ -25019,7 +25019,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G850" t="n">
-        <v>1.43929553031921</v>
+        <v>1.4392956495285</v>
       </c>
       <c r="H850" t="n">
         <v>1026199</v>
@@ -25048,7 +25048,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G851" t="n">
-        <v>1.42543268203735</v>
+        <v>1.42543280124664</v>
       </c>
       <c r="H851" t="n">
         <v>880260</v>
@@ -25077,7 +25077,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G852" t="n">
-        <v>1.4083080291748</v>
+        <v>1.40830790996552</v>
       </c>
       <c r="H852" t="n">
         <v>1055190</v>
@@ -25106,7 +25106,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G853" t="n">
-        <v>1.39852225780487</v>
+        <v>1.39852249622345</v>
       </c>
       <c r="H853" t="n">
         <v>977323</v>
@@ -25135,7 +25135,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G854" t="n">
-        <v>1.39607608318329</v>
+        <v>1.396075963974</v>
       </c>
       <c r="H854" t="n">
         <v>1045489</v>
@@ -25193,7 +25193,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G856" t="n">
-        <v>1.36345744132996</v>
+        <v>1.36345732212067</v>
       </c>
       <c r="H856" t="n">
         <v>726614</v>
@@ -25222,7 +25222,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G857" t="n">
-        <v>1.40341520309448</v>
+        <v>1.40341508388519</v>
       </c>
       <c r="H857" t="n">
         <v>480477</v>
@@ -25280,7 +25280,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G859" t="n">
-        <v>1.38139760494232</v>
+        <v>1.38139748573303</v>
       </c>
       <c r="H859" t="n">
         <v>457572</v>
@@ -25309,7 +25309,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G860" t="n">
-        <v>1.4083080291748</v>
+        <v>1.40830790996552</v>
       </c>
       <c r="H860" t="n">
         <v>331863</v>
@@ -25367,7 +25367,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G862" t="n">
-        <v>1.35204076766968</v>
+        <v>1.35204088687897</v>
       </c>
       <c r="H862" t="n">
         <v>465276</v>
@@ -25396,7 +25396,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G863" t="n">
-        <v>1.38221311569214</v>
+        <v>1.38221299648285</v>
       </c>
       <c r="H863" t="n">
         <v>444989</v>
@@ -25425,7 +25425,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G864" t="n">
-        <v>1.41483151912689</v>
+        <v>1.41483163833618</v>
       </c>
       <c r="H864" t="n">
         <v>442927</v>
@@ -25483,7 +25483,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G866" t="n">
-        <v>1.37487363815308</v>
+        <v>1.37487375736237</v>
       </c>
       <c r="H866" t="n">
         <v>389202</v>
@@ -25686,7 +25686,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G873" t="n">
-        <v>1.47925341129303</v>
+        <v>1.47925329208374</v>
       </c>
       <c r="H873" t="n">
         <v>295354</v>
@@ -25744,7 +25744,7 @@
         <v>1.875</v>
       </c>
       <c r="G875" t="n">
-        <v>1.5289968252182</v>
+        <v>1.52899670600891</v>
       </c>
       <c r="H875" t="n">
         <v>341943</v>
@@ -25773,7 +25773,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G876" t="n">
-        <v>1.51268744468689</v>
+        <v>1.5126873254776</v>
       </c>
       <c r="H876" t="n">
         <v>459318</v>
@@ -25802,7 +25802,7 @@
         <v>1.875</v>
       </c>
       <c r="G877" t="n">
-        <v>1.5289968252182</v>
+        <v>1.52899670600891</v>
       </c>
       <c r="H877" t="n">
         <v>428422</v>
@@ -25976,7 +25976,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G883" t="n">
-        <v>1.45152747631073</v>
+        <v>1.45152771472931</v>
       </c>
       <c r="H883" t="n">
         <v>362785</v>
@@ -26005,7 +26005,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G884" t="n">
-        <v>1.42869448661804</v>
+        <v>1.42869460582733</v>
       </c>
       <c r="H884" t="n">
         <v>364330</v>
@@ -26092,7 +26092,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G887" t="n">
-        <v>1.43032538890839</v>
+        <v>1.43032550811768</v>
       </c>
       <c r="H887" t="n">
         <v>746913</v>
@@ -26121,7 +26121,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G888" t="n">
-        <v>1.44581925868988</v>
+        <v>1.44581937789917</v>
       </c>
       <c r="H888" t="n">
         <v>386625</v>
@@ -26179,7 +26179,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G890" t="n">
-        <v>1.46865224838257</v>
+        <v>1.46865212917328</v>
       </c>
       <c r="H890" t="n">
         <v>251671</v>
@@ -26237,7 +26237,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G892" t="n">
-        <v>1.58689475059509</v>
+        <v>1.5868946313858</v>
       </c>
       <c r="H892" t="n">
         <v>2742260</v>
@@ -26266,7 +26266,7 @@
         <v>1.89900004863739</v>
       </c>
       <c r="G893" t="n">
-        <v>1.5485680103302</v>
+        <v>1.54856789112091</v>
       </c>
       <c r="H893" t="n">
         <v>1852050</v>
@@ -26295,7 +26295,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G894" t="n">
-        <v>1.57058548927307</v>
+        <v>1.57058537006378</v>
       </c>
       <c r="H894" t="n">
         <v>1453003</v>
@@ -26324,7 +26324,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G895" t="n">
-        <v>1.50290191173553</v>
+        <v>1.50290179252625</v>
       </c>
       <c r="H895" t="n">
         <v>1736792</v>
@@ -26353,7 +26353,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G896" t="n">
-        <v>1.5167647600174</v>
+        <v>1.51676487922668</v>
       </c>
       <c r="H896" t="n">
         <v>516545</v>
@@ -26440,7 +26440,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.43521821498871</v>
+        <v>1.435218334198</v>
       </c>
       <c r="H899" t="n">
         <v>1456465</v>
@@ -26527,7 +26527,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G902" t="n">
-        <v>1.2558159828186</v>
+        <v>1.25581586360931</v>
       </c>
       <c r="H902" t="n">
         <v>4703086</v>
@@ -26556,7 +26556,7 @@
         <v>1.51300001144409</v>
       </c>
       <c r="G903" t="n">
-        <v>1.23379850387573</v>
+        <v>1.23379838466644</v>
       </c>
       <c r="H903" t="n">
         <v>1637956</v>
@@ -26614,7 +26614,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G905" t="n">
-        <v>1.27049446105957</v>
+        <v>1.27049434185028</v>
       </c>
       <c r="H905" t="n">
         <v>1458633</v>
@@ -26672,7 +26672,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G907" t="n">
-        <v>1.37732040882111</v>
+        <v>1.37732028961182</v>
       </c>
       <c r="H907" t="n">
         <v>2492653</v>
@@ -26701,7 +26701,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G908" t="n">
-        <v>1.35367166996002</v>
+        <v>1.35367178916931</v>
       </c>
       <c r="H908" t="n">
         <v>1043256</v>
@@ -26730,7 +26730,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G909" t="n">
-        <v>1.36182630062103</v>
+        <v>1.36182653903961</v>
       </c>
       <c r="H909" t="n">
         <v>619098</v>
@@ -26846,7 +26846,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G913" t="n">
-        <v>1.50045549869537</v>
+        <v>1.50045561790466</v>
       </c>
       <c r="H913" t="n">
         <v>1415328</v>
@@ -26904,7 +26904,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G915" t="n">
-        <v>1.51024103164673</v>
+        <v>1.51024091243744</v>
       </c>
       <c r="H915" t="n">
         <v>2409241</v>
@@ -26962,7 +26962,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G917" t="n">
-        <v>1.55753815174103</v>
+        <v>1.55753803253174</v>
       </c>
       <c r="H917" t="n">
         <v>1214649</v>
@@ -26991,7 +26991,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G918" t="n">
-        <v>1.48251521587372</v>
+        <v>1.48251509666443</v>
       </c>
       <c r="H918" t="n">
         <v>1320240</v>
@@ -27078,7 +27078,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G921" t="n">
-        <v>1.40341520309448</v>
+        <v>1.40341508388519</v>
       </c>
       <c r="H921" t="n">
         <v>457312</v>
@@ -27107,7 +27107,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G922" t="n">
-        <v>1.39933788776398</v>
+        <v>1.39933776855469</v>
       </c>
       <c r="H922" t="n">
         <v>482861</v>
@@ -27136,7 +27136,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G923" t="n">
-        <v>1.45968210697174</v>
+        <v>1.45968234539032</v>
       </c>
       <c r="H923" t="n">
         <v>650528</v>
@@ -27165,7 +27165,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G924" t="n">
-        <v>1.44092655181885</v>
+        <v>1.44092643260956</v>
       </c>
       <c r="H924" t="n">
         <v>445435</v>
@@ -27281,7 +27281,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G928" t="n">
-        <v>1.39933788776398</v>
+        <v>1.39933776855469</v>
       </c>
       <c r="H928" t="n">
         <v>1082932</v>
@@ -27310,7 +27310,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G929" t="n">
-        <v>1.43277180194855</v>
+        <v>1.43277192115784</v>
       </c>
       <c r="H929" t="n">
         <v>844650</v>
@@ -27339,7 +27339,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G930" t="n">
-        <v>1.46539044380188</v>
+        <v>1.46539056301117</v>
       </c>
       <c r="H930" t="n">
         <v>521674</v>
@@ -27397,7 +27397,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G932" t="n">
-        <v>1.44255745410919</v>
+        <v>1.4425573348999</v>
       </c>
       <c r="H932" t="n">
         <v>480648</v>
@@ -27426,7 +27426,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G933" t="n">
-        <v>1.46865224838257</v>
+        <v>1.46865212917328</v>
       </c>
       <c r="H933" t="n">
         <v>252434</v>
@@ -27484,7 +27484,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G935" t="n">
-        <v>1.45152747631073</v>
+        <v>1.45152771472931</v>
       </c>
       <c r="H935" t="n">
         <v>676456</v>
@@ -27513,7 +27513,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.45152747631073</v>
+        <v>1.45152771472931</v>
       </c>
       <c r="H936" t="n">
         <v>484220</v>
@@ -27716,7 +27716,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.67170298099518</v>
+        <v>1.67170310020447</v>
       </c>
       <c r="H943" t="n">
         <v>2434409</v>
@@ -27774,7 +27774,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G945" t="n">
-        <v>1.73041653633118</v>
+        <v>1.73041641712189</v>
       </c>
       <c r="H945" t="n">
         <v>2501849</v>
@@ -27832,7 +27832,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G947" t="n">
-        <v>1.6651793718338</v>
+        <v>1.66517961025238</v>
       </c>
       <c r="H947" t="n">
         <v>727311</v>
@@ -27861,7 +27861,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G948" t="n">
-        <v>1.65050089359283</v>
+        <v>1.65050101280212</v>
       </c>
       <c r="H948" t="n">
         <v>447219</v>
@@ -27890,7 +27890,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G949" t="n">
-        <v>1.6814888715744</v>
+        <v>1.68148875236511</v>
       </c>
       <c r="H949" t="n">
         <v>561915</v>
@@ -27919,7 +27919,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G950" t="n">
-        <v>1.65702486038208</v>
+        <v>1.65702474117279</v>
       </c>
       <c r="H950" t="n">
         <v>604544</v>
@@ -27948,7 +27948,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G951" t="n">
-        <v>1.67496478557587</v>
+        <v>1.67496490478516</v>
       </c>
       <c r="H951" t="n">
         <v>449178</v>
@@ -28006,7 +28006,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G953" t="n">
-        <v>1.63256084918976</v>
+        <v>1.63256072998047</v>
       </c>
       <c r="H953" t="n">
         <v>297419</v>
@@ -28151,7 +28151,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G958" t="n">
-        <v>1.57058548927307</v>
+        <v>1.57058537006378</v>
       </c>
       <c r="H958" t="n">
         <v>358093</v>
@@ -28209,7 +28209,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G960" t="n">
-        <v>1.51350295543671</v>
+        <v>1.51350283622742</v>
       </c>
       <c r="H960" t="n">
         <v>1017531</v>
@@ -28267,7 +28267,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G962" t="n">
-        <v>1.55753815174103</v>
+        <v>1.55753803253174</v>
       </c>
       <c r="H962" t="n">
         <v>432157</v>
@@ -28325,7 +28325,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G964" t="n">
-        <v>1.55019891262054</v>
+        <v>1.55019879341125</v>
       </c>
       <c r="H964" t="n">
         <v>472301</v>
@@ -28354,7 +28354,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>1.56161534786224</v>
+        <v>1.56161546707153</v>
       </c>
       <c r="H965" t="n">
         <v>523670</v>
@@ -28412,7 +28412,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G967" t="n">
-        <v>1.53878223896027</v>
+        <v>1.53878235816956</v>
       </c>
       <c r="H967" t="n">
         <v>338780</v>
@@ -28441,7 +28441,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G968" t="n">
-        <v>1.54938328266144</v>
+        <v>1.54938340187073</v>
       </c>
       <c r="H968" t="n">
         <v>929523</v>
@@ -28470,7 +28470,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G969" t="n">
-        <v>1.61135852336884</v>
+        <v>1.61135864257812</v>
       </c>
       <c r="H969" t="n">
         <v>2221457</v>
@@ -28528,7 +28528,7 @@
         <v>1.875</v>
       </c>
       <c r="G971" t="n">
-        <v>1.5289968252182</v>
+        <v>1.52899670600891</v>
       </c>
       <c r="H971" t="n">
         <v>1073312</v>
@@ -28586,7 +28586,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G973" t="n">
-        <v>1.49311625957489</v>
+        <v>1.49311637878418</v>
       </c>
       <c r="H973" t="n">
         <v>788984</v>
@@ -28644,7 +28644,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G975" t="n">
-        <v>1.48740792274475</v>
+        <v>1.48740804195404</v>
       </c>
       <c r="H975" t="n">
         <v>965861</v>
@@ -28673,7 +28673,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G976" t="n">
-        <v>1.48903894424438</v>
+        <v>1.4890388250351</v>
       </c>
       <c r="H976" t="n">
         <v>660748</v>
@@ -28760,7 +28760,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G979" t="n">
-        <v>1.45968210697174</v>
+        <v>1.45968234539032</v>
       </c>
       <c r="H979" t="n">
         <v>1897039</v>
@@ -28789,7 +28789,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>1.45968210697174</v>
+        <v>1.45968234539032</v>
       </c>
       <c r="H980" t="n">
         <v>899353</v>
@@ -28818,7 +28818,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G981" t="n">
-        <v>1.42053997516632</v>
+        <v>1.42053985595703</v>
       </c>
       <c r="H981" t="n">
         <v>7154588</v>
@@ -28847,7 +28847,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G982" t="n">
-        <v>1.37324297428131</v>
+        <v>1.37324285507202</v>
       </c>
       <c r="H982" t="n">
         <v>21650203</v>
@@ -28876,7 +28876,7 @@
         <v>1.77199995517731</v>
       </c>
       <c r="G983" t="n">
-        <v>1.44500374794006</v>
+        <v>1.44500386714935</v>
       </c>
       <c r="H983" t="n">
         <v>15004698</v>
@@ -28934,7 +28934,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G985" t="n">
-        <v>1.49556255340576</v>
+        <v>1.49556267261505</v>
       </c>
       <c r="H985" t="n">
         <v>8238334</v>
@@ -28963,7 +28963,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G986" t="n">
-        <v>1.48414623737335</v>
+        <v>1.48414599895477</v>
       </c>
       <c r="H986" t="n">
         <v>3078600</v>
@@ -29021,7 +29021,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G988" t="n">
-        <v>1.44092655181885</v>
+        <v>1.44092643260956</v>
       </c>
       <c r="H988" t="n">
         <v>1635432</v>
@@ -29050,7 +29050,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G989" t="n">
-        <v>1.41320073604584</v>
+        <v>1.41320085525513</v>
       </c>
       <c r="H989" t="n">
         <v>2882134</v>
@@ -29108,7 +29108,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.38221311569214</v>
+        <v>1.38221299648285</v>
       </c>
       <c r="H991" t="n">
         <v>1472350</v>
@@ -29166,7 +29166,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G993" t="n">
-        <v>1.4311408996582</v>
+        <v>1.43114101886749</v>
       </c>
       <c r="H993" t="n">
         <v>4664408</v>
@@ -29195,7 +29195,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G994" t="n">
-        <v>1.43277180194855</v>
+        <v>1.43277192115784</v>
       </c>
       <c r="H994" t="n">
         <v>3291327</v>
@@ -29253,7 +29253,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G996" t="n">
-        <v>1.44174206256866</v>
+        <v>1.44174194335938</v>
       </c>
       <c r="H996" t="n">
         <v>1816638</v>
@@ -29311,7 +29311,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>1.39444518089294</v>
+        <v>1.39444506168365</v>
       </c>
       <c r="H998" t="n">
         <v>2423018</v>
@@ -29340,7 +29340,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G999" t="n">
-        <v>1.38465940952301</v>
+        <v>1.38465929031372</v>
       </c>
       <c r="H999" t="n">
         <v>1961726</v>
@@ -29369,7 +29369,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.41483151912689</v>
+        <v>1.41483163833618</v>
       </c>
       <c r="H1000" t="n">
         <v>2449613</v>
@@ -29398,7 +29398,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.39607608318329</v>
+        <v>1.396075963974</v>
       </c>
       <c r="H1001" t="n">
         <v>888809</v>
@@ -29514,7 +29514,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.37487363815308</v>
+        <v>1.37487375736237</v>
       </c>
       <c r="H1005" t="n">
         <v>1982853</v>
@@ -29543,7 +29543,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.37161207199097</v>
+        <v>1.37161195278168</v>
       </c>
       <c r="H1006" t="n">
         <v>1637952</v>
@@ -29572,7 +29572,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.34633255004883</v>
+        <v>1.34633278846741</v>
       </c>
       <c r="H1007" t="n">
         <v>2611930</v>
@@ -29601,7 +29601,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.37487363815308</v>
+        <v>1.37487375736237</v>
       </c>
       <c r="H1008" t="n">
         <v>2577287</v>
@@ -29630,7 +29630,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.36182630062103</v>
+        <v>1.36182653903961</v>
       </c>
       <c r="H1009" t="n">
         <v>1464133</v>
@@ -29659,7 +29659,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.34470164775848</v>
+        <v>1.34470176696777</v>
       </c>
       <c r="H1010" t="n">
         <v>1693548</v>
@@ -29688,7 +29688,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.33573150634766</v>
+        <v>1.33573162555695</v>
       </c>
       <c r="H1011" t="n">
         <v>1741918</v>
@@ -29775,7 +29775,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.32268404960632</v>
+        <v>1.32268416881561</v>
       </c>
       <c r="H1014" t="n">
         <v>1216109</v>
@@ -29804,7 +29804,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.30882132053375</v>
+        <v>1.30882120132446</v>
       </c>
       <c r="H1015" t="n">
         <v>1336030</v>
@@ -29833,7 +29833,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.34796345233917</v>
+        <v>1.34796357154846</v>
       </c>
       <c r="H1016" t="n">
         <v>1488754</v>
@@ -29862,7 +29862,7 @@
         <v>1.61699998378754</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.31860685348511</v>
+        <v>1.31860673427582</v>
       </c>
       <c r="H1017" t="n">
         <v>3637322</v>
@@ -29949,7 +29949,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.3022974729538</v>
+        <v>1.30229759216309</v>
       </c>
       <c r="H1020" t="n">
         <v>1207943</v>
@@ -30007,7 +30007,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.32268404960632</v>
+        <v>1.32268416881561</v>
       </c>
       <c r="H1022" t="n">
         <v>1384826</v>
@@ -30036,7 +30036,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.33817791938782</v>
+        <v>1.33817803859711</v>
       </c>
       <c r="H1023" t="n">
         <v>1463844</v>
@@ -30239,7 +30239,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.26397049427032</v>
+        <v>1.26397061347961</v>
       </c>
       <c r="H1030" t="n">
         <v>1941692</v>
@@ -30268,7 +30268,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.24521481990814</v>
+        <v>1.24521493911743</v>
       </c>
       <c r="H1031" t="n">
         <v>4013072</v>
@@ -30297,7 +30297,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.27212524414062</v>
+        <v>1.27212512493134</v>
       </c>
       <c r="H1032" t="n">
         <v>2267819</v>
@@ -30355,7 +30355,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.26397049427032</v>
+        <v>1.26397061347961</v>
       </c>
       <c r="H1034" t="n">
         <v>1698992</v>
@@ -30384,7 +30384,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.2558159828186</v>
+        <v>1.25581586360931</v>
       </c>
       <c r="H1035" t="n">
         <v>1254623</v>
@@ -30413,7 +30413,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.22075092792511</v>
+        <v>1.2207510471344</v>
       </c>
       <c r="H1036" t="n">
         <v>2935812</v>
@@ -30442,7 +30442,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.1930251121521</v>
+        <v>1.19302523136139</v>
       </c>
       <c r="H1037" t="n">
         <v>2136222</v>
@@ -30471,7 +30471,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.17834687232971</v>
+        <v>1.178346991539</v>
       </c>
       <c r="H1038" t="n">
         <v>2286641</v>
@@ -30500,7 +30500,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.1930251121521</v>
+        <v>1.19302523136139</v>
       </c>
       <c r="H1039" t="n">
         <v>1987577</v>
@@ -30529,7 +30529,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.21993565559387</v>
+        <v>1.21993553638458</v>
       </c>
       <c r="H1040" t="n">
         <v>2375077</v>
@@ -30616,7 +30616,7 @@
         <v>1.442999958992</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.17671573162079</v>
+        <v>1.17671585083008</v>
       </c>
       <c r="H1043" t="n">
         <v>1518662</v>
@@ -30645,7 +30645,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.2125962972641</v>
+        <v>1.21259641647339</v>
       </c>
       <c r="H1044" t="n">
         <v>2340167</v>
@@ -30703,7 +30703,7 @@
         <v>1.47699999809265</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.20444166660309</v>
+        <v>1.20444178581238</v>
       </c>
       <c r="H1046" t="n">
         <v>1754486</v>
@@ -30732,7 +30732,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.20851898193359</v>
+        <v>1.20851910114288</v>
       </c>
       <c r="H1047" t="n">
         <v>1310560</v>
@@ -30761,7 +30761,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.21830463409424</v>
+        <v>1.21830475330353</v>
       </c>
       <c r="H1048" t="n">
         <v>1782186</v>
@@ -30790,7 +30790,7 @@
         <v>1.47699999809265</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.20444166660309</v>
+        <v>1.20444178581238</v>
       </c>
       <c r="H1049" t="n">
         <v>1633487</v>
@@ -30819,7 +30819,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.2125962972641</v>
+        <v>1.21259641647339</v>
       </c>
       <c r="H1050" t="n">
         <v>1442692</v>
@@ -30935,7 +30935,7 @@
         <v>1.38399994373322</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.12860357761383</v>
+        <v>1.12860345840454</v>
       </c>
       <c r="H1054" t="n">
         <v>4617523</v>
@@ -31167,7 +31167,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.920659899711609</v>
+        <v>0.920659840106964</v>
       </c>
       <c r="H1062" t="n">
         <v>4436272</v>
@@ -31254,7 +31254,7 @@
         <v>0.922500014305115</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.752266466617584</v>
+        <v>0.752266347408295</v>
       </c>
       <c r="H1065" t="n">
         <v>5103415</v>
@@ -31283,7 +31283,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.564301788806915</v>
+        <v>0.564301729202271</v>
       </c>
       <c r="H1066" t="n">
         <v>9939899</v>
@@ -31312,7 +31312,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.588357865810394</v>
+        <v>0.588357925415039</v>
       </c>
       <c r="H1067" t="n">
         <v>5899770</v>
@@ -31370,7 +31370,7 @@
         <v>0.738499999046326</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.602220833301544</v>
+        <v>0.602220892906189</v>
       </c>
       <c r="H1069" t="n">
         <v>4334484</v>
@@ -31399,7 +31399,7 @@
         <v>0.802500009536743</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.654410660266876</v>
+        <v>0.654410600662231</v>
       </c>
       <c r="H1070" t="n">
         <v>2568797</v>
@@ -31428,7 +31428,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.78284627199173</v>
+        <v>0.782846331596375</v>
       </c>
       <c r="H1071" t="n">
         <v>4009260</v>
@@ -31515,7 +31515,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.02259302139282</v>
+        <v>1.02259290218353</v>
       </c>
       <c r="H1074" t="n">
         <v>3835933</v>
@@ -31602,7 +31602,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.870916604995728</v>
+        <v>0.870916545391083</v>
       </c>
       <c r="H1077" t="n">
         <v>1971172</v>
@@ -31631,7 +31631,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.913320779800415</v>
+        <v>0.913320660591125</v>
       </c>
       <c r="H1078" t="n">
         <v>1366165</v>
@@ -31660,7 +31660,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.95083212852478</v>
+        <v>0.950832068920135</v>
       </c>
       <c r="H1079" t="n">
         <v>2082037</v>
@@ -31718,7 +31718,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.949201166629791</v>
+        <v>0.949201226234436</v>
       </c>
       <c r="H1081" t="n">
         <v>929547</v>
@@ -31747,7 +31747,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.951647758483887</v>
+        <v>0.951647698879242</v>
       </c>
       <c r="H1082" t="n">
         <v>443405</v>
@@ -31776,7 +31776,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.96061772108078</v>
+        <v>0.960617542266846</v>
       </c>
       <c r="H1083" t="n">
         <v>863388</v>
@@ -31805,7 +31805,7 @@
         <v>1.12800002098083</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.919844448566437</v>
+        <v>0.919844567775726</v>
       </c>
       <c r="H1084" t="n">
         <v>3047345</v>
@@ -31892,7 +31892,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.0527651309967</v>
+        <v>1.05276525020599</v>
       </c>
       <c r="H1087" t="n">
         <v>4106371</v>
@@ -31921,7 +31921,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.998128950595856</v>
+        <v>0.998129069805145</v>
       </c>
       <c r="H1088" t="n">
         <v>2104508</v>
@@ -31950,7 +31950,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.02014660835266</v>
+        <v>1.02014672756195</v>
       </c>
       <c r="H1089" t="n">
         <v>1696933</v>
@@ -32037,7 +32037,7 @@
         <v>1.33899998664856</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.09190762042999</v>
+        <v>1.0919075012207</v>
       </c>
       <c r="H1092" t="n">
         <v>1156803</v>
@@ -32095,7 +32095,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.08864593505859</v>
+        <v>1.08864569664001</v>
       </c>
       <c r="H1094" t="n">
         <v>648171</v>
@@ -32124,7 +32124,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.08783006668091</v>
+        <v>1.0878301858902</v>
       </c>
       <c r="H1095" t="n">
         <v>841392</v>
@@ -32182,7 +32182,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.09924685955048</v>
+        <v>1.09924674034119</v>
       </c>
       <c r="H1097" t="n">
         <v>2452809</v>
@@ -32211,7 +32211,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.11310958862305</v>
+        <v>1.11310970783234</v>
       </c>
       <c r="H1098" t="n">
         <v>2249016</v>
@@ -32269,7 +32269,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.09272289276123</v>
+        <v>1.09272313117981</v>
       </c>
       <c r="H1100" t="n">
         <v>1093846</v>
@@ -32298,7 +32298,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.08783006668091</v>
+        <v>1.0878301858902</v>
       </c>
       <c r="H1101" t="n">
         <v>1883969</v>
@@ -32327,7 +32327,7 @@
         <v>1.34899997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.10006201267242</v>
+        <v>1.100062251091</v>
       </c>
       <c r="H1102" t="n">
         <v>427120</v>
@@ -32472,7 +32472,7 @@
         <v>1.307000041008</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.06581270694733</v>
+        <v>1.06581258773804</v>
       </c>
       <c r="H1107" t="n">
         <v>548797</v>
@@ -32530,7 +32530,7 @@
         <v>1.26900005340576</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.03482496738434</v>
+        <v>1.03482508659363</v>
       </c>
       <c r="H1109" t="n">
         <v>390613</v>
@@ -32559,7 +32559,7 @@
         <v>1.26300001144409</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.05487012863159</v>
+        <v>1.0548700094223</v>
       </c>
       <c r="H1110" t="n">
         <v>531961</v>
@@ -32588,7 +32588,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.979701101779938</v>
+        <v>0.979701042175293</v>
       </c>
       <c r="H1111" t="n">
         <v>3876340</v>
@@ -32617,7 +32617,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.988888442516327</v>
+        <v>0.988888502120972</v>
       </c>
       <c r="H1112" t="n">
         <v>1956180</v>
@@ -32646,7 +32646,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.991394102573395</v>
+        <v>0.991393983364105</v>
       </c>
       <c r="H1113" t="n">
         <v>885134</v>
@@ -32675,7 +32675,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.02563762664795</v>
+        <v>1.02563774585724</v>
       </c>
       <c r="H1114" t="n">
         <v>1582972</v>
@@ -32704,7 +32704,7 @@
         <v>1.25</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.04401230812073</v>
+        <v>1.04401242733002</v>
       </c>
       <c r="H1115" t="n">
         <v>711035</v>
@@ -32733,7 +32733,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.05737555027008</v>
+        <v>1.05737566947937</v>
       </c>
       <c r="H1116" t="n">
         <v>1440577</v>
@@ -32791,7 +32791,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.04484748840332</v>
+        <v>1.04484760761261</v>
       </c>
       <c r="H1118" t="n">
         <v>714319</v>
@@ -32965,7 +32965,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.18766844272614</v>
+        <v>1.18766832351685</v>
       </c>
       <c r="H1124" t="n">
         <v>2988228</v>
@@ -33023,7 +33023,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.20103168487549</v>
+        <v>1.2010315656662</v>
       </c>
       <c r="H1126" t="n">
         <v>2927344</v>
@@ -33052,7 +33052,7 @@
         <v>1.40100002288818</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.17012894153595</v>
+        <v>1.17012906074524</v>
       </c>
       <c r="H1127" t="n">
         <v>1771983</v>
@@ -33139,7 +33139,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.11082899570465</v>
+        <v>1.11082923412323</v>
       </c>
       <c r="H1130" t="n">
         <v>1128829</v>
@@ -33197,7 +33197,7 @@
         <v>1.44700002670288</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.20854866504669</v>
+        <v>1.2085485458374</v>
       </c>
       <c r="H1132" t="n">
         <v>2622105</v>
@@ -33226,7 +33226,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.24028646945953</v>
+        <v>1.24028658866882</v>
       </c>
       <c r="H1133" t="n">
         <v>2907813</v>
@@ -33313,7 +33313,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.21439516544342</v>
+        <v>1.21439492702484</v>
       </c>
       <c r="H1136" t="n">
         <v>1385149</v>
@@ -33371,7 +33371,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.17764568328857</v>
+        <v>1.17764592170715</v>
       </c>
       <c r="H1138" t="n">
         <v>954584</v>
@@ -33458,7 +33458,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.1651177406311</v>
+        <v>1.16511762142181</v>
       </c>
       <c r="H1141" t="n">
         <v>1238514</v>
@@ -33487,7 +33487,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.14006125926971</v>
+        <v>1.140061378479</v>
       </c>
       <c r="H1142" t="n">
         <v>810784</v>
@@ -33545,7 +33545,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.16428256034851</v>
+        <v>1.1642826795578</v>
       </c>
       <c r="H1144" t="n">
         <v>659890</v>
@@ -33603,7 +33603,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.19434988498688</v>
+        <v>1.19435000419617</v>
       </c>
       <c r="H1146" t="n">
         <v>662446</v>
@@ -33632,7 +33632,7 @@
         <v>1.47599995136261</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.23276960849762</v>
+        <v>1.23276948928833</v>
       </c>
       <c r="H1147" t="n">
         <v>2452614</v>
@@ -33661,7 +33661,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.19852602481842</v>
+        <v>1.19852614402771</v>
       </c>
       <c r="H1148" t="n">
         <v>8763913</v>
@@ -33748,7 +33748,7 @@
         <v>1.42900002002716</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.19351494312286</v>
+        <v>1.19351470470428</v>
       </c>
       <c r="H1151" t="n">
         <v>2176067</v>
@@ -33777,7 +33777,7 @@
         <v>1.45299994945526</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.21355974674225</v>
+        <v>1.21355986595154</v>
       </c>
       <c r="H1152" t="n">
         <v>3560690</v>
@@ -33806,7 +33806,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.19434988498688</v>
+        <v>1.19435000419617</v>
       </c>
       <c r="H1153" t="n">
         <v>2312871</v>
@@ -33835,7 +33835,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.20103168487549</v>
+        <v>1.2010315656662</v>
       </c>
       <c r="H1154" t="n">
         <v>1543751</v>
@@ -33951,7 +33951,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.19602060317993</v>
+        <v>1.19602036476135</v>
       </c>
       <c r="H1158" t="n">
         <v>1169455</v>
@@ -33980,7 +33980,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.16177690029144</v>
+        <v>1.16177678108215</v>
       </c>
       <c r="H1159" t="n">
         <v>1134501</v>
@@ -34009,7 +34009,7 @@
         <v>1.32299995422363</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.10498237609863</v>
+        <v>1.10498249530792</v>
       </c>
       <c r="H1160" t="n">
         <v>2253150</v>
@@ -34067,7 +34067,7 @@
         <v>1.28100001811981</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.06990385055542</v>
+        <v>1.06990361213684</v>
       </c>
       <c r="H1162" t="n">
         <v>1647900</v>
@@ -34096,7 +34096,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.970513641834259</v>
+        <v>0.970513761043549</v>
       </c>
       <c r="H1163" t="n">
         <v>4861508</v>
@@ -34183,7 +34183,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.935435116291046</v>
+        <v>0.935434937477112</v>
       </c>
       <c r="H1166" t="n">
         <v>3217787</v>
@@ -34212,7 +34212,7 @@
         <v>1.09899997711182</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.917895495891571</v>
+        <v>0.917895615100861</v>
       </c>
       <c r="H1167" t="n">
         <v>2532403</v>
@@ -34299,7 +34299,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.918730795383453</v>
+        <v>0.918730735778809</v>
       </c>
       <c r="H1170" t="n">
         <v>1314740</v>
@@ -34328,7 +34328,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.935435116291046</v>
+        <v>0.935434937477112</v>
       </c>
       <c r="H1171" t="n">
         <v>2331133</v>
@@ -34415,7 +34415,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.953809559345245</v>
+        <v>0.95380973815918</v>
       </c>
       <c r="H1174" t="n">
         <v>982082</v>
@@ -34444,7 +34444,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.945457398891449</v>
+        <v>0.945457458496094</v>
       </c>
       <c r="H1175" t="n">
         <v>642129</v>
@@ -34473,7 +34473,7 @@
         <v>1.125</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.93961101770401</v>
+        <v>0.9396111369133</v>
       </c>
       <c r="H1176" t="n">
         <v>937169</v>
@@ -34589,7 +34589,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.942951798439026</v>
+        <v>0.942951858043671</v>
       </c>
       <c r="H1180" t="n">
         <v>992299</v>
@@ -34618,7 +34618,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.918730795383453</v>
+        <v>0.918730735778809</v>
       </c>
       <c r="H1181" t="n">
         <v>976233</v>
@@ -34647,7 +34647,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.910378694534302</v>
+        <v>0.910378813743591</v>
       </c>
       <c r="H1182" t="n">
         <v>1095902</v>
@@ -34676,7 +34676,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.917060494422913</v>
+        <v>0.917060434818268</v>
       </c>
       <c r="H1183" t="n">
         <v>768682</v>
@@ -34705,7 +34705,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.917060494422913</v>
+        <v>0.917060434818268</v>
       </c>
       <c r="H1184" t="n">
         <v>876059</v>
@@ -34763,7 +34763,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.90035605430603</v>
+        <v>0.900356113910675</v>
       </c>
       <c r="H1186" t="n">
         <v>905278</v>
@@ -34792,7 +34792,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.905367374420166</v>
+        <v>0.905367434024811</v>
       </c>
       <c r="H1187" t="n">
         <v>1392144</v>
@@ -34821,7 +34821,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.903697073459625</v>
+        <v>0.90369713306427</v>
       </c>
       <c r="H1188" t="n">
         <v>1543314</v>
@@ -34850,7 +34850,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.888663291931152</v>
+        <v>0.888663232326508</v>
       </c>
       <c r="H1189" t="n">
         <v>842442</v>
@@ -34908,7 +34908,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.897015333175659</v>
+        <v>0.897015392780304</v>
       </c>
       <c r="H1191" t="n">
         <v>1331626</v>
@@ -34937,7 +34937,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.918730795383453</v>
+        <v>0.918730735778809</v>
       </c>
       <c r="H1192" t="n">
         <v>2380908</v>
@@ -34995,7 +34995,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.905367374420166</v>
+        <v>0.905367434024811</v>
       </c>
       <c r="H1194" t="n">
         <v>698588</v>
@@ -35024,7 +35024,7 @@
         <v>1.0809999704361</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.902861714363098</v>
+        <v>0.902861773967743</v>
       </c>
       <c r="H1195" t="n">
         <v>652835</v>
@@ -35053,7 +35053,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.902026653289795</v>
+        <v>0.902026534080505</v>
       </c>
       <c r="H1196" t="n">
         <v>1391559</v>
@@ -35111,7 +35111,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.937105298042297</v>
+        <v>0.937105357646942</v>
       </c>
       <c r="H1198" t="n">
         <v>1687673</v>
@@ -35140,7 +35140,7 @@
         <v>1.10800004005432</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.92541241645813</v>
+        <v>0.925412476062775</v>
       </c>
       <c r="H1199" t="n">
         <v>870459</v>
@@ -35169,7 +35169,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.912049114704132</v>
+        <v>0.912049055099487</v>
       </c>
       <c r="H1200" t="n">
         <v>1226727</v>
@@ -35198,7 +35198,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.890333592891693</v>
+        <v>0.890333712100983</v>
       </c>
       <c r="H1201" t="n">
         <v>2226316</v>
@@ -35227,7 +35227,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.892004132270813</v>
+        <v>0.892004072666168</v>
       </c>
       <c r="H1202" t="n">
         <v>631454</v>
@@ -35256,7 +35256,7 @@
         <v>1.08299994468689</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.904532194137573</v>
+        <v>0.904532253742218</v>
       </c>
       <c r="H1203" t="n">
         <v>1011010</v>
@@ -35314,7 +35314,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.829363346099854</v>
+        <v>0.829363286495209</v>
       </c>
       <c r="H1205" t="n">
         <v>5785783</v>
@@ -35343,7 +35343,7 @@
         <v>0.993499994277954</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.829780876636505</v>
+        <v>0.82978093624115</v>
       </c>
       <c r="H1206" t="n">
         <v>1701993</v>
@@ -35372,7 +35372,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.834374606609344</v>
+        <v>0.834374666213989</v>
       </c>
       <c r="H1207" t="n">
         <v>1051359</v>
@@ -35430,7 +35430,7 @@
         <v>1.0110000371933</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.844397187232971</v>
+        <v>0.844397127628326</v>
       </c>
       <c r="H1209" t="n">
         <v>918635</v>
@@ -35488,7 +35488,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.898685693740845</v>
+        <v>0.8986856341362</v>
       </c>
       <c r="H1211" t="n">
         <v>2105739</v>
@@ -35546,7 +35546,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.917060494422913</v>
+        <v>0.917060434818268</v>
       </c>
       <c r="H1213" t="n">
         <v>1682730</v>
@@ -35575,7 +35575,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.889498472213745</v>
+        <v>0.88949853181839</v>
       </c>
       <c r="H1214" t="n">
         <v>2208181</v>
@@ -35778,7 +35778,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.864442110061646</v>
+        <v>0.86444216966629</v>
       </c>
       <c r="H1221" t="n">
         <v>897836</v>
@@ -35807,7 +35807,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.843561947345734</v>
+        <v>0.843561887741089</v>
       </c>
       <c r="H1222" t="n">
         <v>990227</v>
@@ -35952,7 +35952,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.768393039703369</v>
+        <v>0.768393099308014</v>
       </c>
       <c r="H1227" t="n">
         <v>1311041</v>
@@ -35981,7 +35981,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.729973375797272</v>
+        <v>0.729973435401917</v>
       </c>
       <c r="H1228" t="n">
         <v>1596505</v>
@@ -36039,7 +36039,7 @@
         <v>0.962499976158142</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.803889393806458</v>
+        <v>0.803889453411102</v>
       </c>
       <c r="H1230" t="n">
         <v>1720467</v>
@@ -36068,7 +36068,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.794284462928772</v>
+        <v>0.794284522533417</v>
       </c>
       <c r="H1231" t="n">
         <v>1081621</v>
@@ -36126,7 +36126,7 @@
         <v>0.993499994277954</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.829780876636505</v>
+        <v>0.82978093624115</v>
       </c>
       <c r="H1233" t="n">
         <v>1561801</v>
@@ -36184,7 +36184,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.924577295780182</v>
+        <v>0.924577236175537</v>
       </c>
       <c r="H1235" t="n">
         <v>4003298</v>
@@ -36271,7 +36271,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.957150459289551</v>
+        <v>0.957150399684906</v>
       </c>
       <c r="H1238" t="n">
         <v>2938823</v>
@@ -36300,7 +36300,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.96633768081665</v>
+        <v>0.96633780002594</v>
       </c>
       <c r="H1239" t="n">
         <v>1609545</v>
@@ -36358,7 +36358,7 @@
         <v>1.25</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.04401230812073</v>
+        <v>1.04401242733002</v>
       </c>
       <c r="H1241" t="n">
         <v>2955163</v>
@@ -36387,7 +36387,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.04985880851746</v>
+        <v>1.04985868930817</v>
       </c>
       <c r="H1242" t="n">
         <v>2344652</v>
@@ -36416,7 +36416,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.0298136472702</v>
+        <v>1.02981376647949</v>
       </c>
       <c r="H1243" t="n">
         <v>2819086</v>
@@ -36503,7 +36503,7 @@
         <v>1.3289999961853</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.10999393463135</v>
+        <v>1.10999381542206</v>
       </c>
       <c r="H1246" t="n">
         <v>3085957</v>
@@ -36590,7 +36590,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.06906855106354</v>
+        <v>1.06906843185425</v>
       </c>
       <c r="H1249" t="n">
         <v>3269294</v>
@@ -36619,7 +36619,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.06906855106354</v>
+        <v>1.06906843185425</v>
       </c>
       <c r="H1250" t="n">
         <v>1487972</v>
@@ -36648,7 +36648,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.0790913105011</v>
+        <v>1.07909119129181</v>
       </c>
       <c r="H1251" t="n">
         <v>1682016</v>
@@ -36735,7 +36735,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.04317712783813</v>
+        <v>1.04317700862885</v>
       </c>
       <c r="H1254" t="n">
         <v>2115098</v>
@@ -36764,7 +36764,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.03733050823212</v>
+        <v>1.03733062744141</v>
       </c>
       <c r="H1255" t="n">
         <v>940733</v>
@@ -36822,7 +36822,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.02229678630829</v>
+        <v>1.02229690551758</v>
       </c>
       <c r="H1257" t="n">
         <v>1511324</v>
@@ -36938,7 +36938,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.0298136472702</v>
+        <v>1.02981376647949</v>
       </c>
       <c r="H1261" t="n">
         <v>1624816</v>
@@ -36967,7 +36967,7 @@
         <v>1.21899998188019</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.01812052726746</v>
+        <v>1.01812076568604</v>
       </c>
       <c r="H1262" t="n">
         <v>752242</v>
@@ -36996,7 +36996,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.01060390472412</v>
+        <v>1.01060378551483</v>
       </c>
       <c r="H1263" t="n">
         <v>1133335</v>
@@ -37025,7 +37025,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.998075783252716</v>
+        <v>0.998075604438782</v>
       </c>
       <c r="H1264" t="n">
         <v>1064295</v>
@@ -37083,7 +37083,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.967172920703888</v>
+        <v>0.967172980308533</v>
       </c>
       <c r="H1266" t="n">
         <v>1346794</v>
@@ -37112,7 +37112,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.992229223251343</v>
+        <v>0.992229044437408</v>
       </c>
       <c r="H1267" t="n">
         <v>1350621</v>
@@ -37170,7 +37170,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.991394102573395</v>
+        <v>0.991393983364105</v>
       </c>
       <c r="H1269" t="n">
         <v>1600769</v>
@@ -37199,7 +37199,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.987218022346497</v>
+        <v>0.987217962741852</v>
       </c>
       <c r="H1270" t="n">
         <v>866193</v>
@@ -37228,7 +37228,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.965502619743347</v>
+        <v>0.965502560138702</v>
       </c>
       <c r="H1271" t="n">
         <v>1757719</v>
@@ -37257,7 +37257,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.983042001724243</v>
+        <v>0.983041942119598</v>
       </c>
       <c r="H1272" t="n">
         <v>1421450</v>
@@ -37344,7 +37344,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.05737555027008</v>
+        <v>1.05737566947937</v>
       </c>
       <c r="H1275" t="n">
         <v>1591028</v>
@@ -37373,7 +37373,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.03398990631104</v>
+        <v>1.03398978710175</v>
       </c>
       <c r="H1276" t="n">
         <v>1603132</v>
@@ -37402,7 +37402,7 @@
         <v>1.2610000371933</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.05319964885712</v>
+        <v>1.05319952964783</v>
       </c>
       <c r="H1277" t="n">
         <v>1062423</v>
@@ -37431,7 +37431,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.05069398880005</v>
+        <v>1.05069386959076</v>
       </c>
       <c r="H1278" t="n">
         <v>718663</v>
@@ -37547,7 +37547,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.06906855106354</v>
+        <v>1.06906843185425</v>
       </c>
       <c r="H1282" t="n">
         <v>1751527</v>
@@ -37576,7 +37576,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.07575023174286</v>
+        <v>1.07575011253357</v>
       </c>
       <c r="H1283" t="n">
         <v>1878041</v>
@@ -37634,7 +37634,7 @@
         <v>1.25899994373322</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.05152916908264</v>
+        <v>1.05152904987335</v>
       </c>
       <c r="H1285" t="n">
         <v>1139462</v>
@@ -37692,7 +37692,7 @@
         <v>1.2610000371933</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.05319964885712</v>
+        <v>1.05319952964783</v>
       </c>
       <c r="H1287" t="n">
         <v>1291561</v>
@@ -37779,7 +37779,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.02229678630829</v>
+        <v>1.02229690551758</v>
       </c>
       <c r="H1290" t="n">
         <v>860970</v>
@@ -37808,7 +37808,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.05069398880005</v>
+        <v>1.05069386959076</v>
       </c>
       <c r="H1291" t="n">
         <v>1203524</v>
@@ -37895,7 +37895,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.11416983604431</v>
+        <v>1.1141699552536</v>
       </c>
       <c r="H1294" t="n">
         <v>1778230</v>
@@ -38011,7 +38011,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.31378495693207</v>
+        <v>1.31378483772278</v>
       </c>
       <c r="H1298" t="n">
         <v>6077912</v>
@@ -38098,7 +38098,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.41484534740448</v>
+        <v>1.41484546661377</v>
       </c>
       <c r="H1301" t="n">
         <v>7324721</v>
@@ -38243,7 +38243,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.37141454219818</v>
+        <v>1.37141442298889</v>
       </c>
       <c r="H1306" t="n">
         <v>1438763</v>
@@ -38330,7 +38330,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.30793857574463</v>
+        <v>1.30793845653534</v>
       </c>
       <c r="H1309" t="n">
         <v>2216085</v>
@@ -38359,7 +38359,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.29875111579895</v>
+        <v>1.29875123500824</v>
       </c>
       <c r="H1310" t="n">
         <v>2003780</v>
@@ -38388,7 +38388,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.32046663761139</v>
+        <v>1.3204665184021</v>
       </c>
       <c r="H1311" t="n">
         <v>3540376</v>
@@ -38417,7 +38417,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.30376243591309</v>
+        <v>1.30376255512238</v>
       </c>
       <c r="H1312" t="n">
         <v>1457296</v>
@@ -38446,7 +38446,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.3012570142746</v>
+        <v>1.30125689506531</v>
       </c>
       <c r="H1313" t="n">
         <v>2530993</v>
@@ -38475,7 +38475,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.32798361778259</v>
+        <v>1.32798373699188</v>
       </c>
       <c r="H1314" t="n">
         <v>1461982</v>
@@ -38620,7 +38620,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.36807370185852</v>
+        <v>1.36807382106781</v>
       </c>
       <c r="H1319" t="n">
         <v>2810879</v>
@@ -38649,7 +38649,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.3780962228775</v>
+        <v>1.37809610366821</v>
       </c>
       <c r="H1320" t="n">
         <v>2136490</v>
@@ -38678,7 +38678,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.42152714729309</v>
+        <v>1.42152726650238</v>
       </c>
       <c r="H1321" t="n">
         <v>9920232</v>
@@ -38707,7 +38707,7 @@
         <v>1.75800001621246</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.46829891204834</v>
+        <v>1.46829879283905</v>
       </c>
       <c r="H1322" t="n">
         <v>5258400</v>
@@ -38736,7 +38736,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.44491302967072</v>
+        <v>1.44491291046143</v>
       </c>
       <c r="H1323" t="n">
         <v>2240203</v>
@@ -38765,7 +38765,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.44825375080109</v>
+        <v>1.44825387001038</v>
       </c>
       <c r="H1324" t="n">
         <v>1605888</v>
@@ -38823,7 +38823,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.44825375080109</v>
+        <v>1.44825387001038</v>
       </c>
       <c r="H1326" t="n">
         <v>6989553</v>
@@ -38939,7 +38939,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.50337767601013</v>
+        <v>1.50337755680084</v>
       </c>
       <c r="H1330" t="n">
         <v>6229911</v>
@@ -38997,7 +38997,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.50170719623566</v>
+        <v>1.50170731544495</v>
       </c>
       <c r="H1332" t="n">
         <v>2345616</v>
@@ -39055,7 +39055,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.50337767601013</v>
+        <v>1.50337755680084</v>
       </c>
       <c r="H1334" t="n">
         <v>1519136</v>
@@ -39142,7 +39142,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.54012668132782</v>
+        <v>1.54012680053711</v>
       </c>
       <c r="H1337" t="n">
         <v>3492731</v>
@@ -39171,7 +39171,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.51005923748016</v>
+        <v>1.51005935668945</v>
       </c>
       <c r="H1338" t="n">
         <v>3127651</v>
@@ -39200,7 +39200,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.5225875377655</v>
+        <v>1.52258741855621</v>
       </c>
       <c r="H1339" t="n">
         <v>2478018</v>
@@ -39258,7 +39258,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.53929173946381</v>
+        <v>1.53929162025452</v>
       </c>
       <c r="H1341" t="n">
         <v>1846248</v>
@@ -39287,7 +39287,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.51172971725464</v>
+        <v>1.51172959804535</v>
       </c>
       <c r="H1342" t="n">
         <v>1467621</v>
@@ -39316,7 +39316,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.53261017799377</v>
+        <v>1.53261005878448</v>
       </c>
       <c r="H1343" t="n">
         <v>1607652</v>
@@ -39432,7 +39432,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.5234227180481</v>
+        <v>1.52342283725739</v>
       </c>
       <c r="H1347" t="n">
         <v>1689611</v>
@@ -39490,7 +39490,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.55265510082245</v>
+        <v>1.55265486240387</v>
       </c>
       <c r="H1349" t="n">
         <v>1403593</v>
@@ -39606,7 +39606,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.49753105640411</v>
+        <v>1.4975311756134</v>
       </c>
       <c r="H1353" t="n">
         <v>985226</v>
@@ -39664,7 +39664,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.50922405719757</v>
+        <v>1.50922417640686</v>
       </c>
       <c r="H1355" t="n">
         <v>1657793</v>
@@ -39693,7 +39693,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.5225875377655</v>
+        <v>1.52258741855621</v>
       </c>
       <c r="H1356" t="n">
         <v>1042227</v>
@@ -39722,7 +39722,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.51924645900726</v>
+        <v>1.51924669742584</v>
       </c>
       <c r="H1357" t="n">
         <v>1221440</v>
@@ -39751,7 +39751,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.51924645900726</v>
+        <v>1.51924669742584</v>
       </c>
       <c r="H1358" t="n">
         <v>1480530</v>
@@ -39809,7 +39809,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.59245300292969</v>
+        <v>1.5924528837204</v>
       </c>
       <c r="H1360" t="n">
         <v>1658439</v>
@@ -39867,7 +39867,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.57350552082062</v>
+        <v>1.57350540161133</v>
       </c>
       <c r="H1362" t="n">
         <v>2619062</v>
@@ -39925,7 +39925,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.56489300727844</v>
+        <v>1.56489288806915</v>
       </c>
       <c r="H1364" t="n">
         <v>1599198</v>
@@ -39983,7 +39983,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.56489300727844</v>
+        <v>1.56489288806915</v>
       </c>
       <c r="H1366" t="n">
         <v>2449408</v>
@@ -40070,7 +40070,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.57264411449432</v>
+        <v>1.57264423370361</v>
       </c>
       <c r="H1369" t="n">
         <v>1456339</v>
@@ -40302,7 +40302,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.83101940155029</v>
+        <v>1.83101952075958</v>
       </c>
       <c r="H1377" t="n">
         <v>5655370</v>
@@ -40331,7 +40331,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.8327419757843</v>
+        <v>1.83274209499359</v>
       </c>
       <c r="H1378" t="n">
         <v>2364501</v>
@@ -40360,7 +40360,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.80173683166504</v>
+        <v>1.80173695087433</v>
       </c>
       <c r="H1379" t="n">
         <v>2810289</v>
@@ -40389,7 +40389,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.75867438316345</v>
+        <v>1.75867450237274</v>
       </c>
       <c r="H1380" t="n">
         <v>4582695</v>
@@ -40447,7 +40447,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.74661684036255</v>
+        <v>1.74661695957184</v>
       </c>
       <c r="H1382" t="n">
         <v>2241110</v>
@@ -40505,7 +40505,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.7758994102478</v>
+        <v>1.77589952945709</v>
       </c>
       <c r="H1384" t="n">
         <v>2093668</v>
@@ -40563,7 +40563,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.83963203430176</v>
+        <v>1.83963191509247</v>
       </c>
       <c r="H1386" t="n">
         <v>6728917</v>
@@ -40650,7 +40650,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.79656934738159</v>
+        <v>1.7965692281723</v>
       </c>
       <c r="H1389" t="n">
         <v>2547377</v>
@@ -40737,7 +40737,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.87235939502716</v>
+        <v>1.87235951423645</v>
       </c>
       <c r="H1392" t="n">
         <v>4916415</v>
@@ -40766,7 +40766,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.87063694000244</v>
+        <v>1.87063682079315</v>
       </c>
       <c r="H1393" t="n">
         <v>3124693</v>
@@ -40824,7 +40824,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.8775269985199</v>
+        <v>1.87752687931061</v>
       </c>
       <c r="H1395" t="n">
         <v>1761364</v>
@@ -40853,7 +40853,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.92747938632965</v>
+        <v>1.92747950553894</v>
       </c>
       <c r="H1396" t="n">
         <v>7583378</v>
@@ -40911,7 +40911,7 @@
         <v>2.25</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.93781447410583</v>
+        <v>1.93781459331512</v>
       </c>
       <c r="H1398" t="n">
         <v>2649479</v>
@@ -40969,7 +40969,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.94470453262329</v>
+        <v>1.94470465183258</v>
       </c>
       <c r="H1400" t="n">
         <v>6000564</v>
@@ -41027,7 +41027,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.91542196273804</v>
+        <v>1.91542184352875</v>
       </c>
       <c r="H1402" t="n">
         <v>4795754</v>
@@ -41085,7 +41085,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.9119770526886</v>
+        <v>1.91197693347931</v>
       </c>
       <c r="H1404" t="n">
         <v>1741874</v>
@@ -41143,7 +41143,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.92058944702148</v>
+        <v>1.92058968544006</v>
       </c>
       <c r="H1406" t="n">
         <v>1626077</v>
@@ -41172,7 +41172,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.89475202560425</v>
+        <v>1.89475190639496</v>
       </c>
       <c r="H1407" t="n">
         <v>1693344</v>
@@ -41201,7 +41201,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.88441693782806</v>
+        <v>1.88441669940948</v>
       </c>
       <c r="H1408" t="n">
         <v>2109309</v>
@@ -41520,7 +41520,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.92920219898224</v>
+        <v>1.92920207977295</v>
       </c>
       <c r="H1419" t="n">
         <v>22194642</v>
@@ -41549,7 +41549,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.90336465835571</v>
+        <v>1.90336453914642</v>
       </c>
       <c r="H1420" t="n">
         <v>5111147</v>
@@ -41578,7 +41578,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.91886699199677</v>
+        <v>1.91886687278748</v>
       </c>
       <c r="H1421" t="n">
         <v>2504540</v>
@@ -41607,7 +41607,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.92747938632965</v>
+        <v>1.92747950553894</v>
       </c>
       <c r="H1422" t="n">
         <v>2487435</v>
@@ -41636,7 +41636,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.89647424221039</v>
+        <v>1.89647436141968</v>
       </c>
       <c r="H1423" t="n">
         <v>2073595</v>
@@ -41665,7 +41665,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.90508699417114</v>
+        <v>1.90508687496185</v>
       </c>
       <c r="H1424" t="n">
         <v>1834534</v>
@@ -41694,7 +41694,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.90508699417114</v>
+        <v>1.90508687496185</v>
       </c>
       <c r="H1425" t="n">
         <v>3197473</v>
@@ -41723,7 +41723,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.99293446540833</v>
+        <v>1.99293458461761</v>
       </c>
       <c r="H1426" t="n">
         <v>5731370</v>
@@ -41752,7 +41752,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.01704978942871</v>
+        <v>2.01704955101013</v>
       </c>
       <c r="H1427" t="n">
         <v>5253085</v>
@@ -41810,7 +41810,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.06183433532715</v>
+        <v>2.06183457374573</v>
       </c>
       <c r="H1429" t="n">
         <v>4144115</v>
@@ -41839,7 +41839,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.98087680339813</v>
+        <v>1.98087704181671</v>
       </c>
       <c r="H1430" t="n">
         <v>5086497</v>
@@ -41868,7 +41868,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1431" t="n">
-        <v>2.02049469947815</v>
+        <v>2.02049446105957</v>
       </c>
       <c r="H1431" t="n">
         <v>2887673</v>
@@ -41897,7 +41897,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.96537446975708</v>
+        <v>1.96537458896637</v>
       </c>
       <c r="H1432" t="n">
         <v>4116785</v>
@@ -41955,7 +41955,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.92058944702148</v>
+        <v>1.92058968544006</v>
       </c>
       <c r="H1434" t="n">
         <v>2727200</v>
@@ -41984,7 +41984,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.9119770526886</v>
+        <v>1.91197693347931</v>
       </c>
       <c r="H1435" t="n">
         <v>1399216</v>
@@ -42013,7 +42013,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.92231214046478</v>
+        <v>1.9223119020462</v>
       </c>
       <c r="H1436" t="n">
         <v>1160492</v>
@@ -42100,7 +42100,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.9602073431015</v>
+        <v>1.96020698547363</v>
       </c>
       <c r="H1439" t="n">
         <v>1459843</v>
@@ -42158,7 +42158,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.96192967891693</v>
+        <v>1.96192955970764</v>
       </c>
       <c r="H1441" t="n">
         <v>1857136</v>
@@ -42187,7 +42187,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.01532697677612</v>
+        <v>2.0153272151947</v>
       </c>
       <c r="H1442" t="n">
         <v>4357519</v>
@@ -42216,7 +42216,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.01360440254211</v>
+        <v>2.01360464096069</v>
       </c>
       <c r="H1443" t="n">
         <v>6083558</v>
@@ -42245,7 +42245,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.00671434402466</v>
+        <v>2.00671458244324</v>
       </c>
       <c r="H1444" t="n">
         <v>1600191</v>
@@ -42274,7 +42274,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.99293446540833</v>
+        <v>1.99293458461761</v>
       </c>
       <c r="H1445" t="n">
         <v>1455081</v>
@@ -42303,7 +42303,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.01360440254211</v>
+        <v>2.01360464096069</v>
       </c>
       <c r="H1446" t="n">
         <v>2019884</v>
@@ -42448,7 +42448,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.92747938632965</v>
+        <v>1.92747950553894</v>
       </c>
       <c r="H1451" t="n">
         <v>2973929</v>
@@ -42477,7 +42477,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.95676207542419</v>
+        <v>1.9567619562149</v>
       </c>
       <c r="H1452" t="n">
         <v>3442805</v>
@@ -42506,7 +42506,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.93953692913055</v>
+        <v>1.93953704833984</v>
       </c>
       <c r="H1453" t="n">
         <v>2598555</v>
@@ -42564,7 +42564,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.89475202560425</v>
+        <v>1.89475190639496</v>
       </c>
       <c r="H1455" t="n">
         <v>1370526</v>
@@ -42593,7 +42593,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.92058944702148</v>
+        <v>1.92058968544006</v>
       </c>
       <c r="H1456" t="n">
         <v>920719</v>
@@ -42622,7 +42622,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.92058944702148</v>
+        <v>1.92058968544006</v>
       </c>
       <c r="H1457" t="n">
         <v>1237770</v>
@@ -42680,7 +42680,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.89475202560425</v>
+        <v>1.89475190639496</v>
       </c>
       <c r="H1459" t="n">
         <v>1599201</v>
@@ -42738,7 +42738,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.86030197143555</v>
+        <v>1.86030209064484</v>
       </c>
       <c r="H1461" t="n">
         <v>1395726</v>
@@ -42767,7 +42767,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G1462" t="n">
-        <v>1.89819705486298</v>
+        <v>1.89819693565369</v>
       </c>
       <c r="H1462" t="n">
         <v>2024308</v>
@@ -42912,7 +42912,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.84479939937592</v>
+        <v>1.84479951858521</v>
       </c>
       <c r="H1467" t="n">
         <v>2159433</v>
@@ -42999,7 +42999,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.89647424221039</v>
+        <v>1.89647436141968</v>
       </c>
       <c r="H1470" t="n">
         <v>1507237</v>
@@ -43057,7 +43057,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G1472" t="n">
-        <v>1.84824442863464</v>
+        <v>1.84824454784393</v>
       </c>
       <c r="H1472" t="n">
         <v>2858480</v>
@@ -43115,7 +43115,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.83618676662445</v>
+        <v>1.83618688583374</v>
       </c>
       <c r="H1474" t="n">
         <v>1430703</v>
@@ -43144,7 +43144,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.87235939502716</v>
+        <v>1.87235951423645</v>
       </c>
       <c r="H1475" t="n">
         <v>1685143</v>
@@ -43173,7 +43173,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.86030197143555</v>
+        <v>1.86030209064484</v>
       </c>
       <c r="H1476" t="n">
         <v>1643206</v>
@@ -43260,7 +43260,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.8913072347641</v>
+        <v>1.89130711555481</v>
       </c>
       <c r="H1479" t="n">
         <v>1405366</v>
@@ -43318,7 +43318,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.84479939937592</v>
+        <v>1.84479951858521</v>
       </c>
       <c r="H1481" t="n">
         <v>1640065</v>
@@ -43434,7 +43434,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.83618676662445</v>
+        <v>1.83618688583374</v>
       </c>
       <c r="H1485" t="n">
         <v>2100850</v>
@@ -43550,7 +43550,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.96192967891693</v>
+        <v>1.96192955970764</v>
       </c>
       <c r="H1489" t="n">
         <v>8832976</v>
@@ -43579,7 +43579,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G1490" t="n">
-        <v>1.87235939502716</v>
+        <v>1.87235951423645</v>
       </c>
       <c r="H1490" t="n">
         <v>11464046</v>
@@ -43608,7 +43608,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.86030197143555</v>
+        <v>1.86030209064484</v>
       </c>
       <c r="H1491" t="n">
         <v>3727686</v>
@@ -43782,7 +43782,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.80001425743103</v>
+        <v>1.80001437664032</v>
       </c>
       <c r="H1497" t="n">
         <v>1978111</v>
@@ -43869,7 +43869,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.76211929321289</v>
+        <v>1.76211941242218</v>
       </c>
       <c r="H1500" t="n">
         <v>1463157</v>
@@ -43985,7 +43985,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1504" t="n">
-        <v>1.74833917617798</v>
+        <v>1.74833929538727</v>
       </c>
       <c r="H1504" t="n">
         <v>1584665</v>
@@ -44072,7 +44072,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.75006198883057</v>
+        <v>1.75006186962128</v>
       </c>
       <c r="H1507" t="n">
         <v>1520737</v>
@@ -44101,7 +44101,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.72766935825348</v>
+        <v>1.72766923904419</v>
       </c>
       <c r="H1508" t="n">
         <v>1310633</v>
@@ -44188,7 +44188,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.79656934738159</v>
+        <v>1.7965692281723</v>
       </c>
       <c r="H1511" t="n">
         <v>752410</v>
@@ -44217,7 +44217,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.80173683166504</v>
+        <v>1.80173695087433</v>
       </c>
       <c r="H1512" t="n">
         <v>897905</v>
@@ -44304,7 +44304,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1515" t="n">
-        <v>1.74833917617798</v>
+        <v>1.74833929538727</v>
       </c>
       <c r="H1515" t="n">
         <v>1761149</v>
@@ -44391,7 +44391,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.76211929321289</v>
+        <v>1.76211941242218</v>
       </c>
       <c r="H1518" t="n">
         <v>1147183</v>
@@ -44536,7 +44536,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1523" t="n">
-        <v>1.81379413604736</v>
+        <v>1.81379425525665</v>
       </c>
       <c r="H1523" t="n">
         <v>858585</v>
@@ -44594,7 +44594,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.79484689235687</v>
+        <v>1.79484701156616</v>
       </c>
       <c r="H1525" t="n">
         <v>785060</v>
@@ -44739,7 +44739,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.75006198883057</v>
+        <v>1.75006186962128</v>
       </c>
       <c r="H1530" t="n">
         <v>1262011</v>
@@ -44855,7 +44855,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.75867438316345</v>
+        <v>1.75867450237274</v>
       </c>
       <c r="H1534" t="n">
         <v>4364721</v>
@@ -44913,7 +44913,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.72766935825348</v>
+        <v>1.72766923904419</v>
       </c>
       <c r="H1536" t="n">
         <v>5758603</v>
@@ -45174,7 +45174,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.59245300292969</v>
+        <v>1.5924528837204</v>
       </c>
       <c r="H1545" t="n">
         <v>6343872</v>
@@ -45203,7 +45203,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G1546" t="n">
-        <v>1.62518048286438</v>
+        <v>1.62518036365509</v>
       </c>
       <c r="H1546" t="n">
         <v>2435503</v>
@@ -45232,7 +45232,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.59589791297913</v>
+        <v>1.59589779376984</v>
       </c>
       <c r="H1547" t="n">
         <v>2613730</v>
@@ -45261,7 +45261,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G1548" t="n">
-        <v>1.60364902019501</v>
+        <v>1.6036491394043</v>
       </c>
       <c r="H1548" t="n">
         <v>2683469</v>
@@ -45406,7 +45406,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.52958154678345</v>
+        <v>1.52958178520203</v>
       </c>
       <c r="H1553" t="n">
         <v>1791724</v>
@@ -45464,7 +45464,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.56575405597687</v>
+        <v>1.56575417518616</v>
       </c>
       <c r="H1555" t="n">
         <v>970738</v>
@@ -45522,7 +45522,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.53302657604218</v>
+        <v>1.53302669525146</v>
       </c>
       <c r="H1557" t="n">
         <v>1921397</v>
@@ -45551,7 +45551,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.57608914375305</v>
+        <v>1.57608926296234</v>
       </c>
       <c r="H1558" t="n">
         <v>1301192</v>
@@ -45609,7 +45609,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.58986902236938</v>
+        <v>1.58986914157867</v>
       </c>
       <c r="H1560" t="n">
         <v>1625441</v>
@@ -45667,7 +45667,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G1562" t="n">
-        <v>1.49599277973175</v>
+        <v>1.49599266052246</v>
       </c>
       <c r="H1562" t="n">
         <v>1781997</v>
@@ -45696,7 +45696,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.47101640701294</v>
+        <v>1.47101652622223</v>
       </c>
       <c r="H1563" t="n">
         <v>2448765</v>
@@ -45783,7 +45783,7 @@
         <v>1.7389999628067</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.49771535396576</v>
+        <v>1.49771523475647</v>
       </c>
       <c r="H1566" t="n">
         <v>4014926</v>
@@ -45841,7 +45841,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.40383887290955</v>
+        <v>1.40383899211884</v>
       </c>
       <c r="H1568" t="n">
         <v>2918108</v>
@@ -45899,7 +45899,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.39522647857666</v>
+        <v>1.39522635936737</v>
       </c>
       <c r="H1570" t="n">
         <v>1389022</v>
@@ -46015,7 +46015,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1574" t="n">
-        <v>1.36938905715942</v>
+        <v>1.36938893795013</v>
       </c>
       <c r="H1574" t="n">
         <v>1620281</v>
@@ -46044,7 +46044,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.33063268661499</v>
+        <v>1.3306325674057</v>
       </c>
       <c r="H1575" t="n">
         <v>891189</v>
@@ -46160,7 +46160,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.43656647205353</v>
+        <v>1.43656659126282</v>
       </c>
       <c r="H1579" t="n">
         <v>1730589</v>
@@ -46218,7 +46218,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.39005887508392</v>
+        <v>1.39005899429321</v>
       </c>
       <c r="H1581" t="n">
         <v>7127428</v>
@@ -46276,7 +46276,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.3986713886261</v>
+        <v>1.39867150783539</v>
       </c>
       <c r="H1583" t="n">
         <v>3037320</v>
@@ -46305,7 +46305,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.39092040061951</v>
+        <v>1.39092016220093</v>
       </c>
       <c r="H1584" t="n">
         <v>1647838</v>
@@ -46363,7 +46363,7 @@
         <v>1.6139999628067</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.39005887508392</v>
+        <v>1.39005899429321</v>
       </c>
       <c r="H1586" t="n">
         <v>1398540</v>
@@ -46450,7 +46450,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.40986776351929</v>
+        <v>1.40986764431</v>
       </c>
       <c r="H1589" t="n">
         <v>2619260</v>
@@ -46566,7 +46566,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1593" t="n">
-        <v>1.39522647857666</v>
+        <v>1.39522635936737</v>
       </c>
       <c r="H1593" t="n">
         <v>2458007</v>
@@ -46595,7 +46595,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.34699630737305</v>
+        <v>1.34699642658234</v>
       </c>
       <c r="H1594" t="n">
         <v>2097111</v>
@@ -46740,7 +46740,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.38661396503448</v>
+        <v>1.38661408424377</v>
       </c>
       <c r="H1599" t="n">
         <v>525123</v>
@@ -46798,7 +46798,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.43915033340454</v>
+        <v>1.43915021419525</v>
       </c>
       <c r="H1601" t="n">
         <v>635198</v>
@@ -46914,7 +46914,7 @@
         <v>1.63300001621246</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.40642285346985</v>
+        <v>1.40642273426056</v>
       </c>
       <c r="H1605" t="n">
         <v>628507</v>
@@ -46943,7 +46943,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.39608788490295</v>
+        <v>1.39608776569366</v>
       </c>
       <c r="H1606" t="n">
         <v>1293537</v>
@@ -46972,7 +46972,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.39522647857666</v>
+        <v>1.39522635936737</v>
       </c>
       <c r="H1607" t="n">
         <v>604608</v>
@@ -47001,7 +47001,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.39092040061951</v>
+        <v>1.39092016220093</v>
       </c>
       <c r="H1608" t="n">
         <v>444474</v>
@@ -47030,7 +47030,7 @@
         <v>1.625</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.39953255653381</v>
+        <v>1.3995326757431</v>
       </c>
       <c r="H1609" t="n">
         <v>792740</v>
@@ -47117,7 +47117,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1612" t="n">
-        <v>1.39522647857666</v>
+        <v>1.39522635936737</v>
       </c>
       <c r="H1612" t="n">
         <v>1149117</v>
@@ -47146,7 +47146,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1613" t="n">
-        <v>1.36938905715942</v>
+        <v>1.36938893795013</v>
       </c>
       <c r="H1613" t="n">
         <v>1295309</v>
@@ -47204,7 +47204,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G1615" t="n">
-        <v>1.33580017089844</v>
+        <v>1.33580005168915</v>
       </c>
       <c r="H1615" t="n">
         <v>1354043</v>
@@ -47233,7 +47233,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.33924508094788</v>
+        <v>1.33924496173859</v>
       </c>
       <c r="H1616" t="n">
         <v>1434960</v>
@@ -47262,7 +47262,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G1617" t="n">
-        <v>1.39608788490295</v>
+        <v>1.39608776569366</v>
       </c>
       <c r="H1617" t="n">
         <v>904146</v>
@@ -47349,7 +47349,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1620" t="n">
-        <v>1.43656647205353</v>
+        <v>1.43656659126282</v>
       </c>
       <c r="H1620" t="n">
         <v>585116</v>
@@ -47378,7 +47378,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1621" t="n">
-        <v>1.42967641353607</v>
+        <v>1.42967653274536</v>
       </c>
       <c r="H1621" t="n">
         <v>1304186</v>
@@ -47407,7 +47407,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.42278635501862</v>
+        <v>1.42278647422791</v>
       </c>
       <c r="H1622" t="n">
         <v>505791</v>
@@ -47465,7 +47465,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1624" t="n">
-        <v>1.39092040061951</v>
+        <v>1.39092016220093</v>
       </c>
       <c r="H1624" t="n">
         <v>793598</v>
@@ -47494,7 +47494,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1625" t="n">
-        <v>1.44441699981689</v>
+        <v>1.44441711902618</v>
       </c>
       <c r="H1625" t="n">
         <v>622169</v>
@@ -47610,7 +47610,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1629" t="n">
-        <v>1.51217997074127</v>
+        <v>1.51217985153198</v>
       </c>
       <c r="H1629" t="n">
         <v>1385475</v>
@@ -47668,7 +47668,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G1631" t="n">
-        <v>1.50058889389038</v>
+        <v>1.50058877468109</v>
       </c>
       <c r="H1631" t="n">
         <v>1107827</v>
@@ -47697,7 +47697,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1632" t="n">
-        <v>1.48453986644745</v>
+        <v>1.48453974723816</v>
       </c>
       <c r="H1632" t="n">
         <v>935914</v>
@@ -47755,7 +47755,7 @@
         <v>1.64699995517731</v>
       </c>
       <c r="G1634" t="n">
-        <v>1.46849071979523</v>
+        <v>1.46849060058594</v>
       </c>
       <c r="H1634" t="n">
         <v>570352</v>
@@ -47784,7 +47784,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1635" t="n">
-        <v>1.47473204135895</v>
+        <v>1.47473216056824</v>
       </c>
       <c r="H1635" t="n">
         <v>489579</v>
@@ -47842,7 +47842,7 @@
         <v>1.65699994564056</v>
       </c>
       <c r="G1637" t="n">
-        <v>1.4774067401886</v>
+        <v>1.47740685939789</v>
       </c>
       <c r="H1637" t="n">
         <v>706589</v>
@@ -48016,7 +48016,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.24826169013977</v>
+        <v>1.24826180934906</v>
       </c>
       <c r="H1643" t="n">
         <v>1529156</v>
@@ -48074,7 +48074,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1645" t="n">
-        <v>1.31959092617035</v>
+        <v>1.31959104537964</v>
       </c>
       <c r="H1645" t="n">
         <v>342563</v>
@@ -48219,7 +48219,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.32137417793274</v>
+        <v>1.32137429714203</v>
       </c>
       <c r="H1650" t="n">
         <v>1098067</v>
@@ -48451,7 +48451,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G1658" t="n">
-        <v>1.30354177951813</v>
+        <v>1.30354189872742</v>
       </c>
       <c r="H1658" t="n">
         <v>745709</v>
@@ -48480,7 +48480,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G1659" t="n">
-        <v>1.37041294574738</v>
+        <v>1.37041282653809</v>
       </c>
       <c r="H1659" t="n">
         <v>1866883</v>
@@ -48596,7 +48596,7 @@
         <v>1.46099996566772</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.30265021324158</v>
+        <v>1.30265009403229</v>
       </c>
       <c r="H1663" t="n">
         <v>583859</v>
@@ -48683,7 +48683,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.34277296066284</v>
+        <v>1.34277307987213</v>
       </c>
       <c r="H1666" t="n">
         <v>424633</v>
@@ -48973,7 +48973,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1676" t="n">
-        <v>1.27144372463226</v>
+        <v>1.27144384384155</v>
       </c>
       <c r="H1676" t="n">
         <v>1212900</v>
@@ -49089,7 +49089,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.30443358421326</v>
+        <v>1.30443346500397</v>
       </c>
       <c r="H1680" t="n">
         <v>1465863</v>
@@ -49118,7 +49118,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1681" t="n">
-        <v>1.27946829795837</v>
+        <v>1.27946817874908</v>
       </c>
       <c r="H1681" t="n">
         <v>838453</v>
@@ -49234,7 +49234,7 @@
         <v>1.53400003910065</v>
       </c>
       <c r="G1685" t="n">
-        <v>1.36773824691772</v>
+        <v>1.36773836612701</v>
       </c>
       <c r="H1685" t="n">
         <v>628817</v>
@@ -49379,7 +49379,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G1690" t="n">
-        <v>1.25361132621765</v>
+        <v>1.25361144542694</v>
       </c>
       <c r="H1690" t="n">
         <v>363852</v>
@@ -49669,7 +49669,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.22151327133179</v>
+        <v>1.22151339054108</v>
       </c>
       <c r="H1700" t="n">
         <v>825266</v>
@@ -49698,7 +49698,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.2197300195694</v>
+        <v>1.21973013877869</v>
       </c>
       <c r="H1701" t="n">
         <v>1367203</v>
@@ -49756,7 +49756,7 @@
         <v>1.41100001335144</v>
       </c>
       <c r="G1703" t="n">
-        <v>1.25806939601898</v>
+        <v>1.25806951522827</v>
       </c>
       <c r="H1703" t="n">
         <v>1074004</v>
@@ -49785,7 +49785,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G1704" t="n">
-        <v>1.27144372463226</v>
+        <v>1.27144384384155</v>
       </c>
       <c r="H1704" t="n">
         <v>360923</v>
@@ -49959,7 +49959,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.22418820858002</v>
+        <v>1.22418808937073</v>
       </c>
       <c r="H1710" t="n">
         <v>557136</v>
@@ -50104,7 +50104,7 @@
         <v>1.28600001335144</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.14661753177643</v>
+        <v>1.14661765098572</v>
       </c>
       <c r="H1715" t="n">
         <v>2895836</v>
@@ -50162,7 +50162,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.06102240085602</v>
+        <v>1.06102252006531</v>
       </c>
       <c r="H1717" t="n">
         <v>2834912</v>
@@ -50307,7 +50307,7 @@
         <v>1.35099995136261</v>
       </c>
       <c r="G1722" t="n">
-        <v>1.20457255840302</v>
+        <v>1.20457243919373</v>
       </c>
       <c r="H1722" t="n">
         <v>1086237</v>
@@ -50423,7 +50423,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1726" t="n">
-        <v>1.05567288398743</v>
+        <v>1.05567276477814</v>
       </c>
       <c r="H1726" t="n">
         <v>3347467</v>
@@ -50568,7 +50568,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G1731" t="n">
-        <v>1.15018391609192</v>
+        <v>1.15018403530121</v>
       </c>
       <c r="H1731" t="n">
         <v>979785</v>
@@ -50626,7 +50626,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G1733" t="n">
-        <v>1.15999174118042</v>
+        <v>1.15999186038971</v>
       </c>
       <c r="H1733" t="n">
         <v>559044</v>
@@ -50655,7 +50655,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.19922292232513</v>
+        <v>1.19922280311584</v>
       </c>
       <c r="H1734" t="n">
         <v>1019337</v>
@@ -50829,7 +50829,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.24826169013977</v>
+        <v>1.24826180934906</v>
       </c>
       <c r="H1740" t="n">
         <v>818062</v>
@@ -50858,7 +50858,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.22329640388489</v>
+        <v>1.22329652309418</v>
       </c>
       <c r="H1741" t="n">
         <v>1319461</v>
@@ -50887,7 +50887,7 @@
         <v>1.34500002861023</v>
       </c>
       <c r="G1742" t="n">
-        <v>1.19922292232513</v>
+        <v>1.19922280311584</v>
       </c>
       <c r="H1742" t="n">
         <v>612447</v>
@@ -51090,7 +51090,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G1749" t="n">
-        <v>1.35614717006683</v>
+        <v>1.35614728927612</v>
       </c>
       <c r="H1749" t="n">
         <v>1428102</v>
@@ -51119,7 +51119,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.3534722328186</v>
+        <v>1.35347235202789</v>
       </c>
       <c r="H1750" t="n">
         <v>674800</v>
@@ -51177,7 +51177,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1752" t="n">
-        <v>1.31780791282654</v>
+        <v>1.31780779361725</v>
       </c>
       <c r="H1752" t="n">
         <v>1843499</v>
@@ -51235,7 +51235,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.37130463123322</v>
+        <v>1.3713047504425</v>
       </c>
       <c r="H1754" t="n">
         <v>1124480</v>
@@ -51322,7 +51322,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1757" t="n">
-        <v>1.37130463123322</v>
+        <v>1.3713047504425</v>
       </c>
       <c r="H1757" t="n">
         <v>1076284</v>
@@ -51438,7 +51438,7 @@
         <v>1.50899994373322</v>
       </c>
       <c r="G1761" t="n">
-        <v>1.34544777870178</v>
+        <v>1.34544765949249</v>
       </c>
       <c r="H1761" t="n">
         <v>1634698</v>
@@ -51467,7 +51467,7 @@
         <v>1.51499998569489</v>
       </c>
       <c r="G1762" t="n">
-        <v>1.35079753398895</v>
+        <v>1.35079741477966</v>
       </c>
       <c r="H1762" t="n">
         <v>820656</v>
@@ -51496,7 +51496,7 @@
         <v>1.50600004196167</v>
       </c>
       <c r="G1763" t="n">
-        <v>1.34277296066284</v>
+        <v>1.34277307987213</v>
       </c>
       <c r="H1763" t="n">
         <v>1122725</v>
@@ -51583,7 +51583,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.30621671676636</v>
+        <v>1.30621683597565</v>
       </c>
       <c r="H1766" t="n">
         <v>1297828</v>
@@ -51757,7 +51757,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.28035986423492</v>
+        <v>1.28035998344421</v>
       </c>
       <c r="H1772" t="n">
         <v>1237905</v>
@@ -51786,7 +51786,7 @@
         <v>1.41100001335144</v>
       </c>
       <c r="G1773" t="n">
-        <v>1.25806939601898</v>
+        <v>1.25806951522827</v>
       </c>
       <c r="H1773" t="n">
         <v>1239309</v>
@@ -51815,7 +51815,7 @@
         <v>1.40199995040894</v>
       </c>
       <c r="G1774" t="n">
-        <v>1.25004482269287</v>
+        <v>1.25004494190216</v>
       </c>
       <c r="H1774" t="n">
         <v>291648</v>
@@ -51902,7 +51902,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.23756217956543</v>
+        <v>1.23756229877472</v>
       </c>
       <c r="H1777" t="n">
         <v>1212133</v>
@@ -51931,7 +51931,7 @@
         <v>1.41100001335144</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.25806939601898</v>
+        <v>1.25806951522827</v>
       </c>
       <c r="H1778" t="n">
         <v>578715</v>
@@ -52018,7 +52018,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.25361132621765</v>
+        <v>1.25361144542694</v>
       </c>
       <c r="H1781" t="n">
         <v>586112</v>
@@ -52105,7 +52105,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1784" t="n">
-        <v>1.25539457798004</v>
+        <v>1.25539469718933</v>
       </c>
       <c r="H1784" t="n">
         <v>1113590</v>
@@ -52250,7 +52250,7 @@
         <v>1.46099996566772</v>
       </c>
       <c r="G1789" t="n">
-        <v>1.30265021324158</v>
+        <v>1.30265009403229</v>
       </c>
       <c r="H1789" t="n">
         <v>1472347</v>
@@ -52279,7 +52279,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1790" t="n">
-        <v>1.3106746673584</v>
+        <v>1.31067478656769</v>
       </c>
       <c r="H1790" t="n">
         <v>1393065</v>
@@ -52337,7 +52337,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1792" t="n">
-        <v>1.3106746673584</v>
+        <v>1.31067478656769</v>
       </c>
       <c r="H1792" t="n">
         <v>1115436</v>
@@ -52424,7 +52424,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.52287912368774</v>
+        <v>1.52287924289703</v>
       </c>
       <c r="H1795" t="n">
         <v>10525712</v>
@@ -52482,7 +52482,7 @@
         <v>1.66499996185303</v>
       </c>
       <c r="G1797" t="n">
-        <v>1.48453986644745</v>
+        <v>1.48453974723816</v>
       </c>
       <c r="H1797" t="n">
         <v>3473370</v>
@@ -52511,7 +52511,7 @@
         <v>1.67900002002716</v>
       </c>
       <c r="G1798" t="n">
-        <v>1.49702250957489</v>
+        <v>1.4970223903656</v>
       </c>
       <c r="H1798" t="n">
         <v>1910770</v>
@@ -52540,7 +52540,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1799" t="n">
-        <v>1.49969732761383</v>
+        <v>1.49969744682312</v>
       </c>
       <c r="H1799" t="n">
         <v>4119084</v>
@@ -52569,7 +52569,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G1800" t="n">
-        <v>1.49880564212799</v>
+        <v>1.4988055229187</v>
       </c>
       <c r="H1800" t="n">
         <v>1525844</v>
@@ -52598,7 +52598,7 @@
         <v>1.67299997806549</v>
       </c>
       <c r="G1801" t="n">
-        <v>1.49167287349701</v>
+        <v>1.49167275428772</v>
       </c>
       <c r="H1801" t="n">
         <v>1506591</v>
@@ -52685,7 +52685,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.4408506155014</v>
+        <v>1.44085073471069</v>
       </c>
       <c r="H1804" t="n">
         <v>2971739</v>
@@ -52743,7 +52743,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.5166380405426</v>
+        <v>1.51663792133331</v>
       </c>
       <c r="H1806" t="n">
         <v>2307066</v>
@@ -52772,7 +52772,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.51217997074127</v>
+        <v>1.51217985153198</v>
       </c>
       <c r="H1807" t="n">
         <v>1991227</v>
@@ -52946,7 +52946,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G1813" t="n">
-        <v>1.57548451423645</v>
+        <v>1.57548463344574</v>
       </c>
       <c r="H1813" t="n">
         <v>1515318</v>
@@ -53149,7 +53149,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.51217997074127</v>
+        <v>1.51217985153198</v>
       </c>
       <c r="H1820" t="n">
         <v>1794147</v>
@@ -53381,7 +53381,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.54784440994263</v>
+        <v>1.54784452915192</v>
       </c>
       <c r="H1828" t="n">
         <v>862127</v>
@@ -53468,7 +53468,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1831" t="n">
-        <v>1.54606115818024</v>
+        <v>1.54606127738953</v>
       </c>
       <c r="H1831" t="n">
         <v>662815</v>
@@ -53497,7 +53497,7 @@
         <v>1.70899999141693</v>
       </c>
       <c r="G1832" t="n">
-        <v>1.52377092838287</v>
+        <v>1.52377080917358</v>
       </c>
       <c r="H1832" t="n">
         <v>1322863</v>
@@ -53526,7 +53526,7 @@
         <v>1.65699994564056</v>
       </c>
       <c r="G1833" t="n">
-        <v>1.4774067401886</v>
+        <v>1.47740685939789</v>
       </c>
       <c r="H1833" t="n">
         <v>2340370</v>
@@ -53555,7 +53555,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G1834" t="n">
-        <v>1.49880564212799</v>
+        <v>1.4988055229187</v>
       </c>
       <c r="H1834" t="n">
         <v>905445</v>
@@ -53613,7 +53613,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.57815933227539</v>
+        <v>1.57815945148468</v>
       </c>
       <c r="H1836" t="n">
         <v>6449244</v>
@@ -53642,7 +53642,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.69496119022369</v>
+        <v>1.6949610710144</v>
       </c>
       <c r="H1837" t="n">
         <v>14970083</v>
@@ -54019,7 +54019,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G1850" t="n">
-        <v>1.87774217128754</v>
+        <v>1.87774205207825</v>
       </c>
       <c r="H1850" t="n">
         <v>1129561</v>
@@ -54193,7 +54193,7 @@
         <v>1.97399997711182</v>
       </c>
       <c r="G1856" t="n">
-        <v>1.76004886627197</v>
+        <v>1.76004898548126</v>
       </c>
       <c r="H1856" t="n">
         <v>1781474</v>
@@ -54280,7 +54280,7 @@
         <v>1.93099999427795</v>
       </c>
       <c r="G1859" t="n">
-        <v>1.72170948982239</v>
+        <v>1.7217093706131</v>
       </c>
       <c r="H1859" t="n">
         <v>1460137</v>
@@ -54396,7 +54396,7 @@
         <v>1.9190000295639</v>
       </c>
       <c r="G1863" t="n">
-        <v>1.71101033687592</v>
+        <v>1.71101021766663</v>
       </c>
       <c r="H1863" t="n">
         <v>2341018</v>
@@ -54425,7 +54425,7 @@
         <v>1.95299994945526</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.74132513999939</v>
+        <v>1.7413250207901</v>
       </c>
       <c r="H1864" t="n">
         <v>981386</v>
@@ -54628,7 +54628,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.76539874076843</v>
+        <v>1.76539885997772</v>
       </c>
       <c r="H1871" t="n">
         <v>903446</v>
@@ -54686,7 +54686,7 @@
         <v>1.95299994945526</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.74132513999939</v>
+        <v>1.7413250207901</v>
       </c>
       <c r="H1873" t="n">
         <v>936730</v>
@@ -54860,7 +54860,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.76807355880737</v>
+        <v>1.76807343959808</v>
       </c>
       <c r="H1879" t="n">
         <v>1018260</v>
@@ -80009,6 +80009,35 @@
         <v>2893559</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>1.89300000667572</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>1.93700003623962</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>1.87600004673004</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>1.93499994277954</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>1.93499994277954</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>2246217</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9959831237793</v>
+        <v>2.99598336219788</v>
       </c>
       <c r="H2" t="n">
         <v>726355</v>
@@ -456,7 +456,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91082644462585</v>
+        <v>2.91082620620728</v>
       </c>
       <c r="H3" t="n">
         <v>1077659</v>
@@ -485,7 +485,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G4" t="n">
-        <v>2.87366700172424</v>
+        <v>2.87366652488708</v>
       </c>
       <c r="H4" t="n">
         <v>1045563</v>
@@ -514,7 +514,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G5" t="n">
-        <v>2.80089592933655</v>
+        <v>2.80089640617371</v>
       </c>
       <c r="H5" t="n">
         <v>1006703</v>
@@ -543,7 +543,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78541326522827</v>
+        <v>2.78541278839111</v>
       </c>
       <c r="H6" t="n">
         <v>761745</v>
@@ -601,7 +601,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76218819618225</v>
+        <v>2.76218843460083</v>
       </c>
       <c r="H8" t="n">
         <v>789466</v>
@@ -630,7 +630,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G9" t="n">
-        <v>2.75289845466614</v>
+        <v>2.75289869308472</v>
       </c>
       <c r="H9" t="n">
         <v>581213</v>
@@ -659,7 +659,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75289845466614</v>
+        <v>2.75289869308472</v>
       </c>
       <c r="H10" t="n">
         <v>1613399</v>
@@ -688,7 +688,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G11" t="n">
-        <v>2.69251394271851</v>
+        <v>2.69251418113708</v>
       </c>
       <c r="H11" t="n">
         <v>1573296</v>
@@ -746,7 +746,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66464447975159</v>
+        <v>2.66464519500732</v>
       </c>
       <c r="H13" t="n">
         <v>964050</v>
@@ -804,7 +804,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G15" t="n">
-        <v>2.65690302848816</v>
+        <v>2.65690326690674</v>
       </c>
       <c r="H15" t="n">
         <v>1385445</v>
@@ -833,7 +833,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7482533454895</v>
+        <v>2.74825382232666</v>
       </c>
       <c r="H16" t="n">
         <v>1094217</v>
@@ -891,7 +891,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G18" t="n">
-        <v>2.73896336555481</v>
+        <v>2.73896360397339</v>
       </c>
       <c r="H18" t="n">
         <v>900919</v>
@@ -920,7 +920,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G19" t="n">
-        <v>2.72657752037048</v>
+        <v>2.72657704353333</v>
       </c>
       <c r="H19" t="n">
         <v>765235</v>
@@ -949,7 +949,7 @@
         <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2.70954561233521</v>
+        <v>2.70954537391663</v>
       </c>
       <c r="H20" t="n">
         <v>1434225</v>
@@ -978,7 +978,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G21" t="n">
-        <v>2.76992988586426</v>
+        <v>2.76993012428284</v>
       </c>
       <c r="H21" t="n">
         <v>691660</v>
@@ -1007,7 +1007,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G22" t="n">
-        <v>2.74206018447876</v>
+        <v>2.74206042289734</v>
       </c>
       <c r="H22" t="n">
         <v>585827</v>
@@ -1036,7 +1036,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63213014602661</v>
+        <v>2.63213038444519</v>
       </c>
       <c r="H23" t="n">
         <v>529297</v>
@@ -1065,7 +1065,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G24" t="n">
-        <v>2.55006980895996</v>
+        <v>2.55006957054138</v>
       </c>
       <c r="H24" t="n">
         <v>965335</v>
@@ -1123,7 +1123,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G26" t="n">
-        <v>2.55316662788391</v>
+        <v>2.55316615104675</v>
       </c>
       <c r="H26" t="n">
         <v>2005520</v>
@@ -1152,7 +1152,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G27" t="n">
-        <v>2.43859124183655</v>
+        <v>2.43859100341797</v>
       </c>
       <c r="H27" t="n">
         <v>2592460</v>
@@ -1181,7 +1181,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.39988303184509</v>
+        <v>2.39988327026367</v>
       </c>
       <c r="H28" t="n">
         <v>2628393</v>
@@ -1239,7 +1239,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G30" t="n">
-        <v>2.2729218006134</v>
+        <v>2.27292156219482</v>
       </c>
       <c r="H30" t="n">
         <v>2979842</v>
@@ -1297,7 +1297,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G32" t="n">
-        <v>2.41381812095642</v>
+        <v>2.41381788253784</v>
       </c>
       <c r="H32" t="n">
         <v>2892184</v>
@@ -1355,7 +1355,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G34" t="n">
-        <v>2.60116362571716</v>
+        <v>2.60116386413574</v>
       </c>
       <c r="H34" t="n">
         <v>2832395</v>
@@ -1413,7 +1413,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G36" t="n">
-        <v>2.53768277168274</v>
+        <v>2.5376832485199</v>
       </c>
       <c r="H36" t="n">
         <v>1099387</v>
@@ -1442,7 +1442,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G37" t="n">
-        <v>2.62438869476318</v>
+        <v>2.6243884563446</v>
       </c>
       <c r="H37" t="n">
         <v>1413624</v>
@@ -1471,7 +1471,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G38" t="n">
-        <v>2.63987159729004</v>
+        <v>2.63987183570862</v>
       </c>
       <c r="H38" t="n">
         <v>1416246</v>
@@ -1529,7 +1529,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G40" t="n">
-        <v>2.62129211425781</v>
+        <v>2.62129163742065</v>
       </c>
       <c r="H40" t="n">
         <v>924194</v>
@@ -1587,7 +1587,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G42" t="n">
-        <v>2.77302670478821</v>
+        <v>2.77302646636963</v>
       </c>
       <c r="H42" t="n">
         <v>1241614</v>
@@ -1616,7 +1616,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>2.84115219116211</v>
+        <v>2.84115242958069</v>
       </c>
       <c r="H43" t="n">
         <v>992208</v>
@@ -1645,7 +1645,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G44" t="n">
-        <v>2.85199046134949</v>
+        <v>2.85199069976807</v>
       </c>
       <c r="H44" t="n">
         <v>1524438</v>
@@ -1703,7 +1703,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G46" t="n">
-        <v>2.91701936721802</v>
+        <v>2.9170196056366</v>
       </c>
       <c r="H46" t="n">
         <v>1310637</v>
@@ -1732,7 +1732,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87366700172424</v>
+        <v>2.87366652488708</v>
       </c>
       <c r="H47" t="n">
         <v>1022713</v>
@@ -1761,7 +1761,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G48" t="n">
-        <v>2.8225724697113</v>
+        <v>2.82257223129272</v>
       </c>
       <c r="H48" t="n">
         <v>1053721</v>
@@ -1790,7 +1790,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.80244421958923</v>
+        <v>2.80244469642639</v>
       </c>
       <c r="H49" t="n">
         <v>851655</v>
@@ -1877,7 +1877,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G52" t="n">
-        <v>2.88914966583252</v>
+        <v>2.88915014266968</v>
       </c>
       <c r="H52" t="n">
         <v>1341195</v>
@@ -1906,7 +1906,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G53" t="n">
-        <v>2.91701936721802</v>
+        <v>2.9170196056366</v>
       </c>
       <c r="H53" t="n">
         <v>764014</v>
@@ -1935,7 +1935,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89069771766663</v>
+        <v>2.89069867134094</v>
       </c>
       <c r="H54" t="n">
         <v>839673</v>
@@ -1964,7 +1964,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>2.85199046134949</v>
+        <v>2.85199069976807</v>
       </c>
       <c r="H55" t="n">
         <v>3876711</v>
@@ -2022,7 +2022,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G57" t="n">
-        <v>2.85199046134949</v>
+        <v>2.85199069976807</v>
       </c>
       <c r="H57" t="n">
         <v>1362718</v>
@@ -2138,7 +2138,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.73277044296265</v>
+        <v>2.73276996612549</v>
       </c>
       <c r="H61" t="n">
         <v>652481</v>
@@ -2167,7 +2167,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>2.87211871147156</v>
+        <v>2.87211847305298</v>
       </c>
       <c r="H62" t="n">
         <v>1273096</v>
@@ -2196,7 +2196,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G63" t="n">
-        <v>2.87521529197693</v>
+        <v>2.87521505355835</v>
       </c>
       <c r="H63" t="n">
         <v>1458208</v>
@@ -2225,7 +2225,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>2.87211871147156</v>
+        <v>2.87211847305298</v>
       </c>
       <c r="H64" t="n">
         <v>1060756</v>
@@ -2254,7 +2254,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G65" t="n">
-        <v>2.77921962738037</v>
+        <v>2.77921986579895</v>
       </c>
       <c r="H65" t="n">
         <v>1268914</v>
@@ -2283,7 +2283,7 @@
         <v>3.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.70954561233521</v>
+        <v>2.70954537391663</v>
       </c>
       <c r="H66" t="n">
         <v>781074</v>
@@ -2312,7 +2312,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G67" t="n">
-        <v>2.71109414100647</v>
+        <v>2.71109437942505</v>
       </c>
       <c r="H67" t="n">
         <v>574845</v>
@@ -2341,7 +2341,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G68" t="n">
-        <v>2.72657752037048</v>
+        <v>2.72657704353333</v>
       </c>
       <c r="H68" t="n">
         <v>1070111</v>
@@ -2370,7 +2370,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G69" t="n">
-        <v>2.76992988586426</v>
+        <v>2.76993012428284</v>
       </c>
       <c r="H69" t="n">
         <v>1029308</v>
@@ -2399,7 +2399,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G70" t="n">
-        <v>2.82412099838257</v>
+        <v>2.82412052154541</v>
       </c>
       <c r="H70" t="n">
         <v>925444</v>
@@ -2428,7 +2428,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80244421958923</v>
+        <v>2.80244469642639</v>
       </c>
       <c r="H71" t="n">
         <v>1384237</v>
@@ -2457,7 +2457,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>2.86437678337097</v>
+        <v>2.86437726020813</v>
       </c>
       <c r="H72" t="n">
         <v>2605699</v>
@@ -2515,7 +2515,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G74" t="n">
-        <v>2.84115219116211</v>
+        <v>2.84115242958069</v>
       </c>
       <c r="H74" t="n">
         <v>539769</v>
@@ -2573,7 +2573,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.87986016273499</v>
+        <v>2.87985968589783</v>
       </c>
       <c r="H76" t="n">
         <v>593773</v>
@@ -2602,7 +2602,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G77" t="n">
-        <v>2.88605308532715</v>
+        <v>2.88605332374573</v>
       </c>
       <c r="H77" t="n">
         <v>824413</v>
@@ -2631,7 +2631,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G78" t="n">
-        <v>2.89843964576721</v>
+        <v>2.89843988418579</v>
       </c>
       <c r="H78" t="n">
         <v>973280</v>
@@ -2660,7 +2660,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G79" t="n">
-        <v>2.87521529197693</v>
+        <v>2.87521505355835</v>
       </c>
       <c r="H79" t="n">
         <v>1011988</v>
@@ -2689,7 +2689,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G80" t="n">
-        <v>2.85353875160217</v>
+        <v>2.85353899002075</v>
       </c>
       <c r="H80" t="n">
         <v>489744</v>
@@ -2718,7 +2718,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G81" t="n">
-        <v>2.85199046134949</v>
+        <v>2.85199069976807</v>
       </c>
       <c r="H81" t="n">
         <v>1284292</v>
@@ -2747,7 +2747,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>2.87211871147156</v>
+        <v>2.87211847305298</v>
       </c>
       <c r="H82" t="n">
         <v>647080</v>
@@ -2776,7 +2776,7 @@
         <v>3.88800001144409</v>
       </c>
       <c r="G83" t="n">
-        <v>3.00991821289062</v>
+        <v>3.00991797447205</v>
       </c>
       <c r="H83" t="n">
         <v>2440016</v>
@@ -2805,7 +2805,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G84" t="n">
-        <v>2.95882391929626</v>
+        <v>2.95882368087769</v>
       </c>
       <c r="H84" t="n">
         <v>1543779</v>
@@ -2834,7 +2834,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G85" t="n">
-        <v>2.98978972434998</v>
+        <v>2.98979020118713</v>
       </c>
       <c r="H85" t="n">
         <v>771249</v>
@@ -2892,7 +2892,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G87" t="n">
-        <v>2.91856813430786</v>
+        <v>2.91856741905212</v>
       </c>
       <c r="H87" t="n">
         <v>413653</v>
@@ -2921,7 +2921,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G88" t="n">
-        <v>2.87366700172424</v>
+        <v>2.87366652488708</v>
       </c>
       <c r="H88" t="n">
         <v>401319</v>
@@ -2950,7 +2950,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G89" t="n">
-        <v>2.83960342407227</v>
+        <v>2.83960390090942</v>
       </c>
       <c r="H89" t="n">
         <v>589749</v>
@@ -2979,7 +2979,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>2.80244421958923</v>
+        <v>2.80244469642639</v>
       </c>
       <c r="H90" t="n">
         <v>352951</v>
@@ -3008,7 +3008,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G91" t="n">
-        <v>2.81328272819519</v>
+        <v>2.81328248977661</v>
       </c>
       <c r="H91" t="n">
         <v>397299</v>
@@ -3037,7 +3037,7 @@
         <v>3.69199991226196</v>
       </c>
       <c r="G92" t="n">
-        <v>2.85818362236023</v>
+        <v>2.85818386077881</v>
       </c>
       <c r="H92" t="n">
         <v>520677</v>
@@ -3124,7 +3124,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>2.87986016273499</v>
+        <v>2.87985968589783</v>
       </c>
       <c r="H95" t="n">
         <v>502468</v>
@@ -3153,7 +3153,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G96" t="n">
-        <v>2.91701936721802</v>
+        <v>2.9170196056366</v>
       </c>
       <c r="H96" t="n">
         <v>1488002</v>
@@ -3182,7 +3182,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G97" t="n">
-        <v>2.88605308532715</v>
+        <v>2.88605332374573</v>
       </c>
       <c r="H97" t="n">
         <v>857610</v>
@@ -3211,7 +3211,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G98" t="n">
-        <v>2.84115219116211</v>
+        <v>2.84115242958069</v>
       </c>
       <c r="H98" t="n">
         <v>1366830</v>
@@ -3240,7 +3240,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G99" t="n">
-        <v>2.84579706192017</v>
+        <v>2.84579730033875</v>
       </c>
       <c r="H99" t="n">
         <v>552258</v>
@@ -3327,7 +3327,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G102" t="n">
-        <v>2.49516010284424</v>
+        <v>2.49515962600708</v>
       </c>
       <c r="H102" t="n">
         <v>6755386</v>
@@ -3356,7 +3356,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G103" t="n">
-        <v>2.45759153366089</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H103" t="n">
         <v>4846198</v>
@@ -3385,7 +3385,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G104" t="n">
-        <v>2.4732449054718</v>
+        <v>2.47324514389038</v>
       </c>
       <c r="H104" t="n">
         <v>4700172</v>
@@ -3414,7 +3414,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G105" t="n">
-        <v>2.46854877471924</v>
+        <v>2.4685492515564</v>
       </c>
       <c r="H105" t="n">
         <v>2374462</v>
@@ -3443,7 +3443,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>2.4184582233429</v>
+        <v>2.41845774650574</v>
       </c>
       <c r="H106" t="n">
         <v>2536181</v>
@@ -3530,7 +3530,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G109" t="n">
-        <v>2.34958291053772</v>
+        <v>2.3495831489563</v>
       </c>
       <c r="H109" t="n">
         <v>3325389</v>
@@ -3559,7 +3559,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G110" t="n">
-        <v>2.40750074386597</v>
+        <v>2.40750050544739</v>
       </c>
       <c r="H110" t="n">
         <v>3042621</v>
@@ -3617,7 +3617,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G112" t="n">
-        <v>2.44663381576538</v>
+        <v>2.44663405418396</v>
       </c>
       <c r="H112" t="n">
         <v>2559071</v>
@@ -3675,7 +3675,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>2.35271334648132</v>
+        <v>2.3527135848999</v>
       </c>
       <c r="H114" t="n">
         <v>1983083</v>
@@ -3704,7 +3704,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G115" t="n">
-        <v>2.24940061569214</v>
+        <v>2.24940085411072</v>
       </c>
       <c r="H115" t="n">
         <v>2114026</v>
@@ -3733,7 +3733,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G116" t="n">
-        <v>2.18052554130554</v>
+        <v>2.18052530288696</v>
       </c>
       <c r="H116" t="n">
         <v>1635751</v>
@@ -3762,7 +3762,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G117" t="n">
-        <v>2.11634659767151</v>
+        <v>2.11634635925293</v>
       </c>
       <c r="H117" t="n">
         <v>2151270</v>
@@ -3791,7 +3791,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G118" t="n">
-        <v>2.05060124397278</v>
+        <v>2.05060195922852</v>
       </c>
       <c r="H118" t="n">
         <v>2040356</v>
@@ -3907,7 +3907,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G122" t="n">
-        <v>2.21026682853699</v>
+        <v>2.21026706695557</v>
       </c>
       <c r="H122" t="n">
         <v>1579649</v>
@@ -3936,7 +3936,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G123" t="n">
-        <v>2.28696870803833</v>
+        <v>2.28696894645691</v>
       </c>
       <c r="H123" t="n">
         <v>1894721</v>
@@ -3965,7 +3965,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G124" t="n">
-        <v>2.00990295410156</v>
+        <v>2.00990271568298</v>
       </c>
       <c r="H124" t="n">
         <v>2255357</v>
@@ -3994,7 +3994,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G125" t="n">
-        <v>1.9723345041275</v>
+        <v>1.97233486175537</v>
       </c>
       <c r="H125" t="n">
         <v>1416724</v>
@@ -4023,7 +4023,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G126" t="n">
-        <v>1.93946218490601</v>
+        <v>1.93946242332458</v>
       </c>
       <c r="H126" t="n">
         <v>1598076</v>
@@ -4052,7 +4052,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G127" t="n">
-        <v>1.97389984130859</v>
+        <v>1.97390007972717</v>
       </c>
       <c r="H127" t="n">
         <v>2900139</v>
@@ -4081,7 +4081,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G128" t="n">
-        <v>1.9864227771759</v>
+        <v>1.98642301559448</v>
       </c>
       <c r="H128" t="n">
         <v>1698763</v>
@@ -4110,7 +4110,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G129" t="n">
-        <v>2.15078377723694</v>
+        <v>2.15078353881836</v>
       </c>
       <c r="H129" t="n">
         <v>2569377</v>
@@ -4139,7 +4139,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G130" t="n">
-        <v>2.12260770797729</v>
+        <v>2.12260818481445</v>
       </c>
       <c r="H130" t="n">
         <v>1365226</v>
@@ -4226,7 +4226,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G133" t="n">
-        <v>2.00990295410156</v>
+        <v>2.00990271568298</v>
       </c>
       <c r="H133" t="n">
         <v>2375724</v>
@@ -4255,7 +4255,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.11321592330933</v>
+        <v>2.11321544647217</v>
       </c>
       <c r="H134" t="n">
         <v>2706963</v>
@@ -4284,7 +4284,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G135" t="n">
-        <v>2.17582964897156</v>
+        <v>2.17582941055298</v>
       </c>
       <c r="H135" t="n">
         <v>2019536</v>
@@ -4342,7 +4342,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G137" t="n">
-        <v>2.16487240791321</v>
+        <v>2.16487193107605</v>
       </c>
       <c r="H137" t="n">
         <v>746737</v>
@@ -4371,7 +4371,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G138" t="n">
-        <v>2.21026682853699</v>
+        <v>2.21026706695557</v>
       </c>
       <c r="H138" t="n">
         <v>738553</v>
@@ -4429,7 +4429,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G140" t="n">
-        <v>2.18991804122925</v>
+        <v>2.18991732597351</v>
       </c>
       <c r="H140" t="n">
         <v>492382</v>
@@ -4458,7 +4458,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G141" t="n">
-        <v>2.17426443099976</v>
+        <v>2.17426419258118</v>
       </c>
       <c r="H141" t="n">
         <v>1357980</v>
@@ -4487,7 +4487,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G142" t="n">
-        <v>2.14608764648438</v>
+        <v>2.14608812332153</v>
       </c>
       <c r="H142" t="n">
         <v>760877</v>
@@ -4545,7 +4545,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G144" t="n">
-        <v>2.11478090286255</v>
+        <v>2.11478066444397</v>
       </c>
       <c r="H144" t="n">
         <v>1356729</v>
@@ -4574,7 +4574,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G145" t="n">
-        <v>2.14765310287476</v>
+        <v>2.14765334129333</v>
       </c>
       <c r="H145" t="n">
         <v>979578</v>
@@ -4603,7 +4603,7 @@
         <v>2.74600005149841</v>
       </c>
       <c r="G146" t="n">
-        <v>2.14921855926514</v>
+        <v>2.14921879768372</v>
       </c>
       <c r="H146" t="n">
         <v>1633106</v>
@@ -4632,7 +4632,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G147" t="n">
-        <v>2.20400547981262</v>
+        <v>2.2040057182312</v>
       </c>
       <c r="H147" t="n">
         <v>1296535</v>
@@ -4661,7 +4661,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G148" t="n">
-        <v>2.07564735412598</v>
+        <v>2.07564759254456</v>
       </c>
       <c r="H148" t="n">
         <v>6229742</v>
@@ -4690,7 +4690,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G149" t="n">
-        <v>2.11791205406189</v>
+        <v>2.11791181564331</v>
       </c>
       <c r="H149" t="n">
         <v>3166446</v>
@@ -4719,7 +4719,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G150" t="n">
-        <v>2.06782054901123</v>
+        <v>2.06782102584839</v>
       </c>
       <c r="H150" t="n">
         <v>2120646</v>
@@ -4748,7 +4748,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G151" t="n">
-        <v>1.97859597206116</v>
+        <v>1.97859621047974</v>
       </c>
       <c r="H151" t="n">
         <v>1640032</v>
@@ -4777,7 +4777,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>1.94885468482971</v>
+        <v>1.94885456562042</v>
       </c>
       <c r="H152" t="n">
         <v>1298678</v>
@@ -4806,7 +4806,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>1.94102764129639</v>
+        <v>1.94102787971497</v>
       </c>
       <c r="H153" t="n">
         <v>1093413</v>
@@ -4835,7 +4835,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G154" t="n">
-        <v>1.96137726306915</v>
+        <v>1.96137702465057</v>
       </c>
       <c r="H154" t="n">
         <v>876363</v>
@@ -4864,7 +4864,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G155" t="n">
-        <v>2.01146841049194</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H155" t="n">
         <v>1272598</v>
@@ -4893,7 +4893,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G156" t="n">
-        <v>2.00207662582397</v>
+        <v>2.00207614898682</v>
       </c>
       <c r="H156" t="n">
         <v>1568347</v>
@@ -4922,7 +4922,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>1.99581456184387</v>
+        <v>1.99581491947174</v>
       </c>
       <c r="H157" t="n">
         <v>930572</v>
@@ -5038,7 +5038,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G161" t="n">
-        <v>2.05216717720032</v>
+        <v>2.05216693878174</v>
       </c>
       <c r="H161" t="n">
         <v>1296754</v>
@@ -5067,7 +5067,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G162" t="n">
-        <v>2.07721281051636</v>
+        <v>2.07721328735352</v>
       </c>
       <c r="H162" t="n">
         <v>1353910</v>
@@ -5096,7 +5096,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>2.05060124397278</v>
+        <v>2.05060195922852</v>
       </c>
       <c r="H163" t="n">
         <v>982101</v>
@@ -5125,7 +5125,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>2.05842876434326</v>
+        <v>2.05842900276184</v>
       </c>
       <c r="H164" t="n">
         <v>1061581</v>
@@ -5154,7 +5154,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G165" t="n">
-        <v>2.09756255149841</v>
+        <v>2.09756207466125</v>
       </c>
       <c r="H165" t="n">
         <v>837027</v>
@@ -5183,7 +5183,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.11321592330933</v>
+        <v>2.11321544647217</v>
       </c>
       <c r="H166" t="n">
         <v>813589</v>
@@ -5241,7 +5241,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G168" t="n">
-        <v>2.09756255149841</v>
+        <v>2.09756207466125</v>
       </c>
       <c r="H168" t="n">
         <v>697763</v>
@@ -5328,7 +5328,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G171" t="n">
-        <v>2.1570451259613</v>
+        <v>2.15704536437988</v>
       </c>
       <c r="H171" t="n">
         <v>898895</v>
@@ -5357,7 +5357,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.13669562339783</v>
+        <v>2.13669586181641</v>
       </c>
       <c r="H172" t="n">
         <v>1131229</v>
@@ -5444,7 +5444,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G175" t="n">
-        <v>2.14608764648438</v>
+        <v>2.14608812332153</v>
       </c>
       <c r="H175" t="n">
         <v>554785</v>
@@ -5473,7 +5473,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G176" t="n">
-        <v>2.17582964897156</v>
+        <v>2.17582941055298</v>
       </c>
       <c r="H176" t="n">
         <v>876827</v>
@@ -5502,7 +5502,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>2.14765310287476</v>
+        <v>2.14765334129333</v>
       </c>
       <c r="H177" t="n">
         <v>959389</v>
@@ -5531,7 +5531,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G178" t="n">
-        <v>2.15078377723694</v>
+        <v>2.15078353881836</v>
       </c>
       <c r="H178" t="n">
         <v>548611</v>
@@ -5560,7 +5560,7 @@
         <v>2.64400005340576</v>
       </c>
       <c r="G179" t="n">
-        <v>2.06938600540161</v>
+        <v>2.06938624382019</v>
       </c>
       <c r="H179" t="n">
         <v>1178028</v>
@@ -5589,7 +5589,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>2.01146841049194</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H180" t="n">
         <v>939604</v>
@@ -5618,7 +5618,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G181" t="n">
-        <v>2.00207662582397</v>
+        <v>2.00207614898682</v>
       </c>
       <c r="H181" t="n">
         <v>923059</v>
@@ -5734,7 +5734,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G185" t="n">
-        <v>1.92850518226624</v>
+        <v>1.92850482463837</v>
       </c>
       <c r="H185" t="n">
         <v>1274216</v>
@@ -5763,7 +5763,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>1.92537450790405</v>
+        <v>1.92537438869476</v>
       </c>
       <c r="H186" t="n">
         <v>703328</v>
@@ -5792,7 +5792,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>1.98798811435699</v>
+        <v>1.98798799514771</v>
       </c>
       <c r="H187" t="n">
         <v>900283</v>
@@ -5821,7 +5821,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G188" t="n">
-        <v>1.97859597206116</v>
+        <v>1.97859621047974</v>
       </c>
       <c r="H188" t="n">
         <v>375877</v>
@@ -5850,7 +5850,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G189" t="n">
-        <v>1.91754758358002</v>
+        <v>1.91754770278931</v>
       </c>
       <c r="H189" t="n">
         <v>786779</v>
@@ -5879,7 +5879,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>1.92537450790405</v>
+        <v>1.92537438869476</v>
       </c>
       <c r="H190" t="n">
         <v>1867839</v>
@@ -5908,7 +5908,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G191" t="n">
-        <v>2.0552978515625</v>
+        <v>2.05529761314392</v>
       </c>
       <c r="H191" t="n">
         <v>3388408</v>
@@ -5937,7 +5937,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G192" t="n">
-        <v>1.99268424510956</v>
+        <v>1.99268412590027</v>
       </c>
       <c r="H192" t="n">
         <v>1798626</v>
@@ -5995,7 +5995,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G194" t="n">
-        <v>1.9535505771637</v>
+        <v>1.95355045795441</v>
       </c>
       <c r="H194" t="n">
         <v>944804</v>
@@ -6024,7 +6024,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G195" t="n">
-        <v>1.94885468482971</v>
+        <v>1.94885456562042</v>
       </c>
       <c r="H195" t="n">
         <v>460629</v>
@@ -6111,7 +6111,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G198" t="n">
-        <v>1.9676388502121</v>
+        <v>1.96763896942139</v>
       </c>
       <c r="H198" t="n">
         <v>843471</v>
@@ -6140,7 +6140,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>1.9723345041275</v>
+        <v>1.97233486175537</v>
       </c>
       <c r="H199" t="n">
         <v>1375593</v>
@@ -6169,7 +6169,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G200" t="n">
-        <v>1.9676388502121</v>
+        <v>1.96763896942139</v>
       </c>
       <c r="H200" t="n">
         <v>746930</v>
@@ -6198,7 +6198,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G201" t="n">
-        <v>1.93320119380951</v>
+        <v>1.93320083618164</v>
       </c>
       <c r="H201" t="n">
         <v>830606</v>
@@ -6227,7 +6227,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G202" t="n">
-        <v>1.93320119380951</v>
+        <v>1.93320083618164</v>
       </c>
       <c r="H202" t="n">
         <v>1085623</v>
@@ -6256,7 +6256,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G203" t="n">
-        <v>1.9676388502121</v>
+        <v>1.96763896942139</v>
       </c>
       <c r="H203" t="n">
         <v>470437</v>
@@ -6285,7 +6285,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96450781822205</v>
+        <v>1.96450769901276</v>
       </c>
       <c r="H204" t="n">
         <v>817690</v>
@@ -6314,7 +6314,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G205" t="n">
-        <v>2.00207662582397</v>
+        <v>2.00207614898682</v>
       </c>
       <c r="H205" t="n">
         <v>1166619</v>
@@ -6343,7 +6343,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G206" t="n">
-        <v>2.07721281051636</v>
+        <v>2.07721328735352</v>
       </c>
       <c r="H206" t="n">
         <v>1910349</v>
@@ -6372,7 +6372,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>2.08973574638367</v>
+        <v>2.08973526954651</v>
       </c>
       <c r="H207" t="n">
         <v>859886</v>
@@ -6430,7 +6430,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G209" t="n">
-        <v>2.1038236618042</v>
+        <v>2.10382342338562</v>
       </c>
       <c r="H209" t="n">
         <v>987784</v>
@@ -6459,7 +6459,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G210" t="n">
-        <v>2.08660483360291</v>
+        <v>2.08660459518433</v>
       </c>
       <c r="H210" t="n">
         <v>726475</v>
@@ -6488,7 +6488,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>2.08973574638367</v>
+        <v>2.08973526954651</v>
       </c>
       <c r="H211" t="n">
         <v>544659</v>
@@ -6517,7 +6517,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G212" t="n">
-        <v>2.03338313102722</v>
+        <v>2.0333833694458</v>
       </c>
       <c r="H212" t="n">
         <v>1605178</v>
@@ -6546,7 +6546,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G213" t="n">
-        <v>1.97859597206116</v>
+        <v>1.97859621047974</v>
       </c>
       <c r="H213" t="n">
         <v>1439805</v>
@@ -6575,7 +6575,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>1.98798811435699</v>
+        <v>1.98798799514771</v>
       </c>
       <c r="H214" t="n">
         <v>951415</v>
@@ -6604,7 +6604,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G215" t="n">
-        <v>1.96137726306915</v>
+        <v>1.96137702465057</v>
       </c>
       <c r="H215" t="n">
         <v>535801</v>
@@ -6633,7 +6633,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G216" t="n">
-        <v>1.93163549900055</v>
+        <v>1.93163573741913</v>
       </c>
       <c r="H216" t="n">
         <v>1190452</v>
@@ -6691,7 +6691,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89563274383545</v>
+        <v>1.89563286304474</v>
       </c>
       <c r="H218" t="n">
         <v>762448</v>
@@ -6720,7 +6720,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G219" t="n">
-        <v>1.93163549900055</v>
+        <v>1.93163573741913</v>
       </c>
       <c r="H219" t="n">
         <v>511910</v>
@@ -6778,7 +6778,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>2.05842876434326</v>
+        <v>2.05842900276184</v>
       </c>
       <c r="H221" t="n">
         <v>7385474</v>
@@ -6836,7 +6836,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G223" t="n">
-        <v>2.03025221824646</v>
+        <v>2.03025269508362</v>
       </c>
       <c r="H223" t="n">
         <v>2200910</v>
@@ -6865,7 +6865,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G224" t="n">
-        <v>2.16330671310425</v>
+        <v>2.16330647468567</v>
       </c>
       <c r="H224" t="n">
         <v>3314695</v>
@@ -6894,7 +6894,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G225" t="n">
-        <v>2.14765310287476</v>
+        <v>2.14765334129333</v>
       </c>
       <c r="H225" t="n">
         <v>2264389</v>
@@ -6952,7 +6952,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G227" t="n">
-        <v>2.08660483360291</v>
+        <v>2.08660459518433</v>
       </c>
       <c r="H227" t="n">
         <v>977540</v>
@@ -7010,7 +7010,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G229" t="n">
-        <v>1.99581456184387</v>
+        <v>1.99581491947174</v>
       </c>
       <c r="H229" t="n">
         <v>1137034</v>
@@ -7039,7 +7039,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G230" t="n">
-        <v>2.01146841049194</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H230" t="n">
         <v>871707</v>
@@ -7068,7 +7068,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G231" t="n">
-        <v>2.01146841049194</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H231" t="n">
         <v>940946</v>
@@ -7097,7 +7097,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>1.99581456184387</v>
+        <v>1.99581491947174</v>
       </c>
       <c r="H232" t="n">
         <v>459440</v>
@@ -7155,7 +7155,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>1.92537450790405</v>
+        <v>1.92537438869476</v>
       </c>
       <c r="H234" t="n">
         <v>1382971</v>
@@ -7184,7 +7184,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G235" t="n">
-        <v>1.9676388502121</v>
+        <v>1.96763896942139</v>
       </c>
       <c r="H235" t="n">
         <v>925158</v>
@@ -7213,7 +7213,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G236" t="n">
-        <v>2.03807926177979</v>
+        <v>2.03807902336121</v>
       </c>
       <c r="H236" t="n">
         <v>1447942</v>
@@ -7242,7 +7242,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G237" t="n">
-        <v>2.03807926177979</v>
+        <v>2.03807902336121</v>
       </c>
       <c r="H237" t="n">
         <v>614516</v>
@@ -7300,7 +7300,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G239" t="n">
-        <v>2.09756255149841</v>
+        <v>2.09756207466125</v>
       </c>
       <c r="H239" t="n">
         <v>1527580</v>
@@ -7358,7 +7358,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G241" t="n">
-        <v>2.23687791824341</v>
+        <v>2.23687767982483</v>
       </c>
       <c r="H241" t="n">
         <v>3252090</v>
@@ -7387,7 +7387,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G242" t="n">
-        <v>2.26192355155945</v>
+        <v>2.26192331314087</v>
       </c>
       <c r="H242" t="n">
         <v>2116747</v>
@@ -7416,7 +7416,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G243" t="n">
-        <v>2.24626994132996</v>
+        <v>2.24627041816711</v>
       </c>
       <c r="H243" t="n">
         <v>2334527</v>
@@ -7445,7 +7445,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G244" t="n">
-        <v>2.26192355155945</v>
+        <v>2.26192331314087</v>
       </c>
       <c r="H244" t="n">
         <v>1572345</v>
@@ -7503,7 +7503,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G246" t="n">
-        <v>2.34958291053772</v>
+        <v>2.3495831489563</v>
       </c>
       <c r="H246" t="n">
         <v>3285193</v>
@@ -7532,7 +7532,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G247" t="n">
-        <v>2.37775921821594</v>
+        <v>2.37775897979736</v>
       </c>
       <c r="H247" t="n">
         <v>1476950</v>
@@ -7677,7 +7677,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G252" t="n">
-        <v>2.4200234413147</v>
+        <v>2.42002296447754</v>
       </c>
       <c r="H252" t="n">
         <v>2194065</v>
@@ -7706,7 +7706,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G253" t="n">
-        <v>2.39028167724609</v>
+        <v>2.39028143882751</v>
       </c>
       <c r="H253" t="n">
         <v>1171723</v>
@@ -7735,7 +7735,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G254" t="n">
-        <v>2.39654302597046</v>
+        <v>2.39654350280762</v>
       </c>
       <c r="H254" t="n">
         <v>358245</v>
@@ -7793,7 +7793,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32923316955566</v>
+        <v>2.32923293113708</v>
       </c>
       <c r="H256" t="n">
         <v>542985</v>
@@ -7822,7 +7822,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G257" t="n">
-        <v>2.34958291053772</v>
+        <v>2.3495831489563</v>
       </c>
       <c r="H257" t="n">
         <v>574581</v>
@@ -7851,7 +7851,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G258" t="n">
-        <v>2.43098044395447</v>
+        <v>2.43098068237305</v>
       </c>
       <c r="H258" t="n">
         <v>1363312</v>
@@ -7880,7 +7880,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G259" t="n">
-        <v>2.47794079780579</v>
+        <v>2.47794103622437</v>
       </c>
       <c r="H259" t="n">
         <v>1728143</v>
@@ -7909,7 +7909,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G260" t="n">
-        <v>2.48576831817627</v>
+        <v>2.48576760292053</v>
       </c>
       <c r="H260" t="n">
         <v>1766326</v>
@@ -7938,7 +7938,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G261" t="n">
-        <v>2.45759153366089</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H261" t="n">
         <v>853673</v>
@@ -7967,7 +7967,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G262" t="n">
-        <v>2.49359488487244</v>
+        <v>2.49359464645386</v>
       </c>
       <c r="H262" t="n">
         <v>455999</v>
@@ -7996,7 +7996,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G263" t="n">
-        <v>2.42315411567688</v>
+        <v>2.4231538772583</v>
       </c>
       <c r="H263" t="n">
         <v>982274</v>
@@ -8025,7 +8025,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G264" t="n">
-        <v>2.45759153366089</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H264" t="n">
         <v>879469</v>
@@ -8054,7 +8054,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G265" t="n">
-        <v>2.48576831817627</v>
+        <v>2.48576760292053</v>
       </c>
       <c r="H265" t="n">
         <v>829436</v>
@@ -8083,7 +8083,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G266" t="n">
-        <v>2.47011399269104</v>
+        <v>2.47011423110962</v>
       </c>
       <c r="H266" t="n">
         <v>903243</v>
@@ -8112,7 +8112,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.44976496696472</v>
+        <v>2.4497652053833</v>
       </c>
       <c r="H267" t="n">
         <v>771245</v>
@@ -8141,7 +8141,7 @@
         <v>3.1159999370575</v>
       </c>
       <c r="G268" t="n">
-        <v>2.43880748748779</v>
+        <v>2.43880701065063</v>
       </c>
       <c r="H268" t="n">
         <v>962333</v>
@@ -8228,7 +8228,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G271" t="n">
-        <v>2.42315411567688</v>
+        <v>2.4231538772583</v>
       </c>
       <c r="H271" t="n">
         <v>1200352</v>
@@ -8257,7 +8257,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G272" t="n">
-        <v>2.40280437469482</v>
+        <v>2.4028046131134</v>
       </c>
       <c r="H272" t="n">
         <v>626345</v>
@@ -8286,7 +8286,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G273" t="n">
-        <v>2.38402056694031</v>
+        <v>2.38402032852173</v>
       </c>
       <c r="H273" t="n">
         <v>1065395</v>
@@ -8344,7 +8344,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G275" t="n">
-        <v>2.42628455162048</v>
+        <v>2.42628479003906</v>
       </c>
       <c r="H275" t="n">
         <v>900916</v>
@@ -8373,7 +8373,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G276" t="n">
-        <v>2.35897469520569</v>
+        <v>2.35897493362427</v>
       </c>
       <c r="H276" t="n">
         <v>1343547</v>
@@ -8402,7 +8402,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G277" t="n">
-        <v>2.33862519264221</v>
+        <v>2.33862495422363</v>
       </c>
       <c r="H277" t="n">
         <v>900267</v>
@@ -8431,7 +8431,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.30888414382935</v>
+        <v>2.30888390541077</v>
       </c>
       <c r="H278" t="n">
         <v>1234287</v>
@@ -8460,7 +8460,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G279" t="n">
-        <v>2.2556619644165</v>
+        <v>2.25566220283508</v>
       </c>
       <c r="H279" t="n">
         <v>863160</v>
@@ -8576,7 +8576,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>2.23061609268188</v>
+        <v>2.23061656951904</v>
       </c>
       <c r="H283" t="n">
         <v>840338</v>
@@ -8605,7 +8605,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.24626994132996</v>
+        <v>2.24627041816711</v>
       </c>
       <c r="H284" t="n">
         <v>930384</v>
@@ -8634,7 +8634,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G285" t="n">
-        <v>2.23844289779663</v>
+        <v>2.23844313621521</v>
       </c>
       <c r="H285" t="n">
         <v>543762</v>
@@ -8692,7 +8692,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G287" t="n">
-        <v>2.33862519264221</v>
+        <v>2.33862495422363</v>
       </c>
       <c r="H287" t="n">
         <v>1633765</v>
@@ -8750,7 +8750,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>2.41063141822815</v>
+        <v>2.41063117980957</v>
       </c>
       <c r="H289" t="n">
         <v>1135351</v>
@@ -8779,7 +8779,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G290" t="n">
-        <v>2.4200234413147</v>
+        <v>2.42002296447754</v>
       </c>
       <c r="H290" t="n">
         <v>2382345</v>
@@ -8808,7 +8808,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G291" t="n">
-        <v>2.40437006950378</v>
+        <v>2.40436983108521</v>
       </c>
       <c r="H291" t="n">
         <v>2490093</v>
@@ -8895,7 +8895,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G294" t="n">
-        <v>2.33862519264221</v>
+        <v>2.33862495422363</v>
       </c>
       <c r="H294" t="n">
         <v>975000</v>
@@ -8924,7 +8924,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G295" t="n">
-        <v>2.35584378242493</v>
+        <v>2.35584402084351</v>
       </c>
       <c r="H295" t="n">
         <v>931240</v>
@@ -8953,7 +8953,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G296" t="n">
-        <v>2.33705973625183</v>
+        <v>2.33705997467041</v>
       </c>
       <c r="H296" t="n">
         <v>869769</v>
@@ -9243,7 +9243,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G306" t="n">
-        <v>2.49359488487244</v>
+        <v>2.49359464645386</v>
       </c>
       <c r="H306" t="n">
         <v>740808</v>
@@ -9272,7 +9272,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G307" t="n">
-        <v>2.49202942848206</v>
+        <v>2.49202919006348</v>
       </c>
       <c r="H307" t="n">
         <v>1006054</v>
@@ -9301,7 +9301,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>2.49672532081604</v>
+        <v>2.49672508239746</v>
       </c>
       <c r="H308" t="n">
         <v>948293</v>
@@ -9330,7 +9330,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>2.45759153366089</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H309" t="n">
         <v>969086</v>
@@ -9359,7 +9359,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G310" t="n">
-        <v>2.48889851570129</v>
+        <v>2.48889827728271</v>
       </c>
       <c r="H310" t="n">
         <v>615008</v>
@@ -9388,7 +9388,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G311" t="n">
-        <v>2.57342720031738</v>
+        <v>2.5734269618988</v>
       </c>
       <c r="H311" t="n">
         <v>2285027</v>
@@ -9446,7 +9446,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G313" t="n">
-        <v>2.46541857719421</v>
+        <v>2.46541833877563</v>
       </c>
       <c r="H313" t="n">
         <v>1680814</v>
@@ -9475,7 +9475,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G314" t="n">
-        <v>2.45132994651794</v>
+        <v>2.4513304233551</v>
       </c>
       <c r="H314" t="n">
         <v>1373872</v>
@@ -9504,7 +9504,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G315" t="n">
-        <v>2.44663381576538</v>
+        <v>2.44663405418396</v>
       </c>
       <c r="H315" t="n">
         <v>1339012</v>
@@ -9620,7 +9620,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G319" t="n">
-        <v>2.49359488487244</v>
+        <v>2.49359464645386</v>
       </c>
       <c r="H319" t="n">
         <v>961125</v>
@@ -9678,7 +9678,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G321" t="n">
-        <v>2.4419379234314</v>
+        <v>2.44193768501282</v>
       </c>
       <c r="H321" t="n">
         <v>1174861</v>
@@ -9707,7 +9707,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G322" t="n">
-        <v>2.4419379234314</v>
+        <v>2.44193768501282</v>
       </c>
       <c r="H322" t="n">
         <v>774694</v>
@@ -9736,7 +9736,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G323" t="n">
-        <v>2.40280437469482</v>
+        <v>2.4028046131134</v>
       </c>
       <c r="H323" t="n">
         <v>1842216</v>
@@ -9765,7 +9765,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G324" t="n">
-        <v>2.37619376182556</v>
+        <v>2.3761932849884</v>
       </c>
       <c r="H324" t="n">
         <v>1263595</v>
@@ -9794,7 +9794,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G325" t="n">
-        <v>2.41063141822815</v>
+        <v>2.41063117980957</v>
       </c>
       <c r="H325" t="n">
         <v>1145350</v>
@@ -9852,7 +9852,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.46541857719421</v>
+        <v>2.46541833877563</v>
       </c>
       <c r="H327" t="n">
         <v>1448459</v>
@@ -9881,7 +9881,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.4732449054718</v>
+        <v>2.47324514389038</v>
       </c>
       <c r="H328" t="n">
         <v>633759</v>
@@ -9910,7 +9910,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G329" t="n">
-        <v>2.43254590034485</v>
+        <v>2.43254613876343</v>
       </c>
       <c r="H329" t="n">
         <v>922372</v>
@@ -9939,7 +9939,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G330" t="n">
-        <v>2.39028167724609</v>
+        <v>2.39028143882751</v>
       </c>
       <c r="H330" t="n">
         <v>977417</v>
@@ -9968,7 +9968,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>2.36836695671082</v>
+        <v>2.36836671829224</v>
       </c>
       <c r="H331" t="n">
         <v>1134109</v>
@@ -10055,7 +10055,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G334" t="n">
-        <v>2.41532754898071</v>
+        <v>2.41532707214355</v>
       </c>
       <c r="H334" t="n">
         <v>1143561</v>
@@ -10113,7 +10113,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.42628455162048</v>
+        <v>2.42628479003906</v>
       </c>
       <c r="H336" t="n">
         <v>1305495</v>
@@ -10142,7 +10142,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G337" t="n">
-        <v>2.40750074386597</v>
+        <v>2.40750050544739</v>
       </c>
       <c r="H337" t="n">
         <v>4223005</v>
@@ -10171,7 +10171,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>2.44976496696472</v>
+        <v>2.4497652053833</v>
       </c>
       <c r="H338" t="n">
         <v>2519037</v>
@@ -10200,7 +10200,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G339" t="n">
-        <v>2.42315411567688</v>
+        <v>2.4231538772583</v>
       </c>
       <c r="H339" t="n">
         <v>1415458</v>
@@ -10287,7 +10287,7 @@
         <v>3.18199992179871</v>
       </c>
       <c r="G342" t="n">
-        <v>2.4904637336731</v>
+        <v>2.49046349525452</v>
       </c>
       <c r="H342" t="n">
         <v>772862</v>
@@ -10316,7 +10316,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G343" t="n">
-        <v>2.53272795677185</v>
+        <v>2.53272819519043</v>
       </c>
       <c r="H343" t="n">
         <v>1468440</v>
@@ -10345,7 +10345,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G344" t="n">
-        <v>2.55151176452637</v>
+        <v>2.55151224136353</v>
       </c>
       <c r="H344" t="n">
         <v>1479263</v>
@@ -10374,7 +10374,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G345" t="n">
-        <v>2.53742432594299</v>
+        <v>2.53742408752441</v>
       </c>
       <c r="H345" t="n">
         <v>1106003</v>
@@ -10403,7 +10403,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>2.62195253372192</v>
+        <v>2.6219527721405</v>
       </c>
       <c r="H346" t="n">
         <v>3151258</v>
@@ -10461,7 +10461,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>2.62195253372192</v>
+        <v>2.6219527721405</v>
       </c>
       <c r="H348" t="n">
         <v>2137829</v>
@@ -10490,7 +10490,7 @@
         <v>3.35400009155273</v>
       </c>
       <c r="G349" t="n">
-        <v>2.62508368492126</v>
+        <v>2.62508320808411</v>
       </c>
       <c r="H349" t="n">
         <v>1648864</v>
@@ -10606,7 +10606,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G353" t="n">
-        <v>2.43098044395447</v>
+        <v>2.43098068237305</v>
       </c>
       <c r="H353" t="n">
         <v>3812104</v>
@@ -10664,7 +10664,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G355" t="n">
-        <v>2.52040147781372</v>
+        <v>2.5204017162323</v>
       </c>
       <c r="H355" t="n">
         <v>818695</v>
@@ -10693,7 +10693,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G356" t="n">
-        <v>2.53791570663452</v>
+        <v>2.53791546821594</v>
       </c>
       <c r="H356" t="n">
         <v>987101</v>
@@ -10722,7 +10722,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G357" t="n">
-        <v>2.52517819404602</v>
+        <v>2.52517795562744</v>
       </c>
       <c r="H357" t="n">
         <v>545200</v>
@@ -10751,7 +10751,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>2.55542945861816</v>
+        <v>2.55542969703674</v>
       </c>
       <c r="H358" t="n">
         <v>654062</v>
@@ -10780,7 +10780,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>2.54746890068054</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H359" t="n">
         <v>1292142</v>
@@ -10867,7 +10867,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G362" t="n">
-        <v>2.54746890068054</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H362" t="n">
         <v>1966210</v>
@@ -10896,7 +10896,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G363" t="n">
-        <v>2.54269218444824</v>
+        <v>2.54269194602966</v>
       </c>
       <c r="H363" t="n">
         <v>1225998</v>
@@ -10925,7 +10925,7 @@
         <v>3.23399996757507</v>
       </c>
       <c r="G364" t="n">
-        <v>2.57453513145447</v>
+        <v>2.57453536987305</v>
       </c>
       <c r="H364" t="n">
         <v>1210712</v>
@@ -10954,7 +10954,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G365" t="n">
-        <v>2.56816697120667</v>
+        <v>2.56816673278809</v>
       </c>
       <c r="H365" t="n">
         <v>1146192</v>
@@ -11099,7 +11099,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>2.42009544372559</v>
+        <v>2.42009520530701</v>
       </c>
       <c r="H370" t="n">
         <v>1292806</v>
@@ -11128,7 +11128,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G371" t="n">
-        <v>2.49651908874512</v>
+        <v>2.49651885032654</v>
       </c>
       <c r="H371" t="n">
         <v>1521213</v>
@@ -11157,7 +11157,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G372" t="n">
-        <v>2.49651908874512</v>
+        <v>2.49651885032654</v>
       </c>
       <c r="H372" t="n">
         <v>623912</v>
@@ -11215,7 +11215,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G374" t="n">
-        <v>2.46785974502563</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H374" t="n">
         <v>2480349</v>
@@ -11244,7 +11244,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G375" t="n">
-        <v>2.43124008178711</v>
+        <v>2.43124032020569</v>
       </c>
       <c r="H375" t="n">
         <v>894485</v>
@@ -11360,7 +11360,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G379" t="n">
-        <v>2.41213440895081</v>
+        <v>2.41213417053223</v>
       </c>
       <c r="H379" t="n">
         <v>550090</v>
@@ -11418,7 +11418,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G381" t="n">
-        <v>2.49811100959778</v>
+        <v>2.49811124801636</v>
       </c>
       <c r="H381" t="n">
         <v>1455624</v>
@@ -11447,7 +11447,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G382" t="n">
-        <v>2.48696637153625</v>
+        <v>2.48696613311768</v>
       </c>
       <c r="H382" t="n">
         <v>1591740</v>
@@ -11505,7 +11505,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.41213440895081</v>
+        <v>2.41213417053223</v>
       </c>
       <c r="H384" t="n">
         <v>1637111</v>
@@ -11534,7 +11534,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.42805600166321</v>
+        <v>2.42805576324463</v>
       </c>
       <c r="H385" t="n">
         <v>929588</v>
@@ -11563,7 +11563,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G386" t="n">
-        <v>2.38984417915344</v>
+        <v>2.38984370231628</v>
       </c>
       <c r="H386" t="n">
         <v>1146093</v>
@@ -11592,7 +11592,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G387" t="n">
-        <v>2.39462018013</v>
+        <v>2.39462041854858</v>
       </c>
       <c r="H387" t="n">
         <v>722439</v>
@@ -11621,7 +11621,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>2.37232995033264</v>
+        <v>2.37233018875122</v>
       </c>
       <c r="H388" t="n">
         <v>814149</v>
@@ -11650,7 +11650,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G389" t="n">
-        <v>2.42646408081055</v>
+        <v>2.42646384239197</v>
       </c>
       <c r="H389" t="n">
         <v>1267851</v>
@@ -11679,7 +11679,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.43601655960083</v>
+        <v>2.43601679801941</v>
       </c>
       <c r="H390" t="n">
         <v>1532503</v>
@@ -11708,7 +11708,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G391" t="n">
-        <v>2.38188290596008</v>
+        <v>2.38188314437866</v>
       </c>
       <c r="H391" t="n">
         <v>1358951</v>
@@ -11737,7 +11737,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G392" t="n">
-        <v>2.44716143608093</v>
+        <v>2.44716191291809</v>
       </c>
       <c r="H392" t="n">
         <v>1622777</v>
@@ -11824,7 +11824,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G395" t="n">
-        <v>2.51084852218628</v>
+        <v>2.51084876060486</v>
       </c>
       <c r="H395" t="n">
         <v>4508418</v>
@@ -11853,7 +11853,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G396" t="n">
-        <v>2.48218989372253</v>
+        <v>2.48218965530396</v>
       </c>
       <c r="H396" t="n">
         <v>847477</v>
@@ -11882,7 +11882,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G397" t="n">
-        <v>2.49492692947388</v>
+        <v>2.49492716789246</v>
       </c>
       <c r="H397" t="n">
         <v>540455</v>
@@ -11911,7 +11911,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G398" t="n">
-        <v>2.46149110794067</v>
+        <v>2.46149158477783</v>
       </c>
       <c r="H398" t="n">
         <v>1226827</v>
@@ -11940,7 +11940,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G399" t="n">
-        <v>2.42805600166321</v>
+        <v>2.42805576324463</v>
       </c>
       <c r="H399" t="n">
         <v>1376064</v>
@@ -11969,7 +11969,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G400" t="n">
-        <v>2.42805600166321</v>
+        <v>2.42805576324463</v>
       </c>
       <c r="H400" t="n">
         <v>669595</v>
@@ -12027,7 +12027,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G402" t="n">
-        <v>2.46626806259155</v>
+        <v>2.46626782417297</v>
       </c>
       <c r="H402" t="n">
         <v>623443</v>
@@ -12056,7 +12056,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>2.39621233940125</v>
+        <v>2.39621257781982</v>
       </c>
       <c r="H403" t="n">
         <v>3318841</v>
@@ -12172,7 +12172,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G407" t="n">
-        <v>2.35481643676758</v>
+        <v>2.35481572151184</v>
       </c>
       <c r="H407" t="n">
         <v>777560</v>
@@ -12230,7 +12230,7 @@
         <v>3</v>
       </c>
       <c r="G409" t="n">
-        <v>2.38825154304504</v>
+        <v>2.38825178146362</v>
       </c>
       <c r="H409" t="n">
         <v>757900</v>
@@ -12317,7 +12317,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G412" t="n">
-        <v>2.31660437583923</v>
+        <v>2.31660413742065</v>
       </c>
       <c r="H412" t="n">
         <v>1233935</v>
@@ -12375,7 +12375,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G414" t="n">
-        <v>2.26724720001221</v>
+        <v>2.26724696159363</v>
       </c>
       <c r="H414" t="n">
         <v>1196625</v>
@@ -12404,7 +12404,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G415" t="n">
-        <v>2.30068254470825</v>
+        <v>2.30068278312683</v>
       </c>
       <c r="H415" t="n">
         <v>613532</v>
@@ -12433,7 +12433,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G416" t="n">
-        <v>2.33571004867554</v>
+        <v>2.33571028709412</v>
       </c>
       <c r="H416" t="n">
         <v>923284</v>
@@ -12462,7 +12462,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G417" t="n">
-        <v>2.33571004867554</v>
+        <v>2.33571028709412</v>
       </c>
       <c r="H417" t="n">
         <v>656989</v>
@@ -12520,7 +12520,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G419" t="n">
-        <v>2.28316855430603</v>
+        <v>2.28316879272461</v>
       </c>
       <c r="H419" t="n">
         <v>481583</v>
@@ -12578,7 +12578,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G421" t="n">
-        <v>2.33730244636536</v>
+        <v>2.33730268478394</v>
       </c>
       <c r="H421" t="n">
         <v>1265104</v>
@@ -12636,7 +12636,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G423" t="n">
-        <v>2.34844779968262</v>
+        <v>2.34844756126404</v>
       </c>
       <c r="H423" t="n">
         <v>685400</v>
@@ -12665,7 +12665,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G424" t="n">
-        <v>2.33252644538879</v>
+        <v>2.33252596855164</v>
       </c>
       <c r="H424" t="n">
         <v>735919</v>
@@ -12694,7 +12694,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="n">
-        <v>2.30864334106445</v>
+        <v>2.30864310264587</v>
       </c>
       <c r="H425" t="n">
         <v>805855</v>
@@ -12723,7 +12723,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G426" t="n">
-        <v>2.34844779968262</v>
+        <v>2.34844756126404</v>
       </c>
       <c r="H426" t="n">
         <v>723093</v>
@@ -12752,7 +12752,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G427" t="n">
-        <v>2.34844779968262</v>
+        <v>2.34844756126404</v>
       </c>
       <c r="H427" t="n">
         <v>1614230</v>
@@ -12810,7 +12810,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G429" t="n">
-        <v>2.40258097648621</v>
+        <v>2.40258073806763</v>
       </c>
       <c r="H429" t="n">
         <v>1162563</v>
@@ -12839,7 +12839,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G430" t="n">
-        <v>2.39462018013</v>
+        <v>2.39462041854858</v>
       </c>
       <c r="H430" t="n">
         <v>876149</v>
@@ -12868,7 +12868,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43920087814331</v>
+        <v>2.43920111656189</v>
       </c>
       <c r="H431" t="n">
         <v>1993777</v>
@@ -12897,7 +12897,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G432" t="n">
-        <v>2.46785974502563</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H432" t="n">
         <v>1295449</v>
@@ -12984,7 +12984,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G435" t="n">
-        <v>2.54746890068054</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H435" t="n">
         <v>1669492</v>
@@ -13013,7 +13013,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G436" t="n">
-        <v>2.54746890068054</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H436" t="n">
         <v>607602</v>
@@ -13042,7 +13042,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G437" t="n">
-        <v>2.59682559967041</v>
+        <v>2.59682583808899</v>
       </c>
       <c r="H437" t="n">
         <v>1443378</v>
@@ -13071,7 +13071,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G438" t="n">
-        <v>2.54746890068054</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H438" t="n">
         <v>650215</v>
@@ -13187,7 +13187,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G442" t="n">
-        <v>2.59364128112793</v>
+        <v>2.59364104270935</v>
       </c>
       <c r="H442" t="n">
         <v>856254</v>
@@ -13274,7 +13274,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61433982849121</v>
+        <v>2.61433959007263</v>
       </c>
       <c r="H445" t="n">
         <v>607795</v>
@@ -13332,7 +13332,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>2.61911606788635</v>
+        <v>2.61911582946777</v>
       </c>
       <c r="H447" t="n">
         <v>569921</v>
@@ -13419,7 +13419,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G450" t="n">
-        <v>2.60637879371643</v>
+        <v>2.60637855529785</v>
       </c>
       <c r="H450" t="n">
         <v>654933</v>
@@ -13477,7 +13477,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G452" t="n">
-        <v>2.64459085464478</v>
+        <v>2.6445906162262</v>
       </c>
       <c r="H452" t="n">
         <v>818061</v>
@@ -13506,7 +13506,7 @@
         <v>3.25600004196167</v>
       </c>
       <c r="G453" t="n">
-        <v>2.59204959869385</v>
+        <v>2.59204912185669</v>
       </c>
       <c r="H453" t="n">
         <v>921065</v>
@@ -13564,7 +13564,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G455" t="n">
-        <v>2.57612752914429</v>
+        <v>2.57612776756287</v>
       </c>
       <c r="H455" t="n">
         <v>580340</v>
@@ -13593,7 +13593,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G456" t="n">
-        <v>2.63822197914124</v>
+        <v>2.63822174072266</v>
       </c>
       <c r="H456" t="n">
         <v>1023456</v>
@@ -13651,7 +13651,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G458" t="n">
-        <v>2.70509338378906</v>
+        <v>2.70509314537048</v>
       </c>
       <c r="H458" t="n">
         <v>1265417</v>
@@ -13680,7 +13680,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G459" t="n">
-        <v>2.73852849006653</v>
+        <v>2.73852896690369</v>
       </c>
       <c r="H459" t="n">
         <v>794697</v>
@@ -13709,7 +13709,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G460" t="n">
-        <v>2.72419881820679</v>
+        <v>2.72419905662537</v>
       </c>
       <c r="H460" t="n">
         <v>716646</v>
@@ -13767,7 +13767,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G462" t="n">
-        <v>2.70509338378906</v>
+        <v>2.70509314537048</v>
       </c>
       <c r="H462" t="n">
         <v>996863</v>
@@ -13825,7 +13825,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G464" t="n">
-        <v>2.74330496788025</v>
+        <v>2.74330544471741</v>
       </c>
       <c r="H464" t="n">
         <v>810084</v>
@@ -13854,7 +13854,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G465" t="n">
-        <v>2.79903125762939</v>
+        <v>2.79903078079224</v>
       </c>
       <c r="H465" t="n">
         <v>1541603</v>
@@ -13912,7 +13912,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G467" t="n">
-        <v>2.81813716888428</v>
+        <v>2.8181369304657</v>
       </c>
       <c r="H467" t="n">
         <v>1990345</v>
@@ -13941,7 +13941,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>2.84998083114624</v>
+        <v>2.8499801158905</v>
       </c>
       <c r="H468" t="n">
         <v>1903251</v>
@@ -14028,7 +14028,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G471" t="n">
-        <v>2.94073414802551</v>
+        <v>2.94073367118835</v>
       </c>
       <c r="H471" t="n">
         <v>2019957</v>
@@ -14086,7 +14086,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G473" t="n">
-        <v>2.89296889305115</v>
+        <v>2.89296913146973</v>
       </c>
       <c r="H473" t="n">
         <v>877947</v>
@@ -14144,7 +14144,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>2.93754982948303</v>
+        <v>2.93754959106445</v>
       </c>
       <c r="H475" t="n">
         <v>968072</v>
@@ -14260,7 +14260,7 @@
         <v>3.4539999961853</v>
       </c>
       <c r="G479" t="n">
-        <v>2.74967360496521</v>
+        <v>2.74967384338379</v>
       </c>
       <c r="H479" t="n">
         <v>5446955</v>
@@ -14289,7 +14289,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G480" t="n">
-        <v>2.62548494338989</v>
+        <v>2.62548470497131</v>
       </c>
       <c r="H480" t="n">
         <v>2617438</v>
@@ -14318,7 +14318,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G481" t="n">
-        <v>2.54746890068054</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H481" t="n">
         <v>6308592</v>
@@ -14347,7 +14347,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G482" t="n">
-        <v>2.49492692947388</v>
+        <v>2.49492716789246</v>
       </c>
       <c r="H482" t="n">
         <v>4611280</v>
@@ -14376,7 +14376,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49174284934998</v>
+        <v>2.4917426109314</v>
       </c>
       <c r="H483" t="n">
         <v>3697265</v>
@@ -14405,7 +14405,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>2.46785974502563</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H484" t="n">
         <v>2655168</v>
@@ -14434,7 +14434,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G485" t="n">
-        <v>2.46785974502563</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H485" t="n">
         <v>1101568</v>
@@ -14550,7 +14550,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G489" t="n">
-        <v>2.46785974502563</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H489" t="n">
         <v>2139896</v>
@@ -14579,7 +14579,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G490" t="n">
-        <v>2.43760895729065</v>
+        <v>2.43760919570923</v>
       </c>
       <c r="H490" t="n">
         <v>1832928</v>
@@ -14608,7 +14608,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G491" t="n">
-        <v>2.44716143608093</v>
+        <v>2.44716191291809</v>
       </c>
       <c r="H491" t="n">
         <v>2154714</v>
@@ -14637,7 +14637,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G492" t="n">
-        <v>2.44716143608093</v>
+        <v>2.44716191291809</v>
       </c>
       <c r="H492" t="n">
         <v>1691378</v>
@@ -14666,7 +14666,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G493" t="n">
-        <v>2.46149110794067</v>
+        <v>2.46149158477783</v>
       </c>
       <c r="H493" t="n">
         <v>2679317</v>
@@ -14695,7 +14695,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G494" t="n">
-        <v>2.51721715927124</v>
+        <v>2.51721692085266</v>
       </c>
       <c r="H494" t="n">
         <v>3107216</v>
@@ -14724,7 +14724,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G495" t="n">
-        <v>2.53632378578186</v>
+        <v>2.53632354736328</v>
       </c>
       <c r="H495" t="n">
         <v>1344034</v>
@@ -14753,7 +14753,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G496" t="n">
-        <v>2.53154706954956</v>
+        <v>2.53154683113098</v>
       </c>
       <c r="H496" t="n">
         <v>2034742</v>
@@ -14782,7 +14782,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>2.48378133773804</v>
+        <v>2.4837818145752</v>
       </c>
       <c r="H497" t="n">
         <v>1452840</v>
@@ -14840,7 +14840,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G499" t="n">
-        <v>2.52040147781372</v>
+        <v>2.5204017162323</v>
       </c>
       <c r="H499" t="n">
         <v>1758820</v>
@@ -14869,7 +14869,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G500" t="n">
-        <v>2.53473091125488</v>
+        <v>2.53473114967346</v>
       </c>
       <c r="H500" t="n">
         <v>1330089</v>
@@ -14898,7 +14898,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G501" t="n">
-        <v>2.60160207748413</v>
+        <v>2.60160231590271</v>
       </c>
       <c r="H501" t="n">
         <v>1303907</v>
@@ -14956,7 +14956,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G503" t="n">
-        <v>2.53154706954956</v>
+        <v>2.53154683113098</v>
       </c>
       <c r="H503" t="n">
         <v>1750900</v>
@@ -15014,7 +15014,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G505" t="n">
-        <v>2.51562523841858</v>
+        <v>2.515625</v>
       </c>
       <c r="H505" t="n">
         <v>2056515</v>
@@ -15043,7 +15043,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G506" t="n">
-        <v>2.58886480331421</v>
+        <v>2.58886504173279</v>
       </c>
       <c r="H506" t="n">
         <v>4068179</v>
@@ -15072,7 +15072,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G507" t="n">
-        <v>2.56975889205933</v>
+        <v>2.56975865364075</v>
       </c>
       <c r="H507" t="n">
         <v>1259757</v>
@@ -15101,7 +15101,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G508" t="n">
-        <v>2.51084852218628</v>
+        <v>2.51084876060486</v>
       </c>
       <c r="H508" t="n">
         <v>2514530</v>
@@ -15159,7 +15159,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G510" t="n">
-        <v>2.52517819404602</v>
+        <v>2.52517795562744</v>
       </c>
       <c r="H510" t="n">
         <v>457099</v>
@@ -15188,7 +15188,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G511" t="n">
-        <v>2.56179809570312</v>
+        <v>2.56179785728455</v>
       </c>
       <c r="H511" t="n">
         <v>494732</v>
@@ -15217,7 +15217,7 @@
         <v>3.25799989700317</v>
       </c>
       <c r="G512" t="n">
-        <v>2.59364128112793</v>
+        <v>2.59364104270935</v>
       </c>
       <c r="H512" t="n">
         <v>863626</v>
@@ -15246,7 +15246,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G513" t="n">
-        <v>2.59841799736023</v>
+        <v>2.59841775894165</v>
       </c>
       <c r="H513" t="n">
         <v>975318</v>
@@ -15304,7 +15304,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G515" t="n">
-        <v>2.65892028808594</v>
+        <v>2.65892004966736</v>
       </c>
       <c r="H515" t="n">
         <v>1978965</v>
@@ -15362,7 +15362,7 @@
         <v>3.42400002479553</v>
       </c>
       <c r="G517" t="n">
-        <v>2.72579145431519</v>
+        <v>2.72579121589661</v>
       </c>
       <c r="H517" t="n">
         <v>1064648</v>
@@ -15391,7 +15391,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G518" t="n">
-        <v>2.74808144569397</v>
+        <v>2.74808120727539</v>
       </c>
       <c r="H518" t="n">
         <v>1415599</v>
@@ -15478,7 +15478,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G521" t="n">
-        <v>2.676433801651</v>
+        <v>2.67643404006958</v>
       </c>
       <c r="H521" t="n">
         <v>2011203</v>
@@ -15507,7 +15507,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G522" t="n">
-        <v>2.63822197914124</v>
+        <v>2.63822174072266</v>
       </c>
       <c r="H522" t="n">
         <v>1918826</v>
@@ -15565,7 +15565,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G524" t="n">
-        <v>2.63662981987</v>
+        <v>2.63663005828857</v>
       </c>
       <c r="H524" t="n">
         <v>542943</v>
@@ -15594,7 +15594,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G525" t="n">
-        <v>2.61911606788635</v>
+        <v>2.61911582946777</v>
       </c>
       <c r="H525" t="n">
         <v>990093</v>
@@ -15623,7 +15623,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G526" t="n">
-        <v>2.63185358047485</v>
+        <v>2.6318531036377</v>
       </c>
       <c r="H526" t="n">
         <v>1221618</v>
@@ -15681,7 +15681,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G528" t="n">
-        <v>2.54746890068054</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H528" t="n">
         <v>2145554</v>
@@ -15710,7 +15710,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G529" t="n">
-        <v>2.56816697120667</v>
+        <v>2.56816673278809</v>
       </c>
       <c r="H529" t="n">
         <v>1409532</v>
@@ -15768,7 +15768,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G531" t="n">
-        <v>2.56816697120667</v>
+        <v>2.56816673278809</v>
       </c>
       <c r="H531" t="n">
         <v>2024887</v>
@@ -15826,7 +15826,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G533" t="n">
-        <v>2.58090424537659</v>
+        <v>2.58090400695801</v>
       </c>
       <c r="H533" t="n">
         <v>735592</v>
@@ -15855,7 +15855,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G534" t="n">
-        <v>2.54746890068054</v>
+        <v>2.54746842384338</v>
       </c>
       <c r="H534" t="n">
         <v>2025801</v>
@@ -15884,7 +15884,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G535" t="n">
-        <v>2.41213440895081</v>
+        <v>2.41213417053223</v>
       </c>
       <c r="H535" t="n">
         <v>3237676</v>
@@ -15913,7 +15913,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G536" t="n">
-        <v>2.34526300430298</v>
+        <v>2.34526324272156</v>
       </c>
       <c r="H536" t="n">
         <v>2994862</v>
@@ -15942,7 +15942,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>2.23699593544006</v>
+        <v>2.23699569702148</v>
       </c>
       <c r="H537" t="n">
         <v>6215290</v>
@@ -15971,7 +15971,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G538" t="n">
-        <v>2.2131130695343</v>
+        <v>2.21311283111572</v>
       </c>
       <c r="H538" t="n">
         <v>4141672</v>
@@ -16087,7 +16087,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G542" t="n">
-        <v>2.01409220695496</v>
+        <v>2.01409244537354</v>
       </c>
       <c r="H542" t="n">
         <v>2601422</v>
@@ -16116,7 +16116,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G543" t="n">
-        <v>2.0570809841156</v>
+        <v>2.05708074569702</v>
       </c>
       <c r="H543" t="n">
         <v>1323647</v>
@@ -16145,7 +16145,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G544" t="n">
-        <v>2.07459473609924</v>
+        <v>2.07459449768066</v>
       </c>
       <c r="H544" t="n">
         <v>1590563</v>
@@ -16174,7 +16174,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G545" t="n">
-        <v>2.073002576828</v>
+        <v>2.07300233840942</v>
       </c>
       <c r="H545" t="n">
         <v>2877331</v>
@@ -16203,7 +16203,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G546" t="n">
-        <v>2.0570809841156</v>
+        <v>2.05708074569702</v>
       </c>
       <c r="H546" t="n">
         <v>755000</v>
@@ -16232,7 +16232,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G547" t="n">
-        <v>2.0570809841156</v>
+        <v>2.05708074569702</v>
       </c>
       <c r="H547" t="n">
         <v>813711</v>
@@ -16290,7 +16290,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.09370112419128</v>
+        <v>2.09370064735413</v>
       </c>
       <c r="H549" t="n">
         <v>2976419</v>
@@ -16348,7 +16348,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G551" t="n">
-        <v>2.01727652549744</v>
+        <v>2.01727676391602</v>
       </c>
       <c r="H551" t="n">
         <v>1462101</v>
@@ -16377,7 +16377,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G552" t="n">
-        <v>2.00294733047485</v>
+        <v>2.00294709205627</v>
       </c>
       <c r="H552" t="n">
         <v>2572034</v>
@@ -16406,7 +16406,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G553" t="n">
-        <v>1.98702538013458</v>
+        <v>1.98702573776245</v>
       </c>
       <c r="H553" t="n">
         <v>1328048</v>
@@ -16435,7 +16435,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G554" t="n">
-        <v>1.94881331920624</v>
+        <v>1.94881319999695</v>
       </c>
       <c r="H554" t="n">
         <v>1690849</v>
@@ -16464,7 +16464,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90741682052612</v>
+        <v>1.90741670131683</v>
       </c>
       <c r="H555" t="n">
         <v>2204356</v>
@@ -16493,7 +16493,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G556" t="n">
-        <v>1.89786410331726</v>
+        <v>1.89786398410797</v>
       </c>
       <c r="H556" t="n">
         <v>1534891</v>
@@ -16522,7 +16522,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>2.00613141059875</v>
+        <v>2.00613188743591</v>
       </c>
       <c r="H557" t="n">
         <v>4435894</v>
@@ -16580,7 +16580,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G559" t="n">
-        <v>2.03160572052002</v>
+        <v>2.03160619735718</v>
       </c>
       <c r="H559" t="n">
         <v>1090698</v>
@@ -16609,7 +16609,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G560" t="n">
-        <v>2.10325384140015</v>
+        <v>2.10325360298157</v>
       </c>
       <c r="H560" t="n">
         <v>2761128</v>
@@ -16638,7 +16638,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G561" t="n">
-        <v>2.03001403808594</v>
+        <v>2.03001379966736</v>
       </c>
       <c r="H561" t="n">
         <v>1984054</v>
@@ -16667,7 +16667,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G562" t="n">
-        <v>1.91856217384338</v>
+        <v>1.91856229305267</v>
       </c>
       <c r="H562" t="n">
         <v>4495971</v>
@@ -16696,7 +16696,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G563" t="n">
-        <v>1.80870282649994</v>
+        <v>1.80870270729065</v>
       </c>
       <c r="H563" t="n">
         <v>11295853</v>
@@ -16725,7 +16725,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G564" t="n">
-        <v>1.86442875862122</v>
+        <v>1.86442887783051</v>
       </c>
       <c r="H564" t="n">
         <v>5503208</v>
@@ -16812,7 +16812,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G567" t="n">
-        <v>1.9997626543045</v>
+        <v>1.99976289272308</v>
       </c>
       <c r="H567" t="n">
         <v>1325179</v>
@@ -16841,7 +16841,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G568" t="n">
-        <v>1.93766820430756</v>
+        <v>1.93766856193542</v>
       </c>
       <c r="H568" t="n">
         <v>2277688</v>
@@ -16870,7 +16870,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>1.8548755645752</v>
+        <v>1.85487532615662</v>
       </c>
       <c r="H569" t="n">
         <v>4051183</v>
@@ -16899,7 +16899,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94562911987305</v>
+        <v>1.94562888145447</v>
       </c>
       <c r="H570" t="n">
         <v>2696695</v>
@@ -16957,7 +16957,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91219341754913</v>
+        <v>1.91219365596771</v>
       </c>
       <c r="H572" t="n">
         <v>1317721</v>
@@ -17015,7 +17015,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G574" t="n">
-        <v>1.91856217384338</v>
+        <v>1.91856229305267</v>
       </c>
       <c r="H574" t="n">
         <v>1225403</v>
@@ -17044,7 +17044,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G575" t="n">
-        <v>1.89945590496063</v>
+        <v>1.89945602416992</v>
       </c>
       <c r="H575" t="n">
         <v>1034331</v>
@@ -17073,7 +17073,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G576" t="n">
-        <v>1.90582513809204</v>
+        <v>1.90582489967346</v>
       </c>
       <c r="H576" t="n">
         <v>1701979</v>
@@ -17102,7 +17102,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G577" t="n">
-        <v>1.95199751853943</v>
+        <v>1.95199763774872</v>
       </c>
       <c r="H577" t="n">
         <v>2027295</v>
@@ -17160,7 +17160,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.9265228509903</v>
+        <v>1.92652320861816</v>
       </c>
       <c r="H579" t="n">
         <v>722313</v>
@@ -17189,7 +17189,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G580" t="n">
-        <v>1.92970740795135</v>
+        <v>1.92970716953278</v>
       </c>
       <c r="H580" t="n">
         <v>1260607</v>
@@ -17218,7 +17218,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>1.90264093875885</v>
+        <v>1.90264070034027</v>
       </c>
       <c r="H581" t="n">
         <v>921579</v>
@@ -17247,7 +17247,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G582" t="n">
-        <v>1.90423262119293</v>
+        <v>1.90423274040222</v>
       </c>
       <c r="H582" t="n">
         <v>1500268</v>
@@ -17276,7 +17276,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G583" t="n">
-        <v>1.89627170562744</v>
+        <v>1.89627206325531</v>
       </c>
       <c r="H583" t="n">
         <v>944622</v>
@@ -17305,7 +17305,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G584" t="n">
-        <v>1.88194239139557</v>
+        <v>1.88194227218628</v>
       </c>
       <c r="H584" t="n">
         <v>1407864</v>
@@ -17334,7 +17334,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G585" t="n">
-        <v>1.8548755645752</v>
+        <v>1.85487532615662</v>
       </c>
       <c r="H585" t="n">
         <v>1777023</v>
@@ -17363,7 +17363,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G586" t="n">
-        <v>1.85009896755219</v>
+        <v>1.8500988483429</v>
       </c>
       <c r="H586" t="n">
         <v>1482418</v>
@@ -17392,7 +17392,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G587" t="n">
-        <v>1.86283624172211</v>
+        <v>1.86283648014069</v>
       </c>
       <c r="H587" t="n">
         <v>2223013</v>
@@ -17421,7 +17421,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>1.83099293708801</v>
+        <v>1.83099281787872</v>
       </c>
       <c r="H588" t="n">
         <v>2040960</v>
@@ -17450,7 +17450,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G589" t="n">
-        <v>1.81507134437561</v>
+        <v>1.81507158279419</v>
       </c>
       <c r="H589" t="n">
         <v>1297798</v>
@@ -17479,7 +17479,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G590" t="n">
-        <v>1.81507134437561</v>
+        <v>1.81507158279419</v>
       </c>
       <c r="H590" t="n">
         <v>1110350</v>
@@ -17508,7 +17508,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G591" t="n">
-        <v>1.80392634868622</v>
+        <v>1.80392611026764</v>
       </c>
       <c r="H591" t="n">
         <v>1332399</v>
@@ -17537,7 +17537,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G592" t="n">
-        <v>1.76412189006805</v>
+        <v>1.76412212848663</v>
       </c>
       <c r="H592" t="n">
         <v>2941699</v>
@@ -17566,7 +17566,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G593" t="n">
-        <v>1.78004360198975</v>
+        <v>1.78004372119904</v>
       </c>
       <c r="H593" t="n">
         <v>1670608</v>
@@ -17653,7 +17653,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G596" t="n">
-        <v>1.8914954662323</v>
+        <v>1.89149558544159</v>
       </c>
       <c r="H596" t="n">
         <v>13135214</v>
@@ -17682,7 +17682,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>1.8548755645752</v>
+        <v>1.85487532615662</v>
       </c>
       <c r="H597" t="n">
         <v>5522687</v>
@@ -17711,7 +17711,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G598" t="n">
-        <v>1.87238955497742</v>
+        <v>1.87238943576813</v>
       </c>
       <c r="H598" t="n">
         <v>2693236</v>
@@ -17740,7 +17740,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G599" t="n">
-        <v>1.85169112682343</v>
+        <v>1.85169124603271</v>
       </c>
       <c r="H599" t="n">
         <v>1869245</v>
@@ -17769,7 +17769,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G600" t="n">
-        <v>1.87238955497742</v>
+        <v>1.87238943576813</v>
       </c>
       <c r="H600" t="n">
         <v>1249089</v>
@@ -17856,7 +17856,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G603" t="n">
-        <v>1.8835346698761</v>
+        <v>1.88353431224823</v>
       </c>
       <c r="H603" t="n">
         <v>2143576</v>
@@ -17885,7 +17885,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.8548755645752</v>
+        <v>1.85487532615662</v>
       </c>
       <c r="H604" t="n">
         <v>1300520</v>
@@ -17914,7 +17914,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G605" t="n">
-        <v>1.81825566291809</v>
+        <v>1.8182555437088</v>
       </c>
       <c r="H605" t="n">
         <v>3157751</v>
@@ -17943,7 +17943,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G606" t="n">
-        <v>1.80074191093445</v>
+        <v>1.80074214935303</v>
       </c>
       <c r="H606" t="n">
         <v>1597477</v>
@@ -17972,7 +17972,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.77526712417603</v>
+        <v>1.77526724338531</v>
       </c>
       <c r="H607" t="n">
         <v>1953879</v>
@@ -18001,7 +18001,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G608" t="n">
-        <v>1.83642721176147</v>
+        <v>1.83642709255219</v>
       </c>
       <c r="H608" t="n">
         <v>1235443</v>
@@ -18117,7 +18117,7 @@
         <v>2.18799996376038</v>
       </c>
       <c r="G612" t="n">
-        <v>1.78423714637756</v>
+        <v>1.78423726558685</v>
       </c>
       <c r="H612" t="n">
         <v>1133216</v>
@@ -18233,7 +18233,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G616" t="n">
-        <v>1.71736896038055</v>
+        <v>1.71736884117126</v>
       </c>
       <c r="H616" t="n">
         <v>1661744</v>
@@ -18262,7 +18262,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G617" t="n">
-        <v>1.7858681678772</v>
+        <v>1.78586828708649</v>
       </c>
       <c r="H617" t="n">
         <v>2304857</v>
@@ -18320,7 +18320,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G619" t="n">
-        <v>1.76140403747559</v>
+        <v>1.76140439510345</v>
       </c>
       <c r="H619" t="n">
         <v>995750</v>
@@ -18378,7 +18378,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G621" t="n">
-        <v>1.76140403747559</v>
+        <v>1.76140439510345</v>
       </c>
       <c r="H621" t="n">
         <v>808647</v>
@@ -18407,7 +18407,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G622" t="n">
-        <v>1.7385710477829</v>
+        <v>1.73857116699219</v>
       </c>
       <c r="H622" t="n">
         <v>583631</v>
@@ -18436,7 +18436,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G623" t="n">
-        <v>1.76140403747559</v>
+        <v>1.76140439510345</v>
       </c>
       <c r="H623" t="n">
         <v>810246</v>
@@ -18465,7 +18465,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G624" t="n">
-        <v>1.76629686355591</v>
+        <v>1.7662969827652</v>
       </c>
       <c r="H624" t="n">
         <v>2399225</v>
@@ -18494,7 +18494,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G625" t="n">
-        <v>1.76629686355591</v>
+        <v>1.7662969827652</v>
       </c>
       <c r="H625" t="n">
         <v>566494</v>
@@ -18523,7 +18523,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G626" t="n">
-        <v>1.8445817232132</v>
+        <v>1.84458196163177</v>
       </c>
       <c r="H626" t="n">
         <v>1938784</v>
@@ -18552,7 +18552,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>1.86741471290588</v>
+        <v>1.86741459369659</v>
       </c>
       <c r="H627" t="n">
         <v>2849945</v>
@@ -18581,7 +18581,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G628" t="n">
-        <v>1.8445817232132</v>
+        <v>1.84458196163177</v>
       </c>
       <c r="H628" t="n">
         <v>450028</v>
@@ -18639,7 +18639,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G630" t="n">
-        <v>1.82664144039154</v>
+        <v>1.82664155960083</v>
       </c>
       <c r="H630" t="n">
         <v>683361</v>
@@ -18697,7 +18697,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G632" t="n">
-        <v>1.79239189624786</v>
+        <v>1.79239201545715</v>
       </c>
       <c r="H632" t="n">
         <v>2137127</v>
@@ -18726,7 +18726,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G633" t="n">
-        <v>1.75488030910492</v>
+        <v>1.7548805475235</v>
       </c>
       <c r="H633" t="n">
         <v>634287</v>
@@ -18755,7 +18755,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G634" t="n">
-        <v>1.77282059192657</v>
+        <v>1.77282071113586</v>
       </c>
       <c r="H634" t="n">
         <v>471187</v>
@@ -18813,7 +18813,7 @@
         <v>2.13800001144409</v>
       </c>
       <c r="G636" t="n">
-        <v>1.74346387386322</v>
+        <v>1.7434641122818</v>
       </c>
       <c r="H636" t="n">
         <v>489960</v>
@@ -18842,7 +18842,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G637" t="n">
-        <v>1.82011795043945</v>
+        <v>1.82011771202087</v>
       </c>
       <c r="H637" t="n">
         <v>2298555</v>
@@ -18871,7 +18871,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G638" t="n">
-        <v>1.88698577880859</v>
+        <v>1.8869856595993</v>
       </c>
       <c r="H638" t="n">
         <v>2351541</v>
@@ -18900,7 +18900,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G639" t="n">
-        <v>1.89187848567963</v>
+        <v>1.89187872409821</v>
       </c>
       <c r="H639" t="n">
         <v>1290827</v>
@@ -18929,7 +18929,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G640" t="n">
-        <v>1.81359422206879</v>
+        <v>1.8135941028595</v>
       </c>
       <c r="H640" t="n">
         <v>2559667</v>
@@ -18958,7 +18958,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G641" t="n">
-        <v>1.86578392982483</v>
+        <v>1.86578381061554</v>
       </c>
       <c r="H641" t="n">
         <v>1601256</v>
@@ -18987,7 +18987,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>1.87720024585724</v>
+        <v>1.87720048427582</v>
       </c>
       <c r="H642" t="n">
         <v>1729727</v>
@@ -19016,7 +19016,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G643" t="n">
-        <v>1.90655708312988</v>
+        <v>1.90655732154846</v>
       </c>
       <c r="H643" t="n">
         <v>1155916</v>
@@ -19045,7 +19045,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G644" t="n">
-        <v>1.88372397422791</v>
+        <v>1.88372385501862</v>
       </c>
       <c r="H644" t="n">
         <v>1335295</v>
@@ -19074,7 +19074,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G645" t="n">
-        <v>1.84295070171356</v>
+        <v>1.84295082092285</v>
       </c>
       <c r="H645" t="n">
         <v>1183341</v>
@@ -19103,7 +19103,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>1.86741471290588</v>
+        <v>1.86741459369659</v>
       </c>
       <c r="H646" t="n">
         <v>465309</v>
@@ -19132,7 +19132,7 @@
         <v>2.24200010299683</v>
       </c>
       <c r="G647" t="n">
-        <v>1.82827258110046</v>
+        <v>1.82827246189117</v>
       </c>
       <c r="H647" t="n">
         <v>550682</v>
@@ -19161,7 +19161,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G648" t="n">
-        <v>1.8168557882309</v>
+        <v>1.81685590744019</v>
       </c>
       <c r="H648" t="n">
         <v>605104</v>
@@ -19190,7 +19190,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G649" t="n">
-        <v>1.81196272373199</v>
+        <v>1.81196296215057</v>
       </c>
       <c r="H649" t="n">
         <v>492569</v>
@@ -19248,7 +19248,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G651" t="n">
-        <v>1.79239189624786</v>
+        <v>1.79239201545715</v>
       </c>
       <c r="H651" t="n">
         <v>2071396</v>
@@ -19306,7 +19306,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G653" t="n">
-        <v>1.77282059192657</v>
+        <v>1.77282071113586</v>
       </c>
       <c r="H653" t="n">
         <v>747019</v>
@@ -19335,7 +19335,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78749918937683</v>
+        <v>1.78749895095825</v>
       </c>
       <c r="H654" t="n">
         <v>659037</v>
@@ -19393,7 +19393,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G656" t="n">
-        <v>1.7385710477829</v>
+        <v>1.73857116699219</v>
       </c>
       <c r="H656" t="n">
         <v>3598224</v>
@@ -19422,7 +19422,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G657" t="n">
-        <v>1.79728472232819</v>
+        <v>1.79728484153748</v>
       </c>
       <c r="H657" t="n">
         <v>1981222</v>
@@ -19480,7 +19480,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G659" t="n">
-        <v>1.84295070171356</v>
+        <v>1.84295082092285</v>
       </c>
       <c r="H659" t="n">
         <v>912189</v>
@@ -19509,7 +19509,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G660" t="n">
-        <v>1.84131968021393</v>
+        <v>1.8413200378418</v>
       </c>
       <c r="H660" t="n">
         <v>617222</v>
@@ -19567,7 +19567,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G662" t="n">
-        <v>1.79239189624786</v>
+        <v>1.79239201545715</v>
       </c>
       <c r="H662" t="n">
         <v>897689</v>
@@ -19596,7 +19596,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G663" t="n">
-        <v>1.7907612323761</v>
+        <v>1.79076099395752</v>
       </c>
       <c r="H663" t="n">
         <v>561281</v>
@@ -19625,7 +19625,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G664" t="n">
-        <v>1.82011795043945</v>
+        <v>1.82011771202087</v>
       </c>
       <c r="H664" t="n">
         <v>676673</v>
@@ -19654,7 +19654,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G665" t="n">
-        <v>1.89187848567963</v>
+        <v>1.89187872409821</v>
       </c>
       <c r="H665" t="n">
         <v>4688332</v>
@@ -19683,7 +19683,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G666" t="n">
-        <v>1.88046193122864</v>
+        <v>1.88046205043793</v>
       </c>
       <c r="H666" t="n">
         <v>845679</v>
@@ -19712,7 +19712,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G667" t="n">
-        <v>1.85926008224487</v>
+        <v>1.85926032066345</v>
       </c>
       <c r="H667" t="n">
         <v>963738</v>
@@ -19741,7 +19741,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G668" t="n">
-        <v>1.86415266990662</v>
+        <v>1.86415278911591</v>
       </c>
       <c r="H668" t="n">
         <v>885313</v>
@@ -19770,7 +19770,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G669" t="n">
-        <v>1.85762929916382</v>
+        <v>1.85762941837311</v>
       </c>
       <c r="H669" t="n">
         <v>854370</v>
@@ -19828,7 +19828,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G671" t="n">
-        <v>1.90818774700165</v>
+        <v>1.90818810462952</v>
       </c>
       <c r="H671" t="n">
         <v>1160035</v>
@@ -19944,7 +19944,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G675" t="n">
-        <v>1.95548510551453</v>
+        <v>1.95548486709595</v>
       </c>
       <c r="H675" t="n">
         <v>2650527</v>
@@ -19973,7 +19973,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G676" t="n">
-        <v>1.9685320854187</v>
+        <v>1.96853232383728</v>
       </c>
       <c r="H676" t="n">
         <v>928396</v>
@@ -20002,7 +20002,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G677" t="n">
-        <v>1.9032951593399</v>
+        <v>1.90329527854919</v>
       </c>
       <c r="H677" t="n">
         <v>1584415</v>
@@ -20031,7 +20031,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G678" t="n">
-        <v>1.89024758338928</v>
+        <v>1.89024794101715</v>
       </c>
       <c r="H678" t="n">
         <v>886735</v>
@@ -20060,7 +20060,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G679" t="n">
-        <v>1.86415266990662</v>
+        <v>1.86415278911591</v>
       </c>
       <c r="H679" t="n">
         <v>868801</v>
@@ -20089,7 +20089,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G680" t="n">
-        <v>1.81359422206879</v>
+        <v>1.8135941028595</v>
       </c>
       <c r="H680" t="n">
         <v>1115411</v>
@@ -20118,7 +20118,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71084558963776</v>
+        <v>1.71084547042847</v>
       </c>
       <c r="H681" t="n">
         <v>2819967</v>
@@ -20234,7 +20234,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>1.82664144039154</v>
+        <v>1.82664155960083</v>
       </c>
       <c r="H685" t="n">
         <v>2020822</v>
@@ -20263,7 +20263,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G686" t="n">
-        <v>1.85436713695526</v>
+        <v>1.85436737537384</v>
       </c>
       <c r="H686" t="n">
         <v>826482</v>
@@ -20321,7 +20321,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G688" t="n">
-        <v>1.9032951593399</v>
+        <v>1.90329527854919</v>
       </c>
       <c r="H688" t="n">
         <v>523293</v>
@@ -20350,7 +20350,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G689" t="n">
-        <v>1.91308081150055</v>
+        <v>1.91308057308197</v>
       </c>
       <c r="H689" t="n">
         <v>689161</v>
@@ -20379,7 +20379,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G690" t="n">
-        <v>1.89840233325958</v>
+        <v>1.898402094841</v>
       </c>
       <c r="H690" t="n">
         <v>429766</v>
@@ -20408,7 +20408,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G691" t="n">
-        <v>1.86415266990662</v>
+        <v>1.86415278911591</v>
       </c>
       <c r="H691" t="n">
         <v>339281</v>
@@ -20437,7 +20437,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G692" t="n">
-        <v>1.88046193122864</v>
+        <v>1.88046205043793</v>
       </c>
       <c r="H692" t="n">
         <v>471227</v>
@@ -20466,7 +20466,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G693" t="n">
-        <v>1.84295070171356</v>
+        <v>1.84295082092285</v>
       </c>
       <c r="H693" t="n">
         <v>805042</v>
@@ -20495,7 +20495,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G694" t="n">
-        <v>1.8168557882309</v>
+        <v>1.81685590744019</v>
       </c>
       <c r="H694" t="n">
         <v>1394273</v>
@@ -20553,7 +20553,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>1.81359422206879</v>
+        <v>1.8135941028595</v>
       </c>
       <c r="H696" t="n">
         <v>998393</v>
@@ -20582,7 +20582,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G697" t="n">
-        <v>1.79402303695679</v>
+        <v>1.79402279853821</v>
       </c>
       <c r="H697" t="n">
         <v>672268</v>
@@ -20611,7 +20611,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G698" t="n">
-        <v>1.78749918937683</v>
+        <v>1.78749895095825</v>
       </c>
       <c r="H698" t="n">
         <v>796654</v>
@@ -20698,7 +20698,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G701" t="n">
-        <v>1.73041641712189</v>
+        <v>1.73041653633118</v>
       </c>
       <c r="H701" t="n">
         <v>811499</v>
@@ -20727,7 +20727,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G702" t="n">
-        <v>1.70105993747711</v>
+        <v>1.70105969905853</v>
       </c>
       <c r="H702" t="n">
         <v>929920</v>
@@ -20756,7 +20756,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G703" t="n">
-        <v>1.62929892539978</v>
+        <v>1.62929880619049</v>
       </c>
       <c r="H703" t="n">
         <v>2772603</v>
@@ -20785,7 +20785,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G704" t="n">
-        <v>1.65050113201141</v>
+        <v>1.65050089359283</v>
       </c>
       <c r="H704" t="n">
         <v>2017014</v>
@@ -20814,7 +20814,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G705" t="n">
-        <v>1.6619176864624</v>
+        <v>1.66191756725311</v>
       </c>
       <c r="H705" t="n">
         <v>6571728</v>
@@ -20843,7 +20843,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G706" t="n">
-        <v>1.61869788169861</v>
+        <v>1.61869776248932</v>
       </c>
       <c r="H706" t="n">
         <v>1091102</v>
@@ -20872,7 +20872,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G707" t="n">
-        <v>1.58607923984528</v>
+        <v>1.58607935905457</v>
       </c>
       <c r="H707" t="n">
         <v>1261183</v>
@@ -20901,7 +20901,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G708" t="n">
-        <v>1.57384717464447</v>
+        <v>1.57384729385376</v>
       </c>
       <c r="H708" t="n">
         <v>980940</v>
@@ -20988,7 +20988,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G711" t="n">
-        <v>1.48006892204285</v>
+        <v>1.48006880283356</v>
       </c>
       <c r="H711" t="n">
         <v>2169717</v>
@@ -21104,7 +21104,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G715" t="n">
-        <v>1.4857771396637</v>
+        <v>1.48577702045441</v>
       </c>
       <c r="H715" t="n">
         <v>1758890</v>
@@ -21133,7 +21133,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G716" t="n">
-        <v>1.50208628177643</v>
+        <v>1.50208652019501</v>
       </c>
       <c r="H716" t="n">
         <v>2096415</v>
@@ -21191,7 +21191,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>1.45968234539032</v>
+        <v>1.45968210697174</v>
       </c>
       <c r="H718" t="n">
         <v>1383440</v>
@@ -21249,7 +21249,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>1.53388941287994</v>
+        <v>1.53388953208923</v>
       </c>
       <c r="H720" t="n">
         <v>1295036</v>
@@ -21278,7 +21278,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G721" t="n">
-        <v>1.53470504283905</v>
+        <v>1.53470492362976</v>
       </c>
       <c r="H721" t="n">
         <v>621201</v>
@@ -21307,7 +21307,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G722" t="n">
-        <v>1.60483491420746</v>
+        <v>1.60483503341675</v>
       </c>
       <c r="H722" t="n">
         <v>1425242</v>
@@ -21336,7 +21336,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G723" t="n">
-        <v>1.57874023914337</v>
+        <v>1.57874000072479</v>
       </c>
       <c r="H723" t="n">
         <v>621410</v>
@@ -21365,7 +21365,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G724" t="n">
-        <v>1.58852553367615</v>
+        <v>1.58852577209473</v>
       </c>
       <c r="H724" t="n">
         <v>629415</v>
@@ -21452,7 +21452,7 @@
         <v>2</v>
       </c>
       <c r="G727" t="n">
-        <v>1.63092970848083</v>
+        <v>1.63092982769012</v>
       </c>
       <c r="H727" t="n">
         <v>594452</v>
@@ -21481,7 +21481,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G728" t="n">
-        <v>1.61706697940826</v>
+        <v>1.61706686019897</v>
       </c>
       <c r="H728" t="n">
         <v>586071</v>
@@ -21539,7 +21539,7 @@
         <v>2</v>
       </c>
       <c r="G730" t="n">
-        <v>1.63092970848083</v>
+        <v>1.63092982769012</v>
       </c>
       <c r="H730" t="n">
         <v>355011</v>
@@ -21568,7 +21568,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G731" t="n">
-        <v>1.61625158786774</v>
+        <v>1.61625146865845</v>
       </c>
       <c r="H731" t="n">
         <v>498536</v>
@@ -21626,7 +21626,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G733" t="n">
-        <v>1.51187205314636</v>
+        <v>1.51187193393707</v>
       </c>
       <c r="H733" t="n">
         <v>1759383</v>
@@ -21684,7 +21684,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G735" t="n">
-        <v>1.53144311904907</v>
+        <v>1.53144299983978</v>
       </c>
       <c r="H735" t="n">
         <v>977458</v>
@@ -21713,7 +21713,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G736" t="n">
-        <v>1.54285967350006</v>
+        <v>1.54285955429077</v>
       </c>
       <c r="H736" t="n">
         <v>867680</v>
@@ -21742,7 +21742,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G737" t="n">
-        <v>1.51676464080811</v>
+        <v>1.5167647600174</v>
       </c>
       <c r="H737" t="n">
         <v>745389</v>
@@ -21829,7 +21829,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G740" t="n">
-        <v>1.45234310626984</v>
+        <v>1.45234298706055</v>
       </c>
       <c r="H740" t="n">
         <v>352016</v>
@@ -21858,7 +21858,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G741" t="n">
-        <v>1.47191417217255</v>
+        <v>1.47191405296326</v>
       </c>
       <c r="H741" t="n">
         <v>414540</v>
@@ -21916,7 +21916,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G743" t="n">
-        <v>1.51676464080811</v>
+        <v>1.5167647600174</v>
       </c>
       <c r="H743" t="n">
         <v>805198</v>
@@ -21974,7 +21974,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G745" t="n">
-        <v>1.49800908565521</v>
+        <v>1.49800896644592</v>
       </c>
       <c r="H745" t="n">
         <v>859693</v>
@@ -22003,7 +22003,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>1.45152747631073</v>
+        <v>1.45152759552002</v>
       </c>
       <c r="H746" t="n">
         <v>1189559</v>
@@ -22119,7 +22119,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G750" t="n">
-        <v>1.4115697145462</v>
+        <v>1.41156983375549</v>
       </c>
       <c r="H750" t="n">
         <v>1042775</v>
@@ -22148,7 +22148,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G751" t="n">
-        <v>1.4115697145462</v>
+        <v>1.41156983375549</v>
       </c>
       <c r="H751" t="n">
         <v>519026</v>
@@ -22264,7 +22264,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G755" t="n">
-        <v>1.10087776184082</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H755" t="n">
         <v>12027281</v>
@@ -22322,7 +22322,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>1.03564047813416</v>
+        <v>1.03564035892487</v>
       </c>
       <c r="H757" t="n">
         <v>3305025</v>
@@ -22467,7 +22467,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G762" t="n">
-        <v>1.10087776184082</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H762" t="n">
         <v>2715888</v>
@@ -22496,7 +22496,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G763" t="n">
-        <v>1.15469825267792</v>
+        <v>1.15469837188721</v>
       </c>
       <c r="H763" t="n">
         <v>2560889</v>
@@ -22525,7 +22525,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G764" t="n">
-        <v>1.15388298034668</v>
+        <v>1.15388286113739</v>
       </c>
       <c r="H764" t="n">
         <v>1226156</v>
@@ -22554,7 +22554,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G765" t="n">
-        <v>1.1742696762085</v>
+        <v>1.17426955699921</v>
       </c>
       <c r="H765" t="n">
         <v>2107430</v>
@@ -22583,7 +22583,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>1.1742696762085</v>
+        <v>1.17426955699921</v>
       </c>
       <c r="H766" t="n">
         <v>1555652</v>
@@ -22612,7 +22612,7 @@
         <v>1.55099999904633</v>
       </c>
       <c r="G767" t="n">
-        <v>1.26478600502014</v>
+        <v>1.26478612422943</v>
       </c>
       <c r="H767" t="n">
         <v>2353519</v>
@@ -22670,7 +22670,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G769" t="n">
-        <v>1.30229759216309</v>
+        <v>1.3022974729538</v>
       </c>
       <c r="H769" t="n">
         <v>1170678</v>
@@ -22699,7 +22699,7 @@
         <v>1.66400003433228</v>
       </c>
       <c r="G770" t="n">
-        <v>1.35693359375</v>
+        <v>1.35693371295929</v>
       </c>
       <c r="H770" t="n">
         <v>1347520</v>
@@ -22728,7 +22728,7 @@
         <v>1.60899996757507</v>
       </c>
       <c r="G771" t="n">
-        <v>1.31208312511444</v>
+        <v>1.31208300590515</v>
       </c>
       <c r="H771" t="n">
         <v>1290857</v>
@@ -22757,7 +22757,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G772" t="n">
-        <v>1.30311298370361</v>
+        <v>1.30311286449432</v>
       </c>
       <c r="H772" t="n">
         <v>1651898</v>
@@ -22786,7 +22786,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G773" t="n">
-        <v>1.32920789718628</v>
+        <v>1.32920777797699</v>
       </c>
       <c r="H773" t="n">
         <v>2959691</v>
@@ -22815,7 +22815,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G774" t="n">
-        <v>1.33736252784729</v>
+        <v>1.337362408638</v>
       </c>
       <c r="H774" t="n">
         <v>798141</v>
@@ -22873,7 +22873,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.38629043102264</v>
+        <v>1.38629031181335</v>
       </c>
       <c r="H776" t="n">
         <v>2583893</v>
@@ -22902,7 +22902,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G777" t="n">
-        <v>1.39770674705505</v>
+        <v>1.39770698547363</v>
       </c>
       <c r="H777" t="n">
         <v>2242382</v>
@@ -22931,7 +22931,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G778" t="n">
-        <v>1.31045234203339</v>
+        <v>1.31045198440552</v>
       </c>
       <c r="H778" t="n">
         <v>3033007</v>
@@ -22960,7 +22960,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G779" t="n">
-        <v>1.33491611480713</v>
+        <v>1.33491599559784</v>
       </c>
       <c r="H779" t="n">
         <v>3214064</v>
@@ -22989,7 +22989,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G780" t="n">
-        <v>1.37813591957092</v>
+        <v>1.37813580036163</v>
       </c>
       <c r="H780" t="n">
         <v>3667223</v>
@@ -23018,7 +23018,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G781" t="n">
-        <v>1.435218334198</v>
+        <v>1.43521821498871</v>
       </c>
       <c r="H781" t="n">
         <v>2217306</v>
@@ -23047,7 +23047,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G782" t="n">
-        <v>1.50942540168762</v>
+        <v>1.50942552089691</v>
       </c>
       <c r="H782" t="n">
         <v>2051305</v>
@@ -23192,7 +23192,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G787" t="n">
-        <v>1.57547843456268</v>
+        <v>1.5754781961441</v>
       </c>
       <c r="H787" t="n">
         <v>2151732</v>
@@ -23279,7 +23279,7 @@
         <v>1.98199999332428</v>
       </c>
       <c r="G790" t="n">
-        <v>1.61625158786774</v>
+        <v>1.61625146865845</v>
       </c>
       <c r="H790" t="n">
         <v>1851199</v>
@@ -23308,7 +23308,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G791" t="n">
-        <v>1.53878235816956</v>
+        <v>1.53878223896027</v>
       </c>
       <c r="H791" t="n">
         <v>937385</v>
@@ -23366,7 +23366,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G793" t="n">
-        <v>1.53470504283905</v>
+        <v>1.53470492362976</v>
       </c>
       <c r="H793" t="n">
         <v>557746</v>
@@ -23395,7 +23395,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G794" t="n">
-        <v>1.5208420753479</v>
+        <v>1.52084195613861</v>
       </c>
       <c r="H794" t="n">
         <v>765785</v>
@@ -23424,7 +23424,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G795" t="n">
-        <v>1.67985773086548</v>
+        <v>1.67985761165619</v>
       </c>
       <c r="H795" t="n">
         <v>6571124</v>
@@ -23482,7 +23482,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G797" t="n">
-        <v>1.66681027412415</v>
+        <v>1.66681015491486</v>
       </c>
       <c r="H797" t="n">
         <v>631363</v>
@@ -23540,7 +23540,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G799" t="n">
-        <v>1.67985773086548</v>
+        <v>1.67985761165619</v>
       </c>
       <c r="H799" t="n">
         <v>508447</v>
@@ -23569,7 +23569,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G800" t="n">
-        <v>1.64071547985077</v>
+        <v>1.64071536064148</v>
       </c>
       <c r="H800" t="n">
         <v>489775</v>
@@ -23656,7 +23656,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G803" t="n">
-        <v>1.70595276355743</v>
+        <v>1.70595252513885</v>
       </c>
       <c r="H803" t="n">
         <v>1273027</v>
@@ -23685,7 +23685,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G804" t="n">
-        <v>1.69453620910645</v>
+        <v>1.69453608989716</v>
       </c>
       <c r="H804" t="n">
         <v>415996</v>
@@ -23714,7 +23714,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G805" t="n">
-        <v>1.70921432971954</v>
+        <v>1.70921444892883</v>
       </c>
       <c r="H805" t="n">
         <v>511806</v>
@@ -23772,7 +23772,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G807" t="n">
-        <v>1.69616711139679</v>
+        <v>1.69616687297821</v>
       </c>
       <c r="H807" t="n">
         <v>463656</v>
@@ -23801,7 +23801,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G808" t="n">
-        <v>1.67985773086548</v>
+        <v>1.67985761165619</v>
       </c>
       <c r="H808" t="n">
         <v>531129</v>
@@ -23830,7 +23830,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G809" t="n">
-        <v>1.69942915439606</v>
+        <v>1.69942903518677</v>
       </c>
       <c r="H809" t="n">
         <v>580157</v>
@@ -23859,7 +23859,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G810" t="n">
-        <v>1.68964338302612</v>
+        <v>1.68964302539825</v>
       </c>
       <c r="H810" t="n">
         <v>653322</v>
@@ -23888,7 +23888,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G811" t="n">
-        <v>1.65865552425385</v>
+        <v>1.65865564346313</v>
       </c>
       <c r="H811" t="n">
         <v>550811</v>
@@ -23917,7 +23917,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G812" t="n">
-        <v>1.65865552425385</v>
+        <v>1.65865564346313</v>
       </c>
       <c r="H812" t="n">
         <v>382456</v>
@@ -23946,7 +23946,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G813" t="n">
-        <v>1.64560794830322</v>
+        <v>1.64560806751251</v>
       </c>
       <c r="H813" t="n">
         <v>341000</v>
@@ -24004,7 +24004,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G815" t="n">
-        <v>1.66681027412415</v>
+        <v>1.66681015491486</v>
       </c>
       <c r="H815" t="n">
         <v>693096</v>
@@ -24062,7 +24062,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G817" t="n">
-        <v>1.64071547985077</v>
+        <v>1.64071536064148</v>
       </c>
       <c r="H817" t="n">
         <v>8186934</v>
@@ -24091,7 +24091,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G818" t="n">
-        <v>1.63582265377045</v>
+        <v>1.63582253456116</v>
       </c>
       <c r="H818" t="n">
         <v>1354848</v>
@@ -24120,7 +24120,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G819" t="n">
-        <v>1.60238873958588</v>
+        <v>1.6023885011673</v>
       </c>
       <c r="H819" t="n">
         <v>996560</v>
@@ -24236,7 +24236,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G823" t="n">
-        <v>1.67333424091339</v>
+        <v>1.67333388328552</v>
       </c>
       <c r="H823" t="n">
         <v>1131670</v>
@@ -24265,7 +24265,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G824" t="n">
-        <v>1.6619176864624</v>
+        <v>1.66191756725311</v>
       </c>
       <c r="H824" t="n">
         <v>1727495</v>
@@ -24294,7 +24294,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G825" t="n">
-        <v>1.67496502399445</v>
+        <v>1.67496490478516</v>
       </c>
       <c r="H825" t="n">
         <v>666086</v>
@@ -24352,7 +24352,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G827" t="n">
-        <v>1.70921432971954</v>
+        <v>1.70921444892883</v>
       </c>
       <c r="H827" t="n">
         <v>422823</v>
@@ -24381,7 +24381,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>1.68475067615509</v>
+        <v>1.68475043773651</v>
       </c>
       <c r="H828" t="n">
         <v>596412</v>
@@ -24410,7 +24410,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G829" t="n">
-        <v>1.70432162284851</v>
+        <v>1.70432150363922</v>
       </c>
       <c r="H829" t="n">
         <v>496963</v>
@@ -24439,7 +24439,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G830" t="n">
-        <v>1.71736896038055</v>
+        <v>1.71736884117126</v>
       </c>
       <c r="H830" t="n">
         <v>843159</v>
@@ -24468,7 +24468,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G831" t="n">
-        <v>1.88372397422791</v>
+        <v>1.88372385501862</v>
       </c>
       <c r="H831" t="n">
         <v>8604870</v>
@@ -24497,7 +24497,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G832" t="n">
-        <v>1.89187848567963</v>
+        <v>1.89187872409821</v>
       </c>
       <c r="H832" t="n">
         <v>3573577</v>
@@ -24526,7 +24526,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G833" t="n">
-        <v>1.81196272373199</v>
+        <v>1.81196296215057</v>
       </c>
       <c r="H833" t="n">
         <v>2500836</v>
@@ -24555,7 +24555,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G834" t="n">
-        <v>1.78260660171509</v>
+        <v>1.78260636329651</v>
       </c>
       <c r="H834" t="n">
         <v>1213282</v>
@@ -24642,7 +24642,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>1.7858681678772</v>
+        <v>1.78586828708649</v>
       </c>
       <c r="H837" t="n">
         <v>450642</v>
@@ -24671,7 +24671,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G838" t="n">
-        <v>1.7858681678772</v>
+        <v>1.78586828708649</v>
       </c>
       <c r="H838" t="n">
         <v>377864</v>
@@ -24700,7 +24700,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G839" t="n">
-        <v>1.76140403747559</v>
+        <v>1.76140439510345</v>
       </c>
       <c r="H839" t="n">
         <v>472267</v>
@@ -24758,7 +24758,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>1.67985773086548</v>
+        <v>1.67985761165619</v>
       </c>
       <c r="H841" t="n">
         <v>1113545</v>
@@ -24845,7 +24845,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G844" t="n">
-        <v>1.55182981491089</v>
+        <v>1.5518296957016</v>
       </c>
       <c r="H844" t="n">
         <v>4032631</v>
@@ -24903,7 +24903,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G846" t="n">
-        <v>1.51676464080811</v>
+        <v>1.5167647600174</v>
       </c>
       <c r="H846" t="n">
         <v>2988966</v>
@@ -24932,7 +24932,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G847" t="n">
-        <v>1.54775238037109</v>
+        <v>1.5477522611618</v>
       </c>
       <c r="H847" t="n">
         <v>1669046</v>
@@ -24961,7 +24961,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G848" t="n">
-        <v>1.52328848838806</v>
+        <v>1.52328836917877</v>
       </c>
       <c r="H848" t="n">
         <v>1102200</v>
@@ -25048,7 +25048,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G851" t="n">
-        <v>1.42543268203735</v>
+        <v>1.42543256282806</v>
       </c>
       <c r="H851" t="n">
         <v>880260</v>
@@ -25164,7 +25164,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G855" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H855" t="n">
         <v>367882</v>
@@ -25251,7 +25251,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G858" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H858" t="n">
         <v>480695</v>
@@ -25367,7 +25367,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G862" t="n">
-        <v>1.35204100608826</v>
+        <v>1.35204076766968</v>
       </c>
       <c r="H862" t="n">
         <v>465276</v>
@@ -25396,7 +25396,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G863" t="n">
-        <v>1.38221299648285</v>
+        <v>1.38221311569214</v>
       </c>
       <c r="H863" t="n">
         <v>444989</v>
@@ -25425,7 +25425,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G864" t="n">
-        <v>1.41483163833618</v>
+        <v>1.41483151912689</v>
       </c>
       <c r="H864" t="n">
         <v>442927</v>
@@ -25454,7 +25454,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G865" t="n">
-        <v>1.39770674705505</v>
+        <v>1.39770698547363</v>
       </c>
       <c r="H865" t="n">
         <v>690821</v>
@@ -25483,7 +25483,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G866" t="n">
-        <v>1.37487387657166</v>
+        <v>1.37487375736237</v>
       </c>
       <c r="H866" t="n">
         <v>389202</v>
@@ -25541,7 +25541,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G868" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H868" t="n">
         <v>929548</v>
@@ -25570,7 +25570,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G869" t="n">
-        <v>1.39770674705505</v>
+        <v>1.39770698547363</v>
       </c>
       <c r="H869" t="n">
         <v>452853</v>
@@ -25599,7 +25599,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G870" t="n">
-        <v>1.44989669322968</v>
+        <v>1.44989657402039</v>
       </c>
       <c r="H870" t="n">
         <v>1022788</v>
@@ -25628,7 +25628,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G871" t="n">
-        <v>1.47599136829376</v>
+        <v>1.47599148750305</v>
       </c>
       <c r="H871" t="n">
         <v>608455</v>
@@ -25686,7 +25686,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G873" t="n">
-        <v>1.47925329208374</v>
+        <v>1.47925341129303</v>
       </c>
       <c r="H873" t="n">
         <v>295354</v>
@@ -25773,7 +25773,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G876" t="n">
-        <v>1.51268744468689</v>
+        <v>1.5126873254776</v>
       </c>
       <c r="H876" t="n">
         <v>459318</v>
@@ -25831,7 +25831,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G878" t="n">
-        <v>1.47517621517181</v>
+        <v>1.47517597675323</v>
       </c>
       <c r="H878" t="n">
         <v>350064</v>
@@ -25860,7 +25860,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G879" t="n">
-        <v>1.45234310626984</v>
+        <v>1.45234298706055</v>
       </c>
       <c r="H879" t="n">
         <v>323343</v>
@@ -25889,7 +25889,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G880" t="n">
-        <v>1.47436058521271</v>
+        <v>1.47436046600342</v>
       </c>
       <c r="H880" t="n">
         <v>549520</v>
@@ -25976,7 +25976,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G883" t="n">
-        <v>1.45152747631073</v>
+        <v>1.45152759552002</v>
       </c>
       <c r="H883" t="n">
         <v>362785</v>
@@ -26005,7 +26005,7 @@
         <v>1.75199997425079</v>
       </c>
       <c r="G884" t="n">
-        <v>1.42869448661804</v>
+        <v>1.42869460582733</v>
       </c>
       <c r="H884" t="n">
         <v>364330</v>
@@ -26034,7 +26034,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G885" t="n">
-        <v>1.44989669322968</v>
+        <v>1.44989657402039</v>
       </c>
       <c r="H885" t="n">
         <v>2306619</v>
@@ -26063,7 +26063,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G886" t="n">
-        <v>1.44908118247986</v>
+        <v>1.44908106327057</v>
       </c>
       <c r="H886" t="n">
         <v>474750</v>
@@ -26150,7 +26150,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G889" t="n">
-        <v>1.44989669322968</v>
+        <v>1.44989657402039</v>
       </c>
       <c r="H889" t="n">
         <v>308646</v>
@@ -26179,7 +26179,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G890" t="n">
-        <v>1.46865224838257</v>
+        <v>1.46865236759186</v>
       </c>
       <c r="H890" t="n">
         <v>251671</v>
@@ -26208,7 +26208,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G891" t="n">
-        <v>1.52573478221893</v>
+        <v>1.52573490142822</v>
       </c>
       <c r="H891" t="n">
         <v>1176195</v>
@@ -26237,7 +26237,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G892" t="n">
-        <v>1.58689486980438</v>
+        <v>1.5868946313858</v>
       </c>
       <c r="H892" t="n">
         <v>2742260</v>
@@ -26324,7 +26324,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G895" t="n">
-        <v>1.50290179252625</v>
+        <v>1.50290191173553</v>
       </c>
       <c r="H895" t="n">
         <v>1736792</v>
@@ -26353,7 +26353,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G896" t="n">
-        <v>1.51676464080811</v>
+        <v>1.5167647600174</v>
       </c>
       <c r="H896" t="n">
         <v>516545</v>
@@ -26382,7 +26382,7 @@
         <v>1.84800004959106</v>
       </c>
       <c r="G897" t="n">
-        <v>1.50697910785675</v>
+        <v>1.50697922706604</v>
       </c>
       <c r="H897" t="n">
         <v>691347</v>
@@ -26440,7 +26440,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.435218334198</v>
+        <v>1.43521821498871</v>
       </c>
       <c r="H899" t="n">
         <v>1456465</v>
@@ -26469,7 +26469,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G900" t="n">
-        <v>1.38792109489441</v>
+        <v>1.3879212141037</v>
       </c>
       <c r="H900" t="n">
         <v>2095493</v>
@@ -26498,7 +26498,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G901" t="n">
-        <v>1.33246958255768</v>
+        <v>1.33246970176697</v>
       </c>
       <c r="H901" t="n">
         <v>3767205</v>
@@ -26556,7 +26556,7 @@
         <v>1.51300001144409</v>
       </c>
       <c r="G903" t="n">
-        <v>1.23379838466644</v>
+        <v>1.23379850387573</v>
       </c>
       <c r="H903" t="n">
         <v>1637956</v>
@@ -26643,7 +26643,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G906" t="n">
-        <v>1.33083879947662</v>
+        <v>1.33083868026733</v>
       </c>
       <c r="H906" t="n">
         <v>1628033</v>
@@ -26672,7 +26672,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G907" t="n">
-        <v>1.37732028961182</v>
+        <v>1.37732005119324</v>
       </c>
       <c r="H907" t="n">
         <v>2492653</v>
@@ -26701,7 +26701,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G908" t="n">
-        <v>1.35367166996002</v>
+        <v>1.35367178916931</v>
       </c>
       <c r="H908" t="n">
         <v>1043256</v>
@@ -26759,7 +26759,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G910" t="n">
-        <v>1.34388625621796</v>
+        <v>1.34388613700867</v>
       </c>
       <c r="H910" t="n">
         <v>687288</v>
@@ -26788,7 +26788,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G911" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H911" t="n">
         <v>3720832</v>
@@ -26875,7 +26875,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G914" t="n">
-        <v>1.54122877120972</v>
+        <v>1.54122865200043</v>
       </c>
       <c r="H914" t="n">
         <v>1837118</v>
@@ -26933,7 +26933,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G916" t="n">
-        <v>1.54122877120972</v>
+        <v>1.54122865200043</v>
       </c>
       <c r="H916" t="n">
         <v>871736</v>
@@ -26962,7 +26962,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G917" t="n">
-        <v>1.55753803253174</v>
+        <v>1.55753791332245</v>
       </c>
       <c r="H917" t="n">
         <v>1214649</v>
@@ -27107,7 +27107,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G922" t="n">
-        <v>1.39933776855469</v>
+        <v>1.3993376493454</v>
       </c>
       <c r="H922" t="n">
         <v>482861</v>
@@ -27136,7 +27136,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G923" t="n">
-        <v>1.45968234539032</v>
+        <v>1.45968210697174</v>
       </c>
       <c r="H923" t="n">
         <v>650528</v>
@@ -27165,7 +27165,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G924" t="n">
-        <v>1.44092667102814</v>
+        <v>1.44092643260956</v>
       </c>
       <c r="H924" t="n">
         <v>445435</v>
@@ -27223,7 +27223,7 @@
         <v>1.78100001811981</v>
       </c>
       <c r="G926" t="n">
-        <v>1.45234310626984</v>
+        <v>1.45234298706055</v>
       </c>
       <c r="H926" t="n">
         <v>500312</v>
@@ -27252,7 +27252,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G927" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H927" t="n">
         <v>310073</v>
@@ -27281,7 +27281,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G928" t="n">
-        <v>1.39933776855469</v>
+        <v>1.3993376493454</v>
       </c>
       <c r="H928" t="n">
         <v>1082932</v>
@@ -27310,7 +27310,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G929" t="n">
-        <v>1.43277192115784</v>
+        <v>1.43277168273926</v>
       </c>
       <c r="H929" t="n">
         <v>844650</v>
@@ -27397,7 +27397,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G932" t="n">
-        <v>1.44255757331848</v>
+        <v>1.44255745410919</v>
       </c>
       <c r="H932" t="n">
         <v>480648</v>
@@ -27426,7 +27426,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G933" t="n">
-        <v>1.46865224838257</v>
+        <v>1.46865236759186</v>
       </c>
       <c r="H933" t="n">
         <v>252434</v>
@@ -27484,7 +27484,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G935" t="n">
-        <v>1.45152747631073</v>
+        <v>1.45152759552002</v>
       </c>
       <c r="H935" t="n">
         <v>676456</v>
@@ -27513,7 +27513,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.45152747631073</v>
+        <v>1.45152759552002</v>
       </c>
       <c r="H936" t="n">
         <v>484220</v>
@@ -27542,7 +27542,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G937" t="n">
-        <v>1.46131324768066</v>
+        <v>1.46131312847137</v>
       </c>
       <c r="H937" t="n">
         <v>276015</v>
@@ -27716,7 +27716,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.67170298099518</v>
+        <v>1.67170310020447</v>
       </c>
       <c r="H943" t="n">
         <v>2434409</v>
@@ -27745,7 +27745,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G944" t="n">
-        <v>1.67659592628479</v>
+        <v>1.6765958070755</v>
       </c>
       <c r="H944" t="n">
         <v>894351</v>
@@ -27774,7 +27774,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G945" t="n">
-        <v>1.73041641712189</v>
+        <v>1.73041653633118</v>
       </c>
       <c r="H945" t="n">
         <v>2501849</v>
@@ -27803,7 +27803,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>1.66354846954346</v>
+        <v>1.66354823112488</v>
       </c>
       <c r="H946" t="n">
         <v>2684227</v>
@@ -27861,7 +27861,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G948" t="n">
-        <v>1.65050113201141</v>
+        <v>1.65050089359283</v>
       </c>
       <c r="H948" t="n">
         <v>447219</v>
@@ -27948,7 +27948,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G951" t="n">
-        <v>1.67496502399445</v>
+        <v>1.67496490478516</v>
       </c>
       <c r="H951" t="n">
         <v>449178</v>
@@ -27977,7 +27977,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G952" t="n">
-        <v>1.64071547985077</v>
+        <v>1.64071536064148</v>
       </c>
       <c r="H952" t="n">
         <v>314585</v>
@@ -28093,7 +28093,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G956" t="n">
-        <v>1.55916881561279</v>
+        <v>1.5591686964035</v>
       </c>
       <c r="H956" t="n">
         <v>1158265</v>
@@ -28122,7 +28122,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G957" t="n">
-        <v>1.57547843456268</v>
+        <v>1.5754781961441</v>
       </c>
       <c r="H957" t="n">
         <v>698341</v>
@@ -28180,7 +28180,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G959" t="n">
-        <v>1.52247273921967</v>
+        <v>1.52247297763824</v>
       </c>
       <c r="H959" t="n">
         <v>441507</v>
@@ -28209,7 +28209,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G960" t="n">
-        <v>1.51350271701813</v>
+        <v>1.51350283622742</v>
       </c>
       <c r="H960" t="n">
         <v>1017531</v>
@@ -28238,7 +28238,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G961" t="n">
-        <v>1.54285967350006</v>
+        <v>1.54285955429077</v>
       </c>
       <c r="H961" t="n">
         <v>444176</v>
@@ -28267,7 +28267,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G962" t="n">
-        <v>1.55753803253174</v>
+        <v>1.55753791332245</v>
       </c>
       <c r="H962" t="n">
         <v>432157</v>
@@ -28296,7 +28296,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G963" t="n">
-        <v>1.5281810760498</v>
+        <v>1.52818119525909</v>
       </c>
       <c r="H963" t="n">
         <v>376603</v>
@@ -28325,7 +28325,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G964" t="n">
-        <v>1.55019891262054</v>
+        <v>1.55019879341125</v>
       </c>
       <c r="H964" t="n">
         <v>472301</v>
@@ -28354,7 +28354,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>1.56161546707153</v>
+        <v>1.56161522865295</v>
       </c>
       <c r="H965" t="n">
         <v>523670</v>
@@ -28412,7 +28412,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G967" t="n">
-        <v>1.53878235816956</v>
+        <v>1.53878223896027</v>
       </c>
       <c r="H967" t="n">
         <v>338780</v>
@@ -28441,7 +28441,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G968" t="n">
-        <v>1.54938340187073</v>
+        <v>1.54938352108002</v>
       </c>
       <c r="H968" t="n">
         <v>929523</v>
@@ -28470,7 +28470,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G969" t="n">
-        <v>1.61135852336884</v>
+        <v>1.61135864257812</v>
       </c>
       <c r="H969" t="n">
         <v>2221457</v>
@@ -28499,7 +28499,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G970" t="n">
-        <v>1.53307402133942</v>
+        <v>1.53307414054871</v>
       </c>
       <c r="H970" t="n">
         <v>1687835</v>
@@ -28557,7 +28557,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G972" t="n">
-        <v>1.51921117305756</v>
+        <v>1.51921105384827</v>
       </c>
       <c r="H972" t="n">
         <v>814738</v>
@@ -28615,7 +28615,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G974" t="n">
-        <v>1.52002644538879</v>
+        <v>1.52002656459808</v>
       </c>
       <c r="H974" t="n">
         <v>392240</v>
@@ -28760,7 +28760,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G979" t="n">
-        <v>1.45968234539032</v>
+        <v>1.45968210697174</v>
       </c>
       <c r="H979" t="n">
         <v>1897039</v>
@@ -28789,7 +28789,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>1.45968234539032</v>
+        <v>1.45968210697174</v>
       </c>
       <c r="H980" t="n">
         <v>899353</v>
@@ -28905,7 +28905,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G984" t="n">
-        <v>1.50942540168762</v>
+        <v>1.50942552089691</v>
       </c>
       <c r="H984" t="n">
         <v>15216437</v>
@@ -28934,7 +28934,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G985" t="n">
-        <v>1.49556267261505</v>
+        <v>1.49556279182434</v>
       </c>
       <c r="H985" t="n">
         <v>8238334</v>
@@ -29021,7 +29021,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G988" t="n">
-        <v>1.44092667102814</v>
+        <v>1.44092643260956</v>
       </c>
       <c r="H988" t="n">
         <v>1635432</v>
@@ -29050,7 +29050,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G989" t="n">
-        <v>1.41320061683655</v>
+        <v>1.41320073604584</v>
       </c>
       <c r="H989" t="n">
         <v>2882134</v>
@@ -29079,7 +29079,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G990" t="n">
-        <v>1.39036762714386</v>
+        <v>1.39036774635315</v>
       </c>
       <c r="H990" t="n">
         <v>2466626</v>
@@ -29108,7 +29108,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.38221299648285</v>
+        <v>1.38221311569214</v>
       </c>
       <c r="H991" t="n">
         <v>1472350</v>
@@ -29137,7 +29137,7 @@
         <v>1.71099996566772</v>
       </c>
       <c r="G992" t="n">
-        <v>1.39526033401489</v>
+        <v>1.39526045322418</v>
       </c>
       <c r="H992" t="n">
         <v>1514786</v>
@@ -29166,7 +29166,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G993" t="n">
-        <v>1.4311408996582</v>
+        <v>1.43114101886749</v>
       </c>
       <c r="H993" t="n">
         <v>4664408</v>
@@ -29195,7 +29195,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G994" t="n">
-        <v>1.43277192115784</v>
+        <v>1.43277168273926</v>
       </c>
       <c r="H994" t="n">
         <v>3291327</v>
@@ -29282,7 +29282,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G997" t="n">
-        <v>1.44337296485901</v>
+        <v>1.44337284564972</v>
       </c>
       <c r="H997" t="n">
         <v>1986347</v>
@@ -29311,7 +29311,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>1.39444494247437</v>
+        <v>1.39444506168365</v>
       </c>
       <c r="H998" t="n">
         <v>2423018</v>
@@ -29340,7 +29340,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G999" t="n">
-        <v>1.38465929031372</v>
+        <v>1.38465940952301</v>
       </c>
       <c r="H999" t="n">
         <v>1961726</v>
@@ -29369,7 +29369,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.41483163833618</v>
+        <v>1.41483151912689</v>
       </c>
       <c r="H1000" t="n">
         <v>2449613</v>
@@ -29514,7 +29514,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.37487387657166</v>
+        <v>1.37487375736237</v>
       </c>
       <c r="H1005" t="n">
         <v>1982853</v>
@@ -29601,7 +29601,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.37487387657166</v>
+        <v>1.37487375736237</v>
       </c>
       <c r="H1008" t="n">
         <v>2577287</v>
@@ -29659,7 +29659,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.34470176696777</v>
+        <v>1.34470164775848</v>
       </c>
       <c r="H1010" t="n">
         <v>1693548</v>
@@ -29688,7 +29688,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.33573138713837</v>
+        <v>1.33573150634766</v>
       </c>
       <c r="H1011" t="n">
         <v>1741918</v>
@@ -29746,7 +29746,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.33002316951752</v>
+        <v>1.33002328872681</v>
       </c>
       <c r="H1013" t="n">
         <v>2067340</v>
@@ -29833,7 +29833,7 @@
         <v>1.65299999713898</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.34796357154846</v>
+        <v>1.34796345233917</v>
       </c>
       <c r="H1016" t="n">
         <v>1488754</v>
@@ -29862,7 +29862,7 @@
         <v>1.61699998378754</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.31860661506653</v>
+        <v>1.31860685348511</v>
       </c>
       <c r="H1017" t="n">
         <v>3637322</v>
@@ -29891,7 +29891,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.28843462467194</v>
+        <v>1.28843450546265</v>
       </c>
       <c r="H1018" t="n">
         <v>1970341</v>
@@ -29920,7 +29920,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.30474400520325</v>
+        <v>1.30474388599396</v>
       </c>
       <c r="H1019" t="n">
         <v>1457803</v>
@@ -29949,7 +29949,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.30229759216309</v>
+        <v>1.3022974729538</v>
       </c>
       <c r="H1020" t="n">
         <v>1207943</v>
@@ -29978,7 +29978,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.31779158115387</v>
+        <v>1.31779134273529</v>
       </c>
       <c r="H1021" t="n">
         <v>1664512</v>
@@ -30065,7 +30065,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.33328521251678</v>
+        <v>1.3332850933075</v>
       </c>
       <c r="H1024" t="n">
         <v>1949168</v>
@@ -30094,7 +30094,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.32431483268738</v>
+        <v>1.32431495189667</v>
       </c>
       <c r="H1025" t="n">
         <v>1894862</v>
@@ -30123,7 +30123,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.32105326652527</v>
+        <v>1.32105314731598</v>
       </c>
       <c r="H1026" t="n">
         <v>1110494</v>
@@ -30152,7 +30152,7 @@
         <v>1.63199996948242</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.33083879947662</v>
+        <v>1.33083868026733</v>
       </c>
       <c r="H1027" t="n">
         <v>2738968</v>
@@ -30181,7 +30181,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.30474400520325</v>
+        <v>1.30474388599396</v>
       </c>
       <c r="H1028" t="n">
         <v>2569962</v>
@@ -30210,7 +30210,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.28517258167267</v>
+        <v>1.28517282009125</v>
       </c>
       <c r="H1029" t="n">
         <v>2106241</v>
@@ -30297,7 +30297,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.27212512493134</v>
+        <v>1.27212524414062</v>
       </c>
       <c r="H1032" t="n">
         <v>2267819</v>
@@ -30413,7 +30413,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.22075092792511</v>
+        <v>1.2207510471344</v>
       </c>
       <c r="H1036" t="n">
         <v>2935812</v>
@@ -30442,7 +30442,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.19302535057068</v>
+        <v>1.19302523136139</v>
       </c>
       <c r="H1037" t="n">
         <v>2136222</v>
@@ -30471,7 +30471,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.17834675312042</v>
+        <v>1.17834687232971</v>
       </c>
       <c r="H1038" t="n">
         <v>2286641</v>
@@ -30500,7 +30500,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.19302535057068</v>
+        <v>1.19302523136139</v>
       </c>
       <c r="H1039" t="n">
         <v>1987577</v>
@@ -30587,7 +30587,7 @@
         <v>1.45799994468689</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.18894791603088</v>
+        <v>1.18894779682159</v>
       </c>
       <c r="H1042" t="n">
         <v>1662033</v>
@@ -30616,7 +30616,7 @@
         <v>1.442999958992</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.17671585083008</v>
+        <v>1.17671597003937</v>
       </c>
       <c r="H1043" t="n">
         <v>1518662</v>
@@ -30645,7 +30645,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.21259641647339</v>
+        <v>1.2125962972641</v>
       </c>
       <c r="H1044" t="n">
         <v>2340167</v>
@@ -30761,7 +30761,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.21830463409424</v>
+        <v>1.21830451488495</v>
       </c>
       <c r="H1048" t="n">
         <v>1782186</v>
@@ -30819,7 +30819,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.21259641647339</v>
+        <v>1.2125962972641</v>
       </c>
       <c r="H1050" t="n">
         <v>1442692</v>
@@ -30877,7 +30877,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.19057881832123</v>
+        <v>1.19057869911194</v>
       </c>
       <c r="H1052" t="n">
         <v>3034895</v>
@@ -30906,7 +30906,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.08456838130951</v>
+        <v>1.08456826210022</v>
       </c>
       <c r="H1053" t="n">
         <v>6068429</v>
@@ -30964,7 +30964,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.13349616527557</v>
+        <v>1.13349604606628</v>
       </c>
       <c r="H1055" t="n">
         <v>2667646</v>
@@ -30993,7 +30993,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.10740125179291</v>
+        <v>1.1074013710022</v>
       </c>
       <c r="H1056" t="n">
         <v>2426604</v>
@@ -31051,7 +31051,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.05928897857666</v>
+        <v>1.05928909778595</v>
       </c>
       <c r="H1058" t="n">
         <v>4847716</v>
@@ -31080,7 +31080,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.03400957584381</v>
+        <v>1.03400945663452</v>
       </c>
       <c r="H1059" t="n">
         <v>2652066</v>
@@ -31109,7 +31109,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.03564047813416</v>
+        <v>1.03564035892487</v>
       </c>
       <c r="H1060" t="n">
         <v>3564489</v>
@@ -31138,7 +31138,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.98834353685379</v>
+        <v>0.988343477249146</v>
       </c>
       <c r="H1061" t="n">
         <v>4115706</v>
@@ -31167,7 +31167,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.920659840106964</v>
+        <v>0.920660018920898</v>
       </c>
       <c r="H1062" t="n">
         <v>4436272</v>
@@ -31196,7 +31196,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.804048418998718</v>
+        <v>0.804048299789429</v>
       </c>
       <c r="H1063" t="n">
         <v>4912177</v>
@@ -31225,7 +31225,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.760013222694397</v>
+        <v>0.760013282299042</v>
       </c>
       <c r="H1064" t="n">
         <v>6550694</v>
@@ -31312,7 +31312,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.588357925415039</v>
+        <v>0.588357985019684</v>
       </c>
       <c r="H1067" t="n">
         <v>5899770</v>
@@ -31457,7 +31457,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.858684480190277</v>
+        <v>0.858684420585632</v>
       </c>
       <c r="H1072" t="n">
         <v>4219076</v>
@@ -31486,7 +31486,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.898642361164093</v>
+        <v>0.898642420768738</v>
       </c>
       <c r="H1073" t="n">
         <v>3269863</v>
@@ -31515,7 +31515,7 @@
         <v>1.25399994850159</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.02259302139282</v>
+        <v>1.02259290218353</v>
       </c>
       <c r="H1074" t="n">
         <v>3835933</v>
@@ -31573,7 +31573,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.918213605880737</v>
+        <v>0.918213546276093</v>
       </c>
       <c r="H1076" t="n">
         <v>2250973</v>
@@ -31602,7 +31602,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.870916485786438</v>
+        <v>0.870916545391083</v>
       </c>
       <c r="H1077" t="n">
         <v>1971172</v>
@@ -31631,7 +31631,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.91332072019577</v>
+        <v>0.913320779800415</v>
       </c>
       <c r="H1078" t="n">
         <v>1366165</v>
@@ -31660,7 +31660,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.950832009315491</v>
+        <v>0.950832188129425</v>
       </c>
       <c r="H1079" t="n">
         <v>2082037</v>
@@ -31689,7 +31689,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.939415514469147</v>
+        <v>0.939415633678436</v>
       </c>
       <c r="H1080" t="n">
         <v>655666</v>
@@ -31718,7 +31718,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.949201166629791</v>
+        <v>0.949201047420502</v>
       </c>
       <c r="H1081" t="n">
         <v>929547</v>
@@ -31747,7 +31747,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.951647579669952</v>
+        <v>0.951647639274597</v>
       </c>
       <c r="H1082" t="n">
         <v>443405</v>
@@ -31834,7 +31834,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.956540405750275</v>
+        <v>0.956540286540985</v>
       </c>
       <c r="H1085" t="n">
         <v>1486613</v>
@@ -31892,7 +31892,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.05276536941528</v>
+        <v>1.05276525020599</v>
       </c>
       <c r="H1087" t="n">
         <v>4106371</v>
@@ -31921,7 +31921,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.9981290102005</v>
+        <v>0.998128950595856</v>
       </c>
       <c r="H1088" t="n">
         <v>2104508</v>
@@ -32008,7 +32008,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.10087776184082</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H1091" t="n">
         <v>1946332</v>
@@ -32037,7 +32037,7 @@
         <v>1.33899998664856</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.09190738201141</v>
+        <v>1.09190762042999</v>
       </c>
       <c r="H1092" t="n">
         <v>1156803</v>
@@ -32095,7 +32095,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.08864557743073</v>
+        <v>1.08864569664001</v>
       </c>
       <c r="H1094" t="n">
         <v>648171</v>
@@ -32153,7 +32153,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.10087776184082</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H1096" t="n">
         <v>929546</v>
@@ -32240,7 +32240,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.10087776184082</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H1099" t="n">
         <v>820249</v>
@@ -32327,7 +32327,7 @@
         <v>1.34899997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.10006213188171</v>
+        <v>1.100062251091</v>
       </c>
       <c r="H1102" t="n">
         <v>427120</v>
@@ -32356,7 +32356,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.06662809848785</v>
+        <v>1.06662821769714</v>
       </c>
       <c r="H1103" t="n">
         <v>840686</v>
@@ -32385,7 +32385,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.06010437011719</v>
+        <v>1.06010448932648</v>
       </c>
       <c r="H1104" t="n">
         <v>3327803</v>
@@ -32414,7 +32414,7 @@
         <v>1.31900000572205</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.07559823989868</v>
+        <v>1.07559835910797</v>
       </c>
       <c r="H1105" t="n">
         <v>463491</v>
@@ -32472,7 +32472,7 @@
         <v>1.307000041008</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.06581270694733</v>
+        <v>1.06581282615662</v>
       </c>
       <c r="H1107" t="n">
         <v>548797</v>
@@ -32501,7 +32501,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.04379498958588</v>
+        <v>1.04379522800446</v>
       </c>
       <c r="H1108" t="n">
         <v>692318</v>
@@ -32530,7 +32530,7 @@
         <v>1.26900005340576</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.03482496738434</v>
+        <v>1.03482508659363</v>
       </c>
       <c r="H1109" t="n">
         <v>390613</v>
@@ -32617,7 +32617,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.988888382911682</v>
+        <v>0.988888442516327</v>
       </c>
       <c r="H1112" t="n">
         <v>1956180</v>
@@ -32646,7 +32646,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.991394102573395</v>
+        <v>0.99139416217804</v>
       </c>
       <c r="H1113" t="n">
         <v>885134</v>
@@ -32704,7 +32704,7 @@
         <v>1.25</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.04401218891144</v>
+        <v>1.04401230812073</v>
       </c>
       <c r="H1115" t="n">
         <v>711035</v>
@@ -32733,7 +32733,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.05737566947937</v>
+        <v>1.05737578868866</v>
       </c>
       <c r="H1116" t="n">
         <v>1440577</v>
@@ -32762,7 +32762,7 @@
         <v>1.22899997234344</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.02647280693054</v>
+        <v>1.02647292613983</v>
       </c>
       <c r="H1117" t="n">
         <v>1389434</v>
@@ -32878,7 +32878,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.08243203163147</v>
+        <v>1.08243191242218</v>
       </c>
       <c r="H1121" t="n">
         <v>1294125</v>
@@ -32907,7 +32907,7 @@
         <v>1.36099994182587</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.13672065734863</v>
+        <v>1.13672041893005</v>
       </c>
       <c r="H1122" t="n">
         <v>2770265</v>
@@ -32936,7 +32936,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.19518506526947</v>
+        <v>1.19518518447876</v>
       </c>
       <c r="H1123" t="n">
         <v>4288487</v>
@@ -32965,7 +32965,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.18766844272614</v>
+        <v>1.18766832351685</v>
       </c>
       <c r="H1124" t="n">
         <v>2988228</v>
@@ -33110,7 +33110,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.08911371231079</v>
+        <v>1.0891135931015</v>
       </c>
       <c r="H1129" t="n">
         <v>1315970</v>
@@ -33139,7 +33139,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.11082911491394</v>
+        <v>1.11082899570465</v>
       </c>
       <c r="H1130" t="n">
         <v>1128829</v>
@@ -33168,7 +33168,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.23026394844055</v>
+        <v>1.23026406764984</v>
       </c>
       <c r="H1131" t="n">
         <v>6561575</v>
@@ -33255,7 +33255,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.23026394844055</v>
+        <v>1.23026406764984</v>
       </c>
       <c r="H1134" t="n">
         <v>2095844</v>
@@ -33313,7 +33313,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.21439504623413</v>
+        <v>1.21439516544342</v>
       </c>
       <c r="H1136" t="n">
         <v>1385149</v>
@@ -33342,7 +33342,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.17597544193268</v>
+        <v>1.17597556114197</v>
       </c>
       <c r="H1137" t="n">
         <v>1151867</v>
@@ -33371,7 +33371,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.17764592170715</v>
+        <v>1.17764580249786</v>
       </c>
       <c r="H1138" t="n">
         <v>954584</v>
@@ -33400,7 +33400,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.16595280170441</v>
+        <v>1.1659529209137</v>
       </c>
       <c r="H1139" t="n">
         <v>669422</v>
@@ -33429,7 +33429,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.18516278266907</v>
+        <v>1.18516266345978</v>
       </c>
       <c r="H1140" t="n">
         <v>968825</v>
@@ -33458,7 +33458,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.16511762142181</v>
+        <v>1.1651177406311</v>
       </c>
       <c r="H1141" t="n">
         <v>1238514</v>
@@ -33516,7 +33516,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.17597544193268</v>
+        <v>1.17597556114197</v>
       </c>
       <c r="H1143" t="n">
         <v>748993</v>
@@ -33545,7 +33545,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.16428256034851</v>
+        <v>1.1642826795578</v>
       </c>
       <c r="H1144" t="n">
         <v>659890</v>
@@ -33574,7 +33574,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.18599784374237</v>
+        <v>1.18599796295166</v>
       </c>
       <c r="H1145" t="n">
         <v>1023147</v>
@@ -33893,7 +33893,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.18516278266907</v>
+        <v>1.18516266345978</v>
       </c>
       <c r="H1156" t="n">
         <v>2537098</v>
@@ -33951,7 +33951,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.19602048397064</v>
+        <v>1.19602036476135</v>
       </c>
       <c r="H1158" t="n">
         <v>1169455</v>
@@ -33980,7 +33980,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.16177690029144</v>
+        <v>1.16177678108215</v>
       </c>
       <c r="H1159" t="n">
         <v>1134501</v>
@@ -34038,7 +34038,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.10247695446014</v>
+        <v>1.10247707366943</v>
       </c>
       <c r="H1161" t="n">
         <v>1753450</v>
@@ -34096,7 +34096,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.970513820648193</v>
+        <v>0.970513761043549</v>
       </c>
       <c r="H1163" t="n">
         <v>4861508</v>
@@ -34183,7 +34183,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.935434937477112</v>
+        <v>0.935435056686401</v>
       </c>
       <c r="H1166" t="n">
         <v>3217787</v>
@@ -34212,7 +34212,7 @@
         <v>1.09899997711182</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.917895674705505</v>
+        <v>0.917895615100861</v>
       </c>
       <c r="H1167" t="n">
         <v>2532403</v>
@@ -34270,7 +34270,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.896180093288422</v>
+        <v>0.896180033683777</v>
       </c>
       <c r="H1169" t="n">
         <v>1798654</v>
@@ -34299,7 +34299,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.918730735778809</v>
+        <v>0.918730795383453</v>
       </c>
       <c r="H1170" t="n">
         <v>1314740</v>
@@ -34328,7 +34328,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.935434937477112</v>
+        <v>0.935435056686401</v>
       </c>
       <c r="H1171" t="n">
         <v>2331133</v>
@@ -34386,7 +34386,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.950468719005585</v>
+        <v>0.950468778610229</v>
       </c>
       <c r="H1173" t="n">
         <v>1092249</v>
@@ -34415,7 +34415,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.953809559345245</v>
+        <v>0.95380961894989</v>
       </c>
       <c r="H1174" t="n">
         <v>982082</v>
@@ -34444,7 +34444,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.945457518100739</v>
+        <v>0.945457577705383</v>
       </c>
       <c r="H1175" t="n">
         <v>642129</v>
@@ -34473,7 +34473,7 @@
         <v>1.125</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.939610958099365</v>
+        <v>0.93961101770401</v>
       </c>
       <c r="H1176" t="n">
         <v>937169</v>
@@ -34531,7 +34531,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.921236515045166</v>
+        <v>0.921236455440521</v>
       </c>
       <c r="H1178" t="n">
         <v>1249603</v>
@@ -34589,7 +34589,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.942951858043671</v>
+        <v>0.94295197725296</v>
       </c>
       <c r="H1180" t="n">
         <v>992299</v>
@@ -34618,7 +34618,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.918730735778809</v>
+        <v>0.918730795383453</v>
       </c>
       <c r="H1181" t="n">
         <v>976233</v>
@@ -34676,7 +34676,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.917060494422913</v>
+        <v>0.917060375213623</v>
       </c>
       <c r="H1183" t="n">
         <v>768682</v>
@@ -34705,7 +34705,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.917060494422913</v>
+        <v>0.917060375213623</v>
       </c>
       <c r="H1184" t="n">
         <v>876059</v>
@@ -34734,7 +34734,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.908708393573761</v>
+        <v>0.908708333969116</v>
       </c>
       <c r="H1185" t="n">
         <v>1886603</v>
@@ -34792,7 +34792,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.9053675532341</v>
+        <v>0.905367434024811</v>
       </c>
       <c r="H1187" t="n">
         <v>1392144</v>
@@ -34850,7 +34850,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.888663232326508</v>
+        <v>0.888663172721863</v>
       </c>
       <c r="H1189" t="n">
         <v>842442</v>
@@ -34908,7 +34908,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.897015392780304</v>
+        <v>0.897015333175659</v>
       </c>
       <c r="H1191" t="n">
         <v>1331626</v>
@@ -34937,7 +34937,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.918730735778809</v>
+        <v>0.918730795383453</v>
       </c>
       <c r="H1192" t="n">
         <v>2380908</v>
@@ -34966,7 +34966,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.901191413402557</v>
+        <v>0.901191353797913</v>
       </c>
       <c r="H1193" t="n">
         <v>993458</v>
@@ -34995,7 +34995,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.9053675532341</v>
+        <v>0.905367434024811</v>
       </c>
       <c r="H1194" t="n">
         <v>698588</v>
@@ -35024,7 +35024,7 @@
         <v>1.0809999704361</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.902861714363098</v>
+        <v>0.902861773967743</v>
       </c>
       <c r="H1195" t="n">
         <v>652835</v>
@@ -35082,7 +35082,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.914554715156555</v>
+        <v>0.9145547747612</v>
       </c>
       <c r="H1197" t="n">
         <v>1059605</v>
@@ -35111,7 +35111,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.937105417251587</v>
+        <v>0.937105536460876</v>
       </c>
       <c r="H1198" t="n">
         <v>1687673</v>
@@ -35140,7 +35140,7 @@
         <v>1.10800004005432</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.92541241645813</v>
+        <v>0.925412476062775</v>
       </c>
       <c r="H1199" t="n">
         <v>870459</v>
@@ -35169,7 +35169,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.912048995494843</v>
+        <v>0.912049174308777</v>
       </c>
       <c r="H1200" t="n">
         <v>1226727</v>
@@ -35227,7 +35227,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.892004132270813</v>
+        <v>0.892004072666168</v>
       </c>
       <c r="H1202" t="n">
         <v>631454</v>
@@ -35285,7 +35285,7 @@
         <v>1.05099999904633</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.877805590629578</v>
+        <v>0.877805531024933</v>
       </c>
       <c r="H1204" t="n">
         <v>2019330</v>
@@ -35314,7 +35314,7 @@
         <v>0.992999970912933</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.829363346099854</v>
+        <v>0.829363226890564</v>
       </c>
       <c r="H1205" t="n">
         <v>5785783</v>
@@ -35343,7 +35343,7 @@
         <v>0.993499994277954</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.829780995845795</v>
+        <v>0.82978093624115</v>
       </c>
       <c r="H1206" t="n">
         <v>1701993</v>
@@ -35372,7 +35372,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.834374666213989</v>
+        <v>0.8343745470047</v>
       </c>
       <c r="H1207" t="n">
         <v>1051359</v>
@@ -35401,7 +35401,7 @@
         <v>0.992500007152557</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.828945755958557</v>
+        <v>0.828945696353912</v>
       </c>
       <c r="H1208" t="n">
         <v>916167</v>
@@ -35459,7 +35459,7 @@
         <v>1.02799999713898</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.858595728874207</v>
+        <v>0.858595669269562</v>
       </c>
       <c r="H1210" t="n">
         <v>796084</v>
@@ -35517,7 +35517,7 @@
         <v>1.07099997997284</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.894509613513947</v>
+        <v>0.894509673118591</v>
       </c>
       <c r="H1212" t="n">
         <v>597717</v>
@@ -35546,7 +35546,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.917060494422913</v>
+        <v>0.917060375213623</v>
       </c>
       <c r="H1213" t="n">
         <v>1682730</v>
@@ -35633,7 +35633,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.855254828929901</v>
+        <v>0.855254888534546</v>
       </c>
       <c r="H1216" t="n">
         <v>846295</v>
@@ -35720,7 +35720,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.868618190288544</v>
+        <v>0.868618130683899</v>
       </c>
       <c r="H1219" t="n">
         <v>1717438</v>
@@ -35749,7 +35749,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.863606989383698</v>
+        <v>0.863607048988342</v>
       </c>
       <c r="H1220" t="n">
         <v>628973</v>
@@ -35807,7 +35807,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.843561947345734</v>
+        <v>0.843561887741089</v>
       </c>
       <c r="H1222" t="n">
         <v>990227</v>
@@ -35894,7 +35894,7 @@
         <v>0.981500029563904</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.819758474826813</v>
+        <v>0.819758415222168</v>
       </c>
       <c r="H1225" t="n">
         <v>975009</v>
@@ -35952,7 +35952,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.768393039703369</v>
+        <v>0.768393099308014</v>
       </c>
       <c r="H1227" t="n">
         <v>1311041</v>
@@ -35981,7 +35981,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.729973375797272</v>
+        <v>0.729973316192627</v>
       </c>
       <c r="H1228" t="n">
         <v>1596505</v>
@@ -36039,7 +36039,7 @@
         <v>0.962499976158142</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.803889393806458</v>
+        <v>0.803889334201813</v>
       </c>
       <c r="H1230" t="n">
         <v>1720467</v>
@@ -36097,7 +36097,7 @@
         <v>0.966499984264374</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.807230234146118</v>
+        <v>0.807230293750763</v>
       </c>
       <c r="H1232" t="n">
         <v>635898</v>
@@ -36126,7 +36126,7 @@
         <v>0.993499994277954</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.829780995845795</v>
+        <v>0.82978093624115</v>
       </c>
       <c r="H1233" t="n">
         <v>1561801</v>
@@ -36155,7 +36155,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.856090009212494</v>
+        <v>0.856090068817139</v>
       </c>
       <c r="H1234" t="n">
         <v>2709801</v>
@@ -36213,7 +36213,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.96466737985611</v>
+        <v>0.96466726064682</v>
       </c>
       <c r="H1236" t="n">
         <v>3202394</v>
@@ -36242,7 +36242,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.951303958892822</v>
+        <v>0.951304137706757</v>
       </c>
       <c r="H1237" t="n">
         <v>1870101</v>
@@ -36271,7 +36271,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.957150518894196</v>
+        <v>0.95715057849884</v>
       </c>
       <c r="H1238" t="n">
         <v>2938823</v>
@@ -36300,7 +36300,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.966337621212006</v>
+        <v>0.96633768081665</v>
       </c>
       <c r="H1239" t="n">
         <v>1609545</v>
@@ -36329,7 +36329,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.0206264257431</v>
+        <v>1.02062630653381</v>
       </c>
       <c r="H1240" t="n">
         <v>3536526</v>
@@ -36358,7 +36358,7 @@
         <v>1.25</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.04401218891144</v>
+        <v>1.04401230812073</v>
       </c>
       <c r="H1241" t="n">
         <v>2955163</v>
@@ -36503,7 +36503,7 @@
         <v>1.3289999961853</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.10999381542206</v>
+        <v>1.10999393463135</v>
       </c>
       <c r="H1246" t="n">
         <v>3085957</v>
@@ -36532,7 +36532,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.08577275276184</v>
+        <v>1.08577287197113</v>
       </c>
       <c r="H1247" t="n">
         <v>2297900</v>
@@ -36561,7 +36561,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.08911371231079</v>
+        <v>1.0891135931015</v>
       </c>
       <c r="H1248" t="n">
         <v>1046280</v>
@@ -36590,7 +36590,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.06906855106354</v>
+        <v>1.06906867027283</v>
       </c>
       <c r="H1249" t="n">
         <v>3269294</v>
@@ -36619,7 +36619,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.06906855106354</v>
+        <v>1.06906867027283</v>
       </c>
       <c r="H1250" t="n">
         <v>1487972</v>
@@ -36764,7 +36764,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.03733062744141</v>
+        <v>1.03733050823212</v>
       </c>
       <c r="H1255" t="n">
         <v>940733</v>
@@ -36822,7 +36822,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.02229678630829</v>
+        <v>1.022296667099</v>
       </c>
       <c r="H1257" t="n">
         <v>1511324</v>
@@ -36880,7 +36880,7 @@
         <v>1.20299994945526</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.0047572851181</v>
+        <v>1.00475740432739</v>
       </c>
       <c r="H1259" t="n">
         <v>892409</v>
@@ -36909,7 +36909,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.01477980613708</v>
+        <v>1.01477992534637</v>
       </c>
       <c r="H1260" t="n">
         <v>1115623</v>
@@ -36967,7 +36967,7 @@
         <v>1.21899998188019</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.01812076568604</v>
+        <v>1.01812088489532</v>
       </c>
       <c r="H1262" t="n">
         <v>752242</v>
@@ -37054,7 +37054,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.951303958892822</v>
+        <v>0.951304137706757</v>
       </c>
       <c r="H1265" t="n">
         <v>3011175</v>
@@ -37083,7 +37083,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.967172861099243</v>
+        <v>0.967172920703888</v>
       </c>
       <c r="H1266" t="n">
         <v>1346794</v>
@@ -37141,7 +37141,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.01477980613708</v>
+        <v>1.01477992534637</v>
       </c>
       <c r="H1268" t="n">
         <v>1173116</v>
@@ -37170,7 +37170,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.991394102573395</v>
+        <v>0.99139416217804</v>
       </c>
       <c r="H1269" t="n">
         <v>1600769</v>
@@ -37199,7 +37199,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.987218022346497</v>
+        <v>0.987217903137207</v>
       </c>
       <c r="H1270" t="n">
         <v>866193</v>
@@ -37257,7 +37257,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.983042001724243</v>
+        <v>0.983042061328888</v>
       </c>
       <c r="H1272" t="n">
         <v>1421450</v>
@@ -37315,7 +37315,7 @@
         <v>1.27699995040894</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.06656277179718</v>
+        <v>1.06656289100647</v>
       </c>
       <c r="H1274" t="n">
         <v>4976055</v>
@@ -37344,7 +37344,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.05737566947937</v>
+        <v>1.05737578868866</v>
       </c>
       <c r="H1275" t="n">
         <v>1591028</v>
@@ -37431,7 +37431,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.05069410800934</v>
+        <v>1.05069386959076</v>
       </c>
       <c r="H1278" t="n">
         <v>718663</v>
@@ -37518,7 +37518,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.0632221698761</v>
+        <v>1.06322205066681</v>
       </c>
       <c r="H1281" t="n">
         <v>1622751</v>
@@ -37547,7 +37547,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.06906855106354</v>
+        <v>1.06906867027283</v>
       </c>
       <c r="H1282" t="n">
         <v>1751527</v>
@@ -37576,7 +37576,7 @@
         <v>1.28799998760223</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.07575011253357</v>
+        <v>1.07575023174286</v>
       </c>
       <c r="H1283" t="n">
         <v>1878041</v>
@@ -37634,7 +37634,7 @@
         <v>1.25899994373322</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.05152904987335</v>
+        <v>1.05152928829193</v>
       </c>
       <c r="H1285" t="n">
         <v>1139462</v>
@@ -37663,7 +37663,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.03482484817505</v>
+        <v>1.03482496738434</v>
       </c>
       <c r="H1286" t="n">
         <v>1259004</v>
@@ -37721,7 +37721,7 @@
         <v>1.22899997234344</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.02647280693054</v>
+        <v>1.02647292613983</v>
       </c>
       <c r="H1288" t="n">
         <v>1184343</v>
@@ -37779,7 +37779,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.02229678630829</v>
+        <v>1.022296667099</v>
       </c>
       <c r="H1290" t="n">
         <v>860970</v>
@@ -37808,7 +37808,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.05069410800934</v>
+        <v>1.05069386959076</v>
       </c>
       <c r="H1291" t="n">
         <v>1203524</v>
@@ -37895,7 +37895,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.11416983604431</v>
+        <v>1.1141699552536</v>
       </c>
       <c r="H1294" t="n">
         <v>1778230</v>
@@ -37924,7 +37924,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.20270204544067</v>
+        <v>1.20270216464996</v>
       </c>
       <c r="H1295" t="n">
         <v>8584230</v>
@@ -37982,7 +37982,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.2678484916687</v>
+        <v>1.26784837245941</v>
       </c>
       <c r="H1297" t="n">
         <v>4152067</v>
@@ -38011,7 +38011,7 @@
         <v>1.57299995422363</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.31378483772278</v>
+        <v>1.31378495693207</v>
       </c>
       <c r="H1298" t="n">
         <v>6077912</v>
@@ -38040,7 +38040,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.2929048538208</v>
+        <v>1.29290473461151</v>
       </c>
       <c r="H1299" t="n">
         <v>4101534</v>
@@ -38069,7 +38069,7 @@
         <v>1.58700001239777</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.32547807693481</v>
+        <v>1.32547795772552</v>
       </c>
       <c r="H1300" t="n">
         <v>2409150</v>
@@ -38156,7 +38156,7 @@
         <v>1.63100004196167</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.3622270822525</v>
+        <v>1.36222720146179</v>
       </c>
       <c r="H1303" t="n">
         <v>5477397</v>
@@ -38243,7 +38243,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.37141454219818</v>
+        <v>1.37141442298889</v>
       </c>
       <c r="H1306" t="n">
         <v>1438763</v>
@@ -38272,7 +38272,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.35638082027435</v>
+        <v>1.35638070106506</v>
       </c>
       <c r="H1307" t="n">
         <v>1681134</v>
@@ -38301,7 +38301,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.35638082027435</v>
+        <v>1.35638070106506</v>
       </c>
       <c r="H1308" t="n">
         <v>1410687</v>
@@ -38330,7 +38330,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.30793869495392</v>
+        <v>1.30793857574463</v>
       </c>
       <c r="H1309" t="n">
         <v>2216085</v>
@@ -38388,7 +38388,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.32046663761139</v>
+        <v>1.3204665184021</v>
       </c>
       <c r="H1311" t="n">
         <v>3540376</v>
@@ -38417,7 +38417,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.30376267433167</v>
+        <v>1.30376243591309</v>
       </c>
       <c r="H1312" t="n">
         <v>1457296</v>
@@ -38533,7 +38533,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.3355005979538</v>
+        <v>1.33550035953522</v>
       </c>
       <c r="H1316" t="n">
         <v>1494787</v>
@@ -38562,7 +38562,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.35638082027435</v>
+        <v>1.35638070106506</v>
       </c>
       <c r="H1317" t="n">
         <v>3043688</v>
@@ -38620,7 +38620,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.36807370185852</v>
+        <v>1.36807358264923</v>
       </c>
       <c r="H1319" t="n">
         <v>2810879</v>
@@ -38649,7 +38649,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.37809610366821</v>
+        <v>1.3780962228775</v>
       </c>
       <c r="H1320" t="n">
         <v>2136490</v>
@@ -38678,7 +38678,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.42152714729309</v>
+        <v>1.4215270280838</v>
       </c>
       <c r="H1321" t="n">
         <v>9920232</v>
@@ -38736,7 +38736,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.44491302967072</v>
+        <v>1.44491291046143</v>
       </c>
       <c r="H1323" t="n">
         <v>2240203</v>
@@ -38765,7 +38765,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.4482536315918</v>
+        <v>1.44825375080109</v>
       </c>
       <c r="H1324" t="n">
         <v>1605888</v>
@@ -38823,7 +38823,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.4482536315918</v>
+        <v>1.44825375080109</v>
       </c>
       <c r="H1326" t="n">
         <v>6989553</v>
@@ -38852,7 +38852,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.43489050865173</v>
+        <v>1.43489038944244</v>
       </c>
       <c r="H1327" t="n">
         <v>3619939</v>
@@ -38881,7 +38881,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.471639752388</v>
+        <v>1.47163963317871</v>
       </c>
       <c r="H1328" t="n">
         <v>2715511</v>
@@ -38910,7 +38910,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.44073677062988</v>
+        <v>1.44073700904846</v>
       </c>
       <c r="H1329" t="n">
         <v>2512664</v>
@@ -38968,7 +38968,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.51841151714325</v>
+        <v>1.51841139793396</v>
       </c>
       <c r="H1331" t="n">
         <v>2026143</v>
@@ -38997,7 +38997,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.50170731544495</v>
+        <v>1.50170719623566</v>
       </c>
       <c r="H1332" t="n">
         <v>2345616</v>
@@ -39084,7 +39084,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.56518304347992</v>
+        <v>1.56518316268921</v>
       </c>
       <c r="H1335" t="n">
         <v>6436688</v>
@@ -39142,7 +39142,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.54012703895569</v>
+        <v>1.5401269197464</v>
       </c>
       <c r="H1337" t="n">
         <v>3492731</v>
@@ -39171,7 +39171,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.51005935668945</v>
+        <v>1.51005923748016</v>
       </c>
       <c r="H1338" t="n">
         <v>3127651</v>
@@ -39200,7 +39200,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.52258741855621</v>
+        <v>1.52258729934692</v>
       </c>
       <c r="H1339" t="n">
         <v>2478018</v>
@@ -39229,7 +39229,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.52425789833069</v>
+        <v>1.52425801753998</v>
       </c>
       <c r="H1340" t="n">
         <v>1890433</v>
@@ -39316,7 +39316,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.53261017799377</v>
+        <v>1.5326099395752</v>
       </c>
       <c r="H1343" t="n">
         <v>1607652</v>
@@ -39432,7 +39432,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.52342283725739</v>
+        <v>1.52342259883881</v>
       </c>
       <c r="H1347" t="n">
         <v>1689611</v>
@@ -39461,7 +39461,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.53010427951813</v>
+        <v>1.53010439872742</v>
       </c>
       <c r="H1348" t="n">
         <v>1071676</v>
@@ -39577,7 +39577,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.5150705575943</v>
+        <v>1.51507067680359</v>
       </c>
       <c r="H1352" t="n">
         <v>1198582</v>
@@ -39635,7 +39635,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.51590585708618</v>
+        <v>1.51590573787689</v>
       </c>
       <c r="H1354" t="n">
         <v>1355627</v>
@@ -39693,7 +39693,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.52258741855621</v>
+        <v>1.52258729934692</v>
       </c>
       <c r="H1356" t="n">
         <v>1042227</v>
@@ -39809,7 +39809,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.5924528837204</v>
+        <v>1.59245300292969</v>
       </c>
       <c r="H1360" t="n">
         <v>1658439</v>
@@ -40041,7 +40041,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.55800306797028</v>
+        <v>1.55800294876099</v>
       </c>
       <c r="H1368" t="n">
         <v>792658</v>
@@ -40070,7 +40070,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.57264411449432</v>
+        <v>1.57264399528503</v>
       </c>
       <c r="H1369" t="n">
         <v>1456339</v>
@@ -40157,7 +40157,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.63982176780701</v>
+        <v>1.63982164859772</v>
       </c>
       <c r="H1372" t="n">
         <v>2388166</v>
@@ -40215,7 +40215,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.69235801696777</v>
+        <v>1.69235813617706</v>
       </c>
       <c r="H1374" t="n">
         <v>3511135</v>
@@ -40447,7 +40447,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.74661672115326</v>
+        <v>1.74661684036255</v>
       </c>
       <c r="H1382" t="n">
         <v>2241110</v>
@@ -40505,7 +40505,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.7758994102478</v>
+        <v>1.77589929103851</v>
       </c>
       <c r="H1384" t="n">
         <v>2093668</v>
@@ -40621,7 +40621,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.77762174606323</v>
+        <v>1.77762162685394</v>
       </c>
       <c r="H1388" t="n">
         <v>3273311</v>
@@ -40650,7 +40650,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.79656946659088</v>
+        <v>1.79656934738159</v>
       </c>
       <c r="H1389" t="n">
         <v>2547377</v>
@@ -40853,7 +40853,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.92747938632965</v>
+        <v>1.92747950553894</v>
       </c>
       <c r="H1396" t="n">
         <v>7583378</v>
@@ -40882,7 +40882,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.92403447628021</v>
+        <v>1.92403435707092</v>
       </c>
       <c r="H1397" t="n">
         <v>3318629</v>
@@ -40969,7 +40969,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.94470453262329</v>
+        <v>1.94470465183258</v>
       </c>
       <c r="H1400" t="n">
         <v>6000564</v>
@@ -40998,7 +40998,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.94125950336456</v>
+        <v>1.94125938415527</v>
       </c>
       <c r="H1401" t="n">
         <v>2335253</v>
@@ -41027,7 +41027,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.91542196273804</v>
+        <v>1.91542184352875</v>
       </c>
       <c r="H1402" t="n">
         <v>4795754</v>
@@ -41085,7 +41085,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.91197693347931</v>
+        <v>1.91197717189789</v>
       </c>
       <c r="H1404" t="n">
         <v>1741874</v>
@@ -41259,7 +41259,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.81207180023193</v>
+        <v>1.81207191944122</v>
       </c>
       <c r="H1410" t="n">
         <v>3028379</v>
@@ -41491,7 +41491,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.97915434837341</v>
+        <v>1.97915458679199</v>
       </c>
       <c r="H1418" t="n">
         <v>16220336</v>
@@ -41520,7 +41520,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.92920196056366</v>
+        <v>1.92920207977295</v>
       </c>
       <c r="H1419" t="n">
         <v>22194642</v>
@@ -41549,7 +41549,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.90336453914642</v>
+        <v>1.90336465835571</v>
       </c>
       <c r="H1420" t="n">
         <v>5111147</v>
@@ -41607,7 +41607,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.92747938632965</v>
+        <v>1.92747950553894</v>
       </c>
       <c r="H1422" t="n">
         <v>2487435</v>
@@ -41665,7 +41665,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.90508687496185</v>
+        <v>1.90508699417114</v>
       </c>
       <c r="H1424" t="n">
         <v>1834534</v>
@@ -41694,7 +41694,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.90508687496185</v>
+        <v>1.90508699417114</v>
       </c>
       <c r="H1425" t="n">
         <v>3197473</v>
@@ -41781,7 +41781,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.11006474494934</v>
+        <v>2.11006498336792</v>
       </c>
       <c r="H1428" t="n">
         <v>7160511</v>
@@ -41810,7 +41810,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G1429" t="n">
-        <v>2.06183457374573</v>
+        <v>2.06183481216431</v>
       </c>
       <c r="H1429" t="n">
         <v>4144115</v>
@@ -41897,7 +41897,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.96537470817566</v>
+        <v>1.96537446975708</v>
       </c>
       <c r="H1432" t="n">
         <v>4116785</v>
@@ -41984,7 +41984,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.91197693347931</v>
+        <v>1.91197717189789</v>
       </c>
       <c r="H1435" t="n">
         <v>1399216</v>
@@ -42013,7 +42013,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.92231214046478</v>
+        <v>1.92231202125549</v>
       </c>
       <c r="H1436" t="n">
         <v>1160492</v>
@@ -42042,7 +42042,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.94125950336456</v>
+        <v>1.94125938415527</v>
       </c>
       <c r="H1437" t="n">
         <v>1502670</v>
@@ -42071,7 +42071,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.95159435272217</v>
+        <v>1.95159447193146</v>
       </c>
       <c r="H1438" t="n">
         <v>1225651</v>
@@ -42129,7 +42129,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.9481498003006</v>
+        <v>1.94814968109131</v>
       </c>
       <c r="H1440" t="n">
         <v>1765949</v>
@@ -42216,7 +42216,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.01360464096069</v>
+        <v>2.01360440254211</v>
       </c>
       <c r="H1443" t="n">
         <v>6083558</v>
@@ -42303,7 +42303,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.01360464096069</v>
+        <v>2.01360440254211</v>
       </c>
       <c r="H1446" t="n">
         <v>2019884</v>
@@ -42419,7 +42419,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.98259973526001</v>
+        <v>1.98259949684143</v>
       </c>
       <c r="H1450" t="n">
         <v>2068642</v>
@@ -42448,7 +42448,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.92747938632965</v>
+        <v>1.92747950553894</v>
       </c>
       <c r="H1451" t="n">
         <v>2973929</v>
@@ -42477,7 +42477,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.95676207542419</v>
+        <v>1.95676231384277</v>
       </c>
       <c r="H1452" t="n">
         <v>3442805</v>
@@ -42506,7 +42506,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.93953716754913</v>
+        <v>1.93953692913055</v>
       </c>
       <c r="H1453" t="n">
         <v>2598555</v>
@@ -42709,7 +42709,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.84996700286865</v>
+        <v>1.84996712207794</v>
       </c>
       <c r="H1460" t="n">
         <v>2076390</v>
@@ -42767,7 +42767,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G1462" t="n">
-        <v>1.89819693565369</v>
+        <v>1.8981968164444</v>
       </c>
       <c r="H1462" t="n">
         <v>2024308</v>
@@ -42825,7 +42825,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.87580454349518</v>
+        <v>1.87580442428589</v>
       </c>
       <c r="H1464" t="n">
         <v>1232432</v>
@@ -42883,7 +42883,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.82929682731628</v>
+        <v>1.82929694652557</v>
       </c>
       <c r="H1466" t="n">
         <v>4060132</v>
@@ -43086,7 +43086,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.86202430725098</v>
+        <v>1.86202442646027</v>
       </c>
       <c r="H1473" t="n">
         <v>2883877</v>
@@ -43231,7 +43231,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.89302968978882</v>
+        <v>1.89302957057953</v>
       </c>
       <c r="H1478" t="n">
         <v>1181498</v>
@@ -43260,7 +43260,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.8913072347641</v>
+        <v>1.89130711555481</v>
       </c>
       <c r="H1479" t="n">
         <v>1405366</v>
@@ -43289,7 +43289,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G1480" t="n">
-        <v>1.88958442211151</v>
+        <v>1.8895845413208</v>
       </c>
       <c r="H1480" t="n">
         <v>758846</v>
@@ -43376,7 +43376,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.84307706356049</v>
+        <v>1.8430769443512</v>
       </c>
       <c r="H1483" t="n">
         <v>1233098</v>
@@ -43521,7 +43521,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.86719214916229</v>
+        <v>1.867192029953</v>
       </c>
       <c r="H1488" t="n">
         <v>2302894</v>
@@ -43637,7 +43637,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.86202430725098</v>
+        <v>1.86202442646027</v>
       </c>
       <c r="H1492" t="n">
         <v>1317744</v>
@@ -43666,7 +43666,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.84307706356049</v>
+        <v>1.8430769443512</v>
       </c>
       <c r="H1493" t="n">
         <v>5523646</v>
@@ -43724,7 +43724,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.84307706356049</v>
+        <v>1.8430769443512</v>
       </c>
       <c r="H1495" t="n">
         <v>1533678</v>
@@ -43753,7 +43753,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.81207180023193</v>
+        <v>1.81207191944122</v>
       </c>
       <c r="H1496" t="n">
         <v>1731235</v>
@@ -43811,7 +43811,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1498" t="n">
-        <v>1.7741767168045</v>
+        <v>1.77417683601379</v>
       </c>
       <c r="H1498" t="n">
         <v>2719202</v>
@@ -43898,7 +43898,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G1501" t="n">
-        <v>1.77762174606323</v>
+        <v>1.77762162685394</v>
       </c>
       <c r="H1501" t="n">
         <v>1440707</v>
@@ -44014,7 +44014,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1505" t="n">
-        <v>1.71388912200928</v>
+        <v>1.71388924121857</v>
       </c>
       <c r="H1505" t="n">
         <v>3082214</v>
@@ -44072,7 +44072,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G1507" t="n">
-        <v>1.75006186962128</v>
+        <v>1.75006198883057</v>
       </c>
       <c r="H1507" t="n">
         <v>1520737</v>
@@ -44130,7 +44130,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.77934432029724</v>
+        <v>1.77934443950653</v>
       </c>
       <c r="H1509" t="n">
         <v>1165284</v>
@@ -44159,7 +44159,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.82929682731628</v>
+        <v>1.82929694652557</v>
       </c>
       <c r="H1510" t="n">
         <v>1482468</v>
@@ -44188,7 +44188,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.79656946659088</v>
+        <v>1.79656934738159</v>
       </c>
       <c r="H1511" t="n">
         <v>752410</v>
@@ -44420,7 +44420,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G1519" t="n">
-        <v>1.71044433116913</v>
+        <v>1.71044421195984</v>
       </c>
       <c r="H1519" t="n">
         <v>1805129</v>
@@ -44507,7 +44507,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.78623414039612</v>
+        <v>1.78623402118683</v>
       </c>
       <c r="H1522" t="n">
         <v>534622</v>
@@ -44710,7 +44710,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.77934432029724</v>
+        <v>1.77934443950653</v>
       </c>
       <c r="H1529" t="n">
         <v>1393116</v>
@@ -44739,7 +44739,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.75006186962128</v>
+        <v>1.75006198883057</v>
       </c>
       <c r="H1530" t="n">
         <v>1262011</v>
@@ -44768,7 +44768,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.72077941894531</v>
+        <v>1.72077929973602</v>
       </c>
       <c r="H1531" t="n">
         <v>1793895</v>
@@ -45029,7 +45029,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.72077941894531</v>
+        <v>1.72077929973602</v>
       </c>
       <c r="H1540" t="n">
         <v>1566494</v>
@@ -45174,7 +45174,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G1545" t="n">
-        <v>1.5924528837204</v>
+        <v>1.59245300292969</v>
       </c>
       <c r="H1545" t="n">
         <v>6343872</v>
@@ -45232,7 +45232,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.59589791297913</v>
+        <v>1.59589779376984</v>
       </c>
       <c r="H1547" t="n">
         <v>2613730</v>
@@ -45406,7 +45406,7 @@
         <v>1.77600002288818</v>
       </c>
       <c r="G1553" t="n">
-        <v>1.52958166599274</v>
+        <v>1.52958154678345</v>
       </c>
       <c r="H1553" t="n">
         <v>1791724</v>
@@ -45435,7 +45435,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.55972540378571</v>
+        <v>1.559725522995</v>
       </c>
       <c r="H1554" t="n">
         <v>1475966</v>
@@ -45580,7 +45580,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.5933141708374</v>
+        <v>1.59331429004669</v>
       </c>
       <c r="H1559" t="n">
         <v>1734770</v>
@@ -45696,7 +45696,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.47101640701294</v>
+        <v>1.47101652622223</v>
       </c>
       <c r="H1563" t="n">
         <v>2448765</v>
@@ -45841,7 +45841,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.40383887290955</v>
+        <v>1.40383899211884</v>
       </c>
       <c r="H1568" t="n">
         <v>2918108</v>
@@ -45870,7 +45870,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.41245138645172</v>
+        <v>1.41245150566101</v>
       </c>
       <c r="H1569" t="n">
         <v>3160029</v>
@@ -45957,7 +45957,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.26431620121002</v>
+        <v>1.26431632041931</v>
       </c>
       <c r="H1572" t="n">
         <v>3671085</v>
@@ -46044,7 +46044,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.33063244819641</v>
+        <v>1.3306325674057</v>
       </c>
       <c r="H1575" t="n">
         <v>891189</v>
@@ -46073,7 +46073,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.36077642440796</v>
+        <v>1.36077630519867</v>
       </c>
       <c r="H1576" t="n">
         <v>1279112</v>
@@ -46102,7 +46102,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G1577" t="n">
-        <v>1.36852777004242</v>
+        <v>1.36852765083313</v>
       </c>
       <c r="H1577" t="n">
         <v>1241512</v>
@@ -46160,7 +46160,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.43656647205353</v>
+        <v>1.43656659126282</v>
       </c>
       <c r="H1579" t="n">
         <v>1730589</v>
@@ -46421,7 +46421,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1588" t="n">
-        <v>1.4348441362381</v>
+        <v>1.43484401702881</v>
       </c>
       <c r="H1588" t="n">
         <v>2104855</v>
@@ -46508,7 +46508,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.4210638999939</v>
+        <v>1.42106401920319</v>
       </c>
       <c r="H1591" t="n">
         <v>1826584</v>
@@ -46537,7 +46537,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.41589653491974</v>
+        <v>1.41589641571045</v>
       </c>
       <c r="H1592" t="n">
         <v>1112144</v>
@@ -46595,7 +46595,7 @@
         <v>1.56400001049042</v>
       </c>
       <c r="G1594" t="n">
-        <v>1.34699630737305</v>
+        <v>1.34699642658234</v>
       </c>
       <c r="H1594" t="n">
         <v>2097111</v>
@@ -46624,7 +46624,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.36077642440796</v>
+        <v>1.36077630519867</v>
       </c>
       <c r="H1595" t="n">
         <v>1346527</v>
@@ -46769,7 +46769,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1600" t="n">
-        <v>1.41589653491974</v>
+        <v>1.41589641571045</v>
       </c>
       <c r="H1600" t="n">
         <v>941807</v>
@@ -46798,7 +46798,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G1601" t="n">
-        <v>1.43915033340454</v>
+        <v>1.43915021419525</v>
       </c>
       <c r="H1601" t="n">
         <v>635198</v>
@@ -46914,7 +46914,7 @@
         <v>1.63300001621246</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.40642285346985</v>
+        <v>1.40642273426056</v>
       </c>
       <c r="H1605" t="n">
         <v>628507</v>
@@ -47291,7 +47291,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.3780015707016</v>
+        <v>1.37800145149231</v>
       </c>
       <c r="H1618" t="n">
         <v>976808</v>
@@ -47349,7 +47349,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G1620" t="n">
-        <v>1.43656647205353</v>
+        <v>1.43656659126282</v>
       </c>
       <c r="H1620" t="n">
         <v>585116</v>
@@ -80067,6 +80067,35 @@
         <v>2387655</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>1.91199994087219</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>1.87300002574921</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>1.8860000371933</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>1.8860000371933</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>1279965</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G2" t="n">
-        <v>2.99598336219788</v>
+        <v>2.9959831237793</v>
       </c>
       <c r="H2" t="n">
         <v>726355</v>
@@ -456,7 +456,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91082572937012</v>
+        <v>2.91082620620728</v>
       </c>
       <c r="H3" t="n">
         <v>1077659</v>
@@ -543,7 +543,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78541302680969</v>
+        <v>2.78541326522827</v>
       </c>
       <c r="H6" t="n">
         <v>761745</v>
@@ -601,7 +601,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76218843460083</v>
+        <v>2.76218819618225</v>
       </c>
       <c r="H8" t="n">
         <v>789466</v>
@@ -688,7 +688,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G11" t="n">
-        <v>2.69251441955566</v>
+        <v>2.69251418113708</v>
       </c>
       <c r="H11" t="n">
         <v>1573296</v>
@@ -717,7 +717,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G12" t="n">
-        <v>2.61045408248901</v>
+        <v>2.61045360565186</v>
       </c>
       <c r="H12" t="n">
         <v>1596810</v>
@@ -746,7 +746,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66464447975159</v>
+        <v>2.66464424133301</v>
       </c>
       <c r="H13" t="n">
         <v>964050</v>
@@ -804,7 +804,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G15" t="n">
-        <v>2.65690279006958</v>
+        <v>2.65690302848816</v>
       </c>
       <c r="H15" t="n">
         <v>1385445</v>
@@ -833,7 +833,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G16" t="n">
-        <v>2.74825358390808</v>
+        <v>2.74825382232666</v>
       </c>
       <c r="H16" t="n">
         <v>1094217</v>
@@ -862,7 +862,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G17" t="n">
-        <v>2.70180439949036</v>
+        <v>2.70180416107178</v>
       </c>
       <c r="H17" t="n">
         <v>491722</v>
@@ -920,7 +920,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G19" t="n">
-        <v>2.72657752037048</v>
+        <v>2.7265772819519</v>
       </c>
       <c r="H19" t="n">
         <v>765235</v>
@@ -949,7 +949,7 @@
         <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2.70954561233521</v>
+        <v>2.70954537391663</v>
       </c>
       <c r="H20" t="n">
         <v>1434225</v>
@@ -978,7 +978,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G21" t="n">
-        <v>2.76992964744568</v>
+        <v>2.76992988586426</v>
       </c>
       <c r="H21" t="n">
         <v>691660</v>
@@ -1036,7 +1036,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63213014602661</v>
+        <v>2.63213038444519</v>
       </c>
       <c r="H23" t="n">
         <v>529297</v>
@@ -1123,7 +1123,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G26" t="n">
-        <v>2.55316662788391</v>
+        <v>2.55316615104675</v>
       </c>
       <c r="H26" t="n">
         <v>2005520</v>
@@ -1152,7 +1152,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G27" t="n">
-        <v>2.43859148025513</v>
+        <v>2.43859100341797</v>
       </c>
       <c r="H27" t="n">
         <v>2592460</v>
@@ -1181,7 +1181,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>2.39988303184509</v>
+        <v>2.39988327026367</v>
       </c>
       <c r="H28" t="n">
         <v>2628393</v>
@@ -1210,7 +1210,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G29" t="n">
-        <v>2.47884702682495</v>
+        <v>2.47884726524353</v>
       </c>
       <c r="H29" t="n">
         <v>1883723</v>
@@ -1239,7 +1239,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G30" t="n">
-        <v>2.27292203903198</v>
+        <v>2.27292156219482</v>
       </c>
       <c r="H30" t="n">
         <v>2979842</v>
@@ -1326,7 +1326,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G33" t="n">
-        <v>2.39214181900024</v>
+        <v>2.39214205741882</v>
       </c>
       <c r="H33" t="n">
         <v>1757704</v>
@@ -1355,7 +1355,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G34" t="n">
-        <v>2.60116386413574</v>
+        <v>2.60116362571716</v>
       </c>
       <c r="H34" t="n">
         <v>2832395</v>
@@ -1384,7 +1384,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G35" t="n">
-        <v>2.59342217445374</v>
+        <v>2.59342241287231</v>
       </c>
       <c r="H35" t="n">
         <v>1621895</v>
@@ -1413,7 +1413,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G36" t="n">
-        <v>2.5376832485199</v>
+        <v>2.53768301010132</v>
       </c>
       <c r="H36" t="n">
         <v>1099387</v>
@@ -1442,7 +1442,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G37" t="n">
-        <v>2.62438893318176</v>
+        <v>2.62438869476318</v>
       </c>
       <c r="H37" t="n">
         <v>1413624</v>
@@ -1471,7 +1471,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G38" t="n">
-        <v>2.63987183570862</v>
+        <v>2.63987159729004</v>
       </c>
       <c r="H38" t="n">
         <v>1416246</v>
@@ -1529,7 +1529,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G40" t="n">
-        <v>2.62129187583923</v>
+        <v>2.62129211425781</v>
       </c>
       <c r="H40" t="n">
         <v>924194</v>
@@ -1558,7 +1558,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G41" t="n">
-        <v>2.73122215270996</v>
+        <v>2.73122239112854</v>
       </c>
       <c r="H41" t="n">
         <v>1616252</v>
@@ -1645,7 +1645,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G44" t="n">
-        <v>2.85199022293091</v>
+        <v>2.85199046134949</v>
       </c>
       <c r="H44" t="n">
         <v>1524438</v>
@@ -1703,7 +1703,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G46" t="n">
-        <v>2.91701936721802</v>
+        <v>2.9170196056366</v>
       </c>
       <c r="H46" t="n">
         <v>1310637</v>
@@ -1761,7 +1761,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G48" t="n">
-        <v>2.82257223129272</v>
+        <v>2.8225724697113</v>
       </c>
       <c r="H48" t="n">
         <v>1053721</v>
@@ -1790,7 +1790,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.80244445800781</v>
+        <v>2.80244469642639</v>
       </c>
       <c r="H49" t="n">
         <v>851655</v>
@@ -1819,7 +1819,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G50" t="n">
-        <v>2.79005837440491</v>
+        <v>2.79005789756775</v>
       </c>
       <c r="H50" t="n">
         <v>1078720</v>
@@ -1848,7 +1848,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G51" t="n">
-        <v>2.8334105014801</v>
+        <v>2.83341073989868</v>
       </c>
       <c r="H51" t="n">
         <v>1171012</v>
@@ -1877,7 +1877,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G52" t="n">
-        <v>2.8891499042511</v>
+        <v>2.88914966583252</v>
       </c>
       <c r="H52" t="n">
         <v>1341195</v>
@@ -1906,7 +1906,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G53" t="n">
-        <v>2.91701936721802</v>
+        <v>2.9170196056366</v>
       </c>
       <c r="H53" t="n">
         <v>764014</v>
@@ -1935,7 +1935,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89069819450378</v>
+        <v>2.89069843292236</v>
       </c>
       <c r="H54" t="n">
         <v>839673</v>
@@ -1964,7 +1964,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>2.85199022293091</v>
+        <v>2.85199046134949</v>
       </c>
       <c r="H55" t="n">
         <v>3876711</v>
@@ -2022,7 +2022,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G57" t="n">
-        <v>2.85199022293091</v>
+        <v>2.85199046134949</v>
       </c>
       <c r="H57" t="n">
         <v>1362718</v>
@@ -2051,7 +2051,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G58" t="n">
-        <v>2.86592483520508</v>
+        <v>2.86592531204224</v>
       </c>
       <c r="H58" t="n">
         <v>663781</v>
@@ -2080,7 +2080,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G59" t="n">
-        <v>2.86128067970276</v>
+        <v>2.86128044128418</v>
       </c>
       <c r="H59" t="n">
         <v>582437</v>
@@ -2109,7 +2109,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G60" t="n">
-        <v>2.78696155548096</v>
+        <v>2.7869610786438</v>
       </c>
       <c r="H60" t="n">
         <v>440085</v>
@@ -2138,7 +2138,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.73277044296265</v>
+        <v>2.73276996612549</v>
       </c>
       <c r="H61" t="n">
         <v>652481</v>
@@ -2196,7 +2196,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G63" t="n">
-        <v>2.87521529197693</v>
+        <v>2.87521505355835</v>
       </c>
       <c r="H63" t="n">
         <v>1458208</v>
@@ -2283,7 +2283,7 @@
         <v>3.5</v>
       </c>
       <c r="G66" t="n">
-        <v>2.70954561233521</v>
+        <v>2.70954537391663</v>
       </c>
       <c r="H66" t="n">
         <v>781074</v>
@@ -2312,7 +2312,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G67" t="n">
-        <v>2.71109437942505</v>
+        <v>2.71109390258789</v>
       </c>
       <c r="H67" t="n">
         <v>574845</v>
@@ -2341,7 +2341,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G68" t="n">
-        <v>2.72657752037048</v>
+        <v>2.7265772819519</v>
       </c>
       <c r="H68" t="n">
         <v>1070111</v>
@@ -2370,7 +2370,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G69" t="n">
-        <v>2.76992964744568</v>
+        <v>2.76992988586426</v>
       </c>
       <c r="H69" t="n">
         <v>1029308</v>
@@ -2428,7 +2428,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80244445800781</v>
+        <v>2.80244469642639</v>
       </c>
       <c r="H71" t="n">
         <v>1384237</v>
@@ -2457,7 +2457,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>2.86437726020813</v>
+        <v>2.86437702178955</v>
       </c>
       <c r="H72" t="n">
         <v>2605699</v>
@@ -2544,7 +2544,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G75" t="n">
-        <v>2.84424901008606</v>
+        <v>2.84424877166748</v>
       </c>
       <c r="H75" t="n">
         <v>709531</v>
@@ -2573,7 +2573,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.87986016273499</v>
+        <v>2.87985968589783</v>
       </c>
       <c r="H76" t="n">
         <v>593773</v>
@@ -2631,7 +2631,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G78" t="n">
-        <v>2.89843964576721</v>
+        <v>2.89843940734863</v>
       </c>
       <c r="H78" t="n">
         <v>973280</v>
@@ -2660,7 +2660,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G79" t="n">
-        <v>2.87521529197693</v>
+        <v>2.87521505355835</v>
       </c>
       <c r="H79" t="n">
         <v>1011988</v>
@@ -2718,7 +2718,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G81" t="n">
-        <v>2.85199022293091</v>
+        <v>2.85199046134949</v>
       </c>
       <c r="H81" t="n">
         <v>1284292</v>
@@ -2805,7 +2805,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G84" t="n">
-        <v>2.95882391929626</v>
+        <v>2.95882439613342</v>
       </c>
       <c r="H84" t="n">
         <v>1543779</v>
@@ -2892,7 +2892,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G87" t="n">
-        <v>2.91856789588928</v>
+        <v>2.9185676574707</v>
       </c>
       <c r="H87" t="n">
         <v>413653</v>
@@ -2950,7 +2950,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G89" t="n">
-        <v>2.839604139328</v>
+        <v>2.83960437774658</v>
       </c>
       <c r="H89" t="n">
         <v>589749</v>
@@ -2979,7 +2979,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>2.80244445800781</v>
+        <v>2.80244469642639</v>
       </c>
       <c r="H90" t="n">
         <v>352951</v>
@@ -3008,7 +3008,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G91" t="n">
-        <v>2.81328272819519</v>
+        <v>2.81328248977661</v>
       </c>
       <c r="H91" t="n">
         <v>397299</v>
@@ -3095,7 +3095,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87057018280029</v>
+        <v>2.87056994438171</v>
       </c>
       <c r="H94" t="n">
         <v>882620</v>
@@ -3124,7 +3124,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>2.87986016273499</v>
+        <v>2.87985968589783</v>
       </c>
       <c r="H95" t="n">
         <v>502468</v>
@@ -3153,7 +3153,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G96" t="n">
-        <v>2.91701936721802</v>
+        <v>2.9170196056366</v>
       </c>
       <c r="H96" t="n">
         <v>1488002</v>
@@ -3298,7 +3298,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.48107147216797</v>
+        <v>2.48107171058655</v>
       </c>
       <c r="H101" t="n">
         <v>14577083</v>
@@ -3327,7 +3327,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G102" t="n">
-        <v>2.49515986442566</v>
+        <v>2.49516010284424</v>
       </c>
       <c r="H102" t="n">
         <v>6755386</v>
@@ -3356,7 +3356,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G103" t="n">
-        <v>2.45759129524231</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H103" t="n">
         <v>4846198</v>
@@ -3414,7 +3414,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G105" t="n">
-        <v>2.46854877471924</v>
+        <v>2.46854901313782</v>
       </c>
       <c r="H105" t="n">
         <v>2374462</v>
@@ -3443,7 +3443,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G106" t="n">
-        <v>2.41845774650574</v>
+        <v>2.41845798492432</v>
       </c>
       <c r="H106" t="n">
         <v>2536181</v>
@@ -3472,7 +3472,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H107" t="n">
         <v>2771779</v>
@@ -3501,7 +3501,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G108" t="n">
-        <v>2.38715124130249</v>
+        <v>2.38715076446533</v>
       </c>
       <c r="H108" t="n">
         <v>1816564</v>
@@ -3530,7 +3530,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G109" t="n">
-        <v>2.3495831489563</v>
+        <v>2.34958291053772</v>
       </c>
       <c r="H109" t="n">
         <v>3325389</v>
@@ -3559,7 +3559,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G110" t="n">
-        <v>2.40750050544739</v>
+        <v>2.40750026702881</v>
       </c>
       <c r="H110" t="n">
         <v>3042621</v>
@@ -3588,7 +3588,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G111" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H111" t="n">
         <v>1834416</v>
@@ -3617,7 +3617,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G112" t="n">
-        <v>2.44663381576538</v>
+        <v>2.44663405418396</v>
       </c>
       <c r="H112" t="n">
         <v>2559071</v>
@@ -3646,7 +3646,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G113" t="n">
-        <v>2.41219639778137</v>
+        <v>2.41219663619995</v>
       </c>
       <c r="H113" t="n">
         <v>3288781</v>
@@ -3675,7 +3675,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>2.3527135848999</v>
+        <v>2.35271310806274</v>
       </c>
       <c r="H114" t="n">
         <v>1983083</v>
@@ -3733,7 +3733,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G116" t="n">
-        <v>2.18052530288696</v>
+        <v>2.18052554130554</v>
       </c>
       <c r="H116" t="n">
         <v>1635751</v>
@@ -3762,7 +3762,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G117" t="n">
-        <v>2.11634612083435</v>
+        <v>2.11634635925293</v>
       </c>
       <c r="H117" t="n">
         <v>2151270</v>
@@ -3791,7 +3791,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G118" t="n">
-        <v>2.05060148239136</v>
+        <v>2.05060195922852</v>
       </c>
       <c r="H118" t="n">
         <v>2040356</v>
@@ -3849,7 +3849,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G120" t="n">
-        <v>2.22748613357544</v>
+        <v>2.22748565673828</v>
       </c>
       <c r="H120" t="n">
         <v>2220357</v>
@@ -3878,7 +3878,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G121" t="n">
-        <v>2.20557117462158</v>
+        <v>2.20557141304016</v>
       </c>
       <c r="H121" t="n">
         <v>1243898</v>
@@ -3907,7 +3907,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G122" t="n">
-        <v>2.21026706695557</v>
+        <v>2.21026682853699</v>
       </c>
       <c r="H122" t="n">
         <v>1579649</v>
@@ -3936,7 +3936,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G123" t="n">
-        <v>2.28696846961975</v>
+        <v>2.28696894645691</v>
       </c>
       <c r="H123" t="n">
         <v>1894721</v>
@@ -3994,7 +3994,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G125" t="n">
-        <v>1.97233438491821</v>
+        <v>1.97233462333679</v>
       </c>
       <c r="H125" t="n">
         <v>1416724</v>
@@ -4081,7 +4081,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G128" t="n">
-        <v>1.98642265796661</v>
+        <v>1.9864227771759</v>
       </c>
       <c r="H128" t="n">
         <v>1698763</v>
@@ -4110,7 +4110,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G129" t="n">
-        <v>2.15078377723694</v>
+        <v>2.15078401565552</v>
       </c>
       <c r="H129" t="n">
         <v>2569377</v>
@@ -4139,7 +4139,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G130" t="n">
-        <v>2.12260746955872</v>
+        <v>2.12260770797729</v>
       </c>
       <c r="H130" t="n">
         <v>1365226</v>
@@ -4168,7 +4168,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G131" t="n">
-        <v>2.09130096435547</v>
+        <v>2.09130072593689</v>
       </c>
       <c r="H131" t="n">
         <v>2319336</v>
@@ -4197,7 +4197,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>2.00364184379578</v>
+        <v>2.00364136695862</v>
       </c>
       <c r="H132" t="n">
         <v>3889902</v>
@@ -4255,7 +4255,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.11321592330933</v>
+        <v>2.11321544647217</v>
       </c>
       <c r="H134" t="n">
         <v>2706963</v>
@@ -4313,7 +4313,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G136" t="n">
-        <v>2.21652841567993</v>
+        <v>2.21652817726135</v>
       </c>
       <c r="H136" t="n">
         <v>1159022</v>
@@ -4342,7 +4342,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G137" t="n">
-        <v>2.16487216949463</v>
+        <v>2.16487169265747</v>
       </c>
       <c r="H137" t="n">
         <v>746737</v>
@@ -4371,7 +4371,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G138" t="n">
-        <v>2.21026706695557</v>
+        <v>2.21026682853699</v>
       </c>
       <c r="H138" t="n">
         <v>738553</v>
@@ -4516,7 +4516,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16800308227539</v>
+        <v>2.16800260543823</v>
       </c>
       <c r="H143" t="n">
         <v>1335820</v>
@@ -4545,7 +4545,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G144" t="n">
-        <v>2.11478090286255</v>
+        <v>2.11478066444397</v>
       </c>
       <c r="H144" t="n">
         <v>1356729</v>
@@ -4632,7 +4632,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G147" t="n">
-        <v>2.20400547981262</v>
+        <v>2.20400595664978</v>
       </c>
       <c r="H147" t="n">
         <v>1296535</v>
@@ -4690,7 +4690,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G149" t="n">
-        <v>2.11791205406189</v>
+        <v>2.11791181564331</v>
       </c>
       <c r="H149" t="n">
         <v>3166446</v>
@@ -4777,7 +4777,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>1.94885456562042</v>
+        <v>1.94885432720184</v>
       </c>
       <c r="H152" t="n">
         <v>1298678</v>
@@ -4806,7 +4806,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>1.94102776050568</v>
+        <v>1.94102764129639</v>
       </c>
       <c r="H153" t="n">
         <v>1093413</v>
@@ -4835,7 +4835,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G154" t="n">
-        <v>1.96137738227844</v>
+        <v>1.96137726306915</v>
       </c>
       <c r="H154" t="n">
         <v>876363</v>
@@ -4864,7 +4864,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G155" t="n">
-        <v>2.01146841049194</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H155" t="n">
         <v>1272598</v>
@@ -4893,7 +4893,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G156" t="n">
-        <v>2.00207614898682</v>
+        <v>2.00207591056824</v>
       </c>
       <c r="H156" t="n">
         <v>1568347</v>
@@ -4922,7 +4922,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>1.99581468105316</v>
+        <v>1.99581491947174</v>
       </c>
       <c r="H157" t="n">
         <v>930572</v>
@@ -4951,7 +4951,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G158" t="n">
-        <v>2.105388879776</v>
+        <v>2.10538911819458</v>
       </c>
       <c r="H158" t="n">
         <v>3572397</v>
@@ -5009,7 +5009,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G160" t="n">
-        <v>2.0834743976593</v>
+        <v>2.08347415924072</v>
       </c>
       <c r="H160" t="n">
         <v>1937826</v>
@@ -5038,7 +5038,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G161" t="n">
-        <v>2.05216693878174</v>
+        <v>2.05216717720032</v>
       </c>
       <c r="H161" t="n">
         <v>1296754</v>
@@ -5096,7 +5096,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>2.05060148239136</v>
+        <v>2.05060195922852</v>
       </c>
       <c r="H163" t="n">
         <v>982101</v>
@@ -5125,7 +5125,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>2.05842876434326</v>
+        <v>2.0584282875061</v>
       </c>
       <c r="H164" t="n">
         <v>1061581</v>
@@ -5154,7 +5154,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G165" t="n">
-        <v>2.09756231307983</v>
+        <v>2.09756183624268</v>
       </c>
       <c r="H165" t="n">
         <v>837027</v>
@@ -5183,7 +5183,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.11321592330933</v>
+        <v>2.11321544647217</v>
       </c>
       <c r="H166" t="n">
         <v>813589</v>
@@ -5212,7 +5212,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>2.0740818977356</v>
+        <v>2.07408237457275</v>
       </c>
       <c r="H167" t="n">
         <v>749117</v>
@@ -5241,7 +5241,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G168" t="n">
-        <v>2.09756231307983</v>
+        <v>2.09756183624268</v>
       </c>
       <c r="H168" t="n">
         <v>697763</v>
@@ -5270,7 +5270,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G169" t="n">
-        <v>2.11947727203369</v>
+        <v>2.11947703361511</v>
       </c>
       <c r="H169" t="n">
         <v>499989</v>
@@ -5328,7 +5328,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G171" t="n">
-        <v>2.1570451259613</v>
+        <v>2.15704560279846</v>
       </c>
       <c r="H171" t="n">
         <v>898895</v>
@@ -5357,7 +5357,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.13669562339783</v>
+        <v>2.13669610023499</v>
       </c>
       <c r="H172" t="n">
         <v>1131229</v>
@@ -5386,7 +5386,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>2.16017580032349</v>
+        <v>2.16017603874207</v>
       </c>
       <c r="H173" t="n">
         <v>498741</v>
@@ -5531,7 +5531,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G178" t="n">
-        <v>2.15078377723694</v>
+        <v>2.15078401565552</v>
       </c>
       <c r="H178" t="n">
         <v>548611</v>
@@ -5589,7 +5589,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G180" t="n">
-        <v>2.01146841049194</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H180" t="n">
         <v>939604</v>
@@ -5618,7 +5618,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G181" t="n">
-        <v>2.00207614898682</v>
+        <v>2.00207591056824</v>
       </c>
       <c r="H181" t="n">
         <v>923059</v>
@@ -5647,7 +5647,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G182" t="n">
-        <v>1.98955357074738</v>
+        <v>1.98955321311951</v>
       </c>
       <c r="H182" t="n">
         <v>1468702</v>
@@ -5734,7 +5734,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G185" t="n">
-        <v>1.92850530147552</v>
+        <v>1.92850494384766</v>
       </c>
       <c r="H185" t="n">
         <v>1274216</v>
@@ -5763,7 +5763,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G186" t="n">
-        <v>1.92537426948547</v>
+        <v>1.92537438869476</v>
       </c>
       <c r="H186" t="n">
         <v>703328</v>
@@ -5792,7 +5792,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>1.98798787593842</v>
+        <v>1.98798799514771</v>
       </c>
       <c r="H187" t="n">
         <v>900283</v>
@@ -5850,7 +5850,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G189" t="n">
-        <v>1.91754758358002</v>
+        <v>1.9175478219986</v>
       </c>
       <c r="H189" t="n">
         <v>786779</v>
@@ -5879,7 +5879,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>1.92537426948547</v>
+        <v>1.92537438869476</v>
       </c>
       <c r="H190" t="n">
         <v>1867839</v>
@@ -5908,7 +5908,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G191" t="n">
-        <v>2.05529761314392</v>
+        <v>2.0552978515625</v>
       </c>
       <c r="H191" t="n">
         <v>3388408</v>
@@ -5966,7 +5966,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G193" t="n">
-        <v>2.00677227973938</v>
+        <v>2.0067720413208</v>
       </c>
       <c r="H193" t="n">
         <v>1366609</v>
@@ -5995,7 +5995,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G194" t="n">
-        <v>1.95355069637299</v>
+        <v>1.95355045795441</v>
       </c>
       <c r="H194" t="n">
         <v>944804</v>
@@ -6024,7 +6024,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G195" t="n">
-        <v>1.94885456562042</v>
+        <v>1.94885432720184</v>
       </c>
       <c r="H195" t="n">
         <v>460629</v>
@@ -6111,7 +6111,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G198" t="n">
-        <v>1.96763849258423</v>
+        <v>1.96763873100281</v>
       </c>
       <c r="H198" t="n">
         <v>843471</v>
@@ -6140,7 +6140,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G199" t="n">
-        <v>1.97233438491821</v>
+        <v>1.97233462333679</v>
       </c>
       <c r="H199" t="n">
         <v>1375593</v>
@@ -6169,7 +6169,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G200" t="n">
-        <v>1.96763849258423</v>
+        <v>1.96763873100281</v>
       </c>
       <c r="H200" t="n">
         <v>746930</v>
@@ -6198,7 +6198,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G201" t="n">
-        <v>1.93320119380951</v>
+        <v>1.93320107460022</v>
       </c>
       <c r="H201" t="n">
         <v>830606</v>
@@ -6227,7 +6227,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G202" t="n">
-        <v>1.93320119380951</v>
+        <v>1.93320107460022</v>
       </c>
       <c r="H202" t="n">
         <v>1085623</v>
@@ -6256,7 +6256,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G203" t="n">
-        <v>1.96763849258423</v>
+        <v>1.96763873100281</v>
       </c>
       <c r="H203" t="n">
         <v>470437</v>
@@ -6285,7 +6285,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96450781822205</v>
+        <v>1.96450769901276</v>
       </c>
       <c r="H204" t="n">
         <v>817690</v>
@@ -6314,7 +6314,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G205" t="n">
-        <v>2.00207614898682</v>
+        <v>2.00207591056824</v>
       </c>
       <c r="H205" t="n">
         <v>1166619</v>
@@ -6372,7 +6372,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>2.08973526954651</v>
+        <v>2.08973550796509</v>
       </c>
       <c r="H207" t="n">
         <v>859886</v>
@@ -6401,7 +6401,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G208" t="n">
-        <v>2.08190870285034</v>
+        <v>2.0819091796875</v>
       </c>
       <c r="H208" t="n">
         <v>1477868</v>
@@ -6430,7 +6430,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G209" t="n">
-        <v>2.10382342338562</v>
+        <v>2.1038236618042</v>
       </c>
       <c r="H209" t="n">
         <v>987784</v>
@@ -6459,7 +6459,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G210" t="n">
-        <v>2.08660507202148</v>
+        <v>2.08660459518433</v>
       </c>
       <c r="H210" t="n">
         <v>726475</v>
@@ -6488,7 +6488,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>2.08973526954651</v>
+        <v>2.08973550796509</v>
       </c>
       <c r="H211" t="n">
         <v>544659</v>
@@ -6517,7 +6517,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G212" t="n">
-        <v>2.0333833694458</v>
+        <v>2.03338313102722</v>
       </c>
       <c r="H212" t="n">
         <v>1605178</v>
@@ -6575,7 +6575,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>1.98798787593842</v>
+        <v>1.98798799514771</v>
       </c>
       <c r="H214" t="n">
         <v>951415</v>
@@ -6604,7 +6604,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G215" t="n">
-        <v>1.96137738227844</v>
+        <v>1.96137726306915</v>
       </c>
       <c r="H215" t="n">
         <v>535801</v>
@@ -6633,7 +6633,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G216" t="n">
-        <v>1.93163573741913</v>
+        <v>1.93163561820984</v>
       </c>
       <c r="H216" t="n">
         <v>1190452</v>
@@ -6662,7 +6662,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G217" t="n">
-        <v>1.9112856388092</v>
+        <v>1.91128587722778</v>
       </c>
       <c r="H217" t="n">
         <v>763654</v>
@@ -6691,7 +6691,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G218" t="n">
-        <v>1.89563262462616</v>
+        <v>1.89563286304474</v>
       </c>
       <c r="H218" t="n">
         <v>762448</v>
@@ -6720,7 +6720,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G219" t="n">
-        <v>1.93163573741913</v>
+        <v>1.93163561820984</v>
       </c>
       <c r="H219" t="n">
         <v>511910</v>
@@ -6749,7 +6749,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G220" t="n">
-        <v>1.9112856388092</v>
+        <v>1.91128587722778</v>
       </c>
       <c r="H220" t="n">
         <v>476146</v>
@@ -6778,7 +6778,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>2.05842876434326</v>
+        <v>2.0584282875061</v>
       </c>
       <c r="H221" t="n">
         <v>7385474</v>
@@ -6807,7 +6807,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G222" t="n">
-        <v>2.08817028999329</v>
+        <v>2.08817005157471</v>
       </c>
       <c r="H222" t="n">
         <v>4219197</v>
@@ -6836,7 +6836,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G223" t="n">
-        <v>2.03025245666504</v>
+        <v>2.03025269508362</v>
       </c>
       <c r="H223" t="n">
         <v>2200910</v>
@@ -6865,7 +6865,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G224" t="n">
-        <v>2.16330695152283</v>
+        <v>2.16330671310425</v>
       </c>
       <c r="H224" t="n">
         <v>3314695</v>
@@ -6923,7 +6923,7 @@
         <v>2.66799998283386</v>
       </c>
       <c r="G226" t="n">
-        <v>2.08817028999329</v>
+        <v>2.08817005157471</v>
       </c>
       <c r="H226" t="n">
         <v>1286080</v>
@@ -6952,7 +6952,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G227" t="n">
-        <v>2.08660507202148</v>
+        <v>2.08660459518433</v>
       </c>
       <c r="H227" t="n">
         <v>977540</v>
@@ -7010,7 +7010,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G229" t="n">
-        <v>1.99581468105316</v>
+        <v>1.99581491947174</v>
       </c>
       <c r="H229" t="n">
         <v>1137034</v>
@@ -7039,7 +7039,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G230" t="n">
-        <v>2.01146841049194</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H230" t="n">
         <v>871707</v>
@@ -7068,7 +7068,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G231" t="n">
-        <v>2.01146841049194</v>
+        <v>2.01146817207336</v>
       </c>
       <c r="H231" t="n">
         <v>940946</v>
@@ -7097,7 +7097,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G232" t="n">
-        <v>1.99581468105316</v>
+        <v>1.99581491947174</v>
       </c>
       <c r="H232" t="n">
         <v>459440</v>
@@ -7126,7 +7126,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G233" t="n">
-        <v>1.98955357074738</v>
+        <v>1.98955321311951</v>
       </c>
       <c r="H233" t="n">
         <v>602925</v>
@@ -7155,7 +7155,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>1.92537426948547</v>
+        <v>1.92537438869476</v>
       </c>
       <c r="H234" t="n">
         <v>1382971</v>
@@ -7184,7 +7184,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G235" t="n">
-        <v>1.96763849258423</v>
+        <v>1.96763873100281</v>
       </c>
       <c r="H235" t="n">
         <v>925158</v>
@@ -7271,7 +7271,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G238" t="n">
-        <v>2.04434061050415</v>
+        <v>2.04434037208557</v>
       </c>
       <c r="H238" t="n">
         <v>1826358</v>
@@ -7300,7 +7300,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G239" t="n">
-        <v>2.09756231307983</v>
+        <v>2.09756183624268</v>
       </c>
       <c r="H239" t="n">
         <v>1527580</v>
@@ -7387,7 +7387,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G242" t="n">
-        <v>2.26192331314087</v>
+        <v>2.26192355155945</v>
       </c>
       <c r="H242" t="n">
         <v>2116747</v>
@@ -7416,7 +7416,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G243" t="n">
-        <v>2.24626994132996</v>
+        <v>2.24626970291138</v>
       </c>
       <c r="H243" t="n">
         <v>2334527</v>
@@ -7445,7 +7445,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G244" t="n">
-        <v>2.26192331314087</v>
+        <v>2.26192355155945</v>
       </c>
       <c r="H244" t="n">
         <v>1572345</v>
@@ -7503,7 +7503,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G246" t="n">
-        <v>2.3495831489563</v>
+        <v>2.34958291053772</v>
       </c>
       <c r="H246" t="n">
         <v>3285193</v>
@@ -7561,7 +7561,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H248" t="n">
         <v>2467677</v>
@@ -7590,7 +7590,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H249" t="n">
         <v>2372938</v>
@@ -7619,7 +7619,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G250" t="n">
-        <v>2.38088941574097</v>
+        <v>2.38088965415955</v>
       </c>
       <c r="H250" t="n">
         <v>1340592</v>
@@ -7648,7 +7648,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G251" t="n">
-        <v>2.37932443618774</v>
+        <v>2.37932419776917</v>
       </c>
       <c r="H251" t="n">
         <v>1637113</v>
@@ -7706,7 +7706,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G253" t="n">
-        <v>2.39028191566467</v>
+        <v>2.39028143882751</v>
       </c>
       <c r="H253" t="n">
         <v>1171723</v>
@@ -7735,7 +7735,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G254" t="n">
-        <v>2.39654278755188</v>
+        <v>2.39654326438904</v>
       </c>
       <c r="H254" t="n">
         <v>358245</v>
@@ -7822,7 +7822,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G257" t="n">
-        <v>2.3495831489563</v>
+        <v>2.34958291053772</v>
       </c>
       <c r="H257" t="n">
         <v>574581</v>
@@ -7851,7 +7851,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G258" t="n">
-        <v>2.43098044395447</v>
+        <v>2.43098068237305</v>
       </c>
       <c r="H258" t="n">
         <v>1363312</v>
@@ -7909,7 +7909,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G260" t="n">
-        <v>2.48576807975769</v>
+        <v>2.48576760292053</v>
       </c>
       <c r="H260" t="n">
         <v>1766326</v>
@@ -7938,7 +7938,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G261" t="n">
-        <v>2.45759129524231</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H261" t="n">
         <v>853673</v>
@@ -7967,7 +7967,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G262" t="n">
-        <v>2.49359440803528</v>
+        <v>2.49359464645386</v>
       </c>
       <c r="H262" t="n">
         <v>455999</v>
@@ -8025,7 +8025,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G264" t="n">
-        <v>2.45759129524231</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H264" t="n">
         <v>879469</v>
@@ -8054,7 +8054,7 @@
         <v>3.17600011825562</v>
       </c>
       <c r="G265" t="n">
-        <v>2.48576807975769</v>
+        <v>2.48576760292053</v>
       </c>
       <c r="H265" t="n">
         <v>829436</v>
@@ -8112,7 +8112,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.44976472854614</v>
+        <v>2.44976496696472</v>
       </c>
       <c r="H267" t="n">
         <v>771245</v>
@@ -8170,7 +8170,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G269" t="n">
-        <v>2.41376209259033</v>
+        <v>2.41376185417175</v>
       </c>
       <c r="H269" t="n">
         <v>690659</v>
@@ -8199,7 +8199,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G270" t="n">
-        <v>2.39497756958008</v>
+        <v>2.39497780799866</v>
       </c>
       <c r="H270" t="n">
         <v>486139</v>
@@ -8257,7 +8257,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G272" t="n">
-        <v>2.4028046131134</v>
+        <v>2.40280437469482</v>
       </c>
       <c r="H272" t="n">
         <v>626345</v>
@@ -8286,7 +8286,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G273" t="n">
-        <v>2.38402056694031</v>
+        <v>2.38402032852173</v>
       </c>
       <c r="H273" t="n">
         <v>1065395</v>
@@ -8315,7 +8315,7 @@
         <v>3.08400011062622</v>
       </c>
       <c r="G274" t="n">
-        <v>2.41376209259033</v>
+        <v>2.41376185417175</v>
       </c>
       <c r="H274" t="n">
         <v>621910</v>
@@ -8344,7 +8344,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G275" t="n">
-        <v>2.4262843132019</v>
+        <v>2.42628479003906</v>
       </c>
       <c r="H275" t="n">
         <v>900916</v>
@@ -8373,7 +8373,7 @@
         <v>3.01399993896484</v>
       </c>
       <c r="G276" t="n">
-        <v>2.35897469520569</v>
+        <v>2.35897493362427</v>
       </c>
       <c r="H276" t="n">
         <v>1343547</v>
@@ -8402,7 +8402,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G277" t="n">
-        <v>2.33862519264221</v>
+        <v>2.33862543106079</v>
       </c>
       <c r="H277" t="n">
         <v>900267</v>
@@ -8431,7 +8431,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.30888390541077</v>
+        <v>2.30888414382935</v>
       </c>
       <c r="H278" t="n">
         <v>1234287</v>
@@ -8460,7 +8460,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G279" t="n">
-        <v>2.25566172599792</v>
+        <v>2.25566244125366</v>
       </c>
       <c r="H279" t="n">
         <v>863160</v>
@@ -8489,7 +8489,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G280" t="n">
-        <v>2.30575299263</v>
+        <v>2.30575323104858</v>
       </c>
       <c r="H280" t="n">
         <v>1071680</v>
@@ -8547,7 +8547,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.27757716178894</v>
+        <v>2.27757668495178</v>
       </c>
       <c r="H282" t="n">
         <v>900313</v>
@@ -8576,7 +8576,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G283" t="n">
-        <v>2.23061633110046</v>
+        <v>2.23061656951904</v>
       </c>
       <c r="H283" t="n">
         <v>840338</v>
@@ -8605,7 +8605,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.24626994132996</v>
+        <v>2.24626970291138</v>
       </c>
       <c r="H284" t="n">
         <v>930384</v>
@@ -8692,7 +8692,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G287" t="n">
-        <v>2.33862519264221</v>
+        <v>2.33862543106079</v>
       </c>
       <c r="H287" t="n">
         <v>1633765</v>
@@ -8721,7 +8721,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G288" t="n">
-        <v>2.39341235160828</v>
+        <v>2.39341259002686</v>
       </c>
       <c r="H288" t="n">
         <v>860854</v>
@@ -8808,7 +8808,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G291" t="n">
-        <v>2.40437006950378</v>
+        <v>2.40436983108521</v>
       </c>
       <c r="H291" t="n">
         <v>2490093</v>
@@ -8866,7 +8866,7 @@
         <v>3</v>
       </c>
       <c r="G293" t="n">
-        <v>2.34801745414734</v>
+        <v>2.34801721572876</v>
       </c>
       <c r="H293" t="n">
         <v>865361</v>
@@ -8895,7 +8895,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G294" t="n">
-        <v>2.33862519264221</v>
+        <v>2.33862543106079</v>
       </c>
       <c r="H294" t="n">
         <v>975000</v>
@@ -8953,7 +8953,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G296" t="n">
-        <v>2.33705997467041</v>
+        <v>2.33706021308899</v>
       </c>
       <c r="H296" t="n">
         <v>869769</v>
@@ -8982,7 +8982,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G297" t="n">
-        <v>2.4528956413269</v>
+        <v>2.45289540290833</v>
       </c>
       <c r="H297" t="n">
         <v>4692514</v>
@@ -9040,7 +9040,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G299" t="n">
-        <v>2.48107147216797</v>
+        <v>2.48107171058655</v>
       </c>
       <c r="H299" t="n">
         <v>1238634</v>
@@ -9069,7 +9069,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G300" t="n">
-        <v>2.53429317474365</v>
+        <v>2.53429341316223</v>
       </c>
       <c r="H300" t="n">
         <v>2015772</v>
@@ -9098,7 +9098,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G301" t="n">
-        <v>2.54525065422058</v>
+        <v>2.54525113105774</v>
       </c>
       <c r="H301" t="n">
         <v>1841917</v>
@@ -9127,7 +9127,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G302" t="n">
-        <v>2.53585839271545</v>
+        <v>2.53585863113403</v>
       </c>
       <c r="H302" t="n">
         <v>879229</v>
@@ -9156,7 +9156,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G303" t="n">
-        <v>2.50455236434937</v>
+        <v>2.50455212593079</v>
       </c>
       <c r="H303" t="n">
         <v>952772</v>
@@ -9185,7 +9185,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G304" t="n">
-        <v>2.50455236434937</v>
+        <v>2.50455212593079</v>
       </c>
       <c r="H304" t="n">
         <v>820425</v>
@@ -9214,7 +9214,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G305" t="n">
-        <v>2.51707482337952</v>
+        <v>2.5170750617981</v>
       </c>
       <c r="H305" t="n">
         <v>842737</v>
@@ -9243,7 +9243,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G306" t="n">
-        <v>2.49359440803528</v>
+        <v>2.49359464645386</v>
       </c>
       <c r="H306" t="n">
         <v>740808</v>
@@ -9272,7 +9272,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G307" t="n">
-        <v>2.4920289516449</v>
+        <v>2.49202942848206</v>
       </c>
       <c r="H307" t="n">
         <v>1006054</v>
@@ -9330,7 +9330,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G309" t="n">
-        <v>2.45759129524231</v>
+        <v>2.45759177207947</v>
       </c>
       <c r="H309" t="n">
         <v>969086</v>
@@ -9359,7 +9359,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G310" t="n">
-        <v>2.48889851570129</v>
+        <v>2.48889827728271</v>
       </c>
       <c r="H310" t="n">
         <v>615008</v>
@@ -9446,7 +9446,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G313" t="n">
-        <v>2.46541857719421</v>
+        <v>2.46541833877563</v>
       </c>
       <c r="H313" t="n">
         <v>1680814</v>
@@ -9475,7 +9475,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G314" t="n">
-        <v>2.45133018493652</v>
+        <v>2.45132994651794</v>
       </c>
       <c r="H314" t="n">
         <v>1373872</v>
@@ -9504,7 +9504,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G315" t="n">
-        <v>2.44663381576538</v>
+        <v>2.44663405418396</v>
       </c>
       <c r="H315" t="n">
         <v>1339012</v>
@@ -9562,7 +9562,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.50455236434937</v>
+        <v>2.50455212593079</v>
       </c>
       <c r="H317" t="n">
         <v>1108703</v>
@@ -9620,7 +9620,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G319" t="n">
-        <v>2.49359440803528</v>
+        <v>2.49359464645386</v>
       </c>
       <c r="H319" t="n">
         <v>961125</v>
@@ -9649,7 +9649,7 @@
         <v>3.10400009155273</v>
       </c>
       <c r="G320" t="n">
-        <v>2.42941570281982</v>
+        <v>2.42941522598267</v>
       </c>
       <c r="H320" t="n">
         <v>1672455</v>
@@ -9678,7 +9678,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G321" t="n">
-        <v>2.44193816184998</v>
+        <v>2.4419379234314</v>
       </c>
       <c r="H321" t="n">
         <v>1174861</v>
@@ -9707,7 +9707,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G322" t="n">
-        <v>2.44193816184998</v>
+        <v>2.4419379234314</v>
       </c>
       <c r="H322" t="n">
         <v>774694</v>
@@ -9736,7 +9736,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G323" t="n">
-        <v>2.4028046131134</v>
+        <v>2.40280437469482</v>
       </c>
       <c r="H323" t="n">
         <v>1842216</v>
@@ -9852,7 +9852,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.46541857719421</v>
+        <v>2.46541833877563</v>
       </c>
       <c r="H327" t="n">
         <v>1448459</v>
@@ -9910,7 +9910,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G329" t="n">
-        <v>2.43254613876343</v>
+        <v>2.43254590034485</v>
       </c>
       <c r="H329" t="n">
         <v>922372</v>
@@ -9939,7 +9939,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G330" t="n">
-        <v>2.39028191566467</v>
+        <v>2.39028143882751</v>
       </c>
       <c r="H330" t="n">
         <v>977417</v>
@@ -9968,7 +9968,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>2.36836671829224</v>
+        <v>2.36836719512939</v>
       </c>
       <c r="H331" t="n">
         <v>1134109</v>
@@ -9997,7 +9997,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G332" t="n">
-        <v>2.29792642593384</v>
+        <v>2.29792618751526</v>
       </c>
       <c r="H332" t="n">
         <v>1838891</v>
@@ -10026,7 +10026,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G333" t="n">
-        <v>2.38715124130249</v>
+        <v>2.38715076446533</v>
       </c>
       <c r="H333" t="n">
         <v>1119719</v>
@@ -10084,7 +10084,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>2.39497756958008</v>
+        <v>2.39497780799866</v>
       </c>
       <c r="H335" t="n">
         <v>2078075</v>
@@ -10113,7 +10113,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.4262843132019</v>
+        <v>2.42628479003906</v>
       </c>
       <c r="H336" t="n">
         <v>1305495</v>
@@ -10142,7 +10142,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G337" t="n">
-        <v>2.40750050544739</v>
+        <v>2.40750026702881</v>
       </c>
       <c r="H337" t="n">
         <v>4223005</v>
@@ -10171,7 +10171,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>2.44976472854614</v>
+        <v>2.44976496696472</v>
       </c>
       <c r="H338" t="n">
         <v>2519037</v>
@@ -10345,7 +10345,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G344" t="n">
-        <v>2.55151224136353</v>
+        <v>2.55151200294495</v>
       </c>
       <c r="H344" t="n">
         <v>1479263</v>
@@ -10374,7 +10374,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G345" t="n">
-        <v>2.53742432594299</v>
+        <v>2.53742408752441</v>
       </c>
       <c r="H345" t="n">
         <v>1106003</v>
@@ -10548,7 +10548,7 @@
         <v>3.40599989891052</v>
       </c>
       <c r="G351" t="n">
-        <v>2.66578269004822</v>
+        <v>2.66578245162964</v>
       </c>
       <c r="H351" t="n">
         <v>1367008</v>
@@ -10577,7 +10577,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.53585839271545</v>
+        <v>2.53585863113403</v>
       </c>
       <c r="H352" t="n">
         <v>2123505</v>
@@ -10606,7 +10606,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G353" t="n">
-        <v>2.43098044395447</v>
+        <v>2.43098068237305</v>
       </c>
       <c r="H353" t="n">
         <v>3812104</v>
@@ -10635,7 +10635,7 @@
         <v>3.14599990844727</v>
       </c>
       <c r="G354" t="n">
-        <v>2.46228766441345</v>
+        <v>2.46228790283203</v>
       </c>
       <c r="H354" t="n">
         <v>1374536</v>
@@ -10664,7 +10664,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G355" t="n">
-        <v>2.52040147781372</v>
+        <v>2.5204017162323</v>
       </c>
       <c r="H355" t="n">
         <v>818695</v>
@@ -10693,7 +10693,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G356" t="n">
-        <v>2.53791546821594</v>
+        <v>2.53791570663452</v>
       </c>
       <c r="H356" t="n">
         <v>987101</v>
@@ -10722,7 +10722,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G357" t="n">
-        <v>2.5251784324646</v>
+        <v>2.52517819404602</v>
       </c>
       <c r="H357" t="n">
         <v>545200</v>
@@ -10751,7 +10751,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>2.55542898178101</v>
+        <v>2.55542945861816</v>
       </c>
       <c r="H358" t="n">
         <v>654062</v>
@@ -10809,7 +10809,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G360" t="n">
-        <v>2.56020593643188</v>
+        <v>2.56020617485046</v>
       </c>
       <c r="H360" t="n">
         <v>747549</v>
@@ -10838,7 +10838,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>2.5235857963562</v>
+        <v>2.52358603477478</v>
       </c>
       <c r="H361" t="n">
         <v>1301649</v>
@@ -10925,7 +10925,7 @@
         <v>3.23399996757507</v>
       </c>
       <c r="G364" t="n">
-        <v>2.57453536987305</v>
+        <v>2.57453513145447</v>
       </c>
       <c r="H364" t="n">
         <v>1210712</v>
@@ -10954,7 +10954,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G365" t="n">
-        <v>2.56816697120667</v>
+        <v>2.56816673278809</v>
       </c>
       <c r="H365" t="n">
         <v>1146192</v>
@@ -10983,7 +10983,7 @@
         <v>3.20600008964539</v>
       </c>
       <c r="G366" t="n">
-        <v>2.55224537849426</v>
+        <v>2.55224514007568</v>
       </c>
       <c r="H366" t="n">
         <v>1387432</v>
@@ -11012,7 +11012,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G367" t="n">
-        <v>2.44875407218933</v>
+        <v>2.44875383377075</v>
       </c>
       <c r="H367" t="n">
         <v>1658630</v>
@@ -11041,7 +11041,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G368" t="n">
-        <v>2.45830702781677</v>
+        <v>2.45830750465393</v>
       </c>
       <c r="H368" t="n">
         <v>2334871</v>
@@ -11070,7 +11070,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G369" t="n">
-        <v>2.41372632980347</v>
+        <v>2.41372656822205</v>
       </c>
       <c r="H369" t="n">
         <v>1844465</v>
@@ -11244,7 +11244,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G375" t="n">
-        <v>2.43124032020569</v>
+        <v>2.43124008178711</v>
       </c>
       <c r="H375" t="n">
         <v>894485</v>
@@ -11331,7 +11331,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>2.4041736125946</v>
+        <v>2.40417337417603</v>
       </c>
       <c r="H378" t="n">
         <v>554483</v>
@@ -11360,7 +11360,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G379" t="n">
-        <v>2.41213417053223</v>
+        <v>2.41213440895081</v>
       </c>
       <c r="H379" t="n">
         <v>550090</v>
@@ -11389,7 +11389,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G380" t="n">
-        <v>2.44397759437561</v>
+        <v>2.44397735595703</v>
       </c>
       <c r="H380" t="n">
         <v>696668</v>
@@ -11418,7 +11418,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G381" t="n">
-        <v>2.49811124801636</v>
+        <v>2.49811148643494</v>
       </c>
       <c r="H381" t="n">
         <v>1455624</v>
@@ -11447,7 +11447,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G382" t="n">
-        <v>2.48696637153625</v>
+        <v>2.48696613311768</v>
       </c>
       <c r="H382" t="n">
         <v>1591740</v>
@@ -11476,7 +11476,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G383" t="n">
-        <v>2.39780473709106</v>
+        <v>2.39780449867249</v>
       </c>
       <c r="H383" t="n">
         <v>1899296</v>
@@ -11505,7 +11505,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.41213417053223</v>
+        <v>2.41213440895081</v>
       </c>
       <c r="H384" t="n">
         <v>1637111</v>
@@ -11534,7 +11534,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.42805624008179</v>
+        <v>2.42805576324463</v>
       </c>
       <c r="H385" t="n">
         <v>929588</v>
@@ -11563,7 +11563,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G386" t="n">
-        <v>2.38984394073486</v>
+        <v>2.38984417915344</v>
       </c>
       <c r="H386" t="n">
         <v>1146093</v>
@@ -11592,7 +11592,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G387" t="n">
-        <v>2.39462041854858</v>
+        <v>2.39462018013</v>
       </c>
       <c r="H387" t="n">
         <v>722439</v>
@@ -11650,7 +11650,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G389" t="n">
-        <v>2.42646408081055</v>
+        <v>2.42646384239197</v>
       </c>
       <c r="H389" t="n">
         <v>1267851</v>
@@ -11737,7 +11737,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G392" t="n">
-        <v>2.44716167449951</v>
+        <v>2.44716191291809</v>
       </c>
       <c r="H392" t="n">
         <v>1622777</v>
@@ -11766,7 +11766,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G393" t="n">
-        <v>2.50129580497742</v>
+        <v>2.50129556655884</v>
       </c>
       <c r="H393" t="n">
         <v>2306454</v>
@@ -11795,7 +11795,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G394" t="n">
-        <v>2.45989918708801</v>
+        <v>2.45989942550659</v>
       </c>
       <c r="H394" t="n">
         <v>617432</v>
@@ -11824,7 +11824,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G395" t="n">
-        <v>2.51084852218628</v>
+        <v>2.51084876060486</v>
       </c>
       <c r="H395" t="n">
         <v>4508418</v>
@@ -11882,7 +11882,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G397" t="n">
-        <v>2.49492716789246</v>
+        <v>2.49492692947388</v>
       </c>
       <c r="H397" t="n">
         <v>540455</v>
@@ -11911,7 +11911,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G398" t="n">
-        <v>2.46149110794067</v>
+        <v>2.46149158477783</v>
       </c>
       <c r="H398" t="n">
         <v>1226827</v>
@@ -11940,7 +11940,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G399" t="n">
-        <v>2.42805624008179</v>
+        <v>2.42805576324463</v>
       </c>
       <c r="H399" t="n">
         <v>1376064</v>
@@ -11969,7 +11969,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G400" t="n">
-        <v>2.42805624008179</v>
+        <v>2.42805576324463</v>
       </c>
       <c r="H400" t="n">
         <v>669595</v>
@@ -12056,7 +12056,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>2.3962128162384</v>
+        <v>2.39621233940125</v>
       </c>
       <c r="H403" t="n">
         <v>3318841</v>
@@ -12114,7 +12114,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G405" t="n">
-        <v>2.36596131324768</v>
+        <v>2.3659610748291</v>
       </c>
       <c r="H405" t="n">
         <v>997374</v>
@@ -12201,7 +12201,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G408" t="n">
-        <v>2.36436915397644</v>
+        <v>2.36436939239502</v>
       </c>
       <c r="H408" t="n">
         <v>484836</v>
@@ -12230,7 +12230,7 @@
         <v>3</v>
       </c>
       <c r="G409" t="n">
-        <v>2.38825178146362</v>
+        <v>2.38825154304504</v>
       </c>
       <c r="H409" t="n">
         <v>757900</v>
@@ -12259,7 +12259,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G410" t="n">
-        <v>2.36436915397644</v>
+        <v>2.36436939239502</v>
       </c>
       <c r="H410" t="n">
         <v>977540</v>
@@ -12346,7 +12346,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G413" t="n">
-        <v>2.27679991722107</v>
+        <v>2.27679967880249</v>
       </c>
       <c r="H413" t="n">
         <v>1403718</v>
@@ -12375,7 +12375,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G414" t="n">
-        <v>2.26724720001221</v>
+        <v>2.26724696159363</v>
       </c>
       <c r="H414" t="n">
         <v>1196625</v>
@@ -12404,7 +12404,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G415" t="n">
-        <v>2.30068254470825</v>
+        <v>2.30068278312683</v>
       </c>
       <c r="H415" t="n">
         <v>613532</v>
@@ -12549,7 +12549,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G420" t="n">
-        <v>2.29431390762329</v>
+        <v>2.29431414604187</v>
       </c>
       <c r="H420" t="n">
         <v>457338</v>
@@ -12578,7 +12578,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G421" t="n">
-        <v>2.33730244636536</v>
+        <v>2.33730220794678</v>
       </c>
       <c r="H421" t="n">
         <v>1265104</v>
@@ -12607,7 +12607,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G422" t="n">
-        <v>2.33411812782288</v>
+        <v>2.3341178894043</v>
       </c>
       <c r="H422" t="n">
         <v>683681</v>
@@ -12636,7 +12636,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G423" t="n">
-        <v>2.34844756126404</v>
+        <v>2.34844779968262</v>
       </c>
       <c r="H423" t="n">
         <v>685400</v>
@@ -12665,7 +12665,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G424" t="n">
-        <v>2.33252620697021</v>
+        <v>2.33252596855164</v>
       </c>
       <c r="H424" t="n">
         <v>735919</v>
@@ -12694,7 +12694,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="n">
-        <v>2.30864357948303</v>
+        <v>2.30864334106445</v>
       </c>
       <c r="H425" t="n">
         <v>805855</v>
@@ -12723,7 +12723,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G426" t="n">
-        <v>2.34844756126404</v>
+        <v>2.34844779968262</v>
       </c>
       <c r="H426" t="n">
         <v>723093</v>
@@ -12752,7 +12752,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G427" t="n">
-        <v>2.34844756126404</v>
+        <v>2.34844779968262</v>
       </c>
       <c r="H427" t="n">
         <v>1614230</v>
@@ -12781,7 +12781,7 @@
         <v>2.98399996757507</v>
       </c>
       <c r="G428" t="n">
-        <v>2.37551426887512</v>
+        <v>2.3755145072937</v>
       </c>
       <c r="H428" t="n">
         <v>1245196</v>
@@ -12810,7 +12810,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G429" t="n">
-        <v>2.40258097648621</v>
+        <v>2.40258145332336</v>
       </c>
       <c r="H429" t="n">
         <v>1162563</v>
@@ -12839,7 +12839,7 @@
         <v>3.00799989700317</v>
       </c>
       <c r="G430" t="n">
-        <v>2.39462041854858</v>
+        <v>2.39462018013</v>
       </c>
       <c r="H430" t="n">
         <v>876149</v>
@@ -12868,7 +12868,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43920111656189</v>
+        <v>2.43920087814331</v>
       </c>
       <c r="H431" t="n">
         <v>1993777</v>
@@ -12955,7 +12955,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G434" t="n">
-        <v>2.57771968841553</v>
+        <v>2.57771992683411</v>
       </c>
       <c r="H434" t="n">
         <v>2373534</v>
@@ -13042,7 +13042,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G437" t="n">
-        <v>2.59682559967041</v>
+        <v>2.59682583808899</v>
       </c>
       <c r="H437" t="n">
         <v>1443378</v>
@@ -13100,7 +13100,7 @@
         <v>3.2039999961853</v>
       </c>
       <c r="G439" t="n">
-        <v>2.55065298080444</v>
+        <v>2.55065274238586</v>
       </c>
       <c r="H439" t="n">
         <v>489510</v>
@@ -13129,7 +13129,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G440" t="n">
-        <v>2.58568024635315</v>
+        <v>2.58568072319031</v>
       </c>
       <c r="H440" t="n">
         <v>421765</v>
@@ -13158,7 +13158,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G441" t="n">
-        <v>2.58568024635315</v>
+        <v>2.58568072319031</v>
       </c>
       <c r="H441" t="n">
         <v>629599</v>
@@ -13216,7 +13216,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G443" t="n">
-        <v>2.56498193740845</v>
+        <v>2.56498217582703</v>
       </c>
       <c r="H443" t="n">
         <v>512784</v>
@@ -13245,7 +13245,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G444" t="n">
-        <v>2.60001063346863</v>
+        <v>2.60000991821289</v>
       </c>
       <c r="H444" t="n">
         <v>722959</v>
@@ -13303,7 +13303,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G446" t="n">
-        <v>2.60001063346863</v>
+        <v>2.60000991821289</v>
       </c>
       <c r="H446" t="n">
         <v>507708</v>
@@ -13332,7 +13332,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>2.61911606788635</v>
+        <v>2.61911582946777</v>
       </c>
       <c r="H447" t="n">
         <v>569921</v>
@@ -13390,7 +13390,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G449" t="n">
-        <v>2.61274743080139</v>
+        <v>2.61274766921997</v>
       </c>
       <c r="H449" t="n">
         <v>1008192</v>
@@ -13477,7 +13477,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G452" t="n">
-        <v>2.64459109306335</v>
+        <v>2.64459085464478</v>
       </c>
       <c r="H452" t="n">
         <v>818061</v>
@@ -13535,7 +13535,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G454" t="n">
-        <v>2.56020593643188</v>
+        <v>2.56020617485046</v>
       </c>
       <c r="H454" t="n">
         <v>934398</v>
@@ -13564,7 +13564,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G455" t="n">
-        <v>2.57612776756287</v>
+        <v>2.57612752914429</v>
       </c>
       <c r="H455" t="n">
         <v>580340</v>
@@ -13593,7 +13593,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G456" t="n">
-        <v>2.63822174072266</v>
+        <v>2.63822221755981</v>
       </c>
       <c r="H456" t="n">
         <v>1023456</v>
@@ -13680,7 +13680,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G459" t="n">
-        <v>2.73852849006653</v>
+        <v>2.73852896690369</v>
       </c>
       <c r="H459" t="n">
         <v>794697</v>
@@ -13709,7 +13709,7 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G460" t="n">
-        <v>2.72419881820679</v>
+        <v>2.72419929504395</v>
       </c>
       <c r="H460" t="n">
         <v>716646</v>
@@ -13738,7 +13738,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G461" t="n">
-        <v>2.74012088775635</v>
+        <v>2.74012064933777</v>
       </c>
       <c r="H461" t="n">
         <v>4070428</v>
@@ -13825,7 +13825,7 @@
         <v>3.44600009918213</v>
       </c>
       <c r="G464" t="n">
-        <v>2.74330496788025</v>
+        <v>2.74330520629883</v>
       </c>
       <c r="H464" t="n">
         <v>810084</v>
@@ -13854,7 +13854,7 @@
         <v>3.51600003242493</v>
       </c>
       <c r="G465" t="n">
-        <v>2.79903125762939</v>
+        <v>2.79903101921082</v>
       </c>
       <c r="H465" t="n">
         <v>1541603</v>
@@ -13883,7 +13883,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G466" t="n">
-        <v>2.80221581459045</v>
+        <v>2.80221557617188</v>
       </c>
       <c r="H466" t="n">
         <v>1027608</v>
@@ -13941,7 +13941,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>2.84998059272766</v>
+        <v>2.84998035430908</v>
       </c>
       <c r="H468" t="n">
         <v>1903251</v>
@@ -14028,7 +14028,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G471" t="n">
-        <v>2.94073414802551</v>
+        <v>2.94073390960693</v>
       </c>
       <c r="H471" t="n">
         <v>2019957</v>
@@ -14144,7 +14144,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>2.93754959106445</v>
+        <v>2.93754982948303</v>
       </c>
       <c r="H475" t="n">
         <v>968072</v>
@@ -14173,7 +14173,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G476" t="n">
-        <v>2.90252184867859</v>
+        <v>2.90252208709717</v>
       </c>
       <c r="H476" t="n">
         <v>1820893</v>
@@ -14202,7 +14202,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G477" t="n">
-        <v>2.8420193195343</v>
+        <v>2.84201955795288</v>
       </c>
       <c r="H477" t="n">
         <v>4515902</v>
@@ -14231,7 +14231,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G478" t="n">
-        <v>2.81017637252808</v>
+        <v>2.81017589569092</v>
       </c>
       <c r="H478" t="n">
         <v>3456844</v>
@@ -14260,7 +14260,7 @@
         <v>3.4539999961853</v>
       </c>
       <c r="G479" t="n">
-        <v>2.74967384338379</v>
+        <v>2.74967408180237</v>
       </c>
       <c r="H479" t="n">
         <v>5446955</v>
@@ -14289,7 +14289,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G480" t="n">
-        <v>2.62548518180847</v>
+        <v>2.62548470497131</v>
       </c>
       <c r="H480" t="n">
         <v>2617438</v>
@@ -14347,7 +14347,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G482" t="n">
-        <v>2.49492716789246</v>
+        <v>2.49492692947388</v>
       </c>
       <c r="H482" t="n">
         <v>4611280</v>
@@ -14376,7 +14376,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.4917426109314</v>
+        <v>2.49174284934998</v>
       </c>
       <c r="H483" t="n">
         <v>3697265</v>
@@ -14463,7 +14463,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G486" t="n">
-        <v>2.48537373542786</v>
+        <v>2.48537421226501</v>
       </c>
       <c r="H486" t="n">
         <v>1237843</v>
@@ -14492,7 +14492,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G487" t="n">
-        <v>2.45989918708801</v>
+        <v>2.45989942550659</v>
       </c>
       <c r="H487" t="n">
         <v>932298</v>
@@ -14579,7 +14579,7 @@
         <v>3.06200003623962</v>
       </c>
       <c r="G490" t="n">
-        <v>2.43760871887207</v>
+        <v>2.43760895729065</v>
       </c>
       <c r="H490" t="n">
         <v>1832928</v>
@@ -14608,7 +14608,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G491" t="n">
-        <v>2.44716167449951</v>
+        <v>2.44716191291809</v>
       </c>
       <c r="H491" t="n">
         <v>2154714</v>
@@ -14637,7 +14637,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G492" t="n">
-        <v>2.44716167449951</v>
+        <v>2.44716191291809</v>
       </c>
       <c r="H492" t="n">
         <v>1691378</v>
@@ -14666,7 +14666,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G493" t="n">
-        <v>2.46149110794067</v>
+        <v>2.46149158477783</v>
       </c>
       <c r="H493" t="n">
         <v>2679317</v>
@@ -14695,7 +14695,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G494" t="n">
-        <v>2.5172176361084</v>
+        <v>2.51721739768982</v>
       </c>
       <c r="H494" t="n">
         <v>3107216</v>
@@ -14753,7 +14753,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G496" t="n">
-        <v>2.53154683113098</v>
+        <v>2.5315465927124</v>
       </c>
       <c r="H496" t="n">
         <v>2034742</v>
@@ -14782,7 +14782,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>2.48378157615662</v>
+        <v>2.4837818145752</v>
       </c>
       <c r="H497" t="n">
         <v>1452840</v>
@@ -14840,7 +14840,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G499" t="n">
-        <v>2.52040147781372</v>
+        <v>2.5204017162323</v>
       </c>
       <c r="H499" t="n">
         <v>1758820</v>
@@ -14869,7 +14869,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G500" t="n">
-        <v>2.53473091125488</v>
+        <v>2.53473162651062</v>
       </c>
       <c r="H500" t="n">
         <v>1330089</v>
@@ -14898,7 +14898,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G501" t="n">
-        <v>2.60160207748413</v>
+        <v>2.60160183906555</v>
       </c>
       <c r="H501" t="n">
         <v>1303907</v>
@@ -14927,7 +14927,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G502" t="n">
-        <v>2.55383729934692</v>
+        <v>2.55383706092834</v>
       </c>
       <c r="H502" t="n">
         <v>1941059</v>
@@ -14956,7 +14956,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G503" t="n">
-        <v>2.53154683113098</v>
+        <v>2.5315465927124</v>
       </c>
       <c r="H503" t="n">
         <v>1750900</v>
@@ -14985,7 +14985,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>2.50766444206238</v>
+        <v>2.5076642036438</v>
       </c>
       <c r="H504" t="n">
         <v>1490065</v>
@@ -15014,7 +15014,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G505" t="n">
-        <v>2.515625</v>
+        <v>2.51562523841858</v>
       </c>
       <c r="H505" t="n">
         <v>2056515</v>
@@ -15043,7 +15043,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G506" t="n">
-        <v>2.58886480331421</v>
+        <v>2.58886504173279</v>
       </c>
       <c r="H506" t="n">
         <v>4068179</v>
@@ -15072,7 +15072,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G507" t="n">
-        <v>2.56975865364075</v>
+        <v>2.56975889205933</v>
       </c>
       <c r="H507" t="n">
         <v>1259757</v>
@@ -15101,7 +15101,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G508" t="n">
-        <v>2.51084852218628</v>
+        <v>2.51084876060486</v>
       </c>
       <c r="H508" t="n">
         <v>2514530</v>
@@ -15159,7 +15159,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G510" t="n">
-        <v>2.5251784324646</v>
+        <v>2.52517819404602</v>
       </c>
       <c r="H510" t="n">
         <v>457099</v>
@@ -15188,7 +15188,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G511" t="n">
-        <v>2.56179809570312</v>
+        <v>2.56179785728455</v>
       </c>
       <c r="H511" t="n">
         <v>494732</v>
@@ -15246,7 +15246,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G513" t="n">
-        <v>2.59841775894165</v>
+        <v>2.59841799736023</v>
       </c>
       <c r="H513" t="n">
         <v>975318</v>
@@ -15275,7 +15275,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G514" t="n">
-        <v>2.62707686424255</v>
+        <v>2.62707662582397</v>
       </c>
       <c r="H514" t="n">
         <v>1221081</v>
@@ -15304,7 +15304,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G515" t="n">
-        <v>2.65892052650452</v>
+        <v>2.65892004966736</v>
       </c>
       <c r="H515" t="n">
         <v>1978965</v>
@@ -15333,7 +15333,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G516" t="n">
-        <v>2.75604248046875</v>
+        <v>2.75604271888733</v>
       </c>
       <c r="H516" t="n">
         <v>1906217</v>
@@ -15391,7 +15391,7 @@
         <v>3.45199990272522</v>
       </c>
       <c r="G518" t="n">
-        <v>2.74808144569397</v>
+        <v>2.74808168411255</v>
       </c>
       <c r="H518" t="n">
         <v>1415599</v>
@@ -15420,7 +15420,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G519" t="n">
-        <v>2.74012088775635</v>
+        <v>2.74012064933777</v>
       </c>
       <c r="H519" t="n">
         <v>911320</v>
@@ -15449,7 +15449,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G520" t="n">
-        <v>2.75604248046875</v>
+        <v>2.75604271888733</v>
       </c>
       <c r="H520" t="n">
         <v>605258</v>
@@ -15478,7 +15478,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G521" t="n">
-        <v>2.67643427848816</v>
+        <v>2.67643404006958</v>
       </c>
       <c r="H521" t="n">
         <v>2011203</v>
@@ -15507,7 +15507,7 @@
         <v>3.31399989128113</v>
       </c>
       <c r="G522" t="n">
-        <v>2.63822174072266</v>
+        <v>2.63822221755981</v>
       </c>
       <c r="H522" t="n">
         <v>1918826</v>
@@ -15536,7 +15536,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G523" t="n">
-        <v>2.63503789901733</v>
+        <v>2.63503766059875</v>
       </c>
       <c r="H523" t="n">
         <v>1392619</v>
@@ -15594,7 +15594,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G525" t="n">
-        <v>2.61911606788635</v>
+        <v>2.61911582946777</v>
       </c>
       <c r="H525" t="n">
         <v>990093</v>
@@ -15623,7 +15623,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G526" t="n">
-        <v>2.63185358047485</v>
+        <v>2.6318531036377</v>
       </c>
       <c r="H526" t="n">
         <v>1221618</v>
@@ -15710,7 +15710,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G529" t="n">
-        <v>2.56816697120667</v>
+        <v>2.56816673278809</v>
       </c>
       <c r="H529" t="n">
         <v>1409532</v>
@@ -15739,7 +15739,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G530" t="n">
-        <v>2.541100025177</v>
+        <v>2.54109978675842</v>
       </c>
       <c r="H530" t="n">
         <v>2378901</v>
@@ -15768,7 +15768,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G531" t="n">
-        <v>2.56816697120667</v>
+        <v>2.56816673278809</v>
       </c>
       <c r="H531" t="n">
         <v>2024887</v>
@@ -15826,7 +15826,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G533" t="n">
-        <v>2.58090424537659</v>
+        <v>2.58090400695801</v>
       </c>
       <c r="H533" t="n">
         <v>735592</v>
@@ -15884,7 +15884,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G535" t="n">
-        <v>2.41213417053223</v>
+        <v>2.41213440895081</v>
       </c>
       <c r="H535" t="n">
         <v>3237676</v>
@@ -15913,7 +15913,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G536" t="n">
-        <v>2.34526348114014</v>
+        <v>2.34526324272156</v>
       </c>
       <c r="H536" t="n">
         <v>2994862</v>
@@ -15942,7 +15942,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>2.23699593544006</v>
+        <v>2.23699569702148</v>
       </c>
       <c r="H537" t="n">
         <v>6215290</v>
@@ -16000,7 +16000,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G539" t="n">
-        <v>2.12872838973999</v>
+        <v>2.12872862815857</v>
       </c>
       <c r="H539" t="n">
         <v>4819283</v>
@@ -16058,7 +16058,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>2.05389642715454</v>
+        <v>2.05389666557312</v>
       </c>
       <c r="H541" t="n">
         <v>1892118</v>
@@ -16087,7 +16087,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G542" t="n">
-        <v>2.01409268379211</v>
+        <v>2.01409220695496</v>
       </c>
       <c r="H542" t="n">
         <v>2601422</v>
@@ -16116,7 +16116,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G543" t="n">
-        <v>2.0570809841156</v>
+        <v>2.05708074569702</v>
       </c>
       <c r="H543" t="n">
         <v>1323647</v>
@@ -16174,7 +16174,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G545" t="n">
-        <v>2.07300281524658</v>
+        <v>2.073002576828</v>
       </c>
       <c r="H545" t="n">
         <v>2877331</v>
@@ -16203,7 +16203,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G546" t="n">
-        <v>2.0570809841156</v>
+        <v>2.05708074569702</v>
       </c>
       <c r="H546" t="n">
         <v>755000</v>
@@ -16232,7 +16232,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G547" t="n">
-        <v>2.0570809841156</v>
+        <v>2.05708074569702</v>
       </c>
       <c r="H547" t="n">
         <v>813711</v>
@@ -16261,7 +16261,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G548" t="n">
-        <v>2.10643792152405</v>
+        <v>2.10643768310547</v>
       </c>
       <c r="H548" t="n">
         <v>1554469</v>
@@ -16290,7 +16290,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.09370088577271</v>
+        <v>2.09370064735413</v>
       </c>
       <c r="H549" t="n">
         <v>2976419</v>
@@ -16319,7 +16319,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G550" t="n">
-        <v>2.04593563079834</v>
+        <v>2.04593539237976</v>
       </c>
       <c r="H550" t="n">
         <v>1865883</v>
@@ -16348,7 +16348,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G551" t="n">
-        <v>2.01727652549744</v>
+        <v>2.01727676391602</v>
       </c>
       <c r="H551" t="n">
         <v>1462101</v>
@@ -16377,7 +16377,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G552" t="n">
-        <v>2.00294733047485</v>
+        <v>2.00294756889343</v>
       </c>
       <c r="H552" t="n">
         <v>2572034</v>
@@ -16406,7 +16406,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G553" t="n">
-        <v>1.98702573776245</v>
+        <v>1.98702526092529</v>
       </c>
       <c r="H553" t="n">
         <v>1328048</v>
@@ -16464,7 +16464,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G555" t="n">
-        <v>1.90741693973541</v>
+        <v>1.9074170589447</v>
       </c>
       <c r="H555" t="n">
         <v>2204356</v>
@@ -16493,7 +16493,7 @@
         <v>2.3840000629425</v>
       </c>
       <c r="G556" t="n">
-        <v>1.89786410331726</v>
+        <v>1.89786398410797</v>
       </c>
       <c r="H556" t="n">
         <v>1534891</v>
@@ -16522,7 +16522,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>2.00613141059875</v>
+        <v>2.00613164901733</v>
       </c>
       <c r="H557" t="n">
         <v>4435894</v>
@@ -16551,7 +16551,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G558" t="n">
-        <v>2.01090812683105</v>
+        <v>2.01090788841248</v>
       </c>
       <c r="H558" t="n">
         <v>1799452</v>
@@ -16580,7 +16580,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G559" t="n">
-        <v>2.03160619735718</v>
+        <v>2.0316059589386</v>
       </c>
       <c r="H559" t="n">
         <v>1090698</v>
@@ -16638,7 +16638,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G561" t="n">
-        <v>2.03001379966736</v>
+        <v>2.03001403808594</v>
       </c>
       <c r="H561" t="n">
         <v>1984054</v>
@@ -16667,7 +16667,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G562" t="n">
-        <v>1.91856229305267</v>
+        <v>1.91856217384338</v>
       </c>
       <c r="H562" t="n">
         <v>4495971</v>
@@ -16696,7 +16696,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G563" t="n">
-        <v>1.80870306491852</v>
+        <v>1.80870270729065</v>
       </c>
       <c r="H563" t="n">
         <v>11295853</v>
@@ -16725,7 +16725,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G564" t="n">
-        <v>1.86442875862122</v>
+        <v>1.86442863941193</v>
       </c>
       <c r="H564" t="n">
         <v>5503208</v>
@@ -16812,7 +16812,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G567" t="n">
-        <v>1.99976301193237</v>
+        <v>1.99976289272308</v>
       </c>
       <c r="H567" t="n">
         <v>1325179</v>
@@ -16841,7 +16841,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G568" t="n">
-        <v>1.93766808509827</v>
+        <v>1.93766844272614</v>
       </c>
       <c r="H568" t="n">
         <v>2277688</v>
@@ -16870,7 +16870,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>1.85487568378448</v>
+        <v>1.85487532615662</v>
       </c>
       <c r="H569" t="n">
         <v>4051183</v>
@@ -16928,7 +16928,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G571" t="n">
-        <v>1.88990330696106</v>
+        <v>1.88990354537964</v>
       </c>
       <c r="H571" t="n">
         <v>1404482</v>
@@ -17015,7 +17015,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G574" t="n">
-        <v>1.91856229305267</v>
+        <v>1.91856217384338</v>
       </c>
       <c r="H574" t="n">
         <v>1225403</v>
@@ -17044,7 +17044,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G575" t="n">
-        <v>1.89945602416992</v>
+        <v>1.8994562625885</v>
       </c>
       <c r="H575" t="n">
         <v>1034331</v>
@@ -17073,7 +17073,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G576" t="n">
-        <v>1.90582513809204</v>
+        <v>1.90582489967346</v>
       </c>
       <c r="H576" t="n">
         <v>1701979</v>
@@ -17102,7 +17102,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G577" t="n">
-        <v>1.95199751853943</v>
+        <v>1.95199799537659</v>
       </c>
       <c r="H577" t="n">
         <v>2027295</v>
@@ -17160,7 +17160,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.92652308940887</v>
+        <v>1.92652332782745</v>
       </c>
       <c r="H579" t="n">
         <v>722313</v>
@@ -17189,7 +17189,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G580" t="n">
-        <v>1.92970728874207</v>
+        <v>1.92970740795135</v>
       </c>
       <c r="H580" t="n">
         <v>1260607</v>
@@ -17218,7 +17218,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>1.90264070034027</v>
+        <v>1.90264093875885</v>
       </c>
       <c r="H581" t="n">
         <v>921579</v>
@@ -17247,7 +17247,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G582" t="n">
-        <v>1.90423262119293</v>
+        <v>1.90423285961151</v>
       </c>
       <c r="H582" t="n">
         <v>1500268</v>
@@ -17276,7 +17276,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G583" t="n">
-        <v>1.89627182483673</v>
+        <v>1.8962721824646</v>
       </c>
       <c r="H583" t="n">
         <v>944622</v>
@@ -17334,7 +17334,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G585" t="n">
-        <v>1.85487568378448</v>
+        <v>1.85487532615662</v>
       </c>
       <c r="H585" t="n">
         <v>1777023</v>
@@ -17363,7 +17363,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G586" t="n">
-        <v>1.85009908676147</v>
+        <v>1.8500988483429</v>
       </c>
       <c r="H586" t="n">
         <v>1482418</v>
@@ -17392,7 +17392,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G587" t="n">
-        <v>1.86283624172211</v>
+        <v>1.86283612251282</v>
       </c>
       <c r="H587" t="n">
         <v>2223013</v>
@@ -17421,7 +17421,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>1.83099317550659</v>
+        <v>1.83099293708801</v>
       </c>
       <c r="H588" t="n">
         <v>2040960</v>
@@ -17450,7 +17450,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G589" t="n">
-        <v>1.81507134437561</v>
+        <v>1.81507122516632</v>
       </c>
       <c r="H589" t="n">
         <v>1297798</v>
@@ -17479,7 +17479,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G590" t="n">
-        <v>1.81507134437561</v>
+        <v>1.81507122516632</v>
       </c>
       <c r="H590" t="n">
         <v>1110350</v>
@@ -17508,7 +17508,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G591" t="n">
-        <v>1.80392634868622</v>
+        <v>1.80392611026764</v>
       </c>
       <c r="H591" t="n">
         <v>1332399</v>
@@ -17537,7 +17537,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G592" t="n">
-        <v>1.76412177085876</v>
+        <v>1.76412224769592</v>
       </c>
       <c r="H592" t="n">
         <v>2941699</v>
@@ -17566,7 +17566,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G593" t="n">
-        <v>1.78004372119904</v>
+        <v>1.78004360198975</v>
       </c>
       <c r="H593" t="n">
         <v>1670608</v>
@@ -17595,7 +17595,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G594" t="n">
-        <v>1.88990330696106</v>
+        <v>1.88990354537964</v>
       </c>
       <c r="H594" t="n">
         <v>5320330</v>
@@ -17624,7 +17624,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G595" t="n">
-        <v>2.06663393974304</v>
+        <v>2.06663370132446</v>
       </c>
       <c r="H595" t="n">
         <v>11848663</v>
@@ -17653,7 +17653,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G596" t="n">
-        <v>1.8914954662323</v>
+        <v>1.89149534702301</v>
       </c>
       <c r="H596" t="n">
         <v>13135214</v>
@@ -17682,7 +17682,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>1.85487568378448</v>
+        <v>1.85487532615662</v>
       </c>
       <c r="H597" t="n">
         <v>5522687</v>
@@ -17711,7 +17711,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G598" t="n">
-        <v>1.87238955497742</v>
+        <v>1.87238931655884</v>
       </c>
       <c r="H598" t="n">
         <v>2693236</v>
@@ -17740,7 +17740,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G599" t="n">
-        <v>1.85169100761414</v>
+        <v>1.851691365242</v>
       </c>
       <c r="H599" t="n">
         <v>1869245</v>
@@ -17769,7 +17769,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G600" t="n">
-        <v>1.87238955497742</v>
+        <v>1.87238931655884</v>
       </c>
       <c r="H600" t="n">
         <v>1249089</v>
@@ -17798,7 +17798,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G601" t="n">
-        <v>1.826216340065</v>
+        <v>1.82621645927429</v>
       </c>
       <c r="H601" t="n">
         <v>2208316</v>
@@ -17827,7 +17827,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>1.83576941490173</v>
+        <v>1.83576953411102</v>
       </c>
       <c r="H602" t="n">
         <v>981017</v>
@@ -17885,7 +17885,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G604" t="n">
-        <v>1.85487568378448</v>
+        <v>1.85487532615662</v>
       </c>
       <c r="H604" t="n">
         <v>1300520</v>
@@ -17914,7 +17914,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G605" t="n">
-        <v>1.8182555437088</v>
+        <v>1.81825542449951</v>
       </c>
       <c r="H605" t="n">
         <v>3157751</v>
@@ -17943,7 +17943,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G606" t="n">
-        <v>1.80074179172516</v>
+        <v>1.80074191093445</v>
       </c>
       <c r="H606" t="n">
         <v>1597477</v>
@@ -17972,7 +17972,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.77526712417603</v>
+        <v>1.77526724338531</v>
       </c>
       <c r="H607" t="n">
         <v>1953879</v>
@@ -18001,7 +18001,7 @@
         <v>2.25200009346008</v>
       </c>
       <c r="G608" t="n">
-        <v>1.83642721176147</v>
+        <v>1.8364269733429</v>
       </c>
       <c r="H608" t="n">
         <v>1235443</v>
@@ -18030,7 +18030,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G609" t="n">
-        <v>1.8250105381012</v>
+        <v>1.82501041889191</v>
       </c>
       <c r="H609" t="n">
         <v>1866217</v>
@@ -18059,7 +18059,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>1.81848692893982</v>
+        <v>1.81848680973053</v>
       </c>
       <c r="H610" t="n">
         <v>1189890</v>
@@ -18088,7 +18088,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G611" t="n">
-        <v>1.82174849510193</v>
+        <v>1.82174861431122</v>
       </c>
       <c r="H611" t="n">
         <v>639504</v>
@@ -18146,7 +18146,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>1.72878539562225</v>
+        <v>1.72878551483154</v>
       </c>
       <c r="H613" t="n">
         <v>2708744</v>
@@ -18204,7 +18204,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G615" t="n">
-        <v>1.72878539562225</v>
+        <v>1.72878551483154</v>
       </c>
       <c r="H615" t="n">
         <v>1733659</v>
@@ -18233,7 +18233,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G616" t="n">
-        <v>1.71736896038055</v>
+        <v>1.71736907958984</v>
       </c>
       <c r="H616" t="n">
         <v>1661744</v>
@@ -18262,7 +18262,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G617" t="n">
-        <v>1.7858681678772</v>
+        <v>1.78586828708649</v>
       </c>
       <c r="H617" t="n">
         <v>2304857</v>
@@ -18291,7 +18291,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G618" t="n">
-        <v>1.75814235210419</v>
+        <v>1.7581422328949</v>
       </c>
       <c r="H618" t="n">
         <v>921766</v>
@@ -18320,7 +18320,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G619" t="n">
-        <v>1.76140415668488</v>
+        <v>1.76140427589417</v>
       </c>
       <c r="H619" t="n">
         <v>995750</v>
@@ -18349,7 +18349,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G620" t="n">
-        <v>1.7744517326355</v>
+        <v>1.77445161342621</v>
       </c>
       <c r="H620" t="n">
         <v>1303635</v>
@@ -18378,7 +18378,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G621" t="n">
-        <v>1.76140415668488</v>
+        <v>1.76140427589417</v>
       </c>
       <c r="H621" t="n">
         <v>808647</v>
@@ -18407,7 +18407,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G622" t="n">
-        <v>1.7385710477829</v>
+        <v>1.73857116699219</v>
       </c>
       <c r="H622" t="n">
         <v>583631</v>
@@ -18436,7 +18436,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G623" t="n">
-        <v>1.76140415668488</v>
+        <v>1.76140427589417</v>
       </c>
       <c r="H623" t="n">
         <v>810246</v>
@@ -18465,7 +18465,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G624" t="n">
-        <v>1.76629674434662</v>
+        <v>1.76629710197449</v>
       </c>
       <c r="H624" t="n">
         <v>2399225</v>
@@ -18494,7 +18494,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G625" t="n">
-        <v>1.76629674434662</v>
+        <v>1.76629710197449</v>
       </c>
       <c r="H625" t="n">
         <v>566494</v>
@@ -18523,7 +18523,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G626" t="n">
-        <v>1.84458184242249</v>
+        <v>1.8445817232132</v>
       </c>
       <c r="H626" t="n">
         <v>1938784</v>
@@ -18552,7 +18552,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>1.86741483211517</v>
+        <v>1.86741471290588</v>
       </c>
       <c r="H627" t="n">
         <v>2849945</v>
@@ -18581,7 +18581,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G628" t="n">
-        <v>1.84458184242249</v>
+        <v>1.8445817232132</v>
       </c>
       <c r="H628" t="n">
         <v>450028</v>
@@ -18639,7 +18639,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G630" t="n">
-        <v>1.82664132118225</v>
+        <v>1.82664144039154</v>
       </c>
       <c r="H630" t="n">
         <v>683361</v>
@@ -18697,7 +18697,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G632" t="n">
-        <v>1.79239201545715</v>
+        <v>1.79239177703857</v>
       </c>
       <c r="H632" t="n">
         <v>2137127</v>
@@ -18726,7 +18726,7 @@
         <v>2.15199995040894</v>
       </c>
       <c r="G633" t="n">
-        <v>1.75488030910492</v>
+        <v>1.7548805475235</v>
       </c>
       <c r="H633" t="n">
         <v>634287</v>
@@ -18842,7 +18842,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G637" t="n">
-        <v>1.82011795043945</v>
+        <v>1.82011783123016</v>
       </c>
       <c r="H637" t="n">
         <v>2298555</v>
@@ -18871,7 +18871,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G638" t="n">
-        <v>1.8869856595993</v>
+        <v>1.88698577880859</v>
       </c>
       <c r="H638" t="n">
         <v>2351541</v>
@@ -18900,7 +18900,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G639" t="n">
-        <v>1.89187836647034</v>
+        <v>1.89187860488892</v>
       </c>
       <c r="H639" t="n">
         <v>1290827</v>
@@ -18929,7 +18929,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G640" t="n">
-        <v>1.8135941028595</v>
+        <v>1.81359398365021</v>
       </c>
       <c r="H640" t="n">
         <v>2559667</v>
@@ -18958,7 +18958,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G641" t="n">
-        <v>1.86578369140625</v>
+        <v>1.86578404903412</v>
       </c>
       <c r="H641" t="n">
         <v>1601256</v>
@@ -19016,7 +19016,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G643" t="n">
-        <v>1.90655732154846</v>
+        <v>1.9065568447113</v>
       </c>
       <c r="H643" t="n">
         <v>1155916</v>
@@ -19045,7 +19045,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G644" t="n">
-        <v>1.88372409343719</v>
+        <v>1.88372397422791</v>
       </c>
       <c r="H644" t="n">
         <v>1335295</v>
@@ -19074,7 +19074,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G645" t="n">
-        <v>1.84295058250427</v>
+        <v>1.84295082092285</v>
       </c>
       <c r="H645" t="n">
         <v>1183341</v>
@@ -19103,7 +19103,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>1.86741483211517</v>
+        <v>1.86741471290588</v>
       </c>
       <c r="H646" t="n">
         <v>465309</v>
@@ -19161,7 +19161,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G648" t="n">
-        <v>1.81685566902161</v>
+        <v>1.81685602664948</v>
       </c>
       <c r="H648" t="n">
         <v>605104</v>
@@ -19190,7 +19190,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G649" t="n">
-        <v>1.81196272373199</v>
+        <v>1.81196296215057</v>
       </c>
       <c r="H649" t="n">
         <v>492569</v>
@@ -19219,7 +19219,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>1.81848692893982</v>
+        <v>1.81848680973053</v>
       </c>
       <c r="H650" t="n">
         <v>710538</v>
@@ -19248,7 +19248,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G651" t="n">
-        <v>1.79239201545715</v>
+        <v>1.79239177703857</v>
       </c>
       <c r="H651" t="n">
         <v>2071396</v>
@@ -19277,7 +19277,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G652" t="n">
-        <v>1.7744517326355</v>
+        <v>1.77445161342621</v>
       </c>
       <c r="H652" t="n">
         <v>882911</v>
@@ -19335,7 +19335,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78749918937683</v>
+        <v>1.78749883174896</v>
       </c>
       <c r="H654" t="n">
         <v>659037</v>
@@ -19364,7 +19364,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>1.75324964523315</v>
+        <v>1.75324976444244</v>
       </c>
       <c r="H655" t="n">
         <v>913367</v>
@@ -19393,7 +19393,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G656" t="n">
-        <v>1.7385710477829</v>
+        <v>1.73857116699219</v>
       </c>
       <c r="H656" t="n">
         <v>3598224</v>
@@ -19451,7 +19451,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G658" t="n">
-        <v>1.83316504955292</v>
+        <v>1.8331652879715</v>
       </c>
       <c r="H658" t="n">
         <v>1422538</v>
@@ -19480,7 +19480,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G659" t="n">
-        <v>1.84295058250427</v>
+        <v>1.84295082092285</v>
       </c>
       <c r="H659" t="n">
         <v>912189</v>
@@ -19509,7 +19509,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G660" t="n">
-        <v>1.84131979942322</v>
+        <v>1.84131968021393</v>
       </c>
       <c r="H660" t="n">
         <v>617222</v>
@@ -19538,7 +19538,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G661" t="n">
-        <v>1.82337975502014</v>
+        <v>1.82337951660156</v>
       </c>
       <c r="H661" t="n">
         <v>839503</v>
@@ -19567,7 +19567,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G662" t="n">
-        <v>1.79239201545715</v>
+        <v>1.79239177703857</v>
       </c>
       <c r="H662" t="n">
         <v>897689</v>
@@ -19596,7 +19596,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G663" t="n">
-        <v>1.79076099395752</v>
+        <v>1.79076111316681</v>
       </c>
       <c r="H663" t="n">
         <v>561281</v>
@@ -19625,7 +19625,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G664" t="n">
-        <v>1.82011795043945</v>
+        <v>1.82011783123016</v>
       </c>
       <c r="H664" t="n">
         <v>676673</v>
@@ -19654,7 +19654,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G665" t="n">
-        <v>1.89187836647034</v>
+        <v>1.89187860488892</v>
       </c>
       <c r="H665" t="n">
         <v>4688332</v>
@@ -19683,7 +19683,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G666" t="n">
-        <v>1.88046193122864</v>
+        <v>1.88046205043793</v>
       </c>
       <c r="H666" t="n">
         <v>845679</v>
@@ -19712,7 +19712,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G667" t="n">
-        <v>1.85926008224487</v>
+        <v>1.85925984382629</v>
       </c>
       <c r="H667" t="n">
         <v>963738</v>
@@ -19741,7 +19741,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G668" t="n">
-        <v>1.86415266990662</v>
+        <v>1.8641529083252</v>
       </c>
       <c r="H668" t="n">
         <v>885313</v>
@@ -19799,7 +19799,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G670" t="n">
-        <v>1.87556946277618</v>
+        <v>1.8755692243576</v>
       </c>
       <c r="H670" t="n">
         <v>1047101</v>
@@ -19828,7 +19828,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G671" t="n">
-        <v>1.90818786621094</v>
+        <v>1.90818774700165</v>
       </c>
       <c r="H671" t="n">
         <v>1160035</v>
@@ -19886,7 +19886,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G673" t="n">
-        <v>1.99136519432068</v>
+        <v>1.9913649559021</v>
       </c>
       <c r="H673" t="n">
         <v>853924</v>
@@ -19915,7 +19915,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G674" t="n">
-        <v>1.99136519432068</v>
+        <v>1.9913649559021</v>
       </c>
       <c r="H674" t="n">
         <v>854975</v>
@@ -19944,7 +19944,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G675" t="n">
-        <v>1.95548498630524</v>
+        <v>1.95548462867737</v>
       </c>
       <c r="H675" t="n">
         <v>2650527</v>
@@ -19973,7 +19973,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G676" t="n">
-        <v>1.9685320854187</v>
+        <v>1.96853232383728</v>
       </c>
       <c r="H676" t="n">
         <v>928396</v>
@@ -20031,7 +20031,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G678" t="n">
-        <v>1.89024794101715</v>
+        <v>1.89024782180786</v>
       </c>
       <c r="H678" t="n">
         <v>886735</v>
@@ -20060,7 +20060,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G679" t="n">
-        <v>1.86415266990662</v>
+        <v>1.8641529083252</v>
       </c>
       <c r="H679" t="n">
         <v>868801</v>
@@ -20089,7 +20089,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G680" t="n">
-        <v>1.8135941028595</v>
+        <v>1.81359398365021</v>
       </c>
       <c r="H680" t="n">
         <v>1115411</v>
@@ -20118,7 +20118,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71084558963776</v>
+        <v>1.71084547042847</v>
       </c>
       <c r="H681" t="n">
         <v>2819967</v>
@@ -20205,7 +20205,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82337975502014</v>
+        <v>1.82337951660156</v>
       </c>
       <c r="H684" t="n">
         <v>2326497</v>
@@ -20234,7 +20234,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>1.82664132118225</v>
+        <v>1.82664144039154</v>
       </c>
       <c r="H685" t="n">
         <v>2020822</v>
@@ -20263,7 +20263,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G686" t="n">
-        <v>1.85436713695526</v>
+        <v>1.85436701774597</v>
       </c>
       <c r="H686" t="n">
         <v>826482</v>
@@ -20292,7 +20292,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G687" t="n">
-        <v>1.9147115945816</v>
+        <v>1.91471171379089</v>
       </c>
       <c r="H687" t="n">
         <v>1051261</v>
@@ -20350,7 +20350,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G689" t="n">
-        <v>1.91308093070984</v>
+        <v>1.91308045387268</v>
       </c>
       <c r="H689" t="n">
         <v>689161</v>
@@ -20379,7 +20379,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G690" t="n">
-        <v>1.89840245246887</v>
+        <v>1.89840221405029</v>
       </c>
       <c r="H690" t="n">
         <v>429766</v>
@@ -20408,7 +20408,7 @@
         <v>2.28600001335144</v>
       </c>
       <c r="G691" t="n">
-        <v>1.86415266990662</v>
+        <v>1.8641529083252</v>
       </c>
       <c r="H691" t="n">
         <v>339281</v>
@@ -20437,7 +20437,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G692" t="n">
-        <v>1.88046193122864</v>
+        <v>1.88046205043793</v>
       </c>
       <c r="H692" t="n">
         <v>471227</v>
@@ -20466,7 +20466,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G693" t="n">
-        <v>1.84295058250427</v>
+        <v>1.84295082092285</v>
       </c>
       <c r="H693" t="n">
         <v>805042</v>
@@ -20495,7 +20495,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G694" t="n">
-        <v>1.81685566902161</v>
+        <v>1.81685602664948</v>
       </c>
       <c r="H694" t="n">
         <v>1394273</v>
@@ -20524,7 +20524,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G695" t="n">
-        <v>1.80707013607025</v>
+        <v>1.80707037448883</v>
       </c>
       <c r="H695" t="n">
         <v>756669</v>
@@ -20553,7 +20553,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G696" t="n">
-        <v>1.8135941028595</v>
+        <v>1.81359398365021</v>
       </c>
       <c r="H696" t="n">
         <v>998393</v>
@@ -20582,7 +20582,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G697" t="n">
-        <v>1.7940229177475</v>
+        <v>1.79402267932892</v>
       </c>
       <c r="H697" t="n">
         <v>672268</v>
@@ -20611,7 +20611,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G698" t="n">
-        <v>1.78749918937683</v>
+        <v>1.78749883174896</v>
       </c>
       <c r="H698" t="n">
         <v>796654</v>
@@ -20640,7 +20640,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G699" t="n">
-        <v>1.75324964523315</v>
+        <v>1.75324976444244</v>
       </c>
       <c r="H699" t="n">
         <v>1589594</v>
@@ -20669,7 +20669,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>1.75324964523315</v>
+        <v>1.75324976444244</v>
       </c>
       <c r="H700" t="n">
         <v>570256</v>
@@ -20698,7 +20698,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G701" t="n">
-        <v>1.73041641712189</v>
+        <v>1.73041653633118</v>
       </c>
       <c r="H701" t="n">
         <v>811499</v>
@@ -20727,7 +20727,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G702" t="n">
-        <v>1.70105981826782</v>
+        <v>1.70105969905853</v>
       </c>
       <c r="H702" t="n">
         <v>929920</v>
@@ -20756,7 +20756,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G703" t="n">
-        <v>1.62929904460907</v>
+        <v>1.62929892539978</v>
       </c>
       <c r="H703" t="n">
         <v>2772603</v>
@@ -20785,7 +20785,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G704" t="n">
-        <v>1.65050113201141</v>
+        <v>1.65050101280212</v>
       </c>
       <c r="H704" t="n">
         <v>2017014</v>
@@ -20814,7 +20814,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G705" t="n">
-        <v>1.6619176864624</v>
+        <v>1.66191744804382</v>
       </c>
       <c r="H705" t="n">
         <v>6571728</v>
@@ -20843,7 +20843,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G706" t="n">
-        <v>1.6186980009079</v>
+        <v>1.61869788169861</v>
       </c>
       <c r="H706" t="n">
         <v>1091102</v>
@@ -20872,7 +20872,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G707" t="n">
-        <v>1.58607923984528</v>
+        <v>1.58607935905457</v>
       </c>
       <c r="H707" t="n">
         <v>1261183</v>
@@ -20901,7 +20901,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G708" t="n">
-        <v>1.57384717464447</v>
+        <v>1.57384729385376</v>
       </c>
       <c r="H708" t="n">
         <v>980940</v>
@@ -20959,7 +20959,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G710" t="n">
-        <v>1.48169982433319</v>
+        <v>1.4816997051239</v>
       </c>
       <c r="H710" t="n">
         <v>2572970</v>
@@ -21017,7 +21017,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G712" t="n">
-        <v>1.48496162891388</v>
+        <v>1.48496150970459</v>
       </c>
       <c r="H712" t="n">
         <v>915632</v>
@@ -21075,7 +21075,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.48822355270386</v>
+        <v>1.48822343349457</v>
       </c>
       <c r="H714" t="n">
         <v>3092187</v>
@@ -21104,7 +21104,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G715" t="n">
-        <v>1.4857771396637</v>
+        <v>1.48577690124512</v>
       </c>
       <c r="H715" t="n">
         <v>1758890</v>
@@ -21133,7 +21133,7 @@
         <v>1.84200000762939</v>
       </c>
       <c r="G716" t="n">
-        <v>1.50208628177643</v>
+        <v>1.50208640098572</v>
       </c>
       <c r="H716" t="n">
         <v>2096415</v>
@@ -21162,7 +21162,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G717" t="n">
-        <v>1.46212863922119</v>
+        <v>1.46212875843048</v>
       </c>
       <c r="H717" t="n">
         <v>814779</v>
@@ -21191,7 +21191,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>1.45968234539032</v>
+        <v>1.45968210697174</v>
       </c>
       <c r="H718" t="n">
         <v>1383440</v>
@@ -21220,7 +21220,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G719" t="n">
-        <v>1.46457517147064</v>
+        <v>1.46457505226135</v>
       </c>
       <c r="H719" t="n">
         <v>887906</v>
@@ -21249,7 +21249,7 @@
         <v>1.88100004196167</v>
       </c>
       <c r="G720" t="n">
-        <v>1.53388953208923</v>
+        <v>1.53388965129852</v>
       </c>
       <c r="H720" t="n">
         <v>1295036</v>
@@ -21394,7 +21394,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G725" t="n">
-        <v>1.62032866477966</v>
+        <v>1.62032890319824</v>
       </c>
       <c r="H725" t="n">
         <v>678094</v>
@@ -21481,7 +21481,7 @@
         <v>1.98300004005432</v>
       </c>
       <c r="G728" t="n">
-        <v>1.61706686019897</v>
+        <v>1.61706697940826</v>
       </c>
       <c r="H728" t="n">
         <v>586071</v>
@@ -21597,7 +21597,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>1.59831118583679</v>
+        <v>1.59831130504608</v>
       </c>
       <c r="H732" t="n">
         <v>398648</v>
@@ -21626,7 +21626,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G733" t="n">
-        <v>1.51187205314636</v>
+        <v>1.51187181472778</v>
       </c>
       <c r="H733" t="n">
         <v>1759383</v>
@@ -21655,7 +21655,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G734" t="n">
-        <v>1.50453281402588</v>
+        <v>1.50453293323517</v>
       </c>
       <c r="H734" t="n">
         <v>1397140</v>
@@ -21684,7 +21684,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G735" t="n">
-        <v>1.53144299983978</v>
+        <v>1.53144323825836</v>
       </c>
       <c r="H735" t="n">
         <v>977458</v>
@@ -21742,7 +21742,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G737" t="n">
-        <v>1.51676487922668</v>
+        <v>1.51676464080811</v>
       </c>
       <c r="H737" t="n">
         <v>745389</v>
@@ -21800,7 +21800,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G739" t="n">
-        <v>1.44581937789917</v>
+        <v>1.44581925868988</v>
       </c>
       <c r="H739" t="n">
         <v>982774</v>
@@ -21858,7 +21858,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G741" t="n">
-        <v>1.47191429138184</v>
+        <v>1.47191405296326</v>
       </c>
       <c r="H741" t="n">
         <v>414540</v>
@@ -21887,7 +21887,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G742" t="n">
-        <v>1.51024103164673</v>
+        <v>1.51024091243744</v>
       </c>
       <c r="H742" t="n">
         <v>802068</v>
@@ -21916,7 +21916,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G743" t="n">
-        <v>1.51676487922668</v>
+        <v>1.51676464080811</v>
       </c>
       <c r="H743" t="n">
         <v>805198</v>
@@ -21945,7 +21945,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G744" t="n">
-        <v>1.50453281402588</v>
+        <v>1.50453293323517</v>
       </c>
       <c r="H744" t="n">
         <v>1047194</v>
@@ -22119,7 +22119,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G750" t="n">
-        <v>1.4115697145462</v>
+        <v>1.41156983375549</v>
       </c>
       <c r="H750" t="n">
         <v>1042775</v>
@@ -22148,7 +22148,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G751" t="n">
-        <v>1.4115697145462</v>
+        <v>1.41156983375549</v>
       </c>
       <c r="H751" t="n">
         <v>519026</v>
@@ -22235,7 +22235,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G754" t="n">
-        <v>1.37242746353149</v>
+        <v>1.3724273443222</v>
       </c>
       <c r="H754" t="n">
         <v>1083070</v>
@@ -22264,7 +22264,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G755" t="n">
-        <v>1.10087776184082</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H755" t="n">
         <v>12027281</v>
@@ -22380,7 +22380,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G759" t="n">
-        <v>1.01525390148163</v>
+        <v>1.01525378227234</v>
       </c>
       <c r="H759" t="n">
         <v>3366532</v>
@@ -22409,7 +22409,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G760" t="n">
-        <v>1.03074789047241</v>
+        <v>1.03074777126312</v>
       </c>
       <c r="H760" t="n">
         <v>6151251</v>
@@ -22467,7 +22467,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G762" t="n">
-        <v>1.10087776184082</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H762" t="n">
         <v>2715888</v>
@@ -22496,7 +22496,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G763" t="n">
-        <v>1.15469837188721</v>
+        <v>1.15469825267792</v>
       </c>
       <c r="H763" t="n">
         <v>2560889</v>
@@ -22641,7 +22641,7 @@
         <v>1.56500005722046</v>
       </c>
       <c r="G768" t="n">
-        <v>1.27620267868042</v>
+        <v>1.27620255947113</v>
       </c>
       <c r="H768" t="n">
         <v>2602064</v>
@@ -22670,7 +22670,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G769" t="n">
-        <v>1.30229735374451</v>
+        <v>1.3022974729538</v>
       </c>
       <c r="H769" t="n">
         <v>1170678</v>
@@ -22757,7 +22757,7 @@
         <v>1.59800004959106</v>
       </c>
       <c r="G772" t="n">
-        <v>1.30311286449432</v>
+        <v>1.30311298370361</v>
       </c>
       <c r="H772" t="n">
         <v>1651898</v>
@@ -22786,7 +22786,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G773" t="n">
-        <v>1.32920777797699</v>
+        <v>1.32920789718628</v>
       </c>
       <c r="H773" t="n">
         <v>2959691</v>
@@ -22815,7 +22815,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G774" t="n">
-        <v>1.33736252784729</v>
+        <v>1.337362408638</v>
       </c>
       <c r="H774" t="n">
         <v>798141</v>
@@ -22844,7 +22844,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G775" t="n">
-        <v>1.36019551753998</v>
+        <v>1.36019563674927</v>
       </c>
       <c r="H775" t="n">
         <v>1881833</v>
@@ -22931,7 +22931,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G778" t="n">
-        <v>1.31045234203339</v>
+        <v>1.31045210361481</v>
       </c>
       <c r="H778" t="n">
         <v>3033007</v>
@@ -22960,7 +22960,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G779" t="n">
-        <v>1.33491599559784</v>
+        <v>1.33491587638855</v>
       </c>
       <c r="H779" t="n">
         <v>3214064</v>
@@ -22989,7 +22989,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G780" t="n">
-        <v>1.37813568115234</v>
+        <v>1.37813580036163</v>
       </c>
       <c r="H780" t="n">
         <v>3667223</v>
@@ -23018,7 +23018,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G781" t="n">
-        <v>1.435218334198</v>
+        <v>1.43521821498871</v>
       </c>
       <c r="H781" t="n">
         <v>2217306</v>
@@ -23047,7 +23047,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G782" t="n">
-        <v>1.50942540168762</v>
+        <v>1.5094256401062</v>
       </c>
       <c r="H782" t="n">
         <v>2051305</v>
@@ -23076,7 +23076,7 @@
         <v>1.89699995517731</v>
       </c>
       <c r="G783" t="n">
-        <v>1.54693686962128</v>
+        <v>1.54693698883057</v>
       </c>
       <c r="H783" t="n">
         <v>2009197</v>
@@ -23105,7 +23105,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G784" t="n">
-        <v>1.58037102222443</v>
+        <v>1.58037090301514</v>
       </c>
       <c r="H784" t="n">
         <v>2580032</v>
@@ -23192,7 +23192,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G787" t="n">
-        <v>1.5754781961441</v>
+        <v>1.57547807693481</v>
       </c>
       <c r="H787" t="n">
         <v>2151732</v>
@@ -23308,7 +23308,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G791" t="n">
-        <v>1.53878235816956</v>
+        <v>1.53878223896027</v>
       </c>
       <c r="H791" t="n">
         <v>937385</v>
@@ -23424,7 +23424,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G795" t="n">
-        <v>1.67985796928406</v>
+        <v>1.67985761165619</v>
       </c>
       <c r="H795" t="n">
         <v>6571124</v>
@@ -23511,7 +23511,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G798" t="n">
-        <v>1.67007231712341</v>
+        <v>1.67007219791412</v>
       </c>
       <c r="H798" t="n">
         <v>497000</v>
@@ -23540,7 +23540,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G799" t="n">
-        <v>1.67985796928406</v>
+        <v>1.67985761165619</v>
       </c>
       <c r="H799" t="n">
         <v>508447</v>
@@ -23569,7 +23569,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G800" t="n">
-        <v>1.64071547985077</v>
+        <v>1.64071536064148</v>
       </c>
       <c r="H800" t="n">
         <v>489775</v>
@@ -23598,7 +23598,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G801" t="n">
-        <v>1.65702474117279</v>
+        <v>1.65702486038208</v>
       </c>
       <c r="H801" t="n">
         <v>829278</v>
@@ -23627,7 +23627,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G802" t="n">
-        <v>1.68148863315582</v>
+        <v>1.68148875236511</v>
       </c>
       <c r="H802" t="n">
         <v>808567</v>
@@ -23656,7 +23656,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G803" t="n">
-        <v>1.70595276355743</v>
+        <v>1.70595264434814</v>
       </c>
       <c r="H803" t="n">
         <v>1273027</v>
@@ -23685,7 +23685,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G804" t="n">
-        <v>1.69453620910645</v>
+        <v>1.69453608989716</v>
       </c>
       <c r="H804" t="n">
         <v>415996</v>
@@ -23714,7 +23714,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G805" t="n">
-        <v>1.70921432971954</v>
+        <v>1.70921444892883</v>
       </c>
       <c r="H805" t="n">
         <v>511806</v>
@@ -23743,7 +23743,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G806" t="n">
-        <v>1.70269083976746</v>
+        <v>1.70269072055817</v>
       </c>
       <c r="H806" t="n">
         <v>871066</v>
@@ -23772,7 +23772,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G807" t="n">
-        <v>1.69616711139679</v>
+        <v>1.6961669921875</v>
       </c>
       <c r="H807" t="n">
         <v>463656</v>
@@ -23801,7 +23801,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G808" t="n">
-        <v>1.67985796928406</v>
+        <v>1.67985761165619</v>
       </c>
       <c r="H808" t="n">
         <v>531129</v>
@@ -23830,7 +23830,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G809" t="n">
-        <v>1.69942891597748</v>
+        <v>1.69942903518677</v>
       </c>
       <c r="H809" t="n">
         <v>580157</v>
@@ -23859,7 +23859,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G810" t="n">
-        <v>1.68964326381683</v>
+        <v>1.68964314460754</v>
       </c>
       <c r="H810" t="n">
         <v>653322</v>
@@ -23888,7 +23888,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G811" t="n">
-        <v>1.65865540504456</v>
+        <v>1.65865552425385</v>
       </c>
       <c r="H811" t="n">
         <v>550811</v>
@@ -23917,7 +23917,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G812" t="n">
-        <v>1.65865540504456</v>
+        <v>1.65865552425385</v>
       </c>
       <c r="H812" t="n">
         <v>382456</v>
@@ -23975,7 +23975,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G814" t="n">
-        <v>1.67007231712341</v>
+        <v>1.67007219791412</v>
       </c>
       <c r="H814" t="n">
         <v>399189</v>
@@ -24062,7 +24062,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G817" t="n">
-        <v>1.64071547985077</v>
+        <v>1.64071536064148</v>
       </c>
       <c r="H817" t="n">
         <v>8186934</v>
@@ -24091,7 +24091,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G818" t="n">
-        <v>1.63582265377045</v>
+        <v>1.63582253456116</v>
       </c>
       <c r="H818" t="n">
         <v>1354848</v>
@@ -24120,7 +24120,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G819" t="n">
-        <v>1.6023885011673</v>
+        <v>1.60238862037659</v>
       </c>
       <c r="H819" t="n">
         <v>996560</v>
@@ -24207,7 +24207,7 @@
         <v>1.96399998664856</v>
       </c>
       <c r="G822" t="n">
-        <v>1.60157287120819</v>
+        <v>1.60157310962677</v>
       </c>
       <c r="H822" t="n">
         <v>833731</v>
@@ -24236,7 +24236,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G823" t="n">
-        <v>1.6733341217041</v>
+        <v>1.67333400249481</v>
       </c>
       <c r="H823" t="n">
         <v>1131670</v>
@@ -24265,7 +24265,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G824" t="n">
-        <v>1.6619176864624</v>
+        <v>1.66191744804382</v>
       </c>
       <c r="H824" t="n">
         <v>1727495</v>
@@ -24294,7 +24294,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G825" t="n">
-        <v>1.67496502399445</v>
+        <v>1.67496478557587</v>
       </c>
       <c r="H825" t="n">
         <v>666086</v>
@@ -24352,7 +24352,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G827" t="n">
-        <v>1.70921432971954</v>
+        <v>1.70921444892883</v>
       </c>
       <c r="H827" t="n">
         <v>422823</v>
@@ -24381,7 +24381,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>1.68475067615509</v>
+        <v>1.68475043773651</v>
       </c>
       <c r="H828" t="n">
         <v>596412</v>
@@ -24410,7 +24410,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G829" t="n">
-        <v>1.70432150363922</v>
+        <v>1.70432162284851</v>
       </c>
       <c r="H829" t="n">
         <v>496963</v>
@@ -24439,7 +24439,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G830" t="n">
-        <v>1.71736896038055</v>
+        <v>1.71736907958984</v>
       </c>
       <c r="H830" t="n">
         <v>843159</v>
@@ -24468,7 +24468,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G831" t="n">
-        <v>1.88372409343719</v>
+        <v>1.88372397422791</v>
       </c>
       <c r="H831" t="n">
         <v>8604870</v>
@@ -24497,7 +24497,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G832" t="n">
-        <v>1.89187836647034</v>
+        <v>1.89187860488892</v>
       </c>
       <c r="H832" t="n">
         <v>3573577</v>
@@ -24526,7 +24526,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G833" t="n">
-        <v>1.81196272373199</v>
+        <v>1.81196296215057</v>
       </c>
       <c r="H833" t="n">
         <v>2500836</v>
@@ -24555,7 +24555,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G834" t="n">
-        <v>1.78260660171509</v>
+        <v>1.78260624408722</v>
       </c>
       <c r="H834" t="n">
         <v>1213282</v>
@@ -24584,7 +24584,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G835" t="n">
-        <v>1.77771353721619</v>
+        <v>1.77771365642548</v>
       </c>
       <c r="H835" t="n">
         <v>401140</v>
@@ -24613,7 +24613,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G836" t="n">
-        <v>1.7744517326355</v>
+        <v>1.77445161342621</v>
       </c>
       <c r="H836" t="n">
         <v>445873</v>
@@ -24642,7 +24642,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>1.7858681678772</v>
+        <v>1.78586828708649</v>
       </c>
       <c r="H837" t="n">
         <v>450642</v>
@@ -24671,7 +24671,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G838" t="n">
-        <v>1.7858681678772</v>
+        <v>1.78586828708649</v>
       </c>
       <c r="H838" t="n">
         <v>377864</v>
@@ -24700,7 +24700,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G839" t="n">
-        <v>1.76140415668488</v>
+        <v>1.76140427589417</v>
       </c>
       <c r="H839" t="n">
         <v>472267</v>
@@ -24758,7 +24758,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>1.67985796928406</v>
+        <v>1.67985761165619</v>
       </c>
       <c r="H841" t="n">
         <v>1113545</v>
@@ -24787,7 +24787,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G842" t="n">
-        <v>1.66028666496277</v>
+        <v>1.66028654575348</v>
       </c>
       <c r="H842" t="n">
         <v>1706967</v>
@@ -24874,7 +24874,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>1.59831118583679</v>
+        <v>1.59831130504608</v>
       </c>
       <c r="H845" t="n">
         <v>2241138</v>
@@ -24903,7 +24903,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G846" t="n">
-        <v>1.51676487922668</v>
+        <v>1.51676464080811</v>
       </c>
       <c r="H846" t="n">
         <v>2988966</v>
@@ -24932,7 +24932,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G847" t="n">
-        <v>1.54775249958038</v>
+        <v>1.54775238037109</v>
       </c>
       <c r="H847" t="n">
         <v>1669046</v>
@@ -24961,7 +24961,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G848" t="n">
-        <v>1.52328848838806</v>
+        <v>1.52328824996948</v>
       </c>
       <c r="H848" t="n">
         <v>1102200</v>
@@ -24990,7 +24990,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G849" t="n">
-        <v>1.49148523807526</v>
+        <v>1.49148535728455</v>
       </c>
       <c r="H849" t="n">
         <v>955483</v>
@@ -25019,7 +25019,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G850" t="n">
-        <v>1.4392956495285</v>
+        <v>1.43929553031921</v>
       </c>
       <c r="H850" t="n">
         <v>1026199</v>
@@ -25048,7 +25048,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G851" t="n">
-        <v>1.42543268203735</v>
+        <v>1.42543256282806</v>
       </c>
       <c r="H851" t="n">
         <v>880260</v>
@@ -25077,7 +25077,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G852" t="n">
-        <v>1.4083080291748</v>
+        <v>1.40830790996552</v>
       </c>
       <c r="H852" t="n">
         <v>1055190</v>
@@ -25164,7 +25164,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G855" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H855" t="n">
         <v>367882</v>
@@ -25222,7 +25222,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G857" t="n">
-        <v>1.40341508388519</v>
+        <v>1.4034149646759</v>
       </c>
       <c r="H857" t="n">
         <v>480477</v>
@@ -25251,7 +25251,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G858" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H858" t="n">
         <v>480695</v>
@@ -25309,7 +25309,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G860" t="n">
-        <v>1.4083080291748</v>
+        <v>1.40830790996552</v>
       </c>
       <c r="H860" t="n">
         <v>331863</v>
@@ -25367,7 +25367,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G862" t="n">
-        <v>1.35204088687897</v>
+        <v>1.35204100608826</v>
       </c>
       <c r="H862" t="n">
         <v>465276</v>
@@ -25396,7 +25396,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G863" t="n">
-        <v>1.38221311569214</v>
+        <v>1.38221323490143</v>
       </c>
       <c r="H863" t="n">
         <v>444989</v>
@@ -25425,7 +25425,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G864" t="n">
-        <v>1.41483163833618</v>
+        <v>1.41483151912689</v>
       </c>
       <c r="H864" t="n">
         <v>442927</v>
@@ -25483,7 +25483,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G866" t="n">
-        <v>1.37487387657166</v>
+        <v>1.37487375736237</v>
       </c>
       <c r="H866" t="n">
         <v>389202</v>
@@ -25541,7 +25541,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G868" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H868" t="n">
         <v>929548</v>
@@ -25599,7 +25599,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G870" t="n">
-        <v>1.44989669322968</v>
+        <v>1.44989657402039</v>
       </c>
       <c r="H870" t="n">
         <v>1022788</v>
@@ -25628,7 +25628,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G871" t="n">
-        <v>1.47599136829376</v>
+        <v>1.47599148750305</v>
       </c>
       <c r="H871" t="n">
         <v>608455</v>
@@ -25744,7 +25744,7 @@
         <v>1.875</v>
       </c>
       <c r="G875" t="n">
-        <v>1.52899670600891</v>
+        <v>1.52899694442749</v>
       </c>
       <c r="H875" t="n">
         <v>341943</v>
@@ -25802,7 +25802,7 @@
         <v>1.875</v>
       </c>
       <c r="G877" t="n">
-        <v>1.52899670600891</v>
+        <v>1.52899694442749</v>
       </c>
       <c r="H877" t="n">
         <v>428422</v>
@@ -25918,7 +25918,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G881" t="n">
-        <v>1.45886671543121</v>
+        <v>1.45886659622192</v>
       </c>
       <c r="H881" t="n">
         <v>1315058</v>
@@ -25947,7 +25947,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G882" t="n">
-        <v>1.45886671543121</v>
+        <v>1.45886659622192</v>
       </c>
       <c r="H882" t="n">
         <v>276357</v>
@@ -26034,7 +26034,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G885" t="n">
-        <v>1.44989669322968</v>
+        <v>1.44989657402039</v>
       </c>
       <c r="H885" t="n">
         <v>2306619</v>
@@ -26092,7 +26092,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G887" t="n">
-        <v>1.43032550811768</v>
+        <v>1.4303252696991</v>
       </c>
       <c r="H887" t="n">
         <v>746913</v>
@@ -26121,7 +26121,7 @@
         <v>1.77300000190735</v>
       </c>
       <c r="G888" t="n">
-        <v>1.44581937789917</v>
+        <v>1.44581925868988</v>
       </c>
       <c r="H888" t="n">
         <v>386625</v>
@@ -26150,7 +26150,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G889" t="n">
-        <v>1.44989669322968</v>
+        <v>1.44989657402039</v>
       </c>
       <c r="H889" t="n">
         <v>308646</v>
@@ -26179,7 +26179,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G890" t="n">
-        <v>1.46865224838257</v>
+        <v>1.46865236759186</v>
       </c>
       <c r="H890" t="n">
         <v>251671</v>
@@ -26208,7 +26208,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G891" t="n">
-        <v>1.52573502063751</v>
+        <v>1.52573490142822</v>
       </c>
       <c r="H891" t="n">
         <v>1176195</v>
@@ -26237,7 +26237,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G892" t="n">
-        <v>1.58689475059509</v>
+        <v>1.58689486980438</v>
       </c>
       <c r="H892" t="n">
         <v>2742260</v>
@@ -26295,7 +26295,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G894" t="n">
-        <v>1.57058537006378</v>
+        <v>1.57058548927307</v>
       </c>
       <c r="H894" t="n">
         <v>1453003</v>
@@ -26324,7 +26324,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G895" t="n">
-        <v>1.50290191173553</v>
+        <v>1.50290203094482</v>
       </c>
       <c r="H895" t="n">
         <v>1736792</v>
@@ -26353,7 +26353,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G896" t="n">
-        <v>1.51676487922668</v>
+        <v>1.51676464080811</v>
       </c>
       <c r="H896" t="n">
         <v>516545</v>
@@ -26440,7 +26440,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.435218334198</v>
+        <v>1.43521821498871</v>
       </c>
       <c r="H899" t="n">
         <v>1456465</v>
@@ -26527,7 +26527,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G902" t="n">
-        <v>1.25581586360931</v>
+        <v>1.25581610202789</v>
       </c>
       <c r="H902" t="n">
         <v>4703086</v>
@@ -26614,7 +26614,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G905" t="n">
-        <v>1.27049422264099</v>
+        <v>1.27049434185028</v>
       </c>
       <c r="H905" t="n">
         <v>1458633</v>
@@ -26672,7 +26672,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G907" t="n">
-        <v>1.37732028961182</v>
+        <v>1.37732017040253</v>
       </c>
       <c r="H907" t="n">
         <v>2492653</v>
@@ -26701,7 +26701,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G908" t="n">
-        <v>1.35367166996002</v>
+        <v>1.3536719083786</v>
       </c>
       <c r="H908" t="n">
         <v>1043256</v>
@@ -26730,7 +26730,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G909" t="n">
-        <v>1.36182653903961</v>
+        <v>1.36182641983032</v>
       </c>
       <c r="H909" t="n">
         <v>619098</v>
@@ -26759,7 +26759,7 @@
         <v>1.64800000190735</v>
       </c>
       <c r="G910" t="n">
-        <v>1.34388625621796</v>
+        <v>1.34388613700867</v>
       </c>
       <c r="H910" t="n">
         <v>687288</v>
@@ -26788,7 +26788,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G911" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H911" t="n">
         <v>3720832</v>
@@ -26904,7 +26904,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G915" t="n">
-        <v>1.51024103164673</v>
+        <v>1.51024091243744</v>
       </c>
       <c r="H915" t="n">
         <v>2409241</v>
@@ -27020,7 +27020,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G919" t="n">
-        <v>1.41727805137634</v>
+        <v>1.41727793216705</v>
       </c>
       <c r="H919" t="n">
         <v>3017439</v>
@@ -27078,7 +27078,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G921" t="n">
-        <v>1.40341508388519</v>
+        <v>1.4034149646759</v>
       </c>
       <c r="H921" t="n">
         <v>457312</v>
@@ -27107,7 +27107,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G922" t="n">
-        <v>1.39933788776398</v>
+        <v>1.3993376493454</v>
       </c>
       <c r="H922" t="n">
         <v>482861</v>
@@ -27136,7 +27136,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G923" t="n">
-        <v>1.45968234539032</v>
+        <v>1.45968210697174</v>
       </c>
       <c r="H923" t="n">
         <v>650528</v>
@@ -27165,7 +27165,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G924" t="n">
-        <v>1.44092655181885</v>
+        <v>1.44092643260956</v>
       </c>
       <c r="H924" t="n">
         <v>445435</v>
@@ -27194,7 +27194,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G925" t="n">
-        <v>1.45478940010071</v>
+        <v>1.45478928089142</v>
       </c>
       <c r="H925" t="n">
         <v>495556</v>
@@ -27252,7 +27252,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G927" t="n">
-        <v>1.41890907287598</v>
+        <v>1.41890895366669</v>
       </c>
       <c r="H927" t="n">
         <v>310073</v>
@@ -27281,7 +27281,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G928" t="n">
-        <v>1.39933788776398</v>
+        <v>1.3993376493454</v>
       </c>
       <c r="H928" t="n">
         <v>1082932</v>
@@ -27310,7 +27310,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G929" t="n">
-        <v>1.43277180194855</v>
+        <v>1.43277168273926</v>
       </c>
       <c r="H929" t="n">
         <v>844650</v>
@@ -27397,7 +27397,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G932" t="n">
-        <v>1.44255745410919</v>
+        <v>1.44255757331848</v>
       </c>
       <c r="H932" t="n">
         <v>480648</v>
@@ -27426,7 +27426,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G933" t="n">
-        <v>1.46865224838257</v>
+        <v>1.46865236759186</v>
       </c>
       <c r="H933" t="n">
         <v>252434</v>
@@ -27542,7 +27542,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G937" t="n">
-        <v>1.46131324768066</v>
+        <v>1.46131312847137</v>
       </c>
       <c r="H937" t="n">
         <v>276015</v>
@@ -27687,7 +27687,7 @@
         <v>1.99300003051758</v>
       </c>
       <c r="G942" t="n">
-        <v>1.62522161006927</v>
+        <v>1.62522172927856</v>
       </c>
       <c r="H942" t="n">
         <v>2559453</v>
@@ -27716,7 +27716,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.67170298099518</v>
+        <v>1.67170310020447</v>
       </c>
       <c r="H943" t="n">
         <v>2434409</v>
@@ -27774,7 +27774,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G945" t="n">
-        <v>1.73041641712189</v>
+        <v>1.73041653633118</v>
       </c>
       <c r="H945" t="n">
         <v>2501849</v>
@@ -27861,7 +27861,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G948" t="n">
-        <v>1.65050113201141</v>
+        <v>1.65050101280212</v>
       </c>
       <c r="H948" t="n">
         <v>447219</v>
@@ -27890,7 +27890,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G949" t="n">
-        <v>1.68148863315582</v>
+        <v>1.68148875236511</v>
       </c>
       <c r="H949" t="n">
         <v>561915</v>
@@ -27919,7 +27919,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G950" t="n">
-        <v>1.65702474117279</v>
+        <v>1.65702486038208</v>
       </c>
       <c r="H950" t="n">
         <v>604544</v>
@@ -27948,7 +27948,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G951" t="n">
-        <v>1.67496502399445</v>
+        <v>1.67496478557587</v>
       </c>
       <c r="H951" t="n">
         <v>449178</v>
@@ -27977,7 +27977,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G952" t="n">
-        <v>1.64071547985077</v>
+        <v>1.64071536064148</v>
       </c>
       <c r="H952" t="n">
         <v>314585</v>
@@ -28064,7 +28064,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G955" t="n">
-        <v>1.60401964187622</v>
+        <v>1.60401952266693</v>
       </c>
       <c r="H955" t="n">
         <v>624169</v>
@@ -28093,7 +28093,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G956" t="n">
-        <v>1.55916893482208</v>
+        <v>1.55916881561279</v>
       </c>
       <c r="H956" t="n">
         <v>1158265</v>
@@ -28122,7 +28122,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G957" t="n">
-        <v>1.5754781961441</v>
+        <v>1.57547807693481</v>
       </c>
       <c r="H957" t="n">
         <v>698341</v>
@@ -28151,7 +28151,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G958" t="n">
-        <v>1.57058537006378</v>
+        <v>1.57058548927307</v>
       </c>
       <c r="H958" t="n">
         <v>358093</v>
@@ -28180,7 +28180,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G959" t="n">
-        <v>1.52247285842896</v>
+        <v>1.52247309684753</v>
       </c>
       <c r="H959" t="n">
         <v>441507</v>
@@ -28209,7 +28209,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G960" t="n">
-        <v>1.51350271701813</v>
+        <v>1.51350283622742</v>
       </c>
       <c r="H960" t="n">
         <v>1017531</v>
@@ -28325,7 +28325,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G964" t="n">
-        <v>1.55019879341125</v>
+        <v>1.55019867420197</v>
       </c>
       <c r="H964" t="n">
         <v>472301</v>
@@ -28354,7 +28354,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G965" t="n">
-        <v>1.56161546707153</v>
+        <v>1.56161534786224</v>
       </c>
       <c r="H965" t="n">
         <v>523670</v>
@@ -28412,7 +28412,7 @@
         <v>1.88699996471405</v>
       </c>
       <c r="G967" t="n">
-        <v>1.53878235816956</v>
+        <v>1.53878223896027</v>
       </c>
       <c r="H967" t="n">
         <v>338780</v>
@@ -28441,7 +28441,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G968" t="n">
-        <v>1.54938340187073</v>
+        <v>1.54938328266144</v>
       </c>
       <c r="H968" t="n">
         <v>929523</v>
@@ -28470,7 +28470,7 @@
         <v>1.97599995136261</v>
       </c>
       <c r="G969" t="n">
-        <v>1.61135852336884</v>
+        <v>1.61135864257812</v>
       </c>
       <c r="H969" t="n">
         <v>2221457</v>
@@ -28499,7 +28499,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G970" t="n">
-        <v>1.53307390213013</v>
+        <v>1.53307402133942</v>
       </c>
       <c r="H970" t="n">
         <v>1687835</v>
@@ -28528,7 +28528,7 @@
         <v>1.875</v>
       </c>
       <c r="G971" t="n">
-        <v>1.52899670600891</v>
+        <v>1.52899694442749</v>
       </c>
       <c r="H971" t="n">
         <v>1073312</v>
@@ -28557,7 +28557,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G972" t="n">
-        <v>1.51921117305756</v>
+        <v>1.51921105384827</v>
       </c>
       <c r="H972" t="n">
         <v>814738</v>
@@ -28586,7 +28586,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G973" t="n">
-        <v>1.49311625957489</v>
+        <v>1.4931161403656</v>
       </c>
       <c r="H973" t="n">
         <v>788984</v>
@@ -28615,7 +28615,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G974" t="n">
-        <v>1.52002644538879</v>
+        <v>1.52002656459808</v>
       </c>
       <c r="H974" t="n">
         <v>392240</v>
@@ -28702,7 +28702,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G977" t="n">
-        <v>1.48985433578491</v>
+        <v>1.4898544549942</v>
       </c>
       <c r="H977" t="n">
         <v>461421</v>
@@ -28731,7 +28731,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G978" t="n">
-        <v>1.46212863922119</v>
+        <v>1.46212875843048</v>
       </c>
       <c r="H978" t="n">
         <v>2195345</v>
@@ -28760,7 +28760,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G979" t="n">
-        <v>1.45968234539032</v>
+        <v>1.45968210697174</v>
       </c>
       <c r="H979" t="n">
         <v>1897039</v>
@@ -28789,7 +28789,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>1.45968234539032</v>
+        <v>1.45968210697174</v>
       </c>
       <c r="H980" t="n">
         <v>899353</v>
@@ -28818,7 +28818,7 @@
         <v>1.74199998378754</v>
       </c>
       <c r="G981" t="n">
-        <v>1.42053973674774</v>
+        <v>1.42053985595703</v>
       </c>
       <c r="H981" t="n">
         <v>7154588</v>
@@ -28847,7 +28847,7 @@
         <v>1.68400001525879</v>
       </c>
       <c r="G982" t="n">
-        <v>1.3732430934906</v>
+        <v>1.37324285507202</v>
       </c>
       <c r="H982" t="n">
         <v>21650203</v>
@@ -28905,7 +28905,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G984" t="n">
-        <v>1.50942540168762</v>
+        <v>1.5094256401062</v>
       </c>
       <c r="H984" t="n">
         <v>15216437</v>
@@ -28963,7 +28963,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G986" t="n">
-        <v>1.48414623737335</v>
+        <v>1.48414599895477</v>
       </c>
       <c r="H986" t="n">
         <v>3078600</v>
@@ -29021,7 +29021,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G988" t="n">
-        <v>1.44092655181885</v>
+        <v>1.44092643260956</v>
       </c>
       <c r="H988" t="n">
         <v>1635432</v>
@@ -29050,7 +29050,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G989" t="n">
-        <v>1.41320073604584</v>
+        <v>1.41320085525513</v>
       </c>
       <c r="H989" t="n">
         <v>2882134</v>
@@ -29079,7 +29079,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G990" t="n">
-        <v>1.39036774635315</v>
+        <v>1.39036762714386</v>
       </c>
       <c r="H990" t="n">
         <v>2466626</v>
@@ -29108,7 +29108,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.38221311569214</v>
+        <v>1.38221323490143</v>
       </c>
       <c r="H991" t="n">
         <v>1472350</v>
@@ -29166,7 +29166,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G993" t="n">
-        <v>1.4311408996582</v>
+        <v>1.43114101886749</v>
       </c>
       <c r="H993" t="n">
         <v>4664408</v>
@@ -29195,7 +29195,7 @@
         <v>1.75699996948242</v>
       </c>
       <c r="G994" t="n">
-        <v>1.43277180194855</v>
+        <v>1.43277168273926</v>
       </c>
       <c r="H994" t="n">
         <v>3291327</v>
@@ -29224,7 +29224,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G995" t="n">
-        <v>1.46212863922119</v>
+        <v>1.46212875843048</v>
       </c>
       <c r="H995" t="n">
         <v>4135413</v>
@@ -29253,7 +29253,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G996" t="n">
-        <v>1.44174194335938</v>
+        <v>1.44174182415009</v>
       </c>
       <c r="H996" t="n">
         <v>1816638</v>
@@ -29282,7 +29282,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G997" t="n">
-        <v>1.44337272644043</v>
+        <v>1.44337284564972</v>
       </c>
       <c r="H997" t="n">
         <v>1986347</v>
@@ -29311,7 +29311,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>1.39444506168365</v>
+        <v>1.39444494247437</v>
       </c>
       <c r="H998" t="n">
         <v>2423018</v>
@@ -29369,7 +29369,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.41483163833618</v>
+        <v>1.41483151912689</v>
       </c>
       <c r="H1000" t="n">
         <v>2449613</v>
@@ -29427,7 +29427,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.41727805137634</v>
+        <v>1.41727793216705</v>
       </c>
       <c r="H1002" t="n">
         <v>1850120</v>
@@ -29456,7 +29456,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.39199841022491</v>
+        <v>1.39199876785278</v>
       </c>
       <c r="H1003" t="n">
         <v>1669083</v>
@@ -29485,7 +29485,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.39199841022491</v>
+        <v>1.39199876785278</v>
       </c>
       <c r="H1004" t="n">
         <v>964142</v>
@@ -29514,7 +29514,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.37487387657166</v>
+        <v>1.37487375736237</v>
       </c>
       <c r="H1005" t="n">
         <v>1982853</v>
@@ -29543,7 +29543,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.37161207199097</v>
+        <v>1.37161195278168</v>
       </c>
       <c r="H1006" t="n">
         <v>1637952</v>
@@ -29572,7 +29572,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.34633266925812</v>
+        <v>1.34633255004883</v>
       </c>
       <c r="H1007" t="n">
         <v>2611930</v>
@@ -29601,7 +29601,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.37487387657166</v>
+        <v>1.37487375736237</v>
       </c>
       <c r="H1008" t="n">
         <v>2577287</v>
@@ -29630,7 +29630,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.36182653903961</v>
+        <v>1.36182641983032</v>
       </c>
       <c r="H1009" t="n">
         <v>1464133</v>
@@ -29659,7 +29659,7 @@
         <v>1.64900004863739</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.34470164775848</v>
+        <v>1.34470176696777</v>
       </c>
       <c r="H1010" t="n">
         <v>1693548</v>
@@ -29688,7 +29688,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.33573150634766</v>
+        <v>1.33573162555695</v>
       </c>
       <c r="H1011" t="n">
         <v>1741918</v>
@@ -29717,7 +29717,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.35856449604034</v>
+        <v>1.35856461524963</v>
       </c>
       <c r="H1012" t="n">
         <v>5867694</v>
@@ -29775,7 +29775,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.32268404960632</v>
+        <v>1.32268416881561</v>
       </c>
       <c r="H1014" t="n">
         <v>1216109</v>
@@ -29862,7 +29862,7 @@
         <v>1.61699998378754</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.31860673427582</v>
+        <v>1.31860685348511</v>
       </c>
       <c r="H1017" t="n">
         <v>3637322</v>
@@ -29891,7 +29891,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.28843450546265</v>
+        <v>1.28843474388123</v>
       </c>
       <c r="H1018" t="n">
         <v>1970341</v>
@@ -29920,7 +29920,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.30474388599396</v>
+        <v>1.30474400520325</v>
       </c>
       <c r="H1019" t="n">
         <v>1457803</v>
@@ -29949,7 +29949,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.30229735374451</v>
+        <v>1.3022974729538</v>
       </c>
       <c r="H1020" t="n">
         <v>1207943</v>
@@ -29978,7 +29978,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.31779134273529</v>
+        <v>1.31779146194458</v>
       </c>
       <c r="H1021" t="n">
         <v>1664512</v>
@@ -30007,7 +30007,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.32268404960632</v>
+        <v>1.32268416881561</v>
       </c>
       <c r="H1022" t="n">
         <v>1384826</v>
@@ -30065,7 +30065,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.33328521251678</v>
+        <v>1.3332850933075</v>
       </c>
       <c r="H1024" t="n">
         <v>1949168</v>
@@ -30094,7 +30094,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.32431483268738</v>
+        <v>1.32431507110596</v>
       </c>
       <c r="H1025" t="n">
         <v>1894862</v>
@@ -30181,7 +30181,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.30474388599396</v>
+        <v>1.30474400520325</v>
       </c>
       <c r="H1028" t="n">
         <v>2569962</v>
@@ -30268,7 +30268,7 @@
         <v>1.52699995040894</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.24521505832672</v>
+        <v>1.24521493911743</v>
       </c>
       <c r="H1031" t="n">
         <v>4013072</v>
@@ -30297,7 +30297,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.27212536334991</v>
+        <v>1.27212524414062</v>
       </c>
       <c r="H1032" t="n">
         <v>2267819</v>
@@ -30384,7 +30384,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.25581586360931</v>
+        <v>1.25581610202789</v>
       </c>
       <c r="H1035" t="n">
         <v>1254623</v>
@@ -30442,7 +30442,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.19302535057068</v>
+        <v>1.19302523136139</v>
       </c>
       <c r="H1037" t="n">
         <v>2136222</v>
@@ -30471,7 +30471,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.17834675312042</v>
+        <v>1.17834687232971</v>
       </c>
       <c r="H1038" t="n">
         <v>2286641</v>
@@ -30500,7 +30500,7 @@
         <v>1.46300005912781</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.19302535057068</v>
+        <v>1.19302523136139</v>
       </c>
       <c r="H1039" t="n">
         <v>1987577</v>
@@ -30529,7 +30529,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.21993565559387</v>
+        <v>1.21993553638458</v>
       </c>
       <c r="H1040" t="n">
         <v>2375077</v>
@@ -30558,7 +30558,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.21504271030426</v>
+        <v>1.21504282951355</v>
       </c>
       <c r="H1041" t="n">
         <v>1855988</v>
@@ -30616,7 +30616,7 @@
         <v>1.442999958992</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.17671573162079</v>
+        <v>1.17671585083008</v>
       </c>
       <c r="H1043" t="n">
         <v>1518662</v>
@@ -30645,7 +30645,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.2125962972641</v>
+        <v>1.21259617805481</v>
       </c>
       <c r="H1044" t="n">
         <v>2340167</v>
@@ -30674,7 +30674,7 @@
         <v>1.49199998378754</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.2166736125946</v>
+        <v>1.21667373180389</v>
       </c>
       <c r="H1045" t="n">
         <v>2549634</v>
@@ -30761,7 +30761,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.21830475330353</v>
+        <v>1.21830463409424</v>
       </c>
       <c r="H1048" t="n">
         <v>1782186</v>
@@ -30819,7 +30819,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.2125962972641</v>
+        <v>1.21259617805481</v>
       </c>
       <c r="H1050" t="n">
         <v>1442692</v>
@@ -30848,7 +30848,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.23298275470734</v>
+        <v>1.23298299312592</v>
       </c>
       <c r="H1051" t="n">
         <v>4186263</v>
@@ -30877,7 +30877,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.19057857990265</v>
+        <v>1.19057881832123</v>
       </c>
       <c r="H1052" t="n">
         <v>3034895</v>
@@ -30906,7 +30906,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.08456838130951</v>
+        <v>1.0845685005188</v>
       </c>
       <c r="H1053" t="n">
         <v>6068429</v>
@@ -30964,7 +30964,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.13349628448486</v>
+        <v>1.13349616527557</v>
       </c>
       <c r="H1055" t="n">
         <v>2667646</v>
@@ -31022,7 +31022,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.08538389205933</v>
+        <v>1.08538377285004</v>
       </c>
       <c r="H1057" t="n">
         <v>4048851</v>
@@ -31051,7 +31051,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.05928885936737</v>
+        <v>1.05928897857666</v>
       </c>
       <c r="H1058" t="n">
         <v>4847716</v>
@@ -31080,7 +31080,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.0340096950531</v>
+        <v>1.03400933742523</v>
       </c>
       <c r="H1059" t="n">
         <v>2652066</v>
@@ -31138,7 +31138,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.98834353685379</v>
+        <v>0.988343477249146</v>
       </c>
       <c r="H1061" t="n">
         <v>4115706</v>
@@ -31167,7 +31167,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.920659899711609</v>
+        <v>0.920659840106964</v>
       </c>
       <c r="H1062" t="n">
         <v>4436272</v>
@@ -31196,7 +31196,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.804048478603363</v>
+        <v>0.804048299789429</v>
       </c>
       <c r="H1063" t="n">
         <v>4912177</v>
@@ -31225,7 +31225,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.760013222694397</v>
+        <v>0.760013282299042</v>
       </c>
       <c r="H1064" t="n">
         <v>6550694</v>
@@ -31254,7 +31254,7 @@
         <v>0.922500014305115</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.752266407012939</v>
+        <v>0.752266466617584</v>
       </c>
       <c r="H1065" t="n">
         <v>5103415</v>
@@ -31312,7 +31312,7 @@
         <v>0.721499979496002</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.588357865810394</v>
+        <v>0.588357925415039</v>
       </c>
       <c r="H1067" t="n">
         <v>5899770</v>
@@ -31341,7 +31341,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.59365850687027</v>
+        <v>0.593658447265625</v>
       </c>
       <c r="H1068" t="n">
         <v>5402453</v>
@@ -31457,7 +31457,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.858684480190277</v>
+        <v>0.858684539794922</v>
       </c>
       <c r="H1072" t="n">
         <v>4219076</v>
@@ -31544,7 +31544,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.937784731388092</v>
+        <v>0.937784612178802</v>
       </c>
       <c r="H1075" t="n">
         <v>5198714</v>
@@ -31573,7 +31573,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.918213605880737</v>
+        <v>0.918213486671448</v>
       </c>
       <c r="H1076" t="n">
         <v>2250973</v>
@@ -31602,7 +31602,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.870916485786438</v>
+        <v>0.870916545391083</v>
       </c>
       <c r="H1077" t="n">
         <v>1971172</v>
@@ -31631,7 +31631,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.913320660591125</v>
+        <v>0.91332072019577</v>
       </c>
       <c r="H1078" t="n">
         <v>1366165</v>
@@ -31660,7 +31660,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.950832009315491</v>
+        <v>0.950832068920135</v>
       </c>
       <c r="H1079" t="n">
         <v>2082037</v>
@@ -31689,7 +31689,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.939415633678436</v>
+        <v>0.939415574073792</v>
       </c>
       <c r="H1080" t="n">
         <v>655666</v>
@@ -31718,7 +31718,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.949201226234436</v>
+        <v>0.949201107025146</v>
       </c>
       <c r="H1081" t="n">
         <v>929547</v>
@@ -31834,7 +31834,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.956540465354919</v>
+        <v>0.95654022693634</v>
       </c>
       <c r="H1085" t="n">
         <v>1486613</v>
@@ -31892,7 +31892,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.05276525020599</v>
+        <v>1.05276536941528</v>
       </c>
       <c r="H1087" t="n">
         <v>4106371</v>
@@ -31921,7 +31921,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.998129069805145</v>
+        <v>0.998129189014435</v>
       </c>
       <c r="H1088" t="n">
         <v>2104508</v>
@@ -31950,7 +31950,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.02014672756195</v>
+        <v>1.02014660835266</v>
       </c>
       <c r="H1089" t="n">
         <v>1696933</v>
@@ -32008,7 +32008,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.10087776184082</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H1091" t="n">
         <v>1946332</v>
@@ -32037,7 +32037,7 @@
         <v>1.33899998664856</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.09190738201141</v>
+        <v>1.0919075012207</v>
       </c>
       <c r="H1092" t="n">
         <v>1156803</v>
@@ -32066,7 +32066,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.08538389205933</v>
+        <v>1.08538377285004</v>
       </c>
       <c r="H1093" t="n">
         <v>1097046</v>
@@ -32095,7 +32095,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.08864557743073</v>
+        <v>1.08864569664001</v>
       </c>
       <c r="H1094" t="n">
         <v>648171</v>
@@ -32124,7 +32124,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.08783030509949</v>
+        <v>1.0878301858902</v>
       </c>
       <c r="H1095" t="n">
         <v>841392</v>
@@ -32153,7 +32153,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.10087776184082</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H1096" t="n">
         <v>929546</v>
@@ -32240,7 +32240,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.10087776184082</v>
+        <v>1.10087764263153</v>
       </c>
       <c r="H1099" t="n">
         <v>820249</v>
@@ -32298,7 +32298,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.08783030509949</v>
+        <v>1.0878301858902</v>
       </c>
       <c r="H1101" t="n">
         <v>1883969</v>
@@ -32327,7 +32327,7 @@
         <v>1.34899997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.100062251091</v>
+        <v>1.10006201267242</v>
       </c>
       <c r="H1102" t="n">
         <v>427120</v>
@@ -32356,7 +32356,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.06662809848785</v>
+        <v>1.06662821769714</v>
       </c>
       <c r="H1103" t="n">
         <v>840686</v>
@@ -32414,7 +32414,7 @@
         <v>1.31900000572205</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.07559835910797</v>
+        <v>1.07559812068939</v>
       </c>
       <c r="H1105" t="n">
         <v>463491</v>
@@ -32530,7 +32530,7 @@
         <v>1.26900005340576</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.03482508659363</v>
+        <v>1.03482496738434</v>
       </c>
       <c r="H1109" t="n">
         <v>390613</v>
@@ -32559,7 +32559,7 @@
         <v>1.26300001144409</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.0548700094223</v>
+        <v>1.05486989021301</v>
       </c>
       <c r="H1110" t="n">
         <v>531961</v>
@@ -32588,7 +32588,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.979701042175293</v>
+        <v>0.979700982570648</v>
       </c>
       <c r="H1111" t="n">
         <v>3876340</v>
@@ -32617,7 +32617,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.988888382911682</v>
+        <v>0.988888502120972</v>
       </c>
       <c r="H1112" t="n">
         <v>1956180</v>
@@ -32733,7 +32733,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.05737566947937</v>
+        <v>1.05737578868866</v>
       </c>
       <c r="H1116" t="n">
         <v>1440577</v>
@@ -32791,7 +32791,7 @@
         <v>1.25100004673004</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.04484760761261</v>
+        <v>1.04484748840332</v>
       </c>
       <c r="H1118" t="n">
         <v>714319</v>
@@ -32820,7 +32820,7 @@
         <v>1.24300003051758</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.03816604614258</v>
+        <v>1.038165807724</v>
       </c>
       <c r="H1119" t="n">
         <v>1124431</v>
@@ -32849,7 +32849,7 @@
         <v>1.26900005340576</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.05988132953644</v>
+        <v>1.05988121032715</v>
       </c>
       <c r="H1120" t="n">
         <v>899339</v>
@@ -32878,7 +32878,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.08243179321289</v>
+        <v>1.08243203163147</v>
       </c>
       <c r="H1121" t="n">
         <v>1294125</v>
@@ -32936,7 +32936,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.19518530368805</v>
+        <v>1.19518518447876</v>
       </c>
       <c r="H1123" t="n">
         <v>4288487</v>
@@ -33023,7 +33023,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.2010315656662</v>
+        <v>1.20103168487549</v>
       </c>
       <c r="H1126" t="n">
         <v>2927344</v>
@@ -33081,7 +33081,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.08660793304443</v>
+        <v>1.08660781383514</v>
       </c>
       <c r="H1128" t="n">
         <v>2648710</v>
@@ -33110,7 +33110,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.08911371231079</v>
+        <v>1.0891135931015</v>
       </c>
       <c r="H1129" t="n">
         <v>1315970</v>
@@ -33139,7 +33139,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.11082911491394</v>
+        <v>1.11082923412323</v>
       </c>
       <c r="H1130" t="n">
         <v>1128829</v>
@@ -33197,7 +33197,7 @@
         <v>1.44700002670288</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.2085485458374</v>
+        <v>1.20854866504669</v>
       </c>
       <c r="H1132" t="n">
         <v>2622105</v>
@@ -33313,7 +33313,7 @@
         <v>1.4539999961853</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.21439504623413</v>
+        <v>1.21439492702484</v>
       </c>
       <c r="H1136" t="n">
         <v>1385149</v>
@@ -33342,7 +33342,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.17597544193268</v>
+        <v>1.17597556114197</v>
       </c>
       <c r="H1137" t="n">
         <v>1151867</v>
@@ -33371,7 +33371,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.17764580249786</v>
+        <v>1.17764592170715</v>
       </c>
       <c r="H1138" t="n">
         <v>954584</v>
@@ -33400,7 +33400,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.1659529209137</v>
+        <v>1.16595280170441</v>
       </c>
       <c r="H1139" t="n">
         <v>669422</v>
@@ -33487,7 +33487,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.14006149768829</v>
+        <v>1.140061378479</v>
       </c>
       <c r="H1142" t="n">
         <v>810784</v>
@@ -33516,7 +33516,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.17597544193268</v>
+        <v>1.17597556114197</v>
       </c>
       <c r="H1143" t="n">
         <v>748993</v>
@@ -33545,7 +33545,7 @@
         <v>1.39400005340576</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.1642826795578</v>
+        <v>1.16428256034851</v>
       </c>
       <c r="H1144" t="n">
         <v>659890</v>
@@ -33574,7 +33574,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.18599808216095</v>
+        <v>1.18599796295166</v>
       </c>
       <c r="H1145" t="n">
         <v>1023147</v>
@@ -33603,7 +33603,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.19434988498688</v>
+        <v>1.19435000419617</v>
       </c>
       <c r="H1146" t="n">
         <v>662446</v>
@@ -33661,7 +33661,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.19852614402771</v>
+        <v>1.19852602481842</v>
       </c>
       <c r="H1148" t="n">
         <v>8763913</v>
@@ -33690,7 +33690,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.1734699010849</v>
+        <v>1.17346966266632</v>
       </c>
       <c r="H1149" t="n">
         <v>1614825</v>
@@ -33777,7 +33777,7 @@
         <v>1.45299994945526</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.21355986595154</v>
+        <v>1.21355974674225</v>
       </c>
       <c r="H1152" t="n">
         <v>3560690</v>
@@ -33806,7 +33806,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.19434988498688</v>
+        <v>1.19435000419617</v>
       </c>
       <c r="H1153" t="n">
         <v>2312871</v>
@@ -33835,7 +33835,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.2010315656662</v>
+        <v>1.20103168487549</v>
       </c>
       <c r="H1154" t="n">
         <v>1543751</v>
@@ -33980,7 +33980,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.16177690029144</v>
+        <v>1.16177678108215</v>
       </c>
       <c r="H1159" t="n">
         <v>1134501</v>
@@ -34009,7 +34009,7 @@
         <v>1.32299995422363</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.10498261451721</v>
+        <v>1.10498237609863</v>
       </c>
       <c r="H1160" t="n">
         <v>2253150</v>
@@ -34038,7 +34038,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.10247707366943</v>
+        <v>1.10247695446014</v>
       </c>
       <c r="H1161" t="n">
         <v>1753450</v>
@@ -34096,7 +34096,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.970513880252838</v>
+        <v>0.970513761043549</v>
       </c>
       <c r="H1163" t="n">
         <v>4861508</v>
@@ -34154,7 +34154,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.916225135326385</v>
+        <v>0.91622519493103</v>
       </c>
       <c r="H1165" t="n">
         <v>2858950</v>
@@ -34212,7 +34212,7 @@
         <v>1.09899997711182</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.917895615100861</v>
+        <v>0.917895495891571</v>
       </c>
       <c r="H1167" t="n">
         <v>2532403</v>
@@ -34241,7 +34241,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.886157631874084</v>
+        <v>0.88615757226944</v>
       </c>
       <c r="H1168" t="n">
         <v>1993581</v>
@@ -34299,7 +34299,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.918730854988098</v>
+        <v>0.918730735778809</v>
       </c>
       <c r="H1170" t="n">
         <v>1314740</v>
@@ -34415,7 +34415,7 @@
         <v>1.14199995994568</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.95380961894989</v>
+        <v>0.953809499740601</v>
       </c>
       <c r="H1174" t="n">
         <v>982082</v>
@@ -34444,7 +34444,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.945457577705383</v>
+        <v>0.945457458496094</v>
       </c>
       <c r="H1175" t="n">
         <v>642129</v>
@@ -34473,7 +34473,7 @@
         <v>1.125</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.939610958099365</v>
+        <v>0.939611077308655</v>
       </c>
       <c r="H1176" t="n">
         <v>937169</v>
@@ -34502,7 +34502,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.937940716743469</v>
+        <v>0.937940657138824</v>
       </c>
       <c r="H1177" t="n">
         <v>740490</v>
@@ -34531,7 +34531,7 @@
         <v>1.10300004482269</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.921236574649811</v>
+        <v>0.921236395835876</v>
       </c>
       <c r="H1178" t="n">
         <v>1249603</v>
@@ -34560,7 +34560,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.915389895439148</v>
+        <v>0.915389835834503</v>
       </c>
       <c r="H1179" t="n">
         <v>613195</v>
@@ -34589,7 +34589,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.942951917648315</v>
+        <v>0.942951798439026</v>
       </c>
       <c r="H1180" t="n">
         <v>992299</v>
@@ -34618,7 +34618,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.918730854988098</v>
+        <v>0.918730735778809</v>
       </c>
       <c r="H1181" t="n">
         <v>976233</v>
@@ -34734,7 +34734,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.908708333969116</v>
+        <v>0.908708274364471</v>
       </c>
       <c r="H1185" t="n">
         <v>1886603</v>
@@ -34792,7 +34792,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.905367434024811</v>
+        <v>0.905367493629456</v>
       </c>
       <c r="H1187" t="n">
         <v>1392144</v>
@@ -34850,7 +34850,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.888663232326508</v>
+        <v>0.888663291931152</v>
       </c>
       <c r="H1189" t="n">
         <v>842442</v>
@@ -34908,7 +34908,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.897015392780304</v>
+        <v>0.897015333175659</v>
       </c>
       <c r="H1191" t="n">
         <v>1331626</v>
@@ -34937,7 +34937,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.918730854988098</v>
+        <v>0.918730735778809</v>
       </c>
       <c r="H1192" t="n">
         <v>2380908</v>
@@ -34995,7 +34995,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.905367434024811</v>
+        <v>0.905367493629456</v>
       </c>
       <c r="H1194" t="n">
         <v>698588</v>
@@ -35024,7 +35024,7 @@
         <v>1.0809999704361</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.902861773967743</v>
+        <v>0.902861833572388</v>
       </c>
       <c r="H1195" t="n">
         <v>652835</v>
@@ -35082,7 +35082,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.91455465555191</v>
+        <v>0.9145547747612</v>
       </c>
       <c r="H1197" t="n">
         <v>1059605</v>
@@ -35111,7 +35111,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.937105417251587</v>
+        <v>0.937105476856232</v>
       </c>
       <c r="H1198" t="n">
         <v>1687673</v>
@@ -35140,7 +35140,7 @@
         <v>1.10800004005432</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.925412476062775</v>
+        <v>0.925412535667419</v>
       </c>
       <c r="H1199" t="n">
         <v>870459</v>
@@ -35169,7 +35169,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.912049114704132</v>
+        <v>0.912049055099487</v>
       </c>
       <c r="H1200" t="n">
         <v>1226727</v>
@@ -35198,7 +35198,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.890333712100983</v>
+        <v>0.890333652496338</v>
       </c>
       <c r="H1201" t="n">
         <v>2226316</v>
@@ -35227,7 +35227,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.892004132270813</v>
+        <v>0.892004072666168</v>
       </c>
       <c r="H1202" t="n">
         <v>631454</v>
@@ -35343,7 +35343,7 @@
         <v>0.993499994277954</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.82978093624115</v>
+        <v>0.829780995845795</v>
       </c>
       <c r="H1206" t="n">
         <v>1701993</v>
@@ -35372,7 +35372,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.8343745470047</v>
+        <v>0.834374606609344</v>
       </c>
       <c r="H1207" t="n">
         <v>1051359</v>
@@ -35430,7 +35430,7 @@
         <v>1.0110000371933</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.844397127628326</v>
+        <v>0.844397068023682</v>
       </c>
       <c r="H1209" t="n">
         <v>918635</v>
@@ -35459,7 +35459,7 @@
         <v>1.02799999713898</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.858595728874207</v>
+        <v>0.858595669269562</v>
       </c>
       <c r="H1210" t="n">
         <v>796084</v>
@@ -35488,7 +35488,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.898685812950134</v>
+        <v>0.89868575334549</v>
       </c>
       <c r="H1211" t="n">
         <v>2105739</v>
@@ -35604,7 +35604,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.884487211704254</v>
+        <v>0.884487152099609</v>
       </c>
       <c r="H1215" t="n">
         <v>491423</v>
@@ -35633,7 +35633,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.855254948139191</v>
+        <v>0.855254888534546</v>
       </c>
       <c r="H1216" t="n">
         <v>846295</v>
@@ -35662,7 +35662,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.915389895439148</v>
+        <v>0.915389835834503</v>
       </c>
       <c r="H1217" t="n">
         <v>2997238</v>
@@ -35720,7 +35720,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.868618130683899</v>
+        <v>0.868618190288544</v>
       </c>
       <c r="H1219" t="n">
         <v>1717438</v>
@@ -35778,7 +35778,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.86444216966629</v>
+        <v>0.864442110061646</v>
       </c>
       <c r="H1221" t="n">
         <v>897836</v>
@@ -35807,7 +35807,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.843561887741089</v>
+        <v>0.843561947345734</v>
       </c>
       <c r="H1222" t="n">
         <v>990227</v>
@@ -35865,7 +35865,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.836880266666412</v>
+        <v>0.836880207061768</v>
       </c>
       <c r="H1224" t="n">
         <v>577518</v>
@@ -35923,7 +35923,7 @@
         <v>0.961000025272369</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.802636682987213</v>
+        <v>0.802636623382568</v>
       </c>
       <c r="H1226" t="n">
         <v>970518</v>
@@ -35952,7 +35952,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.768393099308014</v>
+        <v>0.768393039703369</v>
       </c>
       <c r="H1227" t="n">
         <v>1311041</v>
@@ -35981,7 +35981,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.729973375797272</v>
+        <v>0.729973316192627</v>
       </c>
       <c r="H1228" t="n">
         <v>1596505</v>
@@ -36039,7 +36039,7 @@
         <v>0.962499976158142</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.803889393806458</v>
+        <v>0.803889453411102</v>
       </c>
       <c r="H1230" t="n">
         <v>1720467</v>
@@ -36068,7 +36068,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.794284522533417</v>
+        <v>0.794284403324127</v>
       </c>
       <c r="H1231" t="n">
         <v>1081621</v>
@@ -36097,7 +36097,7 @@
         <v>0.966499984264374</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.807230293750763</v>
+        <v>0.807230234146118</v>
       </c>
       <c r="H1232" t="n">
         <v>635898</v>
@@ -36126,7 +36126,7 @@
         <v>0.993499994277954</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.82978093624115</v>
+        <v>0.829780995845795</v>
       </c>
       <c r="H1233" t="n">
         <v>1561801</v>
@@ -36155,7 +36155,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.856090009212494</v>
+        <v>0.856090068817139</v>
       </c>
       <c r="H1234" t="n">
         <v>2709801</v>
@@ -36184,7 +36184,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.924577236175537</v>
+        <v>0.924577295780182</v>
       </c>
       <c r="H1235" t="n">
         <v>4003298</v>
@@ -36242,7 +36242,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.951304078102112</v>
+        <v>0.951303958892822</v>
       </c>
       <c r="H1237" t="n">
         <v>1870101</v>
@@ -36271,7 +36271,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.957150518894196</v>
+        <v>0.957150638103485</v>
       </c>
       <c r="H1238" t="n">
         <v>2938823</v>
@@ -36300,7 +36300,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.96633768081665</v>
+        <v>0.966337740421295</v>
       </c>
       <c r="H1239" t="n">
         <v>1609545</v>
@@ -36329,7 +36329,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.0206264257431</v>
+        <v>1.02062630653381</v>
       </c>
       <c r="H1240" t="n">
         <v>3536526</v>
@@ -36416,7 +36416,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.02981376647949</v>
+        <v>1.0298136472702</v>
       </c>
       <c r="H1243" t="n">
         <v>2819086</v>
@@ -36445,7 +36445,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.07491493225098</v>
+        <v>1.07491481304169</v>
       </c>
       <c r="H1244" t="n">
         <v>2961990</v>
@@ -36474,7 +36474,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.07491493225098</v>
+        <v>1.07491481304169</v>
       </c>
       <c r="H1245" t="n">
         <v>2543126</v>
@@ -36503,7 +36503,7 @@
         <v>1.3289999961853</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.10999381542206</v>
+        <v>1.10999393463135</v>
       </c>
       <c r="H1246" t="n">
         <v>3085957</v>
@@ -36561,7 +36561,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.08911371231079</v>
+        <v>1.0891135931015</v>
       </c>
       <c r="H1248" t="n">
         <v>1046280</v>
@@ -36590,7 +36590,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.06906867027283</v>
+        <v>1.06906855106354</v>
       </c>
       <c r="H1249" t="n">
         <v>3269294</v>
@@ -36619,7 +36619,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.06906867027283</v>
+        <v>1.06906855106354</v>
       </c>
       <c r="H1250" t="n">
         <v>1487972</v>
@@ -36648,7 +36648,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.07909107208252</v>
+        <v>1.07909119129181</v>
       </c>
       <c r="H1251" t="n">
         <v>1682016</v>
@@ -36677,7 +36677,7 @@
         <v>1.28299999237061</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.0715743303299</v>
+        <v>1.07157421112061</v>
       </c>
       <c r="H1252" t="n">
         <v>1240166</v>
@@ -36706,7 +36706,7 @@
         <v>1.27499997615814</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.06489241123199</v>
+        <v>1.06489253044128</v>
       </c>
       <c r="H1253" t="n">
         <v>1869943</v>
@@ -36735,7 +36735,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.04317712783813</v>
+        <v>1.04317688941956</v>
       </c>
       <c r="H1254" t="n">
         <v>2115098</v>
@@ -36822,7 +36822,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.02229678630829</v>
+        <v>1.02229690551758</v>
       </c>
       <c r="H1257" t="n">
         <v>1511324</v>
@@ -36851,7 +36851,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.0122743844986</v>
+        <v>1.01227426528931</v>
       </c>
       <c r="H1258" t="n">
         <v>1499780</v>
@@ -36880,7 +36880,7 @@
         <v>1.20299994945526</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.00475752353668</v>
+        <v>1.0047572851181</v>
       </c>
       <c r="H1259" t="n">
         <v>892409</v>
@@ -36938,7 +36938,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.02981376647949</v>
+        <v>1.0298136472702</v>
       </c>
       <c r="H1261" t="n">
         <v>1624816</v>
@@ -36967,7 +36967,7 @@
         <v>1.21899998188019</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.01812088489532</v>
+        <v>1.01812076568604</v>
       </c>
       <c r="H1262" t="n">
         <v>752242</v>
@@ -37025,7 +37025,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.998075723648071</v>
+        <v>0.998075842857361</v>
       </c>
       <c r="H1264" t="n">
         <v>1064295</v>
@@ -37054,7 +37054,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.951304078102112</v>
+        <v>0.951303958892822</v>
       </c>
       <c r="H1265" t="n">
         <v>3011175</v>
@@ -37083,7 +37083,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.967172920703888</v>
+        <v>0.967172980308533</v>
       </c>
       <c r="H1266" t="n">
         <v>1346794</v>
@@ -37344,7 +37344,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.05737566947937</v>
+        <v>1.05737578868866</v>
       </c>
       <c r="H1275" t="n">
         <v>1591028</v>
@@ -37431,7 +37431,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.05069398880005</v>
+        <v>1.05069410800934</v>
       </c>
       <c r="H1278" t="n">
         <v>718663</v>
@@ -37460,7 +37460,7 @@
         <v>1.26400005817413</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.0557051897049</v>
+        <v>1.05570530891418</v>
       </c>
       <c r="H1279" t="n">
         <v>1280781</v>
@@ -37518,7 +37518,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.06322205066681</v>
+        <v>1.06322193145752</v>
       </c>
       <c r="H1281" t="n">
         <v>1622751</v>
@@ -37547,7 +37547,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G1282" t="n">
-        <v>1.06906867027283</v>
+        <v>1.06906855106354</v>
       </c>
       <c r="H1282" t="n">
         <v>1751527</v>
@@ -37634,7 +37634,7 @@
         <v>1.25899994373322</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.05152904987335</v>
+        <v>1.05152916908264</v>
       </c>
       <c r="H1285" t="n">
         <v>1139462</v>
@@ -37663,7 +37663,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.03482496738434</v>
+        <v>1.03482484817505</v>
       </c>
       <c r="H1286" t="n">
         <v>1259004</v>
@@ -37779,7 +37779,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.02229678630829</v>
+        <v>1.02229690551758</v>
       </c>
       <c r="H1290" t="n">
         <v>860970</v>
@@ -37808,7 +37808,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.05069398880005</v>
+        <v>1.05069410800934</v>
       </c>
       <c r="H1291" t="n">
         <v>1203524</v>
@@ -37895,7 +37895,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.1141699552536</v>
+        <v>1.11416983604431</v>
       </c>
       <c r="H1294" t="n">
         <v>1778230</v>
@@ -37953,7 +37953,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.28371751308441</v>
+        <v>1.28371739387512</v>
       </c>
       <c r="H1296" t="n">
         <v>8648318</v>
@@ -37982,7 +37982,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.26784837245941</v>
+        <v>1.2678484916687</v>
       </c>
       <c r="H1297" t="n">
         <v>4152067</v>
@@ -38098,7 +38098,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.41484546661377</v>
+        <v>1.41484534740448</v>
       </c>
       <c r="H1301" t="n">
         <v>7324721</v>
@@ -38127,7 +38127,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.37392008304596</v>
+        <v>1.37391996383667</v>
       </c>
       <c r="H1302" t="n">
         <v>7579786</v>
@@ -38185,7 +38185,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.37392008304596</v>
+        <v>1.37391996383667</v>
       </c>
       <c r="H1304" t="n">
         <v>5369157</v>
@@ -38214,7 +38214,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.3705792427063</v>
+        <v>1.37057936191559</v>
       </c>
       <c r="H1305" t="n">
         <v>2174460</v>
@@ -38272,7 +38272,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.35638058185577</v>
+        <v>1.35638082027435</v>
       </c>
       <c r="H1307" t="n">
         <v>1681134</v>
@@ -38301,7 +38301,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.35638058185577</v>
+        <v>1.35638082027435</v>
       </c>
       <c r="H1308" t="n">
         <v>1410687</v>
@@ -38330,7 +38330,7 @@
         <v>1.56599998474121</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.30793857574463</v>
+        <v>1.30793845653534</v>
       </c>
       <c r="H1309" t="n">
         <v>2216085</v>
@@ -38388,7 +38388,7 @@
         <v>1.5809999704361</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.3204665184021</v>
+        <v>1.32046663761139</v>
       </c>
       <c r="H1311" t="n">
         <v>3540376</v>
@@ -38417,7 +38417,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.30376243591309</v>
+        <v>1.30376255512238</v>
       </c>
       <c r="H1312" t="n">
         <v>1457296</v>
@@ -38446,7 +38446,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.30125677585602</v>
+        <v>1.30125689506531</v>
       </c>
       <c r="H1313" t="n">
         <v>2530993</v>
@@ -38562,7 +38562,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.35638058185577</v>
+        <v>1.35638082027435</v>
       </c>
       <c r="H1317" t="n">
         <v>3043688</v>
@@ -38591,7 +38591,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.37392008304596</v>
+        <v>1.37391996383667</v>
       </c>
       <c r="H1318" t="n">
         <v>2115244</v>
@@ -38678,7 +38678,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.4215270280838</v>
+        <v>1.42152714729309</v>
       </c>
       <c r="H1321" t="n">
         <v>9920232</v>
@@ -38736,7 +38736,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.44491302967072</v>
+        <v>1.44491291046143</v>
       </c>
       <c r="H1323" t="n">
         <v>2240203</v>
@@ -38765,7 +38765,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.44825387001038</v>
+        <v>1.44825375080109</v>
       </c>
       <c r="H1324" t="n">
         <v>1605888</v>
@@ -38794,7 +38794,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.40565812587738</v>
+        <v>1.40565800666809</v>
       </c>
       <c r="H1325" t="n">
         <v>2689682</v>
@@ -38823,7 +38823,7 @@
         <v>1.73399996757507</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.44825387001038</v>
+        <v>1.44825375080109</v>
       </c>
       <c r="H1326" t="n">
         <v>6989553</v>
@@ -38852,7 +38852,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.43489050865173</v>
+        <v>1.43489038944244</v>
       </c>
       <c r="H1327" t="n">
         <v>3619939</v>
@@ -38910,7 +38910,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.44073688983917</v>
+        <v>1.44073700904846</v>
       </c>
       <c r="H1329" t="n">
         <v>2512664</v>
@@ -38939,7 +38939,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.50337767601013</v>
+        <v>1.50337755680084</v>
       </c>
       <c r="H1330" t="n">
         <v>6229911</v>
@@ -39055,7 +39055,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.50337767601013</v>
+        <v>1.50337755680084</v>
       </c>
       <c r="H1334" t="n">
         <v>1519136</v>
@@ -39200,7 +39200,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.52258741855621</v>
+        <v>1.5225875377655</v>
       </c>
       <c r="H1339" t="n">
         <v>2478018</v>
@@ -39258,7 +39258,7 @@
         <v>1.84300005435944</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.53929162025452</v>
+        <v>1.5392918586731</v>
       </c>
       <c r="H1341" t="n">
         <v>1846248</v>
@@ -39316,7 +39316,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.53261005878448</v>
+        <v>1.53261017799377</v>
       </c>
       <c r="H1343" t="n">
         <v>1607652</v>
@@ -39345,7 +39345,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.52676355838776</v>
+        <v>1.52676343917847</v>
       </c>
       <c r="H1344" t="n">
         <v>2246042</v>
@@ -39432,7 +39432,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.52342259883881</v>
+        <v>1.5234227180481</v>
       </c>
       <c r="H1347" t="n">
         <v>1689611</v>
@@ -39461,7 +39461,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.53010439872742</v>
+        <v>1.53010427951813</v>
       </c>
       <c r="H1348" t="n">
         <v>1071676</v>
@@ -39519,7 +39519,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.52843403816223</v>
+        <v>1.52843391895294</v>
       </c>
       <c r="H1350" t="n">
         <v>1164177</v>
@@ -39577,7 +39577,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.51507067680359</v>
+        <v>1.5150705575943</v>
       </c>
       <c r="H1352" t="n">
         <v>1198582</v>
@@ -39606,7 +39606,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.4975311756134</v>
+        <v>1.49753129482269</v>
       </c>
       <c r="H1353" t="n">
         <v>985226</v>
@@ -39635,7 +39635,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.51590573787689</v>
+        <v>1.51590585708618</v>
       </c>
       <c r="H1354" t="n">
         <v>1355627</v>
@@ -39664,7 +39664,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.50922417640686</v>
+        <v>1.50922429561615</v>
       </c>
       <c r="H1355" t="n">
         <v>1657793</v>
@@ -39693,7 +39693,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.52258741855621</v>
+        <v>1.5225875377655</v>
       </c>
       <c r="H1356" t="n">
         <v>1042227</v>
@@ -39722,7 +39722,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.51924681663513</v>
+        <v>1.51924669742584</v>
       </c>
       <c r="H1357" t="n">
         <v>1221440</v>
@@ -39751,7 +39751,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.51924681663513</v>
+        <v>1.51924669742584</v>
       </c>
       <c r="H1358" t="n">
         <v>1480530</v>
@@ -39838,7 +39838,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.59848177433014</v>
+        <v>1.59848165512085</v>
       </c>
       <c r="H1361" t="n">
         <v>1925364</v>
@@ -39896,7 +39896,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.57436668872833</v>
+        <v>1.57436656951904</v>
       </c>
       <c r="H1363" t="n">
         <v>1985641</v>
@@ -39954,7 +39954,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.57781171798706</v>
+        <v>1.57781159877777</v>
       </c>
       <c r="H1365" t="n">
         <v>2528781</v>
@@ -40041,7 +40041,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.5580028295517</v>
+        <v>1.55800294876099</v>
       </c>
       <c r="H1368" t="n">
         <v>792658</v>
@@ -40128,7 +40128,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.61053907871246</v>
+        <v>1.61053919792175</v>
       </c>
       <c r="H1371" t="n">
         <v>3323900</v>
@@ -40244,7 +40244,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.76384198665619</v>
+        <v>1.7638418674469</v>
       </c>
       <c r="H1375" t="n">
         <v>6289366</v>
@@ -40302,7 +40302,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.831019282341</v>
+        <v>1.83101940155029</v>
       </c>
       <c r="H1377" t="n">
         <v>5655370</v>
@@ -40360,7 +40360,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.80173683166504</v>
+        <v>1.80173695087433</v>
       </c>
       <c r="H1379" t="n">
         <v>2810289</v>
@@ -40534,7 +40534,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.88269448280334</v>
+        <v>1.88269436359406</v>
       </c>
       <c r="H1385" t="n">
         <v>10053816</v>
@@ -40592,7 +40592,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.82585191726685</v>
+        <v>1.82585179805756</v>
       </c>
       <c r="H1387" t="n">
         <v>2856954</v>
@@ -40650,7 +40650,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.79656946659088</v>
+        <v>1.79656934738159</v>
       </c>
       <c r="H1389" t="n">
         <v>2547377</v>
@@ -40998,7 +40998,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.94125938415527</v>
+        <v>1.94125962257385</v>
       </c>
       <c r="H1401" t="n">
         <v>2335253</v>
@@ -41027,7 +41027,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.91542196273804</v>
+        <v>1.91542208194733</v>
       </c>
       <c r="H1402" t="n">
         <v>4795754</v>
@@ -41056,7 +41056,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.93264698982239</v>
+        <v>1.93264710903168</v>
       </c>
       <c r="H1403" t="n">
         <v>1862149</v>
@@ -41085,7 +41085,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.91197681427002</v>
+        <v>1.91197693347931</v>
       </c>
       <c r="H1404" t="n">
         <v>1741874</v>
@@ -41114,7 +41114,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.9343695640564</v>
+        <v>1.93436968326569</v>
       </c>
       <c r="H1405" t="n">
         <v>1889156</v>
@@ -41143,7 +41143,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.92058956623077</v>
+        <v>1.92058968544006</v>
       </c>
       <c r="H1406" t="n">
         <v>1626077</v>
@@ -41172,7 +41172,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.89475202560425</v>
+        <v>1.89475190639496</v>
       </c>
       <c r="H1407" t="n">
         <v>1693344</v>
@@ -41259,7 +41259,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.81207191944122</v>
+        <v>1.81207180023193</v>
       </c>
       <c r="H1410" t="n">
         <v>3028379</v>
@@ -41520,7 +41520,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.92920196056366</v>
+        <v>1.92920207977295</v>
       </c>
       <c r="H1419" t="n">
         <v>22194642</v>
@@ -41549,7 +41549,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.90336465835571</v>
+        <v>1.90336453914642</v>
       </c>
       <c r="H1420" t="n">
         <v>5111147</v>
@@ -41578,7 +41578,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.91886687278748</v>
+        <v>1.91886711120605</v>
       </c>
       <c r="H1421" t="n">
         <v>2504540</v>
@@ -41636,7 +41636,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.89647436141968</v>
+        <v>1.8964741230011</v>
       </c>
       <c r="H1423" t="n">
         <v>2073595</v>
@@ -41723,7 +41723,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.99293434619904</v>
+        <v>1.99293458461761</v>
       </c>
       <c r="H1426" t="n">
         <v>5731370</v>
@@ -41752,7 +41752,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.01704978942871</v>
+        <v>2.01704955101013</v>
       </c>
       <c r="H1427" t="n">
         <v>5253085</v>
@@ -41781,7 +41781,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.11006474494934</v>
+        <v>2.11006498336792</v>
       </c>
       <c r="H1428" t="n">
         <v>7160511</v>
@@ -41868,7 +41868,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1431" t="n">
-        <v>2.02049469947815</v>
+        <v>2.02049446105957</v>
       </c>
       <c r="H1431" t="n">
         <v>2887673</v>
@@ -41955,7 +41955,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.92058956623077</v>
+        <v>1.92058968544006</v>
       </c>
       <c r="H1434" t="n">
         <v>2727200</v>
@@ -41984,7 +41984,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.91197681427002</v>
+        <v>1.91197693347931</v>
       </c>
       <c r="H1435" t="n">
         <v>1399216</v>
@@ -42042,7 +42042,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.94125938415527</v>
+        <v>1.94125962257385</v>
       </c>
       <c r="H1437" t="n">
         <v>1502670</v>
@@ -42100,7 +42100,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.96020722389221</v>
+        <v>1.96020698547363</v>
       </c>
       <c r="H1439" t="n">
         <v>1459843</v>
@@ -42187,7 +42187,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.0153272151947</v>
+        <v>2.01532697677612</v>
       </c>
       <c r="H1442" t="n">
         <v>4357519</v>
@@ -42274,7 +42274,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.99293434619904</v>
+        <v>1.99293458461761</v>
       </c>
       <c r="H1445" t="n">
         <v>1455081</v>
@@ -42564,7 +42564,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.89475202560425</v>
+        <v>1.89475190639496</v>
       </c>
       <c r="H1455" t="n">
         <v>1370526</v>
@@ -42593,7 +42593,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1456" t="n">
-        <v>1.92058956623077</v>
+        <v>1.92058968544006</v>
       </c>
       <c r="H1456" t="n">
         <v>920719</v>
@@ -42622,7 +42622,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1457" t="n">
-        <v>1.92058956623077</v>
+        <v>1.92058968544006</v>
       </c>
       <c r="H1457" t="n">
         <v>1237770</v>
@@ -42651,7 +42651,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.90680944919586</v>
+        <v>1.90680956840515</v>
       </c>
       <c r="H1458" t="n">
         <v>1242219</v>
@@ -42680,7 +42680,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.89475202560425</v>
+        <v>1.89475190639496</v>
       </c>
       <c r="H1459" t="n">
         <v>1599201</v>
@@ -42738,7 +42738,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.86030185222626</v>
+        <v>1.86030197143555</v>
       </c>
       <c r="H1461" t="n">
         <v>1395726</v>
@@ -42767,7 +42767,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G1462" t="n">
-        <v>1.89819705486298</v>
+        <v>1.89819693565369</v>
       </c>
       <c r="H1462" t="n">
         <v>2024308</v>
@@ -42796,7 +42796,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.88269448280334</v>
+        <v>1.88269436359406</v>
       </c>
       <c r="H1463" t="n">
         <v>1629758</v>
@@ -42883,7 +42883,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.82929694652557</v>
+        <v>1.82929706573486</v>
       </c>
       <c r="H1466" t="n">
         <v>4060132</v>
@@ -42912,7 +42912,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.84479928016663</v>
+        <v>1.84479939937592</v>
       </c>
       <c r="H1467" t="n">
         <v>2159433</v>
@@ -42941,7 +42941,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.85513436794281</v>
+        <v>1.85513424873352</v>
       </c>
       <c r="H1468" t="n">
         <v>1757422</v>
@@ -42999,7 +42999,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G1470" t="n">
-        <v>1.89647436141968</v>
+        <v>1.8964741230011</v>
       </c>
       <c r="H1470" t="n">
         <v>1507237</v>
@@ -43173,7 +43173,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1476" t="n">
-        <v>1.86030185222626</v>
+        <v>1.86030197143555</v>
       </c>
       <c r="H1476" t="n">
         <v>1643206</v>
@@ -43202,7 +43202,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G1477" t="n">
-        <v>1.88269448280334</v>
+        <v>1.88269436359406</v>
       </c>
       <c r="H1477" t="n">
         <v>3127656</v>
@@ -43231,7 +43231,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.89302945137024</v>
+        <v>1.89302933216095</v>
       </c>
       <c r="H1478" t="n">
         <v>1181498</v>
@@ -43318,7 +43318,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.84479928016663</v>
+        <v>1.84479939937592</v>
       </c>
       <c r="H1481" t="n">
         <v>1640065</v>
@@ -43405,7 +43405,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.87408196926117</v>
+        <v>1.87408208847046</v>
       </c>
       <c r="H1484" t="n">
         <v>2025662</v>
@@ -43608,7 +43608,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1491" t="n">
-        <v>1.86030185222626</v>
+        <v>1.86030197143555</v>
       </c>
       <c r="H1491" t="n">
         <v>3727686</v>
@@ -43753,7 +43753,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.81207191944122</v>
+        <v>1.81207180023193</v>
       </c>
       <c r="H1496" t="n">
         <v>1731235</v>
@@ -43782,7 +43782,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.80001413822174</v>
+        <v>1.80001425743103</v>
       </c>
       <c r="H1497" t="n">
         <v>1978111</v>
@@ -44043,7 +44043,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.74489438533783</v>
+        <v>1.74489450454712</v>
       </c>
       <c r="H1506" t="n">
         <v>3370365</v>
@@ -44101,7 +44101,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.72766935825348</v>
+        <v>1.72766923904419</v>
       </c>
       <c r="H1508" t="n">
         <v>1310633</v>
@@ -44159,7 +44159,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.82929694652557</v>
+        <v>1.82929706573486</v>
       </c>
       <c r="H1510" t="n">
         <v>1482468</v>
@@ -44188,7 +44188,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.79656946659088</v>
+        <v>1.79656934738159</v>
       </c>
       <c r="H1511" t="n">
         <v>752410</v>
@@ -44217,7 +44217,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.80173683166504</v>
+        <v>1.80173695087433</v>
       </c>
       <c r="H1512" t="n">
         <v>897905</v>
@@ -44275,7 +44275,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G1514" t="n">
-        <v>1.75350689888</v>
+        <v>1.75350677967072</v>
       </c>
       <c r="H1514" t="n">
         <v>1408688</v>
@@ -44449,7 +44449,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.74489438533783</v>
+        <v>1.74489450454712</v>
       </c>
       <c r="H1520" t="n">
         <v>1054836</v>
@@ -44652,7 +44652,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G1527" t="n">
-        <v>1.80518174171448</v>
+        <v>1.80518186092377</v>
       </c>
       <c r="H1527" t="n">
         <v>921673</v>
@@ -44681,7 +44681,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G1528" t="n">
-        <v>1.80518174171448</v>
+        <v>1.80518186092377</v>
       </c>
       <c r="H1528" t="n">
         <v>1918247</v>
@@ -44884,7 +44884,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G1535" t="n">
-        <v>1.75350689888</v>
+        <v>1.75350677967072</v>
       </c>
       <c r="H1535" t="n">
         <v>3155367</v>
@@ -44913,7 +44913,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.72766935825348</v>
+        <v>1.72766923904419</v>
       </c>
       <c r="H1536" t="n">
         <v>5758603</v>
@@ -44942,7 +44942,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.78278946876526</v>
+        <v>1.78278934955597</v>
       </c>
       <c r="H1537" t="n">
         <v>2586008</v>
@@ -45000,7 +45000,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G1539" t="n">
-        <v>1.74489438533783</v>
+        <v>1.74489450454712</v>
       </c>
       <c r="H1539" t="n">
         <v>1187215</v>
@@ -45116,7 +45116,7 @@
         <v>1.875</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.61484551429749</v>
+        <v>1.61484563350677</v>
       </c>
       <c r="H1543" t="n">
         <v>1541075</v>
@@ -45145,7 +45145,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G1544" t="n">
-        <v>1.56661546230316</v>
+        <v>1.56661534309387</v>
       </c>
       <c r="H1544" t="n">
         <v>6401161</v>
@@ -45232,7 +45232,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.59589791297913</v>
+        <v>1.59589779376984</v>
       </c>
       <c r="H1547" t="n">
         <v>2613730</v>
@@ -45290,7 +45290,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G1549" t="n">
-        <v>1.60020411014557</v>
+        <v>1.60020422935486</v>
       </c>
       <c r="H1549" t="n">
         <v>2078255</v>
@@ -45493,7 +45493,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.57436668872833</v>
+        <v>1.57436656951904</v>
       </c>
       <c r="H1556" t="n">
         <v>1037392</v>
@@ -45696,7 +45696,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.47101640701294</v>
+        <v>1.47101652622223</v>
       </c>
       <c r="H1563" t="n">
         <v>2448765</v>
@@ -45725,7 +45725,7 @@
         <v>1.68099999427795</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.44776296615601</v>
+        <v>1.44776284694672</v>
       </c>
       <c r="H1564" t="n">
         <v>1508958</v>
@@ -45754,7 +45754,7 @@
         <v>1.62300002574921</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.39781033992767</v>
+        <v>1.39781022071838</v>
       </c>
       <c r="H1565" t="n">
         <v>4082257</v>
@@ -45783,7 +45783,7 @@
         <v>1.7389999628067</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.49771547317505</v>
+        <v>1.49771535396576</v>
       </c>
       <c r="H1566" t="n">
         <v>4014926</v>
@@ -45812,7 +45812,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.45206892490387</v>
+        <v>1.45206880569458</v>
       </c>
       <c r="H1567" t="n">
         <v>2169113</v>
@@ -45870,7 +45870,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.41245150566101</v>
+        <v>1.41245138645172</v>
       </c>
       <c r="H1569" t="n">
         <v>3160029</v>
@@ -45957,7 +45957,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.2643164396286</v>
+        <v>1.26431632041931</v>
       </c>
       <c r="H1572" t="n">
         <v>3671085</v>
@@ -46044,7 +46044,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.3306325674057</v>
+        <v>1.33063268661499</v>
       </c>
       <c r="H1575" t="n">
         <v>891189</v>
@@ -46247,7 +46247,7 @@
         <v>1.60699999332428</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.38402998447418</v>
+        <v>1.38403010368347</v>
       </c>
       <c r="H1582" t="n">
         <v>1407014</v>
@@ -46276,7 +46276,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.3986713886261</v>
+        <v>1.39867150783539</v>
       </c>
       <c r="H1583" t="n">
         <v>3037320</v>
@@ -46711,7 +46711,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.38316893577576</v>
+        <v>1.38316881656647</v>
       </c>
       <c r="H1598" t="n">
         <v>507869</v>
@@ -46885,7 +46885,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.42795395851135</v>
+        <v>1.42795407772064</v>
       </c>
       <c r="H1604" t="n">
         <v>1349109</v>
@@ -47030,7 +47030,7 @@
         <v>1.625</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.3995326757431</v>
+        <v>1.39953279495239</v>
       </c>
       <c r="H1609" t="n">
         <v>792740</v>
@@ -47088,7 +47088,7 @@
         <v>1.62800002098083</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.40211629867554</v>
+        <v>1.40211641788483</v>
       </c>
       <c r="H1611" t="n">
         <v>949471</v>
@@ -80183,6 +80183,35 @@
         <v>4852049</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>2.05200004577637</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>2.09999990463257</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>2.03999996185303</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>2.09800004959106</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>2.09800004959106</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>3160956</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WBD.MI.xlsx
+++ b/data/WBD.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9959831237793</v>
+        <v>2.99598336219788</v>
       </c>
       <c r="H2" t="n">
         <v>726355</v>
@@ -456,7 +456,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91082620620728</v>
+        <v>2.91082644462585</v>
       </c>
       <c r="H3" t="n">
         <v>1077659</v>
@@ -485,7 +485,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G4" t="n">
-        <v>2.87366676330566</v>
+        <v>2.87366652488708</v>
       </c>
       <c r="H4" t="n">
         <v>1045563</v>
@@ -572,7 +572,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G7" t="n">
-        <v>2.75599503517151</v>
+        <v>2.75599479675293</v>
       </c>
       <c r="H7" t="n">
         <v>914159</v>
@@ -601,7 +601,7 @@
         <v>3.56800007820129</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76218819618225</v>
+        <v>2.76218867301941</v>
       </c>
       <c r="H8" t="n">
         <v>789466</v>
@@ -630,7 +630,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G9" t="n">
-        <v>2.75289845466614</v>
+        <v>2.75289821624756</v>
       </c>
       <c r="H9" t="n">
         <v>581213</v>
@@ -659,7 +659,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75289845466614</v>
+        <v>2.75289821624756</v>
       </c>
       <c r="H10" t="n">
         <v>1613399</v>
@@ -688,7 +688,7 @@
         <v>3.4779999256134</v>
       </c>
       <c r="G11" t="n">
-        <v>2.69251418113708</v>
+        <v>2.69251441955566</v>
       </c>
       <c r="H11" t="n">
         <v>1573296</v>
@@ -717,7 +717,7 @@
         <v>3.37199997901917</v>
       </c>
       <c r="G12" t="n">
-        <v>2.61045360565186</v>
+        <v>2.61045384407043</v>
       </c>
       <c r="H12" t="n">
         <v>1596810</v>
@@ -746,7 +746,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66464424133301</v>
+        <v>2.66464471817017</v>
       </c>
       <c r="H13" t="n">
         <v>964050</v>
@@ -775,7 +775,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G14" t="n">
-        <v>2.58877730369568</v>
+        <v>2.58877754211426</v>
       </c>
       <c r="H14" t="n">
         <v>2075260</v>
@@ -833,7 +833,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G16" t="n">
-        <v>2.74825382232666</v>
+        <v>2.74825310707092</v>
       </c>
       <c r="H16" t="n">
         <v>1094217</v>
@@ -1007,7 +1007,7 @@
         <v>3.54200005531311</v>
       </c>
       <c r="G22" t="n">
-        <v>2.74206018447876</v>
+        <v>2.74206066131592</v>
       </c>
       <c r="H22" t="n">
         <v>585827</v>
@@ -1036,7 +1036,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G23" t="n">
-        <v>2.63213038444519</v>
+        <v>2.63213014602661</v>
       </c>
       <c r="H23" t="n">
         <v>529297</v>
@@ -1065,7 +1065,7 @@
         <v>3.29399991035461</v>
       </c>
       <c r="G24" t="n">
-        <v>2.5500693321228</v>
+        <v>2.55006957054138</v>
       </c>
       <c r="H24" t="n">
         <v>965335</v>
@@ -1094,7 +1094,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G25" t="n">
-        <v>2.61664724349976</v>
+        <v>2.61664700508118</v>
       </c>
       <c r="H25" t="n">
         <v>1715094</v>
@@ -1123,7 +1123,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G26" t="n">
-        <v>2.55316615104675</v>
+        <v>2.55316662788391</v>
       </c>
       <c r="H26" t="n">
         <v>2005520</v>
@@ -1152,7 +1152,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G27" t="n">
-        <v>2.43859100341797</v>
+        <v>2.43859124183655</v>
       </c>
       <c r="H27" t="n">
         <v>2592460</v>
@@ -1210,7 +1210,7 @@
         <v>3.20199990272522</v>
       </c>
       <c r="G29" t="n">
-        <v>2.47884726524353</v>
+        <v>2.47884702682495</v>
       </c>
       <c r="H29" t="n">
         <v>1883723</v>
@@ -1239,7 +1239,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G30" t="n">
-        <v>2.27292156219482</v>
+        <v>2.2729218006134</v>
       </c>
       <c r="H30" t="n">
         <v>2979842</v>
@@ -1355,7 +1355,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G34" t="n">
-        <v>2.60116362571716</v>
+        <v>2.60116410255432</v>
       </c>
       <c r="H34" t="n">
         <v>2832395</v>
@@ -1384,7 +1384,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G35" t="n">
-        <v>2.59342241287231</v>
+        <v>2.59342265129089</v>
       </c>
       <c r="H35" t="n">
         <v>1621895</v>
@@ -1442,7 +1442,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G37" t="n">
-        <v>2.62438869476318</v>
+        <v>2.62438893318176</v>
       </c>
       <c r="H37" t="n">
         <v>1413624</v>
@@ -1471,7 +1471,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G38" t="n">
-        <v>2.63987159729004</v>
+        <v>2.63987183570862</v>
       </c>
       <c r="H38" t="n">
         <v>1416246</v>
@@ -1500,7 +1500,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G39" t="n">
-        <v>2.54077982902527</v>
+        <v>2.54077959060669</v>
       </c>
       <c r="H39" t="n">
         <v>1700027</v>
@@ -1587,7 +1587,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G42" t="n">
-        <v>2.77302646636963</v>
+        <v>2.77302622795105</v>
       </c>
       <c r="H42" t="n">
         <v>1241614</v>
@@ -1645,7 +1645,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G44" t="n">
-        <v>2.85199046134949</v>
+        <v>2.85199022293091</v>
       </c>
       <c r="H44" t="n">
         <v>1524438</v>
@@ -1674,7 +1674,7 @@
         <v>3.7039999961853</v>
       </c>
       <c r="G45" t="n">
-        <v>2.86747336387634</v>
+        <v>2.86747360229492</v>
       </c>
       <c r="H45" t="n">
         <v>1536186</v>
@@ -1703,7 +1703,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G46" t="n">
-        <v>2.9170196056366</v>
+        <v>2.91701936721802</v>
       </c>
       <c r="H46" t="n">
         <v>1310637</v>
@@ -1732,7 +1732,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G47" t="n">
-        <v>2.87366676330566</v>
+        <v>2.87366652488708</v>
       </c>
       <c r="H47" t="n">
         <v>1022713</v>
@@ -1761,7 +1761,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G48" t="n">
-        <v>2.8225724697113</v>
+        <v>2.82257223129272</v>
       </c>
       <c r="H48" t="n">
         <v>1053721</v>
@@ -1790,7 +1790,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>2.80244469642639</v>
+        <v>2.80244421958923</v>
       </c>
       <c r="H49" t="n">
         <v>851655</v>
@@ -1819,7 +1819,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G50" t="n">
-        <v>2.79005789756775</v>
+        <v>2.79005837440491</v>
       </c>
       <c r="H50" t="n">
         <v>1078720</v>
@@ -1848,7 +1848,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G51" t="n">
-        <v>2.83341073989868</v>
+        <v>2.8334105014801</v>
       </c>
       <c r="H51" t="n">
         <v>1171012</v>
@@ -1877,7 +1877,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G52" t="n">
-        <v>2.88914966583252</v>
+        <v>2.88915014266968</v>
       </c>
       <c r="H52" t="n">
         <v>1341195</v>
@@ -1906,7 +1906,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G53" t="n">
-        <v>2.9170196056366</v>
+        <v>2.91701936721802</v>
       </c>
       <c r="H53" t="n">
         <v>764014</v>
@@ -1935,7 +1935,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G54" t="n">
-        <v>2.89069843292236</v>
+        <v>2.89069819450378</v>
       </c>
       <c r="H54" t="n">
         <v>839673</v>
@@ -1964,7 +1964,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>2.85199046134949</v>
+        <v>2.85199022293091</v>
       </c>
       <c r="H55" t="n">
         <v>3876711</v>
@@ -2022,7 +2022,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G57" t="n">
-        <v>2.85199046134949</v>
+        <v>2.85199022293091</v>
       </c>
       <c r="H57" t="n">
         <v>1362718</v>
@@ -2051,7 +2051,7 @@
         <v>3.70199990272522</v>
       </c>
       <c r="G58" t="n">
-        <v>2.86592531204224</v>
+        <v>2.86592507362366</v>
       </c>
       <c r="H58" t="n">
         <v>663781</v>
@@ -2109,7 +2109,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G60" t="n">
-        <v>2.7869610786438</v>
+        <v>2.78696131706238</v>
       </c>
       <c r="H60" t="n">
         <v>440085</v>
@@ -2138,7 +2138,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G61" t="n">
-        <v>2.73276996612549</v>
+        <v>2.73277020454407</v>
       </c>
       <c r="H61" t="n">
         <v>652481</v>
@@ -2167,7 +2167,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>2.87211847305298</v>
+        <v>2.8721182346344</v>
       </c>
       <c r="H62" t="n">
         <v>1273096</v>
@@ -2225,7 +2225,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>2.87211847305298</v>
+        <v>2.8721182346344</v>
       </c>
       <c r="H64" t="n">
         <v>1060756</v>
@@ -2312,7 +2312,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G67" t="n">
-        <v>2.71109390258789</v>
+        <v>2.71109414100647</v>
       </c>
       <c r="H67" t="n">
         <v>574845</v>
@@ -2428,7 +2428,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80244469642639</v>
+        <v>2.80244421958923</v>
       </c>
       <c r="H71" t="n">
         <v>1384237</v>
@@ -2457,7 +2457,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G72" t="n">
-        <v>2.86437702178955</v>
+        <v>2.86437726020813</v>
       </c>
       <c r="H72" t="n">
         <v>2605699</v>
@@ -2486,7 +2486,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G73" t="n">
-        <v>2.89379453659058</v>
+        <v>2.89379501342773</v>
       </c>
       <c r="H73" t="n">
         <v>1090424</v>
@@ -2544,7 +2544,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G75" t="n">
-        <v>2.84424877166748</v>
+        <v>2.84424901008606</v>
       </c>
       <c r="H75" t="n">
         <v>709531</v>
@@ -2573,7 +2573,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.87985968589783</v>
+        <v>2.87986016273499</v>
       </c>
       <c r="H76" t="n">
         <v>593773</v>
@@ -2631,7 +2631,7 @@
         <v>3.74399995803833</v>
       </c>
       <c r="G78" t="n">
-        <v>2.89843940734863</v>
+        <v>2.89843988418579</v>
       </c>
       <c r="H78" t="n">
         <v>973280</v>
@@ -2689,7 +2689,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G80" t="n">
-        <v>2.85353899002075</v>
+        <v>2.85353922843933</v>
       </c>
       <c r="H80" t="n">
         <v>489744</v>
@@ -2718,7 +2718,7 @@
         <v>3.68400001525879</v>
       </c>
       <c r="G81" t="n">
-        <v>2.85199046134949</v>
+        <v>2.85199022293091</v>
       </c>
       <c r="H81" t="n">
         <v>1284292</v>
@@ -2747,7 +2747,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G82" t="n">
-        <v>2.87211847305298</v>
+        <v>2.8721182346344</v>
       </c>
       <c r="H82" t="n">
         <v>647080</v>
@@ -2805,7 +2805,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G84" t="n">
-        <v>2.95882439613342</v>
+        <v>2.95882391929626</v>
       </c>
       <c r="H84" t="n">
         <v>1543779</v>
@@ -2863,7 +2863,7 @@
         <v>3.78800010681152</v>
       </c>
       <c r="G86" t="n">
-        <v>2.93250274658203</v>
+        <v>2.93250298500061</v>
       </c>
       <c r="H86" t="n">
         <v>839175</v>
@@ -2921,7 +2921,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G88" t="n">
-        <v>2.87366676330566</v>
+        <v>2.87366652488708</v>
       </c>
       <c r="H88" t="n">
         <v>401319</v>
@@ -2950,7 +2950,7 @@
         <v>3.66799998283386</v>
       </c>
       <c r="G89" t="n">
-        <v>2.83960437774658</v>
+        <v>2.839604139328</v>
       </c>
       <c r="H89" t="n">
         <v>589749</v>
@@ -2979,7 +2979,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G90" t="n">
-        <v>2.80244469642639</v>
+        <v>2.80244421958923</v>
       </c>
       <c r="H90" t="n">
         <v>352951</v>
@@ -3037,7 +3037,7 @@
         <v>3.69199991226196</v>
       </c>
       <c r="G92" t="n">
-        <v>2.85818362236023</v>
+        <v>2.85818386077881</v>
       </c>
       <c r="H92" t="n">
         <v>520677</v>
@@ -3066,7 +3066,7 @@
         <v>3.68199992179871</v>
       </c>
       <c r="G93" t="n">
-        <v>2.85044240951538</v>
+        <v>2.85044193267822</v>
       </c>
       <c r="H93" t="n">
         <v>591196</v>
@@ -3095,7 +3095,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87056994438171</v>
+        <v>2.87057018280029</v>
       </c>
       <c r="H94" t="n">
         <v>882620</v>
@@ -3124,7 +3124,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>2.87985968589783</v>
+        <v>2.87986016273499</v>
       </c>
       <c r="H95" t="n">
         <v>502468</v>
@@ -3153,7 +3153,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G96" t="n">
-        <v>2.9170196056366</v>
+        <v>2.91701936721802</v>
       </c>
       <c r="H96" t="n">
         <v>1488002</v>
@@ -3269,7 +3269,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G100" t="n">
-        <v>2.87240815162659</v>
+        <v>2.87240839004517</v>
       </c>
       <c r="H100" t="n">
         <v>2157318</v>
@@ -3298,7 +3298,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G101" t="n">
-        <v>2.48107171058655</v>
+        <v>2.48107218742371</v>
       </c>
       <c r="H101" t="n">
         <v>14577083</v>
@@ -3327,7 +3327,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G102" t="n">
-        <v>2.49516010284424</v>
+        <v>2.49515962600708</v>
       </c>
       <c r="H102" t="n">
         <v>6755386</v>
@@ -3385,7 +3385,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G104" t="n">
-        <v>2.47324514389038</v>
+        <v>2.4732449054718</v>
       </c>
       <c r="H104" t="n">
         <v>4700172</v>
@@ -3414,7 +3414,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G105" t="n">
-        <v>2.46854901313782</v>
+        <v>2.46854877471924</v>
       </c>
       <c r="H105" t="n">
         <v>2374462</v>
@@ -3501,7 +3501,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G108" t="n">
-        <v>2.38715076446533</v>
+        <v>2.38715124130249</v>
       </c>
       <c r="H108" t="n">
         <v>1816564</v>
@@ -3559,7 +3559,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G110" t="n">
-        <v>2.40750026702881</v>
+        <v>2.40750050544739</v>
       </c>
       <c r="H110" t="n">
         <v>3042621</v>
@@ -3617,7 +3617,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G112" t="n">
-        <v>2.44663405418396</v>
+        <v>2.44663429260254</v>
       </c>
       <c r="H112" t="n">
         <v>2559071</v>
@@ -3646,7 +3646,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G113" t="n">
-        <v>2.41219663619995</v>
+        <v>2.41219615936279</v>
       </c>
       <c r="H113" t="n">
         <v>3288781</v>
@@ -3675,7 +3675,7 @@
         <v>3.00600004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>2.35271310806274</v>
+        <v>2.3527135848999</v>
       </c>
       <c r="H114" t="n">
         <v>1983083</v>
@@ -3704,7 +3704,7 @@
         <v>2.87400007247925</v>
       </c>
       <c r="G115" t="n">
-        <v>2.24940085411072</v>
+        <v>2.24940061569214</v>
       </c>
       <c r="H115" t="n">
         <v>2114026</v>
@@ -3733,7 +3733,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G116" t="n">
-        <v>2.18052554130554</v>
+        <v>2.18052530288696</v>
       </c>
       <c r="H116" t="n">
         <v>1635751</v>
@@ -3762,7 +3762,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G117" t="n">
-        <v>2.11634635925293</v>
+        <v>2.11634659767151</v>
       </c>
       <c r="H117" t="n">
         <v>2151270</v>
@@ -3791,7 +3791,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G118" t="n">
-        <v>2.05060195922852</v>
+        <v>2.05060172080994</v>
       </c>
       <c r="H118" t="n">
         <v>2040356</v>
@@ -3820,7 +3820,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>2.14452266693115</v>
+        <v>2.14452219009399</v>
       </c>
       <c r="H119" t="n">
         <v>3285866</v>
@@ -3849,7 +3849,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G120" t="n">
-        <v>2.22748565673828</v>
+        <v>2.22748589515686</v>
       </c>
       <c r="H120" t="n">
         <v>2220357</v>
@@ -3878,7 +3878,7 @@
         <v>2.81800007820129</v>
       </c>
       <c r="G121" t="n">
-        <v>2.20557141304016</v>
+        <v>2.205570936203</v>
       </c>
       <c r="H121" t="n">
         <v>1243898</v>
@@ -3907,7 +3907,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G122" t="n">
-        <v>2.21026682853699</v>
+        <v>2.21026706695557</v>
       </c>
       <c r="H122" t="n">
         <v>1579649</v>
@@ -3936,7 +3936,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G123" t="n">
-        <v>2.28696894645691</v>
+        <v>2.28696870803833</v>
       </c>
       <c r="H123" t="n">
         <v>1894721</v>
@@ -3965,7 +3965,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G124" t="n">
-        <v>2.00990271568298</v>
+        <v>2.00990295410156</v>
       </c>
       <c r="H124" t="n">
         <v>2255357</v>
@@ -4023,7 +4023,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G126" t="n">
-        <v>1.93946242332458</v>
+        <v>1.9394623041153</v>
       </c>
       <c r="H126" t="n">
         <v>1598076</v>
@@ -4052,7 +4052,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G127" t="n">
-        <v>1.97390007972717</v>
+        <v>1.97389984130859</v>
       </c>
       <c r="H127" t="n">
         <v>2900139</v>
@@ -4081,7 +4081,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G128" t="n">
-        <v>1.9864227771759</v>
+        <v>1.98642265796661</v>
       </c>
       <c r="H128" t="n">
         <v>1698763</v>
@@ -4168,7 +4168,7 @@
         <v>2.67199993133545</v>
       </c>
       <c r="G131" t="n">
-        <v>2.09130072593689</v>
+        <v>2.09130048751831</v>
       </c>
       <c r="H131" t="n">
         <v>2319336</v>
@@ -4197,7 +4197,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G132" t="n">
-        <v>2.00364136695862</v>
+        <v>2.0036416053772</v>
       </c>
       <c r="H132" t="n">
         <v>3889902</v>
@@ -4226,7 +4226,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G133" t="n">
-        <v>2.00990271568298</v>
+        <v>2.00990295410156</v>
       </c>
       <c r="H133" t="n">
         <v>2375724</v>
@@ -4255,7 +4255,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G134" t="n">
-        <v>2.11321544647217</v>
+        <v>2.11321568489075</v>
       </c>
       <c r="H134" t="n">
         <v>2706963</v>
@@ -4284,7 +4284,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G135" t="n">
-        <v>2.17582941055298</v>
+        <v>2.17582964897156</v>
       </c>
       <c r="H135" t="n">
         <v>2019536</v>
@@ -4342,7 +4342,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G137" t="n">
-        <v>2.16487169265747</v>
+        <v>2.16487216949463</v>
       </c>
       <c r="H137" t="n">
         <v>746737</v>
@@ -4371,7 +4371,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G138" t="n">
-        <v>2.21026682853699</v>
+        <v>2.21026706695557</v>
       </c>
       <c r="H138" t="n">
         <v>738553</v>
@@ -4429,7 +4429,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G140" t="n">
-        <v>2.18991780281067</v>
+        <v>2.18991756439209</v>
       </c>
       <c r="H140" t="n">
         <v>492382</v>
@@ -4458,7 +4458,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G141" t="n">
-        <v>2.17426443099976</v>
+        <v>2.17426419258118</v>
       </c>
       <c r="H141" t="n">
         <v>1357980</v>
@@ -4516,7 +4516,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16800260543823</v>
+        <v>2.16800236701965</v>
       </c>
       <c r="H143" t="n">
         <v>1335820</v>
@@ -4545,7 +4545,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G144" t="n">
-        <v>2.11478066444397</v>
+        <v>2.11478090286255</v>
       </c>
       <c r="H144" t="n">
         <v>1356729</v>
@@ -4574,7 +4574,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G145" t="n">
-        <v>2.14765310287476</v>
+        <v>2.14765334129333</v>
       </c>
       <c r="H145" t="n">
         <v>979578</v>
@@ -4632,7 +4632,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G147" t="n">
-        <v>2.20400595664978</v>
+        <v>2.2040057182312</v>
       </c>
       <c r="H147" t="n">
         <v>1296535</v>
@@ -4661,7 +4661,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G148" t="n">
-        <v>2.07564759254456</v>
+        <v>2.07564735412598</v>
       </c>
       <c r="H148" t="n">
         <v>6229742</v>
@@ -4690,7 +4690,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G149" t="n">
-        <v>2.11791181564331</v>
+        <v>2.11791205406189</v>
       </c>
       <c r="H149" t="n">
         <v>3166446</v>
@@ -4748,7 +4748,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G151" t="n">
-        <v>1.97859597206116</v>
+        <v>1.97859621047974</v>
       </c>
       <c r="H151" t="n">
         <v>1640032</v>
@@ -4777,7 +4777,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G152" t="n">
-        <v>1.94885432720184</v>
+        <v>1.94885456562042</v>
       </c>
       <c r="H152" t="n">
         <v>1298678</v>
@@ -4806,7 +4806,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>1.94102764129639</v>
+        <v>1.94102799892426</v>
       </c>
       <c r="H153" t="n">
         <v>1093413</v>
@@ -4835,7 +4835,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G154" t="n">
-        <v>1.96137726306915</v>
+        <v>1.96137690544128</v>
       </c>
       <c r="H154" t="n">
         <v>876363</v>
@@ -4893,7 +4893,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G156" t="n">
-        <v>2.00207591056824</v>
+        <v>2.00207614898682</v>
       </c>
       <c r="H156" t="n">
         <v>1568347</v>
@@ -4951,7 +4951,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G158" t="n">
-        <v>2.10538911819458</v>
+        <v>2.10538864135742</v>
       </c>
       <c r="H158" t="n">
         <v>3572397</v>
@@ -5009,7 +5009,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G160" t="n">
-        <v>2.08347415924072</v>
+        <v>2.0834743976593</v>
       </c>
       <c r="H160" t="n">
         <v>1937826</v>
@@ -5038,7 +5038,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G161" t="n">
-        <v>2.05216717720032</v>
+        <v>2.05216693878174</v>
       </c>
       <c r="H161" t="n">
         <v>1296754</v>
@@ -5067,7 +5067,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G162" t="n">
-        <v>2.07721281051636</v>
+        <v>2.07721257209778</v>
       </c>
       <c r="H162" t="n">
         <v>1353910</v>
@@ -5096,7 +5096,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>2.05060195922852</v>
+        <v>2.05060172080994</v>
       </c>
       <c r="H163" t="n">
         <v>982101</v>
@@ -5125,7 +5125,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>2.0584282875061</v>
+        <v>2.05842876434326</v>
       </c>
       <c r="H164" t="n">
         <v>1061581</v>
@@ -5183,7 +5183,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G166" t="n">
-        <v>2.11321544647217</v>
+        <v>2.11321568489075</v>
       </c>
       <c r="H166" t="n">
         <v>813589</v>
@@ -5212,7 +5212,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G167" t="n">
-        <v>2.07408237457275</v>
+        <v>2.0740818977356</v>
       </c>
       <c r="H167" t="n">
         <v>749117</v>
@@ -5270,7 +5270,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G169" t="n">
-        <v>2.11947703361511</v>
+        <v>2.11947727203369</v>
       </c>
       <c r="H169" t="n">
         <v>499989</v>
@@ -5328,7 +5328,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G171" t="n">
-        <v>2.15704560279846</v>
+        <v>2.1570451259613</v>
       </c>
       <c r="H171" t="n">
         <v>898895</v>
@@ -5357,7 +5357,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>2.13669610023499</v>
+        <v>2.13669562339783</v>
       </c>
       <c r="H172" t="n">
         <v>1131229</v>
@@ -5386,7 +5386,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G173" t="n">
-        <v>2.16017603874207</v>
+        <v>2.16017627716064</v>
       </c>
       <c r="H173" t="n">
         <v>498741</v>
@@ -5415,7 +5415,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G174" t="n">
-        <v>2.14452266693115</v>
+        <v>2.14452219009399</v>
       </c>
       <c r="H174" t="n">
         <v>280821</v>
@@ -5473,7 +5473,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G176" t="n">
-        <v>2.17582941055298</v>
+        <v>2.17582964897156</v>
       </c>
       <c r="H176" t="n">
         <v>876827</v>
@@ -5502,7 +5502,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>2.14765310287476</v>
+        <v>2.14765334129333</v>
       </c>
       <c r="H177" t="n">
         <v>959389</v>
@@ -5618,7 +5618,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G181" t="n">
-        <v>2.00207591056824</v>
+        <v>2.00207614898682</v>
       </c>
       <c r="H181" t="n">
         <v>923059</v>
@@ -5647,7 +5647,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G182" t="n">
-        <v>1.98955321311951</v>
+        <v>1.98955357074738</v>
       </c>
       <c r="H182" t="n">
         <v>1468702</v>
@@ -5705,7 +5705,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G184" t="n">
-        <v>1.99424970149994</v>
+        <v>1.99424946308136</v>
       </c>
       <c r="H184" t="n">
         <v>1176506</v>
@@ -5792,7 +5792,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>1.98798799514771</v>
+        <v>1.98798811435699</v>
       </c>
       <c r="H187" t="n">
         <v>900283</v>
@@ -5821,7 +5821,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G188" t="n">
-        <v>1.97859597206116</v>
+        <v>1.97859621047974</v>
       </c>
       <c r="H188" t="n">
         <v>375877</v>
@@ -5850,7 +5850,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G189" t="n">
-        <v>1.9175478219986</v>
+        <v>1.91754758358002</v>
       </c>
       <c r="H189" t="n">
         <v>786779</v>
@@ -5937,7 +5937,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G192" t="n">
-        <v>1.99268400669098</v>
+        <v>1.99268424510956</v>
       </c>
       <c r="H192" t="n">
         <v>1798626</v>
@@ -5966,7 +5966,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G193" t="n">
-        <v>2.0067720413208</v>
+        <v>2.00677227973938</v>
       </c>
       <c r="H193" t="n">
         <v>1366609</v>
@@ -5995,7 +5995,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G194" t="n">
-        <v>1.95355045795441</v>
+        <v>1.95355069637299</v>
       </c>
       <c r="H194" t="n">
         <v>944804</v>
@@ -6024,7 +6024,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G195" t="n">
-        <v>1.94885432720184</v>
+        <v>1.94885456562042</v>
       </c>
       <c r="H195" t="n">
         <v>460629</v>
@@ -6053,7 +6053,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G196" t="n">
-        <v>2.02868723869324</v>
+        <v>2.02868700027466</v>
       </c>
       <c r="H196" t="n">
         <v>1217923</v>
@@ -6082,7 +6082,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G197" t="n">
-        <v>2.02242588996887</v>
+        <v>2.02242565155029</v>
       </c>
       <c r="H197" t="n">
         <v>682441</v>
@@ -6285,7 +6285,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G204" t="n">
-        <v>1.96450769901276</v>
+        <v>1.96450805664062</v>
       </c>
       <c r="H204" t="n">
         <v>817690</v>
@@ -6314,7 +6314,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G205" t="n">
-        <v>2.00207591056824</v>
+        <v>2.00207614898682</v>
       </c>
       <c r="H205" t="n">
         <v>1166619</v>
@@ -6343,7 +6343,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G206" t="n">
-        <v>2.07721281051636</v>
+        <v>2.07721257209778</v>
       </c>
       <c r="H206" t="n">
         <v>1910349</v>
@@ -6372,7 +6372,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G207" t="n">
-        <v>2.08973550796509</v>
+        <v>2.08973574638367</v>
       </c>
       <c r="H207" t="n">
         <v>859886</v>
@@ -6401,7 +6401,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G208" t="n">
-        <v>2.0819091796875</v>
+        <v>2.08190894126892</v>
       </c>
       <c r="H208" t="n">
         <v>1477868</v>
@@ -6430,7 +6430,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G209" t="n">
-        <v>2.1038236618042</v>
+        <v>2.10382390022278</v>
       </c>
       <c r="H209" t="n">
         <v>987784</v>
@@ -6488,7 +6488,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>2.08973550796509</v>
+        <v>2.08973574638367</v>
       </c>
       <c r="H211" t="n">
         <v>544659</v>
@@ -6546,7 +6546,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G213" t="n">
-        <v>1.97859597206116</v>
+        <v>1.97859621047974</v>
       </c>
       <c r="H213" t="n">
         <v>1439805</v>
@@ -6575,7 +6575,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G214" t="n">
-        <v>1.98798799514771</v>
+        <v>1.98798811435699</v>
       </c>
       <c r="H214" t="n">
         <v>951415</v>
@@ -6604,7 +6604,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G215" t="n">
-        <v>1.96137726306915</v>
+        <v>1.96137690544128</v>
       </c>
       <c r="H215" t="n">
         <v>535801</v>
@@ -6633,7 +6633,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G216" t="n">
-        <v>1.93163561820984</v>
+        <v>1.93163585662842</v>
       </c>
       <c r="H216" t="n">
         <v>1190452</v>
@@ -6720,7 +6720,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G219" t="n">
-        <v>1.93163561820984</v>
+        <v>1.93163585662842</v>
       </c>
       <c r="H219" t="n">
         <v>511910</v>
@@ -6778,7 +6778,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>2.0584282875061</v>
+        <v>2.05842876434326</v>
       </c>
       <c r="H221" t="n">
         <v>7385474</v>
@@ -6836,7 +6836,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G223" t="n">
-        <v>2.03025269508362</v>
+        <v>2.03025245666504</v>
       </c>
       <c r="H223" t="n">
         <v>2200910</v>
@@ -6894,7 +6894,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G225" t="n">
-        <v>2.14765310287476</v>
+        <v>2.14765334129333</v>
       </c>
       <c r="H225" t="n">
         <v>2264389</v>
@@ -6981,7 +6981,7 @@
         <v>2.57200002670288</v>
       </c>
       <c r="G228" t="n">
-        <v>2.01303362846375</v>
+        <v>2.01303386688232</v>
       </c>
       <c r="H228" t="n">
         <v>1577781</v>
@@ -7126,7 +7126,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G233" t="n">
-        <v>1.98955321311951</v>
+        <v>1.98955357074738</v>
       </c>
       <c r="H233" t="n">
         <v>602925</v>
@@ -7213,7 +7213,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G236" t="n">
-        <v>2.03807926177979</v>
+        <v>2.03807902336121</v>
       </c>
       <c r="H236" t="n">
         <v>1447942</v>
@@ -7242,7 +7242,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G237" t="n">
-        <v>2.03807926177979</v>
+        <v>2.03807902336121</v>
       </c>
       <c r="H237" t="n">
         <v>614516</v>
@@ -7271,7 +7271,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G238" t="n">
-        <v>2.04434037208557</v>
+        <v>2.04434061050415</v>
       </c>
       <c r="H238" t="n">
         <v>1826358</v>
@@ -7387,7 +7387,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G242" t="n">
-        <v>2.26192355155945</v>
+        <v>2.26192331314087</v>
       </c>
       <c r="H242" t="n">
         <v>2116747</v>
@@ -7416,7 +7416,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G243" t="n">
-        <v>2.24626970291138</v>
+        <v>2.24627017974854</v>
       </c>
       <c r="H243" t="n">
         <v>2334527</v>
@@ -7445,7 +7445,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G244" t="n">
-        <v>2.26192355155945</v>
+        <v>2.26192331314087</v>
       </c>
       <c r="H244" t="n">
         <v>1572345</v>
@@ -7474,7 +7474,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G245" t="n">
-        <v>2.30105686187744</v>
+        <v>2.30105710029602</v>
       </c>
       <c r="H245" t="n">
         <v>2391677</v>
@@ -7532,7 +7532,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G247" t="n">
-        <v>2.37775897979736</v>
+        <v>2.37775874137878</v>
       </c>
       <c r="H247" t="n">
         <v>1476950</v>
@@ -7706,7 +7706,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G253" t="n">
-        <v>2.39028143882751</v>
+        <v>2.39028191566467</v>
       </c>
       <c r="H253" t="n">
         <v>1171723</v>
@@ -7793,7 +7793,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G256" t="n">
-        <v>2.32923316955566</v>
+        <v>2.32923340797424</v>
       </c>
       <c r="H256" t="n">
         <v>542985</v>
@@ -7851,7 +7851,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G258" t="n">
-        <v>2.43098068237305</v>
+        <v>2.43098092079163</v>
       </c>
       <c r="H258" t="n">
         <v>1363312</v>
@@ -7967,7 +7967,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G262" t="n">
-        <v>2.49359464645386</v>
+        <v>2.49359440803528</v>
       </c>
       <c r="H262" t="n">
         <v>455999</v>
@@ -8083,7 +8083,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G266" t="n">
-        <v>2.47011423110962</v>
+        <v>2.4701144695282</v>
       </c>
       <c r="H266" t="n">
         <v>903243</v>
@@ -8112,7 +8112,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G267" t="n">
-        <v>2.44976496696472</v>
+        <v>2.44976472854614</v>
       </c>
       <c r="H267" t="n">
         <v>771245</v>
@@ -8286,7 +8286,7 @@
         <v>3.0460000038147</v>
       </c>
       <c r="G273" t="n">
-        <v>2.38402032852173</v>
+        <v>2.38402056694031</v>
       </c>
       <c r="H273" t="n">
         <v>1065395</v>
@@ -8344,7 +8344,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G275" t="n">
-        <v>2.42628479003906</v>
+        <v>2.42628455162048</v>
       </c>
       <c r="H275" t="n">
         <v>900916</v>
@@ -8402,7 +8402,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G277" t="n">
-        <v>2.33862543106079</v>
+        <v>2.33862519264221</v>
       </c>
       <c r="H277" t="n">
         <v>900267</v>
@@ -8431,7 +8431,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G278" t="n">
-        <v>2.30888414382935</v>
+        <v>2.30888390541077</v>
       </c>
       <c r="H278" t="n">
         <v>1234287</v>
@@ -8460,7 +8460,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G279" t="n">
-        <v>2.25566244125366</v>
+        <v>2.25566220283508</v>
       </c>
       <c r="H279" t="n">
         <v>863160</v>
@@ -8518,7 +8518,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G281" t="n">
-        <v>2.30105686187744</v>
+        <v>2.30105710029602</v>
       </c>
       <c r="H281" t="n">
         <v>765752</v>
@@ -8547,7 +8547,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G282" t="n">
-        <v>2.27757668495178</v>
+        <v>2.27757716178894</v>
       </c>
       <c r="H282" t="n">
         <v>900313</v>
@@ -8605,7 +8605,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G284" t="n">
-        <v>2.24626970291138</v>
+        <v>2.24627017974854</v>
       </c>
       <c r="H284" t="n">
         <v>930384</v>
@@ -8692,7 +8692,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G287" t="n">
-        <v>2.33862543106079</v>
+        <v>2.33862519264221</v>
       </c>
       <c r="H287" t="n">
         <v>1633765</v>
@@ -8750,7 +8750,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>2.41063141822815</v>
+        <v>2.41063117980957</v>
       </c>
       <c r="H289" t="n">
         <v>1135351</v>
@@ -8808,7 +8808,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G291" t="n">
-        <v>2.40436983108521</v>
+        <v>2.40437006950378</v>
       </c>
       <c r="H291" t="n">
         <v>2490093</v>
@@ -8866,7 +8866,7 @@
         <v>3</v>
       </c>
       <c r="G293" t="n">
-        <v>2.34801721572876</v>
+        <v>2.34801745414734</v>
       </c>
       <c r="H293" t="n">
         <v>865361</v>
@@ -8895,7 +8895,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G294" t="n">
-        <v>2.33862543106079</v>
+        <v>2.33862519264221</v>
       </c>
       <c r="H294" t="n">
         <v>975000</v>
@@ -8953,7 +8953,7 @@
         <v>2.98600006103516</v>
       </c>
       <c r="G296" t="n">
-        <v>2.33706021308899</v>
+        <v>2.33705997467041</v>
       </c>
       <c r="H296" t="n">
         <v>869769</v>
@@ -9040,7 +9040,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G299" t="n">
-        <v>2.48107171058655</v>
+        <v>2.48107218742371</v>
       </c>
       <c r="H299" t="n">
         <v>1238634</v>
@@ -9098,7 +9098,7 @@
         <v>3.25200009346008</v>
       </c>
       <c r="G301" t="n">
-        <v>2.54525113105774</v>
+        <v>2.54525089263916</v>
       </c>
       <c r="H301" t="n">
         <v>1841917</v>
@@ -9127,7 +9127,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G302" t="n">
-        <v>2.53585863113403</v>
+        <v>2.53585839271545</v>
       </c>
       <c r="H302" t="n">
         <v>879229</v>
@@ -9214,7 +9214,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G305" t="n">
-        <v>2.5170750617981</v>
+        <v>2.51707458496094</v>
       </c>
       <c r="H305" t="n">
         <v>842737</v>
@@ -9243,7 +9243,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G306" t="n">
-        <v>2.49359464645386</v>
+        <v>2.49359440803528</v>
       </c>
       <c r="H306" t="n">
         <v>740808</v>
@@ -9272,7 +9272,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G307" t="n">
-        <v>2.49202942848206</v>
+        <v>2.4920289516449</v>
       </c>
       <c r="H307" t="n">
         <v>1006054</v>
@@ -9301,7 +9301,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>2.49672532081604</v>
+        <v>2.49672508239746</v>
       </c>
       <c r="H308" t="n">
         <v>948293</v>
@@ -9388,7 +9388,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G311" t="n">
-        <v>2.5734269618988</v>
+        <v>2.57342672348022</v>
       </c>
       <c r="H311" t="n">
         <v>2285027</v>
@@ -9417,7 +9417,7 @@
         <v>3.17799997329712</v>
       </c>
       <c r="G312" t="n">
-        <v>2.48733305931091</v>
+        <v>2.48733282089233</v>
       </c>
       <c r="H312" t="n">
         <v>2780058</v>
@@ -9446,7 +9446,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G313" t="n">
-        <v>2.46541833877563</v>
+        <v>2.46541857719421</v>
       </c>
       <c r="H313" t="n">
         <v>1680814</v>
@@ -9475,7 +9475,7 @@
         <v>3.13199996948242</v>
       </c>
       <c r="G314" t="n">
-        <v>2.45132994651794</v>
+        <v>2.45133018493652</v>
       </c>
       <c r="H314" t="n">
         <v>1373872</v>
@@ -9504,7 +9504,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G315" t="n">
-        <v>2.44663405418396</v>
+        <v>2.44663429260254</v>
       </c>
       <c r="H315" t="n">
         <v>1339012</v>
@@ -9591,7 +9591,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G318" t="n">
-        <v>2.45446062088013</v>
+        <v>2.45446085929871</v>
       </c>
       <c r="H318" t="n">
         <v>1180996</v>
@@ -9620,7 +9620,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G319" t="n">
-        <v>2.49359464645386</v>
+        <v>2.49359440803528</v>
       </c>
       <c r="H319" t="n">
         <v>961125</v>
@@ -9649,7 +9649,7 @@
         <v>3.10400009155273</v>
       </c>
       <c r="G320" t="n">
-        <v>2.42941522598267</v>
+        <v>2.42941546440125</v>
       </c>
       <c r="H320" t="n">
         <v>1672455</v>
@@ -9765,7 +9765,7 @@
         <v>3.03600001335144</v>
       </c>
       <c r="G324" t="n">
-        <v>2.37619352340698</v>
+        <v>2.37619376182556</v>
       </c>
       <c r="H324" t="n">
         <v>1263595</v>
@@ -9794,7 +9794,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G325" t="n">
-        <v>2.41063141822815</v>
+        <v>2.41063117980957</v>
       </c>
       <c r="H325" t="n">
         <v>1145350</v>
@@ -9852,7 +9852,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G327" t="n">
-        <v>2.46541833877563</v>
+        <v>2.46541857719421</v>
       </c>
       <c r="H327" t="n">
         <v>1448459</v>
@@ -9881,7 +9881,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G328" t="n">
-        <v>2.47324514389038</v>
+        <v>2.4732449054718</v>
       </c>
       <c r="H328" t="n">
         <v>633759</v>
@@ -9910,7 +9910,7 @@
         <v>3.10800004005432</v>
       </c>
       <c r="G329" t="n">
-        <v>2.43254590034485</v>
+        <v>2.43254637718201</v>
       </c>
       <c r="H329" t="n">
         <v>922372</v>
@@ -9939,7 +9939,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G330" t="n">
-        <v>2.39028143882751</v>
+        <v>2.39028191566467</v>
       </c>
       <c r="H330" t="n">
         <v>977417</v>
@@ -9968,7 +9968,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G331" t="n">
-        <v>2.36836719512939</v>
+        <v>2.36836671829224</v>
       </c>
       <c r="H331" t="n">
         <v>1134109</v>
@@ -9997,7 +9997,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G332" t="n">
-        <v>2.29792618751526</v>
+        <v>2.29792642593384</v>
       </c>
       <c r="H332" t="n">
         <v>1838891</v>
@@ -10026,7 +10026,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G333" t="n">
-        <v>2.38715076446533</v>
+        <v>2.38715124130249</v>
       </c>
       <c r="H333" t="n">
         <v>1119719</v>
@@ -10055,7 +10055,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G334" t="n">
-        <v>2.41532731056213</v>
+        <v>2.41532707214355</v>
       </c>
       <c r="H334" t="n">
         <v>1143561</v>
@@ -10113,7 +10113,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.42628479003906</v>
+        <v>2.42628455162048</v>
       </c>
       <c r="H336" t="n">
         <v>1305495</v>
@@ -10142,7 +10142,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G337" t="n">
-        <v>2.40750026702881</v>
+        <v>2.40750050544739</v>
       </c>
       <c r="H337" t="n">
         <v>4223005</v>
@@ -10171,7 +10171,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>2.44976496696472</v>
+        <v>2.44976472854614</v>
       </c>
       <c r="H338" t="n">
         <v>2519037</v>
@@ -10345,7 +10345,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G344" t="n">
-        <v>2.55151200294495</v>
+        <v>2.55151224136353</v>
       </c>
       <c r="H344" t="n">
         <v>1479263</v>
@@ -10374,7 +10374,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G345" t="n">
-        <v>2.53742408752441</v>
+        <v>2.53742432594299</v>
       </c>
       <c r="H345" t="n">
         <v>1106003</v>
@@ -10403,7 +10403,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>2.6219527721405</v>
+        <v>2.62195301055908</v>
       </c>
       <c r="H346" t="n">
         <v>3151258</v>
@@ -10432,7 +10432,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G347" t="n">
-        <v>2.65169405937195</v>
+        <v>2.65169429779053</v>
       </c>
       <c r="H347" t="n">
         <v>1207699</v>
@@ -10461,7 +10461,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G348" t="n">
-        <v>2.6219527721405</v>
+        <v>2.62195301055908</v>
       </c>
       <c r="H348" t="n">
         <v>2137829</v>
@@ -10577,7 +10577,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>2.53585863113403</v>
+        <v>2.53585839271545</v>
       </c>
       <c r="H352" t="n">
         <v>2123505</v>
@@ -10606,7 +10606,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G353" t="n">
-        <v>2.43098068237305</v>
+        <v>2.43098092079163</v>
       </c>
       <c r="H353" t="n">
         <v>3812104</v>
@@ -10635,7 +10635,7 @@
         <v>3.14599990844727</v>
       </c>
       <c r="G354" t="n">
-        <v>2.46228790283203</v>
+        <v>2.46228766441345</v>
       </c>
       <c r="H354" t="n">
         <v>1374536</v>
@@ -10664,7 +10664,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G355" t="n">
-        <v>2.5204017162323</v>
+        <v>2.52040147781372</v>
       </c>
       <c r="H355" t="n">
         <v>818695</v>
@@ -10693,7 +10693,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G356" t="n">
-        <v>2.53791570663452</v>
+        <v>2.53791522979736</v>
       </c>
       <c r="H356" t="n">
         <v>987101</v>
@@ -10751,7 +10751,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>2.55542945861816</v>
+        <v>2.55542898178101</v>
       </c>
       <c r="H358" t="n">
         <v>654062</v>
@@ -10838,7 +10838,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G361" t="n">
-        <v>2.52358603477478</v>
+        <v>2.52358627319336</v>
       </c>
       <c r="H361" t="n">
         <v>1301649</v>
@@ -10896,7 +10896,7 @@
         <v>3.19400000572205</v>
       </c>
       <c r="G363" t="n">
-        <v>2.54269218444824</v>
+        <v>2.54269194602966</v>
       </c>
       <c r="H363" t="n">
         <v>1225998</v>
@@ -10954,7 +10954,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G365" t="n">
-        <v>2.56816673278809</v>
+        <v>2.56816697120667</v>
       </c>
       <c r="H365" t="n">
         <v>1146192</v>
@@ -11012,7 +11012,7 @@
         <v>3.07599997520447</v>
       </c>
       <c r="G367" t="n">
-        <v>2.44875383377075</v>
+        <v>2.44875431060791</v>
       </c>
       <c r="H367" t="n">
         <v>1658630</v>
@@ -11041,7 +11041,7 @@
         <v>3.08800005912781</v>
       </c>
       <c r="G368" t="n">
-        <v>2.45830750465393</v>
+        <v>2.45830702781677</v>
       </c>
       <c r="H368" t="n">
         <v>2334871</v>
@@ -11099,7 +11099,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>2.42009520530701</v>
+        <v>2.42009496688843</v>
       </c>
       <c r="H370" t="n">
         <v>1292806</v>
@@ -11128,7 +11128,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G371" t="n">
-        <v>2.49651885032654</v>
+        <v>2.49651908874512</v>
       </c>
       <c r="H371" t="n">
         <v>1521213</v>
@@ -11157,7 +11157,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G372" t="n">
-        <v>2.49651885032654</v>
+        <v>2.49651908874512</v>
       </c>
       <c r="H372" t="n">
         <v>623912</v>
@@ -11215,7 +11215,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G374" t="n">
-        <v>2.46786022186279</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H374" t="n">
         <v>2480349</v>
@@ -11244,7 +11244,7 @@
         <v>3.05399990081787</v>
       </c>
       <c r="G375" t="n">
-        <v>2.43124008178711</v>
+        <v>2.43124032020569</v>
       </c>
       <c r="H375" t="n">
         <v>894485</v>
@@ -11273,7 +11273,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G376" t="n">
-        <v>2.41531848907471</v>
+        <v>2.41531872749329</v>
       </c>
       <c r="H376" t="n">
         <v>713673</v>
@@ -11302,7 +11302,7 @@
         <v>3.03399991989136</v>
       </c>
       <c r="G377" t="n">
-        <v>2.41531848907471</v>
+        <v>2.41531872749329</v>
       </c>
       <c r="H377" t="n">
         <v>548721</v>
@@ -11389,7 +11389,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G380" t="n">
-        <v>2.44397735595703</v>
+        <v>2.44397759437561</v>
       </c>
       <c r="H380" t="n">
         <v>696668</v>
@@ -11418,7 +11418,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G381" t="n">
-        <v>2.49811148643494</v>
+        <v>2.49811124801636</v>
       </c>
       <c r="H381" t="n">
         <v>1455624</v>
@@ -11447,7 +11447,7 @@
         <v>3.12400007247925</v>
       </c>
       <c r="G382" t="n">
-        <v>2.48696613311768</v>
+        <v>2.48696637153625</v>
       </c>
       <c r="H382" t="n">
         <v>1591740</v>
@@ -11476,7 +11476,7 @@
         <v>3.01200008392334</v>
       </c>
       <c r="G383" t="n">
-        <v>2.39780449867249</v>
+        <v>2.39780497550964</v>
       </c>
       <c r="H383" t="n">
         <v>1899296</v>
@@ -11534,7 +11534,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.42805576324463</v>
+        <v>2.42805624008179</v>
       </c>
       <c r="H385" t="n">
         <v>929588</v>
@@ -11563,7 +11563,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G386" t="n">
-        <v>2.38984417915344</v>
+        <v>2.38984394073486</v>
       </c>
       <c r="H386" t="n">
         <v>1146093</v>
@@ -11650,7 +11650,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G389" t="n">
-        <v>2.42646384239197</v>
+        <v>2.42646360397339</v>
       </c>
       <c r="H389" t="n">
         <v>1267851</v>
@@ -11708,7 +11708,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G391" t="n">
-        <v>2.38188314437866</v>
+        <v>2.38188338279724</v>
       </c>
       <c r="H391" t="n">
         <v>1358951</v>
@@ -11737,7 +11737,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G392" t="n">
-        <v>2.44716191291809</v>
+        <v>2.44716215133667</v>
       </c>
       <c r="H392" t="n">
         <v>1622777</v>
@@ -11795,7 +11795,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G394" t="n">
-        <v>2.45989942550659</v>
+        <v>2.45989918708801</v>
       </c>
       <c r="H394" t="n">
         <v>617432</v>
@@ -11824,7 +11824,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G395" t="n">
-        <v>2.51084876060486</v>
+        <v>2.51084852218628</v>
       </c>
       <c r="H395" t="n">
         <v>4508418</v>
@@ -11853,7 +11853,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G396" t="n">
-        <v>2.48218965530396</v>
+        <v>2.48218941688538</v>
       </c>
       <c r="H396" t="n">
         <v>847477</v>
@@ -11911,7 +11911,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G398" t="n">
-        <v>2.46149158477783</v>
+        <v>2.46149134635925</v>
       </c>
       <c r="H398" t="n">
         <v>1226827</v>
@@ -11940,7 +11940,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G399" t="n">
-        <v>2.42805576324463</v>
+        <v>2.42805624008179</v>
       </c>
       <c r="H399" t="n">
         <v>1376064</v>
@@ -11969,7 +11969,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G400" t="n">
-        <v>2.42805576324463</v>
+        <v>2.42805624008179</v>
       </c>
       <c r="H400" t="n">
         <v>669595</v>
@@ -12027,7 +12027,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G402" t="n">
-        <v>2.46626830101013</v>
+        <v>2.46626806259155</v>
       </c>
       <c r="H402" t="n">
         <v>623443</v>
@@ -12056,7 +12056,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G403" t="n">
-        <v>2.39621233940125</v>
+        <v>2.39621257781982</v>
       </c>
       <c r="H403" t="n">
         <v>3318841</v>
@@ -12114,7 +12114,7 @@
         <v>2.97199988365173</v>
       </c>
       <c r="G405" t="n">
-        <v>2.3659610748291</v>
+        <v>2.36596131324768</v>
       </c>
       <c r="H405" t="n">
         <v>997374</v>
@@ -12172,7 +12172,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G407" t="n">
-        <v>2.354816198349</v>
+        <v>2.35481643676758</v>
       </c>
       <c r="H407" t="n">
         <v>777560</v>
@@ -12201,7 +12201,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G408" t="n">
-        <v>2.36436939239502</v>
+        <v>2.36436891555786</v>
       </c>
       <c r="H408" t="n">
         <v>484836</v>
@@ -12259,7 +12259,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G410" t="n">
-        <v>2.36436939239502</v>
+        <v>2.36436891555786</v>
       </c>
       <c r="H410" t="n">
         <v>977540</v>
@@ -12317,7 +12317,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G412" t="n">
-        <v>2.31660413742065</v>
+        <v>2.31660437583923</v>
       </c>
       <c r="H412" t="n">
         <v>1233935</v>
@@ -12346,7 +12346,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G413" t="n">
-        <v>2.27679967880249</v>
+        <v>2.27679991722107</v>
       </c>
       <c r="H413" t="n">
         <v>1403718</v>
@@ -12404,7 +12404,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G415" t="n">
-        <v>2.30068278312683</v>
+        <v>2.30068230628967</v>
       </c>
       <c r="H415" t="n">
         <v>613532</v>
@@ -12433,7 +12433,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G416" t="n">
-        <v>2.33571028709412</v>
+        <v>2.33571004867554</v>
       </c>
       <c r="H416" t="n">
         <v>923284</v>
@@ -12462,7 +12462,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G417" t="n">
-        <v>2.33571028709412</v>
+        <v>2.33571004867554</v>
       </c>
       <c r="H417" t="n">
         <v>656989</v>
@@ -12491,7 +12491,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G418" t="n">
-        <v>2.28157639503479</v>
+        <v>2.28157663345337</v>
       </c>
       <c r="H418" t="n">
         <v>1740213</v>
@@ -12549,7 +12549,7 @@
         <v>2.88199996948242</v>
       </c>
       <c r="G420" t="n">
-        <v>2.29431414604187</v>
+        <v>2.29431390762329</v>
       </c>
       <c r="H420" t="n">
         <v>457338</v>
@@ -12578,7 +12578,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G421" t="n">
-        <v>2.33730220794678</v>
+        <v>2.33730244636536</v>
       </c>
       <c r="H421" t="n">
         <v>1265104</v>
@@ -12607,7 +12607,7 @@
         <v>2.93199992179871</v>
       </c>
       <c r="G422" t="n">
-        <v>2.3341178894043</v>
+        <v>2.33411812782288</v>
       </c>
       <c r="H422" t="n">
         <v>683681</v>
@@ -12636,7 +12636,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G423" t="n">
-        <v>2.34844779968262</v>
+        <v>2.34844732284546</v>
       </c>
       <c r="H423" t="n">
         <v>685400</v>
@@ -12665,7 +12665,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G424" t="n">
-        <v>2.33252596855164</v>
+        <v>2.33252573013306</v>
       </c>
       <c r="H424" t="n">
         <v>735919</v>
@@ -12694,7 +12694,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G425" t="n">
-        <v>2.30864334106445</v>
+        <v>2.30864357948303</v>
       </c>
       <c r="H425" t="n">
         <v>805855</v>
@@ -12723,7 +12723,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G426" t="n">
-        <v>2.34844779968262</v>
+        <v>2.34844732284546</v>
       </c>
       <c r="H426" t="n">
         <v>723093</v>
@@ -12752,7 +12752,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G427" t="n">
-        <v>2.34844779968262</v>
+        <v>2.34844732284546</v>
       </c>
       <c r="H427" t="n">
         <v>1614230</v>
@@ -12810,7 +12810,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G429" t="n">
-        <v>2.40258145332336</v>
+        <v>2.40258097648621</v>
       </c>
       <c r="H429" t="n">
         <v>1162563</v>
@@ -12868,7 +12868,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G431" t="n">
-        <v>2.43920087814331</v>
+        <v>2.43920135498047</v>
       </c>
       <c r="H431" t="n">
         <v>1993777</v>
@@ -12897,7 +12897,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G432" t="n">
-        <v>2.46786022186279</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H432" t="n">
         <v>1295449</v>
@@ -12926,7 +12926,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G433" t="n">
-        <v>2.52677059173584</v>
+        <v>2.52677035331726</v>
       </c>
       <c r="H433" t="n">
         <v>2579783</v>
@@ -12955,7 +12955,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G434" t="n">
-        <v>2.57771992683411</v>
+        <v>2.57771968841553</v>
       </c>
       <c r="H434" t="n">
         <v>2373534</v>
@@ -13042,7 +13042,7 @@
         <v>3.26200008392334</v>
       </c>
       <c r="G437" t="n">
-        <v>2.59682583808899</v>
+        <v>2.59682559967041</v>
       </c>
       <c r="H437" t="n">
         <v>1443378</v>
@@ -13129,7 +13129,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G440" t="n">
-        <v>2.58568072319031</v>
+        <v>2.58568024635315</v>
       </c>
       <c r="H440" t="n">
         <v>421765</v>
@@ -13158,7 +13158,7 @@
         <v>3.24799990653992</v>
       </c>
       <c r="G441" t="n">
-        <v>2.58568072319031</v>
+        <v>2.58568024635315</v>
       </c>
       <c r="H441" t="n">
         <v>629599</v>
@@ -13216,7 +13216,7 @@
         <v>3.22199988365173</v>
       </c>
       <c r="G443" t="n">
-        <v>2.56498217582703</v>
+        <v>2.56498265266418</v>
       </c>
       <c r="H443" t="n">
         <v>512784</v>
@@ -13245,7 +13245,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G444" t="n">
-        <v>2.60000991821289</v>
+        <v>2.60001015663147</v>
       </c>
       <c r="H444" t="n">
         <v>722959</v>
@@ -13274,7 +13274,7 @@
         <v>3.28399991989136</v>
       </c>
       <c r="G445" t="n">
-        <v>2.61433959007263</v>
+        <v>2.61433935165405</v>
       </c>
       <c r="H445" t="n">
         <v>607795</v>
@@ -13303,7 +13303,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G446" t="n">
-        <v>2.60000991821289</v>
+        <v>2.60001015663147</v>
       </c>
       <c r="H446" t="n">
         <v>507708</v>
@@ -13332,7 +13332,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>2.61911582946777</v>
+        <v>2.61911630630493</v>
       </c>
       <c r="H447" t="n">
         <v>569921</v>
@@ -13361,7 +13361,7 @@
         <v>3.33599996566772</v>
       </c>
       <c r="G448" t="n">
-        <v>2.65573620796204</v>
+        <v>2.65573596954346</v>
       </c>
       <c r="H448" t="n">
         <v>958763</v>
@@ -13390,7 +13390,7 @@
         <v>3.28200006484985</v>
       </c>
       <c r="G449" t="n">
-        <v>2.61274766921997</v>
+        <v>2.61274719238281</v>
       </c>
       <c r="H449" t="n">
         <v>1008192</v>
@@ -13419,7 +13419,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G450" t="n">
-        <v>2.60637831687927</v>
+        <v>2.60637855529785</v>
       </c>
       <c r="H450" t="n">
         <v>654933</v>
@@ -13477,7 +13477,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G452" t="n">
-        <v>2.64459085464478</v>
+        <v>2.64459037780762</v>
       </c>
       <c r="H452" t="n">
         <v>818061</v>
@@ -13651,7 +13651,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G458" t="n">
-        <v>2.70509338378906</v>
+        <v>2.70509314537048</v>
       </c>
       <c r="H458" t="n">
         <v>1265417</v>
@@ -13680,7 +13680,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G459" t="n">
-        <v>2.73852896690369</v>
+        <v>2.73852849006653</v>
       </c>
       <c r="H459" t="n">
         <v>794697</v>
@@ -13738,7 +13738,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G461" t="n">
-        <v>2.74012064933777</v>
+        <v>2.74012088775635</v>
       </c>
       <c r="H461" t="n">
         <v>4070428</v>
@@ -13767,7 +13767,7 @@
         <v>3.39800000190735</v>
       </c>
       <c r="G462" t="n">
-        <v>2.70509338378906</v>
+        <v>2.70509314537048</v>
       </c>
       <c r="H462" t="n">
         <v>996863</v>
@@ -13796,7 +13796,7 @@
         <v>3.41799998283386</v>
       </c>
       <c r="G463" t="n">
-        <v>2.72101473808289</v>
+        <v>2.72101497650146</v>
       </c>
       <c r="H463" t="n">
         <v>1178918</v>
@@ -13883,7 +13883,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G466" t="n">
-        <v>2.80221557617188</v>
+        <v>2.8022153377533</v>
       </c>
       <c r="H466" t="n">
         <v>1027608</v>
@@ -14028,7 +14028,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G471" t="n">
-        <v>2.94073390960693</v>
+        <v>2.94073414802551</v>
       </c>
       <c r="H471" t="n">
         <v>2019957</v>
@@ -14144,7 +14144,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>2.93754982948303</v>
+        <v>2.93754959106445</v>
       </c>
       <c r="H475" t="n">
         <v>968072</v>
@@ -14173,7 +14173,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G476" t="n">
-        <v>2.90252208709717</v>
+        <v>2.90252184867859</v>
       </c>
       <c r="H476" t="n">
         <v>1820893</v>
@@ -14231,7 +14231,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G478" t="n">
-        <v>2.81017589569092</v>
+        <v>2.8101761341095</v>
       </c>
       <c r="H478" t="n">
         <v>3456844</v>
@@ -14289,7 +14289,7 @@
         <v>3.29800009727478</v>
       </c>
       <c r="G480" t="n">
-        <v>2.62548470497131</v>
+        <v>2.62548494338989</v>
       </c>
       <c r="H480" t="n">
         <v>2617438</v>
@@ -14376,7 +14376,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G483" t="n">
-        <v>2.49174284934998</v>
+        <v>2.4917426109314</v>
       </c>
       <c r="H483" t="n">
         <v>3697265</v>
@@ -14405,7 +14405,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>2.46786022186279</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H484" t="n">
         <v>2655168</v>
@@ -14434,7 +14434,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G485" t="n">
-        <v>2.46786022186279</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H485" t="n">
         <v>1101568</v>
@@ -14463,7 +14463,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G486" t="n">
-        <v>2.48537421226501</v>
+        <v>2.48537397384644</v>
       </c>
       <c r="H486" t="n">
         <v>1237843</v>
@@ -14492,7 +14492,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G487" t="n">
-        <v>2.45989942550659</v>
+        <v>2.45989918708801</v>
       </c>
       <c r="H487" t="n">
         <v>932298</v>
@@ -14550,7 +14550,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G489" t="n">
-        <v>2.46786022186279</v>
+        <v>2.46785998344421</v>
       </c>
       <c r="H489" t="n">
         <v>2139896</v>
@@ -14608,7 +14608,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G491" t="n">
-        <v>2.44716191291809</v>
+        <v>2.44716215133667</v>
       </c>
       <c r="H491" t="n">
         <v>2154714</v>
@@ -14637,7 +14637,7 @@
         <v>3.07399988174438</v>
       </c>
       <c r="G492" t="n">
-        <v>2.44716191291809</v>
+        <v>2.44716215133667</v>
       </c>
       <c r="H492" t="n">
         <v>1691378</v>
@@ -14666,7 +14666,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G493" t="n">
-        <v>2.46149158477783</v>
+        <v>2.46149134635925</v>
       </c>
       <c r="H493" t="n">
         <v>2679317</v>
@@ -14724,7 +14724,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G495" t="n">
-        <v>2.53632354736328</v>
+        <v>2.5363233089447</v>
       </c>
       <c r="H495" t="n">
         <v>1344034</v>
@@ -14753,7 +14753,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G496" t="n">
-        <v>2.5315465927124</v>
+        <v>2.53154683113098</v>
       </c>
       <c r="H496" t="n">
         <v>2034742</v>
@@ -14782,7 +14782,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G497" t="n">
-        <v>2.4837818145752</v>
+        <v>2.48378157615662</v>
       </c>
       <c r="H497" t="n">
         <v>1452840</v>
@@ -14840,7 +14840,7 @@
         <v>3.16599988937378</v>
       </c>
       <c r="G499" t="n">
-        <v>2.5204017162323</v>
+        <v>2.52040147781372</v>
       </c>
       <c r="H499" t="n">
         <v>1758820</v>
@@ -14869,7 +14869,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G500" t="n">
-        <v>2.53473162651062</v>
+        <v>2.53473114967346</v>
       </c>
       <c r="H500" t="n">
         <v>1330089</v>
@@ -14898,7 +14898,7 @@
         <v>3.26799988746643</v>
       </c>
       <c r="G501" t="n">
-        <v>2.60160183906555</v>
+        <v>2.60160255432129</v>
       </c>
       <c r="H501" t="n">
         <v>1303907</v>
@@ -14956,7 +14956,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G503" t="n">
-        <v>2.5315465927124</v>
+        <v>2.53154683113098</v>
       </c>
       <c r="H503" t="n">
         <v>1750900</v>
@@ -14985,7 +14985,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G504" t="n">
-        <v>2.5076642036438</v>
+        <v>2.50766444206238</v>
       </c>
       <c r="H504" t="n">
         <v>1490065</v>
@@ -15014,7 +15014,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G505" t="n">
-        <v>2.51562523841858</v>
+        <v>2.515625</v>
       </c>
       <c r="H505" t="n">
         <v>2056515</v>
@@ -15101,7 +15101,7 @@
         <v>3.15400004386902</v>
       </c>
       <c r="G508" t="n">
-        <v>2.51084876060486</v>
+        <v>2.51084852218628</v>
       </c>
       <c r="H508" t="n">
         <v>2514530</v>
@@ -15188,7 +15188,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G511" t="n">
-        <v>2.56179785728455</v>
+        <v>2.56179809570312</v>
       </c>
       <c r="H511" t="n">
         <v>494732</v>
@@ -15246,7 +15246,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G513" t="n">
-        <v>2.59841799736023</v>
+        <v>2.59841775894165</v>
       </c>
       <c r="H513" t="n">
         <v>975318</v>
@@ -15275,7 +15275,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G514" t="n">
-        <v>2.62707662582397</v>
+        <v>2.62707686424255</v>
       </c>
       <c r="H514" t="n">
         <v>1221081</v>
@@ -15304,7 +15304,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G515" t="n">
-        <v>2.65892004966736</v>
+        <v>2.65892028808594</v>
       </c>
       <c r="H515" t="n">
         <v>1978965</v>
@@ -15420,7 +15420,7 @@
         <v>3.44199991226196</v>
       </c>
       <c r="G519" t="n">
-        <v>2.74012064933777</v>
+        <v>2.74012088775635</v>
       </c>
       <c r="H519" t="n">
         <v>911320</v>
@@ -15478,7 +15478,7 @@
         <v>3.36199998855591</v>
       </c>
       <c r="G521" t="n">
-        <v>2.67643404006958</v>
+        <v>2.67643427848816</v>
       </c>
       <c r="H521" t="n">
         <v>2011203</v>
@@ -15565,7 +15565,7 @@
         <v>3.31200003623962</v>
       </c>
       <c r="G524" t="n">
-        <v>2.63663005828857</v>
+        <v>2.63662981987</v>
       </c>
       <c r="H524" t="n">
         <v>542943</v>
@@ -15594,7 +15594,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G525" t="n">
-        <v>2.61911582946777</v>
+        <v>2.61911630630493</v>
       </c>
       <c r="H525" t="n">
         <v>990093</v>
@@ -15623,7 +15623,7 @@
         <v>3.30599999427795</v>
       </c>
       <c r="G526" t="n">
-        <v>2.6318531036377</v>
+        <v>2.63185334205627</v>
       </c>
       <c r="H526" t="n">
         <v>1221618</v>
@@ -15710,7 +15710,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G529" t="n">
-        <v>2.56816673278809</v>
+        <v>2.56816697120667</v>
       </c>
       <c r="H529" t="n">
         <v>1409532</v>
@@ -15739,7 +15739,7 @@
         <v>3.19199991226196</v>
       </c>
       <c r="G530" t="n">
-        <v>2.54109978675842</v>
+        <v>2.541100025177</v>
       </c>
       <c r="H530" t="n">
         <v>2378901</v>
@@ -15768,7 +15768,7 @@
         <v>3.2260000705719</v>
       </c>
       <c r="G531" t="n">
-        <v>2.56816673278809</v>
+        <v>2.56816697120667</v>
       </c>
       <c r="H531" t="n">
         <v>2024887</v>
@@ -15797,7 +15797,7 @@
         <v>3.24399995803833</v>
       </c>
       <c r="G532" t="n">
-        <v>2.58249616622925</v>
+        <v>2.58249592781067</v>
       </c>
       <c r="H532" t="n">
         <v>1967995</v>
@@ -15826,7 +15826,7 @@
         <v>3.24200010299683</v>
       </c>
       <c r="G533" t="n">
-        <v>2.58090400695801</v>
+        <v>2.58090424537659</v>
       </c>
       <c r="H533" t="n">
         <v>735592</v>
@@ -15913,7 +15913,7 @@
         <v>2.94600009918213</v>
       </c>
       <c r="G536" t="n">
-        <v>2.34526324272156</v>
+        <v>2.34526348114014</v>
       </c>
       <c r="H536" t="n">
         <v>2994862</v>
@@ -16000,7 +16000,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G539" t="n">
-        <v>2.12872862815857</v>
+        <v>2.12872838973999</v>
       </c>
       <c r="H539" t="n">
         <v>4819283</v>
@@ -16058,7 +16058,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>2.05389666557312</v>
+        <v>2.05389642715454</v>
       </c>
       <c r="H541" t="n">
         <v>1892118</v>
@@ -16087,7 +16087,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G542" t="n">
-        <v>2.01409220695496</v>
+        <v>2.01409268379211</v>
       </c>
       <c r="H542" t="n">
         <v>2601422</v>
@@ -16116,7 +16116,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G543" t="n">
-        <v>2.05708074569702</v>
+        <v>2.0570809841156</v>
       </c>
       <c r="H543" t="n">
         <v>1323647</v>
@@ -16145,7 +16145,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G544" t="n">
-        <v>2.07459449768066</v>
+        <v>2.07459473609924</v>
       </c>
       <c r="H544" t="n">
         <v>1590563</v>
@@ -16174,7 +16174,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G545" t="n">
-        <v>2.073002576828</v>
+        <v>2.07300281524658</v>
       </c>
       <c r="H545" t="n">
         <v>2877331</v>
@@ -16203,7 +16203,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G546" t="n">
-        <v>2.05708074569702</v>
+        <v>2.0570809841156</v>
       </c>
       <c r="H546" t="n">
         <v>755000</v>
@@ -16232,7 +16232,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G547" t="n">
-        <v>2.05708074569702</v>
+        <v>2.0570809841156</v>
       </c>
       <c r="H547" t="n">
         <v>813711</v>
@@ -16261,7 +16261,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G548" t="n">
-        <v>2.10643768310547</v>
+        <v>2.10643792152405</v>
       </c>
       <c r="H548" t="n">
         <v>1554469</v>
@@ -16290,7 +16290,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.09370064735413</v>
+        <v>2.09370088577271</v>
       </c>
       <c r="H549" t="n">
         <v>2976419</v>
@@ -16319,7 +16319,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G550" t="n">
-        <v>2.04593539237976</v>
+        <v>2.04593563079834</v>
       </c>
       <c r="H550" t="n">
         <v>1865883</v>
@@ -16348,7 +16348,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G551" t="n">
-        <v>2.01727676391602</v>
+        <v>2.01727700233459</v>
       </c>
       <c r="H551" t="n">
         <v>1462101</v>
@@ -16377,7 +16377,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G552" t="n">
-        <v>2.00294756889343</v>
+        <v>2.00294733047485</v>
       </c>
       <c r="H552" t="n">
         <v>2572034</v>
@@ -16406,7 +16406,7 @@
         <v>2.49600005149841</v>
       </c>
       <c r="G553" t="n">
-        <v>1.98702526092529</v>
+        <v>1.98702549934387</v>
       </c>
       <c r="H553" t="n">
         <v>1328048</v>
@@ -16464,7 +16464,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G555" t="n">
-        <v>1.9074170589447</v>
+        <v>1.90741670131683</v>
       </c>
       <c r="H555" t="n">
         <v>2204356</v>
@@ -16551,7 +16551,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G558" t="n">
-        <v>2.01090788841248</v>
+        <v>2.01090812683105</v>
       </c>
       <c r="H558" t="n">
         <v>1799452</v>
@@ -16609,7 +16609,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G560" t="n">
-        <v>2.10325360298157</v>
+        <v>2.10325384140015</v>
       </c>
       <c r="H560" t="n">
         <v>2761128</v>
@@ -16696,7 +16696,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G563" t="n">
-        <v>1.80870270729065</v>
+        <v>1.80870258808136</v>
       </c>
       <c r="H563" t="n">
         <v>11295853</v>
@@ -16812,7 +16812,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G567" t="n">
-        <v>1.99976289272308</v>
+        <v>1.99976301193237</v>
       </c>
       <c r="H567" t="n">
         <v>1325179</v>
@@ -16841,7 +16841,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G568" t="n">
-        <v>1.93766844272614</v>
+        <v>1.93766832351685</v>
       </c>
       <c r="H568" t="n">
         <v>2277688</v>
@@ -16899,7 +16899,7 @@
         <v>2.44400000572205</v>
       </c>
       <c r="G570" t="n">
-        <v>1.94562888145447</v>
+        <v>1.94562911987305</v>
       </c>
       <c r="H570" t="n">
         <v>2696695</v>
@@ -16928,7 +16928,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G571" t="n">
-        <v>1.88990354537964</v>
+        <v>1.88990330696106</v>
       </c>
       <c r="H571" t="n">
         <v>1404482</v>
@@ -16957,7 +16957,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G572" t="n">
-        <v>1.91219353675842</v>
+        <v>1.91219365596771</v>
       </c>
       <c r="H572" t="n">
         <v>1317721</v>
@@ -17044,7 +17044,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G575" t="n">
-        <v>1.8994562625885</v>
+        <v>1.89945602416992</v>
       </c>
       <c r="H575" t="n">
         <v>1034331</v>
@@ -17073,7 +17073,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G576" t="n">
-        <v>1.90582489967346</v>
+        <v>1.90582466125488</v>
       </c>
       <c r="H576" t="n">
         <v>1701979</v>
@@ -17102,7 +17102,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G577" t="n">
-        <v>1.95199799537659</v>
+        <v>1.95199775695801</v>
       </c>
       <c r="H577" t="n">
         <v>2027295</v>
@@ -17160,7 +17160,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>1.92652332782745</v>
+        <v>1.92652308940887</v>
       </c>
       <c r="H579" t="n">
         <v>722313</v>
@@ -17189,7 +17189,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G580" t="n">
-        <v>1.92970740795135</v>
+        <v>1.92970728874207</v>
       </c>
       <c r="H580" t="n">
         <v>1260607</v>
@@ -17218,7 +17218,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G581" t="n">
-        <v>1.90264093875885</v>
+        <v>1.90264046192169</v>
       </c>
       <c r="H581" t="n">
         <v>921579</v>
@@ -17276,7 +17276,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G583" t="n">
-        <v>1.8962721824646</v>
+        <v>1.89627170562744</v>
       </c>
       <c r="H583" t="n">
         <v>944622</v>
@@ -17305,7 +17305,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G584" t="n">
-        <v>1.88194262981415</v>
+        <v>1.88194227218628</v>
       </c>
       <c r="H584" t="n">
         <v>1407864</v>
@@ -17363,7 +17363,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G586" t="n">
-        <v>1.8500988483429</v>
+        <v>1.85009896755219</v>
       </c>
       <c r="H586" t="n">
         <v>1482418</v>
@@ -17392,7 +17392,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G587" t="n">
-        <v>1.86283612251282</v>
+        <v>1.8628363609314</v>
       </c>
       <c r="H587" t="n">
         <v>2223013</v>
@@ -17450,7 +17450,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G589" t="n">
-        <v>1.81507122516632</v>
+        <v>1.81507134437561</v>
       </c>
       <c r="H589" t="n">
         <v>1297798</v>
@@ -17479,7 +17479,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G590" t="n">
-        <v>1.81507122516632</v>
+        <v>1.81507134437561</v>
       </c>
       <c r="H590" t="n">
         <v>1110350</v>
@@ -17537,7 +17537,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G592" t="n">
-        <v>1.76412224769592</v>
+        <v>1.76412189006805</v>
       </c>
       <c r="H592" t="n">
         <v>2941699</v>
@@ -17566,7 +17566,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G593" t="n">
-        <v>1.78004360198975</v>
+        <v>1.78004348278046</v>
       </c>
       <c r="H593" t="n">
         <v>1670608</v>
@@ -17595,7 +17595,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G594" t="n">
-        <v>1.88990354537964</v>
+        <v>1.88990330696106</v>
       </c>
       <c r="H594" t="n">
         <v>5320330</v>
@@ -17653,7 +17653,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G596" t="n">
-        <v>1.89149534702301</v>
+        <v>1.89149570465088</v>
       </c>
       <c r="H596" t="n">
         <v>13135214</v>
@@ -17711,7 +17711,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G598" t="n">
-        <v>1.87238931655884</v>
+        <v>1.87238919734955</v>
       </c>
       <c r="H598" t="n">
         <v>2693236</v>
@@ -17740,7 +17740,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G599" t="n">
-        <v>1.851691365242</v>
+        <v>1.85169112682343</v>
       </c>
       <c r="H599" t="n">
         <v>1869245</v>
@@ -17769,7 +17769,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G600" t="n">
-        <v>1.87238931655884</v>
+        <v>1.87238919734955</v>
       </c>
       <c r="H600" t="n">
         <v>1249089</v>
@@ -17798,7 +17798,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G601" t="n">
-        <v>1.82621645927429</v>
+        <v>1.826216340065</v>
       </c>
       <c r="H601" t="n">
         <v>2208316</v>
@@ -17827,7 +17827,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G602" t="n">
-        <v>1.83576953411102</v>
+        <v>1.83576941490173</v>
       </c>
       <c r="H602" t="n">
         <v>981017</v>
@@ -17856,7 +17856,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G603" t="n">
-        <v>1.88353455066681</v>
+        <v>1.88353443145752</v>
       </c>
       <c r="H603" t="n">
         <v>2143576</v>
@@ -17914,7 +17914,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G605" t="n">
-        <v>1.81825542449951</v>
+        <v>1.8182555437088</v>
       </c>
       <c r="H605" t="n">
         <v>3157751</v>
@@ -17943,7 +17943,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G606" t="n">
-        <v>1.80074191093445</v>
+        <v>1.80074167251587</v>
       </c>
       <c r="H606" t="n">
         <v>1597477</v>
@@ -17972,7 +17972,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G607" t="n">
-        <v>1.77526724338531</v>
+        <v>1.7752673625946</v>
       </c>
       <c r="H607" t="n">
         <v>1953879</v>
@@ -18030,7 +18030,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G609" t="n">
-        <v>1.82501041889191</v>
+        <v>1.82501029968262</v>
       </c>
       <c r="H609" t="n">
         <v>1866217</v>
@@ -18059,7 +18059,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>1.81848680973053</v>
+        <v>1.81848704814911</v>
       </c>
       <c r="H610" t="n">
         <v>1189890</v>
@@ -18088,7 +18088,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G611" t="n">
-        <v>1.82174861431122</v>
+        <v>1.82174849510193</v>
       </c>
       <c r="H611" t="n">
         <v>639504</v>
@@ -18146,7 +18146,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>1.72878551483154</v>
+        <v>1.72878563404083</v>
       </c>
       <c r="H613" t="n">
         <v>2708744</v>
@@ -18175,7 +18175,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G614" t="n">
-        <v>1.73367834091187</v>
+        <v>1.73367822170258</v>
       </c>
       <c r="H614" t="n">
         <v>2260783</v>
@@ -18204,7 +18204,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G615" t="n">
-        <v>1.72878551483154</v>
+        <v>1.72878563404083</v>
       </c>
       <c r="H615" t="n">
         <v>1733659</v>
@@ -18233,7 +18233,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G616" t="n">
-        <v>1.71736907958984</v>
+        <v>1.71736896038055</v>
       </c>
       <c r="H616" t="n">
         <v>1661744</v>
@@ -18262,7 +18262,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G617" t="n">
-        <v>1.78586828708649</v>
+        <v>1.78586804866791</v>
       </c>
       <c r="H617" t="n">
         <v>2304857</v>
@@ -18291,7 +18291,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G618" t="n">
-        <v>1.7581422328949</v>
+        <v>1.75814235210419</v>
       </c>
       <c r="H618" t="n">
         <v>921766</v>
@@ -18349,7 +18349,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G620" t="n">
-        <v>1.77445161342621</v>
+        <v>1.7744517326355</v>
       </c>
       <c r="H620" t="n">
         <v>1303635</v>
@@ -18407,7 +18407,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G622" t="n">
-        <v>1.73857116699219</v>
+        <v>1.73857128620148</v>
       </c>
       <c r="H622" t="n">
         <v>583631</v>
@@ -18523,7 +18523,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G626" t="n">
-        <v>1.8445817232132</v>
+        <v>1.84458160400391</v>
       </c>
       <c r="H626" t="n">
         <v>1938784</v>
@@ -18552,7 +18552,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>1.86741471290588</v>
+        <v>1.86741483211517</v>
       </c>
       <c r="H627" t="n">
         <v>2849945</v>
@@ -18581,7 +18581,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G628" t="n">
-        <v>1.8445817232132</v>
+        <v>1.84458160400391</v>
       </c>
       <c r="H628" t="n">
         <v>450028</v>
@@ -18610,7 +18610,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G629" t="n">
-        <v>1.84947407245636</v>
+        <v>1.84947431087494</v>
       </c>
       <c r="H629" t="n">
         <v>517248</v>
@@ -18639,7 +18639,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G630" t="n">
-        <v>1.82664144039154</v>
+        <v>1.82664132118225</v>
       </c>
       <c r="H630" t="n">
         <v>683361</v>
@@ -18668,7 +18668,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G631" t="n">
-        <v>1.76466619968414</v>
+        <v>1.76466608047485</v>
       </c>
       <c r="H631" t="n">
         <v>968829</v>
@@ -18697,7 +18697,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G632" t="n">
-        <v>1.79239177703857</v>
+        <v>1.79239189624786</v>
       </c>
       <c r="H632" t="n">
         <v>2137127</v>
@@ -18784,7 +18784,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G635" t="n">
-        <v>1.75161862373352</v>
+        <v>1.75161874294281</v>
       </c>
       <c r="H635" t="n">
         <v>794317</v>
@@ -18842,7 +18842,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G637" t="n">
-        <v>1.82011783123016</v>
+        <v>1.82011759281158</v>
       </c>
       <c r="H637" t="n">
         <v>2298555</v>
@@ -18871,7 +18871,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G638" t="n">
-        <v>1.88698577880859</v>
+        <v>1.88698554039001</v>
       </c>
       <c r="H638" t="n">
         <v>2351541</v>
@@ -18900,7 +18900,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G639" t="n">
-        <v>1.89187860488892</v>
+        <v>1.89187872409821</v>
       </c>
       <c r="H639" t="n">
         <v>1290827</v>
@@ -18958,7 +18958,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G641" t="n">
-        <v>1.86578404903412</v>
+        <v>1.86578381061554</v>
       </c>
       <c r="H641" t="n">
         <v>1601256</v>
@@ -18987,7 +18987,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G642" t="n">
-        <v>1.87720024585724</v>
+        <v>1.87720036506653</v>
       </c>
       <c r="H642" t="n">
         <v>1729727</v>
@@ -19016,7 +19016,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G643" t="n">
-        <v>1.9065568447113</v>
+        <v>1.90655708312988</v>
       </c>
       <c r="H643" t="n">
         <v>1155916</v>
@@ -19074,7 +19074,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G645" t="n">
-        <v>1.84295082092285</v>
+        <v>1.84295094013214</v>
       </c>
       <c r="H645" t="n">
         <v>1183341</v>
@@ -19103,7 +19103,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G646" t="n">
-        <v>1.86741471290588</v>
+        <v>1.86741483211517</v>
       </c>
       <c r="H646" t="n">
         <v>465309</v>
@@ -19161,7 +19161,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G648" t="n">
-        <v>1.81685602664948</v>
+        <v>1.8168557882309</v>
       </c>
       <c r="H648" t="n">
         <v>605104</v>
@@ -19219,7 +19219,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G650" t="n">
-        <v>1.81848680973053</v>
+        <v>1.81848704814911</v>
       </c>
       <c r="H650" t="n">
         <v>710538</v>
@@ -19248,7 +19248,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G651" t="n">
-        <v>1.79239177703857</v>
+        <v>1.79239189624786</v>
       </c>
       <c r="H651" t="n">
         <v>2071396</v>
@@ -19277,7 +19277,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G652" t="n">
-        <v>1.77445161342621</v>
+        <v>1.7744517326355</v>
       </c>
       <c r="H652" t="n">
         <v>882911</v>
@@ -19335,7 +19335,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78749883174896</v>
+        <v>1.78749907016754</v>
       </c>
       <c r="H654" t="n">
         <v>659037</v>
@@ -19364,7 +19364,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>1.75324976444244</v>
+        <v>1.75324988365173</v>
       </c>
       <c r="H655" t="n">
         <v>913367</v>
@@ -19393,7 +19393,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G656" t="n">
-        <v>1.73857116699219</v>
+        <v>1.73857128620148</v>
       </c>
       <c r="H656" t="n">
         <v>3598224</v>
@@ -19451,7 +19451,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G658" t="n">
-        <v>1.8331652879715</v>
+        <v>1.83316504955292</v>
       </c>
       <c r="H658" t="n">
         <v>1422538</v>
@@ -19480,7 +19480,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G659" t="n">
-        <v>1.84295082092285</v>
+        <v>1.84295094013214</v>
       </c>
       <c r="H659" t="n">
         <v>912189</v>
@@ -19538,7 +19538,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G661" t="n">
-        <v>1.82337951660156</v>
+        <v>1.82337939739227</v>
       </c>
       <c r="H661" t="n">
         <v>839503</v>
@@ -19567,7 +19567,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G662" t="n">
-        <v>1.79239177703857</v>
+        <v>1.79239189624786</v>
       </c>
       <c r="H662" t="n">
         <v>897689</v>
@@ -19625,7 +19625,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G664" t="n">
-        <v>1.82011783123016</v>
+        <v>1.82011759281158</v>
       </c>
       <c r="H664" t="n">
         <v>676673</v>
@@ -19654,7 +19654,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G665" t="n">
-        <v>1.89187860488892</v>
+        <v>1.89187872409821</v>
       </c>
       <c r="H665" t="n">
         <v>4688332</v>
@@ -19683,7 +19683,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G666" t="n">
-        <v>1.88046205043793</v>
+        <v>1.88046216964722</v>
       </c>
       <c r="H666" t="n">
         <v>845679</v>
@@ -19712,7 +19712,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G667" t="n">
-        <v>1.85925984382629</v>
+        <v>1.85926008224487</v>
       </c>
       <c r="H667" t="n">
         <v>963738</v>
@@ -19770,7 +19770,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G669" t="n">
-        <v>1.85762906074524</v>
+        <v>1.85762917995453</v>
       </c>
       <c r="H669" t="n">
         <v>854370</v>
@@ -19828,7 +19828,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G671" t="n">
-        <v>1.90818774700165</v>
+        <v>1.90818786621094</v>
       </c>
       <c r="H671" t="n">
         <v>1160035</v>
@@ -19857,7 +19857,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G672" t="n">
-        <v>2.00441265106201</v>
+        <v>2.00441241264343</v>
       </c>
       <c r="H672" t="n">
         <v>5364988</v>
@@ -19944,7 +19944,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G675" t="n">
-        <v>1.95548462867737</v>
+        <v>1.95548474788666</v>
       </c>
       <c r="H675" t="n">
         <v>2650527</v>
@@ -19973,7 +19973,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G676" t="n">
-        <v>1.96853232383728</v>
+        <v>1.96853256225586</v>
       </c>
       <c r="H676" t="n">
         <v>928396</v>
@@ -20002,7 +20002,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G677" t="n">
-        <v>1.90329504013062</v>
+        <v>1.9032951593399</v>
       </c>
       <c r="H677" t="n">
         <v>1584415</v>
@@ -20031,7 +20031,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G678" t="n">
-        <v>1.89024782180786</v>
+        <v>1.89024770259857</v>
       </c>
       <c r="H678" t="n">
         <v>886735</v>
@@ -20147,7 +20147,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G682" t="n">
-        <v>1.76466619968414</v>
+        <v>1.76466608047485</v>
       </c>
       <c r="H682" t="n">
         <v>4168427</v>
@@ -20176,7 +20176,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G683" t="n">
-        <v>1.73367834091187</v>
+        <v>1.73367822170258</v>
       </c>
       <c r="H683" t="n">
         <v>2641844</v>
@@ -20205,7 +20205,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G684" t="n">
-        <v>1.82337951660156</v>
+        <v>1.82337939739227</v>
       </c>
       <c r="H684" t="n">
         <v>2326497</v>
@@ -20234,7 +20234,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G685" t="n">
-        <v>1.82664144039154</v>
+        <v>1.82664132118225</v>
       </c>
       <c r="H685" t="n">
         <v>2020822</v>
@@ -20263,7 +20263,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G686" t="n">
-        <v>1.85436701774597</v>
+        <v>1.85436737537384</v>
       </c>
       <c r="H686" t="n">
         <v>826482</v>
@@ -20292,7 +20292,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G687" t="n">
-        <v>1.91471171379089</v>
+        <v>1.9147115945816</v>
       </c>
       <c r="H687" t="n">
         <v>1051261</v>
@@ -20321,7 +20321,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G688" t="n">
-        <v>1.90329504013062</v>
+        <v>1.9032951593399</v>
       </c>
       <c r="H688" t="n">
         <v>523293</v>
@@ -20350,7 +20350,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G689" t="n">
-        <v>1.91308045387268</v>
+        <v>1.91308057308197</v>
       </c>
       <c r="H689" t="n">
         <v>689161</v>
@@ -20437,7 +20437,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G692" t="n">
-        <v>1.88046205043793</v>
+        <v>1.88046216964722</v>
       </c>
       <c r="H692" t="n">
         <v>471227</v>
@@ -20466,7 +20466,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G693" t="n">
-        <v>1.84295082092285</v>
+        <v>1.84295094013214</v>
       </c>
       <c r="H693" t="n">
         <v>805042</v>
@@ -20495,7 +20495,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G694" t="n">
-        <v>1.81685602664948</v>
+        <v>1.8168557882309</v>
       </c>
       <c r="H694" t="n">
         <v>1394273</v>
@@ -20524,7 +20524,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G695" t="n">
-        <v>1.80707037448883</v>
+        <v>1.80707025527954</v>
       </c>
       <c r="H695" t="n">
         <v>756669</v>
@@ -20582,7 +20582,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G697" t="n">
-        <v>1.79402267932892</v>
+        <v>1.79402279853821</v>
       </c>
       <c r="H697" t="n">
         <v>672268</v>
@@ -20611,7 +20611,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G698" t="n">
-        <v>1.78749883174896</v>
+        <v>1.78749907016754</v>
       </c>
       <c r="H698" t="n">
         <v>796654</v>
@@ -20640,7 +20640,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G699" t="n">
-        <v>1.75324976444244</v>
+        <v>1.75324988365173</v>
       </c>
       <c r="H699" t="n">
         <v>1589594</v>
@@ -20669,7 +20669,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>1.75324976444244</v>
+        <v>1.75324988365173</v>
       </c>
       <c r="H700" t="n">
         <v>570256</v>
@@ -20698,7 +20698,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G701" t="n">
-        <v>1.73041653633118</v>
+        <v>1.73041641712189</v>
       </c>
       <c r="H701" t="n">
         <v>811499</v>
@@ -20727,7 +20727,7 @@
         <v>2.08599996566772</v>
       </c>
       <c r="G702" t="n">
-        <v>1.70105969905853</v>
+        <v>1.70105981826782</v>
       </c>
       <c r="H702" t="n">
         <v>929920</v>
@@ -20785,7 +20785,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G704" t="n">
-        <v>1.65050101280212</v>
+        <v>1.65050089359283</v>
       </c>
       <c r="H704" t="n">
         <v>2017014</v>
@@ -20814,7 +20814,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G705" t="n">
-        <v>1.66191744804382</v>
+        <v>1.6619176864624</v>
       </c>
       <c r="H705" t="n">
         <v>6571728</v>
@@ -20872,7 +20872,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G707" t="n">
-        <v>1.58607935905457</v>
+        <v>1.58607912063599</v>
       </c>
       <c r="H707" t="n">
         <v>1261183</v>
@@ -20901,7 +20901,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G708" t="n">
-        <v>1.57384729385376</v>
+        <v>1.57384717464447</v>
       </c>
       <c r="H708" t="n">
         <v>980940</v>
@@ -20930,7 +20930,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G709" t="n">
-        <v>1.52491939067841</v>
+        <v>1.52491927146912</v>
       </c>
       <c r="H709" t="n">
         <v>1978920</v>
@@ -20959,7 +20959,7 @@
         <v>1.81700003147125</v>
       </c>
       <c r="G710" t="n">
-        <v>1.4816997051239</v>
+        <v>1.48169982433319</v>
       </c>
       <c r="H710" t="n">
         <v>2572970</v>
@@ -21017,7 +21017,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G712" t="n">
-        <v>1.48496150970459</v>
+        <v>1.48496162891388</v>
       </c>
       <c r="H712" t="n">
         <v>915632</v>
@@ -21075,7 +21075,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.48822343349457</v>
+        <v>1.48822355270386</v>
       </c>
       <c r="H714" t="n">
         <v>3092187</v>
@@ -21104,7 +21104,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G715" t="n">
-        <v>1.48577690124512</v>
+        <v>1.48577725887299</v>
       </c>
       <c r="H715" t="n">
         <v>1758890</v>
@@ -21162,7 +21162,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G717" t="n">
-        <v>1.46212875843048</v>
+        <v>1.4621285200119</v>
       </c>
       <c r="H717" t="n">
         <v>814779</v>
@@ -21191,7 +21191,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>1.45968210697174</v>
+        <v>1.45968222618103</v>
       </c>
       <c r="H718" t="n">
         <v>1383440</v>
@@ -21220,7 +21220,7 @@
         <v>1.7960000038147</v>
       </c>
       <c r="G719" t="n">
-        <v>1.46457505226135</v>
+        <v>1.46457493305206</v>
       </c>
       <c r="H719" t="n">
         <v>887906</v>
@@ -21278,7 +21278,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G721" t="n">
-        <v>1.53470492362976</v>
+        <v>1.53470504283905</v>
       </c>
       <c r="H721" t="n">
         <v>621201</v>
@@ -21307,7 +21307,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G722" t="n">
-        <v>1.60483503341675</v>
+        <v>1.60483491420746</v>
       </c>
       <c r="H722" t="n">
         <v>1425242</v>
@@ -21336,7 +21336,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G723" t="n">
-        <v>1.57874000072479</v>
+        <v>1.57874011993408</v>
       </c>
       <c r="H723" t="n">
         <v>621410</v>
@@ -21394,7 +21394,7 @@
         <v>1.98699998855591</v>
       </c>
       <c r="G725" t="n">
-        <v>1.62032890319824</v>
+        <v>1.62032878398895</v>
       </c>
       <c r="H725" t="n">
         <v>678094</v>
@@ -21423,7 +21423,7 @@
         <v>2.00399994850159</v>
       </c>
       <c r="G726" t="n">
-        <v>1.63419163227081</v>
+        <v>1.63419151306152</v>
       </c>
       <c r="H726" t="n">
         <v>1024698</v>
@@ -21626,7 +21626,7 @@
         <v>1.85399997234344</v>
       </c>
       <c r="G733" t="n">
-        <v>1.51187181472778</v>
+        <v>1.51187193393707</v>
       </c>
       <c r="H733" t="n">
         <v>1759383</v>
@@ -21655,7 +21655,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G734" t="n">
-        <v>1.50453293323517</v>
+        <v>1.50453281402588</v>
       </c>
       <c r="H734" t="n">
         <v>1397140</v>
@@ -21713,7 +21713,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G736" t="n">
-        <v>1.54285967350006</v>
+        <v>1.54285955429077</v>
       </c>
       <c r="H736" t="n">
         <v>867680</v>
@@ -21742,7 +21742,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G737" t="n">
-        <v>1.51676464080811</v>
+        <v>1.5167647600174</v>
       </c>
       <c r="H737" t="n">
         <v>745389</v>
@@ -21858,7 +21858,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G741" t="n">
-        <v>1.47191405296326</v>
+        <v>1.47191417217255</v>
       </c>
       <c r="H741" t="n">
         <v>414540</v>
@@ -21887,7 +21887,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G742" t="n">
-        <v>1.51024091243744</v>
+        <v>1.51024103164673</v>
       </c>
       <c r="H742" t="n">
         <v>802068</v>
@@ -21916,7 +21916,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G743" t="n">
-        <v>1.51676464080811</v>
+        <v>1.5167647600174</v>
       </c>
       <c r="H743" t="n">
         <v>805198</v>
@@ -21945,7 +21945,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G744" t="n">
-        <v>1.50453293323517</v>
+        <v>1.50453281402588</v>
       </c>
       <c r="H744" t="n">
         <v>1047194</v>
@@ -22003,7 +22003,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G746" t="n">
-        <v>1.45152759552002</v>
+        <v>1.45152747631073</v>
       </c>
       <c r="H746" t="n">
         <v>1189559</v>
@@ -22061,7 +22061,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G748" t="n">
-        <v>1.46049773693085</v>
+        <v>1.46049761772156</v>
       </c>
       <c r="H748" t="n">
         <v>456440</v>
@@ -22177,7 +22177,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G752" t="n">
-        <v>1.36345732212067</v>
+        <v>1.36345744132996</v>
       </c>
       <c r="H752" t="n">
         <v>722243</v>
@@ -22206,7 +22206,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G753" t="n">
-        <v>1.36345732212067</v>
+        <v>1.36345744132996</v>
       </c>
       <c r="H753" t="n">
         <v>680677</v>
@@ -22235,7 +22235,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G754" t="n">
-        <v>1.3724273443222</v>
+        <v>1.37242746353149</v>
       </c>
       <c r="H754" t="n">
         <v>1083070</v>
@@ -22293,7 +22293,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G756" t="n">
-        <v>1.09272301197052</v>
+        <v>1.09272289276123</v>
       </c>
       <c r="H756" t="n">
         <v>13977981</v>
@@ -22380,7 +22380,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G759" t="n">
-        <v>1.01525378227234</v>
+        <v>1.01525390148163</v>
       </c>
       <c r="H759" t="n">
         <v>3366532</v>
@@ -22438,7 +22438,7 @@
         <v>1.32700002193451</v>
       </c>
       <c r="G761" t="n">
-        <v>1.08212196826935</v>
+        <v>1.08212184906006</v>
       </c>
       <c r="H761" t="n">
         <v>3813414</v>
@@ -22525,7 +22525,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G764" t="n">
-        <v>1.15388286113739</v>
+        <v>1.1538827419281</v>
       </c>
       <c r="H764" t="n">
         <v>1226156</v>
@@ -22554,7 +22554,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G765" t="n">
-        <v>1.17426955699921</v>
+        <v>1.1742696762085</v>
       </c>
       <c r="H765" t="n">
         <v>2107430</v>
@@ -22583,7 +22583,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>1.17426955699921</v>
+        <v>1.1742696762085</v>
       </c>
       <c r="H766" t="n">
         <v>1555652</v>
@@ -22670,7 +22670,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G769" t="n">
-        <v>1.3022974729538</v>
+        <v>1.30229735374451</v>
       </c>
       <c r="H769" t="n">
         <v>1170678</v>
@@ -22844,7 +22844,7 @@
         <v>1.66799998283386</v>
       </c>
       <c r="G775" t="n">
-        <v>1.36019563674927</v>
+        <v>1.36019539833069</v>
       </c>
       <c r="H775" t="n">
         <v>1881833</v>
@@ -22902,7 +22902,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G777" t="n">
-        <v>1.39770686626434</v>
+        <v>1.39770674705505</v>
       </c>
       <c r="H777" t="n">
         <v>2242382</v>
@@ -22960,7 +22960,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G779" t="n">
-        <v>1.33491587638855</v>
+        <v>1.33491599559784</v>
       </c>
       <c r="H779" t="n">
         <v>3214064</v>
@@ -22989,7 +22989,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G780" t="n">
-        <v>1.37813580036163</v>
+        <v>1.37813591957092</v>
       </c>
       <c r="H780" t="n">
         <v>3667223</v>
@@ -23047,7 +23047,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G782" t="n">
-        <v>1.5094256401062</v>
+        <v>1.50942540168762</v>
       </c>
       <c r="H782" t="n">
         <v>2051305</v>
@@ -23134,7 +23134,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G785" t="n">
-        <v>1.56569254398346</v>
+        <v>1.56569266319275</v>
       </c>
       <c r="H785" t="n">
         <v>2561988</v>
@@ -23163,7 +23163,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G786" t="n">
-        <v>1.56650805473328</v>
+        <v>1.56650817394257</v>
       </c>
       <c r="H786" t="n">
         <v>2160067</v>
@@ -23192,7 +23192,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G787" t="n">
-        <v>1.57547807693481</v>
+        <v>1.5754781961441</v>
       </c>
       <c r="H787" t="n">
         <v>2151732</v>
@@ -23337,7 +23337,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G792" t="n">
-        <v>1.51839566230774</v>
+        <v>1.51839554309845</v>
       </c>
       <c r="H792" t="n">
         <v>1104048</v>
@@ -23366,7 +23366,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G793" t="n">
-        <v>1.53470492362976</v>
+        <v>1.53470504283905</v>
       </c>
       <c r="H793" t="n">
         <v>557746</v>
@@ -23395,7 +23395,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G794" t="n">
-        <v>1.5208420753479</v>
+        <v>1.52084219455719</v>
       </c>
       <c r="H794" t="n">
         <v>765785</v>
@@ -23424,7 +23424,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G795" t="n">
-        <v>1.67985761165619</v>
+        <v>1.67985773086548</v>
       </c>
       <c r="H795" t="n">
         <v>6571124</v>
@@ -23482,7 +23482,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G797" t="n">
-        <v>1.66681015491486</v>
+        <v>1.66681027412415</v>
       </c>
       <c r="H797" t="n">
         <v>631363</v>
@@ -23511,7 +23511,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G798" t="n">
-        <v>1.67007219791412</v>
+        <v>1.67007231712341</v>
       </c>
       <c r="H798" t="n">
         <v>497000</v>
@@ -23540,7 +23540,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G799" t="n">
-        <v>1.67985761165619</v>
+        <v>1.67985773086548</v>
       </c>
       <c r="H799" t="n">
         <v>508447</v>
@@ -23569,7 +23569,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G800" t="n">
-        <v>1.64071536064148</v>
+        <v>1.64071547985077</v>
       </c>
       <c r="H800" t="n">
         <v>489775</v>
@@ -23598,7 +23598,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G801" t="n">
-        <v>1.65702486038208</v>
+        <v>1.65702474117279</v>
       </c>
       <c r="H801" t="n">
         <v>829278</v>
@@ -23627,7 +23627,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G802" t="n">
-        <v>1.68148875236511</v>
+        <v>1.68148863315582</v>
       </c>
       <c r="H802" t="n">
         <v>808567</v>
@@ -23714,7 +23714,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G805" t="n">
-        <v>1.70921444892883</v>
+        <v>1.70921432971954</v>
       </c>
       <c r="H805" t="n">
         <v>511806</v>
@@ -23743,7 +23743,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G806" t="n">
-        <v>1.70269072055817</v>
+        <v>1.70269060134888</v>
       </c>
       <c r="H806" t="n">
         <v>871066</v>
@@ -23801,7 +23801,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G808" t="n">
-        <v>1.67985761165619</v>
+        <v>1.67985773086548</v>
       </c>
       <c r="H808" t="n">
         <v>531129</v>
@@ -23859,7 +23859,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G810" t="n">
-        <v>1.68964314460754</v>
+        <v>1.68964326381683</v>
       </c>
       <c r="H810" t="n">
         <v>653322</v>
@@ -23946,7 +23946,7 @@
         <v>2.01799988746643</v>
       </c>
       <c r="G813" t="n">
-        <v>1.64560806751251</v>
+        <v>1.64560830593109</v>
       </c>
       <c r="H813" t="n">
         <v>341000</v>
@@ -23975,7 +23975,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G814" t="n">
-        <v>1.67007219791412</v>
+        <v>1.67007231712341</v>
       </c>
       <c r="H814" t="n">
         <v>399189</v>
@@ -24004,7 +24004,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G815" t="n">
-        <v>1.66681015491486</v>
+        <v>1.66681027412415</v>
       </c>
       <c r="H815" t="n">
         <v>693096</v>
@@ -24033,7 +24033,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G816" t="n">
-        <v>1.69290506839752</v>
+        <v>1.69290518760681</v>
       </c>
       <c r="H816" t="n">
         <v>1060991</v>
@@ -24062,7 +24062,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G817" t="n">
-        <v>1.64071536064148</v>
+        <v>1.64071547985077</v>
       </c>
       <c r="H817" t="n">
         <v>8186934</v>
@@ -24236,7 +24236,7 @@
         <v>2.05200004577637</v>
       </c>
       <c r="G823" t="n">
-        <v>1.67333400249481</v>
+        <v>1.67333388328552</v>
       </c>
       <c r="H823" t="n">
         <v>1131670</v>
@@ -24265,7 +24265,7 @@
         <v>2.03800010681152</v>
       </c>
       <c r="G824" t="n">
-        <v>1.66191744804382</v>
+        <v>1.6619176864624</v>
       </c>
       <c r="H824" t="n">
         <v>1727495</v>
@@ -24294,7 +24294,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G825" t="n">
-        <v>1.67496478557587</v>
+        <v>1.67496490478516</v>
       </c>
       <c r="H825" t="n">
         <v>666086</v>
@@ -24323,7 +24323,7 @@
         <v>2.07399988174438</v>
       </c>
       <c r="G826" t="n">
-        <v>1.69127404689789</v>
+        <v>1.69127416610718</v>
       </c>
       <c r="H826" t="n">
         <v>1668598</v>
@@ -24352,7 +24352,7 @@
         <v>2.09599995613098</v>
       </c>
       <c r="G827" t="n">
-        <v>1.70921444892883</v>
+        <v>1.70921432971954</v>
       </c>
       <c r="H827" t="n">
         <v>422823</v>
@@ -24381,7 +24381,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G828" t="n">
-        <v>1.68475043773651</v>
+        <v>1.6847505569458</v>
       </c>
       <c r="H828" t="n">
         <v>596412</v>
@@ -24410,7 +24410,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G829" t="n">
-        <v>1.70432162284851</v>
+        <v>1.70432150363922</v>
       </c>
       <c r="H829" t="n">
         <v>496963</v>
@@ -24439,7 +24439,7 @@
         <v>2.10599994659424</v>
       </c>
       <c r="G830" t="n">
-        <v>1.71736907958984</v>
+        <v>1.71736896038055</v>
       </c>
       <c r="H830" t="n">
         <v>843159</v>
@@ -24497,7 +24497,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G832" t="n">
-        <v>1.89187860488892</v>
+        <v>1.89187872409821</v>
       </c>
       <c r="H832" t="n">
         <v>3573577</v>
@@ -24555,7 +24555,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G834" t="n">
-        <v>1.78260624408722</v>
+        <v>1.7826064825058</v>
       </c>
       <c r="H834" t="n">
         <v>1213282</v>
@@ -24584,7 +24584,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G835" t="n">
-        <v>1.77771365642548</v>
+        <v>1.77771377563477</v>
       </c>
       <c r="H835" t="n">
         <v>401140</v>
@@ -24613,7 +24613,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G836" t="n">
-        <v>1.77445161342621</v>
+        <v>1.7744517326355</v>
       </c>
       <c r="H836" t="n">
         <v>445873</v>
@@ -24642,7 +24642,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>1.78586828708649</v>
+        <v>1.78586804866791</v>
       </c>
       <c r="H837" t="n">
         <v>450642</v>
@@ -24671,7 +24671,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G838" t="n">
-        <v>1.78586828708649</v>
+        <v>1.78586804866791</v>
       </c>
       <c r="H838" t="n">
         <v>377864</v>
@@ -24729,7 +24729,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G840" t="n">
-        <v>1.72063088417053</v>
+        <v>1.72063100337982</v>
       </c>
       <c r="H840" t="n">
         <v>770563</v>
@@ -24758,7 +24758,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>1.67985761165619</v>
+        <v>1.67985773086548</v>
       </c>
       <c r="H841" t="n">
         <v>1113545</v>
@@ -24787,7 +24787,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G842" t="n">
-        <v>1.66028654575348</v>
+        <v>1.66028666496277</v>
       </c>
       <c r="H842" t="n">
         <v>1706967</v>
@@ -24816,7 +24816,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G843" t="n">
-        <v>1.63908445835114</v>
+        <v>1.63908457756042</v>
       </c>
       <c r="H843" t="n">
         <v>1322486</v>
@@ -24845,7 +24845,7 @@
         <v>1.90299999713898</v>
       </c>
       <c r="G844" t="n">
-        <v>1.5518296957016</v>
+        <v>1.55182981491089</v>
       </c>
       <c r="H844" t="n">
         <v>4032631</v>
@@ -24903,7 +24903,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G846" t="n">
-        <v>1.51676464080811</v>
+        <v>1.5167647600174</v>
       </c>
       <c r="H846" t="n">
         <v>2988966</v>
@@ -24932,7 +24932,7 @@
         <v>1.89800000190735</v>
       </c>
       <c r="G847" t="n">
-        <v>1.54775238037109</v>
+        <v>1.54775249958038</v>
       </c>
       <c r="H847" t="n">
         <v>1669046</v>
@@ -24961,7 +24961,7 @@
         <v>1.86800003051758</v>
       </c>
       <c r="G848" t="n">
-        <v>1.52328824996948</v>
+        <v>1.52328848838806</v>
       </c>
       <c r="H848" t="n">
         <v>1102200</v>
@@ -24990,7 +24990,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G849" t="n">
-        <v>1.49148535728455</v>
+        <v>1.49148523807526</v>
       </c>
       <c r="H849" t="n">
         <v>955483</v>
@@ -25019,7 +25019,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G850" t="n">
-        <v>1.43929553031921</v>
+        <v>1.43929541110992</v>
       </c>
       <c r="H850" t="n">
         <v>1026199</v>
@@ -25048,7 +25048,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G851" t="n">
-        <v>1.42543256282806</v>
+        <v>1.42543268203735</v>
       </c>
       <c r="H851" t="n">
         <v>880260</v>
@@ -25077,7 +25077,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G852" t="n">
-        <v>1.40830790996552</v>
+        <v>1.4083080291748</v>
       </c>
       <c r="H852" t="n">
         <v>1055190</v>
@@ -25193,7 +25193,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G856" t="n">
-        <v>1.36345732212067</v>
+        <v>1.36345744132996</v>
       </c>
       <c r="H856" t="n">
         <v>726614</v>
@@ -25222,7 +25222,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G857" t="n">
-        <v>1.4034149646759</v>
+        <v>1.40341520309448</v>
       </c>
       <c r="H857" t="n">
         <v>480477</v>
@@ -25309,7 +25309,7 @@
         <v>1.72699999809265</v>
       </c>
       <c r="G860" t="n">
-        <v>1.40830790996552</v>
+        <v>1.4083080291748</v>
       </c>
       <c r="H860" t="n">
         <v>331863</v>
@@ -25338,7 +25338,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G861" t="n">
-        <v>1.39281404018402</v>
+        <v>1.39281415939331</v>
       </c>
       <c r="H861" t="n">
         <v>257728</v>
@@ -25367,7 +25367,7 @@
         <v>1.65799999237061</v>
       </c>
       <c r="G862" t="n">
-        <v>1.35204100608826</v>
+        <v>1.35204088687897</v>
       </c>
       <c r="H862" t="n">
         <v>465276</v>
@@ -25396,7 +25396,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G863" t="n">
-        <v>1.38221323490143</v>
+        <v>1.38221311569214</v>
       </c>
       <c r="H863" t="n">
         <v>444989</v>
@@ -25454,7 +25454,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G865" t="n">
-        <v>1.39770686626434</v>
+        <v>1.39770674705505</v>
       </c>
       <c r="H865" t="n">
         <v>690821</v>
@@ -25570,7 +25570,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G869" t="n">
-        <v>1.39770686626434</v>
+        <v>1.39770674705505</v>
       </c>
       <c r="H869" t="n">
         <v>452853</v>
@@ -25599,7 +25599,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G870" t="n">
-        <v>1.44989657402039</v>
+        <v>1.44989669322968</v>
       </c>
       <c r="H870" t="n">
         <v>1022788</v>
@@ -25628,7 +25628,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G871" t="n">
-        <v>1.47599148750305</v>
+        <v>1.47599136829376</v>
       </c>
       <c r="H871" t="n">
         <v>608455</v>
@@ -25686,7 +25686,7 @@
         <v>1.81400001049042</v>
       </c>
       <c r="G873" t="n">
-        <v>1.47925329208374</v>
+        <v>1.47925317287445</v>
       </c>
       <c r="H873" t="n">
         <v>295354</v>
@@ -25715,7 +25715,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G874" t="n">
-        <v>1.52491939067841</v>
+        <v>1.52491927146912</v>
       </c>
       <c r="H874" t="n">
         <v>551183</v>
@@ -25744,7 +25744,7 @@
         <v>1.875</v>
       </c>
       <c r="G875" t="n">
-        <v>1.52899694442749</v>
+        <v>1.5289968252182</v>
       </c>
       <c r="H875" t="n">
         <v>341943</v>
@@ -25802,7 +25802,7 @@
         <v>1.875</v>
       </c>
       <c r="G877" t="n">
-        <v>1.52899694442749</v>
+        <v>1.5289968252182</v>
       </c>
       <c r="H877" t="n">
         <v>428422</v>
@@ -25918,7 +25918,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G881" t="n">
-        <v>1.45886659622192</v>
+        <v>1.45886671543121</v>
       </c>
       <c r="H881" t="n">
         <v>1315058</v>
@@ -25947,7 +25947,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G882" t="n">
-        <v>1.45886659622192</v>
+        <v>1.45886671543121</v>
       </c>
       <c r="H882" t="n">
         <v>276357</v>
@@ -25976,7 +25976,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G883" t="n">
-        <v>1.45152759552002</v>
+        <v>1.45152747631073</v>
       </c>
       <c r="H883" t="n">
         <v>362785</v>
@@ -26034,7 +26034,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G885" t="n">
-        <v>1.44989657402039</v>
+        <v>1.44989669322968</v>
       </c>
       <c r="H885" t="n">
         <v>2306619</v>
@@ -26063,7 +26063,7 @@
         <v>1.77699995040894</v>
       </c>
       <c r="G886" t="n">
-        <v>1.44908130168915</v>
+        <v>1.44908118247986</v>
       </c>
       <c r="H886" t="n">
         <v>474750</v>
@@ -26092,7 +26092,7 @@
         <v>1.75399994850159</v>
       </c>
       <c r="G887" t="n">
-        <v>1.4303252696991</v>
+        <v>1.43032550811768</v>
       </c>
       <c r="H887" t="n">
         <v>746913</v>
@@ -26150,7 +26150,7 @@
         <v>1.77799999713898</v>
       </c>
       <c r="G889" t="n">
-        <v>1.44989657402039</v>
+        <v>1.44989669322968</v>
       </c>
       <c r="H889" t="n">
         <v>308646</v>
@@ -26208,7 +26208,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G891" t="n">
-        <v>1.52573490142822</v>
+        <v>1.52573502063751</v>
       </c>
       <c r="H891" t="n">
         <v>1176195</v>
@@ -26237,7 +26237,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G892" t="n">
-        <v>1.58689486980438</v>
+        <v>1.5868946313858</v>
       </c>
       <c r="H892" t="n">
         <v>2742260</v>
@@ -26295,7 +26295,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G894" t="n">
-        <v>1.57058548927307</v>
+        <v>1.57058537006378</v>
       </c>
       <c r="H894" t="n">
         <v>1453003</v>
@@ -26353,7 +26353,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G896" t="n">
-        <v>1.51676464080811</v>
+        <v>1.5167647600174</v>
       </c>
       <c r="H896" t="n">
         <v>516545</v>
@@ -26411,7 +26411,7 @@
         <v>1.79100000858307</v>
       </c>
       <c r="G898" t="n">
-        <v>1.46049773693085</v>
+        <v>1.46049761772156</v>
       </c>
       <c r="H898" t="n">
         <v>1349408</v>
@@ -26498,7 +26498,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G901" t="n">
-        <v>1.33246958255768</v>
+        <v>1.33246982097626</v>
       </c>
       <c r="H901" t="n">
         <v>3767205</v>
@@ -26556,7 +26556,7 @@
         <v>1.51300001144409</v>
       </c>
       <c r="G903" t="n">
-        <v>1.23379850387573</v>
+        <v>1.23379838466644</v>
       </c>
       <c r="H903" t="n">
         <v>1637956</v>
@@ -26614,7 +26614,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G905" t="n">
-        <v>1.27049434185028</v>
+        <v>1.27049422264099</v>
       </c>
       <c r="H905" t="n">
         <v>1458633</v>
@@ -26672,7 +26672,7 @@
         <v>1.68900001049042</v>
       </c>
       <c r="G907" t="n">
-        <v>1.37732017040253</v>
+        <v>1.37732040882111</v>
       </c>
       <c r="H907" t="n">
         <v>2492653</v>
@@ -26701,7 +26701,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G908" t="n">
-        <v>1.3536719083786</v>
+        <v>1.35367178916931</v>
       </c>
       <c r="H908" t="n">
         <v>1043256</v>
@@ -26875,7 +26875,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G914" t="n">
-        <v>1.54122865200043</v>
+        <v>1.54122877120972</v>
       </c>
       <c r="H914" t="n">
         <v>1837118</v>
@@ -26904,7 +26904,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G915" t="n">
-        <v>1.51024091243744</v>
+        <v>1.51024103164673</v>
       </c>
       <c r="H915" t="n">
         <v>2409241</v>
@@ -26933,7 +26933,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G916" t="n">
-        <v>1.54122865200043</v>
+        <v>1.54122877120972</v>
       </c>
       <c r="H916" t="n">
         <v>871736</v>
@@ -26962,7 +26962,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G917" t="n">
-        <v>1.55753803253174</v>
+        <v>1.55753791332245</v>
       </c>
       <c r="H917" t="n">
         <v>1214649</v>
@@ -27020,7 +27020,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G919" t="n">
-        <v>1.41727793216705</v>
+        <v>1.41727805137634</v>
       </c>
       <c r="H919" t="n">
         <v>3017439</v>
@@ -27078,7 +27078,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G921" t="n">
-        <v>1.4034149646759</v>
+        <v>1.40341520309448</v>
       </c>
       <c r="H921" t="n">
         <v>457312</v>
@@ -27136,7 +27136,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G923" t="n">
-        <v>1.45968210697174</v>
+        <v>1.45968222618103</v>
       </c>
       <c r="H923" t="n">
         <v>650528</v>
@@ -27165,7 +27165,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G924" t="n">
-        <v>1.44092643260956</v>
+        <v>1.44092631340027</v>
       </c>
       <c r="H924" t="n">
         <v>445435</v>
@@ -27194,7 +27194,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G925" t="n">
-        <v>1.45478928089142</v>
+        <v>1.45478963851929</v>
       </c>
       <c r="H925" t="n">
         <v>495556</v>
@@ -27339,7 +27339,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G930" t="n">
-        <v>1.46539056301117</v>
+        <v>1.46539044380188</v>
       </c>
       <c r="H930" t="n">
         <v>521674</v>
@@ -27484,7 +27484,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G935" t="n">
-        <v>1.45152759552002</v>
+        <v>1.45152747631073</v>
       </c>
       <c r="H935" t="n">
         <v>676456</v>
@@ -27513,7 +27513,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G936" t="n">
-        <v>1.45152759552002</v>
+        <v>1.45152747631073</v>
       </c>
       <c r="H936" t="n">
         <v>484220</v>
@@ -27542,7 +27542,7 @@
         <v>1.79200005531311</v>
       </c>
       <c r="G937" t="n">
-        <v>1.46131312847137</v>
+        <v>1.46131324768066</v>
       </c>
       <c r="H937" t="n">
         <v>276015</v>
@@ -27600,7 +27600,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G939" t="n">
-        <v>1.47680699825287</v>
+        <v>1.47680687904358</v>
       </c>
       <c r="H939" t="n">
         <v>314613</v>
@@ -27629,7 +27629,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G940" t="n">
-        <v>1.47680699825287</v>
+        <v>1.47680687904358</v>
       </c>
       <c r="H940" t="n">
         <v>612587</v>
@@ -27658,7 +27658,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G941" t="n">
-        <v>1.57955551147461</v>
+        <v>1.5795556306839</v>
       </c>
       <c r="H941" t="n">
         <v>1907959</v>
@@ -27716,7 +27716,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.67170310020447</v>
+        <v>1.67170298099518</v>
       </c>
       <c r="H943" t="n">
         <v>2434409</v>
@@ -27774,7 +27774,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G945" t="n">
-        <v>1.73041653633118</v>
+        <v>1.73041641712189</v>
       </c>
       <c r="H945" t="n">
         <v>2501849</v>
@@ -27803,7 +27803,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>1.66354835033417</v>
+        <v>1.66354846954346</v>
       </c>
       <c r="H946" t="n">
         <v>2684227</v>
@@ -27832,7 +27832,7 @@
         <v>2.04200005531311</v>
       </c>
       <c r="G947" t="n">
-        <v>1.66517949104309</v>
+        <v>1.6651793718338</v>
       </c>
       <c r="H947" t="n">
         <v>727311</v>
@@ -27861,7 +27861,7 @@
         <v>2.0239999294281</v>
       </c>
       <c r="G948" t="n">
-        <v>1.65050101280212</v>
+        <v>1.65050089359283</v>
       </c>
       <c r="H948" t="n">
         <v>447219</v>
@@ -27890,7 +27890,7 @@
         <v>2.06200003623962</v>
       </c>
       <c r="G949" t="n">
-        <v>1.68148875236511</v>
+        <v>1.68148863315582</v>
       </c>
       <c r="H949" t="n">
         <v>561915</v>
@@ -27919,7 +27919,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G950" t="n">
-        <v>1.65702486038208</v>
+        <v>1.65702474117279</v>
       </c>
       <c r="H950" t="n">
         <v>604544</v>
@@ -27948,7 +27948,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G951" t="n">
-        <v>1.67496478557587</v>
+        <v>1.67496490478516</v>
       </c>
       <c r="H951" t="n">
         <v>449178</v>
@@ -27977,7 +27977,7 @@
         <v>2.01200008392334</v>
       </c>
       <c r="G952" t="n">
-        <v>1.64071536064148</v>
+        <v>1.64071547985077</v>
       </c>
       <c r="H952" t="n">
         <v>314585</v>
@@ -28006,7 +28006,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G953" t="n">
-        <v>1.63256072998047</v>
+        <v>1.63256084918976</v>
       </c>
       <c r="H953" t="n">
         <v>297419</v>
@@ -28122,7 +28122,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G957" t="n">
-        <v>1.57547807693481</v>
+        <v>1.5754781961441</v>
       </c>
       <c r="H957" t="n">
         <v>698341</v>
@@ -28151,7 +28151,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G958" t="n">
-        <v>1.57058548927307</v>
+        <v>1.57058537006378</v>
       </c>
       <c r="H958" t="n">
         <v>358093</v>
@@ -28209,7 +28209,7 @@
         <v>1.85599994659424</v>
       </c>
       <c r="G960" t="n">
-        <v>1.51350283622742</v>
+        <v>1.51350271701813</v>
       </c>
       <c r="H960" t="n">
         <v>1017531</v>
@@ -28238,7 +28238,7 @@
         <v>1.89199995994568</v>
       </c>
       <c r="G961" t="n">
-        <v>1.54285967350006</v>
+        <v>1.54285955429077</v>
       </c>
       <c r="H961" t="n">
         <v>444176</v>
@@ -28267,7 +28267,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G962" t="n">
-        <v>1.55753803253174</v>
+        <v>1.55753791332245</v>
       </c>
       <c r="H962" t="n">
         <v>432157</v>
@@ -28325,7 +28325,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G964" t="n">
-        <v>1.55019867420197</v>
+        <v>1.55019879341125</v>
       </c>
       <c r="H964" t="n">
         <v>472301</v>
@@ -28383,7 +28383,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G966" t="n">
-        <v>1.57955551147461</v>
+        <v>1.5795556306839</v>
       </c>
       <c r="H966" t="n">
         <v>770616</v>
@@ -28499,7 +28499,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G970" t="n">
-        <v>1.53307402133942</v>
+        <v>1.53307414054871</v>
       </c>
       <c r="H970" t="n">
         <v>1687835</v>
@@ -28528,7 +28528,7 @@
         <v>1.875</v>
       </c>
       <c r="G971" t="n">
-        <v>1.52899694442749</v>
+        <v>1.5289968252182</v>
       </c>
       <c r="H971" t="n">
         <v>1073312</v>
@@ -28557,7 +28557,7 @@
         <v>1.86300003528595</v>
       </c>
       <c r="G972" t="n">
-        <v>1.51921105384827</v>
+        <v>1.51921117305756</v>
       </c>
       <c r="H972" t="n">
         <v>814738</v>
@@ -28586,7 +28586,7 @@
         <v>1.8309999704361</v>
       </c>
       <c r="G973" t="n">
-        <v>1.4931161403656</v>
+        <v>1.49311625957489</v>
       </c>
       <c r="H973" t="n">
         <v>788984</v>
@@ -28615,7 +28615,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G974" t="n">
-        <v>1.52002656459808</v>
+        <v>1.52002644538879</v>
       </c>
       <c r="H974" t="n">
         <v>392240</v>
@@ -28644,7 +28644,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G975" t="n">
-        <v>1.48740804195404</v>
+        <v>1.48740816116333</v>
       </c>
       <c r="H975" t="n">
         <v>965861</v>
@@ -28702,7 +28702,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G977" t="n">
-        <v>1.4898544549942</v>
+        <v>1.48985457420349</v>
       </c>
       <c r="H977" t="n">
         <v>461421</v>
@@ -28731,7 +28731,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G978" t="n">
-        <v>1.46212875843048</v>
+        <v>1.4621285200119</v>
       </c>
       <c r="H978" t="n">
         <v>2195345</v>
@@ -28760,7 +28760,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G979" t="n">
-        <v>1.45968210697174</v>
+        <v>1.45968222618103</v>
       </c>
       <c r="H979" t="n">
         <v>1897039</v>
@@ -28789,7 +28789,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G980" t="n">
-        <v>1.45968210697174</v>
+        <v>1.45968222618103</v>
       </c>
       <c r="H980" t="n">
         <v>899353</v>
@@ -28905,7 +28905,7 @@
         <v>1.85099995136261</v>
       </c>
       <c r="G984" t="n">
-        <v>1.5094256401062</v>
+        <v>1.50942540168762</v>
       </c>
       <c r="H984" t="n">
         <v>15216437</v>
@@ -28934,7 +28934,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G985" t="n">
-        <v>1.49556279182434</v>
+        <v>1.49556267261505</v>
       </c>
       <c r="H985" t="n">
         <v>8238334</v>
@@ -28963,7 +28963,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G986" t="n">
-        <v>1.48414599895477</v>
+        <v>1.48414623737335</v>
       </c>
       <c r="H986" t="n">
         <v>3078600</v>
@@ -29021,7 +29021,7 @@
         <v>1.76699995994568</v>
       </c>
       <c r="G988" t="n">
-        <v>1.44092643260956</v>
+        <v>1.44092631340027</v>
       </c>
       <c r="H988" t="n">
         <v>1635432</v>
@@ -29050,7 +29050,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G989" t="n">
-        <v>1.41320085525513</v>
+        <v>1.41320073604584</v>
       </c>
       <c r="H989" t="n">
         <v>2882134</v>
@@ -29079,7 +29079,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G990" t="n">
-        <v>1.39036762714386</v>
+        <v>1.39036774635315</v>
       </c>
       <c r="H990" t="n">
         <v>2466626</v>
@@ -29108,7 +29108,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.38221323490143</v>
+        <v>1.38221311569214</v>
       </c>
       <c r="H991" t="n">
         <v>1472350</v>
@@ -29166,7 +29166,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G993" t="n">
-        <v>1.43114101886749</v>
+        <v>1.4311408996582</v>
       </c>
       <c r="H993" t="n">
         <v>4664408</v>
@@ -29224,7 +29224,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G995" t="n">
-        <v>1.46212875843048</v>
+        <v>1.4621285200119</v>
       </c>
       <c r="H995" t="n">
         <v>4135413</v>
@@ -29253,7 +29253,7 @@
         <v>1.76800000667572</v>
       </c>
       <c r="G996" t="n">
-        <v>1.44174182415009</v>
+        <v>1.44174194335938</v>
       </c>
       <c r="H996" t="n">
         <v>1816638</v>
@@ -29282,7 +29282,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G997" t="n">
-        <v>1.44337284564972</v>
+        <v>1.44337296485901</v>
       </c>
       <c r="H997" t="n">
         <v>1986347</v>
@@ -29311,7 +29311,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>1.39444494247437</v>
+        <v>1.39444506168365</v>
       </c>
       <c r="H998" t="n">
         <v>2423018</v>
@@ -29427,7 +29427,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.41727793216705</v>
+        <v>1.41727805137634</v>
       </c>
       <c r="H1002" t="n">
         <v>1850120</v>
@@ -29456,7 +29456,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.39199876785278</v>
+        <v>1.39199864864349</v>
       </c>
       <c r="H1003" t="n">
         <v>1669083</v>
@@ -29485,7 +29485,7 @@
         <v>1.70700001716614</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.39199876785278</v>
+        <v>1.39199864864349</v>
       </c>
       <c r="H1004" t="n">
         <v>964142</v>
@@ -29543,7 +29543,7 @@
         <v>1.682000041008</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.37161195278168</v>
+        <v>1.37161207199097</v>
       </c>
       <c r="H1006" t="n">
         <v>1637952</v>
@@ -29572,7 +29572,7 @@
         <v>1.65100002288818</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.34633255004883</v>
+        <v>1.34633278846741</v>
       </c>
       <c r="H1007" t="n">
         <v>2611930</v>
@@ -29688,7 +29688,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.33573162555695</v>
+        <v>1.33573150634766</v>
       </c>
       <c r="H1011" t="n">
         <v>1741918</v>
@@ -29775,7 +29775,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.32268416881561</v>
+        <v>1.32268404960632</v>
       </c>
       <c r="H1014" t="n">
         <v>1216109</v>
@@ -29862,7 +29862,7 @@
         <v>1.61699998378754</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.31860685348511</v>
+        <v>1.31860661506653</v>
       </c>
       <c r="H1017" t="n">
         <v>3637322</v>
@@ -29891,7 +29891,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.28843474388123</v>
+        <v>1.28843450546265</v>
       </c>
       <c r="H1018" t="n">
         <v>1970341</v>
@@ -29920,7 +29920,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.30474400520325</v>
+        <v>1.30474388599396</v>
       </c>
       <c r="H1019" t="n">
         <v>1457803</v>
@@ -29949,7 +29949,7 @@
         <v>1.59700000286102</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.3022974729538</v>
+        <v>1.30229735374451</v>
       </c>
       <c r="H1020" t="n">
         <v>1207943</v>
@@ -29978,7 +29978,7 @@
         <v>1.61600005626678</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.31779146194458</v>
+        <v>1.317791223526</v>
       </c>
       <c r="H1021" t="n">
         <v>1664512</v>
@@ -30007,7 +30007,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.32268416881561</v>
+        <v>1.32268404960632</v>
       </c>
       <c r="H1022" t="n">
         <v>1384826</v>
@@ -30036,7 +30036,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.33817803859711</v>
+        <v>1.33817791938782</v>
       </c>
       <c r="H1023" t="n">
         <v>1463844</v>
@@ -30065,7 +30065,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.3332850933075</v>
+        <v>1.33328521251678</v>
       </c>
       <c r="H1024" t="n">
         <v>1949168</v>
@@ -30094,7 +30094,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.32431507110596</v>
+        <v>1.32431495189667</v>
       </c>
       <c r="H1025" t="n">
         <v>1894862</v>
@@ -30123,7 +30123,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.32105314731598</v>
+        <v>1.32105302810669</v>
       </c>
       <c r="H1026" t="n">
         <v>1110494</v>
@@ -30181,7 +30181,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.30474400520325</v>
+        <v>1.30474388599396</v>
       </c>
       <c r="H1028" t="n">
         <v>2569962</v>
@@ -30210,7 +30210,7 @@
         <v>1.57599997520447</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.28517270088196</v>
+        <v>1.28517293930054</v>
       </c>
       <c r="H1029" t="n">
         <v>2106241</v>
@@ -30297,7 +30297,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.27212524414062</v>
+        <v>1.27212512493134</v>
       </c>
       <c r="H1032" t="n">
         <v>2267819</v>
@@ -30326,7 +30326,7 @@
         <v>1.51699995994568</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.23706018924713</v>
+        <v>1.23706030845642</v>
       </c>
       <c r="H1033" t="n">
         <v>2193205</v>
@@ -30413,7 +30413,7 @@
         <v>1.49699997901917</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.22075092792511</v>
+        <v>1.2207510471344</v>
       </c>
       <c r="H1036" t="n">
         <v>2935812</v>
@@ -30471,7 +30471,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.17834687232971</v>
+        <v>1.17834675312042</v>
       </c>
       <c r="H1038" t="n">
         <v>2286641</v>
@@ -30529,7 +30529,7 @@
         <v>1.49600005149841</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.21993553638458</v>
+        <v>1.21993565559387</v>
       </c>
       <c r="H1040" t="n">
         <v>2375077</v>
@@ -30558,7 +30558,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.21504282951355</v>
+        <v>1.21504271030426</v>
       </c>
       <c r="H1041" t="n">
         <v>1855988</v>
@@ -30645,7 +30645,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.21259617805481</v>
+        <v>1.2125962972641</v>
       </c>
       <c r="H1044" t="n">
         <v>2340167</v>
@@ -30732,7 +30732,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.20851910114288</v>
+        <v>1.20851898193359</v>
       </c>
       <c r="H1047" t="n">
         <v>1310560</v>
@@ -30819,7 +30819,7 @@
         <v>1.48699998855591</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.21259617805481</v>
+        <v>1.2125962972641</v>
       </c>
       <c r="H1050" t="n">
         <v>1442692</v>
@@ -30848,7 +30848,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.23298299312592</v>
+        <v>1.23298287391663</v>
       </c>
       <c r="H1051" t="n">
         <v>4186263</v>
@@ -30877,7 +30877,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.19057881832123</v>
+        <v>1.19057869911194</v>
       </c>
       <c r="H1052" t="n">
         <v>3034895</v>
@@ -30906,7 +30906,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.0845685005188</v>
+        <v>1.08456838130951</v>
       </c>
       <c r="H1053" t="n">
         <v>6068429</v>
@@ -30964,7 +30964,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.13349616527557</v>
+        <v>1.13349628448486</v>
       </c>
       <c r="H1055" t="n">
         <v>2667646</v>
@@ -31022,7 +31022,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.08538377285004</v>
+        <v>1.08538389205933</v>
       </c>
       <c r="H1057" t="n">
         <v>4048851</v>
@@ -31051,7 +31051,7 @@
         <v>1.29900002479553</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.05928897857666</v>
+        <v>1.05928909778595</v>
       </c>
       <c r="H1058" t="n">
         <v>4847716</v>
@@ -31080,7 +31080,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.03400933742523</v>
+        <v>1.03400945663452</v>
       </c>
       <c r="H1059" t="n">
         <v>2652066</v>
@@ -31138,7 +31138,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.988343477249146</v>
+        <v>0.988343417644501</v>
       </c>
       <c r="H1061" t="n">
         <v>4115706</v>
@@ -31196,7 +31196,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.804048299789429</v>
+        <v>0.804048418998718</v>
       </c>
       <c r="H1063" t="n">
         <v>4912177</v>
@@ -31225,7 +31225,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.760013282299042</v>
+        <v>0.760013222694397</v>
       </c>
       <c r="H1064" t="n">
         <v>6550694</v>
@@ -31254,7 +31254,7 @@
         <v>0.922500014305115</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.752266466617584</v>
+        <v>0.752266407012939</v>
       </c>
       <c r="H1065" t="n">
         <v>5103415</v>
@@ -31341,7 +31341,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.593658447265625</v>
+        <v>0.59365850687027</v>
       </c>
       <c r="H1068" t="n">
         <v>5402453</v>
@@ -31428,7 +31428,7 @@
         <v>0.959999978542328</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.78284627199173</v>
+        <v>0.782846331596375</v>
       </c>
       <c r="H1071" t="n">
         <v>4009260</v>
@@ -31457,7 +31457,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.858684539794922</v>
+        <v>0.858684480190277</v>
       </c>
       <c r="H1072" t="n">
         <v>4219076</v>
@@ -31602,7 +31602,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.870916545391083</v>
+        <v>0.870916604995728</v>
       </c>
       <c r="H1077" t="n">
         <v>1971172</v>
@@ -31631,7 +31631,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.91332072019577</v>
+        <v>0.913320660591125</v>
       </c>
       <c r="H1078" t="n">
         <v>1366165</v>
@@ -31660,7 +31660,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.950832068920135</v>
+        <v>0.950832188129425</v>
       </c>
       <c r="H1079" t="n">
         <v>2082037</v>
@@ -31689,7 +31689,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.939415574073792</v>
+        <v>0.939415633678436</v>
       </c>
       <c r="H1080" t="n">
         <v>655666</v>
@@ -31747,7 +31747,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.951647520065308</v>
+        <v>0.951647579669952</v>
       </c>
       <c r="H1082" t="n">
         <v>443405</v>
@@ -31805,7 +31805,7 @@
         <v>1.12800002098083</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.919844448566437</v>
+        <v>0.919844567775726</v>
       </c>
       <c r="H1084" t="n">
         <v>3047345</v>
@@ -31834,7 +31834,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.95654022693634</v>
+        <v>0.956540286540985</v>
       </c>
       <c r="H1085" t="n">
         <v>1486613</v>
@@ -31863,7 +31863,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.02177751064301</v>
+        <v>1.02177739143372</v>
       </c>
       <c r="H1086" t="n">
         <v>5524167</v>
@@ -31892,7 +31892,7 @@
         <v>1.29100000858307</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.05276536941528</v>
+        <v>1.05276525020599</v>
       </c>
       <c r="H1087" t="n">
         <v>4106371</v>
@@ -31921,7 +31921,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.998129189014435</v>
+        <v>0.998129069805145</v>
       </c>
       <c r="H1088" t="n">
         <v>2104508</v>
@@ -31979,7 +31979,7 @@
         <v>1.30900001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.06744360923767</v>
+        <v>1.06744349002838</v>
       </c>
       <c r="H1090" t="n">
         <v>2209568</v>
@@ -32037,7 +32037,7 @@
         <v>1.33899998664856</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.0919075012207</v>
+        <v>1.09190773963928</v>
       </c>
       <c r="H1092" t="n">
         <v>1156803</v>
@@ -32066,7 +32066,7 @@
         <v>1.3309999704361</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.08538377285004</v>
+        <v>1.08538389205933</v>
       </c>
       <c r="H1093" t="n">
         <v>1097046</v>
@@ -32182,7 +32182,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.09924674034119</v>
+        <v>1.0992466211319</v>
       </c>
       <c r="H1097" t="n">
         <v>2452809</v>
@@ -32211,7 +32211,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.11310958862305</v>
+        <v>1.11310946941376</v>
       </c>
       <c r="H1098" t="n">
         <v>2249016</v>
@@ -32269,7 +32269,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.09272301197052</v>
+        <v>1.09272289276123</v>
       </c>
       <c r="H1100" t="n">
         <v>1093846</v>
@@ -32327,7 +32327,7 @@
         <v>1.34899997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.10006201267242</v>
+        <v>1.10006213188171</v>
       </c>
       <c r="H1102" t="n">
         <v>427120</v>
@@ -32356,7 +32356,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.06662821769714</v>
+        <v>1.06662809848785</v>
       </c>
       <c r="H1103" t="n">
         <v>840686</v>
@@ -32385,7 +32385,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.06010437011719</v>
+        <v>1.06010448932648</v>
       </c>
       <c r="H1104" t="n">
         <v>3327803</v>
@@ -32414,7 +32414,7 @@
         <v>1.31900000572205</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.07559812068939</v>
+        <v>1.07559823989868</v>
       </c>
       <c r="H1105" t="n">
         <v>463491</v>
@@ -32559,7 +32559,7 @@
         <v>1.26300001144409</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.05486989021301</v>
+        <v>1.05487012863159</v>
       </c>
       <c r="H1110" t="n">
         <v>531961</v>
@@ -32588,7 +32588,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.979700982570648</v>
+        <v>0.979701042175293</v>
       </c>
       <c r="H1111" t="n">
         <v>3876340</v>
@@ -32675,7 +32675,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.02563774585724</v>
+        <v>1.02563762664795</v>
       </c>
       <c r="H1114" t="n">
         <v>1582972</v>
@@ -32733,7 +32733,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.05737578868866</v>
+        <v>1.05737566947937</v>
       </c>
       <c r="H1116" t="n">
         <v>1440577</v>
@@ -32878,7 +32878,7 @@
         <v>1.2960000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.08243203163147</v>
+        <v>1.08243191242218</v>
       </c>
       <c r="H1121" t="n">
         <v>1294125</v>
@@ -32907,7 +32907,7 @@
         <v>1.36099994182587</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.13672053813934</v>
+        <v>1.13672065734863</v>
       </c>
       <c r="H1122" t="n">
         <v>2770265</v>
@@ -32936,7 +32936,7 @@
         <v>1.43099999427795</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.19518518447876</v>
+        <v>1.19518530368805</v>
       </c>
       <c r="H1123" t="n">
         <v>4288487</v>
@@ -33081,7 +33081,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.08660781383514</v>
+        <v>1.08660805225372</v>
       </c>
       <c r="H1128" t="n">
         <v>2648710</v>
@@ -33139,7 +33139,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.11082923412323</v>
+        <v>1.11082911491394</v>
       </c>
       <c r="H1130" t="n">
         <v>1128829</v>
@@ -33168,7 +33168,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.23026406764984</v>
+        <v>1.23026418685913</v>
       </c>
       <c r="H1131" t="n">
         <v>6561575</v>
@@ -33197,7 +33197,7 @@
         <v>1.44700002670288</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.20854866504669</v>
+        <v>1.2085485458374</v>
       </c>
       <c r="H1132" t="n">
         <v>2622105</v>
@@ -33255,7 +33255,7 @@
         <v>1.47300004959106</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.23026406764984</v>
+        <v>1.23026418685913</v>
       </c>
       <c r="H1134" t="n">
         <v>2095844</v>
@@ -33342,7 +33342,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.17597556114197</v>
+        <v>1.17597544193268</v>
       </c>
       <c r="H1137" t="n">
         <v>1151867</v>
@@ -33458,7 +33458,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.16511762142181</v>
+        <v>1.1651177406311</v>
       </c>
       <c r="H1141" t="n">
         <v>1238514</v>
@@ -33487,7 +33487,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.140061378479</v>
+        <v>1.14006125926971</v>
       </c>
       <c r="H1142" t="n">
         <v>810784</v>
@@ -33516,7 +33516,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.17597556114197</v>
+        <v>1.17597544193268</v>
       </c>
       <c r="H1143" t="n">
         <v>748993</v>
@@ -33574,7 +33574,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.18599796295166</v>
+        <v>1.18599808216095</v>
       </c>
       <c r="H1145" t="n">
         <v>1023147</v>
@@ -33603,7 +33603,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.19435000419617</v>
+        <v>1.19434988498688</v>
       </c>
       <c r="H1146" t="n">
         <v>662446</v>
@@ -33661,7 +33661,7 @@
         <v>1.43499994277954</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.19852602481842</v>
+        <v>1.19852614402771</v>
       </c>
       <c r="H1148" t="n">
         <v>8763913</v>
@@ -33690,7 +33690,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.17346966266632</v>
+        <v>1.17346978187561</v>
       </c>
       <c r="H1149" t="n">
         <v>1614825</v>
@@ -33777,7 +33777,7 @@
         <v>1.45299994945526</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.21355974674225</v>
+        <v>1.21355986595154</v>
       </c>
       <c r="H1152" t="n">
         <v>3560690</v>
@@ -33806,7 +33806,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.19435000419617</v>
+        <v>1.19434988498688</v>
       </c>
       <c r="H1153" t="n">
         <v>2312871</v>
@@ -33980,7 +33980,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.16177678108215</v>
+        <v>1.16177690029144</v>
       </c>
       <c r="H1159" t="n">
         <v>1134501</v>
@@ -34009,7 +34009,7 @@
         <v>1.32299995422363</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.10498237609863</v>
+        <v>1.10498261451721</v>
       </c>
       <c r="H1160" t="n">
         <v>2253150</v>
@@ -34038,7 +34038,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.10247695446014</v>
+        <v>1.10247707366943</v>
       </c>
       <c r="H1161" t="n">
         <v>1753450</v>
@@ -34125,7 +34125,7 @@
         <v>1.08899998664856</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.909543514251709</v>
+        <v>0.909543454647064</v>
       </c>
       <c r="H1164" t="n">
         <v>3448371</v>
@@ -34183,7 +34183,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.935434997081757</v>
+        <v>0.935434937477112</v>
       </c>
       <c r="H1166" t="n">
         <v>3217787</v>
@@ -34212,7 +34212,7 @@
         <v>1.09899997711182</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.917895495891571</v>
+        <v>0.917895555496216</v>
       </c>
       <c r="H1167" t="n">
         <v>2532403</v>
@@ -34299,7 +34299,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.918730735778809</v>
+        <v>0.918730795383453</v>
       </c>
       <c r="H1170" t="n">
         <v>1314740</v>
@@ -34328,7 +34328,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.935434997081757</v>
+        <v>0.935434937477112</v>
       </c>
       <c r="H1171" t="n">
         <v>2331133</v>
@@ -34444,7 +34444,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.945457458496094</v>
+        <v>0.945457518100739</v>
       </c>
       <c r="H1175" t="n">
         <v>642129</v>
@@ -34473,7 +34473,7 @@
         <v>1.125</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.939611077308655</v>
+        <v>0.93961101770401</v>
       </c>
       <c r="H1176" t="n">
         <v>937169</v>
@@ -34502,7 +34502,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.937940657138824</v>
+        <v>0.93794059753418</v>
       </c>
       <c r="H1177" t="n">
         <v>740490</v>
@@ -34560,7 +34560,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.915389835834503</v>
+        <v>0.915389895439148</v>
       </c>
       <c r="H1179" t="n">
         <v>613195</v>
@@ -34618,7 +34618,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.918730735778809</v>
+        <v>0.918730795383453</v>
       </c>
       <c r="H1181" t="n">
         <v>976233</v>
@@ -34647,7 +34647,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.910378754138947</v>
+        <v>0.910378813743591</v>
       </c>
       <c r="H1182" t="n">
         <v>1095902</v>
@@ -34676,7 +34676,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.917060434818268</v>
+        <v>0.917060494422913</v>
       </c>
       <c r="H1183" t="n">
         <v>768682</v>
@@ -34705,7 +34705,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.917060434818268</v>
+        <v>0.917060494422913</v>
       </c>
       <c r="H1184" t="n">
         <v>876059</v>
@@ -34792,7 +34792,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.905367493629456</v>
+        <v>0.905367434024811</v>
       </c>
       <c r="H1187" t="n">
         <v>1392144</v>
@@ -34821,7 +34821,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.903697073459625</v>
+        <v>0.90369701385498</v>
       </c>
       <c r="H1188" t="n">
         <v>1543314</v>
@@ -34850,7 +34850,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.888663291931152</v>
+        <v>0.888663232326508</v>
       </c>
       <c r="H1189" t="n">
         <v>842442</v>
@@ -34879,7 +34879,7 @@
         <v>1.08899998664856</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.909543514251709</v>
+        <v>0.909543454647064</v>
       </c>
       <c r="H1190" t="n">
         <v>614372</v>
@@ -34908,7 +34908,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.897015333175659</v>
+        <v>0.897015392780304</v>
       </c>
       <c r="H1191" t="n">
         <v>1331626</v>
@@ -34937,7 +34937,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.918730735778809</v>
+        <v>0.918730795383453</v>
       </c>
       <c r="H1192" t="n">
         <v>2380908</v>
@@ -34966,7 +34966,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.901191353797913</v>
+        <v>0.901191413402557</v>
       </c>
       <c r="H1193" t="n">
         <v>993458</v>
@@ -34995,7 +34995,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.905367493629456</v>
+        <v>0.905367434024811</v>
       </c>
       <c r="H1194" t="n">
         <v>698588</v>
@@ -35024,7 +35024,7 @@
         <v>1.0809999704361</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.902861833572388</v>
+        <v>0.902861773967743</v>
       </c>
       <c r="H1195" t="n">
         <v>652835</v>
@@ -35082,7 +35082,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.9145547747612</v>
+        <v>0.914554715156555</v>
       </c>
       <c r="H1197" t="n">
         <v>1059605</v>
@@ -35111,7 +35111,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.937105476856232</v>
+        <v>0.937105536460876</v>
       </c>
       <c r="H1198" t="n">
         <v>1687673</v>
@@ -35140,7 +35140,7 @@
         <v>1.10800004005432</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.925412535667419</v>
+        <v>0.925412476062775</v>
       </c>
       <c r="H1199" t="n">
         <v>870459</v>
@@ -35169,7 +35169,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.912049055099487</v>
+        <v>0.912049114704132</v>
       </c>
       <c r="H1200" t="n">
         <v>1226727</v>
@@ -35198,7 +35198,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.890333652496338</v>
+        <v>0.890333712100983</v>
       </c>
       <c r="H1201" t="n">
         <v>2226316</v>
@@ -35227,7 +35227,7 @@
         <v>1.067999958992</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.892004072666168</v>
+        <v>0.892004132270813</v>
       </c>
       <c r="H1202" t="n">
         <v>631454</v>
@@ -35343,7 +35343,7 @@
         <v>0.993499994277954</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.829780995845795</v>
+        <v>0.82978093624115</v>
       </c>
       <c r="H1206" t="n">
         <v>1701993</v>
@@ -35401,7 +35401,7 @@
         <v>0.992500007152557</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.828945755958557</v>
+        <v>0.828945696353912</v>
       </c>
       <c r="H1208" t="n">
         <v>916167</v>
@@ -35488,7 +35488,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.89868575334549</v>
+        <v>0.898685812950134</v>
       </c>
       <c r="H1211" t="n">
         <v>2105739</v>
@@ -35517,7 +35517,7 @@
         <v>1.07099997997284</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.894509673118591</v>
+        <v>0.894509613513947</v>
       </c>
       <c r="H1212" t="n">
         <v>597717</v>
@@ -35546,7 +35546,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.917060434818268</v>
+        <v>0.917060494422913</v>
       </c>
       <c r="H1213" t="n">
         <v>1682730</v>
@@ -35604,7 +35604,7 @@
         <v>1.05900001525879</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.884487152099609</v>
+        <v>0.884487211704254</v>
       </c>
       <c r="H1215" t="n">
         <v>491423</v>
@@ -35633,7 +35633,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.855254888534546</v>
+        <v>0.855254948139191</v>
       </c>
       <c r="H1216" t="n">
         <v>846295</v>
@@ -35662,7 +35662,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.915389835834503</v>
+        <v>0.915389895439148</v>
       </c>
       <c r="H1217" t="n">
         <v>2997238</v>
@@ -35778,7 +35778,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.864442110061646</v>
+        <v>0.86444216966629</v>
       </c>
       <c r="H1221" t="n">
         <v>897836</v>
@@ -35865,7 +35865,7 @@
         <v>1.00199997425079</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.836880207061768</v>
+        <v>0.836880147457123</v>
       </c>
       <c r="H1224" t="n">
         <v>577518</v>
@@ -35981,7 +35981,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.729973316192627</v>
+        <v>0.729973375797272</v>
       </c>
       <c r="H1228" t="n">
         <v>1596505</v>
@@ -36010,7 +36010,7 @@
         <v>0.91949999332428</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.767975389957428</v>
+        <v>0.767975449562073</v>
       </c>
       <c r="H1229" t="n">
         <v>1412591</v>
@@ -36068,7 +36068,7 @@
         <v>0.950999975204468</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.794284403324127</v>
+        <v>0.794284462928772</v>
       </c>
       <c r="H1231" t="n">
         <v>1081621</v>
@@ -36126,7 +36126,7 @@
         <v>0.993499994277954</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.829780995845795</v>
+        <v>0.82978093624115</v>
       </c>
       <c r="H1233" t="n">
         <v>1561801</v>
@@ -36155,7 +36155,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.856090068817139</v>
+        <v>0.856090009212494</v>
       </c>
       <c r="H1234" t="n">
         <v>2709801</v>
@@ -36184,7 +36184,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.924577295780182</v>
+        <v>0.924577414989471</v>
       </c>
       <c r="H1235" t="n">
         <v>4003298</v>
@@ -36242,7 +36242,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.951303958892822</v>
+        <v>0.951304018497467</v>
       </c>
       <c r="H1237" t="n">
         <v>1870101</v>
@@ -36271,7 +36271,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.957150638103485</v>
+        <v>0.957150518894196</v>
       </c>
       <c r="H1238" t="n">
         <v>2938823</v>
@@ -36300,7 +36300,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.966337740421295</v>
+        <v>0.966337621212006</v>
       </c>
       <c r="H1239" t="n">
         <v>1609545</v>
@@ -36329,7 +36329,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.02062630653381</v>
+        <v>1.0206264257431</v>
       </c>
       <c r="H1240" t="n">
         <v>3536526</v>
@@ -36416,7 +36416,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.0298136472702</v>
+        <v>1.02981376647949</v>
       </c>
       <c r="H1243" t="n">
         <v>2819086</v>
@@ -36445,7 +36445,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.07491481304169</v>
+        <v>1.07491505146027</v>
       </c>
       <c r="H1244" t="n">
         <v>2961990</v>
@@ -36474,7 +36474,7 @@
         <v>1.28699994087219</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.07491481304169</v>
+        <v>1.07491505146027</v>
       </c>
       <c r="H1245" t="n">
         <v>2543126</v>
@@ -36648,7 +36648,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.07909119129181</v>
+        <v>1.07909107208252</v>
       </c>
       <c r="H1251" t="n">
         <v>1682016</v>
@@ -36677,7 +36677,7 @@
         <v>1.28299999237061</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.07157421112061</v>
+        <v>1.0715743303299</v>
       </c>
       <c r="H1252" t="n">
         <v>1240166</v>
@@ -36735,7 +36735,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.04317688941956</v>
+        <v>1.04317700862885</v>
       </c>
       <c r="H1254" t="n">
         <v>2115098</v>
@@ -36793,7 +36793,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.03148412704468</v>
+        <v>1.03148424625397</v>
       </c>
       <c r="H1256" t="n">
         <v>1184716</v>
@@ -36880,7 +36880,7 @@
         <v>1.20299994945526</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.0047572851181</v>
+        <v>1.00475752353668</v>
       </c>
       <c r="H1259" t="n">
         <v>892409</v>
@@ -36938,7 +36938,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.0298136472702</v>
+        <v>1.02981376647949</v>
       </c>
       <c r="H1261" t="n">
         <v>1624816</v>
@@ -36967,7 +36967,7 @@
         <v>1.21899998188019</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.01812076568604</v>
+        <v>1.01812088489532</v>
       </c>
       <c r="H1262" t="n">
         <v>752242</v>
@@ -36996,7 +36996,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.01060390472412</v>
+        <v>1.01060378551483</v>
       </c>
       <c r="H1263" t="n">
         <v>1133335</v>
@@ -37025,7 +37025,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.998075842857361</v>
+        <v>0.998075723648071</v>
       </c>
       <c r="H1264" t="n">
         <v>1064295</v>
@@ -37054,7 +37054,7 @@
         <v>1.13900005817413</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.951303958892822</v>
+        <v>0.951304018497467</v>
       </c>
       <c r="H1265" t="n">
         <v>3011175</v>
@@ -37112,7 +37112,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.992229282855988</v>
+        <v>0.992229402065277</v>
       </c>
       <c r="H1267" t="n">
         <v>1350621</v>
@@ -37199,7 +37199,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.987218081951141</v>
+        <v>0.987217962741852</v>
       </c>
       <c r="H1270" t="n">
         <v>866193</v>
@@ -37228,7 +37228,7 @@
         <v>1.15600001811981</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.965502440929413</v>
+        <v>0.965502560138702</v>
       </c>
       <c r="H1271" t="n">
         <v>1757719</v>
@@ -37344,7 +37344,7 @@
         <v>1.26600003242493</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.05737578868866</v>
+        <v>1.05737566947937</v>
       </c>
       <c r="H1275" t="n">
         <v>1591028</v>
@@ -37402,7 +37402,7 @@
         <v>1.2610000371933</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.05319964885712</v>
+        <v>1.05319952964783</v>
       </c>
       <c r="H1277" t="n">
         <v>1062423</v>
@@ -37431,7 +37431,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.05069410800934</v>
+        <v>1.05069398880005</v>
       </c>
       <c r="H1278" t="n">
         <v>718663</v>
@@ -37489,7 +37489,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.03148412704468</v>
+        <v>1.03148424625397</v>
       </c>
       <c r="H1280" t="n">
         <v>1054107</v>
@@ -37518,7 +37518,7 @@
         <v>1.27300000190735</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.06322193145752</v>
+        <v>1.06322205066681</v>
       </c>
       <c r="H1281" t="n">
         <v>1622751</v>
@@ -37634,7 +37634,7 @@
         <v>1.25899994373322</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.05152916908264</v>
+        <v>1.05152904987335</v>
       </c>
       <c r="H1285" t="n">
         <v>1139462</v>
@@ -37663,7 +37663,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.03482484817505</v>
+        <v>1.03482496738434</v>
       </c>
       <c r="H1286" t="n">
         <v>1259004</v>
@@ -37692,7 +37692,7 @@
         <v>1.2610000371933</v>
       </c>
       <c r="G1287" t="n">
-        <v>1.05319964885712</v>
+        <v>1.05319952964783</v>
       </c>
       <c r="H1287" t="n">
         <v>1291561</v>
@@ -37750,7 +37750,7 @@
         <v>1.24100005626678</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.03649532794952</v>
+        <v>1.03649544715881</v>
       </c>
       <c r="H1289" t="n">
         <v>1078393</v>
@@ -37808,7 +37808,7 @@
         <v>1.25800001621246</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.05069410800934</v>
+        <v>1.05069398880005</v>
       </c>
       <c r="H1291" t="n">
         <v>1203524</v>
@@ -37924,7 +37924,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.20270216464996</v>
+        <v>1.20270228385925</v>
       </c>
       <c r="H1295" t="n">
         <v>8584230</v>
@@ -37953,7 +37953,7 @@
         <v>1.53699994087219</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.28371739387512</v>
+        <v>1.28371751308441</v>
       </c>
       <c r="H1296" t="n">
         <v>8648318</v>
@@ -38040,7 +38040,7 @@
         <v>1.54799997806549</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.29290497303009</v>
+        <v>1.2929048538208</v>
       </c>
       <c r="H1299" t="n">
         <v>4101534</v>
@@ -38127,7 +38127,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.37391996383667</v>
+        <v>1.37392008304596</v>
       </c>
       <c r="H1302" t="n">
         <v>7579786</v>
@@ -38185,7 +38185,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.37391996383667</v>
+        <v>1.37392008304596</v>
       </c>
       <c r="H1304" t="n">
         <v>5369157</v>
@@ -38214,7 +38214,7 @@
         <v>1.64100003242493</v>
       </c>
       <c r="G1305" t="n">
-        <v>1.37057936191559</v>
+        <v>1.3705792427063</v>
       </c>
       <c r="H1305" t="n">
         <v>2174460</v>
@@ -38272,7 +38272,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.35638082027435</v>
+        <v>1.35638058185577</v>
       </c>
       <c r="H1307" t="n">
         <v>1681134</v>
@@ -38301,7 +38301,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.35638082027435</v>
+        <v>1.35638058185577</v>
       </c>
       <c r="H1308" t="n">
         <v>1410687</v>
@@ -38359,7 +38359,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.29875111579895</v>
+        <v>1.29875135421753</v>
       </c>
       <c r="H1310" t="n">
         <v>2003780</v>
@@ -38417,7 +38417,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.30376255512238</v>
+        <v>1.30376243591309</v>
       </c>
       <c r="H1312" t="n">
         <v>1457296</v>
@@ -38446,7 +38446,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.30125689506531</v>
+        <v>1.30125677585602</v>
       </c>
       <c r="H1313" t="n">
         <v>2530993</v>
@@ -38533,7 +38533,7 @@
         <v>1.59899997711182</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.33550047874451</v>
+        <v>1.33550035953522</v>
       </c>
       <c r="H1316" t="n">
         <v>1494787</v>
@@ -38562,7 +38562,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.35638082027435</v>
+        <v>1.35638058185577</v>
       </c>
       <c r="H1317" t="n">
         <v>3043688</v>
@@ -38591,7 +38591,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.37391996383667</v>
+        <v>1.37392008304596</v>
       </c>
       <c r="H1318" t="n">
         <v>2115244</v>
@@ -38620,7 +38620,7 @@
         <v>1.63800001144409</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.36807370185852</v>
+        <v>1.36807358264923</v>
       </c>
       <c r="H1319" t="n">
         <v>2810879</v>
@@ -38736,7 +38736,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.44491291046143</v>
+        <v>1.44491302967072</v>
       </c>
       <c r="H1323" t="n">
         <v>2240203</v>
@@ -38852,7 +38852,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.43489038944244</v>
+        <v>1.43489050865173</v>
       </c>
       <c r="H1327" t="n">
         <v>3619939</v>
@@ -38910,7 +38910,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.44073700904846</v>
+        <v>1.44073688983917</v>
       </c>
       <c r="H1329" t="n">
         <v>2512664</v>
@@ -39026,7 +39026,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.4900141954422</v>
+        <v>1.49001443386078</v>
       </c>
       <c r="H1333" t="n">
         <v>1783246</v>
@@ -39084,7 +39084,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.56518316268921</v>
+        <v>1.56518304347992</v>
       </c>
       <c r="H1335" t="n">
         <v>6436688</v>
@@ -39113,7 +39113,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.56768882274628</v>
+        <v>1.56768870353699</v>
       </c>
       <c r="H1336" t="n">
         <v>4997095</v>
@@ -39200,7 +39200,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.5225875377655</v>
+        <v>1.52258741855621</v>
       </c>
       <c r="H1339" t="n">
         <v>2478018</v>
@@ -39287,7 +39287,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.51172971725464</v>
+        <v>1.51172959804535</v>
       </c>
       <c r="H1342" t="n">
         <v>1467621</v>
@@ -39345,7 +39345,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.52676343917847</v>
+        <v>1.52676355838776</v>
       </c>
       <c r="H1344" t="n">
         <v>2246042</v>
@@ -39432,7 +39432,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.5234227180481</v>
+        <v>1.52342283725739</v>
       </c>
       <c r="H1347" t="n">
         <v>1689611</v>
@@ -39490,7 +39490,7 @@
         <v>1.85899996757507</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.55265510082245</v>
+        <v>1.55265498161316</v>
       </c>
       <c r="H1349" t="n">
         <v>1403593</v>
@@ -39519,7 +39519,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.52843391895294</v>
+        <v>1.52843403816223</v>
       </c>
       <c r="H1350" t="n">
         <v>1164177</v>
@@ -39548,7 +39548,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.53177487850189</v>
+        <v>1.5317747592926</v>
       </c>
       <c r="H1351" t="n">
         <v>1298059</v>
@@ -39606,7 +39606,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.49753129482269</v>
+        <v>1.4975311756134</v>
       </c>
       <c r="H1353" t="n">
         <v>985226</v>
@@ -39693,7 +39693,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.5225875377655</v>
+        <v>1.52258741855621</v>
       </c>
       <c r="H1356" t="n">
         <v>1042227</v>
@@ -39780,7 +39780,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.60709416866302</v>
+        <v>1.60709428787231</v>
       </c>
       <c r="H1359" t="n">
         <v>4790217</v>
@@ -39896,7 +39896,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.57436656951904</v>
+        <v>1.57436668872833</v>
       </c>
       <c r="H1363" t="n">
         <v>1985641</v>
@@ -40041,7 +40041,7 @@
         <v>1.80900001525879</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.55800294876099</v>
+        <v>1.55800306797028</v>
       </c>
       <c r="H1368" t="n">
         <v>792658</v>
@@ -40070,7 +40070,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.57264423370361</v>
+        <v>1.57264411449432</v>
       </c>
       <c r="H1369" t="n">
         <v>1456339</v>
@@ -40099,7 +40099,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.65187919139862</v>
+        <v>1.65187931060791</v>
       </c>
       <c r="H1370" t="n">
         <v>6774314</v>
@@ -40128,7 +40128,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.61053919792175</v>
+        <v>1.61053907871246</v>
       </c>
       <c r="H1371" t="n">
         <v>3323900</v>
@@ -40157,7 +40157,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.63982164859772</v>
+        <v>1.63982176780701</v>
       </c>
       <c r="H1372" t="n">
         <v>2388166</v>
@@ -40186,7 +40186,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.66565918922424</v>
+        <v>1.66565930843353</v>
       </c>
       <c r="H1373" t="n">
         <v>2970585</v>
@@ -40244,7 +40244,7 @@
         <v>2.04800009727478</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.7638418674469</v>
+        <v>1.76384198665619</v>
       </c>
       <c r="H1375" t="n">
         <v>6289366</v>
@@ -40273,7 +40273,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.88613951206207</v>
+        <v>1.88613939285278</v>
       </c>
       <c r="H1376" t="n">
         <v>5798781</v>
@@ -40302,7 +40302,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.83101940155029</v>
+        <v>1.831019282341</v>
       </c>
       <c r="H1377" t="n">
         <v>5655370</v>
@@ -40331,7 +40331,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.83274209499359</v>
+        <v>1.83274185657501</v>
       </c>
       <c r="H1378" t="n">
         <v>2364501</v>
@@ -40360,7 +40360,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.80173695087433</v>
+        <v>1.80173683166504</v>
       </c>
       <c r="H1379" t="n">
         <v>2810289</v>
@@ -40447,7 +40447,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.74661695957184</v>
+        <v>1.74661684036255</v>
       </c>
       <c r="H1382" t="n">
         <v>2241110</v>
@@ -40534,7 +40534,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.88269436359406</v>
+        <v>1.88269460201263</v>
       </c>
       <c r="H1385" t="n">
         <v>10053816</v>
@@ -40563,7 +40563,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.83963191509247</v>
+        <v>1.83963203430176</v>
       </c>
       <c r="H1386" t="n">
         <v>6728917</v>
@@ -40592,7 +40592,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.82585179805756</v>
+        <v>1.82585191726685</v>
       </c>
       <c r="H1387" t="n">
         <v>2856954</v>
@@ -40621,7 +40621,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.77762186527252</v>
+        <v>1.77762174606323</v>
       </c>
       <c r="H1388" t="n">
         <v>3273311</v>
@@ -40679,7 +40679,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.80345952510834</v>
+        <v>1.80345940589905</v>
       </c>
       <c r="H1390" t="n">
         <v>1999768</v>
@@ -40708,7 +40708,7 @@
         <v>2.08800005912781</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.7982919216156</v>
+        <v>1.79829180240631</v>
       </c>
       <c r="H1391" t="n">
         <v>2148110</v>
@@ -40766,7 +40766,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.87063694000244</v>
+        <v>1.87063682079315</v>
       </c>
       <c r="H1393" t="n">
         <v>3124693</v>
@@ -40795,7 +40795,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.86891436576843</v>
+        <v>1.86891448497772</v>
       </c>
       <c r="H1394" t="n">
         <v>3432153</v>
@@ -40824,7 +40824,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.87752711772919</v>
+        <v>1.87752723693848</v>
       </c>
       <c r="H1395" t="n">
         <v>1761364</v>
@@ -40882,7 +40882,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.92403447628021</v>
+        <v>1.92403435707092</v>
       </c>
       <c r="H1397" t="n">
         <v>3318629</v>
@@ -40911,7 +40911,7 @@
         <v>2.25</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.93781459331512</v>
+        <v>1.93781435489655</v>
       </c>
       <c r="H1398" t="n">
         <v>2649479</v>
@@ -40998,7 +40998,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.94125962257385</v>
+        <v>1.94125938415527</v>
       </c>
       <c r="H1401" t="n">
         <v>2335253</v>
@@ -41027,7 +41027,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.91542208194733</v>
+        <v>1.91542196273804</v>
       </c>
       <c r="H1402" t="n">
         <v>4795754</v>
@@ -41056,7 +41056,7 @@
         <v>2.24399995803833</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.93264710903168</v>
+        <v>1.93264722824097</v>
       </c>
       <c r="H1403" t="n">
         <v>1862149</v>
@@ -41114,7 +41114,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.93436968326569</v>
+        <v>1.9343695640564</v>
       </c>
       <c r="H1405" t="n">
         <v>1889156</v>
@@ -41172,7 +41172,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.89475190639496</v>
+        <v>1.89475202560425</v>
       </c>
       <c r="H1407" t="n">
         <v>1693344</v>
@@ -41259,7 +41259,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.81207180023193</v>
+        <v>1.81207191944122</v>
       </c>
       <c r="H1410" t="n">
         <v>3028379</v>
@@ -41288,7 +41288,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.84652209281921</v>
+        <v>1.84652197360992</v>
       </c>
       <c r="H1411" t="n">
         <v>2012524</v>
@@ -41317,7 +41317,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.83790969848633</v>
+        <v>1.83790957927704</v>
       </c>
       <c r="H1412" t="n">
         <v>1424377</v>
@@ -41346,7 +41346,7 @@
         <v>2.11400008201599</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.8206844329834</v>
+        <v>1.82068455219269</v>
       </c>
       <c r="H1413" t="n">
         <v>2462344</v>
@@ -41375,7 +41375,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.85168969631195</v>
+        <v>1.85168981552124</v>
       </c>
       <c r="H1414" t="n">
         <v>1142348</v>
@@ -41404,7 +41404,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.85168969631195</v>
+        <v>1.85168981552124</v>
       </c>
       <c r="H1415" t="n">
         <v>1088449</v>
@@ -41433,7 +41433,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.83790969848633</v>
+        <v>1.83790957927704</v>
       </c>
       <c r="H1416" t="n">
         <v>1709498</v>
@@ -41462,7 +41462,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.85685682296753</v>
+        <v>1.85685670375824</v>
       </c>
       <c r="H1417" t="n">
         <v>3159435</v>
@@ -41491,7 +41491,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.97915470600128</v>
+        <v>1.9791544675827</v>
       </c>
       <c r="H1418" t="n">
         <v>16220336</v>
@@ -41520,7 +41520,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.92920207977295</v>
+        <v>1.92920196056366</v>
       </c>
       <c r="H1419" t="n">
         <v>22194642</v>
@@ -41549,7 +41549,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.90336453914642</v>
+        <v>1.90336465835571</v>
       </c>
       <c r="H1420" t="n">
         <v>5111147</v>
@@ -41578,7 +41578,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.91886711120605</v>
+        <v>1.91886699199677</v>
       </c>
       <c r="H1421" t="n">
         <v>2504540</v>
@@ -41665,7 +41665,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.90508687496185</v>
+        <v>1.90508699417114</v>
       </c>
       <c r="H1424" t="n">
         <v>1834534</v>
@@ -41694,7 +41694,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.90508687496185</v>
+        <v>1.90508699417114</v>
       </c>
       <c r="H1425" t="n">
         <v>3197473</v>
@@ -41723,7 +41723,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.99293458461761</v>
+        <v>1.99293434619904</v>
       </c>
       <c r="H1426" t="n">
         <v>5731370</v>
@@ -41752,7 +41752,7 @@
         <v>2.34200000762939</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.01704955101013</v>
+        <v>2.01704978942871</v>
       </c>
       <c r="H1427" t="n">
         <v>5253085</v>
@@ -41781,7 +41781,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.11006498336792</v>
+        <v>2.11006474494934</v>
       </c>
       <c r="H1428" t="n">
         <v>7160511</v>
@@ -41868,7 +41868,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G1431" t="n">
-        <v>2.02049446105957</v>
+        <v>2.02049469947815</v>
       </c>
       <c r="H1431" t="n">
         <v>2887673</v>
@@ -41926,7 +41926,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.88613951206207</v>
+        <v>1.88613939285278</v>
       </c>
       <c r="H1433" t="n">
         <v>8135763</v>
@@ -42013,7 +42013,7 @@
         <v>2.23200011253357</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.92231214046478</v>
+        <v>1.92231178283691</v>
       </c>
       <c r="H1436" t="n">
         <v>1160492</v>
@@ -42042,7 +42042,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.94125962257385</v>
+        <v>1.94125938415527</v>
       </c>
       <c r="H1437" t="n">
         <v>1502670</v>
@@ -42129,7 +42129,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.94814968109131</v>
+        <v>1.94814944267273</v>
       </c>
       <c r="H1440" t="n">
         <v>1765949</v>
@@ -42158,7 +42158,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.96192955970764</v>
+        <v>1.96192979812622</v>
       </c>
       <c r="H1441" t="n">
         <v>1857136</v>
@@ -42187,7 +42187,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1442" t="n">
-        <v>2.01532697677612</v>
+        <v>2.0153272151947</v>
       </c>
       <c r="H1442" t="n">
         <v>4357519</v>
@@ -42216,7 +42216,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G1443" t="n">
-        <v>2.01360464096069</v>
+        <v>2.01360487937927</v>
       </c>
       <c r="H1443" t="n">
         <v>6083558</v>
@@ -42245,7 +42245,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1444" t="n">
-        <v>2.00671458244324</v>
+        <v>2.00671434402466</v>
       </c>
       <c r="H1444" t="n">
         <v>1600191</v>
@@ -42274,7 +42274,7 @@
         <v>2.31399989128113</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.99293458461761</v>
+        <v>1.99293434619904</v>
       </c>
       <c r="H1445" t="n">
         <v>1455081</v>
@@ -42303,7 +42303,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G1446" t="n">
-        <v>2.01360464096069</v>
+        <v>2.01360487937927</v>
       </c>
       <c r="H1446" t="n">
         <v>2019884</v>
@@ -42419,7 +42419,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.98259949684143</v>
+        <v>1.98259973526001</v>
       </c>
       <c r="H1450" t="n">
         <v>2068642</v>
@@ -42477,7 +42477,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G1452" t="n">
-        <v>1.9567619562149</v>
+        <v>1.95676219463348</v>
       </c>
       <c r="H1452" t="n">
         <v>3442805</v>
@@ -42535,7 +42535,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.88613951206207</v>
+        <v>1.88613939285278</v>
       </c>
       <c r="H1454" t="n">
         <v>3629122</v>
@@ -42564,7 +42564,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1455" t="n">
-        <v>1.89475190639496</v>
+        <v>1.89475202560425</v>
       </c>
       <c r="H1455" t="n">
         <v>1370526</v>
@@ -42651,7 +42651,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.90680956840515</v>
+        <v>1.90680968761444</v>
       </c>
       <c r="H1458" t="n">
         <v>1242219</v>
@@ -42680,7 +42680,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.89475190639496</v>
+        <v>1.89475202560425</v>
       </c>
       <c r="H1459" t="n">
         <v>1599201</v>
@@ -42709,7 +42709,7 @@
         <v>2.14800000190735</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.84996688365936</v>
+        <v>1.84996700286865</v>
       </c>
       <c r="H1460" t="n">
         <v>2076390</v>
@@ -42796,7 +42796,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G1463" t="n">
-        <v>1.88269436359406</v>
+        <v>1.88269460201263</v>
       </c>
       <c r="H1463" t="n">
         <v>1629758</v>
@@ -42825,7 +42825,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.87580454349518</v>
+        <v>1.87580442428589</v>
       </c>
       <c r="H1464" t="n">
         <v>1232432</v>
@@ -42854,7 +42854,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.88613951206207</v>
+        <v>1.88613939285278</v>
       </c>
       <c r="H1465" t="n">
         <v>1087524</v>
@@ -42883,7 +42883,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.82929706573486</v>
+        <v>1.82929682731628</v>
       </c>
       <c r="H1466" t="n">
         <v>4060132</v>
@@ -42912,7 +42912,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.84479939937592</v>
+        <v>1.84479928016663</v>
       </c>
       <c r="H1467" t="n">
         <v>2159433</v>
@@ -42941,7 +42941,7 @@
         <v>2.15400004386902</v>
       </c>
       <c r="G1468" t="n">
-        <v>1.85513424873352</v>
+        <v>1.8551344871521</v>
       </c>
       <c r="H1468" t="n">
         <v>1757422</v>
@@ -42970,7 +42970,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.85168969631195</v>
+        <v>1.85168981552124</v>
       </c>
       <c r="H1469" t="n">
         <v>1548024</v>
@@ -43028,7 +43028,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G1471" t="n">
-        <v>1.85685682296753</v>
+        <v>1.85685670375824</v>
       </c>
       <c r="H1471" t="n">
         <v>2678460</v>
@@ -43086,7 +43086,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G1473" t="n">
-        <v>1.86202454566956</v>
+        <v>1.86202442646027</v>
       </c>
       <c r="H1473" t="n">
         <v>2883877</v>
@@ -43115,7 +43115,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.83618688583374</v>
+        <v>1.83618700504303</v>
       </c>
       <c r="H1474" t="n">
         <v>1430703</v>
@@ -43202,7 +43202,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G1477" t="n">
-        <v>1.88269436359406</v>
+        <v>1.88269460201263</v>
       </c>
       <c r="H1477" t="n">
         <v>3127656</v>
@@ -43231,7 +43231,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G1478" t="n">
-        <v>1.89302933216095</v>
+        <v>1.89302945137024</v>
       </c>
       <c r="H1478" t="n">
         <v>1181498</v>
@@ -43260,7 +43260,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G1479" t="n">
-        <v>1.89130711555481</v>
+        <v>1.8913072347641</v>
       </c>
       <c r="H1479" t="n">
         <v>1405366</v>
@@ -43289,7 +43289,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G1480" t="n">
-        <v>1.8895845413208</v>
+        <v>1.88958442211151</v>
       </c>
       <c r="H1480" t="n">
         <v>758846</v>
@@ -43318,7 +43318,7 @@
         <v>2.14199995994568</v>
       </c>
       <c r="G1481" t="n">
-        <v>1.84479939937592</v>
+        <v>1.84479928016663</v>
       </c>
       <c r="H1481" t="n">
         <v>1640065</v>
@@ -43347,7 +43347,7 @@
         <v>2.15599989891052</v>
       </c>
       <c r="G1482" t="n">
-        <v>1.85685682296753</v>
+        <v>1.85685670375824</v>
       </c>
       <c r="H1482" t="n">
         <v>2620300</v>
@@ -43376,7 +43376,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1483" t="n">
-        <v>1.84307706356049</v>
+        <v>1.8430769443512</v>
       </c>
       <c r="H1483" t="n">
         <v>1233098</v>
@@ -43405,7 +43405,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G1484" t="n">
-        <v>1.87408208847046</v>
+        <v>1.87408196926117</v>
       </c>
       <c r="H1484" t="n">
         <v>2025662</v>
@@ -43434,7 +43434,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.83618688583374</v>
+        <v>1.83618700504303</v>
       </c>
       <c r="H1485" t="n">
         <v>2100850</v>
@@ -43463,7 +43463,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.81723928451538</v>
+        <v>1.81723916530609</v>
       </c>
       <c r="H1486" t="n">
         <v>1966762</v>
@@ -43492,7 +43492,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.83790969848633</v>
+        <v>1.83790957927704</v>
       </c>
       <c r="H1487" t="n">
         <v>3745529</v>
@@ -43521,7 +43521,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.867192029953</v>
+        <v>1.86719191074371</v>
       </c>
       <c r="H1488" t="n">
         <v>2302894</v>
@@ -43550,7 +43550,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G1489" t="n">
-        <v>1.96192955970764</v>
+        <v>1.96192979812622</v>
       </c>
       <c r="H1489" t="n">
         <v>8832976</v>
@@ -43637,7 +43637,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G1492" t="n">
-        <v>1.86202454566956</v>
+        <v>1.86202442646027</v>
       </c>
       <c r="H1492" t="n">
         <v>1317744</v>
@@ -43666,7 +43666,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1493" t="n">
-        <v>1.84307706356049</v>
+        <v>1.8430769443512</v>
       </c>
       <c r="H1493" t="n">
         <v>5523646</v>
@@ -43724,7 +43724,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.84307706356049</v>
+        <v>1.8430769443512</v>
       </c>
       <c r="H1495" t="n">
         <v>1533678</v>
@@ -43753,7 +43753,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G1496" t="n">
-        <v>1.81207180023193</v>
+        <v>1.81207191944122</v>
       </c>
       <c r="H1496" t="n">
         <v>1731235</v>
@@ -43782,7 +43782,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1497" t="n">
-        <v>1.80001425743103</v>
+        <v>1.80001413822174</v>
       </c>
       <c r="H1497" t="n">
         <v>1978111</v>
@@ -43869,7 +43869,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G1500" t="n">
-        <v>1.76211929321289</v>
+        <v>1.76211941242218</v>
       </c>
       <c r="H1500" t="n">
         <v>1463157</v>
@@ -43898,7 +43898,7 @@
         <v>2.06399989128113</v>
       </c>
       <c r="G1501" t="n">
-        <v>1.77762186527252</v>
+        <v>1.77762174606323</v>
       </c>
       <c r="H1501" t="n">
         <v>1440707</v>
@@ -43956,7 +43956,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.73972690105438</v>
+        <v>1.73972678184509</v>
       </c>
       <c r="H1503" t="n">
         <v>3347233</v>
@@ -44014,7 +44014,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1505" t="n">
-        <v>1.71388936042786</v>
+        <v>1.71388924121857</v>
       </c>
       <c r="H1505" t="n">
         <v>3082214</v>
@@ -44043,7 +44043,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.74489450454712</v>
+        <v>1.74489438533783</v>
       </c>
       <c r="H1506" t="n">
         <v>3370365</v>
@@ -44101,7 +44101,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G1508" t="n">
-        <v>1.72766923904419</v>
+        <v>1.72766935825348</v>
       </c>
       <c r="H1508" t="n">
         <v>1310633</v>
@@ -44159,7 +44159,7 @@
         <v>2.12400007247925</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.82929706573486</v>
+        <v>1.82929682731628</v>
       </c>
       <c r="H1510" t="n">
         <v>1482468</v>
@@ -44217,7 +44217,7 @@
         <v>2.09200000762939</v>
       </c>
       <c r="G1512" t="n">
-        <v>1.80173695087433</v>
+        <v>1.80173683166504</v>
       </c>
       <c r="H1512" t="n">
         <v>897905</v>
@@ -44246,7 +44246,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1513" t="n">
-        <v>1.8086268901825</v>
+        <v>1.80862700939178</v>
       </c>
       <c r="H1513" t="n">
         <v>811698</v>
@@ -44333,7 +44333,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1516" t="n">
-        <v>1.73972690105438</v>
+        <v>1.73972678184509</v>
       </c>
       <c r="H1516" t="n">
         <v>1739728</v>
@@ -44362,7 +44362,7 @@
         <v>2.04399991035461</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.76039671897888</v>
+        <v>1.76039683818817</v>
       </c>
       <c r="H1517" t="n">
         <v>942860</v>
@@ -44391,7 +44391,7 @@
         <v>2.0460000038147</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.76211929321289</v>
+        <v>1.76211941242218</v>
       </c>
       <c r="H1518" t="n">
         <v>1147183</v>
@@ -44449,7 +44449,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.74489450454712</v>
+        <v>1.74489438533783</v>
       </c>
       <c r="H1520" t="n">
         <v>1054836</v>
@@ -44565,7 +44565,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1524" t="n">
-        <v>1.8086268901825</v>
+        <v>1.80862700939178</v>
       </c>
       <c r="H1524" t="n">
         <v>974166</v>
@@ -44594,7 +44594,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G1525" t="n">
-        <v>1.79484701156616</v>
+        <v>1.79484713077545</v>
       </c>
       <c r="H1525" t="n">
         <v>785060</v>
@@ -44768,7 +44768,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.72077929973602</v>
+        <v>1.72077918052673</v>
       </c>
       <c r="H1531" t="n">
         <v>1793895</v>
@@ -44797,7 +44797,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.67513310909271</v>
+        <v>1.67513298988342</v>
       </c>
       <c r="H1532" t="n">
         <v>2020350</v>
@@ -44913,7 +44913,7 @@
         <v>2.00600004196167</v>
       </c>
       <c r="G1536" t="n">
-        <v>1.72766923904419</v>
+        <v>1.72766935825348</v>
       </c>
       <c r="H1536" t="n">
         <v>5758603</v>
@@ -44942,7 +44942,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.78278934955597</v>
+        <v>1.78278946876526</v>
       </c>
       <c r="H1537" t="n">
         <v>2586008</v>
@@ -44971,7 +44971,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1538" t="n">
-        <v>1.73972690105438</v>
+        <v>1.73972678184509</v>
       </c>
       <c r="H1538" t="n">
         <v>1528484</v>
@@ -45000,7 +45000,7 @@
         <v>2.02600002288818</v>
       </c>
       <c r="G1539" t="n">
-        <v>1.74489450454712</v>
+        <v>1.74489438533783</v>
       </c>
       <c r="H1539" t="n">
         <v>1187215</v>
@@ -45029,7 +45029,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G1540" t="n">
-        <v>1.72077929973602</v>
+        <v>1.72077918052673</v>
       </c>
       <c r="H1540" t="n">
         <v>1566494</v>
@@ -45087,7 +45087,7 @@
         <v>1.87800002098083</v>
       </c>
       <c r="G1542" t="n">
-        <v>1.61742925643921</v>
+        <v>1.61742913722992</v>
       </c>
       <c r="H1542" t="n">
         <v>3300233</v>
@@ -45116,7 +45116,7 @@
         <v>1.875</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.61484563350677</v>
+        <v>1.61484551429749</v>
       </c>
       <c r="H1543" t="n">
         <v>1541075</v>
@@ -45232,7 +45232,7 @@
         <v>1.85300004482269</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.59589779376984</v>
+        <v>1.59589791297913</v>
       </c>
       <c r="H1547" t="n">
         <v>2613730</v>
@@ -45319,7 +45319,7 @@
         <v>1.81599998474121</v>
       </c>
       <c r="G1550" t="n">
-        <v>1.56403160095215</v>
+        <v>1.56403172016144</v>
       </c>
       <c r="H1550" t="n">
         <v>2641754</v>
@@ -45348,7 +45348,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1551" t="n">
-        <v>1.52010774612427</v>
+        <v>1.52010762691498</v>
       </c>
       <c r="H1551" t="n">
         <v>3034166</v>
@@ -45493,7 +45493,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G1556" t="n">
-        <v>1.57436656951904</v>
+        <v>1.57436668872833</v>
       </c>
       <c r="H1556" t="n">
         <v>1037392</v>
@@ -45522,7 +45522,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1557" t="n">
-        <v>1.53302669525146</v>
+        <v>1.53302657604218</v>
       </c>
       <c r="H1557" t="n">
         <v>1921397</v>
@@ -45551,7 +45551,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1558" t="n">
-        <v>1.57608914375305</v>
+        <v>1.57608926296234</v>
       </c>
       <c r="H1558" t="n">
         <v>1301192</v>
@@ -45580,7 +45580,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.5933141708374</v>
+        <v>1.59331429004669</v>
       </c>
       <c r="H1559" t="n">
         <v>1734770</v>
@@ -45609,7 +45609,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1560" t="n">
-        <v>1.58986914157867</v>
+        <v>1.58986926078796</v>
       </c>
       <c r="H1560" t="n">
         <v>1625441</v>
@@ -45638,7 +45638,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1561" t="n">
-        <v>1.55886423587799</v>
+        <v>1.5588641166687</v>
       </c>
       <c r="H1561" t="n">
         <v>1148968</v>
@@ -45783,7 +45783,7 @@
         <v>1.7389999628067</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.49771535396576</v>
+        <v>1.49771547317505</v>
       </c>
       <c r="H1566" t="n">
         <v>4014926</v>
@@ -45812,7 +45812,7 @@
         <v>1.68599998950958</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.45206880569458</v>
+        <v>1.45206892490387</v>
       </c>
       <c r="H1567" t="n">
         <v>2169113</v>
@@ -45928,7 +45928,7 @@
         <v>1.5</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.29187619686127</v>
+        <v>1.29187631607056</v>
       </c>
       <c r="H1571" t="n">
         <v>2297924</v>
@@ -46044,7 +46044,7 @@
         <v>1.54499995708466</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.33063268661499</v>
+        <v>1.3306325674057</v>
       </c>
       <c r="H1575" t="n">
         <v>891189</v>
@@ -46073,7 +46073,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.36077654361725</v>
+        <v>1.36077642440796</v>
       </c>
       <c r="H1576" t="n">
         <v>1279112</v>
@@ -46131,7 +46131,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.36594390869141</v>
+        <v>1.36594378948212</v>
       </c>
       <c r="H1578" t="n">
         <v>1023621</v>
@@ -46276,7 +46276,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.39867150783539</v>
+        <v>1.39867126941681</v>
       </c>
       <c r="H1583" t="n">
         <v>3037320</v>
@@ -46305,7 +46305,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1584" t="n">
-        <v>1.39092016220093</v>
+        <v>1.39092028141022</v>
       </c>
       <c r="H1584" t="n">
         <v>1647838</v>
@@ -46334,7 +46334,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G1585" t="n">
-        <v>1.4003940820694</v>
+        <v>1.40039396286011</v>
       </c>
       <c r="H1585" t="n">
         <v>939327</v>
@@ -46392,7 +46392,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G1587" t="n">
-        <v>1.4003940820694</v>
+        <v>1.40039396286011</v>
       </c>
       <c r="H1587" t="n">
         <v>1414021</v>
@@ -46450,7 +46450,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.40986752510071</v>
+        <v>1.40986764431</v>
       </c>
       <c r="H1589" t="n">
         <v>2619260</v>
@@ -46508,7 +46508,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.4210638999939</v>
+        <v>1.42106401920319</v>
       </c>
       <c r="H1591" t="n">
         <v>1826584</v>
@@ -46624,7 +46624,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.36077654361725</v>
+        <v>1.36077642440796</v>
       </c>
       <c r="H1595" t="n">
         <v>1346527</v>
@@ -46682,7 +46682,7 @@
         <v>1.61300003528595</v>
       </c>
       <c r="G1597" t="n">
-        <v>1.38919770717621</v>
+        <v>1.3891978263855</v>
       </c>
       <c r="H1597" t="n">
         <v>1070107</v>
@@ -46711,7 +46711,7 @@
         <v>1.60599994659424</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.38316881656647</v>
+        <v>1.38316893577576</v>
       </c>
       <c r="H1598" t="n">
         <v>507869</v>
@@ -46740,7 +46740,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G1599" t="n">
-        <v>1.38661408424377</v>
+        <v>1.38661396503448</v>
       </c>
       <c r="H1599" t="n">
         <v>525123</v>
@@ -47001,7 +47001,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.39092016220093</v>
+        <v>1.39092028141022</v>
       </c>
       <c r="H1608" t="n">
         <v>444474</v>
@@ -47030,7 +47030,7 @@
         <v>1.625</v>
       </c>
       <c r="G1609" t="n">
-        <v>1.39953279495239</v>
+        <v>1.3995326757431</v>
       </c>
       <c r="H1609" t="n">
         <v>792740</v>
@@ -47175,7 +47175,7 @@
         <v>1.59300005435944</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.37197279930115</v>
+        <v>1.37197268009186</v>
       </c>
       <c r="H1614" t="n">
         <v>1717276</v>
@@ -47233,7 +47233,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.33924508094788</v>
+        <v>1.33924520015717</v>
       </c>
       <c r="H1616" t="n">
         <v>1434960</v>
@@ -47291,7 +47291,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.37800145149231</v>
+        <v>1.3780015707016</v>
       </c>
       <c r="H1618" t="n">
         <v>976808</v>
@@ -47320,7 +47320,7 @@
         <v>1.66299998760223</v>
       </c>
       <c r="G1619" t="n">
-        <v>1.43226027488708</v>
+        <v>1.4322601556778</v>
       </c>
       <c r="H1619" t="n">
         <v>2247068</v>
@@ -47436,7 +47436,7 @@
         <v>1.62699997425079</v>
       </c>
       <c r="G1623" t="n">
-        <v>1.4012553691864</v>
+        <v>1.40125524997711</v>
       </c>
       <c r="H1623" t="n">
         <v>461646</v>
@@ -47465,7 +47465,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G1624" t="n">
-        <v>1.39092016220093</v>
+        <v>1.39092028141022</v>
       </c>
       <c r="H1624" t="n">
         <v>793598</v>
@@ -47610,7 +47610,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1629" t="n">
-        <v>1.51217985153198</v>
+        <v>1.51217973232269</v>
       </c>
       <c r="H1629" t="n">
         <v>1385475</v>
@@ -47668,7 +47668,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G1631" t="n">
-        <v>1.50058877468109</v>
+        <v>1.50058889389038</v>
       </c>
       <c r="H1631" t="n">
         <v>1107827</v>
@@ -47726,7 +47726,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.47919023036957</v>
+        <v>1.47919034957886</v>
       </c>
       <c r="H1633" t="n">
         <v>220293</v>
@@ -47784,7 +47784,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1635" t="n">
-        <v>1.47473216056824</v>
+        <v>1.47473204135895</v>
       </c>
       <c r="H1635" t="n">
         <v>489579</v>
@@ -48190,7 +48190,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.31424129009247</v>
+        <v>1.31424117088318</v>
       </c>
       <c r="H1649" t="n">
         <v>288286</v>
@@ -48219,7 +48219,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.32137429714203</v>
+        <v>1.32137417793274</v>
       </c>
       <c r="H1650" t="n">
         <v>1098067</v>
@@ -48306,7 +48306,7 @@
         <v>1.47899997234344</v>
       </c>
       <c r="G1653" t="n">
-        <v>1.3186993598938</v>
+        <v>1.31869924068451</v>
       </c>
       <c r="H1653" t="n">
         <v>937469</v>
@@ -48451,7 +48451,7 @@
         <v>1.46200001239777</v>
       </c>
       <c r="G1658" t="n">
-        <v>1.30354177951813</v>
+        <v>1.30354189872742</v>
       </c>
       <c r="H1658" t="n">
         <v>745709</v>
@@ -48567,7 +48567,7 @@
         <v>1.47899997234344</v>
       </c>
       <c r="G1662" t="n">
-        <v>1.3186993598938</v>
+        <v>1.31869924068451</v>
       </c>
       <c r="H1662" t="n">
         <v>355370</v>
@@ -48596,7 +48596,7 @@
         <v>1.46099996566772</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.30265009403229</v>
+        <v>1.30265021324158</v>
       </c>
       <c r="H1663" t="n">
         <v>583859</v>
@@ -48915,7 +48915,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.34009802341461</v>
+        <v>1.3400981426239</v>
       </c>
       <c r="H1674" t="n">
         <v>1471103</v>
@@ -49002,7 +49002,7 @@
         <v>1.44400000572205</v>
       </c>
       <c r="G1677" t="n">
-        <v>1.2874927520752</v>
+        <v>1.28749263286591</v>
       </c>
       <c r="H1677" t="n">
         <v>1439183</v>
@@ -49147,7 +49147,7 @@
         <v>1.47399997711182</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.31424129009247</v>
+        <v>1.31424117088318</v>
       </c>
       <c r="H1682" t="n">
         <v>1680539</v>
@@ -49176,7 +49176,7 @@
         <v>1.47099995613098</v>
       </c>
       <c r="G1683" t="n">
-        <v>1.31156647205353</v>
+        <v>1.31156635284424</v>
       </c>
       <c r="H1683" t="n">
         <v>514738</v>
@@ -49205,7 +49205,7 @@
         <v>1.50300002098083</v>
       </c>
       <c r="G1684" t="n">
-        <v>1.34009802341461</v>
+        <v>1.3400981426239</v>
       </c>
       <c r="H1684" t="n">
         <v>866754</v>
@@ -49350,7 +49350,7 @@
         <v>1.39699995517731</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.24558687210083</v>
+        <v>1.24558675289154</v>
       </c>
       <c r="H1689" t="n">
         <v>932713</v>
@@ -49437,7 +49437,7 @@
         <v>1.42900002002716</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.27411842346191</v>
+        <v>1.2741185426712</v>
       </c>
       <c r="H1692" t="n">
         <v>385348</v>
@@ -49466,7 +49466,7 @@
         <v>1.41299998760223</v>
       </c>
       <c r="G1693" t="n">
-        <v>1.25985264778137</v>
+        <v>1.25985276699066</v>
       </c>
       <c r="H1693" t="n">
         <v>482179</v>
@@ -49553,7 +49553,7 @@
         <v>1.40499997138977</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.25271964073181</v>
+        <v>1.2527197599411</v>
       </c>
       <c r="H1696" t="n">
         <v>523266</v>
@@ -49611,7 +49611,7 @@
         <v>1.41600000858307</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.26252746582031</v>
+        <v>1.2625275850296</v>
       </c>
       <c r="H1698" t="n">
         <v>403461</v>
@@ -49669,7 +49669,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.22151339054108</v>
+        <v>1.22151327133179</v>
       </c>
       <c r="H1700" t="n">
         <v>825266</v>
@@ -50017,7 +50017,7 @@
         <v>1.36199998855591</v>
       </c>
       <c r="G1712" t="n">
-        <v>1.21438038349152</v>
+        <v>1.21438026428223</v>
       </c>
       <c r="H1712" t="n">
         <v>369442</v>
@@ -50075,7 +50075,7 @@
         <v>1.32700002193451</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.1831738948822</v>
+        <v>1.18317377567291</v>
       </c>
       <c r="H1714" t="n">
         <v>425223</v>
@@ -50162,7 +50162,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.06102252006531</v>
+        <v>1.06102240085602</v>
       </c>
       <c r="H1717" t="n">
         <v>2834912</v>
@@ -50191,7 +50191,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.11897754669189</v>
+        <v>1.1189774274826</v>
       </c>
       <c r="H1718" t="n">
         <v>1256498</v>
@@ -50249,7 +50249,7 @@
         <v>1.2940000295639</v>
       </c>
       <c r="G1720" t="n">
-        <v>1.15375053882599</v>
+        <v>1.1537504196167</v>
       </c>
       <c r="H1720" t="n">
         <v>649240</v>
@@ -50423,7 +50423,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G1726" t="n">
-        <v>1.05567288398743</v>
+        <v>1.05567276477814</v>
       </c>
       <c r="H1726" t="n">
         <v>3347467</v>
@@ -50510,7 +50510,7 @@
         <v>1.25</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.11451935768127</v>
+        <v>1.11451947689056</v>
       </c>
       <c r="H1729" t="n">
         <v>1160224</v>
@@ -50626,7 +50626,7 @@
         <v>1.30099999904633</v>
       </c>
       <c r="G1733" t="n">
-        <v>1.15999174118042</v>
+        <v>1.15999186038971</v>
       </c>
       <c r="H1733" t="n">
         <v>559044</v>
@@ -50684,7 +50684,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.21259701251984</v>
+        <v>1.21259713172913</v>
       </c>
       <c r="H1735" t="n">
         <v>845206</v>
@@ -50713,7 +50713,7 @@
         <v>1.34899997711182</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.20278918743134</v>
+        <v>1.20278930664062</v>
       </c>
       <c r="H1736" t="n">
         <v>706968</v>
@@ -50742,7 +50742,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G1737" t="n">
-        <v>1.22864627838135</v>
+        <v>1.22864615917206</v>
       </c>
       <c r="H1737" t="n">
         <v>984809</v>
@@ -51061,7 +51061,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.38200402259827</v>
+        <v>1.38200390338898</v>
       </c>
       <c r="H1748" t="n">
         <v>2114235</v>
@@ -51264,7 +51264,7 @@
         <v>1.55799996852875</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.38913679122925</v>
+        <v>1.38913691043854</v>
       </c>
       <c r="H1755" t="n">
         <v>957945</v>
@@ -51293,7 +51293,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.3864620923996</v>
+        <v>1.38646221160889</v>
       </c>
       <c r="H1756" t="n">
         <v>924887</v>
@@ -51380,7 +51380,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.341881275177</v>
+        <v>1.34188139438629</v>
       </c>
       <c r="H1759" t="n">
         <v>1487010</v>
@@ -51583,7 +51583,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1766" t="n">
-        <v>1.30621671676636</v>
+        <v>1.30621683597565</v>
       </c>
       <c r="H1766" t="n">
         <v>1297828</v>
@@ -51612,7 +51612,7 @@
         <v>1.45899999141693</v>
       </c>
       <c r="G1767" t="n">
-        <v>1.30086696147919</v>
+        <v>1.30086708068848</v>
       </c>
       <c r="H1767" t="n">
         <v>640030</v>
@@ -51757,7 +51757,7 @@
         <v>1.43599998950958</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.28035998344421</v>
+        <v>1.28035986423492</v>
       </c>
       <c r="H1772" t="n">
         <v>1237905</v>
@@ -51873,7 +51873,7 @@
         <v>1.41299998760223</v>
       </c>
       <c r="G1776" t="n">
-        <v>1.25985264778137</v>
+        <v>1.25985276699066</v>
       </c>
       <c r="H1776" t="n">
         <v>1229462</v>
@@ -52134,7 +52134,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.28214311599731</v>
+        <v>1.28214299678802</v>
       </c>
       <c r="H1785" t="n">
         <v>1173109</v>
@@ -52192,7 +52192,7 @@
         <v>1.44700002670288</v>
       </c>
       <c r="G1787" t="n">
-        <v>1.29016768932343</v>
+        <v>1.29016757011414</v>
       </c>
       <c r="H1787" t="n">
         <v>450438</v>
@@ -52250,7 +52250,7 @@
         <v>1.46099996566772</v>
       </c>
       <c r="G1789" t="n">
-        <v>1.30265009403229</v>
+        <v>1.30265021324158</v>
       </c>
       <c r="H1789" t="n">
         <v>1472347</v>
@@ -52395,7 +52395,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G1794" t="n">
-        <v>1.40875256061554</v>
+        <v>1.40875244140625</v>
       </c>
       <c r="H1794" t="n">
         <v>3294239</v>
@@ -52424,7 +52424,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G1795" t="n">
-        <v>1.52287924289703</v>
+        <v>1.52287936210632</v>
       </c>
       <c r="H1795" t="n">
         <v>10525712</v>
@@ -52627,7 +52627,7 @@
         <v>1.71599996089935</v>
       </c>
       <c r="G1802" t="n">
-        <v>1.5300121307373</v>
+        <v>1.53001224994659</v>
       </c>
       <c r="H1802" t="n">
         <v>2361997</v>
@@ -52743,7 +52743,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G1806" t="n">
-        <v>1.51663792133331</v>
+        <v>1.51663780212402</v>
       </c>
       <c r="H1806" t="n">
         <v>2307066</v>
@@ -52772,7 +52772,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1807" t="n">
-        <v>1.51217985153198</v>
+        <v>1.51217973232269</v>
       </c>
       <c r="H1807" t="n">
         <v>1991227</v>
@@ -52801,7 +52801,7 @@
         <v>1.71300005912781</v>
       </c>
       <c r="G1808" t="n">
-        <v>1.52733743190765</v>
+        <v>1.52733755111694</v>
       </c>
       <c r="H1808" t="n">
         <v>2468965</v>
@@ -52859,7 +52859,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1810" t="n">
-        <v>1.52466249465942</v>
+        <v>1.52466261386871</v>
       </c>
       <c r="H1810" t="n">
         <v>1122000</v>
@@ -52917,7 +52917,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1812" t="n">
-        <v>1.53803682327271</v>
+        <v>1.53803670406342</v>
       </c>
       <c r="H1812" t="n">
         <v>1219782</v>
@@ -53033,7 +53033,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1816" t="n">
-        <v>1.53803682327271</v>
+        <v>1.53803670406342</v>
       </c>
       <c r="H1816" t="n">
         <v>841047</v>
@@ -53062,7 +53062,7 @@
         <v>1.71800005435944</v>
       </c>
       <c r="G1817" t="n">
-        <v>1.53179538249969</v>
+        <v>1.53179550170898</v>
       </c>
       <c r="H1817" t="n">
         <v>885449</v>
@@ -53091,7 +53091,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G1818" t="n">
-        <v>1.54516971111298</v>
+        <v>1.54516959190369</v>
       </c>
       <c r="H1818" t="n">
         <v>907354</v>
@@ -53149,7 +53149,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1820" t="n">
-        <v>1.51217985153198</v>
+        <v>1.51217973232269</v>
       </c>
       <c r="H1820" t="n">
         <v>1794147</v>
@@ -53265,7 +53265,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G1824" t="n">
-        <v>1.53268694877625</v>
+        <v>1.53268706798553</v>
       </c>
       <c r="H1824" t="n">
         <v>1416185</v>
@@ -53323,7 +53323,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G1826" t="n">
-        <v>1.53625357151031</v>
+        <v>1.5362536907196</v>
       </c>
       <c r="H1826" t="n">
         <v>787792</v>
@@ -53381,7 +53381,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G1828" t="n">
-        <v>1.54784452915192</v>
+        <v>1.54784440994263</v>
       </c>
       <c r="H1828" t="n">
         <v>862127</v>
@@ -53671,7 +53671,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.73775863647461</v>
+        <v>1.73775851726532</v>
       </c>
       <c r="H1838" t="n">
         <v>12593666</v>
@@ -53758,7 +53758,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.85812675952911</v>
+        <v>1.8581268787384</v>
       </c>
       <c r="H1841" t="n">
         <v>6237145</v>
@@ -53903,7 +53903,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G1846" t="n">
-        <v>1.85099363327026</v>
+        <v>1.85099375247955</v>
       </c>
       <c r="H1846" t="n">
         <v>2999543</v>
@@ -54077,7 +54077,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1852" t="n">
-        <v>1.82781183719635</v>
+        <v>1.82781171798706</v>
       </c>
       <c r="H1852" t="n">
         <v>1528786</v>
@@ -54309,7 +54309,7 @@
         <v>1.94099998474121</v>
       </c>
       <c r="G1860" t="n">
-        <v>1.73062574863434</v>
+        <v>1.73062562942505</v>
       </c>
       <c r="H1860" t="n">
         <v>1038595</v>
@@ -54338,7 +54338,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.73865032196045</v>
+        <v>1.73865020275116</v>
       </c>
       <c r="H1861" t="n">
         <v>590577</v>
@@ -54367,7 +54367,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G1862" t="n">
-        <v>1.72705924510956</v>
+        <v>1.72705936431885</v>
       </c>
       <c r="H1862" t="n">
         <v>755989</v>
@@ -54454,7 +54454,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.73865032196045</v>
+        <v>1.73865020275116</v>
       </c>
       <c r="H1865" t="n">
         <v>2397970</v>
@@ -54483,7 +54483,7 @@
         <v>1.9210000038147</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.71279335021973</v>
+        <v>1.71279346942902</v>
       </c>
       <c r="H1866" t="n">
         <v>924918</v>
@@ -54541,7 +54541,7 @@
         <v>1.90699994564056</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.70031082630157</v>
+        <v>1.70031070709229</v>
       </c>
       <c r="H1868" t="n">
         <v>793841</v>
@@ -54715,7 +54715,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.77431488037109</v>
+        <v>1.7743147611618</v>
       </c>
       <c r="H1874" t="n">
         <v>2158685</v>
@@ -54744,7 +54744,7 @@
         <v>1.97699999809265</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.7627238035202</v>
+        <v>1.76272392272949</v>
       </c>
       <c r="H1875" t="n">
         <v>2168052</v>
@@ -54889,7 +54889,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.7689915895462</v>
+        <v>1.76899170875549</v>
       </c>
       <c r="H1880" t="n">
         <v>1326643</v>
@@ -55150,7 +55150,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.72492742538452</v>
+        <v>1.72492730617523</v>
       </c>
       <c r="H1889" t="n">
         <v>879419</v>
@@ -55237,7 +55237,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.71391129493713</v>
+        <v>1.71391141414642</v>
       </c>
       <c r="H1892" t="n">
         <v>839189</v>
@@ -55382,7 +55382,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.71299338340759</v>
+        <v>1.71299350261688</v>
       </c>
       <c r="H1897" t="n">
         <v>1165177</v>
@@ -55411,7 +55411,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.69371545314789</v>
+        <v>1.6937153339386</v>
       </c>
       <c r="H1898" t="n">
         <v>810528</v>
@@ -55556,7 +55556,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.61109507083893</v>
+        <v>1.61109519004822</v>
       </c>
       <c r="H1903" t="n">
         <v>1331788</v>
@@ -55585,7 +55585,7 @@
         <v>1.73300004005432</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.59089910984039</v>
+        <v>1.5908989906311</v>
       </c>
       <c r="H1904" t="n">
         <v>986341</v>
@@ -55904,7 +55904,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.60191512107849</v>
+        <v>1.6019150018692</v>
       </c>
       <c r="H1915" t="n">
         <v>747205</v>
@@ -55991,7 +55991,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.68269920349121</v>
+        <v>1.6826993227005</v>
       </c>
       <c r="H1918" t="n">
         <v>1045610</v>
@@ -56049,7 +56049,7 @@
         <v>1.82099997997284</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.6716833114624</v>
+        <v>1.67168319225311</v>
       </c>
       <c r="H1920" t="n">
         <v>941115</v>
@@ -56165,7 +56165,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G1924" t="n">
-        <v>1.64230728149414</v>
+        <v>1.64230716228485</v>
       </c>
       <c r="H1924" t="n">
         <v>7108733</v>
@@ -56281,7 +56281,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.646897315979</v>
+        <v>1.64689719676971</v>
       </c>
       <c r="H1928" t="n">
         <v>2008268</v>
@@ -56426,7 +56426,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.61201322078705</v>
+        <v>1.61201310157776</v>
       </c>
       <c r="H1933" t="n">
         <v>3043638</v>
@@ -56629,7 +56629,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1940" t="n">
-        <v>1.60191512107849</v>
+        <v>1.6019150018692</v>
       </c>
       <c r="H1940" t="n">
         <v>547439</v>
@@ -56890,7 +56890,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1949" t="n">
-        <v>1.55601489543915</v>
+        <v>1.55601501464844</v>
       </c>
       <c r="H1949" t="n">
         <v>949733</v>
@@ -56948,7 +56948,7 @@
         <v>1.72300004959106</v>
       </c>
       <c r="G1951" t="n">
-        <v>1.58171892166138</v>
+        <v>1.58171904087067</v>
       </c>
       <c r="H1951" t="n">
         <v>729850</v>
@@ -57006,7 +57006,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G1953" t="n">
-        <v>1.72859954833984</v>
+        <v>1.72859942913055</v>
       </c>
       <c r="H1953" t="n">
         <v>2445356</v>
@@ -57035,7 +57035,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1954" t="n">
-        <v>1.66158509254456</v>
+        <v>1.66158521175385</v>
       </c>
       <c r="H1954" t="n">
         <v>1777205</v>
@@ -57064,7 +57064,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.67351925373077</v>
+        <v>1.67351913452148</v>
       </c>
       <c r="H1955" t="n">
         <v>1301065</v>
@@ -57151,7 +57151,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.65056920051575</v>
+        <v>1.65056908130646</v>
       </c>
       <c r="H1958" t="n">
         <v>673614</v>
@@ -57238,7 +57238,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G1961" t="n">
-        <v>1.6771913766861</v>
+        <v>1.67719125747681</v>
       </c>
       <c r="H1961" t="n">
         <v>962261</v>
@@ -57296,7 +57296,7 @@
         <v>1.79799997806549</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.65056920051575</v>
+        <v>1.65056908130646</v>
       </c>
       <c r="H1963" t="n">
         <v>1659227</v>
@@ -57383,7 +57383,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.646897315979</v>
+        <v>1.64689719676971</v>
       </c>
       <c r="H1966" t="n">
         <v>1822285</v>
@@ -57470,7 +57470,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.55509686470032</v>
+        <v>1.55509698390961</v>
       </c>
       <c r="H1969" t="n">
         <v>2066329</v>
@@ -57789,7 +57789,7 @@
         <v>1.69900000095367</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.55968689918518</v>
+        <v>1.55968701839447</v>
       </c>
       <c r="H1980" t="n">
         <v>1064193</v>
@@ -57847,7 +57847,7 @@
         <v>1.67299997806549</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.53581893444061</v>
+        <v>1.53581881523132</v>
       </c>
       <c r="H1982" t="n">
         <v>569794</v>
@@ -57905,7 +57905,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.51929485797882</v>
+        <v>1.51929473876953</v>
       </c>
       <c r="H1984" t="n">
         <v>1206606</v>
@@ -58050,7 +58050,7 @@
         <v>1.62600004673004</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.49267280101776</v>
+        <v>1.49267268180847</v>
       </c>
       <c r="H1989" t="n">
         <v>850818</v>
@@ -58108,7 +58108,7 @@
         <v>1.61099994182587</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.47890245914459</v>
+        <v>1.47890257835388</v>
       </c>
       <c r="H1991" t="n">
         <v>624244</v>
@@ -58311,7 +58311,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G1998" t="n">
-        <v>1.65883123874664</v>
+        <v>1.65883135795593</v>
       </c>
       <c r="H1998" t="n">
         <v>1250666</v>
@@ -58340,7 +58340,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.57988286018372</v>
+        <v>1.57988297939301</v>
       </c>
       <c r="H1999" t="n">
         <v>1927114</v>
@@ -58514,7 +58514,7 @@
         <v>1.81099998950958</v>
       </c>
       <c r="G2005" t="n">
-        <v>1.66250312328339</v>
+        <v>1.66250324249268</v>
       </c>
       <c r="H2005" t="n">
         <v>1505682</v>
@@ -58688,7 +58688,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G2011" t="n">
-        <v>1.70932126045227</v>
+        <v>1.70932137966156</v>
       </c>
       <c r="H2011" t="n">
         <v>599174</v>
@@ -58891,7 +58891,7 @@
         <v>1.87899994850159</v>
       </c>
       <c r="G2018" t="n">
-        <v>1.72492742538452</v>
+        <v>1.72492730617523</v>
       </c>
       <c r="H2018" t="n">
         <v>1214996</v>
@@ -58920,7 +58920,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G2019" t="n">
-        <v>1.70564937591553</v>
+        <v>1.70564949512482</v>
       </c>
       <c r="H2019" t="n">
         <v>710740</v>
@@ -59036,7 +59036,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G2023" t="n">
-        <v>1.74512362480164</v>
+        <v>1.74512350559235</v>
       </c>
       <c r="H2023" t="n">
         <v>968406</v>
@@ -59094,7 +59094,7 @@
         <v>1.89300000667572</v>
       </c>
       <c r="G2025" t="n">
-        <v>1.73777937889099</v>
+        <v>1.73777949810028</v>
       </c>
       <c r="H2025" t="n">
         <v>630296</v>
@@ -59239,7 +59239,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2030" t="n">
-        <v>1.69830548763275</v>
+        <v>1.69830536842346</v>
       </c>
       <c r="H2030" t="n">
         <v>894590</v>
@@ -59268,7 +59268,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.70932126045227</v>
+        <v>1.70932137966156</v>
       </c>
       <c r="H2031" t="n">
         <v>1260256</v>
@@ -59297,7 +59297,7 @@
         <v>1.83700001239777</v>
       </c>
       <c r="G2032" t="n">
-        <v>1.68637132644653</v>
+        <v>1.68637144565582</v>
       </c>
       <c r="H2032" t="n">
         <v>526709</v>
@@ -59413,7 +59413,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G2036" t="n">
-        <v>1.6771913766861</v>
+        <v>1.67719125747681</v>
       </c>
       <c r="H2036" t="n">
         <v>506512</v>
@@ -59442,7 +59442,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G2037" t="n">
-        <v>1.69279718399048</v>
+        <v>1.69279730319977</v>
       </c>
       <c r="H2037" t="n">
         <v>831373</v>
@@ -59529,7 +59529,7 @@
         <v>1.84399998188019</v>
       </c>
       <c r="G2040" t="n">
-        <v>1.69279718399048</v>
+        <v>1.69279730319977</v>
       </c>
       <c r="H2040" t="n">
         <v>1407839</v>
@@ -59616,7 +59616,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G2043" t="n">
-        <v>1.69738733768463</v>
+        <v>1.69738721847534</v>
       </c>
       <c r="H2043" t="n">
         <v>742104</v>
@@ -59703,7 +59703,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G2046" t="n">
-        <v>1.72859954833984</v>
+        <v>1.72859942913055</v>
       </c>
       <c r="H2046" t="n">
         <v>2737868</v>
@@ -59732,7 +59732,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G2047" t="n">
-        <v>1.70932126045227</v>
+        <v>1.70932137966156</v>
       </c>
       <c r="H2047" t="n">
         <v>2393660</v>
@@ -59761,7 +59761,7 @@
         <v>1.96099996566772</v>
       </c>
       <c r="G2048" t="n">
-        <v>1.80020368099213</v>
+        <v>1.80020356178284</v>
       </c>
       <c r="H2048" t="n">
         <v>5763086</v>
@@ -60312,7 +60312,7 @@
         <v>1.88300001621246</v>
       </c>
       <c r="G2067" t="n">
-        <v>1.72859954833984</v>
+        <v>1.72859942913055</v>
       </c>
       <c r="H2067" t="n">
         <v>2208776</v>
@@ -60341,7 +60341,7 @@
         <v>1.90100002288818</v>
       </c>
       <c r="G2068" t="n">
-        <v>1.74512362480164</v>
+        <v>1.74512350559235</v>
       </c>
       <c r="H2068" t="n">
         <v>1665109</v>
@@ -60660,7 +60660,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.7992856502533</v>
+        <v>1.79928576946259</v>
       </c>
       <c r="H2079" t="n">
         <v>2811370</v>
@@ -60689,7 +60689,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.83416974544525</v>
+        <v>1.83416986465454</v>
       </c>
       <c r="H2080" t="n">
         <v>4389358</v>
@@ -61008,7 +61008,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G2091" t="n">
-        <v>2.19769883155823</v>
+        <v>2.19769906997681</v>
       </c>
       <c r="H2091" t="n">
         <v>3673941</v>
@@ -61037,7 +61037,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G2092" t="n">
-        <v>2.21605920791626</v>
+        <v>2.21605896949768</v>
       </c>
       <c r="H2092" t="n">
         <v>2551915</v>
@@ -61211,7 +61211,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G2098" t="n">
-        <v>2.06183433532715</v>
+        <v>2.06183457374573</v>
       </c>
       <c r="H2098" t="n">
         <v>1874711</v>
@@ -61269,7 +61269,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G2100" t="n">
-        <v>2.02327847480774</v>
+        <v>2.02327823638916</v>
       </c>
       <c r="H2100" t="n">
         <v>2692199</v>
@@ -61356,7 +61356,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G2103" t="n">
-        <v>2.06183433532715</v>
+        <v>2.06183457374573</v>
       </c>
       <c r="H2103" t="n">
         <v>2425015</v>
@@ -61472,7 +61472,7 @@
         <v>2.25799989700317</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.07285046577454</v>
+        <v>2.07285022735596</v>
       </c>
       <c r="H2107" t="n">
         <v>3238471</v>
@@ -61501,7 +61501,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G2108" t="n">
-        <v>2.09488248825073</v>
+        <v>2.09488272666931</v>
       </c>
       <c r="H2108" t="n">
         <v>2734136</v>
@@ -61588,7 +61588,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G2111" t="n">
-        <v>2.07101464271545</v>
+        <v>2.07101440429688</v>
       </c>
       <c r="H2111" t="n">
         <v>1685946</v>
@@ -61617,7 +61617,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G2112" t="n">
-        <v>2.08753848075867</v>
+        <v>2.08753871917725</v>
       </c>
       <c r="H2112" t="n">
         <v>1754792</v>
@@ -61646,7 +61646,7 @@
         <v>2.24600005149841</v>
       </c>
       <c r="G2113" t="n">
-        <v>2.06183433532715</v>
+        <v>2.06183457374573</v>
       </c>
       <c r="H2113" t="n">
         <v>2063800</v>
@@ -61907,7 +61907,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G2122" t="n">
-        <v>2.13527464866638</v>
+        <v>2.13527488708496</v>
       </c>
       <c r="H2122" t="n">
         <v>1206905</v>
@@ -61936,7 +61936,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G2123" t="n">
-        <v>2.16465067863464</v>
+        <v>2.16465091705322</v>
       </c>
       <c r="H2123" t="n">
         <v>942377</v>
@@ -61965,7 +61965,7 @@
         <v>2.37400007247925</v>
       </c>
       <c r="G2124" t="n">
-        <v>2.17933893203735</v>
+        <v>2.17933869361877</v>
       </c>
       <c r="H2124" t="n">
         <v>1843573</v>
@@ -62168,7 +62168,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G2131" t="n">
-        <v>2.18117451667786</v>
+        <v>2.18117475509644</v>
       </c>
       <c r="H2131" t="n">
         <v>893911</v>
@@ -62197,7 +62197,7 @@
         <v>2.39400005340576</v>
       </c>
       <c r="G2132" t="n">
-        <v>2.19769883155823</v>
+        <v>2.19769906997681</v>
       </c>
       <c r="H2132" t="n">
         <v>1828378</v>
@@ -80212,6 +80212,35 @@
         <v>3160956</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>2.09200000762939</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>2.09400010108948</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>2.04800009727478</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>2.05200004577637</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>2.05200004577637</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>2398140</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
